--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4220 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000523.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>红棉股份</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9.975099999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1105937043</v>
+      </c>
+      <c r="H2" t="n">
+        <v>136884973.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>108158073.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>245043047.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-28726900</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6479293174.94</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000636.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.1974</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27408111647</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3559826480.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3843313035.69</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7403139516.19</v>
+      </c>
+      <c r="K3" t="n">
+        <v>283486555.19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>67587159174.1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000759.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-7.7491</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1871639240</v>
+      </c>
+      <c r="H4" t="n">
+        <v>222778423.74</v>
+      </c>
+      <c r="I4" t="n">
+        <v>181391518.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>404169942.14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-41386905.34</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4917795187.5</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.0146</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2490848829</v>
+      </c>
+      <c r="H5" t="n">
+        <v>317912689.53</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591301672.08</v>
+      </c>
+      <c r="J5" t="n">
+        <v>909214361.61</v>
+      </c>
+      <c r="K5" t="n">
+        <v>273388982.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13463314939.21</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000911.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>*ST广糖</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.3645</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>498619628</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59352877.49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>69423115.90000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>128775993.39</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10070238.41</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M6" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2169733413.56</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000930.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中粮科技</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.034</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>810369964</v>
+      </c>
+      <c r="H7" t="n">
+        <v>104969915.88</v>
+      </c>
+      <c r="I7" t="n">
+        <v>64853095.17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>169823011.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-40116820.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9819842695.43</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.0304</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1690317684</v>
+      </c>
+      <c r="H8" t="n">
+        <v>103322799.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>144240313.82</v>
+      </c>
+      <c r="J8" t="n">
+        <v>247563113.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40917514.26</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5083800174.18</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000980.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.9057</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2402209660</v>
+      </c>
+      <c r="H9" t="n">
+        <v>309520453.46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>359176595.08</v>
+      </c>
+      <c r="J9" t="n">
+        <v>668697048.54</v>
+      </c>
+      <c r="K9" t="n">
+        <v>49656141.62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11748992004.87</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.0144</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1511076875</v>
+      </c>
+      <c r="H10" t="n">
+        <v>136982032.92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>266721947.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>403703980.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>129739914.33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6992918717.85</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001232.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>嘉立创</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>197.68</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.329700000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3589415560</v>
+      </c>
+      <c r="H11" t="n">
+        <v>479935368.67</v>
+      </c>
+      <c r="I11" t="n">
+        <v>916035943</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1395971311.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>436100574.33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8738750606.32</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001896.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>豫能控股</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.9915</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2170406142</v>
+      </c>
+      <c r="H12" t="n">
+        <v>127972344.84</v>
+      </c>
+      <c r="I12" t="n">
+        <v>479114083.48</v>
+      </c>
+      <c r="J12" t="n">
+        <v>607086428.3200001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>351141738.64</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="N12" t="n">
+        <v>19819899476.7</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002161.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>远望谷</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-9.950200000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>794546822</v>
+      </c>
+      <c r="H13" t="n">
+        <v>127150043.36</v>
+      </c>
+      <c r="I13" t="n">
+        <v>75612016</v>
+      </c>
+      <c r="J13" t="n">
+        <v>202762059.36</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-51538027.36</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5354771694</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002172.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.0877</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1165320728</v>
+      </c>
+      <c r="H14" t="n">
+        <v>111622035.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>208110093</v>
+      </c>
+      <c r="J14" t="n">
+        <v>319732128.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>96488057.59999999</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3841006464.6</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2902361269</v>
+      </c>
+      <c r="H15" t="n">
+        <v>415610480.12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>681094260.1900001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1096704740.31</v>
+      </c>
+      <c r="K15" t="n">
+        <v>265483780.07</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="N15" t="n">
+        <v>19899177606</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002560.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>通达股份</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0291</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1128324626</v>
+      </c>
+      <c r="H16" t="n">
+        <v>138666262.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>235833322.52</v>
+      </c>
+      <c r="J16" t="n">
+        <v>374499584.92</v>
+      </c>
+      <c r="K16" t="n">
+        <v>97167060.12</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4794429068.6</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0117</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2637352990</v>
+      </c>
+      <c r="H17" t="n">
+        <v>316884005.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>597509024.21</v>
+      </c>
+      <c r="J17" t="n">
+        <v>914393029.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>280625018.47</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10962804849.03</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002585.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.0402</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2144036635</v>
+      </c>
+      <c r="H18" t="n">
+        <v>186320299.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>406040406.53</v>
+      </c>
+      <c r="J18" t="n">
+        <v>592360706.13</v>
+      </c>
+      <c r="K18" t="n">
+        <v>219720106.93</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9717045996.48</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002743.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST富煌</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.4961</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G19" t="n">
+        <v>509443803</v>
+      </c>
+      <c r="H19" t="n">
+        <v>68754100.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>65878752.45</v>
+      </c>
+      <c r="J19" t="n">
+        <v>134632852.65</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2875347.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2351028990.98</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002790.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>瑞尔特</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-9.9893</v>
+      </c>
+      <c r="F20" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="G20" t="n">
+        <v>694541217</v>
+      </c>
+      <c r="H20" t="n">
+        <v>154311757</v>
+      </c>
+      <c r="I20" t="n">
+        <v>80810651.23999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>235122408.24</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-73501105.76000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2184645050</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002848.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>高斯贝尔</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.3465</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="G21" t="n">
+        <v>792106788</v>
+      </c>
+      <c r="H21" t="n">
+        <v>97674915.12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>73101805</v>
+      </c>
+      <c r="J21" t="n">
+        <v>170776720.12</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-24573110.12</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2436649282.53</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002897.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>意华股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1621049895</v>
+      </c>
+      <c r="H22" t="n">
+        <v>237138509.86</v>
+      </c>
+      <c r="I22" t="n">
+        <v>559054639.66</v>
+      </c>
+      <c r="J22" t="n">
+        <v>796193149.52</v>
+      </c>
+      <c r="K22" t="n">
+        <v>321916129.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="M22" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13161331041.32</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002909.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>集泰股份</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10.0134</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="G23" t="n">
+        <v>665584836</v>
+      </c>
+      <c r="H23" t="n">
+        <v>72796722.73</v>
+      </c>
+      <c r="I23" t="n">
+        <v>79308214.26000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>152104936.99</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6511491.53</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2564080561.42</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>300010.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST豆神</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-16.8519</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1229039787</v>
+      </c>
+      <c r="H24" t="n">
+        <v>115949200.03</v>
+      </c>
+      <c r="I24" t="n">
+        <v>73542633.98</v>
+      </c>
+      <c r="J24" t="n">
+        <v>189491834.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-42406566.05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7349117024.57</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>300112.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>万讯自控</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.8189</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="G25" t="n">
+        <v>937814406</v>
+      </c>
+      <c r="H25" t="n">
+        <v>96763294.06999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>188393602.67</v>
+      </c>
+      <c r="J25" t="n">
+        <v>285156896.74</v>
+      </c>
+      <c r="K25" t="n">
+        <v>91630308.59999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2821324661.06</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300430.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>*ST益通</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14</v>
+      </c>
+      <c r="G26" t="n">
+        <v>187001947</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29899099</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31145953.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>61045052.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1246854.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M26" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1449986486.22</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300903.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>科翔股份</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3508513363</v>
+      </c>
+      <c r="H27" t="n">
+        <v>388113636.31</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1277195928.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1665309564.61</v>
+      </c>
+      <c r="K27" t="n">
+        <v>889082291.99</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="M27" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="N27" t="n">
+        <v>38054426275.2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>301132.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>满坤科技</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.0041</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>898002257</v>
+      </c>
+      <c r="H28" t="n">
+        <v>177612826.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>229727464.79</v>
+      </c>
+      <c r="J28" t="n">
+        <v>407340291.59</v>
+      </c>
+      <c r="K28" t="n">
+        <v>52114637.99</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5530017110.54</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="G29" t="n">
+        <v>749438168</v>
+      </c>
+      <c r="H29" t="n">
+        <v>69439861.23999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>130815820.86</v>
+      </c>
+      <c r="J29" t="n">
+        <v>200255682.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>61375959.62</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2079620974.8</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301528.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>多浦乐</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>73</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19.3786</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G30" t="n">
+        <v>406250176</v>
+      </c>
+      <c r="H30" t="n">
+        <v>119778175.23</v>
+      </c>
+      <c r="I30" t="n">
+        <v>154259341.45</v>
+      </c>
+      <c r="J30" t="n">
+        <v>274037516.68</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34481166.22</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="M30" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3376712309</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>600088.SH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>中视传媒</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="G31" t="n">
+        <v>856857044</v>
+      </c>
+      <c r="H31" t="n">
+        <v>108871023.03</v>
+      </c>
+      <c r="I31" t="n">
+        <v>110636637.85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>219507660.88</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1765614.82</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M31" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5862192336</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>600108.SH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>亚盛集团</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-9.9366</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7297120008</v>
+      </c>
+      <c r="H32" t="n">
+        <v>558581433.24</v>
+      </c>
+      <c r="I32" t="n">
+        <v>531608882.28</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1090190315.52</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-26972550.96</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M32" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8293858415.46</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.5756</v>
+      </c>
+      <c r="F33" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3459998607</v>
+      </c>
+      <c r="H33" t="n">
+        <v>324108213.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>347985398.44</v>
+      </c>
+      <c r="J33" t="n">
+        <v>672093611.74</v>
+      </c>
+      <c r="K33" t="n">
+        <v>23877185.14</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9094068199.059999</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>600172.SH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F34" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4892615601</v>
+      </c>
+      <c r="H34" t="n">
+        <v>252365129.92</v>
+      </c>
+      <c r="I34" t="n">
+        <v>837514315.8200001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1089879445.74</v>
+      </c>
+      <c r="K34" t="n">
+        <v>585149185.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M34" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="N34" t="n">
+        <v>21229125390.24</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>600180.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>*ST瑞茂</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.883699999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G35" t="n">
+        <v>216665527</v>
+      </c>
+      <c r="H35" t="n">
+        <v>29735824.85</v>
+      </c>
+      <c r="I35" t="n">
+        <v>19443683</v>
+      </c>
+      <c r="J35" t="n">
+        <v>49179507.85</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-10292141.85</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2053725906.96</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600237.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>铜峰电子</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.7245</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2403805273</v>
+      </c>
+      <c r="H36" t="n">
+        <v>355827677.56</v>
+      </c>
+      <c r="I36" t="n">
+        <v>341877025.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>697704703.26</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-13950651.86</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M36" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6146219422.8</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-10.0273</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>987089999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>150129133.09</v>
+      </c>
+      <c r="I37" t="n">
+        <v>131196688.74</v>
+      </c>
+      <c r="J37" t="n">
+        <v>281325821.83</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-18932444.35</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="M37" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5209406529.6</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600359.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>新农开发</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-9.9794</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>210366100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>63327250</v>
+      </c>
+      <c r="I38" t="n">
+        <v>45192000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>108519250</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-18135250</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3338237175</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-3.8566</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1006295486</v>
+      </c>
+      <c r="H39" t="n">
+        <v>134545308.15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>103391669.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>237936977.75</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-31153638.55</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4157533380</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600488.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0935</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="G40" t="n">
+        <v>672027089</v>
+      </c>
+      <c r="H40" t="n">
+        <v>36808572.18</v>
+      </c>
+      <c r="I40" t="n">
+        <v>278067536</v>
+      </c>
+      <c r="J40" t="n">
+        <v>314876108.18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>241258963.82</v>
+      </c>
+      <c r="L40" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6431212545.2</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600491.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ST龙元</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8.5227</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="G41" t="n">
+        <v>234793125</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23366571</v>
+      </c>
+      <c r="I41" t="n">
+        <v>22240409.01</v>
+      </c>
+      <c r="J41" t="n">
+        <v>45606980.01</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-1126161.99</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M41" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2921837694.05</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600491.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ST龙元</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.5227</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="G42" t="n">
+        <v>639853586</v>
+      </c>
+      <c r="H42" t="n">
+        <v>64380673.75</v>
+      </c>
+      <c r="I42" t="n">
+        <v>58696282.67</v>
+      </c>
+      <c r="J42" t="n">
+        <v>123076956.42</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-5684391.08</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="M42" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2921837694.05</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600540.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>新赛股份</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-4.5763</v>
+      </c>
+      <c r="F43" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2797080667</v>
+      </c>
+      <c r="H43" t="n">
+        <v>359593285.18</v>
+      </c>
+      <c r="I43" t="n">
+        <v>347775532.02</v>
+      </c>
+      <c r="J43" t="n">
+        <v>707368817.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-11817753.16</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3273152284.8</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600697.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>欧亚集团</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0452</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G44" t="n">
+        <v>123196762</v>
+      </c>
+      <c r="H44" t="n">
+        <v>15303051</v>
+      </c>
+      <c r="I44" t="n">
+        <v>37044563</v>
+      </c>
+      <c r="J44" t="n">
+        <v>52347614</v>
+      </c>
+      <c r="K44" t="n">
+        <v>21741512</v>
+      </c>
+      <c r="L44" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="M44" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1889372342.4</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600706.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>曲江文旅</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-9.9894</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="G45" t="n">
+        <v>316875735</v>
+      </c>
+      <c r="H45" t="n">
+        <v>71122149</v>
+      </c>
+      <c r="I45" t="n">
+        <v>49509150.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>120631299.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-21612998.8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="M45" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2151635666.95</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600712.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="G46" t="n">
+        <v>502617195</v>
+      </c>
+      <c r="H46" t="n">
+        <v>85291706</v>
+      </c>
+      <c r="I46" t="n">
+        <v>82211827</v>
+      </c>
+      <c r="J46" t="n">
+        <v>167503533</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-3079879</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M46" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3248049677.13</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600737.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>中粮糖业</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-8.8217</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9191335803</v>
+      </c>
+      <c r="H47" t="n">
+        <v>699852438.8200001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>759559797.45</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1459412236.27</v>
+      </c>
+      <c r="K47" t="n">
+        <v>59707358.63</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M47" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="N47" t="n">
+        <v>31612176809.84</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600865.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>百大集团</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-5.3829</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="G48" t="n">
+        <v>935673479</v>
+      </c>
+      <c r="H48" t="n">
+        <v>64066190.99</v>
+      </c>
+      <c r="I48" t="n">
+        <v>76018719</v>
+      </c>
+      <c r="J48" t="n">
+        <v>140084909.99</v>
+      </c>
+      <c r="K48" t="n">
+        <v>11952528.01</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M48" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4695479143.68</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10.0306</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1852252936</v>
+      </c>
+      <c r="H49" t="n">
+        <v>114044989</v>
+      </c>
+      <c r="I49" t="n">
+        <v>177487006</v>
+      </c>
+      <c r="J49" t="n">
+        <v>291531995</v>
+      </c>
+      <c r="K49" t="n">
+        <v>63442017</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M49" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="N49" t="n">
+        <v>11981340000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0306</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3623223432</v>
+      </c>
+      <c r="H50" t="n">
+        <v>215760145.41</v>
+      </c>
+      <c r="I50" t="n">
+        <v>234496315.76</v>
+      </c>
+      <c r="J50" t="n">
+        <v>450256461.17</v>
+      </c>
+      <c r="K50" t="n">
+        <v>18736170.35</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M50" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="N50" t="n">
+        <v>11981340000</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>601118.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-8.7021</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4481766508</v>
+      </c>
+      <c r="H51" t="n">
+        <v>430563112.27</v>
+      </c>
+      <c r="I51" t="n">
+        <v>458322090.78</v>
+      </c>
+      <c r="J51" t="n">
+        <v>888885203.05</v>
+      </c>
+      <c r="K51" t="n">
+        <v>27758978.51</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M51" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="N51" t="n">
+        <v>26489658063.43</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>601123.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0262</v>
+      </c>
+      <c r="F52" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="G52" t="n">
+        <v>464467419</v>
+      </c>
+      <c r="H52" t="n">
+        <v>32982503.68</v>
+      </c>
+      <c r="I52" t="n">
+        <v>104347260.08</v>
+      </c>
+      <c r="J52" t="n">
+        <v>137329763.76</v>
+      </c>
+      <c r="K52" t="n">
+        <v>71364756.40000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="M52" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1608956451.82</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603020.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>爱普股份</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.0493</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G53" t="n">
+        <v>173887946</v>
+      </c>
+      <c r="H53" t="n">
+        <v>14859537</v>
+      </c>
+      <c r="I53" t="n">
+        <v>37274776</v>
+      </c>
+      <c r="J53" t="n">
+        <v>52134313</v>
+      </c>
+      <c r="K53" t="n">
+        <v>22415239</v>
+      </c>
+      <c r="L53" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="M53" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4195873935.58</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-2.6029</v>
+      </c>
+      <c r="F54" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="G54" t="n">
+        <v>603393303</v>
+      </c>
+      <c r="H54" t="n">
+        <v>129160328.56</v>
+      </c>
+      <c r="I54" t="n">
+        <v>116196554</v>
+      </c>
+      <c r="J54" t="n">
+        <v>245356882.56</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-12963774.56</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="M54" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1775581082</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603439.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>三力制药</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.9681</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G55" t="n">
+        <v>682522985</v>
+      </c>
+      <c r="H55" t="n">
+        <v>163424522.75</v>
+      </c>
+      <c r="I55" t="n">
+        <v>146198022.82</v>
+      </c>
+      <c r="J55" t="n">
+        <v>309622545.57</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-17226499.93</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="M55" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5568956578.64</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603618.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>杭电股份</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.8669</v>
+      </c>
+      <c r="F56" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4410025521</v>
+      </c>
+      <c r="H56" t="n">
+        <v>256144385.95</v>
+      </c>
+      <c r="I56" t="n">
+        <v>393640052.38</v>
+      </c>
+      <c r="J56" t="n">
+        <v>649784438.33</v>
+      </c>
+      <c r="K56" t="n">
+        <v>137495666.43</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M56" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="N56" t="n">
+        <v>28671346795.52</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603936.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>博敏电子</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6.7529</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3285731044</v>
+      </c>
+      <c r="H57" t="n">
+        <v>677953324.61</v>
+      </c>
+      <c r="I57" t="n">
+        <v>583385868.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1261339192.94</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-94567456.28</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="M57" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="N57" t="n">
+        <v>14051571509.16</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603989.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>艾华集团</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4.8138</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1453470550</v>
+      </c>
+      <c r="H58" t="n">
+        <v>195860560.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>222152300.49</v>
+      </c>
+      <c r="J58" t="n">
+        <v>418012861.39</v>
+      </c>
+      <c r="K58" t="n">
+        <v>26291739.59</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M58" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="N58" t="n">
+        <v>13805758753.2</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9.997</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="G59" t="n">
+        <v>869352404</v>
+      </c>
+      <c r="H59" t="n">
+        <v>110504956.05</v>
+      </c>
+      <c r="I59" t="n">
+        <v>136070371.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>246575327.65</v>
+      </c>
+      <c r="K59" t="n">
+        <v>25565415.55</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M59" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5236776396.8</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>605069.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G60" t="n">
+        <v>148970006</v>
+      </c>
+      <c r="H60" t="n">
+        <v>35285132</v>
+      </c>
+      <c r="I60" t="n">
+        <v>32161594</v>
+      </c>
+      <c r="J60" t="n">
+        <v>67446726</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-3123538</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2677976891.7</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10.0161</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34552560</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16470720</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4811520</v>
+      </c>
+      <c r="J61" t="n">
+        <v>21282240</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-11659200</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-33.74</v>
+      </c>
+      <c r="M61" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="N61" t="n">
+        <v>7466666676</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19.979</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G62" t="n">
+        <v>32153200</v>
+      </c>
+      <c r="H62" t="n">
+        <v>10645233.34</v>
+      </c>
+      <c r="I62" t="n">
+        <v>24609088</v>
+      </c>
+      <c r="J62" t="n">
+        <v>35254321.34</v>
+      </c>
+      <c r="K62" t="n">
+        <v>13963854.66</v>
+      </c>
+      <c r="L62" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="M62" t="n">
+        <v>109.64</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1827608160</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-19.8675</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G63" t="n">
+        <v>17830900</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4079644.33</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2935811.44</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7015455.77</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-1143832.89</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="M63" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="N63" t="n">
+        <v>245226667.07</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="G64" t="n">
+        <v>648451700</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35874904.38</v>
+      </c>
+      <c r="I64" t="n">
+        <v>109123799.7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>144998704.08</v>
+      </c>
+      <c r="K64" t="n">
+        <v>73248895.31999999</v>
+      </c>
+      <c r="L64" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5369660390.4</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688244.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>永信至诚</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="E65" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G65" t="n">
+        <v>119391100</v>
+      </c>
+      <c r="H65" t="n">
+        <v>18456798.68</v>
+      </c>
+      <c r="I65" t="n">
+        <v>37131276.53</v>
+      </c>
+      <c r="J65" t="n">
+        <v>55588075.21</v>
+      </c>
+      <c r="K65" t="n">
+        <v>18674477.85</v>
+      </c>
+      <c r="L65" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="M65" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2481807372.36</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688260.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>昀冢科技</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8.7079</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2493247300</v>
+      </c>
+      <c r="H66" t="n">
+        <v>238156856.45</v>
+      </c>
+      <c r="I66" t="n">
+        <v>420720596.8</v>
+      </c>
+      <c r="J66" t="n">
+        <v>658877453.25</v>
+      </c>
+      <c r="K66" t="n">
+        <v>182563740.35</v>
+      </c>
+      <c r="L66" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="M66" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="N66" t="n">
+        <v>14336400000</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.0566</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3692995200</v>
+      </c>
+      <c r="H67" t="n">
+        <v>393991004.7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>190975183.35</v>
+      </c>
+      <c r="J67" t="n">
+        <v>584966188.05</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-203015821.35</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="M67" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="N67" t="n">
+        <v>57701430746.7</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>688622.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>*ST禾信</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.6284</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G68" t="n">
+        <v>123294300</v>
+      </c>
+      <c r="H68" t="n">
+        <v>27261196.17</v>
+      </c>
+      <c r="I68" t="n">
+        <v>21697738.03</v>
+      </c>
+      <c r="J68" t="n">
+        <v>48958934.2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-5563458.14</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-4.51</v>
+      </c>
+      <c r="M68" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="N68" t="n">
+        <v>8233896128.85</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>688813.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>泰金新能</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>12.4812</v>
+      </c>
+      <c r="F69" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1369550900</v>
+      </c>
+      <c r="H69" t="n">
+        <v>231480522.14</v>
+      </c>
+      <c r="I69" t="n">
+        <v>379700540.45</v>
+      </c>
+      <c r="J69" t="n">
+        <v>611181062.59</v>
+      </c>
+      <c r="K69" t="n">
+        <v>148220018.31</v>
+      </c>
+      <c r="L69" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="M69" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4279953684.8</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>688835.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>高凯技术</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20.0007</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1128312900</v>
+      </c>
+      <c r="H70" t="n">
+        <v>287614393.09</v>
+      </c>
+      <c r="I70" t="n">
+        <v>200598835.34</v>
+      </c>
+      <c r="J70" t="n">
+        <v>488213228.43</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-87015557.75</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="M70" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="N70" t="n">
+        <v>6093323281.85</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>688835.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>高凯技术</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>324.41</v>
+      </c>
+      <c r="E71" t="n">
+        <v>20.0007</v>
+      </c>
+      <c r="F71" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2223104900</v>
+      </c>
+      <c r="H71" t="n">
+        <v>409804867.19</v>
+      </c>
+      <c r="I71" t="n">
+        <v>449467133.35</v>
+      </c>
+      <c r="J71" t="n">
+        <v>859272000.54</v>
+      </c>
+      <c r="K71" t="n">
+        <v>39662266.16</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M71" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="N71" t="n">
+        <v>6093323281.85</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="E72" t="n">
+        <v>8.5122</v>
+      </c>
+      <c r="F72" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>388765900</v>
+      </c>
+      <c r="H72" t="n">
+        <v>48828190.51</v>
+      </c>
+      <c r="I72" t="n">
+        <v>56140384.26</v>
+      </c>
+      <c r="J72" t="n">
+        <v>104968574.77</v>
+      </c>
+      <c r="K72" t="n">
+        <v>7312193.75</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M72" t="n">
+        <v>27</v>
+      </c>
+      <c r="N72" t="n">
+        <v>907515000</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920117.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>龙鑫智能</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.1622</v>
+      </c>
+      <c r="F73" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="G73" t="n">
+        <v>149878200</v>
+      </c>
+      <c r="H73" t="n">
+        <v>18900752.53</v>
+      </c>
+      <c r="I73" t="n">
+        <v>25383620.69</v>
+      </c>
+      <c r="J73" t="n">
+        <v>44284373.22</v>
+      </c>
+      <c r="K73" t="n">
+        <v>6482868.16</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M73" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="N73" t="n">
+        <v>573066985.05</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-16.8675</v>
+      </c>
+      <c r="F74" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>266780100</v>
+      </c>
+      <c r="H74" t="n">
+        <v>49089459.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>24471449.81</v>
+      </c>
+      <c r="J74" t="n">
+        <v>73560909.41</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-24618009.79</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-9.23</v>
+      </c>
+      <c r="M74" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="N74" t="n">
+        <v>498460692</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>920289.BJ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>华汇智能</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3.4652</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>111084600</v>
+      </c>
+      <c r="H75" t="n">
+        <v>19772689.35</v>
+      </c>
+      <c r="I75" t="n">
+        <v>22327341.43</v>
+      </c>
+      <c r="J75" t="n">
+        <v>42100030.78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2554652.08</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="N75" t="n">
+        <v>396941966.99</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E76" t="n">
+        <v>5.7503</v>
+      </c>
+      <c r="F76" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="G76" t="n">
+        <v>231204900</v>
+      </c>
+      <c r="H76" t="n">
+        <v>24803555.23</v>
+      </c>
+      <c r="I76" t="n">
+        <v>58250660.53</v>
+      </c>
+      <c r="J76" t="n">
+        <v>83054215.76000001</v>
+      </c>
+      <c r="K76" t="n">
+        <v>33447105.3</v>
+      </c>
+      <c r="L76" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M76" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="N76" t="n">
+        <v>771585765</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,3615 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000428.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>华天酒店</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-10.0437</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>383983730</v>
+      </c>
+      <c r="H2" t="n">
+        <v>62449707.74</v>
+      </c>
+      <c r="I2" t="n">
+        <v>79857785.62</v>
+      </c>
+      <c r="J2" t="n">
+        <v>142307493.36</v>
+      </c>
+      <c r="K2" t="n">
+        <v>17408077.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M2" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4197975120</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000523.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>红棉股份</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-9.972300000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>815487326</v>
+      </c>
+      <c r="H3" t="n">
+        <v>92160071.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>84243032.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>176403104.52</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-7917038.92</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="M3" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5833158675.5</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000523.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>红棉股份</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-9.972300000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3403651546</v>
+      </c>
+      <c r="H4" t="n">
+        <v>423639716.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>308250561.37</v>
+      </c>
+      <c r="J4" t="n">
+        <v>731890277.95</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-115389155.21</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5833158675.5</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000759.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>588044207</v>
+      </c>
+      <c r="H5" t="n">
+        <v>84571875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>44704742.17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>129276617.17</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-39867132.83</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4426015668.75</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000759.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4879590431</v>
+      </c>
+      <c r="H6" t="n">
+        <v>375595613.56</v>
+      </c>
+      <c r="I6" t="n">
+        <v>395239146.96</v>
+      </c>
+      <c r="J6" t="n">
+        <v>770834760.52</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19643533.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4426015668.75</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.612</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5794333953</v>
+      </c>
+      <c r="H7" t="n">
+        <v>741420567.8200001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>828475349.73</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1569895917.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87054781.91</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14218878791.3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000930.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中粮科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-6.0491</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2782366969</v>
+      </c>
+      <c r="H8" t="n">
+        <v>192489374.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>254943157.65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>447432532.29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>62453783.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9225825745.99</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0368</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>716839873</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79767573.56</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76377504.02</v>
+      </c>
+      <c r="J9" t="n">
+        <v>156145077.58</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-3390069.54</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4573547670.51</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000980.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.0043</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2097820685</v>
+      </c>
+      <c r="H10" t="n">
+        <v>227966449.89</v>
+      </c>
+      <c r="I10" t="n">
+        <v>198356970.56</v>
+      </c>
+      <c r="J10" t="n">
+        <v>426323420.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-29609479.33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="N10" t="n">
+        <v>11396017996.14</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0196</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2210807016</v>
+      </c>
+      <c r="H11" t="n">
+        <v>250647795.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>316691493.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>567339288.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>66043697.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7693584444</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002059.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>云南旅游</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-9.980399999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="G12" t="n">
+        <v>584500219</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84107644</v>
+      </c>
+      <c r="I12" t="n">
+        <v>67762943</v>
+      </c>
+      <c r="J12" t="n">
+        <v>151870587</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-16344701</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4555808931.6</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002059.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>云南旅游</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-9.980399999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2083327790</v>
+      </c>
+      <c r="H13" t="n">
+        <v>210121248.87</v>
+      </c>
+      <c r="I13" t="n">
+        <v>193076750.16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>403197999.03</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-17044498.71</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4555808931.6</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002212.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2778129936</v>
+      </c>
+      <c r="H14" t="n">
+        <v>370652025.34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>367754799.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>738406825.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-2897225.43</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9066418151.91</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002212.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3712116650</v>
+      </c>
+      <c r="H15" t="n">
+        <v>394806023.36</v>
+      </c>
+      <c r="I15" t="n">
+        <v>594995548.45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>989801571.8099999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>200189525.09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9066418151.91</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002232.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>启明信息</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0131</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>279270521</v>
+      </c>
+      <c r="H16" t="n">
+        <v>44630045</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78884330</v>
+      </c>
+      <c r="J16" t="n">
+        <v>123514375</v>
+      </c>
+      <c r="K16" t="n">
+        <v>34254285</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6867699528.55</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002295.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>精艺股份</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-7.3146</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>520732205</v>
+      </c>
+      <c r="H17" t="n">
+        <v>56392201.54</v>
+      </c>
+      <c r="I17" t="n">
+        <v>52612173.99</v>
+      </c>
+      <c r="J17" t="n">
+        <v>109004375.53</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-3780027.55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2316449056.25</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.0139</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3052763081</v>
+      </c>
+      <c r="H18" t="n">
+        <v>500538433.48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>619166597.26</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1119705030.74</v>
+      </c>
+      <c r="K18" t="n">
+        <v>118628163.78</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24883495291.04</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002491.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.995100000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5840461313</v>
+      </c>
+      <c r="H19" t="n">
+        <v>350286363.77</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1185726839.03</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1536013202.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>835440475.26</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>26152901335.08</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002531.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>天顺风能</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1277484637</v>
+      </c>
+      <c r="H20" t="n">
+        <v>135888016.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>245959454.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>381847471.24</v>
+      </c>
+      <c r="K20" t="n">
+        <v>110071437.56</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13955443758.19</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002560.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>通达股份</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.9815</v>
+      </c>
+      <c r="F21" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1737855959</v>
+      </c>
+      <c r="H21" t="n">
+        <v>337409800.65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>236104941.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>573514742.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-101304859.05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="M21" t="n">
+        <v>33</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4889430965.6</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.0112</v>
+      </c>
+      <c r="F22" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3910512801</v>
+      </c>
+      <c r="H22" t="n">
+        <v>630046616.0700001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>524646790.97</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1154693407.04</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-105399825.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10851951580.2</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002585.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.0365</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2331857903</v>
+      </c>
+      <c r="H23" t="n">
+        <v>305042668.03</v>
+      </c>
+      <c r="I23" t="n">
+        <v>491669982.37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>796712650.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>186627314.34</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10692296963.28</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002815.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>崇达技术</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.5568</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7614655626</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1462368399.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1420439234.89</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2882807633.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-41929164.12</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16832809924.74</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002848.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高斯贝尔</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.3578</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="G25" t="n">
+        <v>609112355</v>
+      </c>
+      <c r="H25" t="n">
+        <v>67619379</v>
+      </c>
+      <c r="I25" t="n">
+        <v>98986594</v>
+      </c>
+      <c r="J25" t="n">
+        <v>166605973</v>
+      </c>
+      <c r="K25" t="n">
+        <v>31367215</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2469733454.73</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002897.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>意华股份</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.0427</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5204051712</v>
+      </c>
+      <c r="H26" t="n">
+        <v>719617638.76</v>
+      </c>
+      <c r="I26" t="n">
+        <v>833861183</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1553478821.76</v>
+      </c>
+      <c r="K26" t="n">
+        <v>114243544.24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="N26" t="n">
+        <v>13825020518.12</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002909.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>集泰股份</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.0831</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1479934743</v>
+      </c>
+      <c r="H27" t="n">
+        <v>131622074.63</v>
+      </c>
+      <c r="I27" t="n">
+        <v>134497478.67</v>
+      </c>
+      <c r="J27" t="n">
+        <v>266119553.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2875404.04</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2408105334.39</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002912.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>中新赛克</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10.0155</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1108487183</v>
+      </c>
+      <c r="H28" t="n">
+        <v>88729264.12</v>
+      </c>
+      <c r="I28" t="n">
+        <v>102771062.12</v>
+      </c>
+      <c r="J28" t="n">
+        <v>191500326.24</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14041798</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M28" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4615239684.2</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>300227.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>光韵达</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-15.2174</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>875517350</v>
+      </c>
+      <c r="H29" t="n">
+        <v>264537067.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>154377888.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>418914956.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-110159179.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-12.58</v>
+      </c>
+      <c r="M29" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4805209961.37</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ST荣科</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-15.3846</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="G30" t="n">
+        <v>570842889</v>
+      </c>
+      <c r="H30" t="n">
+        <v>58575457.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>40507120.16</v>
+      </c>
+      <c r="J30" t="n">
+        <v>99082577.86</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-18068337.54</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="M30" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4713776044.78</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300905.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>宝丽迪</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="E31" t="n">
+        <v>15.5271</v>
+      </c>
+      <c r="F31" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>982068946</v>
+      </c>
+      <c r="H31" t="n">
+        <v>208490520.81</v>
+      </c>
+      <c r="I31" t="n">
+        <v>192860431.87</v>
+      </c>
+      <c r="J31" t="n">
+        <v>401350952.68</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-15630088.94</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5649751981.45</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301132.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>满坤科技</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6.0476</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2743696082</v>
+      </c>
+      <c r="H32" t="n">
+        <v>542095820.51</v>
+      </c>
+      <c r="I32" t="n">
+        <v>623727566.39</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1165823386.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>81631745.88</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M32" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5864451929.8</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.6352</v>
+      </c>
+      <c r="F33" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1127880199</v>
+      </c>
+      <c r="H33" t="n">
+        <v>157996917.89</v>
+      </c>
+      <c r="I33" t="n">
+        <v>126737422.97</v>
+      </c>
+      <c r="J33" t="n">
+        <v>284734340.86</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-31259494.92</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2217608404.26</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301591.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>肯特股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.8126</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="G34" t="n">
+        <v>651460864</v>
+      </c>
+      <c r="H34" t="n">
+        <v>104797945.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>90155320.52</v>
+      </c>
+      <c r="J34" t="n">
+        <v>194953266.24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-14642625.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M34" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2020202609.6</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301662.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>宏工科技</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>15.0307</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="G35" t="n">
+        <v>611935457</v>
+      </c>
+      <c r="H35" t="n">
+        <v>61126346.65</v>
+      </c>
+      <c r="I35" t="n">
+        <v>134316137.48</v>
+      </c>
+      <c r="J35" t="n">
+        <v>195442484.13</v>
+      </c>
+      <c r="K35" t="n">
+        <v>73189790.83</v>
+      </c>
+      <c r="L35" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M35" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3009961215</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-10.0212</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2077788003</v>
+      </c>
+      <c r="H36" t="n">
+        <v>242084438.36</v>
+      </c>
+      <c r="I36" t="n">
+        <v>233099643.27</v>
+      </c>
+      <c r="J36" t="n">
+        <v>475184081.63</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-8984795.09</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8182736029.5</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600180.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>*ST瑞茂</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-10.0529</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G37" t="n">
+        <v>89636670</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12552574.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7017792</v>
+      </c>
+      <c r="J37" t="n">
+        <v>19570366.4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-5534782.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="M37" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1847266688.8</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600184.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>光电股份</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.5316</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3993812100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>450405183.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>438907628.19</v>
+      </c>
+      <c r="J38" t="n">
+        <v>889312811.29</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-11497554.91</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="N38" t="n">
+        <v>12895758866.84</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600318.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>新力金融</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-4.697</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1607743312</v>
+      </c>
+      <c r="H39" t="n">
+        <v>127449481.4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>130829833.81</v>
+      </c>
+      <c r="J39" t="n">
+        <v>258279315.21</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3380352.41</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3225056805.28</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-10.0304</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="G40" t="n">
+        <v>843773325</v>
+      </c>
+      <c r="H40" t="n">
+        <v>63427963</v>
+      </c>
+      <c r="I40" t="n">
+        <v>93134060.16</v>
+      </c>
+      <c r="J40" t="n">
+        <v>156562023.16</v>
+      </c>
+      <c r="K40" t="n">
+        <v>29706097.16</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M40" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4686882470.4</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-10.0304</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4075499276</v>
+      </c>
+      <c r="H41" t="n">
+        <v>430156793.74</v>
+      </c>
+      <c r="I41" t="n">
+        <v>376292657.21</v>
+      </c>
+      <c r="J41" t="n">
+        <v>806449450.95</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-53864136.53</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="M41" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4686882470.4</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-9.0077</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G42" t="n">
+        <v>923742015</v>
+      </c>
+      <c r="H42" t="n">
+        <v>99875560.41</v>
+      </c>
+      <c r="I42" t="n">
+        <v>136923965</v>
+      </c>
+      <c r="J42" t="n">
+        <v>236799525.41</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37048404.59</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3783033540</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600697.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>欧亚集团</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-9.2105</v>
+      </c>
+      <c r="F43" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="G43" t="n">
+        <v>506242704</v>
+      </c>
+      <c r="H43" t="n">
+        <v>70353819.91</v>
+      </c>
+      <c r="I43" t="n">
+        <v>46097368</v>
+      </c>
+      <c r="J43" t="n">
+        <v>116451187.91</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-24256451.91</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-4.79</v>
+      </c>
+      <c r="M43" t="n">
+        <v>23</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1715351205.6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600865.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>百大集团</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-10.016</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2257408652</v>
+      </c>
+      <c r="H44" t="n">
+        <v>141789652.85</v>
+      </c>
+      <c r="I44" t="n">
+        <v>154099151.31</v>
+      </c>
+      <c r="J44" t="n">
+        <v>295888804.16</v>
+      </c>
+      <c r="K44" t="n">
+        <v>12309498.46</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M44" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4225178748.68</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600869.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>远东股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-10.0164</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6344310907</v>
+      </c>
+      <c r="H45" t="n">
+        <v>383803148.17</v>
+      </c>
+      <c r="I45" t="n">
+        <v>335233442.24</v>
+      </c>
+      <c r="J45" t="n">
+        <v>719036590.41</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-48569705.93</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="N45" t="n">
+        <v>48648212192.32</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>601123.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.1787</v>
+      </c>
+      <c r="F46" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>621138861</v>
+      </c>
+      <c r="H46" t="n">
+        <v>95976352.48999999</v>
+      </c>
+      <c r="I46" t="n">
+        <v>86069191.14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>182045543.63</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-9907161.35</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M46" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1606081604.08</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10.0046</v>
+      </c>
+      <c r="F47" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="G47" t="n">
+        <v>686216860</v>
+      </c>
+      <c r="H47" t="n">
+        <v>98214410.17</v>
+      </c>
+      <c r="I47" t="n">
+        <v>149711639.14</v>
+      </c>
+      <c r="J47" t="n">
+        <v>247926049.31</v>
+      </c>
+      <c r="K47" t="n">
+        <v>51497228.97</v>
+      </c>
+      <c r="L47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1953220304</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603090.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>宏盛股份</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.0137</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="G48" t="n">
+        <v>356760823</v>
+      </c>
+      <c r="H48" t="n">
+        <v>40294636</v>
+      </c>
+      <c r="I48" t="n">
+        <v>89940831</v>
+      </c>
+      <c r="J48" t="n">
+        <v>130235467</v>
+      </c>
+      <c r="K48" t="n">
+        <v>49646195</v>
+      </c>
+      <c r="L48" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="M48" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4021000000</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603090.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>宏盛股份</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10.0137</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="G49" t="n">
+        <v>593284159</v>
+      </c>
+      <c r="H49" t="n">
+        <v>59470829.32</v>
+      </c>
+      <c r="I49" t="n">
+        <v>135369962.8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>194840792.12</v>
+      </c>
+      <c r="K49" t="n">
+        <v>75899133.48</v>
+      </c>
+      <c r="L49" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="M49" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4021000000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603200.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0028</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G50" t="n">
+        <v>203153339</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23091044.88</v>
+      </c>
+      <c r="I50" t="n">
+        <v>101216837.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>124307882.38</v>
+      </c>
+      <c r="K50" t="n">
+        <v>78125792.62</v>
+      </c>
+      <c r="L50" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="M50" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="N50" t="n">
+        <v>6985862900.43</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0119</v>
+      </c>
+      <c r="F51" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="G51" t="n">
+        <v>144036302</v>
+      </c>
+      <c r="H51" t="n">
+        <v>20561953.64</v>
+      </c>
+      <c r="I51" t="n">
+        <v>35443093.18</v>
+      </c>
+      <c r="J51" t="n">
+        <v>56005046.82</v>
+      </c>
+      <c r="K51" t="n">
+        <v>14881139.54</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="M51" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1319981395.46</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603270.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>金帝股份</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4.772</v>
+      </c>
+      <c r="F52" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>563292882</v>
+      </c>
+      <c r="H52" t="n">
+        <v>70529600.77</v>
+      </c>
+      <c r="I52" t="n">
+        <v>153980102.09</v>
+      </c>
+      <c r="J52" t="n">
+        <v>224509702.86</v>
+      </c>
+      <c r="K52" t="n">
+        <v>83450501.31999999</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="M52" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2437603511.49</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603353.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>和顺石油</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.008</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G53" t="n">
+        <v>446957816</v>
+      </c>
+      <c r="H53" t="n">
+        <v>64969067</v>
+      </c>
+      <c r="I53" t="n">
+        <v>114228117.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>179197184.6</v>
+      </c>
+      <c r="K53" t="n">
+        <v>49259050.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M53" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7062121920</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603386.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>骏亚科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.1159</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2285075766</v>
+      </c>
+      <c r="H54" t="n">
+        <v>303881481</v>
+      </c>
+      <c r="I54" t="n">
+        <v>280413105</v>
+      </c>
+      <c r="J54" t="n">
+        <v>584294586</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-23468376</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M54" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6085915744</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603421.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="F55" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G55" t="n">
+        <v>661937681</v>
+      </c>
+      <c r="H55" t="n">
+        <v>57282461.3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>67090563</v>
+      </c>
+      <c r="J55" t="n">
+        <v>124373024.3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>9808101.699999999</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M55" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4943604073.38</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>605069.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-2.2925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="G56" t="n">
+        <v>346067209</v>
+      </c>
+      <c r="H56" t="n">
+        <v>46806692.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>34991217</v>
+      </c>
+      <c r="J56" t="n">
+        <v>81797909.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-11815475.7</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="M56" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2616584536.08</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>605188.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>国光连锁</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-10.0224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G57" t="n">
+        <v>229148356</v>
+      </c>
+      <c r="H57" t="n">
+        <v>35410936.09</v>
+      </c>
+      <c r="I57" t="n">
+        <v>23614759</v>
+      </c>
+      <c r="J57" t="n">
+        <v>59025695.09</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-11796177.09</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="M57" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6108190395</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="E58" t="n">
+        <v>19.9825</v>
+      </c>
+      <c r="F58" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G58" t="n">
+        <v>342112600</v>
+      </c>
+      <c r="H58" t="n">
+        <v>70199335.33</v>
+      </c>
+      <c r="I58" t="n">
+        <v>105781142.43</v>
+      </c>
+      <c r="J58" t="n">
+        <v>175980477.76</v>
+      </c>
+      <c r="K58" t="n">
+        <v>35581807.1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M58" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2192809440</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="E59" t="n">
+        <v>19.9825</v>
+      </c>
+      <c r="F59" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>374265900</v>
+      </c>
+      <c r="H59" t="n">
+        <v>70978227.56999999</v>
+      </c>
+      <c r="I59" t="n">
+        <v>111645480.16</v>
+      </c>
+      <c r="J59" t="n">
+        <v>182623707.73</v>
+      </c>
+      <c r="K59" t="n">
+        <v>40667252.59</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="M59" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2192809440</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>688216.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>气派科技</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="E60" t="n">
+        <v>15.9325</v>
+      </c>
+      <c r="F60" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="G60" t="n">
+        <v>725775900</v>
+      </c>
+      <c r="H60" t="n">
+        <v>69242911.01000001</v>
+      </c>
+      <c r="I60" t="n">
+        <v>117818790.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>187061701.61</v>
+      </c>
+      <c r="K60" t="n">
+        <v>48575879.59</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M60" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3942630266.31</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-5.2412</v>
+      </c>
+      <c r="F61" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="G61" t="n">
+        <v>330439200</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50909998.73</v>
+      </c>
+      <c r="I61" t="n">
+        <v>46958104.49</v>
+      </c>
+      <c r="J61" t="n">
+        <v>97868103.22</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-3951894.24</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="N61" t="n">
+        <v>859950000</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>920117.BJ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>龙鑫智能</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.9753</v>
+      </c>
+      <c r="F62" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="G62" t="n">
+        <v>134978500</v>
+      </c>
+      <c r="H62" t="n">
+        <v>22084925.95</v>
+      </c>
+      <c r="I62" t="n">
+        <v>34834147.31</v>
+      </c>
+      <c r="J62" t="n">
+        <v>56919073.26</v>
+      </c>
+      <c r="K62" t="n">
+        <v>12749221.36</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M62" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="N62" t="n">
+        <v>561747143.37</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-8.7536</v>
+      </c>
+      <c r="F63" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="G63" t="n">
+        <v>223894400</v>
+      </c>
+      <c r="H63" t="n">
+        <v>21698845.92</v>
+      </c>
+      <c r="I63" t="n">
+        <v>45122142.55</v>
+      </c>
+      <c r="J63" t="n">
+        <v>66820988.47</v>
+      </c>
+      <c r="K63" t="n">
+        <v>23423296.63</v>
+      </c>
+      <c r="L63" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="M63" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="N63" t="n">
+        <v>454827321.28</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>920289.BJ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>华汇智能</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-5.8609</v>
+      </c>
+      <c r="F64" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="G64" t="n">
+        <v>92908400</v>
+      </c>
+      <c r="H64" t="n">
+        <v>18661171.15</v>
+      </c>
+      <c r="I64" t="n">
+        <v>12899828.88</v>
+      </c>
+      <c r="J64" t="n">
+        <v>31561000.03</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-5761342.27</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="N64" t="n">
+        <v>373677439.62</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-21.0056</v>
+      </c>
+      <c r="F65" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>229194900</v>
+      </c>
+      <c r="H65" t="n">
+        <v>52385518.75</v>
+      </c>
+      <c r="I65" t="n">
+        <v>21834688.57</v>
+      </c>
+      <c r="J65" t="n">
+        <v>74220207.31999999</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-30550830.18</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-13.33</v>
+      </c>
+      <c r="M65" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="N65" t="n">
+        <v>609509649</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1071,7 +1072,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301251.SZ</t>
+          <t>688432.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1080,31 +1081,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69.51000000000001</v>
+        <v>44.55</v>
       </c>
       <c r="D7" t="n">
-        <v>81.78</v>
+        <v>54.06</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>44.55</v>
       </c>
       <c r="F7" t="n">
-        <v>81.78</v>
+        <v>54.06</v>
       </c>
       <c r="G7" t="n">
-        <v>68.15000000000001</v>
+        <v>45.05</v>
       </c>
       <c r="H7" t="n">
-        <v>13.63</v>
+        <v>9.01</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>152714</v>
+        <v>768442.17</v>
       </c>
       <c r="K7" t="n">
-        <v>1197598.36853</v>
+        <v>3913865.959</v>
       </c>
     </row>
     <row r="8">
@@ -1188,7 +1189,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688432.SH</t>
+          <t>301251.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1197,31 +1198,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>44.55</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>54.06</v>
+        <v>81.78</v>
       </c>
       <c r="E10" t="n">
-        <v>44.55</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>54.06</v>
+        <v>81.78</v>
       </c>
       <c r="G10" t="n">
-        <v>45.05</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>9.01</v>
+        <v>13.63</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>768442.17</v>
+        <v>152714</v>
       </c>
       <c r="K10" t="n">
-        <v>3913865.959</v>
+        <v>1197598.36853</v>
       </c>
     </row>
     <row r="11">
@@ -1727,4 +1728,4102 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000592.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>平潭发展</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.9747</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2889960143</v>
+      </c>
+      <c r="H2" t="n">
+        <v>182462120.81</v>
+      </c>
+      <c r="I2" t="n">
+        <v>639088236.46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>821550357.27</v>
+      </c>
+      <c r="K2" t="n">
+        <v>456626115.65</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="N2" t="n">
+        <v>16680455230.79</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000759.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-7.1111</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1160735810</v>
+      </c>
+      <c r="H3" t="n">
+        <v>148538688.83</v>
+      </c>
+      <c r="I3" t="n">
+        <v>149987088</v>
+      </c>
+      <c r="J3" t="n">
+        <v>298525776.83</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1448399.17</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4111276776.75</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.1046</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4925630793</v>
+      </c>
+      <c r="H4" t="n">
+        <v>831794986.48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>611060586.75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1442855573.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-220734399.73</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="M4" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14944696035.04</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.1046</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13210813575</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1516221847.53</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1848914586.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3365136433.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>332692738.59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M5" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14944696035.04</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000868.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>安凯客车</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>298933207</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46080005.26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>41957691.46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>88037696.72</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4122313.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3466806604.65</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.0307</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G7" t="n">
+        <v>140477385</v>
+      </c>
+      <c r="H7" t="n">
+        <v>34494473.94</v>
+      </c>
+      <c r="I7" t="n">
+        <v>37814580</v>
+      </c>
+      <c r="J7" t="n">
+        <v>72309053.94</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3320106.06</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4114788538.77</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000981.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.2715</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2988468860</v>
+      </c>
+      <c r="H8" t="n">
+        <v>466215941.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>266141963.63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>732357904.89</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-200073977.63</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="N8" t="n">
+        <v>26066595694.82</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1811384814</v>
+      </c>
+      <c r="H9" t="n">
+        <v>248592390</v>
+      </c>
+      <c r="I9" t="n">
+        <v>156615352.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>405207742.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-91977037.40000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8462942888.4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4022191830</v>
+      </c>
+      <c r="H10" t="n">
+        <v>434431361.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>317495209.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>751926570.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-116936152.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8462942888.4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9817</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G11" t="n">
+        <v>150474387</v>
+      </c>
+      <c r="H11" t="n">
+        <v>30344775</v>
+      </c>
+      <c r="I11" t="n">
+        <v>69030585.19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>99375360.19</v>
+      </c>
+      <c r="K11" t="n">
+        <v>38685810.19</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="M11" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4460330115.93</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002161.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>远望谷</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.9693</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>726951150</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75663701.51000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>177740857.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>253404558.76</v>
+      </c>
+      <c r="K12" t="n">
+        <v>102077155.74</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="M12" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5302999039.5</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002212.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-10.0386</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="G13" t="n">
+        <v>320673240</v>
+      </c>
+      <c r="H13" t="n">
+        <v>179336139</v>
+      </c>
+      <c r="I13" t="n">
+        <v>51688953</v>
+      </c>
+      <c r="J13" t="n">
+        <v>231025092</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-127647186</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-39.81</v>
+      </c>
+      <c r="M13" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8156275789.17</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002281.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>光迅科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.0018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7404579914</v>
+      </c>
+      <c r="H14" t="n">
+        <v>732732298.11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1747590743.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2480323042.01</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1014858445.79</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="M14" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>145580570367.92</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002396.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5194746709</v>
+      </c>
+      <c r="H15" t="n">
+        <v>655360516.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>776190693.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1431551210.71</v>
+      </c>
+      <c r="K15" t="n">
+        <v>120830177.11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>29410428565.98</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002491.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.986499999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6719072804</v>
+      </c>
+      <c r="H16" t="n">
+        <v>769158464.37</v>
+      </c>
+      <c r="I16" t="n">
+        <v>765303008.21</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1534461472.58</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-3855456.16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M16" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28764662062.2</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002491.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.986499999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12559534118</v>
+      </c>
+      <c r="H17" t="n">
+        <v>941310984.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1855449146.06</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2796760130.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>914138161.16</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="N17" t="n">
+        <v>28764662062.2</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.6452</v>
+      </c>
+      <c r="F18" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3577664911</v>
+      </c>
+      <c r="H18" t="n">
+        <v>511639689.14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>578602472.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1090242161.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>66962783.28</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>11464561750.05</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002584.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>西陇科学</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.023</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1073265706</v>
+      </c>
+      <c r="H19" t="n">
+        <v>175204076</v>
+      </c>
+      <c r="I19" t="n">
+        <v>308617072</v>
+      </c>
+      <c r="J19" t="n">
+        <v>483821148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>133412996</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="M19" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4594880677.9</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002585.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3731112832</v>
+      </c>
+      <c r="H20" t="n">
+        <v>627252905.71</v>
+      </c>
+      <c r="I20" t="n">
+        <v>520825799.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1148078704.89</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-106427106.53</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10789822059.96</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002631.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9.9902</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G21" t="n">
+        <v>803018746</v>
+      </c>
+      <c r="H21" t="n">
+        <v>170253422.94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>152425826.62</v>
+      </c>
+      <c r="J21" t="n">
+        <v>322679249.56</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-17827596.32</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="M21" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8913137037.959999</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002790.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>瑞尔特</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-6.366</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>482844536</v>
+      </c>
+      <c r="H22" t="n">
+        <v>56500870.66</v>
+      </c>
+      <c r="I22" t="n">
+        <v>42934294.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>99435165.26000001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-13566576.06</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1840524350</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002790.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>瑞尔特</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-6.366</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1537023320</v>
+      </c>
+      <c r="H23" t="n">
+        <v>207133929.22</v>
+      </c>
+      <c r="I23" t="n">
+        <v>128573665.24</v>
+      </c>
+      <c r="J23" t="n">
+        <v>335707594.46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-78560263.98</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1840524350</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002846.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>英联股份</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.0086</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>454772834</v>
+      </c>
+      <c r="H24" t="n">
+        <v>54247464</v>
+      </c>
+      <c r="I24" t="n">
+        <v>72953952</v>
+      </c>
+      <c r="J24" t="n">
+        <v>127201416</v>
+      </c>
+      <c r="K24" t="n">
+        <v>18706488</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3460245462.75</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002856.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>*ST美芝</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.138500000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="G25" t="n">
+        <v>216102206</v>
+      </c>
+      <c r="H25" t="n">
+        <v>22855408</v>
+      </c>
+      <c r="I25" t="n">
+        <v>43032386.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>65887794.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20176978.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3095132986.14</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002912.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中新赛克</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-9.9824</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G26" t="n">
+        <v>499557811</v>
+      </c>
+      <c r="H26" t="n">
+        <v>86177835.02</v>
+      </c>
+      <c r="I26" t="n">
+        <v>46988896.59</v>
+      </c>
+      <c r="J26" t="n">
+        <v>133166731.61</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-39188938.43</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="M26" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4154526829.96</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>003026.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中晶科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.0065</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1134391048</v>
+      </c>
+      <c r="H27" t="n">
+        <v>133048146.72</v>
+      </c>
+      <c r="I27" t="n">
+        <v>207522152.99</v>
+      </c>
+      <c r="J27" t="n">
+        <v>340570299.71</v>
+      </c>
+      <c r="K27" t="n">
+        <v>74474006.27</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4849572003.2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>111024.SH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>澳弘转债</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>206.314</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.4548</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>5530056630</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1227019700</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1235038710</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2462058410</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8019010</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>111024.SH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>澳弘转债</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>206.314</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.4548</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>11936702390</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2636847240</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2642771140</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5279618380</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5923900</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M29" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>300243.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>瑞丰高材</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20.0121</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1031960877</v>
+      </c>
+      <c r="H30" t="n">
+        <v>174770614.12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>232982136.32</v>
+      </c>
+      <c r="J30" t="n">
+        <v>407752750.44</v>
+      </c>
+      <c r="K30" t="n">
+        <v>58211522.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="M30" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4439429811.45</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300464.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>星徽股份</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G31" t="n">
+        <v>624619710</v>
+      </c>
+      <c r="H31" t="n">
+        <v>123856479</v>
+      </c>
+      <c r="I31" t="n">
+        <v>158679332</v>
+      </c>
+      <c r="J31" t="n">
+        <v>282535811</v>
+      </c>
+      <c r="K31" t="n">
+        <v>34822853</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="M31" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3558529603.5</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>300656.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>民德电子</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.0081</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>358227608</v>
+      </c>
+      <c r="H32" t="n">
+        <v>83771815.52</v>
+      </c>
+      <c r="I32" t="n">
+        <v>116488934.42</v>
+      </c>
+      <c r="J32" t="n">
+        <v>200260749.94</v>
+      </c>
+      <c r="K32" t="n">
+        <v>32717118.9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3990490483.94</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1197598369</v>
+      </c>
+      <c r="H33" t="n">
+        <v>306373602.86</v>
+      </c>
+      <c r="I33" t="n">
+        <v>408907910.72</v>
+      </c>
+      <c r="J33" t="n">
+        <v>715281513.58</v>
+      </c>
+      <c r="K33" t="n">
+        <v>102534307.86</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="M33" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14216075824.8</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2946798146</v>
+      </c>
+      <c r="H34" t="n">
+        <v>697082493.5700001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>875195616.6900001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1572278110.26</v>
+      </c>
+      <c r="K34" t="n">
+        <v>178113123.12</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="M34" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14216075824.8</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301373.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>凌玮科技</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>128</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.7883</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3789555604</v>
+      </c>
+      <c r="H35" t="n">
+        <v>590168315.13</v>
+      </c>
+      <c r="I35" t="n">
+        <v>732432426.4400001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1322600741.57</v>
+      </c>
+      <c r="K35" t="n">
+        <v>142264111.31</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8915893376</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301486.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>致尚科技</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>214.34</v>
+      </c>
+      <c r="E36" t="n">
+        <v>19.9978</v>
+      </c>
+      <c r="F36" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2534803623</v>
+      </c>
+      <c r="H36" t="n">
+        <v>217363181.53</v>
+      </c>
+      <c r="I36" t="n">
+        <v>477486791.94</v>
+      </c>
+      <c r="J36" t="n">
+        <v>694849973.47</v>
+      </c>
+      <c r="K36" t="n">
+        <v>260123610.41</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="M36" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="N36" t="n">
+        <v>15629424808.62</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>68.20999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5750999999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1058733172</v>
+      </c>
+      <c r="H37" t="n">
+        <v>149853884.28</v>
+      </c>
+      <c r="I37" t="n">
+        <v>121165147.55</v>
+      </c>
+      <c r="J37" t="n">
+        <v>271019031.83</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-28688736.73</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="M37" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2230360797.03</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.2039</v>
+      </c>
+      <c r="F38" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="G38" t="n">
+        <v>736441339</v>
+      </c>
+      <c r="H38" t="n">
+        <v>70408282.59999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>122157291.23</v>
+      </c>
+      <c r="J38" t="n">
+        <v>192565573.83</v>
+      </c>
+      <c r="K38" t="n">
+        <v>51749008.63</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="M38" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1914723073.62</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600103.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>青山纸业</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.1493</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="G39" t="n">
+        <v>928587212</v>
+      </c>
+      <c r="H39" t="n">
+        <v>104102520.02</v>
+      </c>
+      <c r="I39" t="n">
+        <v>246409912</v>
+      </c>
+      <c r="J39" t="n">
+        <v>350512432.02</v>
+      </c>
+      <c r="K39" t="n">
+        <v>142307391.98</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M39" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8163494183.43</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-7.1373</v>
+      </c>
+      <c r="F40" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2841850250</v>
+      </c>
+      <c r="H40" t="n">
+        <v>206967498.02</v>
+      </c>
+      <c r="I40" t="n">
+        <v>303103211.19</v>
+      </c>
+      <c r="J40" t="n">
+        <v>510070709.21</v>
+      </c>
+      <c r="K40" t="n">
+        <v>96135713.17</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M40" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7598713301.12</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600135.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>乐凯胶片</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10.068</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>94020746</v>
+      </c>
+      <c r="H41" t="n">
+        <v>18443058</v>
+      </c>
+      <c r="I41" t="n">
+        <v>46440718</v>
+      </c>
+      <c r="J41" t="n">
+        <v>64883776</v>
+      </c>
+      <c r="K41" t="n">
+        <v>27997660</v>
+      </c>
+      <c r="L41" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="M41" t="n">
+        <v>69.01000000000001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4476254430.91</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.2252</v>
+      </c>
+      <c r="F42" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1305410684</v>
+      </c>
+      <c r="H42" t="n">
+        <v>129028339.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>168754000.97</v>
+      </c>
+      <c r="J42" t="n">
+        <v>297782340.27</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39725661.67</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M42" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4676326428.8</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600359.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>新农开发</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-3.8071</v>
+      </c>
+      <c r="F43" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>849040705</v>
+      </c>
+      <c r="H43" t="n">
+        <v>86798689.33</v>
+      </c>
+      <c r="I43" t="n">
+        <v>223344432.32</v>
+      </c>
+      <c r="J43" t="n">
+        <v>310143121.65</v>
+      </c>
+      <c r="K43" t="n">
+        <v>136545742.99</v>
+      </c>
+      <c r="L43" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="M43" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2891867175.6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600359.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>新农开发</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-3.8071</v>
+      </c>
+      <c r="F44" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1284841775</v>
+      </c>
+      <c r="H44" t="n">
+        <v>111468902.33</v>
+      </c>
+      <c r="I44" t="n">
+        <v>224281064.32</v>
+      </c>
+      <c r="J44" t="n">
+        <v>335749966.65</v>
+      </c>
+      <c r="K44" t="n">
+        <v>112812161.99</v>
+      </c>
+      <c r="L44" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="M44" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2891867175.6</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600712.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-8.6556</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="G45" t="n">
+        <v>390513918</v>
+      </c>
+      <c r="H45" t="n">
+        <v>62930395.17</v>
+      </c>
+      <c r="I45" t="n">
+        <v>82453779.52</v>
+      </c>
+      <c r="J45" t="n">
+        <v>145384174.69</v>
+      </c>
+      <c r="K45" t="n">
+        <v>19523384.35</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2671695920.16</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600712.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-8.6556</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1085763219</v>
+      </c>
+      <c r="H46" t="n">
+        <v>110699519.98</v>
+      </c>
+      <c r="I46" t="n">
+        <v>122881606.24</v>
+      </c>
+      <c r="J46" t="n">
+        <v>233581126.22</v>
+      </c>
+      <c r="K46" t="n">
+        <v>12182086.26</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M46" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2671695920.16</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600865.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>百大集团</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-8.3704</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="G47" t="n">
+        <v>570836754</v>
+      </c>
+      <c r="H47" t="n">
+        <v>61290405</v>
+      </c>
+      <c r="I47" t="n">
+        <v>57570114.04</v>
+      </c>
+      <c r="J47" t="n">
+        <v>118860519.04</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-3720290.96</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M47" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3871512851.64</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-10.0062</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="G48" t="n">
+        <v>697839061</v>
+      </c>
+      <c r="H48" t="n">
+        <v>60167129</v>
+      </c>
+      <c r="I48" t="n">
+        <v>44165626</v>
+      </c>
+      <c r="J48" t="n">
+        <v>104332755</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-16001503</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="M48" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N48" t="n">
+        <v>9703620000</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>601123.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-1.611</v>
+      </c>
+      <c r="F49" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="G49" t="n">
+        <v>406033113</v>
+      </c>
+      <c r="H49" t="n">
+        <v>74892558.33</v>
+      </c>
+      <c r="I49" t="n">
+        <v>58347992.07</v>
+      </c>
+      <c r="J49" t="n">
+        <v>133240550.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-16544566.26</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="M49" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1580207974.42</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>601579.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>会稽山</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0194</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1185726038</v>
+      </c>
+      <c r="H50" t="n">
+        <v>166629365.35</v>
+      </c>
+      <c r="I50" t="n">
+        <v>239126405.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>405755771.05</v>
+      </c>
+      <c r="K50" t="n">
+        <v>72497040.34999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="M50" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="N50" t="n">
+        <v>13583198376.97</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603023.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>威帝股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0775</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G51" t="n">
+        <v>84479475</v>
+      </c>
+      <c r="H51" t="n">
+        <v>15016782</v>
+      </c>
+      <c r="I51" t="n">
+        <v>33472612.88</v>
+      </c>
+      <c r="J51" t="n">
+        <v>48489394.88</v>
+      </c>
+      <c r="K51" t="n">
+        <v>18455830.88</v>
+      </c>
+      <c r="L51" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="M51" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2377580153.82</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0083</v>
+      </c>
+      <c r="F52" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="G52" t="n">
+        <v>714451568</v>
+      </c>
+      <c r="H52" t="n">
+        <v>102289626.52</v>
+      </c>
+      <c r="I52" t="n">
+        <v>141500264.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>243789891.12</v>
+      </c>
+      <c r="K52" t="n">
+        <v>39210638.08</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M52" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2148704562</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.0083</v>
+      </c>
+      <c r="F53" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1400668428</v>
+      </c>
+      <c r="H53" t="n">
+        <v>148413495.3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>283523448.42</v>
+      </c>
+      <c r="J53" t="n">
+        <v>431936943.72</v>
+      </c>
+      <c r="K53" t="n">
+        <v>135109953.12</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="M53" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2148704562</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603136.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>天目湖</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-8.5303</v>
+      </c>
+      <c r="F54" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="G54" t="n">
+        <v>345840964</v>
+      </c>
+      <c r="H54" t="n">
+        <v>42143762.84</v>
+      </c>
+      <c r="I54" t="n">
+        <v>28921781.98</v>
+      </c>
+      <c r="J54" t="n">
+        <v>71065544.81999999</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-13221980.86</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="M54" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2404127719</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10.0217</v>
+      </c>
+      <c r="F55" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="G55" t="n">
+        <v>304084104</v>
+      </c>
+      <c r="H55" t="n">
+        <v>25243235.64</v>
+      </c>
+      <c r="I55" t="n">
+        <v>62901620.18</v>
+      </c>
+      <c r="J55" t="n">
+        <v>88144855.81999999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>37658384.54</v>
+      </c>
+      <c r="L55" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="M55" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1452265554.81</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603429.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>*ST集友</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-5.2632</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G56" t="n">
+        <v>47720705</v>
+      </c>
+      <c r="H56" t="n">
+        <v>18635230</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5799228</v>
+      </c>
+      <c r="J56" t="n">
+        <v>24434458</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-12836002</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="M56" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4625961801.3</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603657.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>春光科技</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.1856</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="G57" t="n">
+        <v>814833024</v>
+      </c>
+      <c r="H57" t="n">
+        <v>145665721.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>169738674.22</v>
+      </c>
+      <c r="J57" t="n">
+        <v>315404395.62</v>
+      </c>
+      <c r="K57" t="n">
+        <v>24072952.82</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M57" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4634314914</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603900.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>莱绅通灵</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0775</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="G58" t="n">
+        <v>189478492</v>
+      </c>
+      <c r="H58" t="n">
+        <v>38254483</v>
+      </c>
+      <c r="I58" t="n">
+        <v>59961427</v>
+      </c>
+      <c r="J58" t="n">
+        <v>98215910</v>
+      </c>
+      <c r="K58" t="n">
+        <v>21706944</v>
+      </c>
+      <c r="L58" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="M58" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2433339264</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603956.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>威派格</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.0787</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G59" t="n">
+        <v>285157121</v>
+      </c>
+      <c r="H59" t="n">
+        <v>46560321</v>
+      </c>
+      <c r="I59" t="n">
+        <v>63368286</v>
+      </c>
+      <c r="J59" t="n">
+        <v>109928607</v>
+      </c>
+      <c r="K59" t="n">
+        <v>16807965</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M59" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3983644939.14</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1207634403</v>
+      </c>
+      <c r="H60" t="n">
+        <v>128513468</v>
+      </c>
+      <c r="I60" t="n">
+        <v>150953927</v>
+      </c>
+      <c r="J60" t="n">
+        <v>279467395</v>
+      </c>
+      <c r="K60" t="n">
+        <v>22440459</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M60" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N60" t="n">
+        <v>6335870569.6</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>605069.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.2654</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="G61" t="n">
+        <v>309561426</v>
+      </c>
+      <c r="H61" t="n">
+        <v>33284703.92</v>
+      </c>
+      <c r="I61" t="n">
+        <v>56645665.2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>89930369.12</v>
+      </c>
+      <c r="K61" t="n">
+        <v>23360961.28</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2675859913.92</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-9.788399999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G62" t="n">
+        <v>662021489</v>
+      </c>
+      <c r="H62" t="n">
+        <v>45840169.71</v>
+      </c>
+      <c r="I62" t="n">
+        <v>31234752.54</v>
+      </c>
+      <c r="J62" t="n">
+        <v>77074922.25</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-14605417.17</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="N62" t="n">
+        <v>6062222229.8</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-9.788399999999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1437292980</v>
+      </c>
+      <c r="H63" t="n">
+        <v>107574260.24</v>
+      </c>
+      <c r="I63" t="n">
+        <v>65224991</v>
+      </c>
+      <c r="J63" t="n">
+        <v>172799251.24</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-42349269.24</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="M63" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="N63" t="n">
+        <v>6062222229.8</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20.0146</v>
+      </c>
+      <c r="F64" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="G64" t="n">
+        <v>698686200</v>
+      </c>
+      <c r="H64" t="n">
+        <v>173161516.25</v>
+      </c>
+      <c r="I64" t="n">
+        <v>162611142.36</v>
+      </c>
+      <c r="J64" t="n">
+        <v>335772658.61</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-10550373.89</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="M64" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2631691680</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688368.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>晶丰明源</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>146.28</v>
+      </c>
+      <c r="E65" t="n">
+        <v>15.2083</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1059323900</v>
+      </c>
+      <c r="H65" t="n">
+        <v>280629627.57</v>
+      </c>
+      <c r="I65" t="n">
+        <v>228769898.91</v>
+      </c>
+      <c r="J65" t="n">
+        <v>509399526.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-51859728.66</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="M65" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="N65" t="n">
+        <v>18095859228.6</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>20</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3913866000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>217760291.12</v>
+      </c>
+      <c r="I66" t="n">
+        <v>923885809.75</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1141646100.87</v>
+      </c>
+      <c r="K66" t="n">
+        <v>706125518.63</v>
+      </c>
+      <c r="L66" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="N66" t="n">
+        <v>67591318443.48</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>688478.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>晶升股份</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="E67" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G67" t="n">
+        <v>379156100</v>
+      </c>
+      <c r="H67" t="n">
+        <v>109864386.64</v>
+      </c>
+      <c r="I67" t="n">
+        <v>106281517.37</v>
+      </c>
+      <c r="J67" t="n">
+        <v>216145904.01</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-3582869.27</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M67" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6611132066.88</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>688620.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>安凯微</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15.1007</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G68" t="n">
+        <v>563928500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>78418601.06999999</v>
+      </c>
+      <c r="I68" t="n">
+        <v>157776874.75</v>
+      </c>
+      <c r="J68" t="n">
+        <v>236195475.82</v>
+      </c>
+      <c r="K68" t="n">
+        <v>79358273.68000001</v>
+      </c>
+      <c r="L68" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="M68" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="N68" t="n">
+        <v>6722800000</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>688790.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>昂瑞微</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-7.4158</v>
+      </c>
+      <c r="F69" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="G69" t="n">
+        <v>582420300</v>
+      </c>
+      <c r="H69" t="n">
+        <v>256534158.54</v>
+      </c>
+      <c r="I69" t="n">
+        <v>50520357.1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>307054515.64</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-206013801.44</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-35.37</v>
+      </c>
+      <c r="M69" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1861441666.38</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-5.0916</v>
+      </c>
+      <c r="F70" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="G70" t="n">
+        <v>305050200</v>
+      </c>
+      <c r="H70" t="n">
+        <v>58308757.11</v>
+      </c>
+      <c r="I70" t="n">
+        <v>34471246.57</v>
+      </c>
+      <c r="J70" t="n">
+        <v>92780003.68000001</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-23837510.54</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="M70" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="N70" t="n">
+        <v>816165000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>920176.BJ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>维琪科技</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.1074</v>
+      </c>
+      <c r="F71" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="G71" t="n">
+        <v>177162800</v>
+      </c>
+      <c r="H71" t="n">
+        <v>22836166.67</v>
+      </c>
+      <c r="I71" t="n">
+        <v>50920235.95</v>
+      </c>
+      <c r="J71" t="n">
+        <v>73756402.62</v>
+      </c>
+      <c r="K71" t="n">
+        <v>28084069.28</v>
+      </c>
+      <c r="L71" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="M71" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="N71" t="n">
+        <v>537614550</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920222.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>益坤电气</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3.4074</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="G72" t="n">
+        <v>70020200</v>
+      </c>
+      <c r="H72" t="n">
+        <v>20115943.68</v>
+      </c>
+      <c r="I72" t="n">
+        <v>17417423.03</v>
+      </c>
+      <c r="J72" t="n">
+        <v>37533366.71</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-2698520.65</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="N72" t="n">
+        <v>322827512.8</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="F73" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="G73" t="n">
+        <v>187621200</v>
+      </c>
+      <c r="H73" t="n">
+        <v>33889600.28</v>
+      </c>
+      <c r="I73" t="n">
+        <v>25362610.87</v>
+      </c>
+      <c r="J73" t="n">
+        <v>59252211.15</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-8526989.41</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="M73" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="N73" t="n">
+        <v>458005911.2</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="F74" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="G74" t="n">
+        <v>160009100</v>
+      </c>
+      <c r="H74" t="n">
+        <v>18247790.68</v>
+      </c>
+      <c r="I74" t="n">
+        <v>44946483.43</v>
+      </c>
+      <c r="J74" t="n">
+        <v>63194274.11</v>
+      </c>
+      <c r="K74" t="n">
+        <v>26698692.75</v>
+      </c>
+      <c r="L74" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="M74" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="N74" t="n">
+        <v>625027575</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,3285 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000056.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*ST皇庭</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9.9291</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G2" t="n">
+        <v>176857163</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34252727.94</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15982533</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50235260.94</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-18270194.94</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-10.33</v>
+      </c>
+      <c r="M2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2436558655.28</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000572.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>海马汽车</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.9208</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="G3" t="n">
+        <v>881286683</v>
+      </c>
+      <c r="H3" t="n">
+        <v>112425591.46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>229377767.24</v>
+      </c>
+      <c r="J3" t="n">
+        <v>341803358.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>116952175.78</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7160223372.12</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-9.328799999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1340238529</v>
+      </c>
+      <c r="H4" t="n">
+        <v>165121877.99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>101169698.99</v>
+      </c>
+      <c r="J4" t="n">
+        <v>266291576.98</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-63952179</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3730928857.11</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-9.328799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2197555788</v>
+      </c>
+      <c r="H5" t="n">
+        <v>223305498.97</v>
+      </c>
+      <c r="I5" t="n">
+        <v>167626125.99</v>
+      </c>
+      <c r="J5" t="n">
+        <v>390931624.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-55679372.98</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3730928857.11</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000980.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.2326</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1443469475</v>
+      </c>
+      <c r="H6" t="n">
+        <v>136466715</v>
+      </c>
+      <c r="I6" t="n">
+        <v>199819773.88</v>
+      </c>
+      <c r="J6" t="n">
+        <v>336286488.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>63353058.88</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11950691438.43</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000981.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.853999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2598886073</v>
+      </c>
+      <c r="H7" t="n">
+        <v>188164455.59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>581698664.97</v>
+      </c>
+      <c r="J7" t="n">
+        <v>769863120.5599999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>393534209.38</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="N7" t="n">
+        <v>28635201839.93</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001209.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>洪兴股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="G8" t="n">
+        <v>370161233</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61721340.31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>58681892</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120403232.31</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-3039448.31</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="M8" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1851398238.96</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>002137.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>实益达</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.2683</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1171882390</v>
+      </c>
+      <c r="H9" t="n">
+        <v>188112517.27</v>
+      </c>
+      <c r="I9" t="n">
+        <v>150802799.79</v>
+      </c>
+      <c r="J9" t="n">
+        <v>338915317.06</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-37309717.48</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3389724073.8</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002163.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>海南发展</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-9.9656</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="G10" t="n">
+        <v>628456719</v>
+      </c>
+      <c r="H10" t="n">
+        <v>274494403.57</v>
+      </c>
+      <c r="I10" t="n">
+        <v>88626047.56</v>
+      </c>
+      <c r="J10" t="n">
+        <v>363120451.13</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-185868356.01</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-29.58</v>
+      </c>
+      <c r="M10" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6315894157.5</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002285.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>世联行</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0418</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>650196338</v>
+      </c>
+      <c r="H11" t="n">
+        <v>71845653.59999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100974244.37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>172819897.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>29128590.77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5204794672.03</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002531.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天顺风能</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.4757</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2074856920</v>
+      </c>
+      <c r="H12" t="n">
+        <v>182691406.29</v>
+      </c>
+      <c r="I12" t="n">
+        <v>189203230.04</v>
+      </c>
+      <c r="J12" t="n">
+        <v>371894636.33</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6511823.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14598716453.83</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.2239</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3648834804</v>
+      </c>
+      <c r="H13" t="n">
+        <v>507206785.98</v>
+      </c>
+      <c r="I13" t="n">
+        <v>534389516.92</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1041596302.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>27182730.94</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M13" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11948815503.36</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002584.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>西陇科学</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.3141</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2610262975</v>
+      </c>
+      <c r="H14" t="n">
+        <v>425816926.18</v>
+      </c>
+      <c r="I14" t="n">
+        <v>255788916.44</v>
+      </c>
+      <c r="J14" t="n">
+        <v>681605842.62</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-170028009.74</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4580446497.76</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002640.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>跨境通</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.9125</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1078934316</v>
+      </c>
+      <c r="H15" t="n">
+        <v>98962433</v>
+      </c>
+      <c r="I15" t="n">
+        <v>313424014</v>
+      </c>
+      <c r="J15" t="n">
+        <v>412386447</v>
+      </c>
+      <c r="K15" t="n">
+        <v>214461581</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="M15" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5836946910.6</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002655.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>共达电声</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0108</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1450991869</v>
+      </c>
+      <c r="H16" t="n">
+        <v>217397143</v>
+      </c>
+      <c r="I16" t="n">
+        <v>400119816</v>
+      </c>
+      <c r="J16" t="n">
+        <v>617516959</v>
+      </c>
+      <c r="K16" t="n">
+        <v>182722673</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14810603517</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002796.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>世嘉科技</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0068</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G17" t="n">
+        <v>756329583</v>
+      </c>
+      <c r="H17" t="n">
+        <v>145263726.76</v>
+      </c>
+      <c r="I17" t="n">
+        <v>151292795</v>
+      </c>
+      <c r="J17" t="n">
+        <v>296556521.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6029068.24</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7409478495.62</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002824.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>和胜股份</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.6604</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2815583588</v>
+      </c>
+      <c r="H18" t="n">
+        <v>542481615.61</v>
+      </c>
+      <c r="I18" t="n">
+        <v>683385226.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1225866842.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>140903611.03</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6712907538.4</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002912.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中新赛克</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-8.6294</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>720783596</v>
+      </c>
+      <c r="H19" t="n">
+        <v>65346966.16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>84369078.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>149716044.71</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19022112.39</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3796014362.4</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002997.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>瑞鹄模具</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-8.4763</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G20" t="n">
+        <v>236355249</v>
+      </c>
+      <c r="H20" t="n">
+        <v>31577122.59</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26534796.54</v>
+      </c>
+      <c r="J20" t="n">
+        <v>58111919.13</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-5042326.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="M20" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5582599737.75</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.0162</v>
+      </c>
+      <c r="F21" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="G21" t="n">
+        <v>714545591</v>
+      </c>
+      <c r="H21" t="n">
+        <v>101211522.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>107098485.92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>208310008.52</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5886963.32</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2323612360.64</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.0162</v>
+      </c>
+      <c r="F22" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1046412094</v>
+      </c>
+      <c r="H22" t="n">
+        <v>127992090.92</v>
+      </c>
+      <c r="I22" t="n">
+        <v>144582359.32</v>
+      </c>
+      <c r="J22" t="n">
+        <v>272574450.24</v>
+      </c>
+      <c r="K22" t="n">
+        <v>16590268.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2323612360.64</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>300189.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>神农种业</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8.617900000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1967012286</v>
+      </c>
+      <c r="H23" t="n">
+        <v>282954762.96</v>
+      </c>
+      <c r="I23" t="n">
+        <v>195419914.13</v>
+      </c>
+      <c r="J23" t="n">
+        <v>478374677.09</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-87534848.83</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5920152832.32</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>300243.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>瑞丰高材</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.9018</v>
+      </c>
+      <c r="F24" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1627352720</v>
+      </c>
+      <c r="H24" t="n">
+        <v>231078179.17</v>
+      </c>
+      <c r="I24" t="n">
+        <v>374968516.15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>606046695.3200001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>143890336.98</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M24" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4745828745.54</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>300434.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>金石亚药</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19.9808</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G25" t="n">
+        <v>552381526</v>
+      </c>
+      <c r="H25" t="n">
+        <v>81982244.56</v>
+      </c>
+      <c r="I25" t="n">
+        <v>191480838</v>
+      </c>
+      <c r="J25" t="n">
+        <v>273463082.56</v>
+      </c>
+      <c r="K25" t="n">
+        <v>109498593.44</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="M25" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4288606817.64</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300741.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>华宝股份</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20.0088</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>820267736</v>
+      </c>
+      <c r="H26" t="n">
+        <v>121890068.07</v>
+      </c>
+      <c r="I26" t="n">
+        <v>133568457.69</v>
+      </c>
+      <c r="J26" t="n">
+        <v>255458525.76</v>
+      </c>
+      <c r="K26" t="n">
+        <v>11678389.62</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M26" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>16733382165.5</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300939.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>秋田微</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.6326</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G27" t="n">
+        <v>811344266</v>
+      </c>
+      <c r="H27" t="n">
+        <v>114400322</v>
+      </c>
+      <c r="I27" t="n">
+        <v>152957176.66</v>
+      </c>
+      <c r="J27" t="n">
+        <v>267357498.66</v>
+      </c>
+      <c r="K27" t="n">
+        <v>38556854.66</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M27" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11448000000</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300939.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>秋田微</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.6326</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1233008039</v>
+      </c>
+      <c r="H28" t="n">
+        <v>213115281.86</v>
+      </c>
+      <c r="I28" t="n">
+        <v>234110188.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>447225470.47</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20994906.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M28" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11448000000</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301390.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>经纬股份</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>45</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G29" t="n">
+        <v>26682615</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7807500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>22063500</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29871000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>14256000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2207528100</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>75.03</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.9985</v>
+      </c>
+      <c r="F30" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1310929499</v>
+      </c>
+      <c r="H30" t="n">
+        <v>130339025.02</v>
+      </c>
+      <c r="I30" t="n">
+        <v>129101284.01</v>
+      </c>
+      <c r="J30" t="n">
+        <v>259440309.03</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1237741.01</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M30" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2453364178.29</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.7774</v>
+      </c>
+      <c r="F31" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1174944437</v>
+      </c>
+      <c r="H31" t="n">
+        <v>191272733.17</v>
+      </c>
+      <c r="I31" t="n">
+        <v>176968700.76</v>
+      </c>
+      <c r="J31" t="n">
+        <v>368241433.93</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-14304032.41</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M31" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3021976230</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.0175</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="G32" t="n">
+        <v>781174584</v>
+      </c>
+      <c r="H32" t="n">
+        <v>93586940.09999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>99752156.51000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>193339096.61</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6165216.41</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M32" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1991647667.52</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.966200000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2373475036</v>
+      </c>
+      <c r="H33" t="n">
+        <v>250532482.25</v>
+      </c>
+      <c r="I33" t="n">
+        <v>465896012.93</v>
+      </c>
+      <c r="J33" t="n">
+        <v>716428495.1799999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>215363530.68</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="M33" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8356017498.36</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.0451</v>
+      </c>
+      <c r="F34" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1284844051</v>
+      </c>
+      <c r="H34" t="n">
+        <v>217151230.76</v>
+      </c>
+      <c r="I34" t="n">
+        <v>164140855.08</v>
+      </c>
+      <c r="J34" t="n">
+        <v>381292085.84</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-53010375.68</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="M34" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5146070280</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>600356.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>恒丰纸业</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10.0432</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G35" t="n">
+        <v>228226439</v>
+      </c>
+      <c r="H35" t="n">
+        <v>46576006.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50883327</v>
+      </c>
+      <c r="J35" t="n">
+        <v>97459333.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4307320.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M35" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3044072741.82</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.985900000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1147572898</v>
+      </c>
+      <c r="H36" t="n">
+        <v>167012365.93</v>
+      </c>
+      <c r="I36" t="n">
+        <v>117063937.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>284076303.63</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-49948428.23</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="M36" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4575919920</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.985900000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1749628688</v>
+      </c>
+      <c r="H37" t="n">
+        <v>190217445.76</v>
+      </c>
+      <c r="I37" t="n">
+        <v>208954678.22</v>
+      </c>
+      <c r="J37" t="n">
+        <v>399172123.98</v>
+      </c>
+      <c r="K37" t="n">
+        <v>18737232.46</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4575919920</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600609.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金杯汽车</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10.1538</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G38" t="n">
+        <v>284158161</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37926249.16</v>
+      </c>
+      <c r="I38" t="n">
+        <v>69644026.78</v>
+      </c>
+      <c r="J38" t="n">
+        <v>107570275.94</v>
+      </c>
+      <c r="K38" t="n">
+        <v>31717777.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M38" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4670319637.64</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.073</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="G39" t="n">
+        <v>327645530</v>
+      </c>
+      <c r="H39" t="n">
+        <v>55714090.27</v>
+      </c>
+      <c r="I39" t="n">
+        <v>55392368.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>111106458.77</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-321721.77</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3203456441.38</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600792.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>云煤能源</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.1031</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G40" t="n">
+        <v>773307370</v>
+      </c>
+      <c r="H40" t="n">
+        <v>90746029</v>
+      </c>
+      <c r="I40" t="n">
+        <v>132688089</v>
+      </c>
+      <c r="J40" t="n">
+        <v>223434118</v>
+      </c>
+      <c r="K40" t="n">
+        <v>41942060</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M40" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5926992024</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1650973388</v>
+      </c>
+      <c r="H41" t="n">
+        <v>99580690.98</v>
+      </c>
+      <c r="I41" t="n">
+        <v>112179750</v>
+      </c>
+      <c r="J41" t="n">
+        <v>211760440.98</v>
+      </c>
+      <c r="K41" t="n">
+        <v>12599059.02</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M41" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="N41" t="n">
+        <v>9723600000</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>373.8041</v>
+      </c>
+      <c r="F42" t="n">
+        <v>79.62</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2181187373</v>
+      </c>
+      <c r="H42" t="n">
+        <v>150749265.38</v>
+      </c>
+      <c r="I42" t="n">
+        <v>188963851.83</v>
+      </c>
+      <c r="J42" t="n">
+        <v>339713117.21</v>
+      </c>
+      <c r="K42" t="n">
+        <v>38214586.45</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M42" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4392194185.6</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>601218.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>吉鑫科技</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9.9617</v>
+      </c>
+      <c r="F43" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1441412430</v>
+      </c>
+      <c r="H43" t="n">
+        <v>113482660.05</v>
+      </c>
+      <c r="I43" t="n">
+        <v>159756050.88</v>
+      </c>
+      <c r="J43" t="n">
+        <v>273238710.93</v>
+      </c>
+      <c r="K43" t="n">
+        <v>46273390.83</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M43" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5562252358.88</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>601218.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>吉鑫科技</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.9617</v>
+      </c>
+      <c r="F44" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3142331331</v>
+      </c>
+      <c r="H44" t="n">
+        <v>202565930.05</v>
+      </c>
+      <c r="I44" t="n">
+        <v>245489057.73</v>
+      </c>
+      <c r="J44" t="n">
+        <v>448054987.78</v>
+      </c>
+      <c r="K44" t="n">
+        <v>42923127.68</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M44" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5562252358.88</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>603042.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>华脉科技</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.0886</v>
+      </c>
+      <c r="F45" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1226822454</v>
+      </c>
+      <c r="H45" t="n">
+        <v>154614816.21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>145020196.81</v>
+      </c>
+      <c r="J45" t="n">
+        <v>299635013.02</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-9594619.4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M45" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3693084550.48</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-3.4164</v>
+      </c>
+      <c r="F46" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1077865587</v>
+      </c>
+      <c r="H46" t="n">
+        <v>216351360.17</v>
+      </c>
+      <c r="I46" t="n">
+        <v>178310120.7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>394661480.87</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-38041239.47</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="M46" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2075296573</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>603159.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>上海亚虹</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-3.3277</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="G47" t="n">
+        <v>409638639</v>
+      </c>
+      <c r="H47" t="n">
+        <v>92300233.59999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>61030289.06</v>
+      </c>
+      <c r="J47" t="n">
+        <v>153330522.66</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-31269944.54</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="M47" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3213000000</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603186.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>华正新材</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>230</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-9.4453</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5935779870</v>
+      </c>
+      <c r="H48" t="n">
+        <v>798130182.05</v>
+      </c>
+      <c r="I48" t="n">
+        <v>969819253.66</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1767949435.71</v>
+      </c>
+      <c r="K48" t="n">
+        <v>171689071.61</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="N48" t="n">
+        <v>36061819140</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9.9641</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G49" t="n">
+        <v>199911692</v>
+      </c>
+      <c r="H49" t="n">
+        <v>26984738</v>
+      </c>
+      <c r="I49" t="n">
+        <v>75542544</v>
+      </c>
+      <c r="J49" t="n">
+        <v>102527282</v>
+      </c>
+      <c r="K49" t="n">
+        <v>48557806</v>
+      </c>
+      <c r="L49" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="M49" t="n">
+        <v>51.29</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4330656750</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="E50" t="n">
+        <v>9.995100000000001</v>
+      </c>
+      <c r="F50" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="G50" t="n">
+        <v>491913242</v>
+      </c>
+      <c r="H50" t="n">
+        <v>80013081.22</v>
+      </c>
+      <c r="I50" t="n">
+        <v>131180977.71</v>
+      </c>
+      <c r="J50" t="n">
+        <v>211194058.93</v>
+      </c>
+      <c r="K50" t="n">
+        <v>51167896.49</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1597420605.34</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603406.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>天富龙</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-7.864</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>125819831</v>
+      </c>
+      <c r="H51" t="n">
+        <v>14276465.44</v>
+      </c>
+      <c r="I51" t="n">
+        <v>13445074</v>
+      </c>
+      <c r="J51" t="n">
+        <v>27721539.44</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-831391.4399999999</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M51" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1623603271.85</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12.9032</v>
+      </c>
+      <c r="F52" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1383781800</v>
+      </c>
+      <c r="H52" t="n">
+        <v>269873545.22</v>
+      </c>
+      <c r="I52" t="n">
+        <v>306812809.56</v>
+      </c>
+      <c r="J52" t="n">
+        <v>576686354.78</v>
+      </c>
+      <c r="K52" t="n">
+        <v>36939264.34</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M52" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2971264800</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="E53" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F53" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1038206100</v>
+      </c>
+      <c r="H53" t="n">
+        <v>118556626.88</v>
+      </c>
+      <c r="I53" t="n">
+        <v>171378435.41</v>
+      </c>
+      <c r="J53" t="n">
+        <v>289935062.29</v>
+      </c>
+      <c r="K53" t="n">
+        <v>52821808.53</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="M53" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6974265936.75</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>688802.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>沐曦股份</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>546.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14.4359</v>
+      </c>
+      <c r="F54" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7175028600</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2351704006.56</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1337498685.83</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3689202692.39</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-1014205320.73</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-14.14</v>
+      </c>
+      <c r="M54" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="N54" t="n">
+        <v>17758288516.5</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>920065.BJ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>千岸科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6.4896</v>
+      </c>
+      <c r="F55" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="G55" t="n">
+        <v>136769900</v>
+      </c>
+      <c r="H55" t="n">
+        <v>12508000.47</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20693400.47</v>
+      </c>
+      <c r="J55" t="n">
+        <v>33201400.94</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8185400</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M55" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="N55" t="n">
+        <v>555660000</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>920176.BJ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>维琪科技</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>67</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.9608</v>
+      </c>
+      <c r="F56" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="G56" t="n">
+        <v>165918400</v>
+      </c>
+      <c r="H56" t="n">
+        <v>45381333.38</v>
+      </c>
+      <c r="I56" t="n">
+        <v>22779034.09</v>
+      </c>
+      <c r="J56" t="n">
+        <v>68160367.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-22602299.29</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-13.62</v>
+      </c>
+      <c r="M56" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="N56" t="n">
+        <v>532449000</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-5.2997</v>
+      </c>
+      <c r="F57" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="G57" t="n">
+        <v>140854700</v>
+      </c>
+      <c r="H57" t="n">
+        <v>18321312.48</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20987208.83</v>
+      </c>
+      <c r="J57" t="n">
+        <v>39308521.31</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2665896.35</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M57" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="N57" t="n">
+        <v>433733042.72</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8.242599999999999</v>
+      </c>
+      <c r="F58" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="G58" t="n">
+        <v>762208000</v>
+      </c>
+      <c r="H58" t="n">
+        <v>95060471.59999999</v>
+      </c>
+      <c r="I58" t="n">
+        <v>82483885.18000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>177544356.78</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-12576586.42</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1064880000</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="E59" t="n">
+        <v>19.4023</v>
+      </c>
+      <c r="F59" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="G59" t="n">
+        <v>248576000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>41161999.74</v>
+      </c>
+      <c r="I59" t="n">
+        <v>42714582.14</v>
+      </c>
+      <c r="J59" t="n">
+        <v>83876581.88</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1552582.4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M59" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="N59" t="n">
+        <v>746297293</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,3120 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000002.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>万科A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.9338</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1419831684</v>
+      </c>
+      <c r="H2" t="n">
+        <v>145416299.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>670668278.79</v>
+      </c>
+      <c r="J2" t="n">
+        <v>816084578.1900001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>525251979.39</v>
+      </c>
+      <c r="L2" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="M2" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32254175671.28</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.8934</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1252680714</v>
+      </c>
+      <c r="H3" t="n">
+        <v>91332124.08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>184337017.16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>275669141.24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>93004893.08</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3913496266.68</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>001365.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>天海电子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.1594</v>
+      </c>
+      <c r="F4" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="G4" t="n">
+        <v>744756095</v>
+      </c>
+      <c r="H4" t="n">
+        <v>118073809.82</v>
+      </c>
+      <c r="I4" t="n">
+        <v>94003426.52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>212077236.34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-24070383.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2203616354.72</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.019</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1466416529</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71412259.90000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>490092910.67</v>
+      </c>
+      <c r="J5" t="n">
+        <v>561505170.5700001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>418680650.77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9976231157.27</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>002185.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.0061</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6386880067</v>
+      </c>
+      <c r="H6" t="n">
+        <v>414180801.42</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1232232280.46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1646413081.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>818051479.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="M6" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="N6" t="n">
+        <v>59968258371.96</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>002360.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST同德</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-8.5763</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>101549274</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19934363.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12190996</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32125359.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-7743367.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1644306620.32</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>002453.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华软科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.1031</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="G8" t="n">
+        <v>564644167</v>
+      </c>
+      <c r="H8" t="n">
+        <v>140908636.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>115931001.18</v>
+      </c>
+      <c r="J8" t="n">
+        <v>256839637.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-24977635.02</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3434161892.52</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>002528.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>*ST英飞</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0279</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G9" t="n">
+        <v>448056591</v>
+      </c>
+      <c r="H9" t="n">
+        <v>102008159</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30538681.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>132546840.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-71469477.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-15.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6784418467.42</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002531.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天顺风能</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-5.6304</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1533211505</v>
+      </c>
+      <c r="H10" t="n">
+        <v>216220415.14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>122640120.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>338860535.74</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-93580294.54000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13776756898.29</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002584.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>西陇科学</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2133692279</v>
+      </c>
+      <c r="H11" t="n">
+        <v>224497634.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>251251535.57</v>
+      </c>
+      <c r="J11" t="n">
+        <v>475749170.07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>26753901.07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4691108545.5</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002631.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.975099999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1262099126</v>
+      </c>
+      <c r="H12" t="n">
+        <v>172652476.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>231519731.44</v>
+      </c>
+      <c r="J12" t="n">
+        <v>404172207.59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>58867255.29</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10500516741.96</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002836.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新宏泽</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.963100000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>271027272</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77457907.28</v>
+      </c>
+      <c r="I13" t="n">
+        <v>72718960.12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>150176867.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4738947.16</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2746368000</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002902.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>铭普光磁</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.9959</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2058407385</v>
+      </c>
+      <c r="H14" t="n">
+        <v>125365703.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>394082915.69</v>
+      </c>
+      <c r="J14" t="n">
+        <v>519448619.19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>268717212.19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5817890395.2</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002980.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>华盛昌</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>128.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0009</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1982778922</v>
+      </c>
+      <c r="H15" t="n">
+        <v>401020600</v>
+      </c>
+      <c r="I15" t="n">
+        <v>586239446.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>987260046.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>185218846.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12967751436.57</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.5748</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>774694509</v>
+      </c>
+      <c r="H16" t="n">
+        <v>120048292.83</v>
+      </c>
+      <c r="I16" t="n">
+        <v>114204868.24</v>
+      </c>
+      <c r="J16" t="n">
+        <v>234253161.07</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-5843424.59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2287020040</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>003026.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中晶科技</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="F17" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2225844622</v>
+      </c>
+      <c r="H17" t="n">
+        <v>277377650.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>190973560.41</v>
+      </c>
+      <c r="J17" t="n">
+        <v>468351211.01</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-86404090.19</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5362784736</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>300464.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>星徽股份</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.3913</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>704053684</v>
+      </c>
+      <c r="H18" t="n">
+        <v>105908163.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>193509059</v>
+      </c>
+      <c r="J18" t="n">
+        <v>299417222.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87600895.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4123206456.75</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>300464.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>星徽股份</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.3913</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1949269134</v>
+      </c>
+      <c r="H19" t="n">
+        <v>312788645.66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>453113575.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>765902220.76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>140324929.44</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4123206456.75</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>300836.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>佰奥智能</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19.4201</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>499243050</v>
+      </c>
+      <c r="H20" t="n">
+        <v>121846197.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>164243831.85</v>
+      </c>
+      <c r="J20" t="n">
+        <v>286090029.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>42397634.35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="M20" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3971973881.2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>301390.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>经纬股份</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>54</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>238877748</v>
+      </c>
+      <c r="H21" t="n">
+        <v>71173188</v>
+      </c>
+      <c r="I21" t="n">
+        <v>52590600</v>
+      </c>
+      <c r="J21" t="n">
+        <v>123763788</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-18582588</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="M21" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2649033720</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>301390.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>经纬股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G22" t="n">
+        <v>265560363</v>
+      </c>
+      <c r="H22" t="n">
+        <v>71173188</v>
+      </c>
+      <c r="I22" t="n">
+        <v>54979200</v>
+      </c>
+      <c r="J22" t="n">
+        <v>126152388</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-16193988</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2649033720</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>72.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.9318</v>
+      </c>
+      <c r="F23" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1288633754</v>
+      </c>
+      <c r="H23" t="n">
+        <v>138744604.48</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100936898.02</v>
+      </c>
+      <c r="J23" t="n">
+        <v>239681502.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-37807706.46</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2356903771.44</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>托伦斯</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>142.56</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1675296902</v>
+      </c>
+      <c r="H24" t="n">
+        <v>206061699.98</v>
+      </c>
+      <c r="I24" t="n">
+        <v>385781404.28</v>
+      </c>
+      <c r="J24" t="n">
+        <v>591843104.26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>179719704.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="M24" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4395320534.88</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>301688.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>格林生物</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>419372498</v>
+      </c>
+      <c r="H25" t="n">
+        <v>37184593.12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>47729815.23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>84914408.34999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10545222.11</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1016271511.83</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>63</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1588249888</v>
+      </c>
+      <c r="H26" t="n">
+        <v>256218388.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>243016962.53</v>
+      </c>
+      <c r="J26" t="n">
+        <v>499235351.13</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-13201426.07</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M26" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3626371476</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12.7458</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1191471767</v>
+      </c>
+      <c r="H27" t="n">
+        <v>147030437.57</v>
+      </c>
+      <c r="I27" t="n">
+        <v>110837704.63</v>
+      </c>
+      <c r="J27" t="n">
+        <v>257868142.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-36192732.94</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="M27" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2245498827.39</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.9846</v>
+      </c>
+      <c r="F28" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4160809340</v>
+      </c>
+      <c r="H28" t="n">
+        <v>518736589.39</v>
+      </c>
+      <c r="I28" t="n">
+        <v>590715703.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1109452293</v>
+      </c>
+      <c r="K28" t="n">
+        <v>71979114.22</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M28" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9190335681.76</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.9846</v>
+      </c>
+      <c r="F29" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6534284376</v>
+      </c>
+      <c r="H29" t="n">
+        <v>693184663.72</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1029884330.47</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1723068994.19</v>
+      </c>
+      <c r="K29" t="n">
+        <v>336699666.75</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9190335681.76</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.5345</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1384581421</v>
+      </c>
+      <c r="H30" t="n">
+        <v>148063047.55</v>
+      </c>
+      <c r="I30" t="n">
+        <v>140339499.75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>288402547.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-7723547.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4505701200</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>600448.SH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>华纺股份</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.937900000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G31" t="n">
+        <v>399340592</v>
+      </c>
+      <c r="H31" t="n">
+        <v>122663156.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>66988010.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>189651166.8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-55675146.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-13.94</v>
+      </c>
+      <c r="M31" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2229561603.48</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.946899999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v>654675214</v>
+      </c>
+      <c r="H32" t="n">
+        <v>65665470.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>92278129.86</v>
+      </c>
+      <c r="J32" t="n">
+        <v>157943600.56</v>
+      </c>
+      <c r="K32" t="n">
+        <v>26612659.16</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M32" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3522102639.13</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>600640.SH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>国脉文化</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10.0365</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G33" t="n">
+        <v>282017303</v>
+      </c>
+      <c r="H33" t="n">
+        <v>39550366.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>103194536.87</v>
+      </c>
+      <c r="J33" t="n">
+        <v>142744903.07</v>
+      </c>
+      <c r="K33" t="n">
+        <v>63644170.67</v>
+      </c>
+      <c r="L33" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9546109160.4</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>600719.SH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>大连热电</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.0654</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>336252647</v>
+      </c>
+      <c r="H34" t="n">
+        <v>35430659</v>
+      </c>
+      <c r="I34" t="n">
+        <v>87380831</v>
+      </c>
+      <c r="J34" t="n">
+        <v>122811490</v>
+      </c>
+      <c r="K34" t="n">
+        <v>51950172</v>
+      </c>
+      <c r="L34" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3406728632</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2016131505</v>
+      </c>
+      <c r="H35" t="n">
+        <v>294950584.07</v>
+      </c>
+      <c r="I35" t="n">
+        <v>174285051.32</v>
+      </c>
+      <c r="J35" t="n">
+        <v>469235635.39</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-120665532.75</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="M35" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4595344238.25</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10.0395</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>135333040</v>
+      </c>
+      <c r="H36" t="n">
+        <v>31733545</v>
+      </c>
+      <c r="I36" t="n">
+        <v>49875400</v>
+      </c>
+      <c r="J36" t="n">
+        <v>81608945</v>
+      </c>
+      <c r="K36" t="n">
+        <v>18141855</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="M36" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2133760608</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600881.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>亚泰集团</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.2857</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G37" t="n">
+        <v>294120289</v>
+      </c>
+      <c r="H37" t="n">
+        <v>34843716.78</v>
+      </c>
+      <c r="I37" t="n">
+        <v>157177843</v>
+      </c>
+      <c r="J37" t="n">
+        <v>192021559.78</v>
+      </c>
+      <c r="K37" t="n">
+        <v>122334126.22</v>
+      </c>
+      <c r="L37" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="M37" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6238051406.84</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1738203709</v>
+      </c>
+      <c r="H38" t="n">
+        <v>109497081</v>
+      </c>
+      <c r="I38" t="n">
+        <v>281657073.62</v>
+      </c>
+      <c r="J38" t="n">
+        <v>391154154.62</v>
+      </c>
+      <c r="K38" t="n">
+        <v>172159992.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10695960000</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>603082.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北自科技</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="F39" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="G39" t="n">
+        <v>673866807</v>
+      </c>
+      <c r="H39" t="n">
+        <v>136226404.92</v>
+      </c>
+      <c r="I39" t="n">
+        <v>110703172.04</v>
+      </c>
+      <c r="J39" t="n">
+        <v>246929576.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-25523232.88</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="M39" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2084624660</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0408</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="G40" t="n">
+        <v>867115987</v>
+      </c>
+      <c r="H40" t="n">
+        <v>148630895.24</v>
+      </c>
+      <c r="I40" t="n">
+        <v>73262749.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>221893644.54</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-75368145.94</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-8.69</v>
+      </c>
+      <c r="M40" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4765490040</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.982100000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>564540096</v>
+      </c>
+      <c r="H41" t="n">
+        <v>74748762.59999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>129897071.66</v>
+      </c>
+      <c r="J41" t="n">
+        <v>204645834.26</v>
+      </c>
+      <c r="K41" t="n">
+        <v>55148309.06</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M41" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1756876646.07</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.982100000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1056453338</v>
+      </c>
+      <c r="H42" t="n">
+        <v>132506375.31</v>
+      </c>
+      <c r="I42" t="n">
+        <v>239683485.23</v>
+      </c>
+      <c r="J42" t="n">
+        <v>372189860.54</v>
+      </c>
+      <c r="K42" t="n">
+        <v>107177109.92</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="M42" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1756876646.07</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>603448.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>天博智能</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.589</v>
+      </c>
+      <c r="F43" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="G43" t="n">
+        <v>467112904</v>
+      </c>
+      <c r="H43" t="n">
+        <v>31513129.35</v>
+      </c>
+      <c r="I43" t="n">
+        <v>33780834.25</v>
+      </c>
+      <c r="J43" t="n">
+        <v>65293963.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2267704.9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M43" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1506488578.22</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>603626.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>科森科技</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0047</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2288164106</v>
+      </c>
+      <c r="H44" t="n">
+        <v>218441198.22</v>
+      </c>
+      <c r="I44" t="n">
+        <v>379621253.74</v>
+      </c>
+      <c r="J44" t="n">
+        <v>598062451.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>161180055.52</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="M44" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="N44" t="n">
+        <v>12995282339.8</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>603880.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>南卫股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-8.5479</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G45" t="n">
+        <v>236472511</v>
+      </c>
+      <c r="H45" t="n">
+        <v>60989453.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>57797025.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>118786479.1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-3192427.9</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="M45" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2566692960</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>688175.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>高凌信息</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19.9779</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="G46" t="n">
+        <v>247409600</v>
+      </c>
+      <c r="H46" t="n">
+        <v>42018140.69</v>
+      </c>
+      <c r="I46" t="n">
+        <v>81947529.81</v>
+      </c>
+      <c r="J46" t="n">
+        <v>123965670.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>39929389.12</v>
+      </c>
+      <c r="L46" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M46" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3654757054</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>688261.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>东微半导</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15.1571</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1304107000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>88273496.36</v>
+      </c>
+      <c r="I47" t="n">
+        <v>209695522.46</v>
+      </c>
+      <c r="J47" t="n">
+        <v>297969018.82</v>
+      </c>
+      <c r="K47" t="n">
+        <v>121422026.1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="M47" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="N47" t="n">
+        <v>9934999446.93</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>688292.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>浩瀚深度</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="E48" t="n">
+        <v>20.0209</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G48" t="n">
+        <v>236030000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>34231013.11</v>
+      </c>
+      <c r="I48" t="n">
+        <v>122755008.85</v>
+      </c>
+      <c r="J48" t="n">
+        <v>156986021.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>88523995.73999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="M48" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3645238892.02</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>688343.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>云天励飞</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15.0877</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1475439300</v>
+      </c>
+      <c r="H49" t="n">
+        <v>163434805.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>246332871.24</v>
+      </c>
+      <c r="J49" t="n">
+        <v>409767676.26</v>
+      </c>
+      <c r="K49" t="n">
+        <v>82898066.22</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="M49" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="N49" t="n">
+        <v>23589981728</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>688802.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>沐曦股份</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>554.83</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.5242</v>
+      </c>
+      <c r="F50" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5535440800</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1049074938.45</v>
+      </c>
+      <c r="I50" t="n">
+        <v>830062442.01</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1879137380.46</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-219012496.44</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="M50" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="N50" t="n">
+        <v>18028968376.23</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>920065.BJ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>千岸科技</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9.7506</v>
+      </c>
+      <c r="F51" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="G51" t="n">
+        <v>270177800</v>
+      </c>
+      <c r="H51" t="n">
+        <v>26629621.66</v>
+      </c>
+      <c r="I51" t="n">
+        <v>27321056.18</v>
+      </c>
+      <c r="J51" t="n">
+        <v>53950677.84</v>
+      </c>
+      <c r="K51" t="n">
+        <v>691434.52</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M51" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="N51" t="n">
+        <v>609840000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6.7033</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="G52" t="n">
+        <v>358462400</v>
+      </c>
+      <c r="H52" t="n">
+        <v>37816376.85</v>
+      </c>
+      <c r="I52" t="n">
+        <v>46789508.15</v>
+      </c>
+      <c r="J52" t="n">
+        <v>84605885</v>
+      </c>
+      <c r="K52" t="n">
+        <v>8973131.300000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N52" t="n">
+        <v>857430000</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.5556</v>
+      </c>
+      <c r="F53" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="G53" t="n">
+        <v>267098200</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50298934.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>38954658.38</v>
+      </c>
+      <c r="J53" t="n">
+        <v>89253592.88</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-11344276.12</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="M53" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="N53" t="n">
+        <v>505540278.64</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>920289.BJ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>华汇智能</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="E54" t="n">
+        <v>15.3077</v>
+      </c>
+      <c r="F54" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="G54" t="n">
+        <v>198160900</v>
+      </c>
+      <c r="H54" t="n">
+        <v>18460207.57</v>
+      </c>
+      <c r="I54" t="n">
+        <v>21887494.79</v>
+      </c>
+      <c r="J54" t="n">
+        <v>40347702.36</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3427287.22</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M54" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="N54" t="n">
+        <v>433211509.66</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E55" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="G55" t="n">
+        <v>827694900</v>
+      </c>
+      <c r="H55" t="n">
+        <v>93695144.27</v>
+      </c>
+      <c r="I55" t="n">
+        <v>131982785.85</v>
+      </c>
+      <c r="J55" t="n">
+        <v>225677930.12</v>
+      </c>
+      <c r="K55" t="n">
+        <v>38287641.58</v>
+      </c>
+      <c r="L55" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M55" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1384344000</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E56" t="n">
+        <v>30</v>
+      </c>
+      <c r="F56" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1589903000</v>
+      </c>
+      <c r="H56" t="n">
+        <v>155262880.28</v>
+      </c>
+      <c r="I56" t="n">
+        <v>177631546.19</v>
+      </c>
+      <c r="J56" t="n">
+        <v>332894426.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>22368665.91</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M56" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1384344000</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,3725 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000002.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>万科A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.9398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2931911902</v>
+      </c>
+      <c r="H2" t="n">
+        <v>652662569.14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>460441061.71</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1113103630.85</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-192221507.43</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="M2" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="N2" t="n">
+        <v>35460163012.1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000504.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G3" t="n">
+        <v>358565216</v>
+      </c>
+      <c r="H3" t="n">
+        <v>47393368</v>
+      </c>
+      <c r="I3" t="n">
+        <v>68883598.29000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>116276966.29</v>
+      </c>
+      <c r="K3" t="n">
+        <v>21490230.29</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3623637601.98</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1304403941</v>
+      </c>
+      <c r="H4" t="n">
+        <v>101928883</v>
+      </c>
+      <c r="I4" t="n">
+        <v>318934391.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>420863274.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>217005508.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7473175099.61</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000668.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>荣丰控股</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-8.032299999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G5" t="n">
+        <v>160706968</v>
+      </c>
+      <c r="H5" t="n">
+        <v>59537435</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35742777</v>
+      </c>
+      <c r="J5" t="n">
+        <v>95280212</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-23794658</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="M5" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2841390571.5</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.7844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4382095039</v>
+      </c>
+      <c r="H6" t="n">
+        <v>899738367.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>700490622.12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1600228990.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-199247745.78</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="M6" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14992290608.4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1016852662</v>
+      </c>
+      <c r="H7" t="n">
+        <v>105163264.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>80863154.39</v>
+      </c>
+      <c r="J7" t="n">
+        <v>186026418.57</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-24300109.79</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3927539913.57</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.0137</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1099984574</v>
+      </c>
+      <c r="H8" t="n">
+        <v>135455539</v>
+      </c>
+      <c r="I8" t="n">
+        <v>139079256.78</v>
+      </c>
+      <c r="J8" t="n">
+        <v>274534795.78</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3623717.78</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5938878947.94</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001317.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.998200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1069318044</v>
+      </c>
+      <c r="H9" t="n">
+        <v>134105076</v>
+      </c>
+      <c r="I9" t="n">
+        <v>180607569.96</v>
+      </c>
+      <c r="J9" t="n">
+        <v>314712645.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46502493.96</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5126730919.32</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001389.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>广合科技</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.998200000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2569046584</v>
+      </c>
+      <c r="H10" t="n">
+        <v>487194173.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>642048358.41</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1129242531.71</v>
+      </c>
+      <c r="K10" t="n">
+        <v>154854185.11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>28330450472.42</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002080.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中材科技</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.996700000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8542074346</v>
+      </c>
+      <c r="H11" t="n">
+        <v>724144381.11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1279412635.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2003557016.86</v>
+      </c>
+      <c r="K11" t="n">
+        <v>555268254.64</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="N11" t="n">
+        <v>111158906204.16</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002285.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>世联行</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0346</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="G12" t="n">
+        <v>859237549</v>
+      </c>
+      <c r="H12" t="n">
+        <v>131415543.88</v>
+      </c>
+      <c r="I12" t="n">
+        <v>157645642.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>289061186.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>26230098.72</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6293249831.58</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002528.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>*ST英飞</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-10.0619</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>315998040</v>
+      </c>
+      <c r="H13" t="n">
+        <v>32246744.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24486980.15</v>
+      </c>
+      <c r="J13" t="n">
+        <v>56733724.95</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-7759764.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6101775742.37</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002528.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>*ST英飞</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-10.0619</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>764054632</v>
+      </c>
+      <c r="H14" t="n">
+        <v>101265828.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50631600.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>151897429</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-50634228.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.63</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6101775742.37</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002584.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>西陇科学</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1768872020</v>
+      </c>
+      <c r="H15" t="n">
+        <v>192584577.19</v>
+      </c>
+      <c r="I15" t="n">
+        <v>231198394.84</v>
+      </c>
+      <c r="J15" t="n">
+        <v>423782972.03</v>
+      </c>
+      <c r="K15" t="n">
+        <v>38613817.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4695919938.88</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002585.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0433</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1570497640</v>
+      </c>
+      <c r="H16" t="n">
+        <v>306446398.34</v>
+      </c>
+      <c r="I16" t="n">
+        <v>394150372.08</v>
+      </c>
+      <c r="J16" t="n">
+        <v>700596770.42</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87703973.73999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11268581625.48</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002631.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.8783</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3339989017</v>
+      </c>
+      <c r="H17" t="n">
+        <v>384384974.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>524567378.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>908952353.36</v>
+      </c>
+      <c r="K17" t="n">
+        <v>140182404.24</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11222774507.28</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002774.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>快意电梯</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-6.4841</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>375359722</v>
+      </c>
+      <c r="H18" t="n">
+        <v>129431847</v>
+      </c>
+      <c r="I18" t="n">
+        <v>40942394</v>
+      </c>
+      <c r="J18" t="n">
+        <v>170374241</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-88489453</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-23.57</v>
+      </c>
+      <c r="M18" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4714044472.55</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002792.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>通宇通讯</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2334817508</v>
+      </c>
+      <c r="H19" t="n">
+        <v>268197942.83</v>
+      </c>
+      <c r="I19" t="n">
+        <v>385141441.71</v>
+      </c>
+      <c r="J19" t="n">
+        <v>653339384.54</v>
+      </c>
+      <c r="K19" t="n">
+        <v>116943498.88</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11708867577.66</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002836.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>新宏泽</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>410160088</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85018806.09999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>39028118.37</v>
+      </c>
+      <c r="J20" t="n">
+        <v>124046924.47</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-45990687.73</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2760192000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002980.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>华盛昌</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-7.4826</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2202695743</v>
+      </c>
+      <c r="H21" t="n">
+        <v>601373096.41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>313378807.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>914751904.21</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-287994288.61</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-13.07</v>
+      </c>
+      <c r="M21" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11997423710.55</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>611042215</v>
+      </c>
+      <c r="H22" t="n">
+        <v>72662725.72</v>
+      </c>
+      <c r="I22" t="n">
+        <v>115459396.01</v>
+      </c>
+      <c r="J22" t="n">
+        <v>188122121.73</v>
+      </c>
+      <c r="K22" t="n">
+        <v>42796670.29</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2387648921.76</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>003013.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>地铁设计</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10.0156</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>314781433</v>
+      </c>
+      <c r="H23" t="n">
+        <v>139694520.25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26585102</v>
+      </c>
+      <c r="J23" t="n">
+        <v>166279622.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-113109418.25</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-35.93</v>
+      </c>
+      <c r="M23" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6956278107.75</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>003026.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中晶科技</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.8548</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1726647704</v>
+      </c>
+      <c r="H24" t="n">
+        <v>205234776.69</v>
+      </c>
+      <c r="I24" t="n">
+        <v>185238964.74</v>
+      </c>
+      <c r="J24" t="n">
+        <v>390473741.43</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-19995811.95</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5462255743.2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>300110.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>华仁药业</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20.073</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>601594888</v>
+      </c>
+      <c r="H25" t="n">
+        <v>132474624.91</v>
+      </c>
+      <c r="I25" t="n">
+        <v>135455160.08</v>
+      </c>
+      <c r="J25" t="n">
+        <v>267929784.99</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2980535.17</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3886888602.03</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300642.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>透景生命</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19.9882</v>
+      </c>
+      <c r="F26" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="G26" t="n">
+        <v>691404677</v>
+      </c>
+      <c r="H26" t="n">
+        <v>62858018.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>210367641.63</v>
+      </c>
+      <c r="J26" t="n">
+        <v>273225659.83</v>
+      </c>
+      <c r="K26" t="n">
+        <v>147509623.43</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2802308369.85</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300691.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>联合光电</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="G27" t="n">
+        <v>504945995</v>
+      </c>
+      <c r="H27" t="n">
+        <v>119683899.85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>135365100.48</v>
+      </c>
+      <c r="J27" t="n">
+        <v>255049000.33</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15681200.63</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3920309011.2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300829.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金丹科技</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.0187</v>
+      </c>
+      <c r="F28" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="G28" t="n">
+        <v>779988888</v>
+      </c>
+      <c r="H28" t="n">
+        <v>106491970.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>182786618.72</v>
+      </c>
+      <c r="J28" t="n">
+        <v>289278588.82</v>
+      </c>
+      <c r="K28" t="n">
+        <v>76294648.62</v>
+      </c>
+      <c r="L28" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4324350693.32</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>300829.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>金丹科技</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20.0187</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2008555577</v>
+      </c>
+      <c r="H29" t="n">
+        <v>303747171.36</v>
+      </c>
+      <c r="I29" t="n">
+        <v>321572453.09</v>
+      </c>
+      <c r="J29" t="n">
+        <v>625319624.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17825281.73</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4324350693.32</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301008.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>宏昌科技</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.2179</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1203293935</v>
+      </c>
+      <c r="H30" t="n">
+        <v>208029244.95</v>
+      </c>
+      <c r="I30" t="n">
+        <v>261180916.42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>469210161.37</v>
+      </c>
+      <c r="K30" t="n">
+        <v>53151671.47</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M30" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6023725834.06</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="E31" t="n">
+        <v>14.2897</v>
+      </c>
+      <c r="F31" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1374343568</v>
+      </c>
+      <c r="H31" t="n">
+        <v>102588823.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>105080109.81</v>
+      </c>
+      <c r="J31" t="n">
+        <v>207668932.9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2491286.72</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2693697734.34</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>托伦斯</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.6554</v>
+      </c>
+      <c r="F32" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1648877533</v>
+      </c>
+      <c r="H32" t="n">
+        <v>392224438.82</v>
+      </c>
+      <c r="I32" t="n">
+        <v>319453876.36</v>
+      </c>
+      <c r="J32" t="n">
+        <v>711678315.1799999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-72770562.45999999</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4322558494.6</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301688.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>格林生物</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>40</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.2756</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="G33" t="n">
+        <v>374093788</v>
+      </c>
+      <c r="H33" t="n">
+        <v>48141966.92</v>
+      </c>
+      <c r="I33" t="n">
+        <v>50448877.36</v>
+      </c>
+      <c r="J33" t="n">
+        <v>98590844.28</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2306910.44</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1039398120</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.4762</v>
+      </c>
+      <c r="F34" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1920132763</v>
+      </c>
+      <c r="H34" t="n">
+        <v>283484851.37</v>
+      </c>
+      <c r="I34" t="n">
+        <v>193951080.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>477435931.63</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-89533771.11</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="M34" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3609103040.4</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="G35" t="n">
+        <v>954342517</v>
+      </c>
+      <c r="H35" t="n">
+        <v>98104515.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>154982920.57</v>
+      </c>
+      <c r="J35" t="n">
+        <v>253087436.32</v>
+      </c>
+      <c r="K35" t="n">
+        <v>56878404.82</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M35" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2196546813.09</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600088.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>中视传媒</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-6.0279</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="G36" t="n">
+        <v>613934104</v>
+      </c>
+      <c r="H36" t="n">
+        <v>63705095.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>51593822.53</v>
+      </c>
+      <c r="J36" t="n">
+        <v>115298917.63</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-12111272.57</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M36" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5890031784</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.986000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2756484586</v>
+      </c>
+      <c r="H37" t="n">
+        <v>399703445.95</v>
+      </c>
+      <c r="I37" t="n">
+        <v>424809291.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>824512737.85</v>
+      </c>
+      <c r="K37" t="n">
+        <v>25105845.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M37" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10108085683.5</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600325.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>华发股份</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E38" t="n">
+        <v>10.0806</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G38" t="n">
+        <v>418253706</v>
+      </c>
+      <c r="H38" t="n">
+        <v>63031692.56</v>
+      </c>
+      <c r="I38" t="n">
+        <v>90633429.18000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>153665121.74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>27601736.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7513375276.68</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600448.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>华纺股份</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.887</v>
+      </c>
+      <c r="F39" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="G39" t="n">
+        <v>938093849</v>
+      </c>
+      <c r="H39" t="n">
+        <v>125677900.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>60617780</v>
+      </c>
+      <c r="J39" t="n">
+        <v>186295680.2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-65060120.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="M39" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2449998485.18</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600593.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>大连圣亚</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0113</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1947008778</v>
+      </c>
+      <c r="H40" t="n">
+        <v>228523167.93</v>
+      </c>
+      <c r="I40" t="n">
+        <v>366757216.47</v>
+      </c>
+      <c r="J40" t="n">
+        <v>595280384.4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>138234048.54</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6255816000</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600606.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>绿地控股</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10.3448</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G41" t="n">
+        <v>847489744</v>
+      </c>
+      <c r="H41" t="n">
+        <v>134656732.62</v>
+      </c>
+      <c r="I41" t="n">
+        <v>153000130.03</v>
+      </c>
+      <c r="J41" t="n">
+        <v>287656862.65</v>
+      </c>
+      <c r="K41" t="n">
+        <v>18343397.41</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M41" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="N41" t="n">
+        <v>22486749302.4</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600606.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>绿地控股</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10.3448</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1553031211</v>
+      </c>
+      <c r="H42" t="n">
+        <v>204751497.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>313817151.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>518568648.58</v>
+      </c>
+      <c r="K42" t="n">
+        <v>109065654.42</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M42" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="N42" t="n">
+        <v>22486749302.4</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600712.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.0935</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="G43" t="n">
+        <v>420821019</v>
+      </c>
+      <c r="H43" t="n">
+        <v>64368689.62</v>
+      </c>
+      <c r="I43" t="n">
+        <v>86010399.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>150379089.42</v>
+      </c>
+      <c r="K43" t="n">
+        <v>21641710.18</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3172638905.19</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0418</v>
+      </c>
+      <c r="F44" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1415415480</v>
+      </c>
+      <c r="H44" t="n">
+        <v>139647717</v>
+      </c>
+      <c r="I44" t="n">
+        <v>305907979</v>
+      </c>
+      <c r="J44" t="n">
+        <v>445555696</v>
+      </c>
+      <c r="K44" t="n">
+        <v>166260262</v>
+      </c>
+      <c r="L44" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M44" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5056801400.25</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.0418</v>
+      </c>
+      <c r="F45" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4476733060</v>
+      </c>
+      <c r="H45" t="n">
+        <v>442171713.07</v>
+      </c>
+      <c r="I45" t="n">
+        <v>669677413.3200001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1111849126.39</v>
+      </c>
+      <c r="K45" t="n">
+        <v>227505700.25</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M45" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5056801400.25</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>601579.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>会稽山</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9.9878</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3120210547</v>
+      </c>
+      <c r="H46" t="n">
+        <v>580825891.0700001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>413704736.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>994530627.5700001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-167121154.57</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M46" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="N46" t="n">
+        <v>17318218333.08</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1240525631</v>
+      </c>
+      <c r="H47" t="n">
+        <v>213731290.7</v>
+      </c>
+      <c r="I47" t="n">
+        <v>91682591.40000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>305413882.1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-122048699.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-9.84</v>
+      </c>
+      <c r="M47" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="N47" t="n">
+        <v>12108210631</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603001.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>奥康国际</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.9712</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G48" t="n">
+        <v>698883818</v>
+      </c>
+      <c r="H48" t="n">
+        <v>138252038</v>
+      </c>
+      <c r="I48" t="n">
+        <v>198519277.55</v>
+      </c>
+      <c r="J48" t="n">
+        <v>336771315.55</v>
+      </c>
+      <c r="K48" t="n">
+        <v>60267239.55</v>
+      </c>
+      <c r="L48" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4599240600</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603120.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>肯特催化</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.6952</v>
+      </c>
+      <c r="F49" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="G49" t="n">
+        <v>643549923</v>
+      </c>
+      <c r="H49" t="n">
+        <v>120377257.38</v>
+      </c>
+      <c r="I49" t="n">
+        <v>170894568.23</v>
+      </c>
+      <c r="J49" t="n">
+        <v>291271825.61</v>
+      </c>
+      <c r="K49" t="n">
+        <v>50517310.85</v>
+      </c>
+      <c r="L49" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="M49" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2349421000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603226.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>菲林格尔</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-6.4227</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="G50" t="n">
+        <v>472528569</v>
+      </c>
+      <c r="H50" t="n">
+        <v>114876750.56</v>
+      </c>
+      <c r="I50" t="n">
+        <v>56094226.01</v>
+      </c>
+      <c r="J50" t="n">
+        <v>170970976.57</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-58782524.55</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-12.44</v>
+      </c>
+      <c r="M50" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="N50" t="n">
+        <v>13000334028.9</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-1.3024</v>
+      </c>
+      <c r="F51" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="G51" t="n">
+        <v>997118407</v>
+      </c>
+      <c r="H51" t="n">
+        <v>205869717.74</v>
+      </c>
+      <c r="I51" t="n">
+        <v>77113515.15000001</v>
+      </c>
+      <c r="J51" t="n">
+        <v>282983232.89</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-128756202.59</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="M51" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1733995061.75</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603289.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>泰瑞机器</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0524</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="G52" t="n">
+        <v>182383943</v>
+      </c>
+      <c r="H52" t="n">
+        <v>39846469</v>
+      </c>
+      <c r="I52" t="n">
+        <v>52579953.7</v>
+      </c>
+      <c r="J52" t="n">
+        <v>92426422.7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>12733484.7</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="M52" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3083611655.74</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>605198.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>安德利</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-10.0023</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G53" t="n">
+        <v>358205391</v>
+      </c>
+      <c r="H53" t="n">
+        <v>84147106</v>
+      </c>
+      <c r="I53" t="n">
+        <v>58360021</v>
+      </c>
+      <c r="J53" t="n">
+        <v>142507127</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-25787085</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="N53" t="n">
+        <v>20909727440</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>688026.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>洁特生物</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="E54" t="n">
+        <v>19.981</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="G54" t="n">
+        <v>398049000</v>
+      </c>
+      <c r="H54" t="n">
+        <v>91686638.08</v>
+      </c>
+      <c r="I54" t="n">
+        <v>83652034.65000001</v>
+      </c>
+      <c r="J54" t="n">
+        <v>175338672.73</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-8034603.43</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="M54" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3539991857.74</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>688112.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>鼎阳科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20.0026</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G55" t="n">
+        <v>942813900</v>
+      </c>
+      <c r="H55" t="n">
+        <v>163269859.66</v>
+      </c>
+      <c r="I55" t="n">
+        <v>223772368.57</v>
+      </c>
+      <c r="J55" t="n">
+        <v>387042228.23</v>
+      </c>
+      <c r="K55" t="n">
+        <v>60502508.91</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="M55" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="N55" t="n">
+        <v>14649397890.57</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>688112.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>鼎阳科技</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20.0026</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1705871600</v>
+      </c>
+      <c r="H56" t="n">
+        <v>324569228.47</v>
+      </c>
+      <c r="I56" t="n">
+        <v>364079779.8</v>
+      </c>
+      <c r="J56" t="n">
+        <v>688649008.27</v>
+      </c>
+      <c r="K56" t="n">
+        <v>39510551.33</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M56" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="N56" t="n">
+        <v>14649397890.57</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G57" t="n">
+        <v>19940400</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3028922.09</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3410565.06</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6439487.15</v>
+      </c>
+      <c r="K57" t="n">
+        <v>381642.97</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M57" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="N57" t="n">
+        <v>279680000.46</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>118.84</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20.004</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1089562800</v>
+      </c>
+      <c r="H58" t="n">
+        <v>118294081.73</v>
+      </c>
+      <c r="I58" t="n">
+        <v>129845076.85</v>
+      </c>
+      <c r="J58" t="n">
+        <v>248139158.58</v>
+      </c>
+      <c r="K58" t="n">
+        <v>11550995.12</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M58" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8308990114.52</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>118.84</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20.004</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3191243800</v>
+      </c>
+      <c r="H59" t="n">
+        <v>350752995.66</v>
+      </c>
+      <c r="I59" t="n">
+        <v>387826555.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>738579550.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>37073559.63</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M59" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N59" t="n">
+        <v>8308990114.52</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>688315.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>诺禾致源</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>320788200</v>
+      </c>
+      <c r="H60" t="n">
+        <v>101399728.59</v>
+      </c>
+      <c r="I60" t="n">
+        <v>108924585.14</v>
+      </c>
+      <c r="J60" t="n">
+        <v>210324313.73</v>
+      </c>
+      <c r="K60" t="n">
+        <v>7524856.55</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M60" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7566516000</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>920117.BJ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>龙鑫智能</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8.122199999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="G61" t="n">
+        <v>282838900</v>
+      </c>
+      <c r="H61" t="n">
+        <v>49587211.16</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31291814.38</v>
+      </c>
+      <c r="J61" t="n">
+        <v>80879025.54000001</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-18295396.78</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="M61" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="N61" t="n">
+        <v>629666193.45</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-4.3727</v>
+      </c>
+      <c r="F62" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="G62" t="n">
+        <v>208845900</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23263642.14</v>
+      </c>
+      <c r="I62" t="n">
+        <v>30746314.47</v>
+      </c>
+      <c r="J62" t="n">
+        <v>54009956.61</v>
+      </c>
+      <c r="K62" t="n">
+        <v>7482672.33</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="N62" t="n">
+        <v>483434630.56</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>920288.BJ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>华大海天</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4.7745</v>
+      </c>
+      <c r="F63" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="G63" t="n">
+        <v>150018900</v>
+      </c>
+      <c r="H63" t="n">
+        <v>20004075.29</v>
+      </c>
+      <c r="I63" t="n">
+        <v>25273536.02</v>
+      </c>
+      <c r="J63" t="n">
+        <v>45277611.31</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5269460.73</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M63" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="N63" t="n">
+        <v>353130000</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>920289.BJ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>华汇智能</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.3002</v>
+      </c>
+      <c r="F64" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="G64" t="n">
+        <v>182034200</v>
+      </c>
+      <c r="H64" t="n">
+        <v>31221303.73</v>
+      </c>
+      <c r="I64" t="n">
+        <v>27909613.28</v>
+      </c>
+      <c r="J64" t="n">
+        <v>59130917.01</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-3311690.45</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="M64" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="N64" t="n">
+        <v>431911008.13</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.443</v>
+      </c>
+      <c r="F65" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="G65" t="n">
+        <v>922502600</v>
+      </c>
+      <c r="H65" t="n">
+        <v>128339732.1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>130268286.32</v>
+      </c>
+      <c r="J65" t="n">
+        <v>258608018.42</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1928554.22</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M65" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1445850000</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>920427.BJ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>华维设计</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="E66" t="n">
+        <v>29.9176</v>
+      </c>
+      <c r="F66" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="G66" t="n">
+        <v>120722200</v>
+      </c>
+      <c r="H66" t="n">
+        <v>21495787.44</v>
+      </c>
+      <c r="I66" t="n">
+        <v>28743539.42</v>
+      </c>
+      <c r="J66" t="n">
+        <v>50239326.86</v>
+      </c>
+      <c r="K66" t="n">
+        <v>7247751.98</v>
+      </c>
+      <c r="L66" t="n">
+        <v>6</v>
+      </c>
+      <c r="M66" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="N66" t="n">
+        <v>560897990.17</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>920478.BJ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>峆一药业</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="E67" t="n">
+        <v>29.9056</v>
+      </c>
+      <c r="F67" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="G67" t="n">
+        <v>241912600</v>
+      </c>
+      <c r="H67" t="n">
+        <v>41938839.09</v>
+      </c>
+      <c r="I67" t="n">
+        <v>48348356.74</v>
+      </c>
+      <c r="J67" t="n">
+        <v>90287195.83</v>
+      </c>
+      <c r="K67" t="n">
+        <v>6409517.65</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M67" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="N67" t="n">
+        <v>829511884.58</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4165 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000002.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>万科A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.3836</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7389607169</v>
+      </c>
+      <c r="H2" t="n">
+        <v>936767842.67</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1061260025.45</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1998027868.12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>124492182.78</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M2" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37014581116.74</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.0313</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1412921349</v>
+      </c>
+      <c r="H3" t="n">
+        <v>202237378.68</v>
+      </c>
+      <c r="I3" t="n">
+        <v>274616275.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>476853653.98</v>
+      </c>
+      <c r="K3" t="n">
+        <v>72378896.62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="N3" t="n">
+        <v>8222835297.69</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.0313</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2717325290</v>
+      </c>
+      <c r="H4" t="n">
+        <v>249076792.99</v>
+      </c>
+      <c r="I4" t="n">
+        <v>467641031</v>
+      </c>
+      <c r="J4" t="n">
+        <v>716717823.99</v>
+      </c>
+      <c r="K4" t="n">
+        <v>218564238.01</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8222835297.69</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000607.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华媒控股</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.9338</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>423040393</v>
+      </c>
+      <c r="H5" t="n">
+        <v>91358263.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>95513963</v>
+      </c>
+      <c r="J5" t="n">
+        <v>186872226.52</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4155699.48</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4407609596.64</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000610.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>*ST西旅</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.9762</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G6" t="n">
+        <v>164786006</v>
+      </c>
+      <c r="H6" t="n">
+        <v>58963589.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27570174</v>
+      </c>
+      <c r="J6" t="n">
+        <v>86533763.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-31393415.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-19.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1785122548.52</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000668.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>荣丰控股</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-9.9742</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="G7" t="n">
+        <v>201315381</v>
+      </c>
+      <c r="H7" t="n">
+        <v>74091191</v>
+      </c>
+      <c r="I7" t="n">
+        <v>29658211</v>
+      </c>
+      <c r="J7" t="n">
+        <v>103749402</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-44432980</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-22.07</v>
+      </c>
+      <c r="M7" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2557985723.8</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000676.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>智度股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.0443</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1277652015</v>
+      </c>
+      <c r="H8" t="n">
+        <v>152125023.43</v>
+      </c>
+      <c r="I8" t="n">
+        <v>156584523.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>308709546.93</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4459500.07</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9379761073.4</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000756.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>新华制药</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.0204</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1563389474</v>
+      </c>
+      <c r="H9" t="n">
+        <v>129284993.11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>274973254</v>
+      </c>
+      <c r="J9" t="n">
+        <v>404258247.11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>145688260.89</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8051808783.54</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000756.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>新华制药</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.0204</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2083891267</v>
+      </c>
+      <c r="H10" t="n">
+        <v>137073109.11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>317368579</v>
+      </c>
+      <c r="J10" t="n">
+        <v>454441688.11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>180295469.89</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="M10" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8051808783.54</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5152772565</v>
+      </c>
+      <c r="H11" t="n">
+        <v>708217961.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>748597668.21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1456815629.61</v>
+      </c>
+      <c r="K11" t="n">
+        <v>40379706.81</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M11" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15004189251.74</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000910.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>大亚圣象</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0639</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>373106277</v>
+      </c>
+      <c r="H12" t="n">
+        <v>38349578.37</v>
+      </c>
+      <c r="I12" t="n">
+        <v>69204178.03</v>
+      </c>
+      <c r="J12" t="n">
+        <v>107553756.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>30854599.66</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3770450011.25</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>000910.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>大亚圣象</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0639</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>675186094</v>
+      </c>
+      <c r="H13" t="n">
+        <v>76934174.87</v>
+      </c>
+      <c r="I13" t="n">
+        <v>82566425.43000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>159500600.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5632250.56</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3770450011.25</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3495</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14112776318.11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14112776318.11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14112776318.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14112776318.11</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9575764924.049999</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>001234.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>泰慕士</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0038</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>263729540</v>
+      </c>
+      <c r="H15" t="n">
+        <v>64843227</v>
+      </c>
+      <c r="I15" t="n">
+        <v>61771490</v>
+      </c>
+      <c r="J15" t="n">
+        <v>126614717</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-3071737</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2677588875</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002028.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>思源电气</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-7.5527</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2289599760</v>
+      </c>
+      <c r="H16" t="n">
+        <v>640129634.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>413780979.95</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1053910614.34</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-226348654.44</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="N16" t="n">
+        <v>78423530672.39999</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002141.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>贤丰控股</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0741</v>
+      </c>
+      <c r="F17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2052062960</v>
+      </c>
+      <c r="H17" t="n">
+        <v>147264301</v>
+      </c>
+      <c r="I17" t="n">
+        <v>405700125</v>
+      </c>
+      <c r="J17" t="n">
+        <v>552964426</v>
+      </c>
+      <c r="K17" t="n">
+        <v>258435824</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7674712979.14</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002172.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-3.6145</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1497682373</v>
+      </c>
+      <c r="H18" t="n">
+        <v>242950284.31</v>
+      </c>
+      <c r="I18" t="n">
+        <v>132570312.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>375520596.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-110379972.02</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4284788088</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002303.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>美盈森</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.0478</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>663851728</v>
+      </c>
+      <c r="H19" t="n">
+        <v>119621070.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>217572148.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>337193218.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>97951078.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7364808322.5</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002453.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>华软科技</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="G20" t="n">
+        <v>822437801</v>
+      </c>
+      <c r="H20" t="n">
+        <v>124918174.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>89130595.90000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>214048769.98</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-35787578.18</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3414868848.18</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002584.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>西陇科学</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.0984</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1297276674</v>
+      </c>
+      <c r="H21" t="n">
+        <v>179700090.14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>185894112.06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>365594202.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6194021.92</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4503464203.68</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002589.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>瑞康医药</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2778</v>
+      </c>
+      <c r="F22" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1743978060</v>
+      </c>
+      <c r="H22" t="n">
+        <v>350042874.58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>250159435.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>600202310.48</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-99883438.68000001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="M22" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4902473657.32</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002614.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>奥佳华</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G23" t="n">
+        <v>151658559</v>
+      </c>
+      <c r="H23" t="n">
+        <v>13603941</v>
+      </c>
+      <c r="I23" t="n">
+        <v>39214789.56</v>
+      </c>
+      <c r="J23" t="n">
+        <v>52818730.56</v>
+      </c>
+      <c r="K23" t="n">
+        <v>25610848.56</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="M23" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3035974139.68</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.4913</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="G24" t="n">
+        <v>814802171</v>
+      </c>
+      <c r="H24" t="n">
+        <v>126670966.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>129053929.43</v>
+      </c>
+      <c r="J24" t="n">
+        <v>255724895.58</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2382963.28</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M24" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4930973240</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002687.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>乔治白</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-8.7218</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="G25" t="n">
+        <v>283841372</v>
+      </c>
+      <c r="H25" t="n">
+        <v>93323443.20999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>67935821.29000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>161259264.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-25387621.92</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-8.94</v>
+      </c>
+      <c r="M25" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2510652537.41</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002768.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>国恩股份</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10.0073</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>997160967</v>
+      </c>
+      <c r="H26" t="n">
+        <v>201567744</v>
+      </c>
+      <c r="I26" t="n">
+        <v>298362987.66</v>
+      </c>
+      <c r="J26" t="n">
+        <v>499930731.66</v>
+      </c>
+      <c r="K26" t="n">
+        <v>96795243.66</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>18884053867.62</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>003026.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中晶科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.8855</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1459362557</v>
+      </c>
+      <c r="H27" t="n">
+        <v>189733681.45</v>
+      </c>
+      <c r="I27" t="n">
+        <v>124843194.93</v>
+      </c>
+      <c r="J27" t="n">
+        <v>314576876.38</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-64890486.52</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="M27" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5140776980.8</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300110.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>华仁药业</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.0608</v>
+      </c>
+      <c r="F28" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1285470564</v>
+      </c>
+      <c r="H28" t="n">
+        <v>155619668.56</v>
+      </c>
+      <c r="I28" t="n">
+        <v>226246319.62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>381865988.18</v>
+      </c>
+      <c r="K28" t="n">
+        <v>70626651.06</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4666629172.65</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>300110.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>华仁药业</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20.0608</v>
+      </c>
+      <c r="F29" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1887065451</v>
+      </c>
+      <c r="H29" t="n">
+        <v>243428583.91</v>
+      </c>
+      <c r="I29" t="n">
+        <v>284096593.88</v>
+      </c>
+      <c r="J29" t="n">
+        <v>527525177.79</v>
+      </c>
+      <c r="K29" t="n">
+        <v>40668009.97</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M29" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4666629172.65</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>300324.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>旋极信息</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1162992703</v>
+      </c>
+      <c r="H30" t="n">
+        <v>143129338.55</v>
+      </c>
+      <c r="I30" t="n">
+        <v>257789627.26</v>
+      </c>
+      <c r="J30" t="n">
+        <v>400918965.81</v>
+      </c>
+      <c r="K30" t="n">
+        <v>114660288.71</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7079331060.72</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300642.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>透景生命</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.2924</v>
+      </c>
+      <c r="F31" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1021639549</v>
+      </c>
+      <c r="H31" t="n">
+        <v>221625816.58</v>
+      </c>
+      <c r="I31" t="n">
+        <v>84534843</v>
+      </c>
+      <c r="J31" t="n">
+        <v>306160659.58</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-137090973.58</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-13.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2894571102.42</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301047.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>义翘神州</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>136.22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2454359058</v>
+      </c>
+      <c r="H32" t="n">
+        <v>184098630.44</v>
+      </c>
+      <c r="I32" t="n">
+        <v>551571127.26</v>
+      </c>
+      <c r="J32" t="n">
+        <v>735669757.7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>367472496.82</v>
+      </c>
+      <c r="L32" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M32" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="N32" t="n">
+        <v>16289272192.62</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301234.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>五洲医疗</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>139.74</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>682924429</v>
+      </c>
+      <c r="H33" t="n">
+        <v>107213278.28</v>
+      </c>
+      <c r="I33" t="n">
+        <v>188177906.15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>295391184.43</v>
+      </c>
+      <c r="K33" t="n">
+        <v>80964627.87</v>
+      </c>
+      <c r="L33" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M33" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5634040953.24</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1541729153</v>
+      </c>
+      <c r="H34" t="n">
+        <v>109062755.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>165941050.94</v>
+      </c>
+      <c r="J34" t="n">
+        <v>275003805.98</v>
+      </c>
+      <c r="K34" t="n">
+        <v>56878295.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="M34" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2693697734.34</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301686.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>中塑股份</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>433</v>
+      </c>
+      <c r="E35" t="n">
+        <v>683.2851000000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2339147535</v>
+      </c>
+      <c r="H35" t="n">
+        <v>56776244.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>241291745.19</v>
+      </c>
+      <c r="J35" t="n">
+        <v>298067989.39</v>
+      </c>
+      <c r="K35" t="n">
+        <v>184515500.99</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3781413681</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.8979</v>
+      </c>
+      <c r="F36" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1698597076</v>
+      </c>
+      <c r="H36" t="n">
+        <v>240433384.35</v>
+      </c>
+      <c r="I36" t="n">
+        <v>144083216.47</v>
+      </c>
+      <c r="J36" t="n">
+        <v>384516600.82</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-96350167.88</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3540604912.52</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.9102</v>
+      </c>
+      <c r="F37" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>778702054</v>
+      </c>
+      <c r="H37" t="n">
+        <v>129501150.03</v>
+      </c>
+      <c r="I37" t="n">
+        <v>76945926.76000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>206447076.79</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-52555223.27</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2154587943.69</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.5714</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4133150168</v>
+      </c>
+      <c r="H38" t="n">
+        <v>527193309.76</v>
+      </c>
+      <c r="I38" t="n">
+        <v>527078457.83</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1054271767.59</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-114851.93</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10570169600.46</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600448.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>华纺股份</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-7.9692</v>
+      </c>
+      <c r="F39" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>906982801</v>
+      </c>
+      <c r="H39" t="n">
+        <v>63498832.27</v>
+      </c>
+      <c r="I39" t="n">
+        <v>48010340</v>
+      </c>
+      <c r="J39" t="n">
+        <v>111509172.27</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-15488492.27</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="M39" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2254754389.96</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600499.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>科达制造</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-9.9328</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1250252987</v>
+      </c>
+      <c r="H40" t="n">
+        <v>569596538.5599999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>92398157.79000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>661994696.35</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-477198380.77</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-38.17</v>
+      </c>
+      <c r="M40" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="N40" t="n">
+        <v>23129348075.46</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600503.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>华丽家族</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.8765</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G41" t="n">
+        <v>769633805</v>
+      </c>
+      <c r="H41" t="n">
+        <v>126112450.97</v>
+      </c>
+      <c r="I41" t="n">
+        <v>146749869.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>272862320.07</v>
+      </c>
+      <c r="K41" t="n">
+        <v>20637418.13</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M41" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4278114300</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.9474</v>
+      </c>
+      <c r="F42" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1351039411</v>
+      </c>
+      <c r="H42" t="n">
+        <v>123557904.18</v>
+      </c>
+      <c r="I42" t="n">
+        <v>143882605.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>267440509.53</v>
+      </c>
+      <c r="K42" t="n">
+        <v>20324701.17</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4027687939.56</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600640.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>国脉文化</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.9378</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1677774902</v>
+      </c>
+      <c r="H43" t="n">
+        <v>239996786.17</v>
+      </c>
+      <c r="I43" t="n">
+        <v>324499740.88</v>
+      </c>
+      <c r="J43" t="n">
+        <v>564496527.05</v>
+      </c>
+      <c r="K43" t="n">
+        <v>84502954.70999999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="M43" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10614703469.4</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600664.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0606</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2779141466</v>
+      </c>
+      <c r="H44" t="n">
+        <v>338097305</v>
+      </c>
+      <c r="I44" t="n">
+        <v>598317576.28</v>
+      </c>
+      <c r="J44" t="n">
+        <v>936414881.28</v>
+      </c>
+      <c r="K44" t="n">
+        <v>260220271.28</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="M44" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="N44" t="n">
+        <v>22868069674.08</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600664.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.0606</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4352365561</v>
+      </c>
+      <c r="H45" t="n">
+        <v>375286482.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>813009424.66</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1188295906.86</v>
+      </c>
+      <c r="K45" t="n">
+        <v>437722942.46</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="M45" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>22868069674.08</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.038</v>
+      </c>
+      <c r="F46" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2739441731</v>
+      </c>
+      <c r="H46" t="n">
+        <v>353000391.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>349866666.98</v>
+      </c>
+      <c r="J46" t="n">
+        <v>702867058.28</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-3133724.32</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M46" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5564404278.45</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600743.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9.8712</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G47" t="n">
+        <v>148119927</v>
+      </c>
+      <c r="H47" t="n">
+        <v>27324328.08</v>
+      </c>
+      <c r="I47" t="n">
+        <v>38009084.21</v>
+      </c>
+      <c r="J47" t="n">
+        <v>65333412.29</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10684756.13</v>
+      </c>
+      <c r="L47" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M47" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6006018237.44</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600792.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>云煤能源</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5.3114</v>
+      </c>
+      <c r="F48" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1033002301</v>
+      </c>
+      <c r="H48" t="n">
+        <v>127978513.07</v>
+      </c>
+      <c r="I48" t="n">
+        <v>118696961</v>
+      </c>
+      <c r="J48" t="n">
+        <v>246675474.07</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-9281552.07</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M48" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6382060700</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.7731</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4868942313</v>
+      </c>
+      <c r="H49" t="n">
+        <v>487858445.32</v>
+      </c>
+      <c r="I49" t="n">
+        <v>691793778.62</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1179652223.94</v>
+      </c>
+      <c r="K49" t="n">
+        <v>203935333.3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M49" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="N49" t="n">
+        <v>12094560000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>601123.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-4.908</v>
+      </c>
+      <c r="F50" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="G50" t="n">
+        <v>983744677</v>
+      </c>
+      <c r="H50" t="n">
+        <v>154359662.41</v>
+      </c>
+      <c r="I50" t="n">
+        <v>118012037.91</v>
+      </c>
+      <c r="J50" t="n">
+        <v>272371700.32</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-36347624.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="M50" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1782405598.8</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603020.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>爱普股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0239</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G51" t="n">
+        <v>353265036</v>
+      </c>
+      <c r="H51" t="n">
+        <v>53357203</v>
+      </c>
+      <c r="I51" t="n">
+        <v>76614169</v>
+      </c>
+      <c r="J51" t="n">
+        <v>129971372</v>
+      </c>
+      <c r="K51" t="n">
+        <v>23256966</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="M51" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5195070414.42</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603020.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>爱普股份</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0239</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G52" t="n">
+        <v>832377369</v>
+      </c>
+      <c r="H52" t="n">
+        <v>80359809</v>
+      </c>
+      <c r="I52" t="n">
+        <v>151246207.25</v>
+      </c>
+      <c r="J52" t="n">
+        <v>231606016.25</v>
+      </c>
+      <c r="K52" t="n">
+        <v>70886398.25</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="M52" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5195070414.42</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603068.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>博通集成</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.0023</v>
+      </c>
+      <c r="F53" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2786085116</v>
+      </c>
+      <c r="H53" t="n">
+        <v>255615460.42</v>
+      </c>
+      <c r="I53" t="n">
+        <v>480519072.04</v>
+      </c>
+      <c r="J53" t="n">
+        <v>736134532.46</v>
+      </c>
+      <c r="K53" t="n">
+        <v>224903611.62</v>
+      </c>
+      <c r="L53" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="M53" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7311595156.23</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603226.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>菲林格尔</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-10.0082</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G54" t="n">
+        <v>380653489</v>
+      </c>
+      <c r="H54" t="n">
+        <v>82468107.45999999</v>
+      </c>
+      <c r="I54" t="n">
+        <v>50744085.66</v>
+      </c>
+      <c r="J54" t="n">
+        <v>133212193.12</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-31724021.8</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="M54" t="n">
+        <v>35</v>
+      </c>
+      <c r="N54" t="n">
+        <v>11699234150.7</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.979799999999999</v>
+      </c>
+      <c r="F55" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2046145592</v>
+      </c>
+      <c r="H55" t="n">
+        <v>168848459.44</v>
+      </c>
+      <c r="I55" t="n">
+        <v>97715926</v>
+      </c>
+      <c r="J55" t="n">
+        <v>266564385.44</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-71132533.44</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="M55" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5765960130</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-1.5258</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="G56" t="n">
+        <v>719809357</v>
+      </c>
+      <c r="H56" t="n">
+        <v>73464521.64</v>
+      </c>
+      <c r="I56" t="n">
+        <v>37749409.59</v>
+      </c>
+      <c r="J56" t="n">
+        <v>111213931.23</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-35715112.05</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M56" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1707538229.88</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603375.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>盛景微</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F57" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G57" t="n">
+        <v>466901023</v>
+      </c>
+      <c r="H57" t="n">
+        <v>148550582.24</v>
+      </c>
+      <c r="I57" t="n">
+        <v>64133716</v>
+      </c>
+      <c r="J57" t="n">
+        <v>212684298.24</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-84416866.23999999</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-18.08</v>
+      </c>
+      <c r="M57" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3088272582.18</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603378.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>*ST亚士</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G58" t="n">
+        <v>19667178</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12494430</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4558635</v>
+      </c>
+      <c r="J58" t="n">
+        <v>17053065</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-7935795</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-40.35</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2275848169.02</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603580.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>艾艾精工</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9.995799999999999</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1780125043</v>
+      </c>
+      <c r="H59" t="n">
+        <v>210862791</v>
+      </c>
+      <c r="I59" t="n">
+        <v>325083523.07</v>
+      </c>
+      <c r="J59" t="n">
+        <v>535946314.07</v>
+      </c>
+      <c r="K59" t="n">
+        <v>114220732.07</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="M59" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="N59" t="n">
+        <v>10281367376</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603636.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10.0275</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G60" t="n">
+        <v>136712405</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16561476</v>
+      </c>
+      <c r="I60" t="n">
+        <v>62324208</v>
+      </c>
+      <c r="J60" t="n">
+        <v>78885684</v>
+      </c>
+      <c r="K60" t="n">
+        <v>45762732</v>
+      </c>
+      <c r="L60" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="M60" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4648687789.23</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603903.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>中持股份</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10.0144</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="G61" t="n">
+        <v>289022451</v>
+      </c>
+      <c r="H61" t="n">
+        <v>58353620</v>
+      </c>
+      <c r="I61" t="n">
+        <v>85879568</v>
+      </c>
+      <c r="J61" t="n">
+        <v>144233188</v>
+      </c>
+      <c r="K61" t="n">
+        <v>27525948</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M61" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3898728459.6</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>605198.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>安德利</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-8.539300000000001</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G62" t="n">
+        <v>680300117</v>
+      </c>
+      <c r="H62" t="n">
+        <v>93851505.86</v>
+      </c>
+      <c r="I62" t="n">
+        <v>110667529.78</v>
+      </c>
+      <c r="J62" t="n">
+        <v>204519035.64</v>
+      </c>
+      <c r="K62" t="n">
+        <v>16816023.92</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M62" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="N62" t="n">
+        <v>19124189840</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>688105.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>诺唯赞</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="E63" t="n">
+        <v>15.5022</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G63" t="n">
+        <v>987247200</v>
+      </c>
+      <c r="H63" t="n">
+        <v>131467397.01</v>
+      </c>
+      <c r="I63" t="n">
+        <v>262463163.97</v>
+      </c>
+      <c r="J63" t="n">
+        <v>393930560.98</v>
+      </c>
+      <c r="K63" t="n">
+        <v>130995766.96</v>
+      </c>
+      <c r="L63" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="M63" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="N63" t="n">
+        <v>13674254942.8</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688117.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>圣诺生物</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-18.6075</v>
+      </c>
+      <c r="F64" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="G64" t="n">
+        <v>954151300</v>
+      </c>
+      <c r="H64" t="n">
+        <v>154539942.13</v>
+      </c>
+      <c r="I64" t="n">
+        <v>91101049.95999999</v>
+      </c>
+      <c r="J64" t="n">
+        <v>245640992.09</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-63438892.17</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="M64" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4404603976.31</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688315.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>诺禾致源</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.6205</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1529198400</v>
+      </c>
+      <c r="H65" t="n">
+        <v>311946563.26</v>
+      </c>
+      <c r="I65" t="n">
+        <v>265108506.18</v>
+      </c>
+      <c r="J65" t="n">
+        <v>577055069.4400001</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-46838057.08</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="M65" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7916124000</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688622.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>*ST禾信</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>138.06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.0168</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G66" t="n">
+        <v>177919700</v>
+      </c>
+      <c r="H66" t="n">
+        <v>23254795.81</v>
+      </c>
+      <c r="I66" t="n">
+        <v>29751920.53</v>
+      </c>
+      <c r="J66" t="n">
+        <v>53006716.34</v>
+      </c>
+      <c r="K66" t="n">
+        <v>6497124.72</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="N66" t="n">
+        <v>9728469829.26</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>688781.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>视涯科技</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20.0046</v>
+      </c>
+      <c r="F67" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>576188200</v>
+      </c>
+      <c r="H67" t="n">
+        <v>53283293.66</v>
+      </c>
+      <c r="I67" t="n">
+        <v>84804953.17</v>
+      </c>
+      <c r="J67" t="n">
+        <v>138088246.83</v>
+      </c>
+      <c r="K67" t="n">
+        <v>31521659.51</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="M67" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2121383289.15</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>688781.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>视涯科技</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="E68" t="n">
+        <v>20.0046</v>
+      </c>
+      <c r="F68" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>760403500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>63459239.55</v>
+      </c>
+      <c r="I68" t="n">
+        <v>112433034.7</v>
+      </c>
+      <c r="J68" t="n">
+        <v>175892274.25</v>
+      </c>
+      <c r="K68" t="n">
+        <v>48973795.15</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="M68" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2121383289.15</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>920065.BJ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>千岸科技</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6.2745</v>
+      </c>
+      <c r="F69" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="G69" t="n">
+        <v>228072600</v>
+      </c>
+      <c r="H69" t="n">
+        <v>38984883.13</v>
+      </c>
+      <c r="I69" t="n">
+        <v>24937079.02</v>
+      </c>
+      <c r="J69" t="n">
+        <v>63921962.15</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-14047804.11</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="M69" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="N69" t="n">
+        <v>640237500</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-3.0783</v>
+      </c>
+      <c r="F70" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="G70" t="n">
+        <v>189162400</v>
+      </c>
+      <c r="H70" t="n">
+        <v>26782553.25</v>
+      </c>
+      <c r="I70" t="n">
+        <v>28252199.46</v>
+      </c>
+      <c r="J70" t="n">
+        <v>55034752.71</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1469646.21</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M70" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="N70" t="n">
+        <v>468553050.48</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>84</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-11.1111</v>
+      </c>
+      <c r="F71" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="G71" t="n">
+        <v>662157000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>75601596.44</v>
+      </c>
+      <c r="I71" t="n">
+        <v>75416792.05</v>
+      </c>
+      <c r="J71" t="n">
+        <v>151018388.49</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-184804.39</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M71" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1285200000</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920427.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>华维设计</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>12.4207</v>
+      </c>
+      <c r="F72" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="G72" t="n">
+        <v>233027200</v>
+      </c>
+      <c r="H72" t="n">
+        <v>29773061.29</v>
+      </c>
+      <c r="I72" t="n">
+        <v>26910486.37</v>
+      </c>
+      <c r="J72" t="n">
+        <v>56683547.66</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-2862574.92</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M72" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="N72" t="n">
+        <v>630565283.6</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920427.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>华维设计</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12.4207</v>
+      </c>
+      <c r="F73" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="G73" t="n">
+        <v>353749400</v>
+      </c>
+      <c r="H73" t="n">
+        <v>43895974.86</v>
+      </c>
+      <c r="I73" t="n">
+        <v>44818267.75</v>
+      </c>
+      <c r="J73" t="n">
+        <v>88714242.61</v>
+      </c>
+      <c r="K73" t="n">
+        <v>922292.89</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M73" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="N73" t="n">
+        <v>630565283.6</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>920478.BJ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>峆一药业</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3.1502</v>
+      </c>
+      <c r="F74" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="G74" t="n">
+        <v>308799500</v>
+      </c>
+      <c r="H74" t="n">
+        <v>62328492.05</v>
+      </c>
+      <c r="I74" t="n">
+        <v>30749685.02</v>
+      </c>
+      <c r="J74" t="n">
+        <v>93078177.06999999</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-31578807.03</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-10.23</v>
+      </c>
+      <c r="M74" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="N74" t="n">
+        <v>855643519.0700001</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>920526.BJ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>凯华材料</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="E75" t="n">
+        <v>29.9851</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>334439300</v>
+      </c>
+      <c r="H75" t="n">
+        <v>30607117.02</v>
+      </c>
+      <c r="I75" t="n">
+        <v>45280233.39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>75887350.41</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14673116.37</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1368886084.04</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -993,7 +994,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301150.SZ</t>
+          <t>688337.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1002,37 +1003,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.3</v>
+        <v>47.67</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2</v>
+        <v>57.18</v>
       </c>
       <c r="E5" t="n">
-        <v>41.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="n">
-        <v>49.2</v>
+        <v>57.18</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>47.65</v>
       </c>
       <c r="H5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>442228.5</v>
+        <v>142033.98</v>
       </c>
       <c r="K5" t="n">
-        <v>2023311.93217</v>
+        <v>753270.316</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688337.SH</t>
+          <t>301150.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1041,31 +1042,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.67</v>
+        <v>41.3</v>
       </c>
       <c r="D6" t="n">
-        <v>57.18</v>
+        <v>49.2</v>
       </c>
       <c r="E6" t="n">
-        <v>46.9</v>
+        <v>41.07</v>
       </c>
       <c r="F6" t="n">
-        <v>57.18</v>
+        <v>49.2</v>
       </c>
       <c r="G6" t="n">
-        <v>47.65</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>9.529999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>142033.98</v>
+        <v>442228.5</v>
       </c>
       <c r="K6" t="n">
-        <v>753270.316</v>
+        <v>2023311.93217</v>
       </c>
     </row>
     <row r="7">
@@ -1727,4 +1728,3886 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000504.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.3675</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1347971788</v>
+      </c>
+      <c r="H2" t="n">
+        <v>153512764.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>82846987.34999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>236359751.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-70665776.90000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4199601798.48</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.971500000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1210342786</v>
+      </c>
+      <c r="H3" t="n">
+        <v>223256795.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>196819979.66</v>
+      </c>
+      <c r="J3" t="n">
+        <v>420076775.16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-26436815.84</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="M3" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9042776139.34</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000607.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>华媒控股</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-10.0402</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>619572569</v>
+      </c>
+      <c r="H4" t="n">
+        <v>94677161.14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>52584147.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>147261308.94</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-42093013.34</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="M4" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3965078512.64</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000756.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>新华制药</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-9.975199999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1333044248</v>
+      </c>
+      <c r="H5" t="n">
+        <v>202565528.49</v>
+      </c>
+      <c r="I5" t="n">
+        <v>103705945.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>306271473.89</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-98859583.09</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7248623396.83</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.8509</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5853080479</v>
+      </c>
+      <c r="H6" t="n">
+        <v>772902021.13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>641546892.52</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1414448913.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-131355128.61</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16182154942.4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.6429</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1235059404</v>
+      </c>
+      <c r="H7" t="n">
+        <v>147638430.88</v>
+      </c>
+      <c r="I7" t="n">
+        <v>104951415.96</v>
+      </c>
+      <c r="J7" t="n">
+        <v>252589846.84</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-42687014.92</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4114788538.77</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.995200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>764107467</v>
+      </c>
+      <c r="H8" t="n">
+        <v>104856058</v>
+      </c>
+      <c r="I8" t="n">
+        <v>168342406</v>
+      </c>
+      <c r="J8" t="n">
+        <v>273198464</v>
+      </c>
+      <c r="K8" t="n">
+        <v>63486348</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8618646383.1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001317.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0061</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>718069029</v>
+      </c>
+      <c r="H9" t="n">
+        <v>128530334.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100007497</v>
+      </c>
+      <c r="J9" t="n">
+        <v>228537831.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-28522837.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="M9" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5075429409.12</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.0123</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1478905678</v>
+      </c>
+      <c r="H10" t="n">
+        <v>222530609.45</v>
+      </c>
+      <c r="I10" t="n">
+        <v>500687789.22</v>
+      </c>
+      <c r="J10" t="n">
+        <v>723218398.67</v>
+      </c>
+      <c r="K10" t="n">
+        <v>278157179.77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="M10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10102645280</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002238.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天威视讯</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0575</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G11" t="n">
+        <v>161295819</v>
+      </c>
+      <c r="H11" t="n">
+        <v>47158953</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50848166.96</v>
+      </c>
+      <c r="J11" t="n">
+        <v>98007119.95999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3689213.96</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M11" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6147603165.6</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002426.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>胜利精密</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0372</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>687815195</v>
+      </c>
+      <c r="H12" t="n">
+        <v>30777748</v>
+      </c>
+      <c r="I12" t="n">
+        <v>204981626.47</v>
+      </c>
+      <c r="J12" t="n">
+        <v>235759374.47</v>
+      </c>
+      <c r="K12" t="n">
+        <v>174203878.47</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="M12" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9455118409.6</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002614.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>奥佳华</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0291</v>
+      </c>
+      <c r="F13" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>991041805</v>
+      </c>
+      <c r="H13" t="n">
+        <v>96164082.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>203447728.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>299611811.13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>107283645.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3340454104.27</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002937.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>兴瑞科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.0037</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>817647792</v>
+      </c>
+      <c r="H14" t="n">
+        <v>268047404.01</v>
+      </c>
+      <c r="I14" t="n">
+        <v>222412101.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>490459505.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-45635302.99</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="M14" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9496515282.17</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>003032.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>传智教育</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-7.0281</v>
+      </c>
+      <c r="F15" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>777909299</v>
+      </c>
+      <c r="H15" t="n">
+        <v>106797676</v>
+      </c>
+      <c r="I15" t="n">
+        <v>87031008</v>
+      </c>
+      <c r="J15" t="n">
+        <v>193828684</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-19766668</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="M15" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2634299690.08</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>003040.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>楚天龙</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-10.0113</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1102452673</v>
+      </c>
+      <c r="H16" t="n">
+        <v>155842157.46</v>
+      </c>
+      <c r="I16" t="n">
+        <v>87260527.81999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>243102685.28</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-68581629.64</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M16" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7268487604.78</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>113710.SH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>N四方转</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>148.651</v>
+      </c>
+      <c r="E17" t="n">
+        <v>48.651</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>257930560</v>
+      </c>
+      <c r="H17" t="n">
+        <v>47743610</v>
+      </c>
+      <c r="I17" t="n">
+        <v>56215980</v>
+      </c>
+      <c r="J17" t="n">
+        <v>103959590</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8472370</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>300192.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>科德教育</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.9725</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1196977625</v>
+      </c>
+      <c r="H18" t="n">
+        <v>204946837.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>302425263.16</v>
+      </c>
+      <c r="J18" t="n">
+        <v>507372100.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>97478425.36</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10452342951</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>300642.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>透景生命</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.9981</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="G19" t="n">
+        <v>887965789</v>
+      </c>
+      <c r="H19" t="n">
+        <v>104077362</v>
+      </c>
+      <c r="I19" t="n">
+        <v>86546020</v>
+      </c>
+      <c r="J19" t="n">
+        <v>190623382</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-17531342</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2952407442.24</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>300691.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>联合光电</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.601000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2171388279</v>
+      </c>
+      <c r="H20" t="n">
+        <v>368021720.71</v>
+      </c>
+      <c r="I20" t="n">
+        <v>455530600.51</v>
+      </c>
+      <c r="J20" t="n">
+        <v>823552321.22</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87508879.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="M20" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4626670995.2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>300931.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>通用电梯</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19.9875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>873672621</v>
+      </c>
+      <c r="H21" t="n">
+        <v>192057546.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>176409407</v>
+      </c>
+      <c r="J21" t="n">
+        <v>368466953.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-15648139.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="M21" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3754141201.63</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>301008.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>宏昌科技</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12.2228</v>
+      </c>
+      <c r="F22" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3339997513</v>
+      </c>
+      <c r="H22" t="n">
+        <v>530466726.62</v>
+      </c>
+      <c r="I22" t="n">
+        <v>608660700</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1139127426.62</v>
+      </c>
+      <c r="K22" t="n">
+        <v>78193973.38</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M22" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6965041408.82</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>301047.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>义翘神州</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.116</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5971937875</v>
+      </c>
+      <c r="H23" t="n">
+        <v>625552132</v>
+      </c>
+      <c r="I23" t="n">
+        <v>776110544.5700001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1401662676.57</v>
+      </c>
+      <c r="K23" t="n">
+        <v>150558412.57</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17937093150</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>301150.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中一科技</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2023311932</v>
+      </c>
+      <c r="H24" t="n">
+        <v>209340760.66</v>
+      </c>
+      <c r="I24" t="n">
+        <v>425171957.03</v>
+      </c>
+      <c r="J24" t="n">
+        <v>634512717.6900001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>215831196.37</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="N24" t="n">
+        <v>14948879095.2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>78.77</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.3821</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1121285445</v>
+      </c>
+      <c r="H25" t="n">
+        <v>118610390.56</v>
+      </c>
+      <c r="I25" t="n">
+        <v>144601573.04</v>
+      </c>
+      <c r="J25" t="n">
+        <v>263211963.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>25991182.48</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M25" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2575656355.11</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>301655.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>绿控传动</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.2723</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="G26" t="n">
+        <v>331881866</v>
+      </c>
+      <c r="H26" t="n">
+        <v>42339119.71</v>
+      </c>
+      <c r="I26" t="n">
+        <v>43348671.98</v>
+      </c>
+      <c r="J26" t="n">
+        <v>85687791.69</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1009552.27</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1086431422.08</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>301688.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>格林生物</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.9571</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>316525748</v>
+      </c>
+      <c r="H27" t="n">
+        <v>52162491.63</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42240857.81</v>
+      </c>
+      <c r="J27" t="n">
+        <v>94403349.44</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-9921633.82</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="M27" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1058107286.16</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13.6401</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1910788880</v>
+      </c>
+      <c r="H28" t="n">
+        <v>147502082.06</v>
+      </c>
+      <c r="I28" t="n">
+        <v>271365193.38</v>
+      </c>
+      <c r="J28" t="n">
+        <v>418867275.44</v>
+      </c>
+      <c r="K28" t="n">
+        <v>123863111.32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M28" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4023545494.8</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>600088.SH</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>中视传媒</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-10.0198</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>475756963</v>
+      </c>
+      <c r="H29" t="n">
+        <v>48910638.05</v>
+      </c>
+      <c r="I29" t="n">
+        <v>43722396.96</v>
+      </c>
+      <c r="J29" t="n">
+        <v>92633035.01000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-5188241.09</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="M29" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5428692360</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.7001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3436627074</v>
+      </c>
+      <c r="H30" t="n">
+        <v>446683887.51</v>
+      </c>
+      <c r="I30" t="n">
+        <v>444198220.58</v>
+      </c>
+      <c r="J30" t="n">
+        <v>890882108.09</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-2485666.93</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10749868901.5</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>600293.SH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>三峡新材</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.119</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="G31" t="n">
+        <v>232240321</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16298265</v>
+      </c>
+      <c r="I31" t="n">
+        <v>107546063</v>
+      </c>
+      <c r="J31" t="n">
+        <v>123844328</v>
+      </c>
+      <c r="K31" t="n">
+        <v>91247798</v>
+      </c>
+      <c r="L31" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="M31" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4292536670.2</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.993600000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1324585012</v>
+      </c>
+      <c r="H32" t="n">
+        <v>133119316.06</v>
+      </c>
+      <c r="I32" t="n">
+        <v>170757829.24</v>
+      </c>
+      <c r="J32" t="n">
+        <v>303877145.3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>37638513.18</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M32" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5055747840</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>600418.SH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.990600000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7849784670</v>
+      </c>
+      <c r="H33" t="n">
+        <v>909342412.99</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1288803676.63</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2198146089.62</v>
+      </c>
+      <c r="K33" t="n">
+        <v>379461263.64</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="M33" t="n">
+        <v>28</v>
+      </c>
+      <c r="N33" t="n">
+        <v>52860478672.75</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>600448.SH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>华纺股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-8.938499999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G34" t="n">
+        <v>633612781</v>
+      </c>
+      <c r="H34" t="n">
+        <v>32224925.51</v>
+      </c>
+      <c r="I34" t="n">
+        <v>34514668.38</v>
+      </c>
+      <c r="J34" t="n">
+        <v>66739593.89</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2289742.87</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M34" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2053212098.12</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>600503.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>华丽家族</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10.1124</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1181594383</v>
+      </c>
+      <c r="H35" t="n">
+        <v>134672178.02</v>
+      </c>
+      <c r="I35" t="n">
+        <v>171604910.27</v>
+      </c>
+      <c r="J35" t="n">
+        <v>306277088.29</v>
+      </c>
+      <c r="K35" t="n">
+        <v>36932732.25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4710732600</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-10.0211</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>522523905</v>
+      </c>
+      <c r="H36" t="n">
+        <v>71529601.68000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>38891018.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>110420620.18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-32638583.18</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="M36" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3624069422.41</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600641.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>先导基电</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.2821</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10507870198</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1309634795.28</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2417567354.77</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3727202150.05</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1107932559.49</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="N37" t="n">
+        <v>44484110176</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-8.1548</v>
+      </c>
+      <c r="F38" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2422425630</v>
+      </c>
+      <c r="H38" t="n">
+        <v>313132877.86</v>
+      </c>
+      <c r="I38" t="n">
+        <v>267855908</v>
+      </c>
+      <c r="J38" t="n">
+        <v>580988785.86</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-45276969.86</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="M38" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5110638069.15</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600743.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.1563</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="G39" t="n">
+        <v>276179433</v>
+      </c>
+      <c r="H39" t="n">
+        <v>36101516.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>72049215.98999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>108150732.59</v>
+      </c>
+      <c r="K39" t="n">
+        <v>35947699.39</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="M39" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6616004464.68</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0548</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="G40" t="n">
+        <v>213775487</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23189723.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>89982460</v>
+      </c>
+      <c r="J40" t="n">
+        <v>113172183.3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>66792736.7</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="M40" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2758655368</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600825.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.9688</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G41" t="n">
+        <v>54717360</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13317436</v>
+      </c>
+      <c r="I41" t="n">
+        <v>36885500</v>
+      </c>
+      <c r="J41" t="n">
+        <v>50202936</v>
+      </c>
+      <c r="K41" t="n">
+        <v>23568064</v>
+      </c>
+      <c r="L41" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="M41" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7376908221</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>601123.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-2.7419</v>
+      </c>
+      <c r="F42" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>587117177</v>
+      </c>
+      <c r="H42" t="n">
+        <v>103994359.84</v>
+      </c>
+      <c r="I42" t="n">
+        <v>61108859.75</v>
+      </c>
+      <c r="J42" t="n">
+        <v>165103219.59</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-42885500.09</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1733533187.22</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>601579.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>会稽山</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.8954</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2679425095</v>
+      </c>
+      <c r="H43" t="n">
+        <v>323661357.32</v>
+      </c>
+      <c r="I43" t="n">
+        <v>368553496.64</v>
+      </c>
+      <c r="J43" t="n">
+        <v>692214853.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>44892139.32</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="N43" t="n">
+        <v>17620280280.75</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.988099999999999</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>374811314</v>
+      </c>
+      <c r="H44" t="n">
+        <v>55788137</v>
+      </c>
+      <c r="I44" t="n">
+        <v>46624130</v>
+      </c>
+      <c r="J44" t="n">
+        <v>102412267</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-9164007</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="M44" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="N44" t="n">
+        <v>14650222150</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1192507582</v>
+      </c>
+      <c r="H45" t="n">
+        <v>62061212.75</v>
+      </c>
+      <c r="I45" t="n">
+        <v>94890132.11</v>
+      </c>
+      <c r="J45" t="n">
+        <v>156951344.86</v>
+      </c>
+      <c r="K45" t="n">
+        <v>32828919.36</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M45" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5935651170</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-10.0084</v>
+      </c>
+      <c r="F46" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="G46" t="n">
+        <v>501187872</v>
+      </c>
+      <c r="H46" t="n">
+        <v>33784668.99</v>
+      </c>
+      <c r="I46" t="n">
+        <v>34428231.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>68212900.39</v>
+      </c>
+      <c r="K46" t="n">
+        <v>643562.41</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M46" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1536641396.99</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>603636.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9.987500000000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="G47" t="n">
+        <v>779215386</v>
+      </c>
+      <c r="H47" t="n">
+        <v>104240082.81</v>
+      </c>
+      <c r="I47" t="n">
+        <v>120758543</v>
+      </c>
+      <c r="J47" t="n">
+        <v>224998625.81</v>
+      </c>
+      <c r="K47" t="n">
+        <v>16518460.19</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M47" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5112976207.63</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603823.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-10.0036</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1333330598</v>
+      </c>
+      <c r="H48" t="n">
+        <v>234627092.16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>105397380.43</v>
+      </c>
+      <c r="J48" t="n">
+        <v>340024472.59</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-129229711.73</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="M48" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>21014078020.88</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603949.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>雪龙集团</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10.0287</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G49" t="n">
+        <v>58430518</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6104280</v>
+      </c>
+      <c r="I49" t="n">
+        <v>34073923.84</v>
+      </c>
+      <c r="J49" t="n">
+        <v>40178203.84</v>
+      </c>
+      <c r="K49" t="n">
+        <v>27969643.84</v>
+      </c>
+      <c r="L49" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="M49" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3228753008.64</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0056</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2546149548</v>
+      </c>
+      <c r="H50" t="n">
+        <v>163520823.95</v>
+      </c>
+      <c r="I50" t="n">
+        <v>210142498.45</v>
+      </c>
+      <c r="J50" t="n">
+        <v>373663322.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>46621674.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M50" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8375412032</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>605179.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>一鸣食品</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-9.8202</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1244307672</v>
+      </c>
+      <c r="H51" t="n">
+        <v>167267483.48</v>
+      </c>
+      <c r="I51" t="n">
+        <v>104432478.66</v>
+      </c>
+      <c r="J51" t="n">
+        <v>271699962.14</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-62835004.82</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="M51" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="N51" t="n">
+        <v>10863090000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-10.0057</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G52" t="n">
+        <v>440713229</v>
+      </c>
+      <c r="H52" t="n">
+        <v>23245563</v>
+      </c>
+      <c r="I52" t="n">
+        <v>24811102.81</v>
+      </c>
+      <c r="J52" t="n">
+        <v>48056665.81</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1565539.81</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M52" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7075555564.4</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>688026.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>洁特生物</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.7747</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1366662000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>235212094.19</v>
+      </c>
+      <c r="I53" t="n">
+        <v>258855597.15</v>
+      </c>
+      <c r="J53" t="n">
+        <v>494067691.34</v>
+      </c>
+      <c r="K53" t="n">
+        <v>23643502.96</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M53" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3899324893.26</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>688056.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>莱伯泰科</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="G54" t="n">
+        <v>127254800</v>
+      </c>
+      <c r="H54" t="n">
+        <v>14753562.66</v>
+      </c>
+      <c r="I54" t="n">
+        <v>23503979.32</v>
+      </c>
+      <c r="J54" t="n">
+        <v>38257541.98</v>
+      </c>
+      <c r="K54" t="n">
+        <v>8750416.66</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="M54" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3569584183.2</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>688203.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>海正生材</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.3793</v>
+      </c>
+      <c r="F55" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1217848200</v>
+      </c>
+      <c r="H55" t="n">
+        <v>304730259.88</v>
+      </c>
+      <c r="I55" t="n">
+        <v>220433745.83</v>
+      </c>
+      <c r="J55" t="n">
+        <v>525164005.71</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-84296514.05</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="M55" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4925077052.4</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>688337.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>普源精电</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="G56" t="n">
+        <v>753270300</v>
+      </c>
+      <c r="H56" t="n">
+        <v>153438467.98</v>
+      </c>
+      <c r="I56" t="n">
+        <v>152240289.64</v>
+      </c>
+      <c r="J56" t="n">
+        <v>305678757.62</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-1198178.34</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M56" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="N56" t="n">
+        <v>10639983153.72</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>688512.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>慧智微</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20.0277</v>
+      </c>
+      <c r="F57" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="G57" t="n">
+        <v>951464300</v>
+      </c>
+      <c r="H57" t="n">
+        <v>191103899.55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>202762219.88</v>
+      </c>
+      <c r="J57" t="n">
+        <v>393866119.43</v>
+      </c>
+      <c r="K57" t="n">
+        <v>11658320.33</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M57" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5668273030.72</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>688628.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>优利德</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="E58" t="n">
+        <v>19.9958</v>
+      </c>
+      <c r="F58" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1408430400</v>
+      </c>
+      <c r="H58" t="n">
+        <v>295784254.99</v>
+      </c>
+      <c r="I58" t="n">
+        <v>364490602.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>660274857.39</v>
+      </c>
+      <c r="K58" t="n">
+        <v>68706347.41</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M58" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="N58" t="n">
+        <v>12862242102.72</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>688628.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>优利德</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="E59" t="n">
+        <v>19.9958</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2528060800</v>
+      </c>
+      <c r="H59" t="n">
+        <v>490517813.59</v>
+      </c>
+      <c r="I59" t="n">
+        <v>755299736.01</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1245817549.6</v>
+      </c>
+      <c r="K59" t="n">
+        <v>264781922.42</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="M59" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="N59" t="n">
+        <v>12862242102.72</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>688656.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>浩欧博</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20.0034</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G60" t="n">
+        <v>245564900</v>
+      </c>
+      <c r="H60" t="n">
+        <v>41790017.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>69170657.5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>110960674.9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>27380640.1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="N60" t="n">
+        <v>8958666305.84</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>688662.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>富信科技</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.2114</v>
+      </c>
+      <c r="F61" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>6161608200</v>
+      </c>
+      <c r="H61" t="n">
+        <v>965387305.09</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1079423763.26</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2044811068.35</v>
+      </c>
+      <c r="K61" t="n">
+        <v>114036458.17</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M61" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="N61" t="n">
+        <v>14981704162.84</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>688837.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>信诺维</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.3616</v>
+      </c>
+      <c r="F62" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1110246100</v>
+      </c>
+      <c r="H62" t="n">
+        <v>91980174.51000001</v>
+      </c>
+      <c r="I62" t="n">
+        <v>104998306.23</v>
+      </c>
+      <c r="J62" t="n">
+        <v>196978480.74</v>
+      </c>
+      <c r="K62" t="n">
+        <v>13018131.72</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M62" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2604637649.6</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>920003.BJ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>中诚咨询</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14.0013</v>
+      </c>
+      <c r="F63" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>91754400</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22838208.7</v>
+      </c>
+      <c r="I63" t="n">
+        <v>13678104.34</v>
+      </c>
+      <c r="J63" t="n">
+        <v>36516313.04</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-9160104.359999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="M63" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N63" t="n">
+        <v>345528955</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>920065.BJ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>千岸科技</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-7.2079</v>
+      </c>
+      <c r="F64" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>170011500</v>
+      </c>
+      <c r="H64" t="n">
+        <v>29449103.88</v>
+      </c>
+      <c r="I64" t="n">
+        <v>16896551.07</v>
+      </c>
+      <c r="J64" t="n">
+        <v>46345654.95</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-12552552.81</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="M64" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="N64" t="n">
+        <v>594090000</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5.7836</v>
+      </c>
+      <c r="F65" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="G65" t="n">
+        <v>250657300</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20682201.58</v>
+      </c>
+      <c r="I65" t="n">
+        <v>26857347.15</v>
+      </c>
+      <c r="J65" t="n">
+        <v>47539548.73</v>
+      </c>
+      <c r="K65" t="n">
+        <v>6175145.57</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M65" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="N65" t="n">
+        <v>893025000</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G66" t="n">
+        <v>42862400</v>
+      </c>
+      <c r="H66" t="n">
+        <v>18350270.4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4499233.2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>22849503.6</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-13851037.2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-32.32</v>
+      </c>
+      <c r="M66" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1048740000</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="E67" t="n">
+        <v>11.5942</v>
+      </c>
+      <c r="F67" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="G67" t="n">
+        <v>281787900</v>
+      </c>
+      <c r="H67" t="n">
+        <v>47596039.92</v>
+      </c>
+      <c r="I67" t="n">
+        <v>23037034.55</v>
+      </c>
+      <c r="J67" t="n">
+        <v>70633074.47</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-24559005.37</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="M67" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="N67" t="n">
+        <v>522878041.84</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.3095</v>
+      </c>
+      <c r="F68" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="G68" t="n">
+        <v>545104000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>89050740.72</v>
+      </c>
+      <c r="I68" t="n">
+        <v>72570778.13</v>
+      </c>
+      <c r="J68" t="n">
+        <v>161621518.85</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-16479962.59</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="M68" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1366290000</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>920427.BJ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>华维设计</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-4.6774</v>
+      </c>
+      <c r="F69" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="G69" t="n">
+        <v>187897600</v>
+      </c>
+      <c r="H69" t="n">
+        <v>22109396.28</v>
+      </c>
+      <c r="I69" t="n">
+        <v>21918140.53</v>
+      </c>
+      <c r="J69" t="n">
+        <v>44027536.81</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-191255.75</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="N69" t="n">
+        <v>601071100.98</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920873.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>中设咨询</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.6849</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="G70" t="n">
+        <v>110830800</v>
+      </c>
+      <c r="H70" t="n">
+        <v>11795315.84</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12803309.04</v>
+      </c>
+      <c r="J70" t="n">
+        <v>24598624.88</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1007993.2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M70" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="N70" t="n">
+        <v>977620183.2</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4055 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000504.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.6019</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1525092476</v>
+      </c>
+      <c r="H2" t="n">
+        <v>117324554</v>
+      </c>
+      <c r="I2" t="n">
+        <v>234403387</v>
+      </c>
+      <c r="J2" t="n">
+        <v>351727941</v>
+      </c>
+      <c r="K2" t="n">
+        <v>117078833</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4518850524.54</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000504.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.6019</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2944361889</v>
+      </c>
+      <c r="H3" t="n">
+        <v>247534312.55</v>
+      </c>
+      <c r="I3" t="n">
+        <v>264869766.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>512404078.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17335453.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4518850524.54</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-5.1813</v>
+      </c>
+      <c r="F4" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2936520453</v>
+      </c>
+      <c r="H4" t="n">
+        <v>450456569.39</v>
+      </c>
+      <c r="I4" t="n">
+        <v>424285977.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>874742546.66</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-26170592.12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8574238515.54</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000592.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>平潭发展</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.0251</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2717291126</v>
+      </c>
+      <c r="H5" t="n">
+        <v>160014489.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>635090848.71</v>
+      </c>
+      <c r="J5" t="n">
+        <v>795105337.8200001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>475076359.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16814511702.22</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000593.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>德龙汇能</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10.0041</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>492443412</v>
+      </c>
+      <c r="H6" t="n">
+        <v>111428402.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>49273695.06</v>
+      </c>
+      <c r="J6" t="n">
+        <v>160702097.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-62154707.78</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-12.62</v>
+      </c>
+      <c r="M6" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7804175323.63</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000607.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>华媒控股</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.0446</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>488481951</v>
+      </c>
+      <c r="H7" t="n">
+        <v>55510701.56</v>
+      </c>
+      <c r="I7" t="n">
+        <v>41729593.01</v>
+      </c>
+      <c r="J7" t="n">
+        <v>97240294.56999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-13781108.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3566800537.04</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3267359876</v>
+      </c>
+      <c r="H8" t="n">
+        <v>493045763.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>437877407.96</v>
+      </c>
+      <c r="J8" t="n">
+        <v>930923171.5599999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-55168355.64</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="M8" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14563939448.16</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000850.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华茂股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.1075</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>189478401</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29499393</v>
+      </c>
+      <c r="I9" t="n">
+        <v>66116648.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>95616041.59999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36617255.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50.46</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4830076820.48</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000978.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10.0114</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>597634389</v>
+      </c>
+      <c r="H10" t="n">
+        <v>74350732.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>72278972.78</v>
+      </c>
+      <c r="J10" t="n">
+        <v>146629704.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2071759.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3702841563.33</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="F11" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2897387829</v>
+      </c>
+      <c r="H11" t="n">
+        <v>231043605.89</v>
+      </c>
+      <c r="I11" t="n">
+        <v>301818490.77</v>
+      </c>
+      <c r="J11" t="n">
+        <v>532862096.66</v>
+      </c>
+      <c r="K11" t="n">
+        <v>70774884.88</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7010148051.6</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001234.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>泰慕士</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0062</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>170037492</v>
+      </c>
+      <c r="H12" t="n">
+        <v>37286264</v>
+      </c>
+      <c r="I12" t="n">
+        <v>81105223.40000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>118391487.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>43818959.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="M12" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3240569100</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001317.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0067</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="G13" t="n">
+        <v>793141125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>136700331.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>130542551.58</v>
+      </c>
+      <c r="J13" t="n">
+        <v>267242882.68</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-6157779.52</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M13" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5583314360.1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002082.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST万邦</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.5409</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G14" t="n">
+        <v>868943882</v>
+      </c>
+      <c r="H14" t="n">
+        <v>127502606</v>
+      </c>
+      <c r="I14" t="n">
+        <v>104843125.67</v>
+      </c>
+      <c r="J14" t="n">
+        <v>232345731.67</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-22659480.33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6814175064</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002106.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>莱宝高科</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>715305554</v>
+      </c>
+      <c r="H15" t="n">
+        <v>68001069.22</v>
+      </c>
+      <c r="I15" t="n">
+        <v>39256729.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>107257798.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-28744339.69</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8819497983.42</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.992599999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3358508146</v>
+      </c>
+      <c r="H16" t="n">
+        <v>741027532.52</v>
+      </c>
+      <c r="I16" t="n">
+        <v>573465677.0700001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1314493209.59</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-167561855.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11112159240</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.992599999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4837413824</v>
+      </c>
+      <c r="H17" t="n">
+        <v>971457927.92</v>
+      </c>
+      <c r="I17" t="n">
+        <v>965239189.9299999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1936697117.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-6218737.99</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M17" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11112159240</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.0253</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="G18" t="n">
+        <v>921657308</v>
+      </c>
+      <c r="H18" t="n">
+        <v>129158495.89</v>
+      </c>
+      <c r="I18" t="n">
+        <v>243760323.73</v>
+      </c>
+      <c r="J18" t="n">
+        <v>372918819.62</v>
+      </c>
+      <c r="K18" t="n">
+        <v>114601827.84</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="M18" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6265863367.58</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.0253</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2175305917</v>
+      </c>
+      <c r="H19" t="n">
+        <v>242185291.08</v>
+      </c>
+      <c r="I19" t="n">
+        <v>507275638.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>749460929.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>265090347.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="M19" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6265863367.58</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002172.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1028721392</v>
+      </c>
+      <c r="H20" t="n">
+        <v>116362136</v>
+      </c>
+      <c r="I20" t="n">
+        <v>83494907.18000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>199857043.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-32867228.82</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="M20" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4147062756.6</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002205.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>国统股份</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9.982799999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G21" t="n">
+        <v>201473191</v>
+      </c>
+      <c r="H21" t="n">
+        <v>26495412.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>33807320</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60302732.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7311907.99</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2375076453.84</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002205.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>国统股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.982799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G22" t="n">
+        <v>327017535</v>
+      </c>
+      <c r="H22" t="n">
+        <v>37925761</v>
+      </c>
+      <c r="I22" t="n">
+        <v>44657319</v>
+      </c>
+      <c r="J22" t="n">
+        <v>82583080</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6731558</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2375076453.84</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002413.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>雷科防务</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.0613</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1977372525</v>
+      </c>
+      <c r="H23" t="n">
+        <v>180387994.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>351385229.27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>531773223.37</v>
+      </c>
+      <c r="K23" t="n">
+        <v>170997235.17</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="M23" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11620011558.09</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3361505550</v>
+      </c>
+      <c r="H24" t="n">
+        <v>641752088.3099999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>536438912.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1178191000.51</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-105313176.11</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="M24" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>11213683299.54</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002614.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>奥佳华</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.0396</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1454429912</v>
+      </c>
+      <c r="H25" t="n">
+        <v>129342444.32</v>
+      </c>
+      <c r="I25" t="n">
+        <v>274768488.74</v>
+      </c>
+      <c r="J25" t="n">
+        <v>404110933.06</v>
+      </c>
+      <c r="K25" t="n">
+        <v>145426044.42</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3675823340.63</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002819.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>东方中科</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.983499999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>713627344</v>
+      </c>
+      <c r="H26" t="n">
+        <v>130906611</v>
+      </c>
+      <c r="I26" t="n">
+        <v>125184552.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>256091163.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-5722058.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6297051636.76</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002836.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>新宏泽</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.0448</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="G27" t="n">
+        <v>286117123</v>
+      </c>
+      <c r="H27" t="n">
+        <v>26384988.76</v>
+      </c>
+      <c r="I27" t="n">
+        <v>77110800.31</v>
+      </c>
+      <c r="J27" t="n">
+        <v>103495789.07</v>
+      </c>
+      <c r="K27" t="n">
+        <v>50725811.55</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="M27" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2827008000</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002849.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>威星智能</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.6087</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1685711101</v>
+      </c>
+      <c r="H28" t="n">
+        <v>311230414.74</v>
+      </c>
+      <c r="I28" t="n">
+        <v>319370374.04</v>
+      </c>
+      <c r="J28" t="n">
+        <v>630600788.78</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8139959.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M28" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5412610714.5</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002856.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>*ST美芝</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-10.0152</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G29" t="n">
+        <v>445689511</v>
+      </c>
+      <c r="H29" t="n">
+        <v>56447199</v>
+      </c>
+      <c r="I29" t="n">
+        <v>70232816</v>
+      </c>
+      <c r="J29" t="n">
+        <v>126680015</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13785617</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M29" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2204260040.97</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002909.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>集泰股份</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.946899999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1146893102</v>
+      </c>
+      <c r="H30" t="n">
+        <v>104564411.97</v>
+      </c>
+      <c r="I30" t="n">
+        <v>161167097.05</v>
+      </c>
+      <c r="J30" t="n">
+        <v>265731509.02</v>
+      </c>
+      <c r="K30" t="n">
+        <v>56602685.08</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M30" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3153743005.07</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300192.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>科德教育</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.2832</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2664255446</v>
+      </c>
+      <c r="H31" t="n">
+        <v>454462227.38</v>
+      </c>
+      <c r="I31" t="n">
+        <v>573798284.88</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1028260512.26</v>
+      </c>
+      <c r="K31" t="n">
+        <v>119336057.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="M31" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="N31" t="n">
+        <v>11527180831.8</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>300300.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>海峡创新</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19.9778</v>
+      </c>
+      <c r="F32" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1604221029</v>
+      </c>
+      <c r="H32" t="n">
+        <v>75838777.23</v>
+      </c>
+      <c r="I32" t="n">
+        <v>363586890.51</v>
+      </c>
+      <c r="J32" t="n">
+        <v>439425667.74</v>
+      </c>
+      <c r="K32" t="n">
+        <v>287748113.28</v>
+      </c>
+      <c r="L32" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="M32" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7208211776</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301311.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>昆船智能</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20.0267</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>569676283</v>
+      </c>
+      <c r="H33" t="n">
+        <v>65234436.73</v>
+      </c>
+      <c r="I33" t="n">
+        <v>94620544.76000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>159854981.49</v>
+      </c>
+      <c r="K33" t="n">
+        <v>29386108.03</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="M33" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4315200000</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301311.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>昆船智能</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20.0267</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1112034082</v>
+      </c>
+      <c r="H34" t="n">
+        <v>164290204.95</v>
+      </c>
+      <c r="I34" t="n">
+        <v>141184300.57</v>
+      </c>
+      <c r="J34" t="n">
+        <v>305474505.52</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-23105904.38</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="M34" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4315200000</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-5.8144</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1112318961</v>
+      </c>
+      <c r="H35" t="n">
+        <v>131172135.52</v>
+      </c>
+      <c r="I35" t="n">
+        <v>105839674.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>237011809.92</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-25332461.12</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="M35" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2425897486.17</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>托伦斯</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>141.89</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.3534</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1920357462</v>
+      </c>
+      <c r="H36" t="n">
+        <v>268999321.14</v>
+      </c>
+      <c r="I36" t="n">
+        <v>155041790.91</v>
+      </c>
+      <c r="J36" t="n">
+        <v>424041112.05</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-113957530.23</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4374663514.97</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2532466819</v>
+      </c>
+      <c r="H37" t="n">
+        <v>304164898.74</v>
+      </c>
+      <c r="I37" t="n">
+        <v>324931664.84</v>
+      </c>
+      <c r="J37" t="n">
+        <v>629096563.58</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20766766.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M37" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4828254593.76</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4443255699</v>
+      </c>
+      <c r="H38" t="n">
+        <v>386383264</v>
+      </c>
+      <c r="I38" t="n">
+        <v>560648767.76</v>
+      </c>
+      <c r="J38" t="n">
+        <v>947032031.76</v>
+      </c>
+      <c r="K38" t="n">
+        <v>174265503.76</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M38" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4828254593.76</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>301697.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>贝特利</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6.4025</v>
+      </c>
+      <c r="F39" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="G39" t="n">
+        <v>600432047</v>
+      </c>
+      <c r="H39" t="n">
+        <v>73308066.23999999</v>
+      </c>
+      <c r="I39" t="n">
+        <v>101668137.51</v>
+      </c>
+      <c r="J39" t="n">
+        <v>174976203.75</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28360071.27</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M39" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1323250302.72</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19.9865</v>
+      </c>
+      <c r="F40" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>867521295</v>
+      </c>
+      <c r="H40" t="n">
+        <v>103833129.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>205217688.19</v>
+      </c>
+      <c r="J40" t="n">
+        <v>309050817.49</v>
+      </c>
+      <c r="K40" t="n">
+        <v>101384558.89</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="M40" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2485363697.46</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.5522</v>
+      </c>
+      <c r="F41" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4318063100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>634960720.64</v>
+      </c>
+      <c r="I41" t="n">
+        <v>613820524.77</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1248781245.41</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-21140195.87</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M41" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10583005264.82</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600189.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>泉阳泉</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10.0363</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G42" t="n">
+        <v>341477434</v>
+      </c>
+      <c r="H42" t="n">
+        <v>59389844</v>
+      </c>
+      <c r="I42" t="n">
+        <v>98700624.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>158090468.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39310780.3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="M42" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6508300089.2</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600371.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>万向德农</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-8.275499999999999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1549957474</v>
+      </c>
+      <c r="H43" t="n">
+        <v>188442212.51</v>
+      </c>
+      <c r="I43" t="n">
+        <v>145533159.23</v>
+      </c>
+      <c r="J43" t="n">
+        <v>333975371.74</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-42909053.28</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M43" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4637361300</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.0551</v>
+      </c>
+      <c r="F44" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="G44" t="n">
+        <v>987104083</v>
+      </c>
+      <c r="H44" t="n">
+        <v>87900877.90000001</v>
+      </c>
+      <c r="I44" t="n">
+        <v>81557943.55</v>
+      </c>
+      <c r="J44" t="n">
+        <v>169458821.45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-6342934.35</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M44" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3662306966.14</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-2.784</v>
+      </c>
+      <c r="F45" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2004408988</v>
+      </c>
+      <c r="H45" t="n">
+        <v>270217911.7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>228515994</v>
+      </c>
+      <c r="J45" t="n">
+        <v>498733905.7</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-41701917.7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="M45" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4968355444.2</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600792.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>云煤能源</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.0386</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1020598468</v>
+      </c>
+      <c r="H46" t="n">
+        <v>122035872</v>
+      </c>
+      <c r="I46" t="n">
+        <v>262107538</v>
+      </c>
+      <c r="J46" t="n">
+        <v>384143410</v>
+      </c>
+      <c r="K46" t="n">
+        <v>140071666</v>
+      </c>
+      <c r="L46" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="M46" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="N46" t="n">
+        <v>6326564520</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9.966799999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="G47" t="n">
+        <v>418892407</v>
+      </c>
+      <c r="H47" t="n">
+        <v>87800717.02</v>
+      </c>
+      <c r="I47" t="n">
+        <v>64043884</v>
+      </c>
+      <c r="J47" t="n">
+        <v>151844601.02</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-23756833.02</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="M47" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3033604408</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.966799999999999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="G48" t="n">
+        <v>632667894</v>
+      </c>
+      <c r="H48" t="n">
+        <v>96910731.72</v>
+      </c>
+      <c r="I48" t="n">
+        <v>131756798</v>
+      </c>
+      <c r="J48" t="n">
+        <v>228667529.72</v>
+      </c>
+      <c r="K48" t="n">
+        <v>34846066.28</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M48" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3033604408</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600815.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>厦工股份</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9.9291</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2618564959</v>
+      </c>
+      <c r="H49" t="n">
+        <v>435187653.43</v>
+      </c>
+      <c r="I49" t="n">
+        <v>549495268.96</v>
+      </c>
+      <c r="J49" t="n">
+        <v>984682922.39</v>
+      </c>
+      <c r="K49" t="n">
+        <v>114307615.53</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M49" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8249539332</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600825.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0567</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G50" t="n">
+        <v>46504942</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8922524.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>35737338</v>
+      </c>
+      <c r="J50" t="n">
+        <v>44659862.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>26814813.9</v>
+      </c>
+      <c r="L50" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="M50" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8118778594.5</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600843.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>上工申贝</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9.9869</v>
+      </c>
+      <c r="F51" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="G51" t="n">
+        <v>447214953</v>
+      </c>
+      <c r="H51" t="n">
+        <v>63484771.53</v>
+      </c>
+      <c r="I51" t="n">
+        <v>48232409.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>111717180.73</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-15252362.33</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="M51" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4002528925.1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>600843.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>上工申贝</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9.9869</v>
+      </c>
+      <c r="F52" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>640303569</v>
+      </c>
+      <c r="H52" t="n">
+        <v>84683185.04000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>73680804.98999999</v>
+      </c>
+      <c r="J52" t="n">
+        <v>158363990.03</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-11002380.05</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="M52" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4002528925.1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>601086.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-9.988200000000001</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1165472055</v>
+      </c>
+      <c r="H53" t="n">
+        <v>199478801</v>
+      </c>
+      <c r="I53" t="n">
+        <v>114172561</v>
+      </c>
+      <c r="J53" t="n">
+        <v>313651362</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-85306240</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="M53" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10203120000</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>27</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F54" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1522465538</v>
+      </c>
+      <c r="H54" t="n">
+        <v>105248780.04</v>
+      </c>
+      <c r="I54" t="n">
+        <v>84996536.91</v>
+      </c>
+      <c r="J54" t="n">
+        <v>190245316.95</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-20252243.13</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="M54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5701405914</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603042.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>华脉科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.9824</v>
+      </c>
+      <c r="F55" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1042459177</v>
+      </c>
+      <c r="H55" t="n">
+        <v>102326645.67</v>
+      </c>
+      <c r="I55" t="n">
+        <v>244201895.73</v>
+      </c>
+      <c r="J55" t="n">
+        <v>346528541.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>141875250.06</v>
+      </c>
+      <c r="L55" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="M55" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3910202014.16</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4.886</v>
+      </c>
+      <c r="F56" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>589350218</v>
+      </c>
+      <c r="H56" t="n">
+        <v>38732190.94</v>
+      </c>
+      <c r="I56" t="n">
+        <v>36817265.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>75549456.34</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-1914925.54</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M56" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1611721595.54</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603322.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>超讯科技</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-10.0124</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="G57" t="n">
+        <v>364776213</v>
+      </c>
+      <c r="H57" t="n">
+        <v>116763924.44</v>
+      </c>
+      <c r="I57" t="n">
+        <v>57204061</v>
+      </c>
+      <c r="J57" t="n">
+        <v>173967985.44</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-59559863.44</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-16.33</v>
+      </c>
+      <c r="M57" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4588927499.52</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603396.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>金辰股份</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="G58" t="n">
+        <v>562001577</v>
+      </c>
+      <c r="H58" t="n">
+        <v>79259765.17</v>
+      </c>
+      <c r="I58" t="n">
+        <v>103890824.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>183150589.87</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24631059.53</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4937119315.92</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603500.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>祥和实业</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.0317</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G59" t="n">
+        <v>143607982</v>
+      </c>
+      <c r="H59" t="n">
+        <v>18648366</v>
+      </c>
+      <c r="I59" t="n">
+        <v>74537872.8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>93186238.8</v>
+      </c>
+      <c r="K59" t="n">
+        <v>55889506.8</v>
+      </c>
+      <c r="L59" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="M59" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3467601423.32</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603823.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-10.0059</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1505987772</v>
+      </c>
+      <c r="H60" t="n">
+        <v>382319822.98</v>
+      </c>
+      <c r="I60" t="n">
+        <v>174579983</v>
+      </c>
+      <c r="J60" t="n">
+        <v>556899805.98</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-207739839.98</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-13.79</v>
+      </c>
+      <c r="M60" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="N60" t="n">
+        <v>18911421115.68</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603949.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>雪龙集团</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10.026</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G61" t="n">
+        <v>133888657</v>
+      </c>
+      <c r="H61" t="n">
+        <v>27114746.6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>44985073.44</v>
+      </c>
+      <c r="J61" t="n">
+        <v>72099820.04000001</v>
+      </c>
+      <c r="K61" t="n">
+        <v>17870326.84</v>
+      </c>
+      <c r="L61" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="M61" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3552469130.6</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>603970.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>中农立华</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.0362</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G62" t="n">
+        <v>90254673</v>
+      </c>
+      <c r="H62" t="n">
+        <v>12048663</v>
+      </c>
+      <c r="I62" t="n">
+        <v>24381160</v>
+      </c>
+      <c r="J62" t="n">
+        <v>36429823</v>
+      </c>
+      <c r="K62" t="n">
+        <v>12332497</v>
+      </c>
+      <c r="L62" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="M62" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3271297630.78</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>605179.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>一鸣食品</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-10.0037</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="G63" t="n">
+        <v>697878709</v>
+      </c>
+      <c r="H63" t="n">
+        <v>72295929.33</v>
+      </c>
+      <c r="I63" t="n">
+        <v>60145707</v>
+      </c>
+      <c r="J63" t="n">
+        <v>132441636.33</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-12150222.33</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="M63" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="N63" t="n">
+        <v>9776380000</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688056.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>莱伯泰科</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.0529</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="G64" t="n">
+        <v>465456700</v>
+      </c>
+      <c r="H64" t="n">
+        <v>59537891.73</v>
+      </c>
+      <c r="I64" t="n">
+        <v>39343958.71</v>
+      </c>
+      <c r="J64" t="n">
+        <v>98881850.44</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-20193933.02</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="M64" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3928431270.4</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688682.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>霍莱沃</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="E65" t="n">
+        <v>19.9873</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G65" t="n">
+        <v>222120500</v>
+      </c>
+      <c r="H65" t="n">
+        <v>45357474.42</v>
+      </c>
+      <c r="I65" t="n">
+        <v>41051007.41</v>
+      </c>
+      <c r="J65" t="n">
+        <v>86408481.83</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-4306467.01</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M65" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3863767676.3</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688837.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>信诺维</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-11.7351</v>
+      </c>
+      <c r="F66" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1020530700</v>
+      </c>
+      <c r="H66" t="n">
+        <v>100270223.11</v>
+      </c>
+      <c r="I66" t="n">
+        <v>74795161.27</v>
+      </c>
+      <c r="J66" t="n">
+        <v>175065384.38</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-25475061.84</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="M66" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2298981477.66</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>920025.BJ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>凯达重工</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F67" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="G67" t="n">
+        <v>577722400</v>
+      </c>
+      <c r="H67" t="n">
+        <v>41067989.33</v>
+      </c>
+      <c r="I67" t="n">
+        <v>48219891.21</v>
+      </c>
+      <c r="J67" t="n">
+        <v>89287880.54000001</v>
+      </c>
+      <c r="K67" t="n">
+        <v>7151901.88</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M67" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1035300000</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>920071.BJ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>金钛股份</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-3.351</v>
+      </c>
+      <c r="F68" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="G68" t="n">
+        <v>346718000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>60411052.61</v>
+      </c>
+      <c r="I68" t="n">
+        <v>23333681.12</v>
+      </c>
+      <c r="J68" t="n">
+        <v>83744733.73</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-37077371.49</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-10.69</v>
+      </c>
+      <c r="M68" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="N68" t="n">
+        <v>863100000</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F69" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="G69" t="n">
+        <v>574268900</v>
+      </c>
+      <c r="H69" t="n">
+        <v>52157251.53</v>
+      </c>
+      <c r="I69" t="n">
+        <v>60742121.9</v>
+      </c>
+      <c r="J69" t="n">
+        <v>112899373.43</v>
+      </c>
+      <c r="K69" t="n">
+        <v>8584870.369999999</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M69" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="N69" t="n">
+        <v>734118000</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F70" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="G70" t="n">
+        <v>617131400</v>
+      </c>
+      <c r="H70" t="n">
+        <v>53935489.53</v>
+      </c>
+      <c r="I70" t="n">
+        <v>55268991.65</v>
+      </c>
+      <c r="J70" t="n">
+        <v>109204481.18</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1333502.12</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M70" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N70" t="n">
+        <v>734118000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-9.3949</v>
+      </c>
+      <c r="F71" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="G71" t="n">
+        <v>198154500</v>
+      </c>
+      <c r="H71" t="n">
+        <v>19745914.39</v>
+      </c>
+      <c r="I71" t="n">
+        <v>22873201.62</v>
+      </c>
+      <c r="J71" t="n">
+        <v>42619116.01</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3127287.23</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M71" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="N71" t="n">
+        <v>473754379.44</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>87.88</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-1.5901</v>
+      </c>
+      <c r="F72" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="G72" t="n">
+        <v>528511500</v>
+      </c>
+      <c r="H72" t="n">
+        <v>70701974.40000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>70295653.26000001</v>
+      </c>
+      <c r="J72" t="n">
+        <v>140997627.66</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-406321.14</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M72" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1344564000</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920748.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>路桥信息</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>29.9858</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G73" t="n">
+        <v>241390800</v>
+      </c>
+      <c r="H73" t="n">
+        <v>47266032.9</v>
+      </c>
+      <c r="I73" t="n">
+        <v>62203338.34</v>
+      </c>
+      <c r="J73" t="n">
+        <v>109469371.24</v>
+      </c>
+      <c r="K73" t="n">
+        <v>14937305.44</v>
+      </c>
+      <c r="L73" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M73" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2568508650</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="margin" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5779,4 +5780,98 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>exchange_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rzye</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rzmre</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rzche</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rqye</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rqmcl</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rzrqye</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rqyl</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SSE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1331841736225</v>
+      </c>
+      <c r="D2" t="n">
+        <v>77396224473</v>
+      </c>
+      <c r="E2" t="n">
+        <v>86320164892</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18664487521</v>
+      </c>
+      <c r="G2" t="n">
+        <v>84996899</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1350506223746</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3159503720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="margin" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>1120</v>
+        <v>898</v>
       </c>
       <c r="D2" t="n">
-        <v>4306</v>
+        <v>4554</v>
       </c>
       <c r="E2" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="F2" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
   </sheetData>
@@ -535,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3888.3738</v>
+        <v>3823.6206</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.22</v>
+        <v>-1.67</v>
       </c>
       <c r="F2" t="n">
-        <v>7836.13</v>
+        <v>8045.44</v>
       </c>
     </row>
     <row r="3">
@@ -561,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13316.9689</v>
+        <v>12858.7532</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.34</v>
+        <v>-3.44</v>
       </c>
       <c r="F3" t="n">
-        <v>4023.49</v>
+        <v>4427.27</v>
       </c>
     </row>
     <row r="4">
@@ -587,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3288.9476</v>
+        <v>3139.8249</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.68</v>
+        <v>-4.53</v>
       </c>
       <c r="F4" t="n">
-        <v>1515.42</v>
+        <v>1732.64</v>
       </c>
     </row>
     <row r="5">
@@ -613,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4439.1443</v>
+        <v>4340.755</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.73</v>
+        <v>-2.22</v>
       </c>
       <c r="F5" t="n">
-        <v>3754.62</v>
+        <v>4286.2</v>
       </c>
     </row>
     <row r="6">
@@ -639,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1621.872</v>
+        <v>1555.9804</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.35</v>
+        <v>-4.06</v>
       </c>
       <c r="F6" t="n">
-        <v>699.88</v>
+        <v>805.86</v>
       </c>
     </row>
     <row r="7">
@@ -665,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7570.1448</v>
+        <v>7294.1735</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.26</v>
+        <v>-3.65</v>
       </c>
       <c r="F7" t="n">
-        <v>3433.06</v>
+        <v>3466.01</v>
       </c>
     </row>
   </sheetData>
@@ -707,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19869.54</v>
+        <v>16429.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16429.8</v>
+        <v>16252.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16252.51</v>
+        <v>18524.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18524.99</v>
+        <v>18365.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18365.14</v>
+        <v>20929.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20929.06</v>
+        <v>20481.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20481.34</v>
+        <v>21536.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21536.52</v>
+        <v>17831.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17831.28</v>
+        <v>16691.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
   </sheetData>
@@ -878,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920201.BJ</t>
+          <t>301190.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>20.96</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>24.95</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>20.95</v>
       </c>
       <c r="F2" t="n">
-        <v>72.34999999999999</v>
+        <v>24.95</v>
       </c>
       <c r="G2" t="n">
-        <v>16.77</v>
+        <v>20.79</v>
       </c>
       <c r="H2" t="n">
-        <v>55.58</v>
+        <v>4.16</v>
       </c>
       <c r="I2" t="n">
-        <v>331.4252</v>
+        <v>20.0096</v>
       </c>
       <c r="J2" t="n">
-        <v>74041.59</v>
+        <v>166219.79</v>
       </c>
       <c r="K2" t="n">
-        <v>608990.44401</v>
+        <v>382851.17588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920748.BJ</t>
+          <t>688244.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>17.06</v>
       </c>
       <c r="D3" t="n">
-        <v>36.5</v>
+        <v>19.8</v>
       </c>
       <c r="E3" t="n">
-        <v>26.93</v>
+        <v>16.72</v>
       </c>
       <c r="F3" t="n">
-        <v>36.5</v>
+        <v>19.8</v>
       </c>
       <c r="G3" t="n">
-        <v>28.08</v>
+        <v>16.5</v>
       </c>
       <c r="H3" t="n">
-        <v>8.42</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>29.9858</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>73676.94</v>
+        <v>147652.72</v>
       </c>
       <c r="K3" t="n">
-        <v>241390.81182</v>
+        <v>270535.534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301311.SZ</t>
+          <t>301004.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.06</v>
+        <v>34.48</v>
       </c>
       <c r="D4" t="n">
-        <v>17.98</v>
+        <v>39.24</v>
       </c>
       <c r="E4" t="n">
-        <v>15.06</v>
+        <v>34.48</v>
       </c>
       <c r="F4" t="n">
-        <v>17.98</v>
+        <v>38.28</v>
       </c>
       <c r="G4" t="n">
-        <v>14.98</v>
+        <v>32.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5.58</v>
       </c>
       <c r="I4" t="n">
-        <v>20.0267</v>
+        <v>17.0642</v>
       </c>
       <c r="J4" t="n">
-        <v>338450.78</v>
+        <v>47611.54</v>
       </c>
       <c r="K4" t="n">
-        <v>569676.28309</v>
+        <v>177021.16249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>301699.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.75</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>83.88</v>
+        <v>42.36</v>
       </c>
       <c r="E5" t="n">
-        <v>70.08</v>
+        <v>34.03</v>
       </c>
       <c r="F5" t="n">
-        <v>83.88</v>
+        <v>40.68</v>
       </c>
       <c r="G5" t="n">
-        <v>69.90000000000001</v>
+        <v>35.54</v>
       </c>
       <c r="H5" t="n">
-        <v>13.98</v>
+        <v>5.14</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>14.4626</v>
       </c>
       <c r="J5" t="n">
-        <v>326417.89</v>
+        <v>458529.47</v>
       </c>
       <c r="K5" t="n">
-        <v>2532466.81932</v>
+        <v>1710375.61493</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688682.SH</t>
+          <t>300162.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>7.93</v>
       </c>
       <c r="D6" t="n">
-        <v>37.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>33.99</v>
+        <v>7.93</v>
       </c>
       <c r="F6" t="n">
-        <v>37.94</v>
+        <v>8.67</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62</v>
+        <v>7.68</v>
       </c>
       <c r="H6" t="n">
-        <v>6.32</v>
+        <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>19.9873</v>
+        <v>12.8906</v>
       </c>
       <c r="J6" t="n">
-        <v>59764.06</v>
+        <v>942429.9</v>
       </c>
       <c r="K6" t="n">
-        <v>222120.487</v>
+        <v>821597.36014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>688152.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.02</v>
+        <v>36.74</v>
       </c>
       <c r="D7" t="n">
-        <v>35.54</v>
+        <v>41.19</v>
       </c>
       <c r="E7" t="n">
-        <v>29.02</v>
+        <v>35.21</v>
       </c>
       <c r="F7" t="n">
-        <v>35.54</v>
+        <v>39.45</v>
       </c>
       <c r="G7" t="n">
-        <v>29.62</v>
+        <v>35.23</v>
       </c>
       <c r="H7" t="n">
-        <v>5.92</v>
+        <v>4.22</v>
       </c>
       <c r="I7" t="n">
-        <v>19.9865</v>
+        <v>11.9784</v>
       </c>
       <c r="J7" t="n">
-        <v>258057.7</v>
+        <v>93926.53999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>867521.2948499999</v>
+        <v>358029.445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300300.SZ</t>
+          <t>920926.BJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="D8" t="n">
-        <v>10.81</v>
+        <v>11.5</v>
       </c>
       <c r="E8" t="n">
-        <v>8.83</v>
+        <v>10.03</v>
       </c>
       <c r="F8" t="n">
-        <v>10.81</v>
+        <v>10.9</v>
       </c>
       <c r="G8" t="n">
-        <v>9.01</v>
+        <v>9.83</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="n">
-        <v>19.9778</v>
+        <v>10.885</v>
       </c>
       <c r="J8" t="n">
-        <v>1617425.13</v>
+        <v>56761.97</v>
       </c>
       <c r="K8" t="n">
-        <v>1604221.02948</v>
+        <v>62371.98091</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>920706.BJ</t>
+          <t>300501.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.94</v>
+        <v>9.58</v>
       </c>
       <c r="D9" t="n">
-        <v>19.19</v>
+        <v>10.46</v>
       </c>
       <c r="E9" t="n">
-        <v>14.9</v>
+        <v>9.48</v>
       </c>
       <c r="F9" t="n">
-        <v>18.01</v>
+        <v>10.45</v>
       </c>
       <c r="G9" t="n">
-        <v>15.09</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>19.3506</v>
+        <v>10.582</v>
       </c>
       <c r="J9" t="n">
-        <v>77235.88</v>
+        <v>151231.17</v>
       </c>
       <c r="K9" t="n">
-        <v>129510.86035</v>
+        <v>151694.31693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>920445.BJ</t>
+          <t>600340.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.11</v>
+        <v>1.18</v>
       </c>
       <c r="D10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="E10" t="n">
-        <v>6.96</v>
+        <v>1.18</v>
       </c>
       <c r="F10" t="n">
-        <v>8.029999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>7.1</v>
+        <v>1.17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93</v>
+        <v>0.12</v>
       </c>
       <c r="I10" t="n">
-        <v>13.0986</v>
+        <v>10.2564</v>
       </c>
       <c r="J10" t="n">
-        <v>88875.03999999999</v>
+        <v>1851706</v>
       </c>
       <c r="K10" t="n">
-        <v>68420.65584000001</v>
+        <v>231359.037</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>301136.SZ</t>
+          <t>600032.SH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.77</v>
+        <v>6.81</v>
       </c>
       <c r="D11" t="n">
-        <v>13.88</v>
+        <v>7.43</v>
       </c>
       <c r="E11" t="n">
-        <v>11.68</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3</v>
+        <v>7.43</v>
       </c>
       <c r="G11" t="n">
-        <v>11.84</v>
+        <v>6.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1.46</v>
+        <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>12.3311</v>
+        <v>10.0741</v>
       </c>
       <c r="J11" t="n">
-        <v>258729.68</v>
+        <v>608576.91</v>
       </c>
       <c r="K11" t="n">
-        <v>325910.11715</v>
+        <v>441559.885</v>
       </c>
     </row>
   </sheetData>
@@ -1339,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920025.BJ</t>
+          <t>920201.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.3</v>
+        <v>62.1</v>
       </c>
       <c r="D2" t="n">
-        <v>25.58</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>20.3</v>
+        <v>52.01</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-20.34</v>
       </c>
       <c r="I2" t="n">
-        <v>-30</v>
+        <v>-28.1133</v>
       </c>
       <c r="J2" t="n">
-        <v>270547.93</v>
+        <v>44180.3</v>
       </c>
       <c r="K2" t="n">
-        <v>577722.35387</v>
+        <v>248456.5001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920229.BJ</t>
+          <t>920025.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>70.11</v>
+        <v>18.23</v>
       </c>
       <c r="D3" t="n">
-        <v>76.88</v>
+        <v>18.49</v>
       </c>
       <c r="E3" t="n">
-        <v>64.68000000000001</v>
+        <v>15.15</v>
       </c>
       <c r="F3" t="n">
-        <v>64.68000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="G3" t="n">
-        <v>92.40000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-27.72</v>
+        <v>-5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>-30</v>
+        <v>-25.1232</v>
       </c>
       <c r="J3" t="n">
-        <v>82620.89</v>
+        <v>241745.87</v>
       </c>
       <c r="K3" t="n">
-        <v>574268.94839</v>
+        <v>397738.46041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920427.BJ</t>
+          <t>300585.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.59</v>
+        <v>15.28</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6</v>
+        <v>15.83</v>
       </c>
       <c r="E4" t="n">
-        <v>10.03</v>
+        <v>13.83</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3</v>
+        <v>13.83</v>
       </c>
       <c r="G4" t="n">
-        <v>11.82</v>
+        <v>16.86</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.52</v>
+        <v>-3.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-12.8596</v>
+        <v>-17.9715</v>
       </c>
       <c r="J4" t="n">
-        <v>131198.3</v>
+        <v>178414.62</v>
       </c>
       <c r="K4" t="n">
-        <v>140937.38908</v>
+        <v>255443.90276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688781.SH</t>
+          <t>300829.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>49.88</v>
+        <v>27.29</v>
       </c>
       <c r="D5" t="n">
-        <v>51.55</v>
+        <v>27.5</v>
       </c>
       <c r="E5" t="n">
-        <v>45.02</v>
+        <v>22.49</v>
       </c>
       <c r="F5" t="n">
-        <v>45.02</v>
+        <v>22.7</v>
       </c>
       <c r="G5" t="n">
-        <v>51.56</v>
+        <v>27.56</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.54</v>
+        <v>-4.86</v>
       </c>
       <c r="I5" t="n">
-        <v>-12.6843</v>
+        <v>-17.6343</v>
       </c>
       <c r="J5" t="n">
-        <v>82801.73</v>
+        <v>433803.13</v>
       </c>
       <c r="K5" t="n">
-        <v>391644.978</v>
+        <v>1029834.22437</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688837.SH</t>
+          <t>688628.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.5</v>
+        <v>106.76</v>
       </c>
       <c r="D6" t="n">
-        <v>54.48</v>
+        <v>108</v>
       </c>
       <c r="E6" t="n">
-        <v>47.31</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>47.31</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>53.6</v>
+        <v>110.89</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.29</v>
+        <v>-18.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-11.7351</v>
+        <v>-17.0439</v>
       </c>
       <c r="J6" t="n">
-        <v>202621.82</v>
+        <v>160399.58</v>
       </c>
       <c r="K6" t="n">
-        <v>1020530.716</v>
+        <v>1489321.885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300147.SZ</t>
+          <t>300291.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.26</v>
+        <v>4.9</v>
       </c>
       <c r="D7" t="n">
-        <v>6.34</v>
+        <v>5.15</v>
       </c>
       <c r="E7" t="n">
-        <v>5.55</v>
+        <v>4.73</v>
       </c>
       <c r="F7" t="n">
-        <v>5.62</v>
+        <v>4.83</v>
       </c>
       <c r="G7" t="n">
-        <v>6.33</v>
+        <v>5.78</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.71</v>
+        <v>-0.95</v>
       </c>
       <c r="I7" t="n">
-        <v>-11.2164</v>
+        <v>-16.436</v>
       </c>
       <c r="J7" t="n">
-        <v>166653.37</v>
+        <v>1295297.08</v>
       </c>
       <c r="K7" t="n">
-        <v>100874.5147</v>
+        <v>633638.02042</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>301176.SZ</t>
+          <t>300862.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>56.71</v>
       </c>
       <c r="D8" t="n">
-        <v>63.6</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>58.37</v>
+        <v>45.99</v>
       </c>
       <c r="F8" t="n">
-        <v>58.43</v>
+        <v>47.48</v>
       </c>
       <c r="G8" t="n">
-        <v>65.52</v>
+        <v>56.23</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.09</v>
+        <v>-8.75</v>
       </c>
       <c r="I8" t="n">
-        <v>-10.8211</v>
+        <v>-15.5611</v>
       </c>
       <c r="J8" t="n">
-        <v>176734.81</v>
+        <v>344533.34</v>
       </c>
       <c r="K8" t="n">
-        <v>1067921.72565</v>
+        <v>1725556.93964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688428.SH</t>
+          <t>688312.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33.14</v>
+        <v>57.45</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>57.9</v>
       </c>
       <c r="E9" t="n">
-        <v>29.8</v>
+        <v>48.97</v>
       </c>
       <c r="F9" t="n">
-        <v>29.86</v>
+        <v>49.17</v>
       </c>
       <c r="G9" t="n">
-        <v>33.4</v>
+        <v>57.79</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.54</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-10.5988</v>
+        <v>-14.9161</v>
       </c>
       <c r="J9" t="n">
-        <v>303183.4</v>
+        <v>126431.02</v>
       </c>
       <c r="K9" t="n">
-        <v>950806.138</v>
+        <v>659256.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300741.SZ</t>
+          <t>688655.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29.3</v>
+        <v>72.69</v>
       </c>
       <c r="D10" t="n">
-        <v>29.8</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>26.57</v>
+        <v>62.2</v>
       </c>
       <c r="F10" t="n">
-        <v>26.6</v>
+        <v>63.08</v>
       </c>
       <c r="G10" t="n">
-        <v>29.59</v>
+        <v>73.8</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.99</v>
+        <v>-10.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-10.1048</v>
+        <v>-14.5257</v>
       </c>
       <c r="J10" t="n">
-        <v>308008.58</v>
+        <v>143154.82</v>
       </c>
       <c r="K10" t="n">
-        <v>853318.36704</v>
+        <v>938840.072</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>000607.SZ</t>
+          <t>688143.SH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.2</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>4.3</v>
+        <v>187.87</v>
       </c>
       <c r="E11" t="n">
-        <v>4.03</v>
+        <v>157.2</v>
       </c>
       <c r="F11" t="n">
-        <v>4.03</v>
+        <v>165.05</v>
       </c>
       <c r="G11" t="n">
-        <v>4.48</v>
+        <v>191.35</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.45</v>
+        <v>-26.3</v>
       </c>
       <c r="I11" t="n">
-        <v>-10.0446</v>
+        <v>-13.7444</v>
       </c>
       <c r="J11" t="n">
-        <v>1187597.76</v>
+        <v>133099.69</v>
       </c>
       <c r="K11" t="n">
-        <v>488481.95101</v>
+        <v>2264936.649</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,161 +1819,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000504.SZ</t>
+          <t>000513.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.73</v>
+        <v>30.34</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6019</v>
+        <v>10.0073</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>4.92</v>
       </c>
       <c r="G2" t="n">
-        <v>1525092476</v>
+        <v>842849421</v>
       </c>
       <c r="H2" t="n">
-        <v>117324554</v>
+        <v>96629694.16</v>
       </c>
       <c r="I2" t="n">
-        <v>234403387</v>
+        <v>217253468.66</v>
       </c>
       <c r="J2" t="n">
-        <v>351727941</v>
+        <v>313883162.82</v>
       </c>
       <c r="K2" t="n">
-        <v>117078833</v>
+        <v>120623774.5</v>
       </c>
       <c r="L2" t="n">
-        <v>7.68</v>
+        <v>14.31</v>
       </c>
       <c r="M2" t="n">
-        <v>23.06</v>
+        <v>37.24</v>
       </c>
       <c r="N2" t="n">
-        <v>4518850524.54</v>
+        <v>17222555247.92</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000504.SZ</t>
+          <t>000560.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.73</v>
+        <v>3.71</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6019</v>
+        <v>1.3661</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>27.11</v>
       </c>
       <c r="G3" t="n">
-        <v>2944361889</v>
+        <v>2310346998</v>
       </c>
       <c r="H3" t="n">
-        <v>247534312.55</v>
+        <v>506730786.81</v>
       </c>
       <c r="I3" t="n">
-        <v>264869766.2</v>
+        <v>316336137.1</v>
       </c>
       <c r="J3" t="n">
-        <v>512404078.75</v>
+        <v>823066923.91</v>
       </c>
       <c r="K3" t="n">
-        <v>17335453.65</v>
+        <v>-190394649.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.59</v>
+        <v>-8.24</v>
       </c>
       <c r="M3" t="n">
-        <v>17.4</v>
+        <v>35.63</v>
       </c>
       <c r="N3" t="n">
-        <v>4518850524.54</v>
+        <v>8691372921.49</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000560.SZ</t>
+          <t>000592.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.66</v>
+        <v>9.09</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.1813</v>
+        <v>3.5308</v>
       </c>
       <c r="F4" t="n">
-        <v>33.08</v>
+        <v>29.09</v>
       </c>
       <c r="G4" t="n">
-        <v>2936520453</v>
+        <v>5083871839</v>
       </c>
       <c r="H4" t="n">
-        <v>450456569.39</v>
+        <v>627707868.76</v>
       </c>
       <c r="I4" t="n">
-        <v>424285977.27</v>
+        <v>514508097.45</v>
       </c>
       <c r="J4" t="n">
-        <v>874742546.66</v>
+        <v>1142215966.21</v>
       </c>
       <c r="K4" t="n">
-        <v>-26170592.12</v>
+        <v>-113199771.31</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.89</v>
+        <v>-2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>29.79</v>
+        <v>22.47</v>
       </c>
       <c r="N4" t="n">
-        <v>8574238515.54</v>
+        <v>17408190361.41</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1985,271 +1984,271 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000592.SZ</t>
+          <t>000678.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.779999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="E5" t="n">
-        <v>10.0251</v>
+        <v>10.0207</v>
       </c>
       <c r="F5" t="n">
-        <v>17.01</v>
+        <v>7.61</v>
       </c>
       <c r="G5" t="n">
-        <v>2717291126</v>
+        <v>626070754</v>
       </c>
       <c r="H5" t="n">
-        <v>160014489.11</v>
+        <v>64242780.61</v>
       </c>
       <c r="I5" t="n">
-        <v>635090848.71</v>
+        <v>121996682.61</v>
       </c>
       <c r="J5" t="n">
-        <v>795105337.8200001</v>
+        <v>186239463.22</v>
       </c>
       <c r="K5" t="n">
-        <v>475076359.6</v>
+        <v>57753902</v>
       </c>
       <c r="L5" t="n">
-        <v>17.48</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>29.26</v>
+        <v>29.75</v>
       </c>
       <c r="N5" t="n">
-        <v>16814511702.22</v>
+        <v>4894865638.05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000593.SZ</t>
+          <t>000790.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>德龙汇能</t>
+          <t>华神科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.77</v>
+        <v>4.42</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.0041</v>
+        <v>-5.5556</v>
       </c>
       <c r="F6" t="n">
-        <v>6.12</v>
+        <v>20.36</v>
       </c>
       <c r="G6" t="n">
-        <v>492443412</v>
+        <v>598560827</v>
       </c>
       <c r="H6" t="n">
-        <v>111428402.84</v>
+        <v>90289170.51000001</v>
       </c>
       <c r="I6" t="n">
-        <v>49273695.06</v>
+        <v>64683870.6</v>
       </c>
       <c r="J6" t="n">
-        <v>160702097.9</v>
+        <v>154973041.11</v>
       </c>
       <c r="K6" t="n">
-        <v>-62154707.78</v>
+        <v>-25605299.91</v>
       </c>
       <c r="L6" t="n">
-        <v>-12.62</v>
+        <v>-4.28</v>
       </c>
       <c r="M6" t="n">
-        <v>32.63</v>
+        <v>25.89</v>
       </c>
       <c r="N6" t="n">
-        <v>7804175323.63</v>
+        <v>2752080906.38</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000607.SZ</t>
+          <t>000823.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华媒控股</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.03</v>
+        <v>22.18</v>
       </c>
       <c r="E7" t="n">
-        <v>-10.0446</v>
+        <v>-9.3954</v>
       </c>
       <c r="F7" t="n">
-        <v>13.42</v>
+        <v>26.92</v>
       </c>
       <c r="G7" t="n">
-        <v>488481951</v>
+        <v>3659096152</v>
       </c>
       <c r="H7" t="n">
-        <v>55510701.56</v>
+        <v>442757445.25</v>
       </c>
       <c r="I7" t="n">
-        <v>41729593.01</v>
+        <v>822386287.03</v>
       </c>
       <c r="J7" t="n">
-        <v>97240294.56999999</v>
+        <v>1265143732.28</v>
       </c>
       <c r="K7" t="n">
-        <v>-13781108.55</v>
+        <v>379628841.78</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.82</v>
+        <v>10.37</v>
       </c>
       <c r="M7" t="n">
-        <v>19.91</v>
+        <v>34.58</v>
       </c>
       <c r="N7" t="n">
-        <v>3566800537.04</v>
+        <v>13195595464.06</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000823.SZ</t>
+          <t>000980.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>众泰汽车</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.48</v>
+        <v>2.24</v>
       </c>
       <c r="E8" t="n">
-        <v>-10</v>
+        <v>9.803900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>21.75</v>
+        <v>9.59</v>
       </c>
       <c r="G8" t="n">
-        <v>3267359876</v>
+        <v>1051055425</v>
       </c>
       <c r="H8" t="n">
-        <v>493045763.6</v>
+        <v>82517069.01000001</v>
       </c>
       <c r="I8" t="n">
-        <v>437877407.96</v>
+        <v>259234178.31</v>
       </c>
       <c r="J8" t="n">
-        <v>930923171.5599999</v>
+        <v>341751247.32</v>
       </c>
       <c r="K8" t="n">
-        <v>-55168355.64</v>
+        <v>176717109.3</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.69</v>
+        <v>16.81</v>
       </c>
       <c r="M8" t="n">
-        <v>28.49</v>
+        <v>32.52</v>
       </c>
       <c r="N8" t="n">
-        <v>14563939448.16</v>
+        <v>11295168279.36</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000850.SZ</t>
+          <t>001330.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.12</v>
+        <v>6.36</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1075</v>
+        <v>10.0346</v>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>3.53</v>
       </c>
       <c r="G9" t="n">
-        <v>189478401</v>
+        <v>2220445536</v>
       </c>
       <c r="H9" t="n">
-        <v>29499393</v>
+        <v>253794813.5</v>
       </c>
       <c r="I9" t="n">
-        <v>66116648.6</v>
+        <v>377871272.1</v>
       </c>
       <c r="J9" t="n">
-        <v>95616041.59999999</v>
+        <v>631666085.6</v>
       </c>
       <c r="K9" t="n">
-        <v>36617255.6</v>
+        <v>124076458.6</v>
       </c>
       <c r="L9" t="n">
-        <v>19.33</v>
+        <v>5.59</v>
       </c>
       <c r="M9" t="n">
-        <v>50.46</v>
+        <v>28.45</v>
       </c>
       <c r="N9" t="n">
-        <v>4830076820.48</v>
+        <v>7395708967.92</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2260,106 +2259,106 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000978.SZ</t>
+          <t>001368.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>桂林旅游</t>
+          <t>通达创智</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.91</v>
+        <v>41.8</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.0114</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>15.92</v>
+        <v>10.63</v>
       </c>
       <c r="G10" t="n">
-        <v>597634389</v>
+        <v>459326893</v>
       </c>
       <c r="H10" t="n">
-        <v>74350732.2</v>
+        <v>98643041.15000001</v>
       </c>
       <c r="I10" t="n">
-        <v>72278972.78</v>
+        <v>67035311</v>
       </c>
       <c r="J10" t="n">
-        <v>146629704.98</v>
+        <v>165678352.15</v>
       </c>
       <c r="K10" t="n">
-        <v>-2071759.42</v>
+        <v>-31607730.15</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.35</v>
+        <v>-6.88</v>
       </c>
       <c r="M10" t="n">
-        <v>24.54</v>
+        <v>36.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3702841563.33</v>
+        <v>4517769038.2</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>001216.SZ</t>
+          <t>001368.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>通达创智</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.4</v>
+        <v>41.8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3179</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>17.36</v>
+        <v>10.63</v>
       </c>
       <c r="G11" t="n">
-        <v>2897387829</v>
+        <v>1153499086</v>
       </c>
       <c r="H11" t="n">
-        <v>231043605.89</v>
+        <v>172407770.65</v>
       </c>
       <c r="I11" t="n">
-        <v>301818490.77</v>
+        <v>177857708.16</v>
       </c>
       <c r="J11" t="n">
-        <v>532862096.66</v>
+        <v>350265478.81</v>
       </c>
       <c r="K11" t="n">
-        <v>70774884.88</v>
+        <v>5449937.51</v>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>18.39</v>
+        <v>30.37</v>
       </c>
       <c r="N11" t="n">
-        <v>7010148051.6</v>
+        <v>4517769038.2</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2370,106 +2369,106 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>001234.SZ</t>
+          <t>002119.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>35.4</v>
+        <v>29.71</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0062</v>
+        <v>0.3377</v>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>33.71</v>
       </c>
       <c r="G12" t="n">
-        <v>170037492</v>
+        <v>3646959347</v>
       </c>
       <c r="H12" t="n">
-        <v>37286264</v>
+        <v>649073540.79</v>
       </c>
       <c r="I12" t="n">
-        <v>81105223.40000001</v>
+        <v>533283310.19</v>
       </c>
       <c r="J12" t="n">
-        <v>118391487.4</v>
+        <v>1182356850.98</v>
       </c>
       <c r="K12" t="n">
-        <v>43818959.4</v>
+        <v>-115790230.6</v>
       </c>
       <c r="L12" t="n">
-        <v>25.77</v>
+        <v>-3.17</v>
       </c>
       <c r="M12" t="n">
-        <v>69.63</v>
+        <v>32.42</v>
       </c>
       <c r="N12" t="n">
-        <v>3240569100</v>
+        <v>11149687640</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>001317.SZ</t>
+          <t>002342.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65.3</v>
+        <v>8.68</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0067</v>
+        <v>10.0127</v>
       </c>
       <c r="F13" t="n">
-        <v>14.87</v>
+        <v>25.01</v>
       </c>
       <c r="G13" t="n">
-        <v>793141125</v>
+        <v>2008963896</v>
       </c>
       <c r="H13" t="n">
-        <v>136700331.1</v>
+        <v>368349656.77</v>
       </c>
       <c r="I13" t="n">
-        <v>130542551.58</v>
+        <v>444698663.54</v>
       </c>
       <c r="J13" t="n">
-        <v>267242882.68</v>
+        <v>813048320.3099999</v>
       </c>
       <c r="K13" t="n">
-        <v>-6157779.52</v>
+        <v>76349006.77</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.78</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>33.69</v>
+        <v>40.47</v>
       </c>
       <c r="N13" t="n">
-        <v>5583314360.1</v>
+        <v>8286709200</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2480,51 +2479,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002082.SZ</t>
+          <t>002342.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ST万邦</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>8.68</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5409</v>
+        <v>10.0127</v>
       </c>
       <c r="F14" t="n">
-        <v>5.46</v>
+        <v>25.01</v>
       </c>
       <c r="G14" t="n">
-        <v>868943882</v>
+        <v>3113342036</v>
       </c>
       <c r="H14" t="n">
-        <v>127502606</v>
+        <v>571712704.8099999</v>
       </c>
       <c r="I14" t="n">
-        <v>104843125.67</v>
+        <v>608264993.8099999</v>
       </c>
       <c r="J14" t="n">
-        <v>232345731.67</v>
+        <v>1179977698.62</v>
       </c>
       <c r="K14" t="n">
-        <v>-22659480.33</v>
+        <v>36552289</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.61</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
-        <v>26.74</v>
+        <v>37.9</v>
       </c>
       <c r="N14" t="n">
-        <v>6814175064</v>
+        <v>8286709200</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2535,271 +2534,271 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002106.SZ</t>
+          <t>002614.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>莱宝高科</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.51</v>
+        <v>8.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-10</v>
+        <v>2.0408</v>
       </c>
       <c r="F15" t="n">
-        <v>7.74</v>
+        <v>42.87</v>
       </c>
       <c r="G15" t="n">
-        <v>715305554</v>
+        <v>1574292219</v>
       </c>
       <c r="H15" t="n">
-        <v>68001069.22</v>
+        <v>244914429.13</v>
       </c>
       <c r="I15" t="n">
-        <v>39256729.53</v>
+        <v>191397095.61</v>
       </c>
       <c r="J15" t="n">
-        <v>107257798.75</v>
+        <v>436311524.74</v>
       </c>
       <c r="K15" t="n">
-        <v>-28744339.69</v>
+        <v>-53517333.52</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.02</v>
+        <v>-3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>14.99</v>
+        <v>27.71</v>
       </c>
       <c r="N15" t="n">
-        <v>8819497983.42</v>
+        <v>3750840143.5</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002119.SZ</t>
+          <t>002640.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>跨境通</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.61</v>
+        <v>3.96</v>
       </c>
       <c r="E16" t="n">
-        <v>9.992599999999999</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>30.86</v>
+        <v>17.28</v>
       </c>
       <c r="G16" t="n">
-        <v>3358508146</v>
+        <v>1049611659</v>
       </c>
       <c r="H16" t="n">
-        <v>741027532.52</v>
+        <v>87363464</v>
       </c>
       <c r="I16" t="n">
-        <v>573465677.0700001</v>
+        <v>311423736.52</v>
       </c>
       <c r="J16" t="n">
-        <v>1314493209.59</v>
+        <v>398787200.52</v>
       </c>
       <c r="K16" t="n">
-        <v>-167561855.45</v>
+        <v>224060272.52</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.99</v>
+        <v>21.35</v>
       </c>
       <c r="M16" t="n">
-        <v>39.14</v>
+        <v>37.99</v>
       </c>
       <c r="N16" t="n">
-        <v>11112159240</v>
+        <v>6131116648.8</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002119.SZ</t>
+          <t>002679.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>福建金森</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.61</v>
+        <v>11.86</v>
       </c>
       <c r="E17" t="n">
-        <v>9.992599999999999</v>
+        <v>2.418</v>
       </c>
       <c r="F17" t="n">
-        <v>30.86</v>
+        <v>16.19</v>
       </c>
       <c r="G17" t="n">
-        <v>4837413824</v>
+        <v>437748698</v>
       </c>
       <c r="H17" t="n">
-        <v>971457927.92</v>
+        <v>61553556.05</v>
       </c>
       <c r="I17" t="n">
-        <v>965239189.9299999</v>
+        <v>66186370.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1936697117.85</v>
+        <v>127739926.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-6218737.99</v>
+        <v>4632814.05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.13</v>
+        <v>1.06</v>
       </c>
       <c r="M17" t="n">
-        <v>40.04</v>
+        <v>29.18</v>
       </c>
       <c r="N17" t="n">
-        <v>11112159240</v>
+        <v>2796066160</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002164.SZ</t>
+          <t>002819.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.06</v>
+        <v>24.97</v>
       </c>
       <c r="E18" t="n">
-        <v>10.0253</v>
+        <v>-6.3391</v>
       </c>
       <c r="F18" t="n">
-        <v>14.93</v>
+        <v>12.38</v>
       </c>
       <c r="G18" t="n">
-        <v>921657308</v>
+        <v>766756067</v>
       </c>
       <c r="H18" t="n">
-        <v>129158495.89</v>
+        <v>92422435.78</v>
       </c>
       <c r="I18" t="n">
-        <v>243760323.73</v>
+        <v>55907474.35</v>
       </c>
       <c r="J18" t="n">
-        <v>372918819.62</v>
+        <v>148329910.13</v>
       </c>
       <c r="K18" t="n">
-        <v>114601827.84</v>
+        <v>-36514961.43</v>
       </c>
       <c r="L18" t="n">
-        <v>12.43</v>
+        <v>-4.76</v>
       </c>
       <c r="M18" t="n">
-        <v>40.46</v>
+        <v>19.35</v>
       </c>
       <c r="N18" t="n">
-        <v>6265863367.58</v>
+        <v>5897876195.42</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002164.SZ</t>
+          <t>002935.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>天奥电子</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.06</v>
+        <v>18.26</v>
       </c>
       <c r="E19" t="n">
-        <v>10.0253</v>
+        <v>0.9956</v>
       </c>
       <c r="F19" t="n">
-        <v>14.93</v>
+        <v>5.65</v>
       </c>
       <c r="G19" t="n">
-        <v>2175305917</v>
+        <v>1216557728</v>
       </c>
       <c r="H19" t="n">
-        <v>242185291.08</v>
+        <v>143645059.32</v>
       </c>
       <c r="I19" t="n">
-        <v>507275638.88</v>
+        <v>146817000.73</v>
       </c>
       <c r="J19" t="n">
-        <v>749460929.96</v>
+        <v>290462060.05</v>
       </c>
       <c r="K19" t="n">
-        <v>265090347.8</v>
+        <v>3171941.41</v>
       </c>
       <c r="L19" t="n">
-        <v>12.19</v>
+        <v>0.26</v>
       </c>
       <c r="M19" t="n">
-        <v>34.45</v>
+        <v>23.88</v>
       </c>
       <c r="N19" t="n">
-        <v>6265863367.58</v>
+        <v>7579559523.58</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2810,1536 +2809,1536 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002172.SZ</t>
+          <t>003001.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>中岩大地</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.42</v>
+        <v>19.83</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3084</v>
+        <v>-6.019</v>
       </c>
       <c r="F20" t="n">
-        <v>24.71</v>
+        <v>16.75</v>
       </c>
       <c r="G20" t="n">
-        <v>1028721392</v>
+        <v>389507058</v>
       </c>
       <c r="H20" t="n">
-        <v>116362136</v>
+        <v>113522391.92</v>
       </c>
       <c r="I20" t="n">
-        <v>83494907.18000001</v>
+        <v>61661883.2</v>
       </c>
       <c r="J20" t="n">
-        <v>199857043.18</v>
+        <v>175184275.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-32867228.82</v>
+        <v>-51860508.72</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.19</v>
+        <v>-13.31</v>
       </c>
       <c r="M20" t="n">
-        <v>19.43</v>
+        <v>44.98</v>
       </c>
       <c r="N20" t="n">
-        <v>4147062756.6</v>
+        <v>2267580369.66</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002205.SZ</t>
+          <t>300291.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>国统股份</t>
+          <t>百纳千成</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.78</v>
+        <v>4.83</v>
       </c>
       <c r="E21" t="n">
-        <v>9.982799999999999</v>
+        <v>-16.436</v>
       </c>
       <c r="F21" t="n">
-        <v>9.41</v>
+        <v>13.92</v>
       </c>
       <c r="G21" t="n">
-        <v>201473191</v>
+        <v>633638020</v>
       </c>
       <c r="H21" t="n">
-        <v>26495412.01</v>
+        <v>50952864.68</v>
       </c>
       <c r="I21" t="n">
-        <v>33807320</v>
+        <v>70870311</v>
       </c>
       <c r="J21" t="n">
-        <v>60302732.01</v>
+        <v>121823175.68</v>
       </c>
       <c r="K21" t="n">
-        <v>7311907.99</v>
+        <v>19917446.32</v>
       </c>
       <c r="L21" t="n">
-        <v>3.63</v>
+        <v>3.14</v>
       </c>
       <c r="M21" t="n">
-        <v>29.93</v>
+        <v>19.23</v>
       </c>
       <c r="N21" t="n">
-        <v>2375076453.84</v>
+        <v>4495564250.52</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002205.SZ</t>
+          <t>300300.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>国统股份</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.78</v>
+        <v>11.08</v>
       </c>
       <c r="E22" t="n">
-        <v>9.982799999999999</v>
+        <v>2.4977</v>
       </c>
       <c r="F22" t="n">
-        <v>9.41</v>
+        <v>35.52</v>
       </c>
       <c r="G22" t="n">
-        <v>327017535</v>
+        <v>2650936634</v>
       </c>
       <c r="H22" t="n">
-        <v>37925761</v>
+        <v>394057141.08</v>
       </c>
       <c r="I22" t="n">
-        <v>44657319</v>
+        <v>260308059.51</v>
       </c>
       <c r="J22" t="n">
-        <v>82583080</v>
+        <v>654365200.59</v>
       </c>
       <c r="K22" t="n">
-        <v>6731558</v>
+        <v>-133749081.57</v>
       </c>
       <c r="L22" t="n">
-        <v>2.06</v>
+        <v>-5.05</v>
       </c>
       <c r="M22" t="n">
-        <v>25.25</v>
+        <v>24.68</v>
       </c>
       <c r="N22" t="n">
-        <v>2375076453.84</v>
+        <v>7388250368</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002413.SZ</t>
+          <t>300585.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>奥联电子</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8.970000000000001</v>
+        <v>13.83</v>
       </c>
       <c r="E23" t="n">
-        <v>10.0613</v>
+        <v>-17.9715</v>
       </c>
       <c r="F23" t="n">
-        <v>17.21</v>
+        <v>10.43</v>
       </c>
       <c r="G23" t="n">
-        <v>1977372525</v>
+        <v>255443903</v>
       </c>
       <c r="H23" t="n">
-        <v>180387994.1</v>
+        <v>36163989</v>
       </c>
       <c r="I23" t="n">
-        <v>351385229.27</v>
+        <v>29143906.42</v>
       </c>
       <c r="J23" t="n">
-        <v>531773223.37</v>
+        <v>65307895.42</v>
       </c>
       <c r="K23" t="n">
-        <v>170997235.17</v>
+        <v>-7020082.58</v>
       </c>
       <c r="L23" t="n">
-        <v>8.65</v>
+        <v>-2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>26.89</v>
+        <v>25.57</v>
       </c>
       <c r="N23" t="n">
-        <v>11620011558.09</v>
+        <v>2366466665.13</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002579.SZ</t>
+          <t>300829.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>金丹科技</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19.22</v>
+        <v>22.7</v>
       </c>
       <c r="E24" t="n">
-        <v>3.3333</v>
+        <v>-17.6343</v>
       </c>
       <c r="F24" t="n">
-        <v>29.7</v>
+        <v>25.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3361505550</v>
+        <v>1029834224</v>
       </c>
       <c r="H24" t="n">
-        <v>641752088.3099999</v>
+        <v>183310815.42</v>
       </c>
       <c r="I24" t="n">
-        <v>536438912.2</v>
+        <v>183784007.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1178191000.51</v>
+        <v>367094822.92</v>
       </c>
       <c r="K24" t="n">
-        <v>-105313176.11</v>
+        <v>473192.08</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.13</v>
+        <v>0.05</v>
       </c>
       <c r="M24" t="n">
-        <v>35.05</v>
+        <v>35.65</v>
       </c>
       <c r="N24" t="n">
-        <v>11213683299.54</v>
+        <v>3816592563.7</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002614.SZ</t>
+          <t>300862.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>蓝盾光电</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.33</v>
+        <v>47.48</v>
       </c>
       <c r="E25" t="n">
-        <v>10.0396</v>
+        <v>-15.5611</v>
       </c>
       <c r="F25" t="n">
-        <v>12.99</v>
+        <v>22.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1454429912</v>
+        <v>1725556940</v>
       </c>
       <c r="H25" t="n">
-        <v>129342444.32</v>
+        <v>254487972.14</v>
       </c>
       <c r="I25" t="n">
-        <v>274768488.74</v>
+        <v>239579809.47</v>
       </c>
       <c r="J25" t="n">
-        <v>404110933.06</v>
+        <v>494067781.61</v>
       </c>
       <c r="K25" t="n">
-        <v>145426044.42</v>
+        <v>-14908162.67</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>-0.86</v>
       </c>
       <c r="M25" t="n">
-        <v>27.78</v>
+        <v>28.63</v>
       </c>
       <c r="N25" t="n">
-        <v>3675823340.63</v>
+        <v>7191843412.36</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002819.SZ</t>
+          <t>301004.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>嘉益股份</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.66</v>
+        <v>38.28</v>
       </c>
       <c r="E26" t="n">
-        <v>9.983499999999999</v>
+        <v>17.0642</v>
       </c>
       <c r="F26" t="n">
-        <v>7.88</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>713627344</v>
+        <v>177021162</v>
       </c>
       <c r="H26" t="n">
-        <v>130906611</v>
+        <v>40670340.79</v>
       </c>
       <c r="I26" t="n">
-        <v>125184552.5</v>
+        <v>25117004.56</v>
       </c>
       <c r="J26" t="n">
-        <v>256091163.5</v>
+        <v>65787345.35</v>
       </c>
       <c r="K26" t="n">
-        <v>-5722058.5</v>
+        <v>-15553336.23</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.8</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>35.89</v>
+        <v>37.16</v>
       </c>
       <c r="N26" t="n">
-        <v>6297051636.76</v>
+        <v>5210190315</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002836.SZ</t>
+          <t>301190.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>新宏泽</t>
+          <t>善水科技</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.27</v>
+        <v>24.95</v>
       </c>
       <c r="E27" t="n">
-        <v>10.0448</v>
+        <v>20.0096</v>
       </c>
       <c r="F27" t="n">
-        <v>10.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>286117123</v>
+        <v>382851176</v>
       </c>
       <c r="H27" t="n">
-        <v>26384988.76</v>
+        <v>72544320.48</v>
       </c>
       <c r="I27" t="n">
-        <v>77110800.31</v>
+        <v>115640749.32</v>
       </c>
       <c r="J27" t="n">
-        <v>103495789.07</v>
+        <v>188185069.8</v>
       </c>
       <c r="K27" t="n">
-        <v>50725811.55</v>
+        <v>43096428.84</v>
       </c>
       <c r="L27" t="n">
-        <v>17.73</v>
+        <v>11.26</v>
       </c>
       <c r="M27" t="n">
-        <v>36.17</v>
+        <v>49.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2827008000</v>
+        <v>4537257300</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002849.SZ</t>
+          <t>301583.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>威星智能</t>
+          <t>托伦斯</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24.75</v>
+        <v>137.13</v>
       </c>
       <c r="E28" t="n">
-        <v>7.6087</v>
+        <v>-3.3547</v>
       </c>
       <c r="F28" t="n">
-        <v>22.74</v>
+        <v>36.98</v>
       </c>
       <c r="G28" t="n">
-        <v>1685711101</v>
+        <v>1627681002</v>
       </c>
       <c r="H28" t="n">
-        <v>311230414.74</v>
+        <v>158394669.18</v>
       </c>
       <c r="I28" t="n">
-        <v>319370374.04</v>
+        <v>176107975.89</v>
       </c>
       <c r="J28" t="n">
-        <v>630600788.78</v>
+        <v>334502645.07</v>
       </c>
       <c r="K28" t="n">
-        <v>8139959.3</v>
+        <v>17713306.71</v>
       </c>
       <c r="L28" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="M28" t="n">
-        <v>37.41</v>
+        <v>20.55</v>
       </c>
       <c r="N28" t="n">
-        <v>5412610714.5</v>
+        <v>4227906179.49</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002856.SZ</t>
+          <t>301689.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>*ST美芝</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17.79</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.0152</v>
+        <v>1.4545</v>
       </c>
       <c r="F29" t="n">
-        <v>10.61</v>
+        <v>56.84</v>
       </c>
       <c r="G29" t="n">
-        <v>445689511</v>
+        <v>2601726950</v>
       </c>
       <c r="H29" t="n">
-        <v>56447199</v>
+        <v>373168515.6</v>
       </c>
       <c r="I29" t="n">
-        <v>70232816</v>
+        <v>323792104.19</v>
       </c>
       <c r="J29" t="n">
-        <v>126680015</v>
+        <v>696960619.79</v>
       </c>
       <c r="K29" t="n">
-        <v>13785617</v>
+        <v>-49376411.41</v>
       </c>
       <c r="L29" t="n">
-        <v>3.09</v>
+        <v>-1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>28.42</v>
+        <v>26.79</v>
       </c>
       <c r="N29" t="n">
-        <v>2204260040.97</v>
+        <v>4898479565.2</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002909.SZ</t>
+          <t>301697.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>集泰股份</t>
+          <t>贝特利</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8.289999999999999</v>
+        <v>28.59</v>
       </c>
       <c r="E30" t="n">
-        <v>9.946899999999999</v>
+        <v>-4.9535</v>
       </c>
       <c r="F30" t="n">
-        <v>19.86</v>
+        <v>33.78</v>
       </c>
       <c r="G30" t="n">
-        <v>1146893102</v>
+        <v>418592545</v>
       </c>
       <c r="H30" t="n">
-        <v>104564411.97</v>
+        <v>87778574.5</v>
       </c>
       <c r="I30" t="n">
-        <v>161167097.05</v>
+        <v>64890028.7</v>
       </c>
       <c r="J30" t="n">
-        <v>265731509.02</v>
+        <v>152668603.2</v>
       </c>
       <c r="K30" t="n">
-        <v>56602685.08</v>
+        <v>-22888545.8</v>
       </c>
       <c r="L30" t="n">
-        <v>4.94</v>
+        <v>-5.47</v>
       </c>
       <c r="M30" t="n">
-        <v>23.17</v>
+        <v>36.47</v>
       </c>
       <c r="N30" t="n">
-        <v>3153743005.07</v>
+        <v>1257703662.06</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300192.SZ</t>
+          <t>301699.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>科德教育</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25.31</v>
+        <v>40.68</v>
       </c>
       <c r="E31" t="n">
-        <v>10.2832</v>
+        <v>14.4626</v>
       </c>
       <c r="F31" t="n">
-        <v>12.81</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>2664255446</v>
+        <v>1710375615</v>
       </c>
       <c r="H31" t="n">
-        <v>454462227.38</v>
+        <v>266133190.07</v>
       </c>
       <c r="I31" t="n">
-        <v>573798284.88</v>
+        <v>161746064.24</v>
       </c>
       <c r="J31" t="n">
-        <v>1028260512.26</v>
+        <v>427879254.31</v>
       </c>
       <c r="K31" t="n">
-        <v>119336057.5</v>
+        <v>-104387125.83</v>
       </c>
       <c r="L31" t="n">
-        <v>4.48</v>
+        <v>-6.1</v>
       </c>
       <c r="M31" t="n">
-        <v>38.59</v>
+        <v>25.02</v>
       </c>
       <c r="N31" t="n">
-        <v>11527180831.8</v>
+        <v>2844811345.32</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300300.SZ</t>
+          <t>301699.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.81</v>
+        <v>40.68</v>
       </c>
       <c r="E32" t="n">
-        <v>19.9778</v>
+        <v>14.4626</v>
       </c>
       <c r="F32" t="n">
-        <v>24.26</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>1604221029</v>
+        <v>2577896910</v>
       </c>
       <c r="H32" t="n">
-        <v>75838777.23</v>
+        <v>352372639.85</v>
       </c>
       <c r="I32" t="n">
-        <v>363586890.51</v>
+        <v>298037943.21</v>
       </c>
       <c r="J32" t="n">
-        <v>439425667.74</v>
+        <v>650410583.0599999</v>
       </c>
       <c r="K32" t="n">
-        <v>287748113.28</v>
+        <v>-54334696.64</v>
       </c>
       <c r="L32" t="n">
-        <v>17.94</v>
+        <v>-2.11</v>
       </c>
       <c r="M32" t="n">
-        <v>27.39</v>
+        <v>25.23</v>
       </c>
       <c r="N32" t="n">
-        <v>7208211776</v>
+        <v>2844811345.32</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>301311.SZ</t>
+          <t>600032.SH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>昆船智能</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17.98</v>
+        <v>7.43</v>
       </c>
       <c r="E33" t="n">
-        <v>20.0267</v>
+        <v>10.0741</v>
       </c>
       <c r="F33" t="n">
-        <v>14.1</v>
+        <v>2.53</v>
       </c>
       <c r="G33" t="n">
-        <v>569676283</v>
+        <v>441559885</v>
       </c>
       <c r="H33" t="n">
-        <v>65234436.73</v>
+        <v>33228975.96</v>
       </c>
       <c r="I33" t="n">
-        <v>94620544.76000001</v>
+        <v>88662630.81</v>
       </c>
       <c r="J33" t="n">
-        <v>159854981.49</v>
+        <v>121891606.77</v>
       </c>
       <c r="K33" t="n">
-        <v>29386108.03</v>
+        <v>55433654.85</v>
       </c>
       <c r="L33" t="n">
-        <v>5.16</v>
+        <v>12.55</v>
       </c>
       <c r="M33" t="n">
-        <v>28.06</v>
+        <v>27.6</v>
       </c>
       <c r="N33" t="n">
-        <v>4315200000</v>
+        <v>17866737657.32</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>301311.SZ</t>
+          <t>600293.SH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>昆船智能</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17.98</v>
+        <v>3.93</v>
       </c>
       <c r="E34" t="n">
-        <v>20.0267</v>
+        <v>3.9683</v>
       </c>
       <c r="F34" t="n">
-        <v>14.1</v>
+        <v>18.04</v>
       </c>
       <c r="G34" t="n">
-        <v>1112034082</v>
+        <v>2059218861</v>
       </c>
       <c r="H34" t="n">
-        <v>164290204.95</v>
+        <v>169533167.58</v>
       </c>
       <c r="I34" t="n">
-        <v>141184300.57</v>
+        <v>151688319.02</v>
       </c>
       <c r="J34" t="n">
-        <v>305474505.52</v>
+        <v>321221486.6</v>
       </c>
       <c r="K34" t="n">
-        <v>-23105904.38</v>
+        <v>-17844848.56</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.08</v>
+        <v>-0.87</v>
       </c>
       <c r="M34" t="n">
-        <v>27.47</v>
+        <v>15.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4315200000</v>
+        <v>4559370030.78</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>600340.SH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74.19</v>
+        <v>1.29</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.8144</v>
+        <v>10.2564</v>
       </c>
       <c r="F35" t="n">
-        <v>43.73</v>
+        <v>4.76</v>
       </c>
       <c r="G35" t="n">
-        <v>1112318961</v>
+        <v>231359037</v>
       </c>
       <c r="H35" t="n">
-        <v>131172135.52</v>
+        <v>18556856.19</v>
       </c>
       <c r="I35" t="n">
-        <v>105839674.4</v>
+        <v>11484817.4</v>
       </c>
       <c r="J35" t="n">
-        <v>237011809.92</v>
+        <v>30041673.59</v>
       </c>
       <c r="K35" t="n">
-        <v>-25332461.12</v>
+        <v>-7072038.79</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.28</v>
+        <v>-3.06</v>
       </c>
       <c r="M35" t="n">
-        <v>21.31</v>
+        <v>12.98</v>
       </c>
       <c r="N35" t="n">
-        <v>2425897486.17</v>
+        <v>5022428029.98</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>600353.SH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>旭光电子</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>141.89</v>
+        <v>29.31</v>
       </c>
       <c r="E36" t="n">
-        <v>5.3534</v>
+        <v>-10.0092</v>
       </c>
       <c r="F36" t="n">
-        <v>43.96</v>
+        <v>5.8</v>
       </c>
       <c r="G36" t="n">
-        <v>1920357462</v>
+        <v>1445828491</v>
       </c>
       <c r="H36" t="n">
-        <v>268999321.14</v>
+        <v>232985348.92</v>
       </c>
       <c r="I36" t="n">
-        <v>155041790.91</v>
+        <v>236923020.74</v>
       </c>
       <c r="J36" t="n">
-        <v>424041112.05</v>
+        <v>469908369.66</v>
       </c>
       <c r="K36" t="n">
-        <v>-113957530.23</v>
+        <v>3937671.82</v>
       </c>
       <c r="L36" t="n">
-        <v>-5.93</v>
+        <v>0.27</v>
       </c>
       <c r="M36" t="n">
-        <v>22.08</v>
+        <v>32.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4374663514.97</v>
+        <v>24292455070.29</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>600540.SH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>新赛股份</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>83.88</v>
+        <v>5.64</v>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>3.8674</v>
       </c>
       <c r="F37" t="n">
-        <v>56.71</v>
+        <v>28.27</v>
       </c>
       <c r="G37" t="n">
-        <v>2532466819</v>
+        <v>952020633</v>
       </c>
       <c r="H37" t="n">
-        <v>304164898.74</v>
+        <v>158684330</v>
       </c>
       <c r="I37" t="n">
-        <v>324931664.84</v>
+        <v>221204138</v>
       </c>
       <c r="J37" t="n">
-        <v>629096563.58</v>
+        <v>379888468</v>
       </c>
       <c r="K37" t="n">
-        <v>20766766.1</v>
+        <v>62519808</v>
       </c>
       <c r="L37" t="n">
-        <v>0.82</v>
+        <v>6.57</v>
       </c>
       <c r="M37" t="n">
-        <v>24.84</v>
+        <v>39.9</v>
       </c>
       <c r="N37" t="n">
-        <v>4828254593.76</v>
+        <v>3278966054.4</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>600547.SH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>山东黄金</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>83.88</v>
+        <v>26.16</v>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>-10.0103</v>
       </c>
       <c r="F38" t="n">
-        <v>56.71</v>
+        <v>3.88</v>
       </c>
       <c r="G38" t="n">
-        <v>4443255699</v>
+        <v>3716226173</v>
       </c>
       <c r="H38" t="n">
-        <v>386383264</v>
+        <v>822681758.8</v>
       </c>
       <c r="I38" t="n">
-        <v>560648767.76</v>
+        <v>595094972.78</v>
       </c>
       <c r="J38" t="n">
-        <v>947032031.76</v>
+        <v>1417776731.58</v>
       </c>
       <c r="K38" t="n">
-        <v>174265503.76</v>
+        <v>-227586786.02</v>
       </c>
       <c r="L38" t="n">
-        <v>3.92</v>
+        <v>-6.12</v>
       </c>
       <c r="M38" t="n">
-        <v>21.31</v>
+        <v>38.15</v>
       </c>
       <c r="N38" t="n">
-        <v>4828254593.76</v>
+        <v>94553837957.52</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>301697.SZ</t>
+          <t>600721.SH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>贝特利</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30.08</v>
+        <v>12.18</v>
       </c>
       <c r="E39" t="n">
-        <v>6.4025</v>
+        <v>-5.7276</v>
       </c>
       <c r="F39" t="n">
-        <v>45.54</v>
+        <v>26.06</v>
       </c>
       <c r="G39" t="n">
-        <v>600432047</v>
+        <v>1231440169</v>
       </c>
       <c r="H39" t="n">
-        <v>73308066.23999999</v>
+        <v>201108406</v>
       </c>
       <c r="I39" t="n">
-        <v>101668137.51</v>
+        <v>128231457</v>
       </c>
       <c r="J39" t="n">
-        <v>174976203.75</v>
+        <v>329339863</v>
       </c>
       <c r="K39" t="n">
-        <v>28360071.27</v>
+        <v>-72876949</v>
       </c>
       <c r="L39" t="n">
-        <v>4.72</v>
+        <v>-5.92</v>
       </c>
       <c r="M39" t="n">
-        <v>29.14</v>
+        <v>26.74</v>
       </c>
       <c r="N39" t="n">
-        <v>1323250302.72</v>
+        <v>4683790194.3</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>600743.SH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>华远控股</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>35.54</v>
+        <v>2.3</v>
       </c>
       <c r="E40" t="n">
-        <v>19.9865</v>
+        <v>-10.1563</v>
       </c>
       <c r="F40" t="n">
-        <v>36.9</v>
+        <v>6.4</v>
       </c>
       <c r="G40" t="n">
-        <v>867521295</v>
+        <v>348103448</v>
       </c>
       <c r="H40" t="n">
-        <v>103833129.3</v>
+        <v>66656391.38</v>
       </c>
       <c r="I40" t="n">
-        <v>205217688.19</v>
+        <v>50458980</v>
       </c>
       <c r="J40" t="n">
-        <v>309050817.49</v>
+        <v>117115371.38</v>
       </c>
       <c r="K40" t="n">
-        <v>101384558.89</v>
+        <v>-16197411.38</v>
       </c>
       <c r="L40" t="n">
-        <v>11.69</v>
+        <v>-4.65</v>
       </c>
       <c r="M40" t="n">
-        <v>35.62</v>
+        <v>33.64</v>
       </c>
       <c r="N40" t="n">
-        <v>2485363697.46</v>
+        <v>5396032010.2</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600127.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.49</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5522</v>
+        <v>10.0386</v>
       </c>
       <c r="F41" t="n">
-        <v>41.31</v>
+        <v>0.48</v>
       </c>
       <c r="G41" t="n">
-        <v>4318063100</v>
+        <v>42985476</v>
       </c>
       <c r="H41" t="n">
-        <v>634960720.64</v>
+        <v>8644905</v>
       </c>
       <c r="I41" t="n">
-        <v>613820524.77</v>
+        <v>37812375</v>
       </c>
       <c r="J41" t="n">
-        <v>1248781245.41</v>
+        <v>46457280</v>
       </c>
       <c r="K41" t="n">
-        <v>-21140195.87</v>
+        <v>29167470</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.49</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>28.92</v>
+        <v>108.08</v>
       </c>
       <c r="N41" t="n">
-        <v>10583005264.82</v>
+        <v>8933791117.5</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600189.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>泉阳泉</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>10.0363</v>
+        <v>10.0386</v>
       </c>
       <c r="F42" t="n">
-        <v>5.38</v>
+        <v>0.48</v>
       </c>
       <c r="G42" t="n">
-        <v>341477434</v>
+        <v>89490418</v>
       </c>
       <c r="H42" t="n">
-        <v>59389844</v>
+        <v>11314445.1</v>
       </c>
       <c r="I42" t="n">
-        <v>98700624.3</v>
+        <v>46458300</v>
       </c>
       <c r="J42" t="n">
-        <v>158090468.3</v>
+        <v>57772745.1</v>
       </c>
       <c r="K42" t="n">
-        <v>39310780.3</v>
+        <v>35143854.9</v>
       </c>
       <c r="L42" t="n">
-        <v>11.51</v>
+        <v>39.27</v>
       </c>
       <c r="M42" t="n">
-        <v>46.3</v>
+        <v>64.56</v>
       </c>
       <c r="N42" t="n">
-        <v>6508300089.2</v>
+        <v>8933791117.5</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600371.SH</t>
+          <t>601086.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>15.85</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.275499999999999</v>
+        <v>3.4595</v>
       </c>
       <c r="F43" t="n">
-        <v>30.99</v>
+        <v>14.71</v>
       </c>
       <c r="G43" t="n">
-        <v>1549957474</v>
+        <v>1454370480</v>
       </c>
       <c r="H43" t="n">
-        <v>188442212.51</v>
+        <v>111502943</v>
       </c>
       <c r="I43" t="n">
-        <v>145533159.23</v>
+        <v>163281722</v>
       </c>
       <c r="J43" t="n">
-        <v>333975371.74</v>
+        <v>274784665</v>
       </c>
       <c r="K43" t="n">
-        <v>-42909053.28</v>
+        <v>51778779</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.77</v>
+        <v>3.56</v>
       </c>
       <c r="M43" t="n">
-        <v>21.55</v>
+        <v>18.89</v>
       </c>
       <c r="N43" t="n">
-        <v>4637361300</v>
+        <v>10556100000</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600630.SH</t>
+          <t>601091.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.619999999999999</v>
+        <v>27.71</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0551</v>
+        <v>2.6296</v>
       </c>
       <c r="F44" t="n">
-        <v>27.58</v>
+        <v>53.59</v>
       </c>
       <c r="G44" t="n">
-        <v>987104083</v>
+        <v>2963675626</v>
       </c>
       <c r="H44" t="n">
-        <v>87900877.90000001</v>
+        <v>188116767.86</v>
       </c>
       <c r="I44" t="n">
-        <v>81557943.55</v>
+        <v>186220735.78</v>
       </c>
       <c r="J44" t="n">
-        <v>169458821.45</v>
+        <v>374337503.64</v>
       </c>
       <c r="K44" t="n">
-        <v>-6342934.35</v>
+        <v>-1896032.08</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.64</v>
+        <v>-0.06</v>
       </c>
       <c r="M44" t="n">
-        <v>17.17</v>
+        <v>12.63</v>
       </c>
       <c r="N44" t="n">
-        <v>3662306966.14</v>
+        <v>5851331773.22</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600721.SH</t>
+          <t>601218.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.92</v>
+        <v>6.05</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.784</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>39.69</v>
+        <v>27.33</v>
       </c>
       <c r="G45" t="n">
-        <v>2004408988</v>
+        <v>1514983777</v>
       </c>
       <c r="H45" t="n">
-        <v>270217911.7</v>
+        <v>214836029.44</v>
       </c>
       <c r="I45" t="n">
-        <v>228515994</v>
+        <v>145625813.17</v>
       </c>
       <c r="J45" t="n">
-        <v>498733905.7</v>
+        <v>360461842.61</v>
       </c>
       <c r="K45" t="n">
-        <v>-41701917.7</v>
+        <v>-69210216.27</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.08</v>
+        <v>-4.57</v>
       </c>
       <c r="M45" t="n">
-        <v>24.88</v>
+        <v>23.79</v>
       </c>
       <c r="N45" t="n">
-        <v>4968355444.2</v>
+        <v>5862652747.6</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600792.SH</t>
+          <t>601218.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>云煤能源</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="E46" t="n">
-        <v>10.0386</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>16.42</v>
+        <v>27.33</v>
       </c>
       <c r="G46" t="n">
-        <v>1020598468</v>
+        <v>2303488046</v>
       </c>
       <c r="H46" t="n">
-        <v>122035872</v>
+        <v>248929494.79</v>
       </c>
       <c r="I46" t="n">
-        <v>262107538</v>
+        <v>290586297.6</v>
       </c>
       <c r="J46" t="n">
-        <v>384143410</v>
+        <v>539515792.39</v>
       </c>
       <c r="K46" t="n">
-        <v>140071666</v>
+        <v>41656802.81</v>
       </c>
       <c r="L46" t="n">
-        <v>13.72</v>
+        <v>1.81</v>
       </c>
       <c r="M46" t="n">
-        <v>37.64</v>
+        <v>23.42</v>
       </c>
       <c r="N46" t="n">
-        <v>6326564520</v>
+        <v>5862652747.6</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600802.SH</t>
+          <t>601811.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.62</v>
+        <v>18.52</v>
       </c>
       <c r="E47" t="n">
-        <v>9.966799999999999</v>
+        <v>-8.992599999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>15.38</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>418892407</v>
+        <v>1317723424</v>
       </c>
       <c r="H47" t="n">
-        <v>87800717.02</v>
+        <v>115611875.08</v>
       </c>
       <c r="I47" t="n">
-        <v>64043884</v>
+        <v>90529955.64</v>
       </c>
       <c r="J47" t="n">
-        <v>151844601.02</v>
+        <v>206141830.72</v>
       </c>
       <c r="K47" t="n">
-        <v>-23756833.02</v>
+        <v>-25081919.44</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.67</v>
+        <v>-1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>36.25</v>
+        <v>15.64</v>
       </c>
       <c r="N47" t="n">
-        <v>3033604408</v>
+        <v>14666060228</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4350,271 +4349,271 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600802.SH</t>
+          <t>603052.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>可川科技</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6.62</v>
+        <v>52.61</v>
       </c>
       <c r="E48" t="n">
-        <v>9.966799999999999</v>
+        <v>-10.0068</v>
       </c>
       <c r="F48" t="n">
-        <v>15.38</v>
+        <v>2.42</v>
       </c>
       <c r="G48" t="n">
-        <v>632667894</v>
+        <v>245235215</v>
       </c>
       <c r="H48" t="n">
-        <v>96910731.72</v>
+        <v>37340174.73</v>
       </c>
       <c r="I48" t="n">
-        <v>131756798</v>
+        <v>26232300.43</v>
       </c>
       <c r="J48" t="n">
-        <v>228667529.72</v>
+        <v>63572475.16</v>
       </c>
       <c r="K48" t="n">
-        <v>34846066.28</v>
+        <v>-11107874.3</v>
       </c>
       <c r="L48" t="n">
-        <v>5.51</v>
+        <v>-4.53</v>
       </c>
       <c r="M48" t="n">
-        <v>36.14</v>
+        <v>25.92</v>
       </c>
       <c r="N48" t="n">
-        <v>3033604408</v>
+        <v>9885276006.02</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>600815.SH</t>
+          <t>603230.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>厦工股份</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.65</v>
+        <v>16.62</v>
       </c>
       <c r="E49" t="n">
-        <v>9.9291</v>
+        <v>-10.0162</v>
       </c>
       <c r="F49" t="n">
-        <v>16.7</v>
+        <v>4.29</v>
       </c>
       <c r="G49" t="n">
-        <v>2618564959</v>
+        <v>262244165</v>
       </c>
       <c r="H49" t="n">
-        <v>435187653.43</v>
+        <v>28203830</v>
       </c>
       <c r="I49" t="n">
-        <v>549495268.96</v>
+        <v>38722120.1</v>
       </c>
       <c r="J49" t="n">
-        <v>984682922.39</v>
+        <v>66925950.1</v>
       </c>
       <c r="K49" t="n">
-        <v>114307615.53</v>
+        <v>10518290.1</v>
       </c>
       <c r="L49" t="n">
-        <v>4.37</v>
+        <v>4.01</v>
       </c>
       <c r="M49" t="n">
-        <v>37.6</v>
+        <v>25.52</v>
       </c>
       <c r="N49" t="n">
-        <v>8249539332</v>
+        <v>5875552260</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>603248.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.77</v>
+        <v>23.2</v>
       </c>
       <c r="E50" t="n">
-        <v>10.0567</v>
+        <v>2.9281</v>
       </c>
       <c r="F50" t="n">
-        <v>0.57</v>
+        <v>38.12</v>
       </c>
       <c r="G50" t="n">
-        <v>46504942</v>
+        <v>603520495</v>
       </c>
       <c r="H50" t="n">
-        <v>8922524.1</v>
+        <v>38046682.86</v>
       </c>
       <c r="I50" t="n">
-        <v>35737338</v>
+        <v>53607818.05</v>
       </c>
       <c r="J50" t="n">
-        <v>44659862.1</v>
+        <v>91654500.91</v>
       </c>
       <c r="K50" t="n">
-        <v>26814813.9</v>
+        <v>15561135.19</v>
       </c>
       <c r="L50" t="n">
-        <v>57.66</v>
+        <v>2.58</v>
       </c>
       <c r="M50" t="n">
-        <v>96.03</v>
+        <v>15.19</v>
       </c>
       <c r="N50" t="n">
-        <v>8118778594.5</v>
+        <v>1658914863.2</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>600843.SH</t>
+          <t>603278.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.369999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="E51" t="n">
-        <v>9.9869</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>12.08</v>
+        <v>18.89</v>
       </c>
       <c r="G51" t="n">
-        <v>447214953</v>
+        <v>819989716</v>
       </c>
       <c r="H51" t="n">
-        <v>63484771.53</v>
+        <v>117815256.8</v>
       </c>
       <c r="I51" t="n">
-        <v>48232409.2</v>
+        <v>111407346.36</v>
       </c>
       <c r="J51" t="n">
-        <v>111717180.73</v>
+        <v>229222603.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-15252362.33</v>
+        <v>-6407910.44</v>
       </c>
       <c r="L51" t="n">
-        <v>-3.41</v>
+        <v>-0.78</v>
       </c>
       <c r="M51" t="n">
-        <v>24.98</v>
+        <v>27.95</v>
       </c>
       <c r="N51" t="n">
-        <v>4002528925.1</v>
+        <v>3684166245.76</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>600843.SH</t>
+          <t>603373.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>安邦护卫</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8.369999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="E52" t="n">
-        <v>9.9869</v>
+        <v>3.7402</v>
       </c>
       <c r="F52" t="n">
-        <v>12.08</v>
+        <v>10.07</v>
       </c>
       <c r="G52" t="n">
-        <v>640303569</v>
+        <v>779797701</v>
       </c>
       <c r="H52" t="n">
-        <v>84683185.04000001</v>
+        <v>125672129.36</v>
       </c>
       <c r="I52" t="n">
-        <v>73680804.98999999</v>
+        <v>147749660.59</v>
       </c>
       <c r="J52" t="n">
-        <v>158363990.03</v>
+        <v>273421789.95</v>
       </c>
       <c r="K52" t="n">
-        <v>-11002380.05</v>
+        <v>22077531.23</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.72</v>
+        <v>2.83</v>
       </c>
       <c r="M52" t="n">
-        <v>24.73</v>
+        <v>35.06</v>
       </c>
       <c r="N52" t="n">
-        <v>4002528925.1</v>
+        <v>3351833357.7</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4625,1250 +4624,551 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>601086.SH</t>
+          <t>603968.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.32</v>
+        <v>11.63</v>
       </c>
       <c r="E53" t="n">
-        <v>-9.988200000000001</v>
+        <v>10.0284</v>
       </c>
       <c r="F53" t="n">
-        <v>10.78</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>1165472055</v>
+        <v>113396778</v>
       </c>
       <c r="H53" t="n">
-        <v>199478801</v>
+        <v>22573273</v>
       </c>
       <c r="I53" t="n">
-        <v>114172561</v>
+        <v>46922376.12</v>
       </c>
       <c r="J53" t="n">
-        <v>313651362</v>
+        <v>69495649.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-85306240</v>
+        <v>24349103.12</v>
       </c>
       <c r="L53" t="n">
-        <v>-7.32</v>
+        <v>21.47</v>
       </c>
       <c r="M53" t="n">
-        <v>26.91</v>
+        <v>61.29</v>
       </c>
       <c r="N53" t="n">
-        <v>10203120000</v>
+        <v>2378102400</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>601091.SH</t>
+          <t>605366.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>27</v>
+        <v>10.14</v>
       </c>
       <c r="E54" t="n">
-        <v>-10</v>
+        <v>9.978300000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>26.15</v>
+        <v>13.53</v>
       </c>
       <c r="G54" t="n">
-        <v>1522465538</v>
+        <v>2075854245</v>
       </c>
       <c r="H54" t="n">
-        <v>105248780.04</v>
+        <v>309779469.26</v>
       </c>
       <c r="I54" t="n">
-        <v>84996536.91</v>
+        <v>243447329.96</v>
       </c>
       <c r="J54" t="n">
-        <v>190245316.95</v>
+        <v>553226799.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-20252243.13</v>
+        <v>-66332139.3</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.33</v>
+        <v>-3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>12.5</v>
+        <v>26.65</v>
       </c>
       <c r="N54" t="n">
-        <v>5701405914</v>
+        <v>7836472878</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>603042.SH</t>
+          <t>688244.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>华脉科技</t>
+          <t>永信至诚</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>18.73</v>
+        <v>19.8</v>
       </c>
       <c r="E55" t="n">
-        <v>9.9824</v>
+        <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>27.66</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>1042459177</v>
+        <v>270535500</v>
       </c>
       <c r="H55" t="n">
-        <v>102326645.67</v>
+        <v>13685218.69</v>
       </c>
       <c r="I55" t="n">
-        <v>244201895.73</v>
+        <v>56813902.22</v>
       </c>
       <c r="J55" t="n">
-        <v>346528541.4</v>
+        <v>70499120.91</v>
       </c>
       <c r="K55" t="n">
-        <v>141875250.06</v>
+        <v>43128683.53</v>
       </c>
       <c r="L55" t="n">
-        <v>13.61</v>
+        <v>15.94</v>
       </c>
       <c r="M55" t="n">
-        <v>33.24</v>
+        <v>26.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3910202014.16</v>
+        <v>2989038076.2</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>603248.SH</t>
+          <t>688628.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>优利德</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>22.54</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>4.886</v>
+        <v>-17.0439</v>
       </c>
       <c r="F56" t="n">
-        <v>36.87</v>
+        <v>14.27</v>
       </c>
       <c r="G56" t="n">
-        <v>589350218</v>
+        <v>1489321900</v>
       </c>
       <c r="H56" t="n">
-        <v>38732190.94</v>
+        <v>387062646.4</v>
       </c>
       <c r="I56" t="n">
-        <v>36817265.4</v>
+        <v>293647943.92</v>
       </c>
       <c r="J56" t="n">
-        <v>75549456.34</v>
+        <v>680710590.3200001</v>
       </c>
       <c r="K56" t="n">
-        <v>-1914925.54</v>
+        <v>-93414702.48</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.32</v>
+        <v>-6.27</v>
       </c>
       <c r="M56" t="n">
-        <v>12.82</v>
+        <v>45.71</v>
       </c>
       <c r="N56" t="n">
-        <v>1611721595.54</v>
+        <v>10339021767.12</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>603322.SH</t>
+          <t>920025.BJ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>超讯科技</t>
+          <t>凯达重工</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>29.12</v>
+        <v>15.2</v>
       </c>
       <c r="E57" t="n">
-        <v>-10.0124</v>
+        <v>-25.1232</v>
       </c>
       <c r="F57" t="n">
-        <v>7.69</v>
+        <v>47.4</v>
       </c>
       <c r="G57" t="n">
-        <v>364776213</v>
+        <v>397738500</v>
       </c>
       <c r="H57" t="n">
-        <v>116763924.44</v>
+        <v>45390596.23</v>
       </c>
       <c r="I57" t="n">
-        <v>57204061</v>
+        <v>21383950.75</v>
       </c>
       <c r="J57" t="n">
-        <v>173967985.44</v>
+        <v>66774546.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-59559863.44</v>
+        <v>-24006645.48</v>
       </c>
       <c r="L57" t="n">
-        <v>-16.33</v>
+        <v>-6.04</v>
       </c>
       <c r="M57" t="n">
-        <v>47.69</v>
+        <v>16.79</v>
       </c>
       <c r="N57" t="n">
-        <v>4588927499.52</v>
+        <v>775200000</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603396.SH</t>
+          <t>920025.BJ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>凯达重工</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>35.64</v>
+        <v>15.2</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>-25.1232</v>
       </c>
       <c r="F58" t="n">
-        <v>7.97</v>
+        <v>47.4</v>
       </c>
       <c r="G58" t="n">
-        <v>562001577</v>
+        <v>975460800</v>
       </c>
       <c r="H58" t="n">
-        <v>79259765.17</v>
+        <v>73178359.2</v>
       </c>
       <c r="I58" t="n">
-        <v>103890824.7</v>
+        <v>68031633.94</v>
       </c>
       <c r="J58" t="n">
-        <v>183150589.87</v>
+        <v>141209993.14</v>
       </c>
       <c r="K58" t="n">
-        <v>24631059.53</v>
+        <v>-5146725.26</v>
       </c>
       <c r="L58" t="n">
-        <v>4.38</v>
+        <v>-0.53</v>
       </c>
       <c r="M58" t="n">
-        <v>32.59</v>
+        <v>14.48</v>
       </c>
       <c r="N58" t="n">
-        <v>4937119315.92</v>
+        <v>775200000</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603500.SH</t>
+          <t>920071.BJ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>祥和实业</t>
+          <t>金钛股份</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.42</v>
+        <v>27</v>
       </c>
       <c r="E59" t="n">
-        <v>10.0317</v>
+        <v>-1.4599</v>
       </c>
       <c r="F59" t="n">
-        <v>4.19</v>
+        <v>27.54</v>
       </c>
       <c r="G59" t="n">
-        <v>143607982</v>
+        <v>234225800</v>
       </c>
       <c r="H59" t="n">
-        <v>18648366</v>
+        <v>36609338.29</v>
       </c>
       <c r="I59" t="n">
-        <v>74537872.8</v>
+        <v>25285642.46</v>
       </c>
       <c r="J59" t="n">
-        <v>93186238.8</v>
+        <v>61894980.75</v>
       </c>
       <c r="K59" t="n">
-        <v>55889506.8</v>
+        <v>-11323695.83</v>
       </c>
       <c r="L59" t="n">
-        <v>38.92</v>
+        <v>-4.83</v>
       </c>
       <c r="M59" t="n">
-        <v>64.89</v>
+        <v>26.43</v>
       </c>
       <c r="N59" t="n">
-        <v>3467601423.32</v>
+        <v>850500000</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603823.SH</t>
+          <t>920201.BJ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>百合花</t>
+          <t>百瑞吉</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>45.42</v>
+        <v>52.01</v>
       </c>
       <c r="E60" t="n">
-        <v>-10.0059</v>
+        <v>-28.1133</v>
       </c>
       <c r="F60" t="n">
-        <v>7.82</v>
+        <v>58.07</v>
       </c>
       <c r="G60" t="n">
-        <v>1505987772</v>
+        <v>248456500</v>
       </c>
       <c r="H60" t="n">
-        <v>382319822.98</v>
+        <v>24767530.76</v>
       </c>
       <c r="I60" t="n">
-        <v>174579983</v>
+        <v>47863309.05</v>
       </c>
       <c r="J60" t="n">
-        <v>556899805.98</v>
+        <v>72630839.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-207739839.98</v>
+        <v>23095778.29</v>
       </c>
       <c r="L60" t="n">
-        <v>-13.79</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>36.98</v>
+        <v>29.23</v>
       </c>
       <c r="N60" t="n">
-        <v>18911421115.68</v>
+        <v>395716368.67</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>603949.SH</t>
+          <t>920229.BJ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>世纪数码</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16.9</v>
+        <v>55.88</v>
       </c>
       <c r="E61" t="n">
-        <v>10.026</v>
+        <v>-13.6054</v>
       </c>
       <c r="F61" t="n">
-        <v>2.12</v>
+        <v>57.54</v>
       </c>
       <c r="G61" t="n">
-        <v>133888657</v>
+        <v>379189800</v>
       </c>
       <c r="H61" t="n">
-        <v>27114746.6</v>
+        <v>40095417.15</v>
       </c>
       <c r="I61" t="n">
-        <v>44985073.44</v>
+        <v>34135931.83</v>
       </c>
       <c r="J61" t="n">
-        <v>72099820.04000001</v>
+        <v>74231348.98</v>
       </c>
       <c r="K61" t="n">
-        <v>17870326.84</v>
+        <v>-5959485.32</v>
       </c>
       <c r="L61" t="n">
-        <v>13.35</v>
+        <v>-1.57</v>
       </c>
       <c r="M61" t="n">
-        <v>53.85</v>
+        <v>19.58</v>
       </c>
       <c r="N61" t="n">
-        <v>3552469130.6</v>
+        <v>634238000</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>603970.SH</t>
+          <t>920298.BJ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中农立华</t>
+          <t>腾信精密</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.17</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>10.0362</v>
+        <v>0.0228</v>
       </c>
       <c r="F62" t="n">
-        <v>2.84</v>
+        <v>34.83</v>
       </c>
       <c r="G62" t="n">
-        <v>90254673</v>
+        <v>479212400</v>
       </c>
       <c r="H62" t="n">
-        <v>12048663</v>
+        <v>89651649.84999999</v>
       </c>
       <c r="I62" t="n">
-        <v>24381160</v>
+        <v>55847212.29</v>
       </c>
       <c r="J62" t="n">
-        <v>36429823</v>
+        <v>145498862.14</v>
       </c>
       <c r="K62" t="n">
-        <v>12332497</v>
+        <v>-33804437.56</v>
       </c>
       <c r="L62" t="n">
-        <v>13.66</v>
+        <v>-7.05</v>
       </c>
       <c r="M62" t="n">
-        <v>40.36</v>
+        <v>30.36</v>
       </c>
       <c r="N62" t="n">
-        <v>3271297630.78</v>
+        <v>1344870000</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>605179.SH</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>一鸣食品</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>24.38</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-10.0037</v>
-      </c>
-      <c r="F63" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="G63" t="n">
-        <v>697878709</v>
-      </c>
-      <c r="H63" t="n">
-        <v>72295929.33</v>
-      </c>
-      <c r="I63" t="n">
-        <v>60145707</v>
-      </c>
-      <c r="J63" t="n">
-        <v>132441636.33</v>
-      </c>
-      <c r="K63" t="n">
-        <v>-12150222.33</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="M63" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="N63" t="n">
-        <v>9776380000</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>688056.SH</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>莱伯泰科</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>58.24</v>
-      </c>
-      <c r="E64" t="n">
-        <v>10.0529</v>
-      </c>
-      <c r="F64" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G64" t="n">
-        <v>465456700</v>
-      </c>
-      <c r="H64" t="n">
-        <v>59537891.73</v>
-      </c>
-      <c r="I64" t="n">
-        <v>39343958.71</v>
-      </c>
-      <c r="J64" t="n">
-        <v>98881850.44</v>
-      </c>
-      <c r="K64" t="n">
-        <v>-20193933.02</v>
-      </c>
-      <c r="L64" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="M64" t="n">
-        <v>21.24</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3928431270.4</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>688682.SH</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>霍莱沃</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>37.94</v>
-      </c>
-      <c r="E65" t="n">
-        <v>19.9873</v>
-      </c>
-      <c r="F65" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="G65" t="n">
-        <v>222120500</v>
-      </c>
-      <c r="H65" t="n">
-        <v>45357474.42</v>
-      </c>
-      <c r="I65" t="n">
-        <v>41051007.41</v>
-      </c>
-      <c r="J65" t="n">
-        <v>86408481.83</v>
-      </c>
-      <c r="K65" t="n">
-        <v>-4306467.01</v>
-      </c>
-      <c r="L65" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="M65" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3863767676.3</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>688837.SH</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>信诺维</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>47.31</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-11.7351</v>
-      </c>
-      <c r="F66" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1020530700</v>
-      </c>
-      <c r="H66" t="n">
-        <v>100270223.11</v>
-      </c>
-      <c r="I66" t="n">
-        <v>74795161.27</v>
-      </c>
-      <c r="J66" t="n">
-        <v>175065384.38</v>
-      </c>
-      <c r="K66" t="n">
-        <v>-25475061.84</v>
-      </c>
-      <c r="L66" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="M66" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2298981477.66</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>920025.BJ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>凯达重工</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F67" t="n">
-        <v>53.05</v>
-      </c>
-      <c r="G67" t="n">
-        <v>577722400</v>
-      </c>
-      <c r="H67" t="n">
-        <v>41067989.33</v>
-      </c>
-      <c r="I67" t="n">
-        <v>48219891.21</v>
-      </c>
-      <c r="J67" t="n">
-        <v>89287880.54000001</v>
-      </c>
-      <c r="K67" t="n">
-        <v>7151901.88</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M67" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1035300000</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>当日收盘价跌幅达到-20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>920071.BJ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>金钛股份</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-3.351</v>
-      </c>
-      <c r="F68" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="G68" t="n">
-        <v>346718000</v>
-      </c>
-      <c r="H68" t="n">
-        <v>60411052.61</v>
-      </c>
-      <c r="I68" t="n">
-        <v>23333681.12</v>
-      </c>
-      <c r="J68" t="n">
-        <v>83744733.73</v>
-      </c>
-      <c r="K68" t="n">
-        <v>-37077371.49</v>
-      </c>
-      <c r="L68" t="n">
-        <v>-10.69</v>
-      </c>
-      <c r="M68" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="N68" t="n">
-        <v>863100000</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
           <t>当日换手率达到20%的前5只股票</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>920229.BJ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>世纪数码</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F69" t="n">
-        <v>72.79000000000001</v>
-      </c>
-      <c r="G69" t="n">
-        <v>574268900</v>
-      </c>
-      <c r="H69" t="n">
-        <v>52157251.53</v>
-      </c>
-      <c r="I69" t="n">
-        <v>60742121.9</v>
-      </c>
-      <c r="J69" t="n">
-        <v>112899373.43</v>
-      </c>
-      <c r="K69" t="n">
-        <v>8584870.369999999</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M69" t="n">
-        <v>19.66</v>
-      </c>
-      <c r="N69" t="n">
-        <v>734118000</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>920229.BJ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>世纪数码</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F70" t="n">
-        <v>72.79000000000001</v>
-      </c>
-      <c r="G70" t="n">
-        <v>617131400</v>
-      </c>
-      <c r="H70" t="n">
-        <v>53935489.53</v>
-      </c>
-      <c r="I70" t="n">
-        <v>55268991.65</v>
-      </c>
-      <c r="J70" t="n">
-        <v>109204481.18</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1333502.12</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M70" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N70" t="n">
-        <v>734118000</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>920268.BJ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>百迈科</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>32.79</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-9.3949</v>
-      </c>
-      <c r="F71" t="n">
-        <v>40.61</v>
-      </c>
-      <c r="G71" t="n">
-        <v>198154500</v>
-      </c>
-      <c r="H71" t="n">
-        <v>19745914.39</v>
-      </c>
-      <c r="I71" t="n">
-        <v>22873201.62</v>
-      </c>
-      <c r="J71" t="n">
-        <v>42619116.01</v>
-      </c>
-      <c r="K71" t="n">
-        <v>3127287.23</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M71" t="n">
-        <v>21.51</v>
-      </c>
-      <c r="N71" t="n">
-        <v>473754379.44</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>920298.BJ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>腾信精密</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>87.88</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-1.5901</v>
-      </c>
-      <c r="F72" t="n">
-        <v>38.61</v>
-      </c>
-      <c r="G72" t="n">
-        <v>528511500</v>
-      </c>
-      <c r="H72" t="n">
-        <v>70701974.40000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>70295653.26000001</v>
-      </c>
-      <c r="J72" t="n">
-        <v>140997627.66</v>
-      </c>
-      <c r="K72" t="n">
-        <v>-406321.14</v>
-      </c>
-      <c r="L72" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="M72" t="n">
-        <v>26.68</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1344564000</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>920748.BJ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>路桥信息</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="E73" t="n">
-        <v>29.9858</v>
-      </c>
-      <c r="F73" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="G73" t="n">
-        <v>241390800</v>
-      </c>
-      <c r="H73" t="n">
-        <v>47266032.9</v>
-      </c>
-      <c r="I73" t="n">
-        <v>62203338.34</v>
-      </c>
-      <c r="J73" t="n">
-        <v>109469371.24</v>
-      </c>
-      <c r="K73" t="n">
-        <v>14937305.44</v>
-      </c>
-      <c r="L73" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="M73" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2568508650</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>trade_date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>exchange_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rzye</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rzmre</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rzche</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>rqye</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>rqmcl</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>rzrqye</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>rqyl</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>20260924</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SSE</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1331841736225</v>
-      </c>
-      <c r="D2" t="n">
-        <v>77396224473</v>
-      </c>
-      <c r="E2" t="n">
-        <v>86320164892</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18664487521</v>
-      </c>
-      <c r="G2" t="n">
-        <v>84996899</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1350506223746</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3159503720</v>
       </c>
     </row>
   </sheetData>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>5559</v>
       </c>
       <c r="C2" t="n">
-        <v>898</v>
+        <v>3471</v>
       </c>
       <c r="D2" t="n">
-        <v>4554</v>
+        <v>1933</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>17167.12</v>
+        <v>14215.96</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3823.6206</v>
+        <v>3830.4513</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.67</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>8045.44</v>
+        <v>6617.04</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12858.7532</v>
+        <v>12901.9474</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.44</v>
+        <v>0.34</v>
       </c>
       <c r="F3" t="n">
-        <v>4427.27</v>
+        <v>3497.17</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3139.8249</v>
+        <v>3142.563</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.53</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>1732.64</v>
+        <v>1340.29</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4340.755</v>
+        <v>4345.2088</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.22</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>4286.2</v>
+        <v>3349.51</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1555.9804</v>
+        <v>1569.3384</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.06</v>
+        <v>0.86</v>
       </c>
       <c r="F6" t="n">
-        <v>805.86</v>
+        <v>645.3</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7294.1735</v>
+        <v>7325.3515</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.65</v>
+        <v>0.43</v>
       </c>
       <c r="F7" t="n">
-        <v>3466.01</v>
+        <v>2689.51</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16429.8</v>
+        <v>16252.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16252.51</v>
+        <v>18524.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18524.99</v>
+        <v>18365.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18365.14</v>
+        <v>20929.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20929.06</v>
+        <v>20481.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20481.34</v>
+        <v>21536.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21536.52</v>
+        <v>17831.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17831.28</v>
+        <v>16691.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17167.12</v>
+        <v>14215.96</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301190.SZ</t>
+          <t>301716.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.96</v>
+        <v>600</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95</v>
+        <v>630.01</v>
       </c>
       <c r="E2" t="n">
-        <v>20.95</v>
+        <v>558.58</v>
       </c>
       <c r="F2" t="n">
-        <v>24.95</v>
+        <v>578.88</v>
       </c>
       <c r="G2" t="n">
-        <v>20.79</v>
+        <v>76.86</v>
       </c>
       <c r="H2" t="n">
-        <v>4.16</v>
+        <v>502.02</v>
       </c>
       <c r="I2" t="n">
-        <v>20.0096</v>
+        <v>653.1616</v>
       </c>
       <c r="J2" t="n">
-        <v>166219.79</v>
+        <v>105283.3</v>
       </c>
       <c r="K2" t="n">
-        <v>382851.17588</v>
+        <v>6231355.53694</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>688244.SH</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.06</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>19.8</v>
+        <v>34.9</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8</v>
+        <v>26.16</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5</v>
+        <v>7.55</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>18.61</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>246.4901</v>
       </c>
       <c r="J3" t="n">
-        <v>147652.72</v>
+        <v>230148.95</v>
       </c>
       <c r="K3" t="n">
-        <v>270535.534</v>
+        <v>644052.4962000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301004.SZ</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.48</v>
+        <v>23.04</v>
       </c>
       <c r="D4" t="n">
-        <v>39.24</v>
+        <v>28.4</v>
       </c>
       <c r="E4" t="n">
-        <v>34.48</v>
+        <v>22.31</v>
       </c>
       <c r="F4" t="n">
-        <v>38.28</v>
+        <v>28.4</v>
       </c>
       <c r="G4" t="n">
-        <v>32.7</v>
+        <v>21.85</v>
       </c>
       <c r="H4" t="n">
-        <v>5.58</v>
+        <v>6.55</v>
       </c>
       <c r="I4" t="n">
-        <v>17.0642</v>
+        <v>29.9771</v>
       </c>
       <c r="J4" t="n">
-        <v>47611.54</v>
+        <v>60443.44</v>
       </c>
       <c r="K4" t="n">
-        <v>177021.16249</v>
+        <v>162736.6659</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>301560.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>28.91</v>
       </c>
       <c r="D5" t="n">
-        <v>42.36</v>
+        <v>33.88</v>
       </c>
       <c r="E5" t="n">
-        <v>34.03</v>
+        <v>28.13</v>
       </c>
       <c r="F5" t="n">
-        <v>40.68</v>
+        <v>33.88</v>
       </c>
       <c r="G5" t="n">
-        <v>35.54</v>
+        <v>28.23</v>
       </c>
       <c r="H5" t="n">
-        <v>5.14</v>
+        <v>5.65</v>
       </c>
       <c r="I5" t="n">
-        <v>14.4626</v>
+        <v>20.0142</v>
       </c>
       <c r="J5" t="n">
-        <v>458529.47</v>
+        <v>142918.97</v>
       </c>
       <c r="K5" t="n">
-        <v>1710375.61493</v>
+        <v>456100.82475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.SZ</t>
+          <t>688685.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.93</v>
+        <v>33.74</v>
       </c>
       <c r="D6" t="n">
-        <v>9.199999999999999</v>
+        <v>39.7</v>
       </c>
       <c r="E6" t="n">
-        <v>7.93</v>
+        <v>33.2</v>
       </c>
       <c r="F6" t="n">
-        <v>8.67</v>
+        <v>39.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7.68</v>
+        <v>33.08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.99</v>
+        <v>6.62</v>
       </c>
       <c r="I6" t="n">
-        <v>12.8906</v>
+        <v>20.0121</v>
       </c>
       <c r="J6" t="n">
-        <v>942429.9</v>
+        <v>88715.97</v>
       </c>
       <c r="K6" t="n">
-        <v>821597.36014</v>
+        <v>332588.937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688152.SH</t>
+          <t>688655.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36.74</v>
+        <v>61.9</v>
       </c>
       <c r="D7" t="n">
-        <v>41.19</v>
+        <v>75.7</v>
       </c>
       <c r="E7" t="n">
-        <v>35.21</v>
+        <v>61.68</v>
       </c>
       <c r="F7" t="n">
-        <v>39.45</v>
+        <v>75.7</v>
       </c>
       <c r="G7" t="n">
-        <v>35.23</v>
+        <v>63.08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.22</v>
+        <v>12.62</v>
       </c>
       <c r="I7" t="n">
-        <v>11.9784</v>
+        <v>20.0063</v>
       </c>
       <c r="J7" t="n">
-        <v>93926.53999999999</v>
+        <v>135937.5</v>
       </c>
       <c r="K7" t="n">
-        <v>358029.445</v>
+        <v>953119.828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>920926.BJ</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.2</v>
+        <v>42.99</v>
       </c>
       <c r="D8" t="n">
-        <v>11.5</v>
+        <v>51.42</v>
       </c>
       <c r="E8" t="n">
-        <v>10.03</v>
+        <v>42.99</v>
       </c>
       <c r="F8" t="n">
-        <v>10.9</v>
+        <v>51.42</v>
       </c>
       <c r="G8" t="n">
-        <v>9.83</v>
+        <v>42.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>8.57</v>
       </c>
       <c r="I8" t="n">
-        <v>10.885</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>56761.97</v>
+        <v>29401.05</v>
       </c>
       <c r="K8" t="n">
-        <v>62371.98091</v>
+        <v>143519.6661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300501.SZ</t>
+          <t>301190.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.58</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>10.46</v>
+        <v>29.94</v>
       </c>
       <c r="E9" t="n">
-        <v>9.48</v>
+        <v>24.5</v>
       </c>
       <c r="F9" t="n">
-        <v>10.45</v>
+        <v>29.94</v>
       </c>
       <c r="G9" t="n">
-        <v>9.449999999999999</v>
+        <v>24.95</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4.99</v>
       </c>
       <c r="I9" t="n">
-        <v>10.582</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>151231.17</v>
+        <v>209316.98</v>
       </c>
       <c r="K9" t="n">
-        <v>151694.31693</v>
+        <v>592781.77767</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>600340.SH</t>
+          <t>301282.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.18</v>
+        <v>39.69</v>
       </c>
       <c r="D10" t="n">
-        <v>1.29</v>
+        <v>46.04</v>
       </c>
       <c r="E10" t="n">
-        <v>1.18</v>
+        <v>39.47</v>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>45.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.17</v>
+        <v>40.03</v>
       </c>
       <c r="H10" t="n">
-        <v>0.12</v>
+        <v>5.46</v>
       </c>
       <c r="I10" t="n">
-        <v>10.2564</v>
+        <v>13.6398</v>
       </c>
       <c r="J10" t="n">
-        <v>1851706</v>
+        <v>202003.54</v>
       </c>
       <c r="K10" t="n">
-        <v>231359.037</v>
+        <v>891279.37502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>600032.SH</t>
+          <t>300917.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.81</v>
+        <v>33.3</v>
       </c>
       <c r="D11" t="n">
-        <v>7.43</v>
+        <v>36.62</v>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>32.1</v>
       </c>
       <c r="F11" t="n">
-        <v>7.43</v>
+        <v>36.18</v>
       </c>
       <c r="G11" t="n">
-        <v>6.75</v>
+        <v>31.88</v>
       </c>
       <c r="H11" t="n">
-        <v>0.68</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>10.0741</v>
+        <v>13.4881</v>
       </c>
       <c r="J11" t="n">
-        <v>608576.91</v>
+        <v>302513.03</v>
       </c>
       <c r="K11" t="n">
-        <v>441559.885</v>
+        <v>1045757.62726</v>
       </c>
     </row>
   </sheetData>
@@ -1338,40 +1338,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920201.BJ</t>
+          <t>301686.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.1</v>
+        <v>225</v>
       </c>
       <c r="D2" t="n">
-        <v>65.98999999999999</v>
+        <v>230</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>191.66</v>
       </c>
       <c r="F2" t="n">
-        <v>52.01</v>
+        <v>192.06</v>
       </c>
       <c r="G2" t="n">
-        <v>72.34999999999999</v>
+        <v>231.67</v>
       </c>
       <c r="H2" t="n">
-        <v>-20.34</v>
+        <v>-39.61</v>
       </c>
       <c r="I2" t="n">
-        <v>-28.1133</v>
+        <v>-17.0976</v>
       </c>
       <c r="J2" t="n">
-        <v>44180.3</v>
+        <v>46331.91</v>
       </c>
       <c r="K2" t="n">
-        <v>248456.5001</v>
+        <v>964909.7877700001</v>
       </c>
     </row>
     <row r="3">
@@ -1382,347 +1382,347 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.23</v>
+        <v>14.23</v>
       </c>
       <c r="D3" t="n">
-        <v>18.49</v>
+        <v>15.1</v>
       </c>
       <c r="E3" t="n">
-        <v>15.15</v>
+        <v>13.2</v>
       </c>
       <c r="F3" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="G3" t="n">
         <v>15.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>20.3</v>
-      </c>
       <c r="H3" t="n">
-        <v>-5.1</v>
+        <v>-1.96</v>
       </c>
       <c r="I3" t="n">
-        <v>-25.1232</v>
+        <v>-12.8947</v>
       </c>
       <c r="J3" t="n">
-        <v>241745.87</v>
+        <v>190622.32</v>
       </c>
       <c r="K3" t="n">
-        <v>397738.46041</v>
+        <v>266604.81999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300585.SZ</t>
+          <t>920229.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.28</v>
+        <v>54.8</v>
       </c>
       <c r="D4" t="n">
-        <v>15.83</v>
+        <v>56.56</v>
       </c>
       <c r="E4" t="n">
-        <v>13.83</v>
+        <v>49.07</v>
       </c>
       <c r="F4" t="n">
-        <v>13.83</v>
+        <v>49.14</v>
       </c>
       <c r="G4" t="n">
-        <v>16.86</v>
+        <v>55.88</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.03</v>
+        <v>-6.74</v>
       </c>
       <c r="I4" t="n">
-        <v>-17.9715</v>
+        <v>-12.0616</v>
       </c>
       <c r="J4" t="n">
-        <v>178414.62</v>
+        <v>53113.74</v>
       </c>
       <c r="K4" t="n">
-        <v>255443.90276</v>
+        <v>275449.7407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300829.SZ</t>
+          <t>920201.BJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.29</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>27.5</v>
+        <v>54.5</v>
       </c>
       <c r="E5" t="n">
-        <v>22.49</v>
+        <v>45.26</v>
       </c>
       <c r="F5" t="n">
-        <v>22.7</v>
+        <v>46.03</v>
       </c>
       <c r="G5" t="n">
-        <v>27.56</v>
+        <v>52.01</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.86</v>
+        <v>-5.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-17.6343</v>
+        <v>-11.4978</v>
       </c>
       <c r="J5" t="n">
-        <v>433803.13</v>
+        <v>33958.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1029834.22437</v>
+        <v>169549.47456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688628.SH</t>
+          <t>002717.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>106.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>108</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>88.70999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>91.98999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>110.89</v>
+        <v>0.77</v>
       </c>
       <c r="H6" t="n">
-        <v>-18.9</v>
+        <v>-0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.0439</v>
+        <v>-10.3896</v>
       </c>
       <c r="J6" t="n">
-        <v>160399.58</v>
+        <v>179572</v>
       </c>
       <c r="K6" t="n">
-        <v>1489321.885</v>
+        <v>12390.468</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300291.SZ</t>
+          <t>600815.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.9</v>
+        <v>3.88</v>
       </c>
       <c r="D7" t="n">
-        <v>5.15</v>
+        <v>3.98</v>
       </c>
       <c r="E7" t="n">
-        <v>4.73</v>
+        <v>3.77</v>
       </c>
       <c r="F7" t="n">
-        <v>4.83</v>
+        <v>3.77</v>
       </c>
       <c r="G7" t="n">
-        <v>5.78</v>
+        <v>4.19</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.95</v>
+        <v>-0.42</v>
       </c>
       <c r="I7" t="n">
-        <v>-16.436</v>
+        <v>-10.0239</v>
       </c>
       <c r="J7" t="n">
-        <v>1295297.08</v>
+        <v>1830255.34</v>
       </c>
       <c r="K7" t="n">
-        <v>633638.02042</v>
+        <v>698680.903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300862.SZ</t>
+          <t>600371.SH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.71</v>
+        <v>13.19</v>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>13.42</v>
       </c>
       <c r="E8" t="n">
-        <v>45.99</v>
+        <v>12.84</v>
       </c>
       <c r="F8" t="n">
-        <v>47.48</v>
+        <v>12.84</v>
       </c>
       <c r="G8" t="n">
-        <v>56.23</v>
+        <v>14.27</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.75</v>
+        <v>-1.43</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.5611</v>
+        <v>-10.021</v>
       </c>
       <c r="J8" t="n">
-        <v>344533.34</v>
+        <v>340429.49</v>
       </c>
       <c r="K8" t="n">
-        <v>1725556.93964</v>
+        <v>439783.617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688312.SH</t>
+          <t>001234.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57.45</v>
+        <v>30.85</v>
       </c>
       <c r="D9" t="n">
-        <v>57.9</v>
+        <v>32.53</v>
       </c>
       <c r="E9" t="n">
-        <v>48.97</v>
+        <v>28.67</v>
       </c>
       <c r="F9" t="n">
-        <v>49.17</v>
+        <v>28.67</v>
       </c>
       <c r="G9" t="n">
-        <v>57.79</v>
+        <v>31.86</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.619999999999999</v>
+        <v>-3.19</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.9161</v>
+        <v>-10.0126</v>
       </c>
       <c r="J9" t="n">
-        <v>126431.02</v>
+        <v>200605.32</v>
       </c>
       <c r="K9" t="n">
-        <v>659256.35</v>
+        <v>586646.11202</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688655.SH</t>
+          <t>603396.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72.69</v>
+        <v>38.51</v>
       </c>
       <c r="D10" t="n">
-        <v>73.48999999999999</v>
+        <v>39.25</v>
       </c>
       <c r="E10" t="n">
-        <v>62.2</v>
+        <v>35.28</v>
       </c>
       <c r="F10" t="n">
-        <v>63.08</v>
+        <v>35.28</v>
       </c>
       <c r="G10" t="n">
-        <v>73.8</v>
+        <v>39.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.72</v>
+        <v>-3.92</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.5257</v>
+        <v>-10</v>
       </c>
       <c r="J10" t="n">
-        <v>143154.82</v>
+        <v>147934.97</v>
       </c>
       <c r="K10" t="n">
-        <v>938840.072</v>
+        <v>531242.447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688143.SH</t>
+          <t>001368.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>39.72</v>
       </c>
       <c r="D11" t="n">
-        <v>187.87</v>
+        <v>39.72</v>
       </c>
       <c r="E11" t="n">
-        <v>157.2</v>
+        <v>37.62</v>
       </c>
       <c r="F11" t="n">
-        <v>165.05</v>
+        <v>37.62</v>
       </c>
       <c r="G11" t="n">
-        <v>191.35</v>
+        <v>41.8</v>
       </c>
       <c r="H11" t="n">
-        <v>-26.3</v>
+        <v>-4.18</v>
       </c>
       <c r="I11" t="n">
-        <v>-13.7444</v>
+        <v>-10</v>
       </c>
       <c r="J11" t="n">
-        <v>133099.69</v>
+        <v>17615</v>
       </c>
       <c r="K11" t="n">
-        <v>2264936.649</v>
+        <v>66977.308</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,51 +1819,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000513.SZ</t>
+          <t>000002.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t>万科A</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.34</v>
+        <v>4.08</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0073</v>
+        <v>9.973000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.92</v>
+        <v>8.26</v>
       </c>
       <c r="G2" t="n">
-        <v>842849421</v>
+        <v>3176619108</v>
       </c>
       <c r="H2" t="n">
-        <v>96629694.16</v>
+        <v>307002423.65</v>
       </c>
       <c r="I2" t="n">
-        <v>217253468.66</v>
+        <v>466610675.4</v>
       </c>
       <c r="J2" t="n">
-        <v>313883162.82</v>
+        <v>773613099.05</v>
       </c>
       <c r="K2" t="n">
-        <v>120623774.5</v>
+        <v>159608251.75</v>
       </c>
       <c r="L2" t="n">
-        <v>14.31</v>
+        <v>5.02</v>
       </c>
       <c r="M2" t="n">
-        <v>37.24</v>
+        <v>24.35</v>
       </c>
       <c r="N2" t="n">
-        <v>17222555247.92</v>
+        <v>39637661668.32</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1874,392 +1874,392 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000560.SZ</t>
+          <t>000011.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.71</v>
+        <v>11.13</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3661</v>
+        <v>9.9802</v>
       </c>
       <c r="F3" t="n">
-        <v>27.11</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>2310346998</v>
+        <v>653227762</v>
       </c>
       <c r="H3" t="n">
-        <v>506730786.81</v>
+        <v>244392241.66</v>
       </c>
       <c r="I3" t="n">
-        <v>316336137.1</v>
+        <v>141177943</v>
       </c>
       <c r="J3" t="n">
-        <v>823066923.91</v>
+        <v>385570184.66</v>
       </c>
       <c r="K3" t="n">
-        <v>-190394649.71</v>
+        <v>-103214298.66</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.24</v>
+        <v>-15.8</v>
       </c>
       <c r="M3" t="n">
-        <v>35.63</v>
+        <v>59.03</v>
       </c>
       <c r="N3" t="n">
-        <v>8691372921.49</v>
+        <v>6063164575.02</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000592.SZ</t>
+          <t>000513.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.09</v>
+        <v>32.23</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5308</v>
+        <v>6.2294</v>
       </c>
       <c r="F4" t="n">
-        <v>29.09</v>
+        <v>11.17</v>
       </c>
       <c r="G4" t="n">
-        <v>5083871839</v>
+        <v>3090837434</v>
       </c>
       <c r="H4" t="n">
-        <v>627707868.76</v>
+        <v>359978916.1</v>
       </c>
       <c r="I4" t="n">
-        <v>514508097.45</v>
+        <v>567789030.99</v>
       </c>
       <c r="J4" t="n">
-        <v>1142215966.21</v>
+        <v>927767947.09</v>
       </c>
       <c r="K4" t="n">
-        <v>-113199771.31</v>
+        <v>207810114.89</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.23</v>
+        <v>6.72</v>
       </c>
       <c r="M4" t="n">
-        <v>22.47</v>
+        <v>30.02</v>
       </c>
       <c r="N4" t="n">
-        <v>17408190361.41</v>
+        <v>18295417127.24</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000678.SZ</t>
+          <t>000560.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.65</v>
+        <v>3.76</v>
       </c>
       <c r="E5" t="n">
-        <v>10.0207</v>
+        <v>1.3477</v>
       </c>
       <c r="F5" t="n">
-        <v>7.61</v>
+        <v>34.39</v>
       </c>
       <c r="G5" t="n">
-        <v>626070754</v>
+        <v>3044448538</v>
       </c>
       <c r="H5" t="n">
-        <v>64242780.61</v>
+        <v>343169522.62</v>
       </c>
       <c r="I5" t="n">
-        <v>121996682.61</v>
+        <v>341661393.14</v>
       </c>
       <c r="J5" t="n">
-        <v>186239463.22</v>
+        <v>684830915.76</v>
       </c>
       <c r="K5" t="n">
-        <v>57753902</v>
+        <v>-1508129.48</v>
       </c>
       <c r="L5" t="n">
-        <v>9.220000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>29.75</v>
+        <v>22.49</v>
       </c>
       <c r="N5" t="n">
-        <v>4894865638.05</v>
+        <v>8808507327.440001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000790.SZ</t>
+          <t>000823.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华神科技</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.42</v>
+        <v>24.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.5556</v>
+        <v>10.009</v>
       </c>
       <c r="F6" t="n">
-        <v>20.36</v>
+        <v>19.56</v>
       </c>
       <c r="G6" t="n">
-        <v>598560827</v>
+        <v>2748775889</v>
       </c>
       <c r="H6" t="n">
-        <v>90289170.51000001</v>
+        <v>361250451.77</v>
       </c>
       <c r="I6" t="n">
-        <v>64683870.6</v>
+        <v>403478872.95</v>
       </c>
       <c r="J6" t="n">
-        <v>154973041.11</v>
+        <v>764729324.72</v>
       </c>
       <c r="K6" t="n">
-        <v>-25605299.91</v>
+        <v>42228421.18</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.28</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>25.89</v>
+        <v>27.82</v>
       </c>
       <c r="N6" t="n">
-        <v>2752080906.38</v>
+        <v>14516344874.8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000823.SZ</t>
+          <t>000850.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>华茂股份</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.18</v>
+        <v>4.63</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.3954</v>
+        <v>-9.9222</v>
       </c>
       <c r="F7" t="n">
-        <v>26.92</v>
+        <v>1.46</v>
       </c>
       <c r="G7" t="n">
-        <v>3659096152</v>
+        <v>63900482</v>
       </c>
       <c r="H7" t="n">
-        <v>442757445.25</v>
+        <v>18436197</v>
       </c>
       <c r="I7" t="n">
-        <v>822386287.03</v>
+        <v>21927680</v>
       </c>
       <c r="J7" t="n">
-        <v>1265143732.28</v>
+        <v>40363877</v>
       </c>
       <c r="K7" t="n">
-        <v>379628841.78</v>
+        <v>3491483</v>
       </c>
       <c r="L7" t="n">
-        <v>10.37</v>
+        <v>5.46</v>
       </c>
       <c r="M7" t="n">
-        <v>34.58</v>
+        <v>63.17</v>
       </c>
       <c r="N7" t="n">
-        <v>13195595464.06</v>
+        <v>4367823374.77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000980.SZ</t>
+          <t>001216.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.24</v>
+        <v>29.09</v>
       </c>
       <c r="E8" t="n">
-        <v>9.803900000000001</v>
+        <v>3.7447</v>
       </c>
       <c r="F8" t="n">
-        <v>9.59</v>
+        <v>16.98</v>
       </c>
       <c r="G8" t="n">
-        <v>1051055425</v>
+        <v>1147473301</v>
       </c>
       <c r="H8" t="n">
-        <v>82517069.01000001</v>
+        <v>80445110.06</v>
       </c>
       <c r="I8" t="n">
-        <v>259234178.31</v>
+        <v>84060211</v>
       </c>
       <c r="J8" t="n">
-        <v>341751247.32</v>
+        <v>164505321.06</v>
       </c>
       <c r="K8" t="n">
-        <v>176717109.3</v>
+        <v>3615100.94</v>
       </c>
       <c r="L8" t="n">
-        <v>16.81</v>
+        <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>32.52</v>
+        <v>14.34</v>
       </c>
       <c r="N8" t="n">
-        <v>11295168279.36</v>
+        <v>7180465028.91</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>001330.SZ</t>
+          <t>001234.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>泰慕士</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.36</v>
+        <v>28.67</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0346</v>
+        <v>-10.0126</v>
       </c>
       <c r="F9" t="n">
-        <v>3.53</v>
+        <v>21.91</v>
       </c>
       <c r="G9" t="n">
-        <v>2220445536</v>
+        <v>586646112</v>
       </c>
       <c r="H9" t="n">
-        <v>253794813.5</v>
+        <v>112309105.68</v>
       </c>
       <c r="I9" t="n">
-        <v>377871272.1</v>
+        <v>58067030.62</v>
       </c>
       <c r="J9" t="n">
-        <v>631666085.6</v>
+        <v>170376136.3</v>
       </c>
       <c r="K9" t="n">
-        <v>124076458.6</v>
+        <v>-54242075.06</v>
       </c>
       <c r="L9" t="n">
-        <v>5.59</v>
+        <v>-9.25</v>
       </c>
       <c r="M9" t="n">
-        <v>28.45</v>
+        <v>29.04</v>
       </c>
       <c r="N9" t="n">
-        <v>7395708967.92</v>
+        <v>2624494805</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2273,147 +2273,147 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41.8</v>
+        <v>37.62</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F10" t="n">
-        <v>10.63</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>459326893</v>
+        <v>66977308</v>
       </c>
       <c r="H10" t="n">
-        <v>98643041.15000001</v>
+        <v>7601070</v>
       </c>
       <c r="I10" t="n">
-        <v>67035311</v>
+        <v>17526866</v>
       </c>
       <c r="J10" t="n">
-        <v>165678352.15</v>
+        <v>25127936</v>
       </c>
       <c r="K10" t="n">
-        <v>-31607730.15</v>
+        <v>9925796</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.88</v>
+        <v>14.82</v>
       </c>
       <c r="M10" t="n">
-        <v>36.07</v>
+        <v>37.52</v>
       </c>
       <c r="N10" t="n">
-        <v>4517769038.2</v>
+        <v>4065992134.38</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>001368.SZ</t>
+          <t>002074.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>通达创智</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41.8</v>
+        <v>28.68</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>10.0115</v>
       </c>
       <c r="F11" t="n">
-        <v>10.63</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>1153499086</v>
+        <v>1301852767</v>
       </c>
       <c r="H11" t="n">
-        <v>172407770.65</v>
+        <v>105628225.58</v>
       </c>
       <c r="I11" t="n">
-        <v>177857708.16</v>
+        <v>474013721.82</v>
       </c>
       <c r="J11" t="n">
-        <v>350265478.81</v>
+        <v>579641947.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5449937.51</v>
+        <v>368385496.24</v>
       </c>
       <c r="L11" t="n">
-        <v>0.47</v>
+        <v>28.3</v>
       </c>
       <c r="M11" t="n">
-        <v>30.37</v>
+        <v>44.52</v>
       </c>
       <c r="N11" t="n">
-        <v>4517769038.2</v>
+        <v>49807342549.2</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002119.SZ</t>
+          <t>002172.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.71</v>
+        <v>5.49</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3377</v>
+        <v>8.284000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>33.71</v>
+        <v>29.02</v>
       </c>
       <c r="G12" t="n">
-        <v>3646959347</v>
+        <v>1214702660</v>
       </c>
       <c r="H12" t="n">
-        <v>649073540.79</v>
+        <v>73432929.45999999</v>
       </c>
       <c r="I12" t="n">
-        <v>533283310.19</v>
+        <v>275686585.18</v>
       </c>
       <c r="J12" t="n">
-        <v>1182356850.98</v>
+        <v>349119514.64</v>
       </c>
       <c r="K12" t="n">
-        <v>-115790230.6</v>
+        <v>202253655.72</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.17</v>
+        <v>16.65</v>
       </c>
       <c r="M12" t="n">
-        <v>32.42</v>
+        <v>28.74</v>
       </c>
       <c r="N12" t="n">
-        <v>11149687640</v>
+        <v>4200622607.7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -2424,106 +2424,106 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002342.SZ</t>
+          <t>002205.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>国统股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.68</v>
+        <v>12.76</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0127</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>25.01</v>
+        <v>13.77</v>
       </c>
       <c r="G13" t="n">
-        <v>2008963896</v>
+        <v>316349680</v>
       </c>
       <c r="H13" t="n">
-        <v>368349656.77</v>
+        <v>20760494</v>
       </c>
       <c r="I13" t="n">
-        <v>444698663.54</v>
+        <v>71671307.59999999</v>
       </c>
       <c r="J13" t="n">
-        <v>813048320.3099999</v>
+        <v>92431801.59999999</v>
       </c>
       <c r="K13" t="n">
-        <v>76349006.77</v>
+        <v>50910813.6</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>16.09</v>
       </c>
       <c r="M13" t="n">
-        <v>40.47</v>
+        <v>29.22</v>
       </c>
       <c r="N13" t="n">
-        <v>8286709200</v>
+        <v>2371359589.28</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002342.SZ</t>
+          <t>002242.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.68</v>
+        <v>11.36</v>
       </c>
       <c r="E14" t="n">
-        <v>10.0127</v>
+        <v>9.971</v>
       </c>
       <c r="F14" t="n">
-        <v>25.01</v>
+        <v>2.51</v>
       </c>
       <c r="G14" t="n">
-        <v>3113342036</v>
+        <v>466312282</v>
       </c>
       <c r="H14" t="n">
-        <v>571712704.8099999</v>
+        <v>31928390</v>
       </c>
       <c r="I14" t="n">
-        <v>608264993.8099999</v>
+        <v>70910978.16</v>
       </c>
       <c r="J14" t="n">
-        <v>1179977698.62</v>
+        <v>102839368.16</v>
       </c>
       <c r="K14" t="n">
-        <v>36552289</v>
+        <v>38982588.16</v>
       </c>
       <c r="L14" t="n">
-        <v>1.17</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>37.9</v>
+        <v>22.05</v>
       </c>
       <c r="N14" t="n">
-        <v>8286709200</v>
+        <v>8653657500</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2534,216 +2534,216 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002614.SZ</t>
+          <t>002303.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>美盈森</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0408</v>
+        <v>10.0164</v>
       </c>
       <c r="F15" t="n">
-        <v>42.87</v>
+        <v>13.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1574292219</v>
+        <v>953673791</v>
       </c>
       <c r="H15" t="n">
-        <v>244914429.13</v>
+        <v>211212533.52</v>
       </c>
       <c r="I15" t="n">
-        <v>191397095.61</v>
+        <v>196112975.66</v>
       </c>
       <c r="J15" t="n">
-        <v>436311524.74</v>
+        <v>407325509.18</v>
       </c>
       <c r="K15" t="n">
-        <v>-53517333.52</v>
+        <v>-15099557.86</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.4</v>
+        <v>-1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>27.71</v>
+        <v>42.71</v>
       </c>
       <c r="N15" t="n">
-        <v>3750840143.5</v>
+        <v>7151335617.5</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002640.SZ</t>
+          <t>002614.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.96</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>-4.3529</v>
       </c>
       <c r="F16" t="n">
-        <v>17.28</v>
+        <v>31.36</v>
       </c>
       <c r="G16" t="n">
-        <v>1049611659</v>
+        <v>1116697151</v>
       </c>
       <c r="H16" t="n">
-        <v>87363464</v>
+        <v>167766311.55</v>
       </c>
       <c r="I16" t="n">
-        <v>311423736.52</v>
+        <v>213012107.12</v>
       </c>
       <c r="J16" t="n">
-        <v>398787200.52</v>
+        <v>380778418.67</v>
       </c>
       <c r="K16" t="n">
-        <v>224060272.52</v>
+        <v>45245795.57</v>
       </c>
       <c r="L16" t="n">
-        <v>21.35</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>37.99</v>
+        <v>34.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6131116648.8</v>
+        <v>3587568278.43</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002679.SZ</t>
+          <t>002640.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>福建金森</t>
+          <t>跨境通</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.86</v>
+        <v>3.94</v>
       </c>
       <c r="E17" t="n">
-        <v>2.418</v>
+        <v>-0.5051</v>
       </c>
       <c r="F17" t="n">
-        <v>16.19</v>
+        <v>30.5</v>
       </c>
       <c r="G17" t="n">
-        <v>437748698</v>
+        <v>1914147358</v>
       </c>
       <c r="H17" t="n">
-        <v>61553556.05</v>
+        <v>358370939.18</v>
       </c>
       <c r="I17" t="n">
-        <v>66186370.1</v>
+        <v>130919642.76</v>
       </c>
       <c r="J17" t="n">
-        <v>127739926.15</v>
+        <v>489290581.94</v>
       </c>
       <c r="K17" t="n">
-        <v>4632814.05</v>
+        <v>-227451296.42</v>
       </c>
       <c r="L17" t="n">
-        <v>1.06</v>
+        <v>-11.88</v>
       </c>
       <c r="M17" t="n">
-        <v>29.18</v>
+        <v>25.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2796066160</v>
+        <v>6100151413.2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002819.SZ</t>
+          <t>002667.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>*ST威领</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>24.97</v>
+        <v>22.19</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.3391</v>
+        <v>0.8636</v>
       </c>
       <c r="F18" t="n">
-        <v>12.38</v>
+        <v>14.68</v>
       </c>
       <c r="G18" t="n">
-        <v>766756067</v>
+        <v>761034222</v>
       </c>
       <c r="H18" t="n">
-        <v>92422435.78</v>
+        <v>74412469</v>
       </c>
       <c r="I18" t="n">
-        <v>55907474.35</v>
+        <v>74743422</v>
       </c>
       <c r="J18" t="n">
-        <v>148329910.13</v>
+        <v>149155891</v>
       </c>
       <c r="K18" t="n">
-        <v>-36514961.43</v>
+        <v>330953</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.76</v>
+        <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>19.35</v>
+        <v>19.6</v>
       </c>
       <c r="N18" t="n">
-        <v>5897876195.42</v>
+        <v>5250398090</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2754,447 +2754,443 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002935.SZ</t>
+          <t>002717.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天奥电子</t>
+          <t>*ST岭南</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9956</v>
+        <v>-10.3896</v>
       </c>
       <c r="F19" t="n">
-        <v>5.65</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1216557728</v>
+        <v>12390468</v>
       </c>
       <c r="H19" t="n">
-        <v>143645059.32</v>
+        <v>5513928</v>
       </c>
       <c r="I19" t="n">
-        <v>146817000.73</v>
+        <v>1880664</v>
       </c>
       <c r="J19" t="n">
-        <v>290462060.05</v>
+        <v>7394592</v>
       </c>
       <c r="K19" t="n">
-        <v>3171941.41</v>
+        <v>-3633264</v>
       </c>
       <c r="L19" t="n">
-        <v>0.26</v>
+        <v>-29.32</v>
       </c>
       <c r="M19" t="n">
-        <v>23.88</v>
+        <v>59.68</v>
       </c>
       <c r="N19" t="n">
-        <v>7579559523.58</v>
+        <v>1234369887.54</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>003001.SZ</t>
+          <t>002813.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>路畅科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19.83</v>
+        <v>26.38</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.019</v>
+        <v>10.0083</v>
       </c>
       <c r="F20" t="n">
-        <v>16.75</v>
+        <v>7.53</v>
       </c>
       <c r="G20" t="n">
-        <v>389507058</v>
+        <v>427428725</v>
       </c>
       <c r="H20" t="n">
-        <v>113522391.92</v>
+        <v>62037591.9</v>
       </c>
       <c r="I20" t="n">
-        <v>61661883.2</v>
+        <v>73709904</v>
       </c>
       <c r="J20" t="n">
-        <v>175184275.12</v>
+        <v>135747495.9</v>
       </c>
       <c r="K20" t="n">
-        <v>-51860508.72</v>
+        <v>11672312.1</v>
       </c>
       <c r="L20" t="n">
-        <v>-13.31</v>
+        <v>2.73</v>
       </c>
       <c r="M20" t="n">
-        <v>44.98</v>
+        <v>31.76</v>
       </c>
       <c r="N20" t="n">
-        <v>2267580369.66</v>
+        <v>3162752437.28</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300291.SZ</t>
+          <t>002815.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>百纳千成</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.83</v>
+        <v>24.44</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.436</v>
+        <v>9.991</v>
       </c>
       <c r="F21" t="n">
-        <v>13.92</v>
+        <v>10.5</v>
       </c>
       <c r="G21" t="n">
-        <v>633638020</v>
+        <v>1935714620</v>
       </c>
       <c r="H21" t="n">
-        <v>50952864.68</v>
+        <v>538727790.72</v>
       </c>
       <c r="I21" t="n">
-        <v>70870311</v>
+        <v>435795500.62</v>
       </c>
       <c r="J21" t="n">
-        <v>121823175.68</v>
+        <v>974523291.34</v>
       </c>
       <c r="K21" t="n">
-        <v>19917446.32</v>
+        <v>-102932290.1</v>
       </c>
       <c r="L21" t="n">
-        <v>3.14</v>
+        <v>-5.32</v>
       </c>
       <c r="M21" t="n">
-        <v>19.23</v>
+        <v>50.34</v>
       </c>
       <c r="N21" t="n">
-        <v>4495564250.52</v>
+        <v>18993253673.16</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300300.SZ</t>
+          <t>002827.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>高争民爆</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.08</v>
+        <v>62.04</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4977</v>
+        <v>-9.9956</v>
       </c>
       <c r="F22" t="n">
-        <v>35.52</v>
+        <v>8.43</v>
       </c>
       <c r="G22" t="n">
-        <v>2650936634</v>
+        <v>1480701592</v>
       </c>
       <c r="H22" t="n">
-        <v>394057141.08</v>
+        <v>313193642.62</v>
       </c>
       <c r="I22" t="n">
-        <v>260308059.51</v>
+        <v>293267577.13</v>
       </c>
       <c r="J22" t="n">
-        <v>654365200.59</v>
+        <v>606461219.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-133749081.57</v>
+        <v>-19926065.49</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.05</v>
+        <v>-1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>24.68</v>
+        <v>40.96</v>
       </c>
       <c r="N22" t="n">
-        <v>7388250368</v>
+        <v>17122970205</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300585.SZ</t>
+          <t>002849.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>奥联电子</t>
+          <t>威星智能</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.83</v>
+        <v>23.22</v>
       </c>
       <c r="E23" t="n">
-        <v>-17.9715</v>
+        <v>4.219</v>
       </c>
       <c r="F23" t="n">
-        <v>10.43</v>
+        <v>15.33</v>
       </c>
       <c r="G23" t="n">
-        <v>255443903</v>
+        <v>745769880</v>
       </c>
       <c r="H23" t="n">
-        <v>36163989</v>
+        <v>169078522.28</v>
       </c>
       <c r="I23" t="n">
-        <v>29143906.42</v>
+        <v>165502381.6</v>
       </c>
       <c r="J23" t="n">
-        <v>65307895.42</v>
+        <v>334580903.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-7020082.58</v>
+        <v>-3576140.68</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.75</v>
+        <v>-0.48</v>
       </c>
       <c r="M23" t="n">
-        <v>25.57</v>
+        <v>44.86</v>
       </c>
       <c r="N23" t="n">
-        <v>2366466665.13</v>
+        <v>5078012961.24</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300829.SZ</t>
+          <t>002909.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>金丹科技</t>
+          <t>集泰股份</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.7</v>
+        <v>7.05</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.6343</v>
+        <v>-5.496</v>
       </c>
       <c r="F24" t="n">
-        <v>25.8</v>
+        <v>32.38</v>
       </c>
       <c r="G24" t="n">
-        <v>1029834224</v>
+        <v>850836459</v>
       </c>
       <c r="H24" t="n">
-        <v>183310815.42</v>
+        <v>177820953.93</v>
       </c>
       <c r="I24" t="n">
-        <v>183784007.5</v>
+        <v>158304322.8</v>
       </c>
       <c r="J24" t="n">
-        <v>367094822.92</v>
+        <v>336125276.73</v>
       </c>
       <c r="K24" t="n">
-        <v>473192.08</v>
+        <v>-19516631.13</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05</v>
+        <v>-2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>35.65</v>
+        <v>39.51</v>
       </c>
       <c r="N24" t="n">
-        <v>3816592563.7</v>
+        <v>2682013050.15</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300862.SZ</t>
+          <t>002912.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>蓝盾光电</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47.48</v>
+        <v>29.12</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.5611</v>
+        <v>10.0113</v>
       </c>
       <c r="F25" t="n">
-        <v>22.75</v>
+        <v>17.1</v>
       </c>
       <c r="G25" t="n">
-        <v>1725556940</v>
+        <v>998785139</v>
       </c>
       <c r="H25" t="n">
-        <v>254487972.14</v>
+        <v>115737648.43</v>
       </c>
       <c r="I25" t="n">
-        <v>239579809.47</v>
+        <v>221249175.29</v>
       </c>
       <c r="J25" t="n">
-        <v>494067781.61</v>
+        <v>336986823.72</v>
       </c>
       <c r="K25" t="n">
-        <v>-14908162.67</v>
+        <v>105511526.86</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.86</v>
+        <v>10.56</v>
       </c>
       <c r="M25" t="n">
-        <v>28.63</v>
+        <v>33.74</v>
       </c>
       <c r="N25" t="n">
-        <v>7191843412.36</v>
+        <v>4723928984.32</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>301004.SZ</t>
+          <t>123285.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>嘉益股份</t>
+          <t>润禾转02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.28</v>
+        <v>157.3</v>
       </c>
       <c r="E26" t="n">
-        <v>17.0642</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3.5</v>
-      </c>
+        <v>57.3</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>177021162</v>
+        <v>39725760</v>
       </c>
       <c r="H26" t="n">
-        <v>40670340.79</v>
+        <v>4365718.5</v>
       </c>
       <c r="I26" t="n">
-        <v>25117004.56</v>
+        <v>31248789</v>
       </c>
       <c r="J26" t="n">
-        <v>65787345.35</v>
+        <v>35614507.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-15553336.23</v>
+        <v>26883070.5</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.789999999999999</v>
+        <v>67.67</v>
       </c>
       <c r="M26" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5210190315</v>
-      </c>
+        <v>89.65000000000001</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>上市首日可转债</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3208,37 +3204,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24.95</v>
+        <v>29.94</v>
       </c>
       <c r="E27" t="n">
-        <v>20.0096</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>9.140000000000001</v>
+        <v>11.51</v>
       </c>
       <c r="G27" t="n">
-        <v>382851176</v>
+        <v>592781778</v>
       </c>
       <c r="H27" t="n">
-        <v>72544320.48</v>
+        <v>102330801.08</v>
       </c>
       <c r="I27" t="n">
-        <v>115640749.32</v>
+        <v>124902911.86</v>
       </c>
       <c r="J27" t="n">
-        <v>188185069.8</v>
+        <v>227233712.94</v>
       </c>
       <c r="K27" t="n">
-        <v>43096428.84</v>
+        <v>22572110.78</v>
       </c>
       <c r="L27" t="n">
-        <v>11.26</v>
+        <v>3.81</v>
       </c>
       <c r="M27" t="n">
-        <v>49.15</v>
+        <v>38.33</v>
       </c>
       <c r="N27" t="n">
-        <v>4537257300</v>
+        <v>5444708760</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3249,161 +3245,161 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>301190.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>善水科技</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>137.13</v>
+        <v>29.94</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.3547</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>36.98</v>
+        <v>11.51</v>
       </c>
       <c r="G28" t="n">
-        <v>1627681002</v>
+        <v>975632954</v>
       </c>
       <c r="H28" t="n">
-        <v>158394669.18</v>
+        <v>159051035.97</v>
       </c>
       <c r="I28" t="n">
-        <v>176107975.89</v>
+        <v>202337680.43</v>
       </c>
       <c r="J28" t="n">
-        <v>334502645.07</v>
+        <v>361388716.4</v>
       </c>
       <c r="K28" t="n">
-        <v>17713306.71</v>
+        <v>43286644.46</v>
       </c>
       <c r="L28" t="n">
-        <v>1.09</v>
+        <v>4.44</v>
       </c>
       <c r="M28" t="n">
-        <v>20.55</v>
+        <v>37.04</v>
       </c>
       <c r="N28" t="n">
-        <v>4227906179.49</v>
+        <v>5444708760</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>尚水智能</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>85.09999999999999</v>
+        <v>51.42</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4545</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>56.84</v>
+        <v>14.59</v>
       </c>
       <c r="G29" t="n">
-        <v>2601726950</v>
+        <v>143519666</v>
       </c>
       <c r="H29" t="n">
-        <v>373168515.6</v>
+        <v>24309699</v>
       </c>
       <c r="I29" t="n">
-        <v>323792104.19</v>
+        <v>86639221.09999999</v>
       </c>
       <c r="J29" t="n">
-        <v>696960619.79</v>
+        <v>110948920.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-49376411.41</v>
+        <v>62329522.1</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.9</v>
+        <v>43.43</v>
       </c>
       <c r="M29" t="n">
-        <v>26.79</v>
+        <v>77.31</v>
       </c>
       <c r="N29" t="n">
-        <v>4898479565.2</v>
+        <v>1036061014.38</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>301697.SZ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>贝特利</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.59</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.9535</v>
+        <v>-0.0278</v>
       </c>
       <c r="F30" t="n">
-        <v>33.78</v>
+        <v>40.87</v>
       </c>
       <c r="G30" t="n">
-        <v>418592545</v>
+        <v>1046998303</v>
       </c>
       <c r="H30" t="n">
-        <v>87778574.5</v>
+        <v>159248296.35</v>
       </c>
       <c r="I30" t="n">
-        <v>64890028.7</v>
+        <v>75123095.08</v>
       </c>
       <c r="J30" t="n">
-        <v>152668603.2</v>
+        <v>234371391.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-22888545.8</v>
+        <v>-84125201.27</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.47</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>36.47</v>
+        <v>22.39</v>
       </c>
       <c r="N30" t="n">
-        <v>1257703662.06</v>
+        <v>2515567896</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3414,106 +3410,106 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>301560.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>众捷股份</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40.68</v>
+        <v>33.88</v>
       </c>
       <c r="E31" t="n">
-        <v>14.4626</v>
+        <v>20.0142</v>
       </c>
       <c r="F31" t="n">
-        <v>65.56999999999999</v>
+        <v>24.46</v>
       </c>
       <c r="G31" t="n">
-        <v>1710375615</v>
+        <v>456100825</v>
       </c>
       <c r="H31" t="n">
-        <v>266133190.07</v>
+        <v>59087755.88</v>
       </c>
       <c r="I31" t="n">
-        <v>161746064.24</v>
+        <v>97916170.12</v>
       </c>
       <c r="J31" t="n">
-        <v>427879254.31</v>
+        <v>157003926</v>
       </c>
       <c r="K31" t="n">
-        <v>-104387125.83</v>
+        <v>38828414.24</v>
       </c>
       <c r="L31" t="n">
-        <v>-6.1</v>
+        <v>8.51</v>
       </c>
       <c r="M31" t="n">
-        <v>25.02</v>
+        <v>34.42</v>
       </c>
       <c r="N31" t="n">
-        <v>2844811345.32</v>
+        <v>1979676160</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>301560.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>众捷股份</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>40.68</v>
+        <v>33.88</v>
       </c>
       <c r="E32" t="n">
-        <v>14.4626</v>
+        <v>20.0142</v>
       </c>
       <c r="F32" t="n">
-        <v>65.56999999999999</v>
+        <v>24.46</v>
       </c>
       <c r="G32" t="n">
-        <v>2577896910</v>
+        <v>1164922802</v>
       </c>
       <c r="H32" t="n">
-        <v>352372639.85</v>
+        <v>183782828.92</v>
       </c>
       <c r="I32" t="n">
-        <v>298037943.21</v>
+        <v>199446313.8</v>
       </c>
       <c r="J32" t="n">
-        <v>650410583.0599999</v>
+        <v>383229142.72</v>
       </c>
       <c r="K32" t="n">
-        <v>-54334696.64</v>
+        <v>15663484.88</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.11</v>
+        <v>1.34</v>
       </c>
       <c r="M32" t="n">
-        <v>25.23</v>
+        <v>32.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2844811345.32</v>
+        <v>1979676160</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3524,491 +3520,491 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>600032.SH</t>
+          <t>301583.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>托伦斯</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.43</v>
+        <v>130.12</v>
       </c>
       <c r="E33" t="n">
-        <v>10.0741</v>
+        <v>-5.1119</v>
       </c>
       <c r="F33" t="n">
-        <v>2.53</v>
+        <v>31.49</v>
       </c>
       <c r="G33" t="n">
-        <v>441559885</v>
+        <v>1306323685</v>
       </c>
       <c r="H33" t="n">
-        <v>33228975.96</v>
+        <v>167504687.82</v>
       </c>
       <c r="I33" t="n">
-        <v>88662630.81</v>
+        <v>205259151.51</v>
       </c>
       <c r="J33" t="n">
-        <v>121891606.77</v>
+        <v>372763839.33</v>
       </c>
       <c r="K33" t="n">
-        <v>55433654.85</v>
+        <v>37754463.69</v>
       </c>
       <c r="L33" t="n">
-        <v>12.55</v>
+        <v>2.89</v>
       </c>
       <c r="M33" t="n">
-        <v>27.6</v>
+        <v>28.54</v>
       </c>
       <c r="N33" t="n">
-        <v>17866737657.32</v>
+        <v>4011778254.76</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>600293.SH</t>
+          <t>301655.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>绿控传动</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.93</v>
+        <v>25.76</v>
       </c>
       <c r="E34" t="n">
-        <v>3.9683</v>
+        <v>8.0084</v>
       </c>
       <c r="F34" t="n">
-        <v>18.04</v>
+        <v>35.57</v>
       </c>
       <c r="G34" t="n">
-        <v>2059218861</v>
+        <v>400263167</v>
       </c>
       <c r="H34" t="n">
-        <v>169533167.58</v>
+        <v>32425897.95</v>
       </c>
       <c r="I34" t="n">
-        <v>151688319.02</v>
+        <v>59670224.26</v>
       </c>
       <c r="J34" t="n">
-        <v>321221486.6</v>
+        <v>92096122.20999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-17844848.56</v>
+        <v>27244326.31</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.87</v>
+        <v>6.81</v>
       </c>
       <c r="M34" t="n">
-        <v>15.6</v>
+        <v>23.01</v>
       </c>
       <c r="N34" t="n">
-        <v>4559370030.78</v>
+        <v>1158380522.88</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>600340.SH</t>
+          <t>301689.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>*ST华幸</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.29</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>10.2564</v>
+        <v>-8.918900000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>4.76</v>
+        <v>40.32</v>
       </c>
       <c r="G35" t="n">
-        <v>231359037</v>
+        <v>1836793430</v>
       </c>
       <c r="H35" t="n">
-        <v>18556856.19</v>
+        <v>332130366.75</v>
       </c>
       <c r="I35" t="n">
-        <v>11484817.4</v>
+        <v>217062295.09</v>
       </c>
       <c r="J35" t="n">
-        <v>30041673.59</v>
+        <v>549192661.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-7072038.79</v>
+        <v>-115068071.66</v>
       </c>
       <c r="L35" t="n">
-        <v>-3.06</v>
+        <v>-6.26</v>
       </c>
       <c r="M35" t="n">
-        <v>12.98</v>
+        <v>29.9</v>
       </c>
       <c r="N35" t="n">
-        <v>5022428029.98</v>
+        <v>4461588144.52</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>600353.SH</t>
+          <t>301699.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>旭光电子</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29.31</v>
+        <v>37.71</v>
       </c>
       <c r="E36" t="n">
-        <v>-10.0092</v>
+        <v>-7.3009</v>
       </c>
       <c r="F36" t="n">
-        <v>5.8</v>
+        <v>54.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1445828491</v>
+        <v>1496775712</v>
       </c>
       <c r="H36" t="n">
-        <v>232985348.92</v>
+        <v>158510938.75</v>
       </c>
       <c r="I36" t="n">
-        <v>236923020.74</v>
+        <v>217378829.84</v>
       </c>
       <c r="J36" t="n">
-        <v>469908369.66</v>
+        <v>375889768.59</v>
       </c>
       <c r="K36" t="n">
-        <v>3937671.82</v>
+        <v>58867891.09</v>
       </c>
       <c r="L36" t="n">
-        <v>0.27</v>
+        <v>3.93</v>
       </c>
       <c r="M36" t="n">
-        <v>32.5</v>
+        <v>25.11</v>
       </c>
       <c r="N36" t="n">
-        <v>24292455070.29</v>
+        <v>2637114941.79</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>600540.SH</t>
+          <t>301716.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>鸿富诚</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.64</v>
+        <v>578.88</v>
       </c>
       <c r="E37" t="n">
-        <v>3.8674</v>
+        <v>653.1616</v>
       </c>
       <c r="F37" t="n">
-        <v>28.27</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>952020633</v>
+        <v>6231355537</v>
       </c>
       <c r="H37" t="n">
-        <v>158684330</v>
+        <v>141291084.45</v>
       </c>
       <c r="I37" t="n">
-        <v>221204138</v>
+        <v>561332137.59</v>
       </c>
       <c r="J37" t="n">
-        <v>379888468</v>
+        <v>702623222.04</v>
       </c>
       <c r="K37" t="n">
-        <v>62519808</v>
+        <v>420041053.14</v>
       </c>
       <c r="L37" t="n">
-        <v>6.57</v>
+        <v>6.74</v>
       </c>
       <c r="M37" t="n">
-        <v>39.9</v>
+        <v>11.28</v>
       </c>
       <c r="N37" t="n">
-        <v>3278966054.4</v>
+        <v>7208991195.84</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>无价格涨跌幅限制的证券</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>600547.SH</t>
+          <t>600032.SH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>山东黄金</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>26.16</v>
+        <v>8.17</v>
       </c>
       <c r="E38" t="n">
-        <v>-10.0103</v>
+        <v>9.9596</v>
       </c>
       <c r="F38" t="n">
-        <v>3.88</v>
+        <v>2.35</v>
       </c>
       <c r="G38" t="n">
-        <v>3716226173</v>
+        <v>896423238</v>
       </c>
       <c r="H38" t="n">
-        <v>822681758.8</v>
+        <v>71871032.52</v>
       </c>
       <c r="I38" t="n">
-        <v>595094972.78</v>
+        <v>161105235.13</v>
       </c>
       <c r="J38" t="n">
-        <v>1417776731.58</v>
+        <v>232976267.65</v>
       </c>
       <c r="K38" t="n">
-        <v>-227586786.02</v>
+        <v>89234202.61</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>38.15</v>
+        <v>25.99</v>
       </c>
       <c r="N38" t="n">
-        <v>94553837957.52</v>
+        <v>19646197397.08</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>600721.SH</t>
+          <t>600207.SH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>安彩高科</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.18</v>
+        <v>5.48</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.7276</v>
+        <v>0.3663</v>
       </c>
       <c r="F39" t="n">
-        <v>26.06</v>
+        <v>6.92</v>
       </c>
       <c r="G39" t="n">
-        <v>1231440169</v>
+        <v>406105365</v>
       </c>
       <c r="H39" t="n">
-        <v>201108406</v>
+        <v>34347002.34</v>
       </c>
       <c r="I39" t="n">
-        <v>128231457</v>
+        <v>31725404.32</v>
       </c>
       <c r="J39" t="n">
-        <v>329339863</v>
+        <v>66072406.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-72876949</v>
+        <v>-2621598.02</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.92</v>
+        <v>-0.65</v>
       </c>
       <c r="M39" t="n">
-        <v>26.74</v>
+        <v>16.27</v>
       </c>
       <c r="N39" t="n">
-        <v>4683790194.3</v>
+        <v>5969432795.92</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>600743.SH</t>
+          <t>600241.SH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>华远控股</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.3</v>
+        <v>8.84</v>
       </c>
       <c r="E40" t="n">
-        <v>-10.1563</v>
+        <v>9.950200000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="G40" t="n">
-        <v>348103448</v>
+        <v>296146374</v>
       </c>
       <c r="H40" t="n">
-        <v>66656391.38</v>
+        <v>99619956</v>
       </c>
       <c r="I40" t="n">
-        <v>50458980</v>
+        <v>57431404</v>
       </c>
       <c r="J40" t="n">
-        <v>117115371.38</v>
+        <v>157051360</v>
       </c>
       <c r="K40" t="n">
-        <v>-16197411.38</v>
+        <v>-42188552</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.65</v>
+        <v>-14.25</v>
       </c>
       <c r="M40" t="n">
-        <v>33.64</v>
+        <v>53.03</v>
       </c>
       <c r="N40" t="n">
-        <v>5396032010.2</v>
+        <v>2601630696.6</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>600325.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.550000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="E41" t="n">
-        <v>10.0386</v>
+        <v>10.0746</v>
       </c>
       <c r="F41" t="n">
-        <v>0.48</v>
+        <v>6.38</v>
       </c>
       <c r="G41" t="n">
-        <v>42985476</v>
+        <v>495959455</v>
       </c>
       <c r="H41" t="n">
-        <v>8644905</v>
+        <v>91827539</v>
       </c>
       <c r="I41" t="n">
-        <v>37812375</v>
+        <v>104399984</v>
       </c>
       <c r="J41" t="n">
-        <v>46457280</v>
+        <v>196227523</v>
       </c>
       <c r="K41" t="n">
-        <v>29167470</v>
+        <v>12572445</v>
       </c>
       <c r="L41" t="n">
-        <v>67.84999999999999</v>
+        <v>2.53</v>
       </c>
       <c r="M41" t="n">
-        <v>108.08</v>
+        <v>39.57</v>
       </c>
       <c r="N41" t="n">
-        <v>8933791117.5</v>
+        <v>8118848742.2</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4019,271 +4015,271 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>600340.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.550000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="E42" t="n">
-        <v>10.0386</v>
+        <v>6.2016</v>
       </c>
       <c r="F42" t="n">
-        <v>0.48</v>
+        <v>6.25</v>
       </c>
       <c r="G42" t="n">
-        <v>89490418</v>
+        <v>325514204</v>
       </c>
       <c r="H42" t="n">
-        <v>11314445.1</v>
+        <v>24520547</v>
       </c>
       <c r="I42" t="n">
-        <v>46458300</v>
+        <v>20108380</v>
       </c>
       <c r="J42" t="n">
-        <v>57772745.1</v>
+        <v>44628927</v>
       </c>
       <c r="K42" t="n">
-        <v>35143854.9</v>
+        <v>-4412167</v>
       </c>
       <c r="L42" t="n">
-        <v>39.27</v>
+        <v>-1.36</v>
       </c>
       <c r="M42" t="n">
-        <v>64.56</v>
+        <v>13.71</v>
       </c>
       <c r="N42" t="n">
-        <v>8933791117.5</v>
+        <v>5333896434.94</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>601086.SH</t>
+          <t>600340.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.85</v>
+        <v>1.37</v>
       </c>
       <c r="E43" t="n">
-        <v>3.4595</v>
+        <v>6.2016</v>
       </c>
       <c r="F43" t="n">
-        <v>14.71</v>
+        <v>6.25</v>
       </c>
       <c r="G43" t="n">
-        <v>1454370480</v>
+        <v>661875379</v>
       </c>
       <c r="H43" t="n">
-        <v>111502943</v>
+        <v>39155206.19</v>
       </c>
       <c r="I43" t="n">
-        <v>163281722</v>
+        <v>35651960.4</v>
       </c>
       <c r="J43" t="n">
-        <v>274784665</v>
+        <v>74807166.59</v>
       </c>
       <c r="K43" t="n">
-        <v>51778779</v>
+        <v>-3503245.79</v>
       </c>
       <c r="L43" t="n">
-        <v>3.56</v>
+        <v>-0.53</v>
       </c>
       <c r="M43" t="n">
-        <v>18.89</v>
+        <v>11.3</v>
       </c>
       <c r="N43" t="n">
-        <v>10556100000</v>
+        <v>5333896434.94</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>601091.SH</t>
+          <t>600371.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.71</v>
+        <v>12.84</v>
       </c>
       <c r="E44" t="n">
-        <v>2.6296</v>
+        <v>-10.021</v>
       </c>
       <c r="F44" t="n">
-        <v>53.59</v>
+        <v>11.64</v>
       </c>
       <c r="G44" t="n">
-        <v>2963675626</v>
+        <v>439783617</v>
       </c>
       <c r="H44" t="n">
-        <v>188116767.86</v>
+        <v>44242597.13</v>
       </c>
       <c r="I44" t="n">
-        <v>186220735.78</v>
+        <v>30464196</v>
       </c>
       <c r="J44" t="n">
-        <v>374337503.64</v>
+        <v>74706793.13</v>
       </c>
       <c r="K44" t="n">
-        <v>-1896032.08</v>
+        <v>-13778401.13</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.06</v>
+        <v>-3.13</v>
       </c>
       <c r="M44" t="n">
-        <v>12.63</v>
+        <v>16.99</v>
       </c>
       <c r="N44" t="n">
-        <v>5851331773.22</v>
+        <v>3756701520</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>601218.SH</t>
+          <t>600371.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.05</v>
+        <v>12.84</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>-10.021</v>
       </c>
       <c r="F45" t="n">
-        <v>27.33</v>
+        <v>11.64</v>
       </c>
       <c r="G45" t="n">
-        <v>1514983777</v>
+        <v>2454765515</v>
       </c>
       <c r="H45" t="n">
-        <v>214836029.44</v>
+        <v>252583970.74</v>
       </c>
       <c r="I45" t="n">
-        <v>145625813.17</v>
+        <v>198757662.23</v>
       </c>
       <c r="J45" t="n">
-        <v>360461842.61</v>
+        <v>451341632.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-69210216.27</v>
+        <v>-53826308.51</v>
       </c>
       <c r="L45" t="n">
-        <v>-4.57</v>
+        <v>-2.19</v>
       </c>
       <c r="M45" t="n">
-        <v>23.79</v>
+        <v>18.39</v>
       </c>
       <c r="N45" t="n">
-        <v>5862652747.6</v>
+        <v>3756701520</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>601218.SH</t>
+          <t>600488.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.05</v>
+        <v>6.9</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>10.0478</v>
       </c>
       <c r="F46" t="n">
-        <v>27.33</v>
+        <v>12.87</v>
       </c>
       <c r="G46" t="n">
-        <v>2303488046</v>
+        <v>1577186544</v>
       </c>
       <c r="H46" t="n">
-        <v>248929494.79</v>
+        <v>189396879.85</v>
       </c>
       <c r="I46" t="n">
-        <v>290586297.6</v>
+        <v>272954989.88</v>
       </c>
       <c r="J46" t="n">
-        <v>539515792.39</v>
+        <v>462351869.73</v>
       </c>
       <c r="K46" t="n">
-        <v>41656802.81</v>
+        <v>83558110.03</v>
       </c>
       <c r="L46" t="n">
-        <v>1.81</v>
+        <v>5.3</v>
       </c>
       <c r="M46" t="n">
-        <v>23.42</v>
+        <v>29.31</v>
       </c>
       <c r="N46" t="n">
-        <v>5862652747.6</v>
+        <v>7534018092</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4294,161 +4290,161 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>601811.SH</t>
+          <t>600657.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>信达地产</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.52</v>
+        <v>3.38</v>
       </c>
       <c r="E47" t="n">
-        <v>-8.992599999999999</v>
+        <v>10.0977</v>
       </c>
       <c r="F47" t="n">
-        <v>8.050000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="G47" t="n">
-        <v>1317723424</v>
+        <v>252867032</v>
       </c>
       <c r="H47" t="n">
-        <v>115611875.08</v>
+        <v>42902106.81</v>
       </c>
       <c r="I47" t="n">
-        <v>90529955.64</v>
+        <v>68690668.45</v>
       </c>
       <c r="J47" t="n">
-        <v>206141830.72</v>
+        <v>111592775.26</v>
       </c>
       <c r="K47" t="n">
-        <v>-25081919.44</v>
+        <v>25788561.64</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.9</v>
+        <v>10.2</v>
       </c>
       <c r="M47" t="n">
-        <v>15.64</v>
+        <v>44.13</v>
       </c>
       <c r="N47" t="n">
-        <v>14666060228</v>
+        <v>9639349651.1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>603052.SH</t>
+          <t>600721.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>可川科技</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>52.61</v>
+        <v>12.95</v>
       </c>
       <c r="E48" t="n">
-        <v>-10.0068</v>
+        <v>6.3218</v>
       </c>
       <c r="F48" t="n">
-        <v>2.42</v>
+        <v>39.12</v>
       </c>
       <c r="G48" t="n">
-        <v>245235215</v>
+        <v>1956660207</v>
       </c>
       <c r="H48" t="n">
-        <v>37340174.73</v>
+        <v>145175658</v>
       </c>
       <c r="I48" t="n">
-        <v>26232300.43</v>
+        <v>205028229</v>
       </c>
       <c r="J48" t="n">
-        <v>63572475.16</v>
+        <v>350203887</v>
       </c>
       <c r="K48" t="n">
-        <v>-11107874.3</v>
+        <v>59852571</v>
       </c>
       <c r="L48" t="n">
-        <v>-4.53</v>
+        <v>3.06</v>
       </c>
       <c r="M48" t="n">
-        <v>25.92</v>
+        <v>17.9</v>
       </c>
       <c r="N48" t="n">
-        <v>9885276006.02</v>
+        <v>4979891873.25</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>603230.SH</t>
+          <t>600815.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>厦工股份</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16.62</v>
+        <v>3.77</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.0162</v>
+        <v>-10.0239</v>
       </c>
       <c r="F49" t="n">
-        <v>4.29</v>
+        <v>10.32</v>
       </c>
       <c r="G49" t="n">
-        <v>262244165</v>
+        <v>698680903</v>
       </c>
       <c r="H49" t="n">
-        <v>28203830</v>
+        <v>213091206.86</v>
       </c>
       <c r="I49" t="n">
-        <v>38722120.1</v>
+        <v>96787099</v>
       </c>
       <c r="J49" t="n">
-        <v>66925950.1</v>
+        <v>309878305.86</v>
       </c>
       <c r="K49" t="n">
-        <v>10518290.1</v>
+        <v>-116304107.86</v>
       </c>
       <c r="L49" t="n">
-        <v>4.01</v>
+        <v>-16.65</v>
       </c>
       <c r="M49" t="n">
-        <v>25.52</v>
+        <v>44.35</v>
       </c>
       <c r="N49" t="n">
-        <v>5875552260</v>
+        <v>6688336189.6</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4459,216 +4455,216 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>603248.SH</t>
+          <t>601091.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>23.2</v>
+        <v>25.19</v>
       </c>
       <c r="E50" t="n">
-        <v>2.9281</v>
+        <v>-9.094200000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>38.12</v>
+        <v>39.71</v>
       </c>
       <c r="G50" t="n">
-        <v>603520495</v>
+        <v>2176461260</v>
       </c>
       <c r="H50" t="n">
-        <v>38046682.86</v>
+        <v>153408406.1</v>
       </c>
       <c r="I50" t="n">
-        <v>53607818.05</v>
+        <v>201972312.93</v>
       </c>
       <c r="J50" t="n">
-        <v>91654500.91</v>
+        <v>355380719.03</v>
       </c>
       <c r="K50" t="n">
-        <v>15561135.19</v>
+        <v>48563906.83</v>
       </c>
       <c r="L50" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="M50" t="n">
-        <v>15.19</v>
+        <v>16.33</v>
       </c>
       <c r="N50" t="n">
-        <v>1658914863.2</v>
+        <v>5319200554.58</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>603278.SH</t>
+          <t>601218.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.78</v>
+        <v>6.13</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>1.3223</v>
       </c>
       <c r="F51" t="n">
-        <v>18.89</v>
+        <v>29.39</v>
       </c>
       <c r="G51" t="n">
-        <v>819989716</v>
+        <v>1760320302</v>
       </c>
       <c r="H51" t="n">
-        <v>117815256.8</v>
+        <v>158281976.7</v>
       </c>
       <c r="I51" t="n">
-        <v>111407346.36</v>
+        <v>154519919.77</v>
       </c>
       <c r="J51" t="n">
-        <v>229222603.16</v>
+        <v>312801896.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-6407910.44</v>
+        <v>-3762056.93</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.78</v>
+        <v>-0.21</v>
       </c>
       <c r="M51" t="n">
-        <v>27.95</v>
+        <v>17.77</v>
       </c>
       <c r="N51" t="n">
-        <v>3684166245.76</v>
+        <v>5940175428.56</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>603373.SH</t>
+          <t>601579.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>安邦护卫</t>
+          <t>会稽山</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>52.7</v>
+        <v>37.66</v>
       </c>
       <c r="E52" t="n">
-        <v>3.7402</v>
+        <v>-9.990399999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>10.07</v>
+        <v>1.46</v>
       </c>
       <c r="G52" t="n">
-        <v>779797701</v>
+        <v>270360448</v>
       </c>
       <c r="H52" t="n">
-        <v>125672129.36</v>
+        <v>52515181</v>
       </c>
       <c r="I52" t="n">
-        <v>147749660.59</v>
+        <v>25649580</v>
       </c>
       <c r="J52" t="n">
-        <v>273421789.95</v>
+        <v>78164761</v>
       </c>
       <c r="K52" t="n">
-        <v>22077531.23</v>
+        <v>-26865601</v>
       </c>
       <c r="L52" t="n">
-        <v>2.83</v>
+        <v>-9.94</v>
       </c>
       <c r="M52" t="n">
-        <v>35.06</v>
+        <v>28.91</v>
       </c>
       <c r="N52" t="n">
-        <v>3351833357.7</v>
+        <v>18056591982.94</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>603968.SH</t>
+          <t>601949.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>中国出版</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.63</v>
+        <v>6.01</v>
       </c>
       <c r="E53" t="n">
-        <v>10.0284</v>
+        <v>10.0733</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G53" t="n">
-        <v>113396778</v>
+        <v>508795221</v>
       </c>
       <c r="H53" t="n">
-        <v>22573273</v>
+        <v>68630404.55</v>
       </c>
       <c r="I53" t="n">
-        <v>46922376.12</v>
+        <v>106412141.92</v>
       </c>
       <c r="J53" t="n">
-        <v>69495649.12</v>
+        <v>175042546.47</v>
       </c>
       <c r="K53" t="n">
-        <v>24349103.12</v>
+        <v>37781737.37</v>
       </c>
       <c r="L53" t="n">
-        <v>21.47</v>
+        <v>7.43</v>
       </c>
       <c r="M53" t="n">
-        <v>61.29</v>
+        <v>34.4</v>
       </c>
       <c r="N53" t="n">
-        <v>2378102400</v>
+        <v>11442848004.54</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4679,493 +4675,1043 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>605366.SH</t>
+          <t>603042.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>华脉科技</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.14</v>
+        <v>16.55</v>
       </c>
       <c r="E54" t="n">
-        <v>9.978300000000001</v>
+        <v>-1.8387</v>
       </c>
       <c r="F54" t="n">
-        <v>13.53</v>
+        <v>25.46</v>
       </c>
       <c r="G54" t="n">
-        <v>2075854245</v>
+        <v>885769590</v>
       </c>
       <c r="H54" t="n">
-        <v>309779469.26</v>
+        <v>142845072.33</v>
       </c>
       <c r="I54" t="n">
-        <v>243447329.96</v>
+        <v>231520692.54</v>
       </c>
       <c r="J54" t="n">
-        <v>553226799.22</v>
+        <v>374365764.87</v>
       </c>
       <c r="K54" t="n">
-        <v>-66332139.3</v>
+        <v>88675620.20999999</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.2</v>
+        <v>10.01</v>
       </c>
       <c r="M54" t="n">
-        <v>26.65</v>
+        <v>42.26</v>
       </c>
       <c r="N54" t="n">
-        <v>7836472878</v>
+        <v>3455090407.6</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>688244.SH</t>
+          <t>603188.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>永信至诚</t>
+          <t>亚邦股份</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19.8</v>
+        <v>4.91</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>10.0897</v>
       </c>
       <c r="F55" t="n">
-        <v>9.779999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="G55" t="n">
-        <v>270535500</v>
+        <v>118209349</v>
       </c>
       <c r="H55" t="n">
-        <v>13685218.69</v>
+        <v>26709476</v>
       </c>
       <c r="I55" t="n">
-        <v>56813902.22</v>
+        <v>54845107</v>
       </c>
       <c r="J55" t="n">
-        <v>70499120.91</v>
+        <v>81554583</v>
       </c>
       <c r="K55" t="n">
-        <v>43128683.53</v>
+        <v>28135631</v>
       </c>
       <c r="L55" t="n">
-        <v>15.94</v>
+        <v>23.8</v>
       </c>
       <c r="M55" t="n">
-        <v>26.06</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>2989038076.2</v>
+        <v>2799534700</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>688628.SH</t>
+          <t>603248.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>优利德</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>91.98999999999999</v>
+        <v>21.31</v>
       </c>
       <c r="E56" t="n">
-        <v>-17.0439</v>
+        <v>-8.146599999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>14.27</v>
+        <v>30.43</v>
       </c>
       <c r="G56" t="n">
-        <v>1489321900</v>
+        <v>470992979</v>
       </c>
       <c r="H56" t="n">
-        <v>387062646.4</v>
+        <v>52462653.13</v>
       </c>
       <c r="I56" t="n">
-        <v>293647943.92</v>
+        <v>26077389.46</v>
       </c>
       <c r="J56" t="n">
-        <v>680710590.3200001</v>
+        <v>78540042.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-93414702.48</v>
+        <v>-26385263.67</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.27</v>
+        <v>-5.6</v>
       </c>
       <c r="M56" t="n">
-        <v>45.71</v>
+        <v>16.68</v>
       </c>
       <c r="N56" t="n">
-        <v>10339021767.12</v>
+        <v>1523770505.81</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>920025.BJ</t>
+          <t>603396.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>凯达重工</t>
+          <t>金辰股份</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.2</v>
+        <v>35.28</v>
       </c>
       <c r="E57" t="n">
-        <v>-25.1232</v>
+        <v>-10</v>
       </c>
       <c r="F57" t="n">
-        <v>47.4</v>
+        <v>10.68</v>
       </c>
       <c r="G57" t="n">
-        <v>397738500</v>
+        <v>531242447</v>
       </c>
       <c r="H57" t="n">
-        <v>45390596.23</v>
+        <v>110705182.25</v>
       </c>
       <c r="I57" t="n">
-        <v>21383950.75</v>
+        <v>86846835.59999999</v>
       </c>
       <c r="J57" t="n">
-        <v>66774546.98</v>
+        <v>197552017.85</v>
       </c>
       <c r="K57" t="n">
-        <v>-24006645.48</v>
+        <v>-23858346.65</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.04</v>
+        <v>-4.49</v>
       </c>
       <c r="M57" t="n">
-        <v>16.79</v>
+        <v>37.19</v>
       </c>
       <c r="N57" t="n">
-        <v>775200000</v>
+        <v>4887249423.84</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>920025.BJ</t>
+          <t>603636.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>凯达重工</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.2</v>
+        <v>7.87</v>
       </c>
       <c r="E58" t="n">
-        <v>-25.1232</v>
+        <v>10.0699</v>
       </c>
       <c r="F58" t="n">
-        <v>47.4</v>
+        <v>12.1</v>
       </c>
       <c r="G58" t="n">
-        <v>975460800</v>
+        <v>532650770</v>
       </c>
       <c r="H58" t="n">
-        <v>73178359.2</v>
+        <v>34137676.75</v>
       </c>
       <c r="I58" t="n">
-        <v>68031633.94</v>
+        <v>96471900.62</v>
       </c>
       <c r="J58" t="n">
-        <v>141209993.14</v>
+        <v>130609577.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-5146725.26</v>
+        <v>62334223.87</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.53</v>
+        <v>11.7</v>
       </c>
       <c r="M58" t="n">
-        <v>14.48</v>
+        <v>24.52</v>
       </c>
       <c r="N58" t="n">
-        <v>775200000</v>
+        <v>4567437316.01</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>920071.BJ</t>
+          <t>603823.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>金钛股份</t>
+          <t>百合花</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27</v>
+        <v>42.69</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4599</v>
+        <v>-9.9937</v>
       </c>
       <c r="F59" t="n">
-        <v>27.54</v>
+        <v>5.88</v>
       </c>
       <c r="G59" t="n">
-        <v>234225800</v>
+        <v>1052101609</v>
       </c>
       <c r="H59" t="n">
-        <v>36609338.29</v>
+        <v>184969541.26</v>
       </c>
       <c r="I59" t="n">
-        <v>25285642.46</v>
+        <v>68230066.65000001</v>
       </c>
       <c r="J59" t="n">
-        <v>61894980.75</v>
+        <v>253199607.91</v>
       </c>
       <c r="K59" t="n">
-        <v>-11323695.83</v>
+        <v>-116739474.61</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.83</v>
+        <v>-11.1</v>
       </c>
       <c r="M59" t="n">
-        <v>26.43</v>
+        <v>24.07</v>
       </c>
       <c r="N59" t="n">
-        <v>850500000</v>
+        <v>17774737283.76</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>920201.BJ</t>
+          <t>603949.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>百瑞吉</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>52.01</v>
+        <v>20.45</v>
       </c>
       <c r="E60" t="n">
-        <v>-28.1133</v>
+        <v>10.0054</v>
       </c>
       <c r="F60" t="n">
-        <v>58.07</v>
+        <v>1.68</v>
       </c>
       <c r="G60" t="n">
-        <v>248456500</v>
+        <v>371118244</v>
       </c>
       <c r="H60" t="n">
-        <v>24767530.76</v>
+        <v>32878783.96</v>
       </c>
       <c r="I60" t="n">
-        <v>47863309.05</v>
+        <v>34661798.1</v>
       </c>
       <c r="J60" t="n">
-        <v>72630839.81</v>
+        <v>67540582.06</v>
       </c>
       <c r="K60" t="n">
-        <v>23095778.29</v>
+        <v>1783014.14</v>
       </c>
       <c r="L60" t="n">
-        <v>9.300000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="M60" t="n">
-        <v>29.23</v>
+        <v>18.2</v>
       </c>
       <c r="N60" t="n">
-        <v>395716368.67</v>
+        <v>4298697853.3</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>920229.BJ</t>
+          <t>605058.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>世纪数码</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>55.88</v>
+        <v>59.6</v>
       </c>
       <c r="E61" t="n">
-        <v>-13.6054</v>
+        <v>10.0037</v>
       </c>
       <c r="F61" t="n">
-        <v>57.54</v>
+        <v>15.4</v>
       </c>
       <c r="G61" t="n">
-        <v>379189800</v>
+        <v>1236139111</v>
       </c>
       <c r="H61" t="n">
-        <v>40095417.15</v>
+        <v>112536600</v>
       </c>
       <c r="I61" t="n">
-        <v>34135931.83</v>
+        <v>164356405.4</v>
       </c>
       <c r="J61" t="n">
-        <v>74231348.98</v>
+        <v>276893005.4</v>
       </c>
       <c r="K61" t="n">
-        <v>-5959485.32</v>
+        <v>51819805.4</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.57</v>
+        <v>4.19</v>
       </c>
       <c r="M61" t="n">
-        <v>19.58</v>
+        <v>22.4</v>
       </c>
       <c r="N61" t="n">
-        <v>634238000</v>
+        <v>8518337152</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>605198.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>安德利</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9.9983</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G62" t="n">
+        <v>387107256</v>
+      </c>
+      <c r="H62" t="n">
+        <v>88511223.40000001</v>
+      </c>
+      <c r="I62" t="n">
+        <v>111953343.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>200464567</v>
+      </c>
+      <c r="K62" t="n">
+        <v>23442120.2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M62" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="N62" t="n">
+        <v>17768804480</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.4707</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G63" t="n">
+        <v>573581708</v>
+      </c>
+      <c r="H63" t="n">
+        <v>31902205.3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>54048163.28</v>
+      </c>
+      <c r="J63" t="n">
+        <v>85950368.58</v>
+      </c>
+      <c r="K63" t="n">
+        <v>22145957.98</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M63" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N63" t="n">
+        <v>6577777786</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688244.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>永信至诚</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7.2727</v>
+      </c>
+      <c r="F64" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="G64" t="n">
+        <v>771088300</v>
+      </c>
+      <c r="H64" t="n">
+        <v>72842654.92</v>
+      </c>
+      <c r="I64" t="n">
+        <v>77807070.01000001</v>
+      </c>
+      <c r="J64" t="n">
+        <v>150649724.93</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4964415.09</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M64" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3206422663.56</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688655.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>迅捷兴</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>20.0063</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="G65" t="n">
+        <v>953119800</v>
+      </c>
+      <c r="H65" t="n">
+        <v>178062011.98</v>
+      </c>
+      <c r="I65" t="n">
+        <v>231513119.88</v>
+      </c>
+      <c r="J65" t="n">
+        <v>409575131.86</v>
+      </c>
+      <c r="K65" t="n">
+        <v>53451107.9</v>
+      </c>
+      <c r="L65" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="M65" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="N65" t="n">
+        <v>10097623000</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688685.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>迈信林</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="E66" t="n">
+        <v>20.0121</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G66" t="n">
+        <v>332588900</v>
+      </c>
+      <c r="H66" t="n">
+        <v>42953604.34</v>
+      </c>
+      <c r="I66" t="n">
+        <v>75816070.75</v>
+      </c>
+      <c r="J66" t="n">
+        <v>118769675.09</v>
+      </c>
+      <c r="K66" t="n">
+        <v>32862466.41</v>
+      </c>
+      <c r="L66" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="M66" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5830011179.9</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>920025.BJ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>凯达重工</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-12.8947</v>
+      </c>
+      <c r="F67" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="G67" t="n">
+        <v>266604800</v>
+      </c>
+      <c r="H67" t="n">
+        <v>23341987.57</v>
+      </c>
+      <c r="I67" t="n">
+        <v>30032515.74</v>
+      </c>
+      <c r="J67" t="n">
+        <v>53374503.31</v>
+      </c>
+      <c r="K67" t="n">
+        <v>6690528.17</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M67" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="N67" t="n">
+        <v>675240000</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>920201.BJ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>百瑞吉</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-11.4978</v>
+      </c>
+      <c r="F68" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="G68" t="n">
+        <v>169549500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>30080711.35</v>
+      </c>
+      <c r="I68" t="n">
+        <v>26643816.85</v>
+      </c>
+      <c r="J68" t="n">
+        <v>56724528.2</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-3436894.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="M68" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="N68" t="n">
+        <v>350217736.01</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-12.0616</v>
+      </c>
+      <c r="F69" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>275449700</v>
+      </c>
+      <c r="H69" t="n">
+        <v>26451304.62</v>
+      </c>
+      <c r="I69" t="n">
+        <v>30598199.77</v>
+      </c>
+      <c r="J69" t="n">
+        <v>57049504.39</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4146895.15</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M69" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="N69" t="n">
+        <v>557739000</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-12.0616</v>
+      </c>
+      <c r="F70" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1271770900</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1271770915.23</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1271770915.23</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1271770915.23</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>100</v>
+      </c>
+      <c r="N70" t="n">
+        <v>557739000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>北交所股票连续10个交易日内日收盘价涨跌幅偏离值累计达到+150%(-60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>920298.BJ</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>腾信精密</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.0228</v>
-      </c>
-      <c r="F62" t="n">
-        <v>34.83</v>
-      </c>
-      <c r="G62" t="n">
-        <v>479212400</v>
-      </c>
-      <c r="H62" t="n">
-        <v>89651649.84999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>55847212.29</v>
-      </c>
-      <c r="J62" t="n">
-        <v>145498862.14</v>
-      </c>
-      <c r="K62" t="n">
-        <v>-33804437.56</v>
-      </c>
-      <c r="L62" t="n">
-        <v>-7.05</v>
-      </c>
-      <c r="M62" t="n">
-        <v>30.36</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1344870000</v>
-      </c>
-      <c r="O62" t="inlineStr">
+      <c r="D71" t="n">
+        <v>79.37</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-9.7042</v>
+      </c>
+      <c r="F71" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="G71" t="n">
+        <v>459834600</v>
+      </c>
+      <c r="H71" t="n">
+        <v>72858123.16</v>
+      </c>
+      <c r="I71" t="n">
+        <v>68529224.53</v>
+      </c>
+      <c r="J71" t="n">
+        <v>141387347.69</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-4328898.63</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M71" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1214361000</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>29.9771</v>
+      </c>
+      <c r="F72" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="G72" t="n">
+        <v>162736700</v>
+      </c>
+      <c r="H72" t="n">
+        <v>17152750.47</v>
+      </c>
+      <c r="I72" t="n">
+        <v>42138487.23</v>
+      </c>
+      <c r="J72" t="n">
+        <v>59291237.7</v>
+      </c>
+      <c r="K72" t="n">
+        <v>24985736.76</v>
+      </c>
+      <c r="L72" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M72" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="N72" t="n">
+        <v>568568056.8</v>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>当日换手率达到20%的前5只股票</t>
         </is>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4440 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000002.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>万科A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.4118</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5158052404</v>
+      </c>
+      <c r="H2" t="n">
+        <v>617580196.4299999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>688964755.91</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1306544952.34</v>
+      </c>
+      <c r="K2" t="n">
+        <v>71384559.48</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>41386382036.04</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000011.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>深物业A</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.973000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>971267913</v>
+      </c>
+      <c r="H3" t="n">
+        <v>163466249.68</v>
+      </c>
+      <c r="I3" t="n">
+        <v>107516407.36</v>
+      </c>
+      <c r="J3" t="n">
+        <v>270982657.04</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-55949842.32</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6653636899.62</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000504.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.0089</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="G4" t="n">
+        <v>860444296</v>
+      </c>
+      <c r="H4" t="n">
+        <v>129992238.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>211621186</v>
+      </c>
+      <c r="J4" t="n">
+        <v>341613424.58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>81628947.42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4087700183.16</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.5957</v>
+      </c>
+      <c r="F5" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2736655375</v>
+      </c>
+      <c r="H5" t="n">
+        <v>294244882.36</v>
+      </c>
+      <c r="I5" t="n">
+        <v>465305276.36</v>
+      </c>
+      <c r="J5" t="n">
+        <v>759550158.72</v>
+      </c>
+      <c r="K5" t="n">
+        <v>171060394</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8667946040.299999</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000678.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.982900000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1074985690</v>
+      </c>
+      <c r="H6" t="n">
+        <v>118352378.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>256972357.22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>375324735.42</v>
+      </c>
+      <c r="K6" t="n">
+        <v>138619979.02</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5924396063.33</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000678.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.982900000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1185742093</v>
+      </c>
+      <c r="H7" t="n">
+        <v>123400182.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>269549089.22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>392949271.42</v>
+      </c>
+      <c r="K7" t="n">
+        <v>146148907.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5924396063.33</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000850.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华茂股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.9352</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>671892787</v>
+      </c>
+      <c r="H8" t="n">
+        <v>106000652.02</v>
+      </c>
+      <c r="I8" t="n">
+        <v>38378519</v>
+      </c>
+      <c r="J8" t="n">
+        <v>144379171.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-67622133.02</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-10.06</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3933871160.43</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0034</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G9" t="n">
+        <v>719082131</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60506863.23</v>
+      </c>
+      <c r="I9" t="n">
+        <v>41328350</v>
+      </c>
+      <c r="J9" t="n">
+        <v>101835213.23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-19178513.23</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6462171689.82</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001234.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>泰慕士</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10.0105</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="G10" t="n">
+        <v>289864061</v>
+      </c>
+      <c r="H10" t="n">
+        <v>44538186.92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19325445.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63863632.72</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-25212741.12</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2361770700</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001234.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>泰慕士</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-10.0105</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1216089983</v>
+      </c>
+      <c r="H11" t="n">
+        <v>210708278.42</v>
+      </c>
+      <c r="I11" t="n">
+        <v>139426309.92</v>
+      </c>
+      <c r="J11" t="n">
+        <v>350134588.34</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-71281968.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="M11" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2361770700</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001246.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>力勤资源</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>206.5944</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8345390509</v>
+      </c>
+      <c r="H12" t="n">
+        <v>241763545.01</v>
+      </c>
+      <c r="I12" t="n">
+        <v>745890681.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>987654226.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>504127136.94</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10240386701.66</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002058.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0218</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G13" t="n">
+        <v>143179917</v>
+      </c>
+      <c r="H13" t="n">
+        <v>34930199.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>39932092</v>
+      </c>
+      <c r="J13" t="n">
+        <v>74862291.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5001892.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="M13" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2895989806.4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-8.7372</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2339128122</v>
+      </c>
+      <c r="H14" t="n">
+        <v>301276658.14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>321307550.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>622584208.34</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20030892.06</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9682327200</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0415</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G15" t="n">
+        <v>648830907</v>
+      </c>
+      <c r="H15" t="n">
+        <v>131924712.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>168633288.85</v>
+      </c>
+      <c r="J15" t="n">
+        <v>300558001.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36708576.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="M15" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6361818396.18</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002172.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.0929</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1026415505</v>
+      </c>
+      <c r="H16" t="n">
+        <v>219447165.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>76335016.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>295782181.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-143112148.55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-13.94</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4154714163.9</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002244.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>滨江集团</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.1882</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1689372530</v>
+      </c>
+      <c r="H17" t="n">
+        <v>249748802.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>283019132.04</v>
+      </c>
+      <c r="J17" t="n">
+        <v>532767934.99</v>
+      </c>
+      <c r="K17" t="n">
+        <v>33270329.09</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M17" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="N17" t="n">
+        <v>27961550307.6</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002244.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>滨江集团</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7.1882</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2879114526</v>
+      </c>
+      <c r="H18" t="n">
+        <v>368004287.94</v>
+      </c>
+      <c r="I18" t="n">
+        <v>560659203.92</v>
+      </c>
+      <c r="J18" t="n">
+        <v>928663491.86</v>
+      </c>
+      <c r="K18" t="n">
+        <v>192654915.98</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27961550307.6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002388.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>新亚制程</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.0363</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1208206397</v>
+      </c>
+      <c r="H19" t="n">
+        <v>225563204.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>266659127.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>492222332.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>41095923.54</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4606633804.5</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002494.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>华斯股份</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-5.0752</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>362348650</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76212831.94</v>
+      </c>
+      <c r="I20" t="n">
+        <v>65580097</v>
+      </c>
+      <c r="J20" t="n">
+        <v>141792928.94</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-10632734.94</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="M20" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1448190711.9</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002640.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>跨境通</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.7614</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1400792199</v>
+      </c>
+      <c r="H21" t="n">
+        <v>116836491.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>163494451</v>
+      </c>
+      <c r="J21" t="n">
+        <v>280330942.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>46657959.99</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6053703559.8</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002717.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>*ST岭南</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-10.1449</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8377688</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3439574</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1651246</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5090820</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1788328</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-21.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1109143956.92</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002717.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>*ST岭南</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10.1449</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>100851841</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25810852.11</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10794186</v>
+      </c>
+      <c r="J23" t="n">
+        <v>36605038.11</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-15016666.11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-14.89</v>
+      </c>
+      <c r="M23" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1109143956.92</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002827.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>高争民爆</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>59</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.9001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3609405491</v>
+      </c>
+      <c r="H24" t="n">
+        <v>746793362.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>549068989.21</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1295862351.41</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-197724372.99</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-5.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16283933625</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.026</v>
+      </c>
+      <c r="F25" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="G25" t="n">
+        <v>577077481</v>
+      </c>
+      <c r="H25" t="n">
+        <v>95473984</v>
+      </c>
+      <c r="I25" t="n">
+        <v>62024452</v>
+      </c>
+      <c r="J25" t="n">
+        <v>157498436</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-33449532</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3105694308.6</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10.026</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="G26" t="n">
+        <v>766120628</v>
+      </c>
+      <c r="H26" t="n">
+        <v>106408694</v>
+      </c>
+      <c r="I26" t="n">
+        <v>107396562</v>
+      </c>
+      <c r="J26" t="n">
+        <v>213805256</v>
+      </c>
+      <c r="K26" t="n">
+        <v>987868</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M26" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3105694308.6</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002962.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>五方光电</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1800074650</v>
+      </c>
+      <c r="H27" t="n">
+        <v>218631746.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>184163629.04</v>
+      </c>
+      <c r="J27" t="n">
+        <v>402795375.14</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-34468117.06</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="M27" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3383018354.1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300893.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>松原安全</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19.9841</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>323471626</v>
+      </c>
+      <c r="H28" t="n">
+        <v>86311631.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>91185273.88</v>
+      </c>
+      <c r="J28" t="n">
+        <v>177496905.08</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4873642.68</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3808115755.72</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301030.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>*ST仕净</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-15.8954</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>127062776</v>
+      </c>
+      <c r="H29" t="n">
+        <v>21423525.16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14225581.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35649106.56</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-7197943.76</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="M29" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>844801867.8</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-72.5076</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>28660561</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2020803</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5016932</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7037735</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2996129</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="M30" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="N30" t="n">
+        <v>69302094.68000001</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301190.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>善水科技</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20.0067</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v>510373314</v>
+      </c>
+      <c r="H31" t="n">
+        <v>82562040.59</v>
+      </c>
+      <c r="I31" t="n">
+        <v>107202761.53</v>
+      </c>
+      <c r="J31" t="n">
+        <v>189764802.12</v>
+      </c>
+      <c r="K31" t="n">
+        <v>24640720.94</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="M31" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="N31" t="n">
+        <v>6534014220</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301218.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>华是科技</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.8445</v>
+      </c>
+      <c r="F32" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1608252150</v>
+      </c>
+      <c r="H32" t="n">
+        <v>235247349.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>397856995.68</v>
+      </c>
+      <c r="J32" t="n">
+        <v>633104345.33</v>
+      </c>
+      <c r="K32" t="n">
+        <v>162609646.03</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="M32" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5001295479.75</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301218.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>华是科技</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="E33" t="n">
+        <v>15.8445</v>
+      </c>
+      <c r="F33" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2869820960</v>
+      </c>
+      <c r="H33" t="n">
+        <v>418729818.41</v>
+      </c>
+      <c r="I33" t="n">
+        <v>702832921.37</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1121562739.78</v>
+      </c>
+      <c r="K33" t="n">
+        <v>284103102.96</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5001295479.75</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.9183</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="G34" t="n">
+        <v>461965585</v>
+      </c>
+      <c r="H34" t="n">
+        <v>105609526.76</v>
+      </c>
+      <c r="I34" t="n">
+        <v>38179937.67</v>
+      </c>
+      <c r="J34" t="n">
+        <v>143789464.43</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-67429589.09</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="M34" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1138820858.28</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.9183</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="G35" t="n">
+        <v>605485251</v>
+      </c>
+      <c r="H35" t="n">
+        <v>127439497.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>107767971.84</v>
+      </c>
+      <c r="J35" t="n">
+        <v>235207469.59</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-19671525.91</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="M35" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1138820858.28</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.3194</v>
+      </c>
+      <c r="F36" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1030116710</v>
+      </c>
+      <c r="H36" t="n">
+        <v>115080061.12</v>
+      </c>
+      <c r="I36" t="n">
+        <v>81738696.09999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>196818757.22</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-33341365.02</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="M36" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2482376375.15</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301686.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>中塑股份</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>165.82</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-13.6624</v>
+      </c>
+      <c r="F37" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>715793859</v>
+      </c>
+      <c r="H37" t="n">
+        <v>59664794.77</v>
+      </c>
+      <c r="I37" t="n">
+        <v>46676772.76</v>
+      </c>
+      <c r="J37" t="n">
+        <v>106341567.53</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-12988022.01</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="M37" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1448115511.74</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>73.43000000000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-5.2638</v>
+      </c>
+      <c r="F38" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1715915881</v>
+      </c>
+      <c r="H38" t="n">
+        <v>193319198.31</v>
+      </c>
+      <c r="I38" t="n">
+        <v>191394956.02</v>
+      </c>
+      <c r="J38" t="n">
+        <v>384714154.33</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1924242.29</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4226737420.36</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>301699.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>洛轴股份</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1320482598</v>
+      </c>
+      <c r="H39" t="n">
+        <v>208668812.31</v>
+      </c>
+      <c r="I39" t="n">
+        <v>162345228.23</v>
+      </c>
+      <c r="J39" t="n">
+        <v>371014040.54</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-46323584.08</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="M39" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2640611514.24</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600059.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>古越龙山</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0448</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1093331572</v>
+      </c>
+      <c r="H40" t="n">
+        <v>108762251.95</v>
+      </c>
+      <c r="I40" t="n">
+        <v>194966568.43</v>
+      </c>
+      <c r="J40" t="n">
+        <v>303728820.38</v>
+      </c>
+      <c r="K40" t="n">
+        <v>86204316.48</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="M40" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="N40" t="n">
+        <v>11184625407.51</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.6467</v>
+      </c>
+      <c r="F41" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2960624365</v>
+      </c>
+      <c r="H41" t="n">
+        <v>330928758.65</v>
+      </c>
+      <c r="I41" t="n">
+        <v>201658604.41</v>
+      </c>
+      <c r="J41" t="n">
+        <v>532587363.06</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-129270154.24</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="M41" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8433031484.52</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600156.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>华升股份</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-10.0367</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="G42" t="n">
+        <v>314199666</v>
+      </c>
+      <c r="H42" t="n">
+        <v>47457354.35</v>
+      </c>
+      <c r="I42" t="n">
+        <v>18928892</v>
+      </c>
+      <c r="J42" t="n">
+        <v>66386246.35</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-28528462.35</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="M42" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2955513659.7</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600383.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金地集团</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E43" t="n">
+        <v>7.451</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1258907881</v>
+      </c>
+      <c r="H43" t="n">
+        <v>139859655.38</v>
+      </c>
+      <c r="I43" t="n">
+        <v>186450220.68</v>
+      </c>
+      <c r="J43" t="n">
+        <v>326309876.06</v>
+      </c>
+      <c r="K43" t="n">
+        <v>46590565.3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="N43" t="n">
+        <v>12369958987.28</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600418.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5.4916</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="G44" t="n">
+        <v>17701036379</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1994801784.83</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1956273167.94</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3951074952.77</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-38528616.89</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M44" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="N44" t="n">
+        <v>61922275016.65</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600657.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>信达地产</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5.0296</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G45" t="n">
+        <v>695869362</v>
+      </c>
+      <c r="H45" t="n">
+        <v>90396715.58</v>
+      </c>
+      <c r="I45" t="n">
+        <v>105109780.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>195506495.78</v>
+      </c>
+      <c r="K45" t="n">
+        <v>14713064.62</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M45" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10124169012.25</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.2355</v>
+      </c>
+      <c r="F46" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1847155692</v>
+      </c>
+      <c r="H46" t="n">
+        <v>201622643</v>
+      </c>
+      <c r="I46" t="n">
+        <v>135802878</v>
+      </c>
+      <c r="J46" t="n">
+        <v>337425521</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-65819765</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="M46" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5041419494.85</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4.3228</v>
+      </c>
+      <c r="F47" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="G47" t="n">
+        <v>761625731</v>
+      </c>
+      <c r="H47" t="n">
+        <v>74643242.97</v>
+      </c>
+      <c r="I47" t="n">
+        <v>80919909.94</v>
+      </c>
+      <c r="J47" t="n">
+        <v>155563152.91</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6276666.97</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M47" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3317718416</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600825.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.9894</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G48" t="n">
+        <v>292030560</v>
+      </c>
+      <c r="H48" t="n">
+        <v>37033644</v>
+      </c>
+      <c r="I48" t="n">
+        <v>129076623.47</v>
+      </c>
+      <c r="J48" t="n">
+        <v>166110267.47</v>
+      </c>
+      <c r="K48" t="n">
+        <v>92042979.47</v>
+      </c>
+      <c r="L48" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="M48" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="N48" t="n">
+        <v>10814589247.5</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-8.0985</v>
+      </c>
+      <c r="F49" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1837817144</v>
+      </c>
+      <c r="H49" t="n">
+        <v>181151229.54</v>
+      </c>
+      <c r="I49" t="n">
+        <v>137874551.7</v>
+      </c>
+      <c r="J49" t="n">
+        <v>319025781.24</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-43276677.84</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="M49" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4888427663.3</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603185.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>弘元绿能</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0218</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G50" t="n">
+        <v>245142444</v>
+      </c>
+      <c r="H50" t="n">
+        <v>56866895.74</v>
+      </c>
+      <c r="I50" t="n">
+        <v>91243438.23</v>
+      </c>
+      <c r="J50" t="n">
+        <v>148110333.97</v>
+      </c>
+      <c r="K50" t="n">
+        <v>34376542.49</v>
+      </c>
+      <c r="L50" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="M50" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10287186360.3</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603188.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>亚邦股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9.9796</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="G51" t="n">
+        <v>289968645</v>
+      </c>
+      <c r="H51" t="n">
+        <v>48724506</v>
+      </c>
+      <c r="I51" t="n">
+        <v>69373194</v>
+      </c>
+      <c r="J51" t="n">
+        <v>118097700</v>
+      </c>
+      <c r="K51" t="n">
+        <v>20648688</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M51" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3078918000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603200.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0074</v>
+      </c>
+      <c r="F52" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1214152011</v>
+      </c>
+      <c r="H52" t="n">
+        <v>98052652.09999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>169278541.38</v>
+      </c>
+      <c r="J52" t="n">
+        <v>267331193.48</v>
+      </c>
+      <c r="K52" t="n">
+        <v>71225889.28</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M52" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7850979808.22</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-8.491199999999999</v>
+      </c>
+      <c r="F53" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="G53" t="n">
+        <v>912497116</v>
+      </c>
+      <c r="H53" t="n">
+        <v>67738424.42</v>
+      </c>
+      <c r="I53" t="n">
+        <v>72190366.91</v>
+      </c>
+      <c r="J53" t="n">
+        <v>139928791.33</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4451942.49</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M53" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4952857230</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-8.491199999999999</v>
+      </c>
+      <c r="F54" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2187751413</v>
+      </c>
+      <c r="H54" t="n">
+        <v>121792566</v>
+      </c>
+      <c r="I54" t="n">
+        <v>139762697.91</v>
+      </c>
+      <c r="J54" t="n">
+        <v>261555263.91</v>
+      </c>
+      <c r="K54" t="n">
+        <v>17970131.91</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4952857230</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603248.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>锡华科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-4.1295</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="G55" t="n">
+        <v>365479429</v>
+      </c>
+      <c r="H55" t="n">
+        <v>22086964.48</v>
+      </c>
+      <c r="I55" t="n">
+        <v>24587422.8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>46674387.28</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2500458.32</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M55" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1460846148.93</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603396.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>金辰股份</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-5.0454</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1171989593</v>
+      </c>
+      <c r="H56" t="n">
+        <v>178104337.14</v>
+      </c>
+      <c r="I56" t="n">
+        <v>182357665.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>360462002.54</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4253328.26</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M56" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4640670513</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603400.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>华之杰</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>53</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-3.0547</v>
+      </c>
+      <c r="F57" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="G57" t="n">
+        <v>603957408</v>
+      </c>
+      <c r="H57" t="n">
+        <v>116474870.78</v>
+      </c>
+      <c r="I57" t="n">
+        <v>89000265.7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>205475136.48</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-27474605.08</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="M57" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1920193975</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603739.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>蔚蓝生物</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0313</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G58" t="n">
+        <v>127913740</v>
+      </c>
+      <c r="H58" t="n">
+        <v>18506698</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23471474.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>41978172.6</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4964776.6</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3552525278.64</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603797.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>联泰环保</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-10.0746</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G59" t="n">
+        <v>159874743</v>
+      </c>
+      <c r="H59" t="n">
+        <v>22407007.48</v>
+      </c>
+      <c r="I59" t="n">
+        <v>25434885</v>
+      </c>
+      <c r="J59" t="n">
+        <v>47841892.48</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3027877.52</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M59" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2779237015.8</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>605011.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>杭州热电</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10.0229</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G60" t="n">
+        <v>231188954</v>
+      </c>
+      <c r="H60" t="n">
+        <v>33148129.69</v>
+      </c>
+      <c r="I60" t="n">
+        <v>48590613.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>81738743.39</v>
+      </c>
+      <c r="K60" t="n">
+        <v>15442484.01</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="M60" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7685921000</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G61" t="n">
+        <v>731314166</v>
+      </c>
+      <c r="H61" t="n">
+        <v>92697732.86</v>
+      </c>
+      <c r="I61" t="n">
+        <v>85479504.68000001</v>
+      </c>
+      <c r="J61" t="n">
+        <v>178177237.54</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-7218228.18</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="M61" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="N61" t="n">
+        <v>7666503436.8</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>605162.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>新中港</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-10.0255</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G62" t="n">
+        <v>363951233</v>
+      </c>
+      <c r="H62" t="n">
+        <v>27665456.65</v>
+      </c>
+      <c r="I62" t="n">
+        <v>18916329</v>
+      </c>
+      <c r="J62" t="n">
+        <v>46581785.65</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-8749127.65</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M62" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4689742433.49</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>605258.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>协和电子</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-9.9977</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G63" t="n">
+        <v>351757940</v>
+      </c>
+      <c r="H63" t="n">
+        <v>58241994</v>
+      </c>
+      <c r="I63" t="n">
+        <v>77944561</v>
+      </c>
+      <c r="J63" t="n">
+        <v>136186555</v>
+      </c>
+      <c r="K63" t="n">
+        <v>19702567</v>
+      </c>
+      <c r="L63" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M63" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3485680000</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>605303.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>园林股份</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.0192</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4940984</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1089080</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4940984</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6030064</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3851904</v>
+      </c>
+      <c r="L64" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="M64" t="n">
+        <v>122.04</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4621064113.28</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>605303.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>园林股份</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.0192</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G65" t="n">
+        <v>11549869</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1684185</v>
+      </c>
+      <c r="I65" t="n">
+        <v>11388871</v>
+      </c>
+      <c r="J65" t="n">
+        <v>13073056</v>
+      </c>
+      <c r="K65" t="n">
+        <v>9704686</v>
+      </c>
+      <c r="L65" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="M65" t="n">
+        <v>113.19</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4621064113.28</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>605388.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>均瑶健康</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9.9702</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G66" t="n">
+        <v>214211034</v>
+      </c>
+      <c r="H66" t="n">
+        <v>35142142</v>
+      </c>
+      <c r="I66" t="n">
+        <v>46052169</v>
+      </c>
+      <c r="J66" t="n">
+        <v>81194311</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10910027</v>
+      </c>
+      <c r="L66" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="M66" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4437576760</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>160.39</v>
+      </c>
+      <c r="E67" t="n">
+        <v>13.4701</v>
+      </c>
+      <c r="F67" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4152432500</v>
+      </c>
+      <c r="H67" t="n">
+        <v>345906661.61</v>
+      </c>
+      <c r="I67" t="n">
+        <v>500648881.57</v>
+      </c>
+      <c r="J67" t="n">
+        <v>846555543.1799999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>154742219.96</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="M67" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="N67" t="n">
+        <v>11214060286.67</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>688137.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>160.39</v>
+      </c>
+      <c r="E68" t="n">
+        <v>13.4701</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G68" t="n">
+        <v>11697284100</v>
+      </c>
+      <c r="H68" t="n">
+        <v>11697284200</v>
+      </c>
+      <c r="I68" t="n">
+        <v>11697284100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>11697284100</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>100</v>
+      </c>
+      <c r="N68" t="n">
+        <v>11214060286.67</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>688185.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>康希诺</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="E69" t="n">
+        <v>20.0047</v>
+      </c>
+      <c r="F69" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1065144300</v>
+      </c>
+      <c r="H69" t="n">
+        <v>155932921.71</v>
+      </c>
+      <c r="I69" t="n">
+        <v>202059786.95</v>
+      </c>
+      <c r="J69" t="n">
+        <v>357992708.66</v>
+      </c>
+      <c r="K69" t="n">
+        <v>46126865.24</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M69" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="N69" t="n">
+        <v>11739234558.64</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>688185.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>康希诺</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20.0047</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2765387200</v>
+      </c>
+      <c r="H70" t="n">
+        <v>333942031.09</v>
+      </c>
+      <c r="I70" t="n">
+        <v>420081838.81</v>
+      </c>
+      <c r="J70" t="n">
+        <v>754023869.9</v>
+      </c>
+      <c r="K70" t="n">
+        <v>86139807.72</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M70" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N70" t="n">
+        <v>11739234558.64</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>688265.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>南模生物</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="E71" t="n">
+        <v>19.8672</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>412269900</v>
+      </c>
+      <c r="H71" t="n">
+        <v>59002303.13</v>
+      </c>
+      <c r="I71" t="n">
+        <v>73467526.61</v>
+      </c>
+      <c r="J71" t="n">
+        <v>132469829.74</v>
+      </c>
+      <c r="K71" t="n">
+        <v>14465223.48</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M71" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5066069074.74</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>688265.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>南模生物</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="E72" t="n">
+        <v>19.8672</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G72" t="n">
+        <v>790072500</v>
+      </c>
+      <c r="H72" t="n">
+        <v>139589652.73</v>
+      </c>
+      <c r="I72" t="n">
+        <v>136580679.64</v>
+      </c>
+      <c r="J72" t="n">
+        <v>276170332.37</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-3008973.09</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="N72" t="n">
+        <v>5066069074.74</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>688806.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>泰诺麦博</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="E73" t="n">
+        <v>19.9922</v>
+      </c>
+      <c r="F73" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="G73" t="n">
+        <v>350550300</v>
+      </c>
+      <c r="H73" t="n">
+        <v>36771999.63</v>
+      </c>
+      <c r="I73" t="n">
+        <v>69724300.81999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>106496300.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>32952301.19</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M73" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1564956992.2</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>688837.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>信诺维</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>13.2768</v>
+      </c>
+      <c r="F74" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="G74" t="n">
+        <v>856739000</v>
+      </c>
+      <c r="H74" t="n">
+        <v>88029390.53</v>
+      </c>
+      <c r="I74" t="n">
+        <v>83176071.28</v>
+      </c>
+      <c r="J74" t="n">
+        <v>171205461.81</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-4853319.25</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M74" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2400542908.4</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>920025.BJ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>凯达重工</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-5.6647</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>180966600</v>
+      </c>
+      <c r="H75" t="n">
+        <v>26152177.2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>26881593.38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>53033770.58</v>
+      </c>
+      <c r="K75" t="n">
+        <v>729416.1800000001</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>636990000</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>920201.BJ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>百瑞吉</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-8.5814</v>
+      </c>
+      <c r="F76" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>120725900</v>
+      </c>
+      <c r="H76" t="n">
+        <v>18309507.81</v>
+      </c>
+      <c r="I76" t="n">
+        <v>17336184.7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>35645692.51</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-973323.11</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M76" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="N76" t="n">
+        <v>320164291.36</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>920201.BJ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>百瑞吉</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-8.5814</v>
+      </c>
+      <c r="F77" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>538731900</v>
+      </c>
+      <c r="H77" t="n">
+        <v>47756180.97</v>
+      </c>
+      <c r="I77" t="n">
+        <v>70178276.73999999</v>
+      </c>
+      <c r="J77" t="n">
+        <v>117934457.71</v>
+      </c>
+      <c r="K77" t="n">
+        <v>22422095.77</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M77" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="N77" t="n">
+        <v>320164291.36</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>920202.BJ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>安达股份</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-29.9694</v>
+      </c>
+      <c r="F78" t="n">
+        <v>66.59</v>
+      </c>
+      <c r="G78" t="n">
+        <v>318422400</v>
+      </c>
+      <c r="H78" t="n">
+        <v>28697285.78</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33807128.15</v>
+      </c>
+      <c r="J78" t="n">
+        <v>62504413.93</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5109842.37</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="N78" t="n">
+        <v>436016000</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>920229.BJ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>世纪数码</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-6.1661</v>
+      </c>
+      <c r="F79" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="G79" t="n">
+        <v>178223700</v>
+      </c>
+      <c r="H79" t="n">
+        <v>22567063.55</v>
+      </c>
+      <c r="I79" t="n">
+        <v>24166002.68</v>
+      </c>
+      <c r="J79" t="n">
+        <v>46733066.23</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1598939.13</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="N79" t="n">
+        <v>523348500</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="F80" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="G80" t="n">
+        <v>242030900</v>
+      </c>
+      <c r="H80" t="n">
+        <v>51081752.99</v>
+      </c>
+      <c r="I80" t="n">
+        <v>21570398.4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>72652151.39</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-29511354.59</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="M80" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="N80" t="n">
+        <v>572572057.2</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="margin" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6164,4 +6165,98 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>exchange_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rzye</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rzmre</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rzche</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>rqye</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rqmcl</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rzrqye</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rqyl</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SSE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1296520652053</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62006897126</v>
+      </c>
+      <c r="E2" t="n">
+        <v>84893467937</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18892593376</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55369387</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1315413245429</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3220216902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="margin" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5561</v>
+        <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>2567</v>
+        <v>1698</v>
       </c>
       <c r="D2" t="n">
-        <v>2824</v>
+        <v>3748</v>
       </c>
       <c r="E2" t="n">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>14500.77</v>
+        <v>16942.91</v>
       </c>
     </row>
   </sheetData>
@@ -535,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3842.1946</v>
+        <v>3811.9043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.31</v>
+        <v>-0.79</v>
       </c>
       <c r="F2" t="n">
-        <v>6793.99</v>
+        <v>8111.83</v>
       </c>
     </row>
     <row r="3">
@@ -561,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12887.6198</v>
+        <v>12620.897</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.11</v>
+        <v>-2.07</v>
       </c>
       <c r="F3" t="n">
-        <v>3572.81</v>
+        <v>4411.05</v>
       </c>
     </row>
     <row r="4">
@@ -587,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3135.2767</v>
+        <v>3036.6573</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.23</v>
+        <v>-3.15</v>
       </c>
       <c r="F4" t="n">
-        <v>1378.5</v>
+        <v>1760.38</v>
       </c>
     </row>
     <row r="5">
@@ -613,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4357.6155</v>
+        <v>4310.2765</v>
       </c>
       <c r="E5" t="n">
-        <v>0.29</v>
+        <v>-1.09</v>
       </c>
       <c r="F5" t="n">
-        <v>3564.92</v>
+        <v>4462.08</v>
       </c>
     </row>
     <row r="6">
@@ -639,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1530.0057</v>
+        <v>1456.3239</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.51</v>
+        <v>-4.82</v>
       </c>
       <c r="F6" t="n">
-        <v>718.79</v>
+        <v>823.98</v>
       </c>
     </row>
     <row r="7">
@@ -665,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7298.8208</v>
+        <v>7138.584</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.36</v>
+        <v>-2.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2744.99</v>
+        <v>3240.05</v>
       </c>
     </row>
   </sheetData>
@@ -707,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18524.99</v>
+        <v>18365.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18365.14</v>
+        <v>20929.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20929.06</v>
+        <v>20481.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20481.34</v>
+        <v>21536.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21536.52</v>
+        <v>17831.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17831.28</v>
+        <v>16691.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17167.12</v>
+        <v>14215.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14215.96</v>
+        <v>14500.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14500.77</v>
+        <v>16942.91</v>
       </c>
     </row>
   </sheetData>
@@ -878,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001246.SZ</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>13.78</v>
       </c>
       <c r="D2" t="n">
-        <v>84.84999999999999</v>
+        <v>17.83</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>13.53</v>
       </c>
       <c r="F2" t="n">
-        <v>65.09</v>
+        <v>17.83</v>
       </c>
       <c r="G2" t="n">
-        <v>21.23</v>
+        <v>13.72</v>
       </c>
       <c r="H2" t="n">
-        <v>43.86</v>
+        <v>4.11</v>
       </c>
       <c r="I2" t="n">
-        <v>206.5944</v>
+        <v>29.9563</v>
       </c>
       <c r="J2" t="n">
-        <v>1178851.62</v>
+        <v>126131.57</v>
       </c>
       <c r="K2" t="n">
-        <v>8345390.50896</v>
+        <v>213939.18755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301190.SZ</t>
+          <t>300522.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33.2</v>
+        <v>14.49</v>
       </c>
       <c r="D3" t="n">
-        <v>35.93</v>
+        <v>16.56</v>
       </c>
       <c r="E3" t="n">
-        <v>33.2</v>
+        <v>14.29</v>
       </c>
       <c r="F3" t="n">
-        <v>35.93</v>
+        <v>16.56</v>
       </c>
       <c r="G3" t="n">
-        <v>29.94</v>
+        <v>13.8</v>
       </c>
       <c r="H3" t="n">
-        <v>5.99</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>20.0067</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>144661.04</v>
+        <v>261136.21</v>
       </c>
       <c r="K3" t="n">
-        <v>510373.31364</v>
+        <v>419527.37476</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688185.SH</t>
+          <t>688196.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.44</v>
+        <v>30.35</v>
       </c>
       <c r="D4" t="n">
-        <v>102.64</v>
+        <v>36.12</v>
       </c>
       <c r="E4" t="n">
-        <v>85.67</v>
+        <v>30.11</v>
       </c>
       <c r="F4" t="n">
-        <v>102.64</v>
+        <v>36.12</v>
       </c>
       <c r="G4" t="n">
-        <v>85.53</v>
+        <v>30.1</v>
       </c>
       <c r="H4" t="n">
-        <v>17.11</v>
+        <v>6.02</v>
       </c>
       <c r="I4" t="n">
-        <v>20.0047</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>106617.44</v>
+        <v>63994.43</v>
       </c>
       <c r="K4" t="n">
-        <v>1065144.349</v>
+        <v>217545.128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688806.SH</t>
+          <t>301697.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25.35</v>
+        <v>26.81</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67</v>
+        <v>31.51</v>
       </c>
       <c r="E5" t="n">
-        <v>25.35</v>
+        <v>26.81</v>
       </c>
       <c r="F5" t="n">
-        <v>30.67</v>
+        <v>31.51</v>
       </c>
       <c r="G5" t="n">
-        <v>25.56</v>
+        <v>26.26</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9922</v>
+        <v>19.9924</v>
       </c>
       <c r="J5" t="n">
-        <v>120375.04</v>
+        <v>203348.6</v>
       </c>
       <c r="K5" t="n">
-        <v>350550.251</v>
+        <v>620816.46738</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300893.SZ</t>
+          <t>300530.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12.76</v>
+        <v>19.92</v>
       </c>
       <c r="D6" t="n">
-        <v>15.13</v>
+        <v>24.08</v>
       </c>
       <c r="E6" t="n">
-        <v>12.76</v>
+        <v>19.75</v>
       </c>
       <c r="F6" t="n">
-        <v>15.13</v>
+        <v>24.08</v>
       </c>
       <c r="G6" t="n">
-        <v>12.61</v>
+        <v>20.07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>4.01</v>
       </c>
       <c r="I6" t="n">
-        <v>19.9841</v>
+        <v>19.9801</v>
       </c>
       <c r="J6" t="n">
-        <v>225226.48</v>
+        <v>177258.63</v>
       </c>
       <c r="K6" t="n">
-        <v>323471.62567</v>
+        <v>400319.98489</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688265.SH</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>54.99</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>65.05</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>53.82</v>
       </c>
       <c r="F7" t="n">
-        <v>64.98</v>
+        <v>67.81</v>
       </c>
       <c r="G7" t="n">
-        <v>54.21</v>
+        <v>56.52</v>
       </c>
       <c r="H7" t="n">
-        <v>10.77</v>
+        <v>11.29</v>
       </c>
       <c r="I7" t="n">
-        <v>19.8672</v>
+        <v>19.9752</v>
       </c>
       <c r="J7" t="n">
-        <v>67113.32000000001</v>
+        <v>97198.28</v>
       </c>
       <c r="K7" t="n">
-        <v>412269.918</v>
+        <v>597216.21584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>301218.SZ</t>
+          <t>300619.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>61.81</v>
+        <v>24.45</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>28.75</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>24.07</v>
       </c>
       <c r="F8" t="n">
-        <v>69.75</v>
+        <v>28.17</v>
       </c>
       <c r="G8" t="n">
-        <v>60.21</v>
+        <v>23.96</v>
       </c>
       <c r="H8" t="n">
-        <v>9.539999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="I8" t="n">
-        <v>15.8445</v>
+        <v>17.571</v>
       </c>
       <c r="J8" t="n">
-        <v>241981.44</v>
+        <v>253409.77</v>
       </c>
       <c r="K8" t="n">
-        <v>1608252.15024</v>
+        <v>698192.8372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>920344.BJ</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.11</v>
+        <v>27.99</v>
       </c>
       <c r="D9" t="n">
-        <v>26.46</v>
+        <v>35.33</v>
       </c>
       <c r="E9" t="n">
-        <v>20.88</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>24.35</v>
+        <v>33.13</v>
       </c>
       <c r="G9" t="n">
-        <v>21.03</v>
+        <v>28.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.32</v>
+        <v>4.53</v>
       </c>
       <c r="I9" t="n">
-        <v>15.787</v>
+        <v>15.8392</v>
       </c>
       <c r="J9" t="n">
-        <v>126310.57</v>
+        <v>81795.67999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>308887.95876</v>
+        <v>258518.21368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>301080.SZ</t>
+          <t>920252.BJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>120.51</v>
+        <v>15.03</v>
       </c>
       <c r="D10" t="n">
-        <v>141.07</v>
+        <v>17.44</v>
       </c>
       <c r="E10" t="n">
-        <v>120.47</v>
+        <v>14.7</v>
       </c>
       <c r="F10" t="n">
-        <v>141.07</v>
+        <v>16.83</v>
       </c>
       <c r="G10" t="n">
-        <v>123</v>
+        <v>14.73</v>
       </c>
       <c r="H10" t="n">
-        <v>18.07</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>14.6911</v>
+        <v>14.2566</v>
       </c>
       <c r="J10" t="n">
-        <v>209411.25</v>
+        <v>95834.02</v>
       </c>
       <c r="K10" t="n">
-        <v>2810188.9589</v>
+        <v>157146.85282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688137.SH</t>
+          <t>301395.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>135.7</v>
+        <v>11.66</v>
       </c>
       <c r="D11" t="n">
-        <v>168.03</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="n">
-        <v>132.5</v>
+        <v>11.54</v>
       </c>
       <c r="F11" t="n">
-        <v>160.39</v>
+        <v>13.09</v>
       </c>
       <c r="G11" t="n">
-        <v>141.35</v>
+        <v>11.51</v>
       </c>
       <c r="H11" t="n">
-        <v>19.04</v>
+        <v>1.58</v>
       </c>
       <c r="I11" t="n">
-        <v>13.4701</v>
+        <v>13.7272</v>
       </c>
       <c r="J11" t="n">
-        <v>104284.39</v>
+        <v>143617.15</v>
       </c>
       <c r="K11" t="n">
-        <v>1584774.846</v>
+        <v>182080.50116</v>
       </c>
     </row>
   </sheetData>
@@ -1339,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301139.SZ</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>16.35</v>
       </c>
       <c r="D2" t="n">
-        <v>1.27</v>
+        <v>16.82</v>
       </c>
       <c r="E2" t="n">
-        <v>0.75</v>
+        <v>14.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91</v>
+        <v>14.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.31</v>
+        <v>18.32</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4</v>
+        <v>-4.02</v>
       </c>
       <c r="I2" t="n">
-        <v>-72.5076</v>
+        <v>-21.9432</v>
       </c>
       <c r="J2" t="n">
-        <v>329007.61</v>
+        <v>116534.4</v>
       </c>
       <c r="K2" t="n">
-        <v>28660.5614</v>
+        <v>177659.40963</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920202.BJ</t>
+          <t>688578.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>92.83</v>
       </c>
       <c r="D3" t="n">
-        <v>23.58</v>
+        <v>94.97</v>
       </c>
       <c r="E3" t="n">
-        <v>18.32</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>18.32</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>26.16</v>
+        <v>111.58</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.84</v>
+        <v>-22.32</v>
       </c>
       <c r="I3" t="n">
-        <v>-29.9694</v>
+        <v>-20.0036</v>
       </c>
       <c r="J3" t="n">
-        <v>158483.66</v>
+        <v>66252.28</v>
       </c>
       <c r="K3" t="n">
-        <v>318422.43598</v>
+        <v>598347.316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301030.SZ</t>
+          <t>688498.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.92</v>
+        <v>1361</v>
       </c>
       <c r="D4" t="n">
-        <v>4.95</v>
+        <v>1412.92</v>
       </c>
       <c r="E4" t="n">
-        <v>4.06</v>
+        <v>1290.4</v>
       </c>
       <c r="F4" t="n">
-        <v>4.18</v>
+        <v>1290.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.97</v>
+        <v>1613</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.79</v>
+        <v>-322.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.8954</v>
+        <v>-20</v>
       </c>
       <c r="J4" t="n">
-        <v>287949.52</v>
+        <v>55108.84</v>
       </c>
       <c r="K4" t="n">
-        <v>127062.77628</v>
+        <v>7298435.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301686.SZ</t>
+          <t>688048.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>186.88</v>
+        <v>250</v>
       </c>
       <c r="D5" t="n">
-        <v>189</v>
+        <v>255.55</v>
       </c>
       <c r="E5" t="n">
-        <v>165.6</v>
+        <v>231.76</v>
       </c>
       <c r="F5" t="n">
-        <v>165.82</v>
+        <v>231.76</v>
       </c>
       <c r="G5" t="n">
-        <v>192.06</v>
+        <v>289.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-26.24</v>
+        <v>-57.94</v>
       </c>
       <c r="I5" t="n">
-        <v>-13.6624</v>
+        <v>-20</v>
       </c>
       <c r="J5" t="n">
-        <v>40787.62</v>
+        <v>125875.79</v>
       </c>
       <c r="K5" t="n">
-        <v>715793.85851</v>
+        <v>2997676.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688622.SH</t>
+          <t>001246.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>134.64</v>
+        <v>60.63</v>
       </c>
       <c r="D6" t="n">
-        <v>135.88</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>119.58</v>
+        <v>52.22</v>
       </c>
       <c r="F6" t="n">
-        <v>119.6</v>
+        <v>53.55</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>65.09</v>
       </c>
       <c r="H6" t="n">
-        <v>-16.4</v>
+        <v>-11.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-12.0588</v>
+        <v>-17.7293</v>
       </c>
       <c r="J6" t="n">
-        <v>12737.97</v>
+        <v>678115.9399999999</v>
       </c>
       <c r="K6" t="n">
-        <v>160894.454</v>
+        <v>3919921.88831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300746.SZ</t>
+          <t>688313.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66</v>
+        <v>137.95</v>
       </c>
       <c r="D7" t="n">
-        <v>17.16</v>
+        <v>142.48</v>
       </c>
       <c r="E7" t="n">
-        <v>14.78</v>
+        <v>126.3</v>
       </c>
       <c r="F7" t="n">
-        <v>14.87</v>
+        <v>127.6</v>
       </c>
       <c r="G7" t="n">
-        <v>16.81</v>
+        <v>154.48</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.94</v>
+        <v>-26.88</v>
       </c>
       <c r="I7" t="n">
-        <v>-11.5407</v>
+        <v>-17.4003</v>
       </c>
       <c r="J7" t="n">
-        <v>220598.5</v>
+        <v>366169.9</v>
       </c>
       <c r="K7" t="n">
-        <v>344154.89514</v>
+        <v>4864029.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688521.SH</t>
+          <t>300684.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>197</v>
+        <v>106.89</v>
       </c>
       <c r="D8" t="n">
-        <v>199.89</v>
+        <v>107.78</v>
       </c>
       <c r="E8" t="n">
-        <v>171.5</v>
+        <v>88.31</v>
       </c>
       <c r="F8" t="n">
-        <v>171.68</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>193.64</v>
+        <v>108.1</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.96</v>
+        <v>-18</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.3406</v>
+        <v>-16.6512</v>
       </c>
       <c r="J8" t="n">
-        <v>306717.7</v>
+        <v>349379.32</v>
       </c>
       <c r="K8" t="n">
-        <v>5461671.075</v>
+        <v>3344494.42134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>300804.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.62</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>0.62</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>0.62</v>
+        <v>46.05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.62</v>
+        <v>46.62</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6899999999999999</v>
+        <v>55.41</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-10.1449</v>
+        <v>-15.8636</v>
       </c>
       <c r="J9" t="n">
-        <v>135124</v>
+        <v>51137.02</v>
       </c>
       <c r="K9" t="n">
-        <v>8377.688</v>
+        <v>249628.31863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>603797.SH</t>
+          <t>688536.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.4</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>5.4</v>
+        <v>326</v>
       </c>
       <c r="E10" t="n">
-        <v>4.82</v>
+        <v>276.12</v>
       </c>
       <c r="F10" t="n">
-        <v>4.82</v>
+        <v>280</v>
       </c>
       <c r="G10" t="n">
-        <v>5.36</v>
+        <v>327</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.54</v>
+        <v>-47</v>
       </c>
       <c r="I10" t="n">
-        <v>-10.0746</v>
+        <v>-14.3731</v>
       </c>
       <c r="J10" t="n">
-        <v>326136</v>
+        <v>55227.02</v>
       </c>
       <c r="K10" t="n">
-        <v>159874.743</v>
+        <v>1629368.192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>600156.SH</t>
+          <t>688036.SH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.77</v>
+        <v>53.3</v>
       </c>
       <c r="D11" t="n">
-        <v>7.77</v>
+        <v>53.3</v>
       </c>
       <c r="E11" t="n">
-        <v>7.35</v>
+        <v>45.26</v>
       </c>
       <c r="F11" t="n">
-        <v>7.35</v>
+        <v>46.1</v>
       </c>
       <c r="G11" t="n">
-        <v>8.17</v>
+        <v>53.8</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.82</v>
+        <v>-7.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-10.0367</v>
+        <v>-14.3123</v>
       </c>
       <c r="J11" t="n">
-        <v>423647</v>
+        <v>275608.33</v>
       </c>
       <c r="K11" t="n">
-        <v>314199.666</v>
+        <v>1300439.787</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,106 +1819,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000002.SZ</t>
+          <t>000513.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>万科A</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.26</v>
+        <v>29.61</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4118</v>
+        <v>-10</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48</v>
+        <v>6.15</v>
       </c>
       <c r="G2" t="n">
-        <v>5158052404</v>
+        <v>1064992550</v>
       </c>
       <c r="H2" t="n">
-        <v>617580196.4299999</v>
+        <v>239848307.26</v>
       </c>
       <c r="I2" t="n">
-        <v>688964755.91</v>
+        <v>177476408.76</v>
       </c>
       <c r="J2" t="n">
-        <v>1306544952.34</v>
+        <v>417324716.02</v>
       </c>
       <c r="K2" t="n">
-        <v>71384559.48</v>
+        <v>-62371898.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>-5.86</v>
       </c>
       <c r="M2" t="n">
-        <v>25.33</v>
+        <v>39.19</v>
       </c>
       <c r="N2" t="n">
-        <v>41386382036.04</v>
+        <v>16808169442.68</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000011.SZ</t>
+          <t>000678.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>12.24</v>
       </c>
       <c r="E3" t="n">
-        <v>9.973000000000001</v>
+        <v>-5.0427</v>
       </c>
       <c r="F3" t="n">
-        <v>17.07</v>
+        <v>28.23</v>
       </c>
       <c r="G3" t="n">
-        <v>971267913</v>
+        <v>1684516377</v>
       </c>
       <c r="H3" t="n">
-        <v>163466249.68</v>
+        <v>318066578</v>
       </c>
       <c r="I3" t="n">
-        <v>107516407.36</v>
+        <v>232681777.63</v>
       </c>
       <c r="J3" t="n">
-        <v>270982657.04</v>
+        <v>550748355.63</v>
       </c>
       <c r="K3" t="n">
-        <v>-55949842.32</v>
+        <v>-85384800.37</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.76</v>
+        <v>-5.07</v>
       </c>
       <c r="M3" t="n">
-        <v>27.9</v>
+        <v>32.69</v>
       </c>
       <c r="N3" t="n">
-        <v>6653636899.62</v>
+        <v>5625648395.28</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1930,51 +1929,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000504.SZ</t>
+          <t>000710.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>贝瑞基因</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.42</v>
+        <v>10.27</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0089</v>
+        <v>-5.5198</v>
       </c>
       <c r="F4" t="n">
-        <v>22.51</v>
+        <v>26.12</v>
       </c>
       <c r="G4" t="n">
-        <v>860444296</v>
+        <v>965448630</v>
       </c>
       <c r="H4" t="n">
-        <v>129992238.58</v>
+        <v>144701834.19</v>
       </c>
       <c r="I4" t="n">
-        <v>211621186</v>
+        <v>96337842.73999999</v>
       </c>
       <c r="J4" t="n">
-        <v>341613424.58</v>
+        <v>241039676.93</v>
       </c>
       <c r="K4" t="n">
-        <v>81628947.42</v>
+        <v>-48363991.45</v>
       </c>
       <c r="L4" t="n">
-        <v>9.49</v>
+        <v>-5.01</v>
       </c>
       <c r="M4" t="n">
-        <v>39.7</v>
+        <v>24.97</v>
       </c>
       <c r="N4" t="n">
-        <v>4087700183.16</v>
+        <v>3445865966.66</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1985,161 +1984,161 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000560.SZ</t>
+          <t>000850.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>华茂股份</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5957</v>
+        <v>-3.3573</v>
       </c>
       <c r="F5" t="n">
-        <v>32.84</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2736655375</v>
+        <v>1082459473</v>
       </c>
       <c r="H5" t="n">
-        <v>294244882.36</v>
+        <v>112760076.65</v>
       </c>
       <c r="I5" t="n">
-        <v>465305276.36</v>
+        <v>77717221.92</v>
       </c>
       <c r="J5" t="n">
-        <v>759550158.72</v>
+        <v>190477298.57</v>
       </c>
       <c r="K5" t="n">
-        <v>171060394</v>
+        <v>-35042854.73</v>
       </c>
       <c r="L5" t="n">
-        <v>6.25</v>
+        <v>-3.24</v>
       </c>
       <c r="M5" t="n">
-        <v>27.75</v>
+        <v>17.6</v>
       </c>
       <c r="N5" t="n">
-        <v>8667946040.299999</v>
+        <v>3801798747.37</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000678.SZ</t>
+          <t>001216.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.89</v>
+        <v>23.56</v>
       </c>
       <c r="E6" t="n">
-        <v>9.982900000000001</v>
+        <v>-10.0076</v>
       </c>
       <c r="F6" t="n">
-        <v>19.65</v>
+        <v>7.17</v>
       </c>
       <c r="G6" t="n">
-        <v>1074985690</v>
+        <v>422116630</v>
       </c>
       <c r="H6" t="n">
-        <v>118352378.2</v>
+        <v>42119756</v>
       </c>
       <c r="I6" t="n">
-        <v>256972357.22</v>
+        <v>28573375</v>
       </c>
       <c r="J6" t="n">
-        <v>375324735.42</v>
+        <v>70693131</v>
       </c>
       <c r="K6" t="n">
-        <v>138619979.02</v>
+        <v>-13546381</v>
       </c>
       <c r="L6" t="n">
-        <v>12.9</v>
+        <v>-3.21</v>
       </c>
       <c r="M6" t="n">
-        <v>34.91</v>
+        <v>16.75</v>
       </c>
       <c r="N6" t="n">
-        <v>5924396063.33</v>
+        <v>5815460848.44</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000678.SZ</t>
+          <t>002074.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.89</v>
+        <v>31.3</v>
       </c>
       <c r="E7" t="n">
-        <v>9.982900000000001</v>
+        <v>6.1017</v>
       </c>
       <c r="F7" t="n">
-        <v>19.65</v>
+        <v>6.87</v>
       </c>
       <c r="G7" t="n">
-        <v>1185742093</v>
+        <v>8499477398</v>
       </c>
       <c r="H7" t="n">
-        <v>123400182.2</v>
+        <v>693167034.92</v>
       </c>
       <c r="I7" t="n">
-        <v>269549089.22</v>
+        <v>741383777.4</v>
       </c>
       <c r="J7" t="n">
-        <v>392949271.42</v>
+        <v>1434550812.32</v>
       </c>
       <c r="K7" t="n">
-        <v>146148907.02</v>
+        <v>48216742.48</v>
       </c>
       <c r="L7" t="n">
-        <v>12.33</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>33.14</v>
+        <v>16.88</v>
       </c>
       <c r="N7" t="n">
-        <v>5924396063.33</v>
+        <v>54357385697</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -2150,1206 +2149,1206 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000850.SZ</t>
+          <t>002188.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>中天服务</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.17</v>
+        <v>5.97</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.9352</v>
+        <v>-6.7188</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8</v>
+        <v>30.32</v>
       </c>
       <c r="G8" t="n">
-        <v>671892787</v>
+        <v>478218174</v>
       </c>
       <c r="H8" t="n">
-        <v>106000652.02</v>
+        <v>76675491.13</v>
       </c>
       <c r="I8" t="n">
-        <v>38378519</v>
+        <v>79537428.70999999</v>
       </c>
       <c r="J8" t="n">
-        <v>144379171.02</v>
+        <v>156212919.84</v>
       </c>
       <c r="K8" t="n">
-        <v>-67622133.02</v>
+        <v>2861937.58</v>
       </c>
       <c r="L8" t="n">
-        <v>-10.06</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>21.49</v>
+        <v>32.67</v>
       </c>
       <c r="N8" t="n">
-        <v>3933871160.43</v>
+        <v>1536457151.79</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>001216.SZ</t>
+          <t>002242.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.18</v>
+        <v>13.75</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.0034</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>10.93</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>719082131</v>
+        <v>587846426</v>
       </c>
       <c r="H9" t="n">
-        <v>60506863.23</v>
+        <v>89014569.5</v>
       </c>
       <c r="I9" t="n">
-        <v>41328350</v>
+        <v>74952868</v>
       </c>
       <c r="J9" t="n">
-        <v>101835213.23</v>
+        <v>163967437.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-19178513.23</v>
+        <v>-14061701.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.67</v>
+        <v>-2.39</v>
       </c>
       <c r="M9" t="n">
-        <v>14.16</v>
+        <v>27.89</v>
       </c>
       <c r="N9" t="n">
-        <v>6462171689.82</v>
+        <v>10474277343.75</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>001234.SZ</t>
+          <t>002285.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>世联行</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.8</v>
+        <v>3.21</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.0105</v>
+        <v>6.2914</v>
       </c>
       <c r="F10" t="n">
-        <v>12.03</v>
+        <v>17.9</v>
       </c>
       <c r="G10" t="n">
-        <v>289864061</v>
+        <v>1140776441</v>
       </c>
       <c r="H10" t="n">
-        <v>44538186.92</v>
+        <v>89277002.5</v>
       </c>
       <c r="I10" t="n">
-        <v>19325445.8</v>
+        <v>335628861.77</v>
       </c>
       <c r="J10" t="n">
-        <v>63863632.72</v>
+        <v>424905864.27</v>
       </c>
       <c r="K10" t="n">
-        <v>-25212741.12</v>
+        <v>246351859.27</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.699999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="M10" t="n">
-        <v>22.03</v>
+        <v>37.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2361770700</v>
+        <v>6352620113.01</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>001234.SZ</t>
+          <t>002316.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>亚联发展</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.8</v>
+        <v>4.98</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.0105</v>
+        <v>0.6061</v>
       </c>
       <c r="F11" t="n">
-        <v>12.03</v>
+        <v>37.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1216089983</v>
+        <v>652297532</v>
       </c>
       <c r="H11" t="n">
-        <v>210708278.42</v>
+        <v>105739849.18</v>
       </c>
       <c r="I11" t="n">
-        <v>139426309.92</v>
+        <v>78443870</v>
       </c>
       <c r="J11" t="n">
-        <v>350134588.34</v>
+        <v>184183719.18</v>
       </c>
       <c r="K11" t="n">
-        <v>-71281968.5</v>
+        <v>-27295979.18</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.86</v>
+        <v>-4.18</v>
       </c>
       <c r="M11" t="n">
-        <v>28.79</v>
+        <v>28.24</v>
       </c>
       <c r="N11" t="n">
-        <v>2361770700</v>
+        <v>1696860300</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>001246.SZ</t>
+          <t>002384.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>力勤资源</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65.09</v>
+        <v>150.66</v>
       </c>
       <c r="E12" t="n">
-        <v>206.5944</v>
+        <v>-10</v>
       </c>
       <c r="F12" t="n">
-        <v>74.93000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="G12" t="n">
-        <v>8345390509</v>
+        <v>8202814551</v>
       </c>
       <c r="H12" t="n">
-        <v>241763545.01</v>
+        <v>1033956224.39</v>
       </c>
       <c r="I12" t="n">
-        <v>745890681.95</v>
+        <v>1404425710.53</v>
       </c>
       <c r="J12" t="n">
-        <v>987654226.96</v>
+        <v>2438381934.92</v>
       </c>
       <c r="K12" t="n">
-        <v>504127136.94</v>
+        <v>370469486.14</v>
       </c>
       <c r="L12" t="n">
-        <v>6.04</v>
+        <v>4.52</v>
       </c>
       <c r="M12" t="n">
-        <v>11.83</v>
+        <v>29.73</v>
       </c>
       <c r="N12" t="n">
-        <v>10240386701.66</v>
+        <v>208863230787.18</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>无价格涨跌幅限制的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002058.SZ</t>
+          <t>002490.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20.2</v>
+        <v>7.6</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0218</v>
+        <v>9.9855</v>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>12.5</v>
       </c>
       <c r="G13" t="n">
-        <v>143179917</v>
+        <v>499360191</v>
       </c>
       <c r="H13" t="n">
-        <v>34930199.2</v>
+        <v>50052997.75</v>
       </c>
       <c r="I13" t="n">
-        <v>39932092</v>
+        <v>128250744.6</v>
       </c>
       <c r="J13" t="n">
-        <v>74862291.2</v>
+        <v>178303742.35</v>
       </c>
       <c r="K13" t="n">
-        <v>5001892.8</v>
+        <v>78197746.84999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.49</v>
+        <v>15.66</v>
       </c>
       <c r="M13" t="n">
-        <v>52.29</v>
+        <v>35.71</v>
       </c>
       <c r="N13" t="n">
-        <v>2895989806.4</v>
+        <v>4117087200</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002119.SZ</t>
+          <t>002565.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.8</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.7372</v>
+        <v>9.9526</v>
       </c>
       <c r="F14" t="n">
-        <v>23.62</v>
+        <v>16.09</v>
       </c>
       <c r="G14" t="n">
-        <v>2339128122</v>
+        <v>1557861796</v>
       </c>
       <c r="H14" t="n">
-        <v>301276658.14</v>
+        <v>128410996.46</v>
       </c>
       <c r="I14" t="n">
-        <v>321307550.2</v>
+        <v>316318873.28</v>
       </c>
       <c r="J14" t="n">
-        <v>622584208.34</v>
+        <v>444729869.74</v>
       </c>
       <c r="K14" t="n">
-        <v>20030892.06</v>
+        <v>187907876.82</v>
       </c>
       <c r="L14" t="n">
-        <v>0.86</v>
+        <v>12.06</v>
       </c>
       <c r="M14" t="n">
-        <v>26.62</v>
+        <v>28.55</v>
       </c>
       <c r="N14" t="n">
-        <v>9682327200</v>
+        <v>9836383996.16</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002164.SZ</t>
+          <t>002580.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.26</v>
+        <v>21.36</v>
       </c>
       <c r="E15" t="n">
-        <v>10.0415</v>
+        <v>9.4262</v>
       </c>
       <c r="F15" t="n">
-        <v>10.41</v>
+        <v>26.89</v>
       </c>
       <c r="G15" t="n">
-        <v>648830907</v>
+        <v>2546677482</v>
       </c>
       <c r="H15" t="n">
-        <v>131924712.2</v>
+        <v>194468814.7</v>
       </c>
       <c r="I15" t="n">
-        <v>168633288.85</v>
+        <v>383046481.49</v>
       </c>
       <c r="J15" t="n">
-        <v>300558001.05</v>
+        <v>577515296.1900001</v>
       </c>
       <c r="K15" t="n">
-        <v>36708576.65</v>
+        <v>188577666.79</v>
       </c>
       <c r="L15" t="n">
-        <v>5.66</v>
+        <v>7.4</v>
       </c>
       <c r="M15" t="n">
-        <v>46.32</v>
+        <v>22.68</v>
       </c>
       <c r="N15" t="n">
-        <v>6361818396.18</v>
+        <v>9661956768</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002172.SZ</t>
+          <t>002614.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.43</v>
+        <v>8.34</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0929</v>
+        <v>7.4742</v>
       </c>
       <c r="F16" t="n">
-        <v>24.52</v>
+        <v>21.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1026415505</v>
+        <v>780647189</v>
       </c>
       <c r="H16" t="n">
-        <v>219447165.05</v>
+        <v>109395002</v>
       </c>
       <c r="I16" t="n">
-        <v>76335016.5</v>
+        <v>207894224.71</v>
       </c>
       <c r="J16" t="n">
-        <v>295782181.55</v>
+        <v>317289226.71</v>
       </c>
       <c r="K16" t="n">
-        <v>-143112148.55</v>
+        <v>98499222.70999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-13.94</v>
+        <v>12.62</v>
       </c>
       <c r="M16" t="n">
-        <v>28.82</v>
+        <v>40.64</v>
       </c>
       <c r="N16" t="n">
-        <v>4154714163.9</v>
+        <v>3680236093.74</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002244.SZ</t>
+          <t>002702.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>滨江集团</t>
+          <t>海欣食品</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.14</v>
+        <v>5.92</v>
       </c>
       <c r="E17" t="n">
-        <v>7.1882</v>
+        <v>10.0372</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>14.39</v>
       </c>
       <c r="G17" t="n">
-        <v>1689372530</v>
+        <v>371309038</v>
       </c>
       <c r="H17" t="n">
-        <v>249748802.95</v>
+        <v>68058342.23999999</v>
       </c>
       <c r="I17" t="n">
-        <v>283019132.04</v>
+        <v>97790367.95999999</v>
       </c>
       <c r="J17" t="n">
-        <v>532767934.99</v>
+        <v>165848710.2</v>
       </c>
       <c r="K17" t="n">
-        <v>33270329.09</v>
+        <v>29732025.72</v>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>8.01</v>
       </c>
       <c r="M17" t="n">
-        <v>31.54</v>
+        <v>44.67</v>
       </c>
       <c r="N17" t="n">
-        <v>27961550307.6</v>
+        <v>2715763000</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002244.SZ</t>
+          <t>002717.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>滨江集团</t>
+          <t>*ST岭南</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>7.1882</v>
+        <v>-9.6774</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>0.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2879114526</v>
+        <v>1203048</v>
       </c>
       <c r="H18" t="n">
-        <v>368004287.94</v>
+        <v>899528</v>
       </c>
       <c r="I18" t="n">
-        <v>560659203.92</v>
+        <v>239176</v>
       </c>
       <c r="J18" t="n">
-        <v>928663491.86</v>
+        <v>1138704</v>
       </c>
       <c r="K18" t="n">
-        <v>192654915.98</v>
+        <v>-660352</v>
       </c>
       <c r="L18" t="n">
-        <v>6.69</v>
+        <v>-54.89</v>
       </c>
       <c r="M18" t="n">
-        <v>32.26</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>27961550307.6</v>
+        <v>1001807444.96</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002388.SZ</t>
+          <t>002805.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新亚制程</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.1</v>
+        <v>17.67</v>
       </c>
       <c r="E19" t="n">
-        <v>10.0363</v>
+        <v>10.0249</v>
       </c>
       <c r="F19" t="n">
-        <v>7.05</v>
+        <v>8.81</v>
       </c>
       <c r="G19" t="n">
-        <v>1208206397</v>
+        <v>424878102</v>
       </c>
       <c r="H19" t="n">
-        <v>225563204.26</v>
+        <v>72556113.2</v>
       </c>
       <c r="I19" t="n">
-        <v>266659127.8</v>
+        <v>120599472.45</v>
       </c>
       <c r="J19" t="n">
-        <v>492222332.06</v>
+        <v>193155585.65</v>
       </c>
       <c r="K19" t="n">
-        <v>41095923.54</v>
+        <v>48043359.25</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4</v>
+        <v>11.31</v>
       </c>
       <c r="M19" t="n">
-        <v>40.74</v>
+        <v>45.46</v>
       </c>
       <c r="N19" t="n">
-        <v>4606633804.5</v>
+        <v>4926679921.56</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002494.SZ</t>
+          <t>002866.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>华斯股份</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.05</v>
+        <v>18.59</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0752</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>25.35</v>
+        <v>20.57</v>
       </c>
       <c r="G20" t="n">
-        <v>362348650</v>
+        <v>671544940</v>
       </c>
       <c r="H20" t="n">
-        <v>76212831.94</v>
+        <v>78757215.53</v>
       </c>
       <c r="I20" t="n">
-        <v>65580097</v>
+        <v>88311905.66</v>
       </c>
       <c r="J20" t="n">
-        <v>141792928.94</v>
+        <v>167069121.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-10632734.94</v>
+        <v>9554690.130000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.93</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
-        <v>39.13</v>
+        <v>24.88</v>
       </c>
       <c r="N20" t="n">
-        <v>1448190711.9</v>
+        <v>3416263739.46</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002640.SZ</t>
+          <t>002881.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>美格智能</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.91</v>
+        <v>38.17</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7614</v>
+        <v>-9.9976</v>
       </c>
       <c r="F21" t="n">
-        <v>23.22</v>
+        <v>5.49</v>
       </c>
       <c r="G21" t="n">
-        <v>1400792199</v>
+        <v>399034367</v>
       </c>
       <c r="H21" t="n">
-        <v>116836491.01</v>
+        <v>138064677.8</v>
       </c>
       <c r="I21" t="n">
-        <v>163494451</v>
+        <v>62268477.78</v>
       </c>
       <c r="J21" t="n">
-        <v>280330942.01</v>
+        <v>200333155.58</v>
       </c>
       <c r="K21" t="n">
-        <v>46657959.99</v>
+        <v>-75796200.02</v>
       </c>
       <c r="L21" t="n">
-        <v>3.33</v>
+        <v>-18.99</v>
       </c>
       <c r="M21" t="n">
-        <v>20.01</v>
+        <v>50.2</v>
       </c>
       <c r="N21" t="n">
-        <v>6053703559.8</v>
+        <v>7008712801.2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>002882.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>*ST岭南</t>
+          <t>金龙羽</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.62</v>
+        <v>26.95</v>
       </c>
       <c r="E22" t="n">
-        <v>-10.1449</v>
+        <v>7.8863</v>
       </c>
       <c r="F22" t="n">
-        <v>0.76</v>
+        <v>14.08</v>
       </c>
       <c r="G22" t="n">
-        <v>8377688</v>
+        <v>2243498153</v>
       </c>
       <c r="H22" t="n">
-        <v>3439574</v>
+        <v>237580058.68</v>
       </c>
       <c r="I22" t="n">
-        <v>1651246</v>
+        <v>288962072.48</v>
       </c>
       <c r="J22" t="n">
-        <v>5090820</v>
+        <v>526542131.16</v>
       </c>
       <c r="K22" t="n">
-        <v>-1788328</v>
+        <v>51382013.8</v>
       </c>
       <c r="L22" t="n">
-        <v>-21.35</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>60.77</v>
+        <v>23.47</v>
       </c>
       <c r="N22" t="n">
-        <v>1109143956.92</v>
+        <v>6656381524.1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>002962.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>*ST岭南</t>
+          <t>五方光电</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.62</v>
+        <v>16.69</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.1449</v>
+        <v>3.2158</v>
       </c>
       <c r="F23" t="n">
-        <v>0.76</v>
+        <v>29.24</v>
       </c>
       <c r="G23" t="n">
-        <v>100851841</v>
+        <v>971753286</v>
       </c>
       <c r="H23" t="n">
-        <v>25810852.11</v>
+        <v>143627753.98</v>
       </c>
       <c r="I23" t="n">
-        <v>10794186</v>
+        <v>99543505</v>
       </c>
       <c r="J23" t="n">
-        <v>36605038.11</v>
+        <v>243171258.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-15016666.11</v>
+        <v>-44084248.98</v>
       </c>
       <c r="L23" t="n">
-        <v>-14.89</v>
+        <v>-4.54</v>
       </c>
       <c r="M23" t="n">
-        <v>36.3</v>
+        <v>25.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1109143956.92</v>
+        <v>3491810533.7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002827.SZ</t>
+          <t>300522.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高争民爆</t>
+          <t>世名科技</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>16.56</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9001</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>8.460000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G24" t="n">
-        <v>3609405491</v>
+        <v>419527375</v>
       </c>
       <c r="H24" t="n">
-        <v>746793362.2</v>
+        <v>54330634</v>
       </c>
       <c r="I24" t="n">
-        <v>549068989.21</v>
+        <v>112478262.2</v>
       </c>
       <c r="J24" t="n">
-        <v>1295862351.41</v>
+        <v>166808896.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-197724372.99</v>
+        <v>58147628.2</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.48</v>
+        <v>13.86</v>
       </c>
       <c r="M24" t="n">
-        <v>35.9</v>
+        <v>39.76</v>
       </c>
       <c r="N24" t="n">
-        <v>16283933625</v>
+        <v>4366789912.08</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002866.SZ</t>
+          <t>300530.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>领湃科技</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.9</v>
+        <v>24.08</v>
       </c>
       <c r="E25" t="n">
-        <v>10.026</v>
+        <v>19.9801</v>
       </c>
       <c r="F25" t="n">
-        <v>18.65</v>
+        <v>10.31</v>
       </c>
       <c r="G25" t="n">
-        <v>577077481</v>
+        <v>400319985</v>
       </c>
       <c r="H25" t="n">
-        <v>95473984</v>
+        <v>27337751.64</v>
       </c>
       <c r="I25" t="n">
-        <v>62024452</v>
+        <v>104104224.25</v>
       </c>
       <c r="J25" t="n">
-        <v>157498436</v>
+        <v>131441975.89</v>
       </c>
       <c r="K25" t="n">
-        <v>-33449532</v>
+        <v>76766472.61</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.8</v>
+        <v>19.18</v>
       </c>
       <c r="M25" t="n">
-        <v>27.29</v>
+        <v>32.83</v>
       </c>
       <c r="N25" t="n">
-        <v>3105694308.6</v>
+        <v>4140588604.32</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002866.SZ</t>
+          <t>300530.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>领湃科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.9</v>
+        <v>24.08</v>
       </c>
       <c r="E26" t="n">
-        <v>10.026</v>
+        <v>19.9801</v>
       </c>
       <c r="F26" t="n">
-        <v>18.65</v>
+        <v>10.31</v>
       </c>
       <c r="G26" t="n">
-        <v>766120628</v>
+        <v>699811967</v>
       </c>
       <c r="H26" t="n">
-        <v>106408694</v>
+        <v>59705310.5</v>
       </c>
       <c r="I26" t="n">
-        <v>107396562</v>
+        <v>125121308.68</v>
       </c>
       <c r="J26" t="n">
-        <v>213805256</v>
+        <v>184826619.18</v>
       </c>
       <c r="K26" t="n">
-        <v>987868</v>
+        <v>65415998.18</v>
       </c>
       <c r="L26" t="n">
-        <v>0.13</v>
+        <v>9.35</v>
       </c>
       <c r="M26" t="n">
-        <v>27.91</v>
+        <v>26.41</v>
       </c>
       <c r="N26" t="n">
-        <v>3105694308.6</v>
+        <v>4140588604.32</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002962.SZ</t>
+          <t>300619.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>五方光电</t>
+          <t>金银河</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.17</v>
+        <v>28.17</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>17.571</v>
       </c>
       <c r="F27" t="n">
-        <v>17.06</v>
+        <v>13.31</v>
       </c>
       <c r="G27" t="n">
-        <v>1800074650</v>
+        <v>698192837</v>
       </c>
       <c r="H27" t="n">
-        <v>218631746.1</v>
+        <v>71530063.06999999</v>
       </c>
       <c r="I27" t="n">
-        <v>184163629.04</v>
+        <v>130133681.2</v>
       </c>
       <c r="J27" t="n">
-        <v>402795375.14</v>
+        <v>201663744.27</v>
       </c>
       <c r="K27" t="n">
-        <v>-34468117.06</v>
+        <v>58603618.13</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.91</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>22.38</v>
+        <v>28.88</v>
       </c>
       <c r="N27" t="n">
-        <v>3383018354.1</v>
+        <v>5364482003.82</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300893.SZ</t>
+          <t>300684.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>松原安全</t>
+          <t>中石科技</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.13</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>19.9841</v>
+        <v>-16.6512</v>
       </c>
       <c r="F28" t="n">
-        <v>8.949999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="G28" t="n">
-        <v>323471626</v>
+        <v>3344494421</v>
       </c>
       <c r="H28" t="n">
-        <v>86311631.2</v>
+        <v>868062183.14</v>
       </c>
       <c r="I28" t="n">
-        <v>91185273.88</v>
+        <v>746367561.3099999</v>
       </c>
       <c r="J28" t="n">
-        <v>177496905.08</v>
+        <v>1614429744.45</v>
       </c>
       <c r="K28" t="n">
-        <v>4873642.68</v>
+        <v>-121694621.83</v>
       </c>
       <c r="L28" t="n">
-        <v>1.51</v>
+        <v>-3.64</v>
       </c>
       <c r="M28" t="n">
-        <v>54.87</v>
+        <v>48.27</v>
       </c>
       <c r="N28" t="n">
-        <v>3808115755.72</v>
+        <v>18468623847.7</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>301030.SZ</t>
+          <t>300804.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>*ST仕净</t>
+          <t>广康生化</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.18</v>
+        <v>46.62</v>
       </c>
       <c r="E29" t="n">
-        <v>-15.8954</v>
+        <v>-15.8636</v>
       </c>
       <c r="F29" t="n">
-        <v>14.25</v>
+        <v>18.6</v>
       </c>
       <c r="G29" t="n">
-        <v>127062776</v>
+        <v>249628319</v>
       </c>
       <c r="H29" t="n">
-        <v>21423525.16</v>
+        <v>42776136.88</v>
       </c>
       <c r="I29" t="n">
-        <v>14225581.4</v>
+        <v>32395203</v>
       </c>
       <c r="J29" t="n">
-        <v>35649106.56</v>
+        <v>75171339.88</v>
       </c>
       <c r="K29" t="n">
-        <v>-7197943.76</v>
+        <v>-10380933.88</v>
       </c>
       <c r="L29" t="n">
-        <v>-5.66</v>
+        <v>-4.16</v>
       </c>
       <c r="M29" t="n">
-        <v>28.06</v>
+        <v>30.11</v>
       </c>
       <c r="N29" t="n">
-        <v>844801867.8</v>
+        <v>1282050000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3360,7 +3359,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3374,37 +3373,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-72.5076</v>
+        <v>3.2967</v>
       </c>
       <c r="F30" t="n">
-        <v>43.2</v>
+        <v>24.84</v>
       </c>
       <c r="G30" t="n">
-        <v>28660561</v>
+        <v>18169047</v>
       </c>
       <c r="H30" t="n">
-        <v>2020803</v>
+        <v>4026454.04</v>
       </c>
       <c r="I30" t="n">
-        <v>5016932</v>
+        <v>5401745.14</v>
       </c>
       <c r="J30" t="n">
-        <v>7037735</v>
+        <v>9428199.18</v>
       </c>
       <c r="K30" t="n">
-        <v>2996129</v>
+        <v>1375291.1</v>
       </c>
       <c r="L30" t="n">
-        <v>10.45</v>
+        <v>7.57</v>
       </c>
       <c r="M30" t="n">
-        <v>24.56</v>
+        <v>51.89</v>
       </c>
       <c r="N30" t="n">
-        <v>69302094.68000001</v>
+        <v>71586779.12</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3415,7 +3414,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3429,202 +3428,202 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>35.93</v>
+        <v>39.52</v>
       </c>
       <c r="E31" t="n">
-        <v>20.0067</v>
+        <v>9.9917</v>
       </c>
       <c r="F31" t="n">
-        <v>7.95</v>
+        <v>19.25</v>
       </c>
       <c r="G31" t="n">
-        <v>510373314</v>
+        <v>1876855229</v>
       </c>
       <c r="H31" t="n">
-        <v>82562040.59</v>
+        <v>257688339.16</v>
       </c>
       <c r="I31" t="n">
-        <v>107202761.53</v>
+        <v>333832391.26</v>
       </c>
       <c r="J31" t="n">
-        <v>189764802.12</v>
+        <v>591520730.42</v>
       </c>
       <c r="K31" t="n">
-        <v>24640720.94</v>
+        <v>76144052.09999999</v>
       </c>
       <c r="L31" t="n">
-        <v>4.83</v>
+        <v>4.06</v>
       </c>
       <c r="M31" t="n">
-        <v>37.18</v>
+        <v>31.52</v>
       </c>
       <c r="N31" t="n">
-        <v>6534014220</v>
+        <v>7186870080</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>301218.SZ</t>
+          <t>301190.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>华是科技</t>
+          <t>善水科技</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>69.75</v>
+        <v>39.52</v>
       </c>
       <c r="E32" t="n">
-        <v>15.8445</v>
+        <v>9.9917</v>
       </c>
       <c r="F32" t="n">
-        <v>33.75</v>
+        <v>19.25</v>
       </c>
       <c r="G32" t="n">
-        <v>1608252150</v>
+        <v>3148935162.11</v>
       </c>
       <c r="H32" t="n">
-        <v>235247349.65</v>
+        <v>3148935162.11</v>
       </c>
       <c r="I32" t="n">
-        <v>397856995.68</v>
+        <v>3148935162.11</v>
       </c>
       <c r="J32" t="n">
-        <v>633104345.33</v>
+        <v>3148935162.11</v>
       </c>
       <c r="K32" t="n">
-        <v>162609646.03</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>10.11</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>39.37</v>
+        <v>100</v>
       </c>
       <c r="N32" t="n">
-        <v>5001295479.75</v>
+        <v>7186870080</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>301218.SZ</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>华是科技</t>
+          <t>尚水智能</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>69.75</v>
+        <v>67.81</v>
       </c>
       <c r="E33" t="n">
-        <v>15.8445</v>
+        <v>19.9752</v>
       </c>
       <c r="F33" t="n">
-        <v>33.75</v>
+        <v>48.24</v>
       </c>
       <c r="G33" t="n">
-        <v>2869820960</v>
+        <v>597216216</v>
       </c>
       <c r="H33" t="n">
-        <v>418729818.41</v>
+        <v>72435592.95</v>
       </c>
       <c r="I33" t="n">
-        <v>702832921.37</v>
+        <v>40747565.21</v>
       </c>
       <c r="J33" t="n">
-        <v>1121562739.78</v>
+        <v>113183158.16</v>
       </c>
       <c r="K33" t="n">
-        <v>284103102.96</v>
+        <v>-31688027.74</v>
       </c>
       <c r="L33" t="n">
-        <v>9.9</v>
+        <v>-5.31</v>
       </c>
       <c r="M33" t="n">
-        <v>39.08</v>
+        <v>18.95</v>
       </c>
       <c r="N33" t="n">
-        <v>5001295479.75</v>
+        <v>1366302944.09</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>301513.SZ</t>
+          <t>301686.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>尚水智能</t>
+          <t>中塑股份</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>56.52</v>
+        <v>160.61</v>
       </c>
       <c r="E34" t="n">
-        <v>9.9183</v>
+        <v>-3.142</v>
       </c>
       <c r="F34" t="n">
-        <v>41.09</v>
+        <v>35.06</v>
       </c>
       <c r="G34" t="n">
-        <v>461965585</v>
+        <v>498836508</v>
       </c>
       <c r="H34" t="n">
-        <v>105609526.76</v>
+        <v>37634677.77</v>
       </c>
       <c r="I34" t="n">
-        <v>38179937.67</v>
+        <v>37085714.03</v>
       </c>
       <c r="J34" t="n">
-        <v>143789464.43</v>
+        <v>74720391.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-67429589.09</v>
+        <v>-548963.74</v>
       </c>
       <c r="L34" t="n">
-        <v>-14.6</v>
+        <v>-0.11</v>
       </c>
       <c r="M34" t="n">
-        <v>31.13</v>
+        <v>14.98</v>
       </c>
       <c r="N34" t="n">
-        <v>1138820858.28</v>
+        <v>1402616284.77</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3635,106 +3634,106 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>301513.SZ</t>
+          <t>301689.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>尚水智能</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>56.52</v>
+        <v>72.2</v>
       </c>
       <c r="E35" t="n">
-        <v>9.9183</v>
+        <v>-1.6751</v>
       </c>
       <c r="F35" t="n">
-        <v>41.09</v>
+        <v>34.1</v>
       </c>
       <c r="G35" t="n">
-        <v>605485251</v>
+        <v>1474938213</v>
       </c>
       <c r="H35" t="n">
-        <v>127439497.75</v>
+        <v>188609805.29</v>
       </c>
       <c r="I35" t="n">
-        <v>107767971.84</v>
+        <v>178672398.87</v>
       </c>
       <c r="J35" t="n">
-        <v>235207469.59</v>
+        <v>367282204.16</v>
       </c>
       <c r="K35" t="n">
-        <v>-19671525.91</v>
+        <v>-9937406.42</v>
       </c>
       <c r="L35" t="n">
-        <v>-3.25</v>
+        <v>-0.67</v>
       </c>
       <c r="M35" t="n">
-        <v>38.85</v>
+        <v>24.9</v>
       </c>
       <c r="N35" t="n">
-        <v>1138820858.28</v>
+        <v>4155936834.4</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>301697.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>贝特利</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>71.05</v>
+        <v>31.51</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3194</v>
+        <v>19.9924</v>
       </c>
       <c r="F36" t="n">
-        <v>40.82</v>
+        <v>46.23</v>
       </c>
       <c r="G36" t="n">
-        <v>1030116710</v>
+        <v>620816467</v>
       </c>
       <c r="H36" t="n">
-        <v>115080061.12</v>
+        <v>35596816</v>
       </c>
       <c r="I36" t="n">
-        <v>81738696.09999999</v>
+        <v>182386730.82</v>
       </c>
       <c r="J36" t="n">
-        <v>196818757.22</v>
+        <v>217983546.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-33341365.02</v>
+        <v>146789914.82</v>
       </c>
       <c r="L36" t="n">
-        <v>-3.24</v>
+        <v>23.64</v>
       </c>
       <c r="M36" t="n">
-        <v>19.11</v>
+        <v>35.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2482376375.15</v>
+        <v>1386157481.34</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3745,51 +3744,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>301686.SZ</t>
+          <t>301699.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>中塑股份</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>165.82</v>
+        <v>34.45</v>
       </c>
       <c r="E37" t="n">
-        <v>-13.6624</v>
+        <v>-8.7659</v>
       </c>
       <c r="F37" t="n">
-        <v>46.7</v>
+        <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>715793859</v>
+        <v>958849301</v>
       </c>
       <c r="H37" t="n">
-        <v>59664794.77</v>
+        <v>109905256.71</v>
       </c>
       <c r="I37" t="n">
-        <v>46676772.76</v>
+        <v>164730546.91</v>
       </c>
       <c r="J37" t="n">
-        <v>106341567.53</v>
+        <v>274635803.62</v>
       </c>
       <c r="K37" t="n">
-        <v>-12988022.01</v>
+        <v>54825290.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.81</v>
+        <v>5.72</v>
       </c>
       <c r="M37" t="n">
-        <v>14.86</v>
+        <v>28.64</v>
       </c>
       <c r="N37" t="n">
-        <v>1448115511.74</v>
+        <v>2409138418.05</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3800,271 +3799,271 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>600127.SH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>73.43000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="E38" t="n">
-        <v>-5.2638</v>
+        <v>5.0228</v>
       </c>
       <c r="F38" t="n">
-        <v>39.19</v>
+        <v>40.85</v>
       </c>
       <c r="G38" t="n">
-        <v>1715915881</v>
+        <v>3659491224</v>
       </c>
       <c r="H38" t="n">
-        <v>193319198.31</v>
+        <v>291332063.83</v>
       </c>
       <c r="I38" t="n">
-        <v>191394956.02</v>
+        <v>415780335.59</v>
       </c>
       <c r="J38" t="n">
-        <v>384714154.33</v>
+        <v>707112399.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-1924242.29</v>
+        <v>124448271.76</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.11</v>
+        <v>3.4</v>
       </c>
       <c r="M38" t="n">
-        <v>22.42</v>
+        <v>19.32</v>
       </c>
       <c r="N38" t="n">
-        <v>4226737420.36</v>
+        <v>8856608408.4</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>600152.SH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>维科技术</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>37.76</v>
+        <v>9.18</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1326</v>
+        <v>8.2547</v>
       </c>
       <c r="F39" t="n">
-        <v>48.43</v>
+        <v>21.71</v>
       </c>
       <c r="G39" t="n">
-        <v>1320482598</v>
+        <v>2129038792</v>
       </c>
       <c r="H39" t="n">
-        <v>208668812.31</v>
+        <v>352685175.15</v>
       </c>
       <c r="I39" t="n">
-        <v>162345228.23</v>
+        <v>257818145.1</v>
       </c>
       <c r="J39" t="n">
-        <v>371014040.54</v>
+        <v>610503320.25</v>
       </c>
       <c r="K39" t="n">
-        <v>-46323584.08</v>
+        <v>-94867030.05</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.51</v>
+        <v>-4.46</v>
       </c>
       <c r="M39" t="n">
-        <v>28.1</v>
+        <v>28.68</v>
       </c>
       <c r="N39" t="n">
-        <v>2640611514.24</v>
+        <v>4856948662.5</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>600059.SH</t>
+          <t>600241.SH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>古越龙山</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.27</v>
+        <v>10.69</v>
       </c>
       <c r="E40" t="n">
-        <v>10.0448</v>
+        <v>9.9794</v>
       </c>
       <c r="F40" t="n">
-        <v>9.869999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="G40" t="n">
-        <v>1093331572</v>
+        <v>326386711</v>
       </c>
       <c r="H40" t="n">
-        <v>108762251.95</v>
+        <v>49903908</v>
       </c>
       <c r="I40" t="n">
-        <v>194966568.43</v>
+        <v>28976646</v>
       </c>
       <c r="J40" t="n">
-        <v>303728820.38</v>
+        <v>78880554</v>
       </c>
       <c r="K40" t="n">
-        <v>86204316.48</v>
+        <v>-20927262</v>
       </c>
       <c r="L40" t="n">
-        <v>7.88</v>
+        <v>-6.41</v>
       </c>
       <c r="M40" t="n">
-        <v>27.78</v>
+        <v>24.17</v>
       </c>
       <c r="N40" t="n">
-        <v>11184625407.51</v>
+        <v>3146089609.35</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600127.SH</t>
+          <t>600241.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.14</v>
+        <v>10.69</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6467</v>
+        <v>9.9794</v>
       </c>
       <c r="F41" t="n">
-        <v>35.15</v>
+        <v>10.88</v>
       </c>
       <c r="G41" t="n">
-        <v>2960624365</v>
+        <v>401047975</v>
       </c>
       <c r="H41" t="n">
-        <v>330928758.65</v>
+        <v>57761681</v>
       </c>
       <c r="I41" t="n">
-        <v>201658604.41</v>
+        <v>51854543</v>
       </c>
       <c r="J41" t="n">
-        <v>532587363.06</v>
+        <v>109616224</v>
       </c>
       <c r="K41" t="n">
-        <v>-129270154.24</v>
+        <v>-5907138</v>
       </c>
       <c r="L41" t="n">
-        <v>-4.37</v>
+        <v>-1.47</v>
       </c>
       <c r="M41" t="n">
-        <v>17.99</v>
+        <v>27.33</v>
       </c>
       <c r="N41" t="n">
-        <v>8433031484.52</v>
+        <v>3146089609.35</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600156.SH</t>
+          <t>600330.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>华升股份</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.35</v>
+        <v>24.21</v>
       </c>
       <c r="E42" t="n">
-        <v>-10.0367</v>
+        <v>-10</v>
       </c>
       <c r="F42" t="n">
-        <v>10.54</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>314199666</v>
+        <v>2549925079</v>
       </c>
       <c r="H42" t="n">
-        <v>47457354.35</v>
+        <v>400718556.76</v>
       </c>
       <c r="I42" t="n">
-        <v>18928892</v>
+        <v>323962810.37</v>
       </c>
       <c r="J42" t="n">
-        <v>66386246.35</v>
+        <v>724681367.13</v>
       </c>
       <c r="K42" t="n">
-        <v>-28528462.35</v>
+        <v>-76755746.39</v>
       </c>
       <c r="L42" t="n">
-        <v>-9.08</v>
+        <v>-3.01</v>
       </c>
       <c r="M42" t="n">
-        <v>21.13</v>
+        <v>28.42</v>
       </c>
       <c r="N42" t="n">
-        <v>2955513659.7</v>
+        <v>29861447211.36</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4075,436 +4074,436 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600383.SH</t>
+          <t>600363.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>金地集团</t>
+          <t>ST联光</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.74</v>
+        <v>10.98</v>
       </c>
       <c r="E43" t="n">
-        <v>7.451</v>
+        <v>-10</v>
       </c>
       <c r="F43" t="n">
-        <v>10.89</v>
+        <v>15.64</v>
       </c>
       <c r="G43" t="n">
-        <v>1258907881</v>
+        <v>776306835</v>
       </c>
       <c r="H43" t="n">
-        <v>139859655.38</v>
+        <v>130726305.97</v>
       </c>
       <c r="I43" t="n">
-        <v>186450220.68</v>
+        <v>70059005.09</v>
       </c>
       <c r="J43" t="n">
-        <v>326309876.06</v>
+        <v>200785311.06</v>
       </c>
       <c r="K43" t="n">
-        <v>46590565.3</v>
+        <v>-60667300.88</v>
       </c>
       <c r="L43" t="n">
-        <v>3.7</v>
+        <v>-7.81</v>
       </c>
       <c r="M43" t="n">
-        <v>25.92</v>
+        <v>25.86</v>
       </c>
       <c r="N43" t="n">
-        <v>12369958987.28</v>
+        <v>4950755181</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600418.SH</t>
+          <t>600400.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.47</v>
+        <v>3.62</v>
       </c>
       <c r="E44" t="n">
-        <v>5.4916</v>
+        <v>10.0304</v>
       </c>
       <c r="F44" t="n">
-        <v>12.19</v>
+        <v>4.81</v>
       </c>
       <c r="G44" t="n">
-        <v>17701036379</v>
+        <v>391041912</v>
       </c>
       <c r="H44" t="n">
-        <v>1994801784.83</v>
+        <v>53522017</v>
       </c>
       <c r="I44" t="n">
-        <v>1956273167.94</v>
+        <v>84348821.76000001</v>
       </c>
       <c r="J44" t="n">
-        <v>3951074952.77</v>
+        <v>137870838.76</v>
       </c>
       <c r="K44" t="n">
-        <v>-38528616.89</v>
+        <v>30826804.76</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.22</v>
+        <v>7.88</v>
       </c>
       <c r="M44" t="n">
-        <v>22.32</v>
+        <v>35.26</v>
       </c>
       <c r="N44" t="n">
-        <v>61922275016.65</v>
+        <v>8294766104.24</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600657.SH</t>
+          <t>600418.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>信达地产</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.55</v>
+        <v>24.72</v>
       </c>
       <c r="E45" t="n">
-        <v>5.0296</v>
+        <v>-10.0109</v>
       </c>
       <c r="F45" t="n">
-        <v>7.31</v>
+        <v>6.35</v>
       </c>
       <c r="G45" t="n">
-        <v>695869362</v>
+        <v>3614355828</v>
       </c>
       <c r="H45" t="n">
-        <v>90396715.58</v>
+        <v>536446969.47</v>
       </c>
       <c r="I45" t="n">
-        <v>105109780.2</v>
+        <v>598174797.35</v>
       </c>
       <c r="J45" t="n">
-        <v>195506495.78</v>
+        <v>1134621766.82</v>
       </c>
       <c r="K45" t="n">
-        <v>14713064.62</v>
+        <v>61727827.88</v>
       </c>
       <c r="L45" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="M45" t="n">
-        <v>28.1</v>
+        <v>31.39</v>
       </c>
       <c r="N45" t="n">
-        <v>10124169012.25</v>
+        <v>55723284980.4</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600721.SH</t>
+          <t>600663.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>陆家嘴</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.11</v>
+        <v>11.12</v>
       </c>
       <c r="E46" t="n">
-        <v>1.2355</v>
+        <v>9.9901</v>
       </c>
       <c r="F46" t="n">
-        <v>36.5</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1847155692</v>
+        <v>784346232</v>
       </c>
       <c r="H46" t="n">
-        <v>201622643</v>
+        <v>160646705.91</v>
       </c>
       <c r="I46" t="n">
-        <v>135802878</v>
+        <v>289004500.07</v>
       </c>
       <c r="J46" t="n">
-        <v>337425521</v>
+        <v>449651205.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-65819765</v>
+        <v>128357794.16</v>
       </c>
       <c r="L46" t="n">
-        <v>-3.56</v>
+        <v>16.36</v>
       </c>
       <c r="M46" t="n">
-        <v>18.27</v>
+        <v>57.33</v>
       </c>
       <c r="N46" t="n">
-        <v>5041419494.85</v>
+        <v>44205328558.48</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600802.SH</t>
+          <t>600699.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>均胜电子</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7.24</v>
+        <v>21.11</v>
       </c>
       <c r="E47" t="n">
-        <v>4.3228</v>
+        <v>-10.0171</v>
       </c>
       <c r="F47" t="n">
-        <v>24.29</v>
+        <v>6.13</v>
       </c>
       <c r="G47" t="n">
-        <v>761625731</v>
+        <v>1849983929</v>
       </c>
       <c r="H47" t="n">
-        <v>74643242.97</v>
+        <v>230340015.86</v>
       </c>
       <c r="I47" t="n">
-        <v>80919909.94</v>
+        <v>127878922.78</v>
       </c>
       <c r="J47" t="n">
-        <v>155563152.91</v>
+        <v>358218938.64</v>
       </c>
       <c r="K47" t="n">
-        <v>6276666.97</v>
+        <v>-102461093.08</v>
       </c>
       <c r="L47" t="n">
-        <v>0.82</v>
+        <v>-5.54</v>
       </c>
       <c r="M47" t="n">
-        <v>20.43</v>
+        <v>19.36</v>
       </c>
       <c r="N47" t="n">
-        <v>3317718416</v>
+        <v>29462605584.93</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>600721.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.35</v>
+        <v>12.58</v>
       </c>
       <c r="E48" t="n">
-        <v>9.9894</v>
+        <v>-4.0427</v>
       </c>
       <c r="F48" t="n">
-        <v>1.34</v>
+        <v>24.54</v>
       </c>
       <c r="G48" t="n">
-        <v>292030560</v>
+        <v>1215941095</v>
       </c>
       <c r="H48" t="n">
-        <v>37033644</v>
+        <v>105965179</v>
       </c>
       <c r="I48" t="n">
-        <v>129076623.47</v>
+        <v>128303864</v>
       </c>
       <c r="J48" t="n">
-        <v>166110267.47</v>
+        <v>234269043</v>
       </c>
       <c r="K48" t="n">
-        <v>92042979.47</v>
+        <v>22338685</v>
       </c>
       <c r="L48" t="n">
-        <v>31.52</v>
+        <v>1.84</v>
       </c>
       <c r="M48" t="n">
-        <v>56.88</v>
+        <v>19.27</v>
       </c>
       <c r="N48" t="n">
-        <v>10814589247.5</v>
+        <v>4837609248.3</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>601091.SH</t>
+          <t>600802.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23.15</v>
+        <v>7.14</v>
       </c>
       <c r="E49" t="n">
-        <v>-8.0985</v>
+        <v>-1.3812</v>
       </c>
       <c r="F49" t="n">
-        <v>36.33</v>
+        <v>17.23</v>
       </c>
       <c r="G49" t="n">
-        <v>1837817144</v>
+        <v>572618337</v>
       </c>
       <c r="H49" t="n">
-        <v>181151229.54</v>
+        <v>49509944.38</v>
       </c>
       <c r="I49" t="n">
-        <v>137874551.7</v>
+        <v>52195372.48</v>
       </c>
       <c r="J49" t="n">
-        <v>319025781.24</v>
+        <v>101705316.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-43276677.84</v>
+        <v>2685428.1</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.35</v>
+        <v>0.47</v>
       </c>
       <c r="M49" t="n">
-        <v>17.36</v>
+        <v>17.76</v>
       </c>
       <c r="N49" t="n">
-        <v>4888427663.3</v>
+        <v>3271893576</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>603185.SH</t>
+          <t>600812.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>弘元绿能</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.15</v>
+        <v>5.48</v>
       </c>
       <c r="E50" t="n">
-        <v>10.0218</v>
+        <v>10.0402</v>
       </c>
       <c r="F50" t="n">
-        <v>2.48</v>
+        <v>5.27</v>
       </c>
       <c r="G50" t="n">
-        <v>245142444</v>
+        <v>494359000</v>
       </c>
       <c r="H50" t="n">
-        <v>56866895.74</v>
+        <v>32265002</v>
       </c>
       <c r="I50" t="n">
-        <v>91243438.23</v>
+        <v>72129398</v>
       </c>
       <c r="J50" t="n">
-        <v>148110333.97</v>
+        <v>104394400</v>
       </c>
       <c r="K50" t="n">
-        <v>34376542.49</v>
+        <v>39864396</v>
       </c>
       <c r="L50" t="n">
-        <v>14.02</v>
+        <v>8.06</v>
       </c>
       <c r="M50" t="n">
-        <v>60.42</v>
+        <v>21.12</v>
       </c>
       <c r="N50" t="n">
-        <v>10287186360.3</v>
+        <v>9402202427.6</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4515,227 +4514,227 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>603188.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>亚邦股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.4</v>
+        <v>11.39</v>
       </c>
       <c r="E51" t="n">
-        <v>9.9796</v>
+        <v>10.0483</v>
       </c>
       <c r="F51" t="n">
-        <v>5.76</v>
+        <v>0.54</v>
       </c>
       <c r="G51" t="n">
-        <v>289968645</v>
+        <v>64324547</v>
       </c>
       <c r="H51" t="n">
-        <v>48724506</v>
+        <v>10415016</v>
       </c>
       <c r="I51" t="n">
-        <v>69373194</v>
+        <v>39762490</v>
       </c>
       <c r="J51" t="n">
-        <v>118097700</v>
+        <v>50177506</v>
       </c>
       <c r="K51" t="n">
-        <v>20648688</v>
+        <v>29347474</v>
       </c>
       <c r="L51" t="n">
-        <v>7.12</v>
+        <v>45.62</v>
       </c>
       <c r="M51" t="n">
-        <v>40.73</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>3078918000</v>
+        <v>11901272611.5</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>603200.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>44.74</v>
+        <v>11.39</v>
       </c>
       <c r="E52" t="n">
-        <v>10.0074</v>
+        <v>10.0483</v>
       </c>
       <c r="F52" t="n">
-        <v>13.87</v>
+        <v>0.54</v>
       </c>
       <c r="G52" t="n">
-        <v>1214152011</v>
+        <v>515086700</v>
       </c>
       <c r="H52" t="n">
-        <v>98052652.09999999</v>
+        <v>515086700</v>
       </c>
       <c r="I52" t="n">
-        <v>169278541.38</v>
+        <v>515086800</v>
       </c>
       <c r="J52" t="n">
-        <v>267331193.48</v>
+        <v>515086800</v>
       </c>
       <c r="K52" t="n">
-        <v>71225889.28</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>22.02</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
-        <v>7850979808.22</v>
+        <v>11901272611.5</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>603230.SH</t>
+          <t>601091.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.01</v>
+        <v>24.2</v>
       </c>
       <c r="E53" t="n">
-        <v>-8.491199999999999</v>
+        <v>4.5356</v>
       </c>
       <c r="F53" t="n">
-        <v>17.01</v>
+        <v>38.82</v>
       </c>
       <c r="G53" t="n">
-        <v>912497116</v>
+        <v>1993050419</v>
       </c>
       <c r="H53" t="n">
-        <v>67738424.42</v>
+        <v>133699807.62</v>
       </c>
       <c r="I53" t="n">
-        <v>72190366.91</v>
+        <v>151054858.82</v>
       </c>
       <c r="J53" t="n">
-        <v>139928791.33</v>
+        <v>284754666.44</v>
       </c>
       <c r="K53" t="n">
-        <v>4451942.49</v>
+        <v>17355051.2</v>
       </c>
       <c r="L53" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="M53" t="n">
-        <v>15.33</v>
+        <v>14.29</v>
       </c>
       <c r="N53" t="n">
-        <v>4952857230</v>
+        <v>5110149004.4</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>603230.SH</t>
+          <t>603189.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>*ST网达</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.01</v>
+        <v>10.2</v>
       </c>
       <c r="E54" t="n">
-        <v>-8.491199999999999</v>
+        <v>10.0324</v>
       </c>
       <c r="F54" t="n">
-        <v>17.01</v>
+        <v>3.19</v>
       </c>
       <c r="G54" t="n">
-        <v>2187751413</v>
+        <v>85105250</v>
       </c>
       <c r="H54" t="n">
-        <v>121792566</v>
+        <v>22821920</v>
       </c>
       <c r="I54" t="n">
-        <v>139762697.91</v>
+        <v>19713386.97</v>
       </c>
       <c r="J54" t="n">
-        <v>261555263.91</v>
+        <v>42535306.97</v>
       </c>
       <c r="K54" t="n">
-        <v>17970131.91</v>
+        <v>-3108533.03</v>
       </c>
       <c r="L54" t="n">
-        <v>0.82</v>
+        <v>-3.65</v>
       </c>
       <c r="M54" t="n">
-        <v>11.96</v>
+        <v>49.98</v>
       </c>
       <c r="N54" t="n">
-        <v>4952857230</v>
+        <v>2749393159.8</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4749,37 +4748,37 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>20.43</v>
+        <v>21.44</v>
       </c>
       <c r="E55" t="n">
-        <v>-4.1295</v>
+        <v>4.9437</v>
       </c>
       <c r="F55" t="n">
-        <v>24.62</v>
+        <v>29.69</v>
       </c>
       <c r="G55" t="n">
-        <v>365479429</v>
+        <v>457048826</v>
       </c>
       <c r="H55" t="n">
-        <v>22086964.48</v>
+        <v>27520193.33</v>
       </c>
       <c r="I55" t="n">
-        <v>24587422.8</v>
+        <v>71000378.18000001</v>
       </c>
       <c r="J55" t="n">
-        <v>46674387.28</v>
+        <v>98520571.51000001</v>
       </c>
       <c r="K55" t="n">
-        <v>2500458.32</v>
+        <v>43480184.85</v>
       </c>
       <c r="L55" t="n">
-        <v>0.68</v>
+        <v>9.51</v>
       </c>
       <c r="M55" t="n">
-        <v>12.77</v>
+        <v>21.56</v>
       </c>
       <c r="N55" t="n">
-        <v>1460846148.93</v>
+        <v>1533066149.44</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4790,1470 +4789,1101 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>603396.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>33.5</v>
+        <v>29.46</v>
       </c>
       <c r="E56" t="n">
-        <v>-5.0454</v>
+        <v>3.043</v>
       </c>
       <c r="F56" t="n">
-        <v>23.57</v>
+        <v>25.68</v>
       </c>
       <c r="G56" t="n">
-        <v>1171989593</v>
+        <v>2502003519</v>
       </c>
       <c r="H56" t="n">
-        <v>178104337.14</v>
+        <v>427480314.59</v>
       </c>
       <c r="I56" t="n">
-        <v>182357665.4</v>
+        <v>236980587.28</v>
       </c>
       <c r="J56" t="n">
-        <v>360462002.54</v>
+        <v>664460901.87</v>
       </c>
       <c r="K56" t="n">
-        <v>4253328.26</v>
+        <v>-190499727.31</v>
       </c>
       <c r="L56" t="n">
-        <v>0.36</v>
+        <v>-7.61</v>
       </c>
       <c r="M56" t="n">
-        <v>30.76</v>
+        <v>26.56</v>
       </c>
       <c r="N56" t="n">
-        <v>4640670513</v>
+        <v>9925661756.459999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>603400.SH</t>
+          <t>603773.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>华之杰</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>53</v>
+        <v>80.7</v>
       </c>
       <c r="E57" t="n">
-        <v>-3.0547</v>
+        <v>-10.0033</v>
       </c>
       <c r="F57" t="n">
-        <v>29.36</v>
+        <v>10.81</v>
       </c>
       <c r="G57" t="n">
-        <v>603957408</v>
+        <v>2041815052</v>
       </c>
       <c r="H57" t="n">
-        <v>116474870.78</v>
+        <v>278949854.85</v>
       </c>
       <c r="I57" t="n">
-        <v>89000265.7</v>
+        <v>254224651.88</v>
       </c>
       <c r="J57" t="n">
-        <v>205475136.48</v>
+        <v>533174506.73</v>
       </c>
       <c r="K57" t="n">
-        <v>-27474605.08</v>
+        <v>-24725202.97</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.55</v>
+        <v>-1.21</v>
       </c>
       <c r="M57" t="n">
-        <v>34.02</v>
+        <v>26.11</v>
       </c>
       <c r="N57" t="n">
-        <v>1920193975</v>
+        <v>18131565683.1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603739.SH</t>
+          <t>603906.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>蔚蓝生物</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.04</v>
+        <v>20.94</v>
       </c>
       <c r="E58" t="n">
-        <v>10.0313</v>
+        <v>9.978999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>3.64</v>
+        <v>14.89</v>
       </c>
       <c r="G58" t="n">
-        <v>127913740</v>
+        <v>2393681611</v>
       </c>
       <c r="H58" t="n">
-        <v>18506698</v>
+        <v>198599701.14</v>
       </c>
       <c r="I58" t="n">
-        <v>23471474.6</v>
+        <v>312657062.17</v>
       </c>
       <c r="J58" t="n">
-        <v>41978172.6</v>
+        <v>511256763.31</v>
       </c>
       <c r="K58" t="n">
-        <v>4964776.6</v>
+        <v>114057361.03</v>
       </c>
       <c r="L58" t="n">
-        <v>3.88</v>
+        <v>4.76</v>
       </c>
       <c r="M58" t="n">
-        <v>32.82</v>
+        <v>21.36</v>
       </c>
       <c r="N58" t="n">
-        <v>3552525278.64</v>
+        <v>11789146772.82</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603797.SH</t>
+          <t>603928.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>联泰环保</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.82</v>
+        <v>14.38</v>
       </c>
       <c r="E59" t="n">
-        <v>-10.0746</v>
+        <v>10.023</v>
       </c>
       <c r="F59" t="n">
-        <v>5.66</v>
+        <v>7.56</v>
       </c>
       <c r="G59" t="n">
-        <v>159874743</v>
+        <v>363872133</v>
       </c>
       <c r="H59" t="n">
-        <v>22407007.48</v>
+        <v>116258886.05</v>
       </c>
       <c r="I59" t="n">
-        <v>25434885</v>
+        <v>44517643.93</v>
       </c>
       <c r="J59" t="n">
-        <v>47841892.48</v>
+        <v>160776529.98</v>
       </c>
       <c r="K59" t="n">
-        <v>3027877.52</v>
+        <v>-71741242.12</v>
       </c>
       <c r="L59" t="n">
-        <v>1.89</v>
+        <v>-19.72</v>
       </c>
       <c r="M59" t="n">
-        <v>29.92</v>
+        <v>44.18</v>
       </c>
       <c r="N59" t="n">
-        <v>2779237015.8</v>
+        <v>4899323520</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>605011.SH</t>
+          <t>603928.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>杭州热电</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>19.21</v>
+        <v>14.38</v>
       </c>
       <c r="E60" t="n">
-        <v>10.0229</v>
+        <v>10.023</v>
       </c>
       <c r="F60" t="n">
-        <v>3.06</v>
+        <v>7.56</v>
       </c>
       <c r="G60" t="n">
-        <v>231188954</v>
+        <v>495783866</v>
       </c>
       <c r="H60" t="n">
-        <v>33148129.69</v>
+        <v>124434685.05</v>
       </c>
       <c r="I60" t="n">
-        <v>48590613.7</v>
+        <v>103858012.48</v>
       </c>
       <c r="J60" t="n">
-        <v>81738743.39</v>
+        <v>228292697.53</v>
       </c>
       <c r="K60" t="n">
-        <v>15442484.01</v>
+        <v>-20576672.57</v>
       </c>
       <c r="L60" t="n">
-        <v>6.68</v>
+        <v>-4.15</v>
       </c>
       <c r="M60" t="n">
-        <v>35.36</v>
+        <v>46.05</v>
       </c>
       <c r="N60" t="n">
-        <v>7685921000</v>
+        <v>4899323520</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>605058.SH</t>
+          <t>605388.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>均瑶健康</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>53.64</v>
+        <v>6.93</v>
       </c>
       <c r="E61" t="n">
-        <v>-10</v>
+        <v>-6.2246</v>
       </c>
       <c r="F61" t="n">
-        <v>9.289999999999999</v>
+        <v>12.48</v>
       </c>
       <c r="G61" t="n">
-        <v>731314166</v>
+        <v>547241611</v>
       </c>
       <c r="H61" t="n">
-        <v>92697732.86</v>
+        <v>75868702.81</v>
       </c>
       <c r="I61" t="n">
-        <v>85479504.68000001</v>
+        <v>50007617.2</v>
       </c>
       <c r="J61" t="n">
-        <v>178177237.54</v>
+        <v>125876320.01</v>
       </c>
       <c r="K61" t="n">
-        <v>-7218228.18</v>
+        <v>-25861085.61</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.99</v>
+        <v>-4.73</v>
       </c>
       <c r="M61" t="n">
-        <v>24.36</v>
+        <v>23</v>
       </c>
       <c r="N61" t="n">
-        <v>7666503436.8</v>
+        <v>4161354120</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>605162.SH</t>
+          <t>688048.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>新中港</t>
+          <t>长光华芯</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.59</v>
+        <v>231.76</v>
       </c>
       <c r="E62" t="n">
-        <v>-10.0255</v>
+        <v>-20</v>
       </c>
       <c r="F62" t="n">
-        <v>7.35</v>
+        <v>7.14</v>
       </c>
       <c r="G62" t="n">
-        <v>363951233</v>
+        <v>2997676800</v>
       </c>
       <c r="H62" t="n">
-        <v>27665456.65</v>
+        <v>790458640.9400001</v>
       </c>
       <c r="I62" t="n">
-        <v>18916329</v>
+        <v>481482264.22</v>
       </c>
       <c r="J62" t="n">
-        <v>46581785.65</v>
+        <v>1271940905.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-8749127.65</v>
+        <v>-308976376.72</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.4</v>
+        <v>-10.31</v>
       </c>
       <c r="M62" t="n">
-        <v>12.8</v>
+        <v>42.43</v>
       </c>
       <c r="N62" t="n">
-        <v>4689742433.49</v>
+        <v>40854639589.68</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>605258.SH</t>
+          <t>688196.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>协和电子</t>
+          <t>卓越新能</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>39.61</v>
+        <v>36.12</v>
       </c>
       <c r="E63" t="n">
-        <v>-9.9977</v>
+        <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>9.84</v>
+        <v>5.03</v>
       </c>
       <c r="G63" t="n">
-        <v>351757940</v>
+        <v>217545100</v>
       </c>
       <c r="H63" t="n">
-        <v>58241994</v>
+        <v>29114635.5</v>
       </c>
       <c r="I63" t="n">
-        <v>77944561</v>
+        <v>74914422.16</v>
       </c>
       <c r="J63" t="n">
-        <v>136186555</v>
+        <v>104029057.66</v>
       </c>
       <c r="K63" t="n">
-        <v>19702567</v>
+        <v>45799786.66</v>
       </c>
       <c r="L63" t="n">
-        <v>5.6</v>
+        <v>21.05</v>
       </c>
       <c r="M63" t="n">
-        <v>38.72</v>
+        <v>47.82</v>
       </c>
       <c r="N63" t="n">
-        <v>3485680000</v>
+        <v>4594131515.4</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>605303.SH</t>
+          <t>688313.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>仕佳光子</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>28.66</v>
+        <v>127.6</v>
       </c>
       <c r="E64" t="n">
-        <v>10.0192</v>
+        <v>-17.4003</v>
       </c>
       <c r="F64" t="n">
-        <v>0.11</v>
+        <v>8.1</v>
       </c>
       <c r="G64" t="n">
-        <v>4940984</v>
+        <v>4864029600</v>
       </c>
       <c r="H64" t="n">
-        <v>1089080</v>
+        <v>952095821.77</v>
       </c>
       <c r="I64" t="n">
-        <v>4940984</v>
+        <v>1087411679.98</v>
       </c>
       <c r="J64" t="n">
-        <v>6030064</v>
+        <v>2039507501.75</v>
       </c>
       <c r="K64" t="n">
-        <v>3851904</v>
+        <v>135315858.21</v>
       </c>
       <c r="L64" t="n">
-        <v>77.95999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="M64" t="n">
-        <v>122.04</v>
+        <v>41.93</v>
       </c>
       <c r="N64" t="n">
-        <v>4621064113.28</v>
+        <v>57673455452.8</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>605303.SH</t>
+          <t>688498.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28.66</v>
+        <v>1290.4</v>
       </c>
       <c r="E65" t="n">
-        <v>10.0192</v>
+        <v>-20</v>
       </c>
       <c r="F65" t="n">
-        <v>0.11</v>
+        <v>4.48</v>
       </c>
       <c r="G65" t="n">
-        <v>11549869</v>
+        <v>7298435200</v>
       </c>
       <c r="H65" t="n">
-        <v>1684185</v>
+        <v>1859170030.03</v>
       </c>
       <c r="I65" t="n">
-        <v>11388871</v>
+        <v>1518283151.96</v>
       </c>
       <c r="J65" t="n">
-        <v>13073056</v>
+        <v>3377453181.99</v>
       </c>
       <c r="K65" t="n">
-        <v>9704686</v>
+        <v>-340886878.07</v>
       </c>
       <c r="L65" t="n">
-        <v>84.02</v>
+        <v>-4.67</v>
       </c>
       <c r="M65" t="n">
-        <v>113.19</v>
+        <v>46.28</v>
       </c>
       <c r="N65" t="n">
-        <v>4621064113.28</v>
+        <v>158580022617.6</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>605388.SH</t>
+          <t>688578.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>艾力斯</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.39</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>9.9702</v>
+        <v>-20.0036</v>
       </c>
       <c r="F66" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="G66" t="n">
-        <v>214211034</v>
+        <v>598347300</v>
       </c>
       <c r="H66" t="n">
-        <v>35142142</v>
+        <v>100011972.41</v>
       </c>
       <c r="I66" t="n">
-        <v>46052169</v>
+        <v>193555467.64</v>
       </c>
       <c r="J66" t="n">
-        <v>81194311</v>
+        <v>293567440.05</v>
       </c>
       <c r="K66" t="n">
-        <v>10910027</v>
+        <v>93543495.23</v>
       </c>
       <c r="L66" t="n">
-        <v>5.09</v>
+        <v>15.63</v>
       </c>
       <c r="M66" t="n">
-        <v>37.9</v>
+        <v>49.06</v>
       </c>
       <c r="N66" t="n">
-        <v>4437576760</v>
+        <v>40167000000</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>688137.SH</t>
+          <t>688806.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>近岸蛋白</t>
+          <t>泰诺麦博</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>160.39</v>
+        <v>27.15</v>
       </c>
       <c r="E67" t="n">
-        <v>13.4701</v>
+        <v>-11.477</v>
       </c>
       <c r="F67" t="n">
-        <v>14.92</v>
+        <v>31.23</v>
       </c>
       <c r="G67" t="n">
-        <v>4152432500</v>
+        <v>451776000</v>
       </c>
       <c r="H67" t="n">
-        <v>345906661.61</v>
+        <v>64777690.18</v>
       </c>
       <c r="I67" t="n">
-        <v>500648881.57</v>
+        <v>60965401.23</v>
       </c>
       <c r="J67" t="n">
-        <v>846555543.1799999</v>
+        <v>125743091.41</v>
       </c>
       <c r="K67" t="n">
-        <v>154742219.96</v>
+        <v>-3812288.95</v>
       </c>
       <c r="L67" t="n">
-        <v>3.73</v>
+        <v>-0.84</v>
       </c>
       <c r="M67" t="n">
-        <v>20.39</v>
+        <v>27.83</v>
       </c>
       <c r="N67" t="n">
-        <v>11214060286.67</v>
+        <v>1385346669</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>688137.SH</t>
+          <t>920025.BJ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>近岸蛋白</t>
+          <t>凯达重工</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>160.39</v>
+        <v>12.62</v>
       </c>
       <c r="E68" t="n">
-        <v>13.4701</v>
+        <v>1.0408</v>
       </c>
       <c r="F68" t="n">
-        <v>14.92</v>
+        <v>26.58</v>
       </c>
       <c r="G68" t="n">
-        <v>11697284100</v>
+        <v>168695600</v>
       </c>
       <c r="H68" t="n">
-        <v>11697284200</v>
+        <v>27743460.07</v>
       </c>
       <c r="I68" t="n">
-        <v>11697284100</v>
+        <v>26626221.45</v>
       </c>
       <c r="J68" t="n">
-        <v>11697284100</v>
+        <v>54369681.52</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-1117238.62</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="M68" t="n">
-        <v>100</v>
+        <v>32.23</v>
       </c>
       <c r="N68" t="n">
-        <v>11214060286.67</v>
+        <v>643620000</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>688185.SH</t>
+          <t>920201.BJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>康希诺</t>
+          <t>百瑞吉</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>102.64</v>
+        <v>39.01</v>
       </c>
       <c r="E69" t="n">
-        <v>20.0047</v>
+        <v>-7.2956</v>
       </c>
       <c r="F69" t="n">
-        <v>9.32</v>
+        <v>30.93</v>
       </c>
       <c r="G69" t="n">
-        <v>1065144300</v>
+        <v>94426400</v>
       </c>
       <c r="H69" t="n">
-        <v>155932921.71</v>
+        <v>17790706.51</v>
       </c>
       <c r="I69" t="n">
-        <v>202059786.95</v>
+        <v>26893047.7</v>
       </c>
       <c r="J69" t="n">
-        <v>357992708.66</v>
+        <v>44683754.21</v>
       </c>
       <c r="K69" t="n">
-        <v>46126865.24</v>
+        <v>9102341.189999999</v>
       </c>
       <c r="L69" t="n">
-        <v>4.33</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>33.61</v>
+        <v>47.32</v>
       </c>
       <c r="N69" t="n">
-        <v>11739234558.64</v>
+        <v>296806297.67</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>688185.SH</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>康希诺</t>
+          <t>安达股份</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>102.64</v>
+        <v>14.3</v>
       </c>
       <c r="E70" t="n">
-        <v>20.0047</v>
+        <v>-21.9432</v>
       </c>
       <c r="F70" t="n">
-        <v>9.32</v>
+        <v>48.96</v>
       </c>
       <c r="G70" t="n">
-        <v>2765387200</v>
+        <v>177659400</v>
       </c>
       <c r="H70" t="n">
-        <v>333942031.09</v>
+        <v>21837052.7</v>
       </c>
       <c r="I70" t="n">
-        <v>420081838.81</v>
+        <v>16135353.5</v>
       </c>
       <c r="J70" t="n">
-        <v>754023869.9</v>
+        <v>37972406.2</v>
       </c>
       <c r="K70" t="n">
-        <v>86139807.72</v>
+        <v>-5701699.2</v>
       </c>
       <c r="L70" t="n">
-        <v>3.11</v>
+        <v>-3.21</v>
       </c>
       <c r="M70" t="n">
-        <v>27.27</v>
+        <v>21.37</v>
       </c>
       <c r="N70" t="n">
-        <v>11739234558.64</v>
+        <v>340340000</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>688265.SH</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>南模生物</t>
+          <t>安达股份</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>64.98</v>
+        <v>14.3</v>
       </c>
       <c r="E71" t="n">
-        <v>19.8672</v>
+        <v>-21.9432</v>
       </c>
       <c r="F71" t="n">
-        <v>8.609999999999999</v>
+        <v>48.96</v>
       </c>
       <c r="G71" t="n">
-        <v>412269900</v>
+        <v>496081800</v>
       </c>
       <c r="H71" t="n">
-        <v>59002303.13</v>
+        <v>37015232.31</v>
       </c>
       <c r="I71" t="n">
-        <v>73467526.61</v>
+        <v>46618212.99</v>
       </c>
       <c r="J71" t="n">
-        <v>132469829.74</v>
+        <v>83633445.3</v>
       </c>
       <c r="K71" t="n">
-        <v>14465223.48</v>
+        <v>9602980.68</v>
       </c>
       <c r="L71" t="n">
-        <v>3.51</v>
+        <v>1.94</v>
       </c>
       <c r="M71" t="n">
-        <v>32.13</v>
+        <v>16.86</v>
       </c>
       <c r="N71" t="n">
-        <v>5066069074.74</v>
+        <v>340340000</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>688265.SH</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>南模生物</t>
+          <t>力王股份</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>64.98</v>
+        <v>17.83</v>
       </c>
       <c r="E72" t="n">
-        <v>19.8672</v>
+        <v>29.9563</v>
       </c>
       <c r="F72" t="n">
-        <v>8.609999999999999</v>
+        <v>25.69</v>
       </c>
       <c r="G72" t="n">
-        <v>790072500</v>
+        <v>213939200</v>
       </c>
       <c r="H72" t="n">
-        <v>139589652.73</v>
+        <v>17020893.9</v>
       </c>
       <c r="I72" t="n">
-        <v>136580679.64</v>
+        <v>32643239.34</v>
       </c>
       <c r="J72" t="n">
-        <v>276170332.37</v>
+        <v>49664133.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-3008973.09</v>
+        <v>15622345.44</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.38</v>
+        <v>7.3</v>
       </c>
       <c r="M72" t="n">
-        <v>34.96</v>
+        <v>23.21</v>
       </c>
       <c r="N72" t="n">
-        <v>5066069074.74</v>
+        <v>875408425</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>688806.SH</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>泰诺麦博</t>
+          <t>力王股份</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30.67</v>
+        <v>17.83</v>
       </c>
       <c r="E73" t="n">
-        <v>19.9922</v>
+        <v>29.9563</v>
       </c>
       <c r="F73" t="n">
-        <v>23.59</v>
+        <v>25.69</v>
       </c>
       <c r="G73" t="n">
-        <v>350550300</v>
+        <v>287974500</v>
       </c>
       <c r="H73" t="n">
-        <v>36771999.63</v>
+        <v>30515041.64</v>
       </c>
       <c r="I73" t="n">
-        <v>69724300.81999999</v>
+        <v>40053504.63</v>
       </c>
       <c r="J73" t="n">
-        <v>106496300.45</v>
+        <v>70568546.27</v>
       </c>
       <c r="K73" t="n">
-        <v>32952301.19</v>
+        <v>9538462.99</v>
       </c>
       <c r="L73" t="n">
-        <v>9.4</v>
+        <v>3.31</v>
       </c>
       <c r="M73" t="n">
-        <v>30.38</v>
+        <v>24.51</v>
       </c>
       <c r="N73" t="n">
-        <v>1564956992.2</v>
+        <v>875408425</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>688837.SH</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>信诺维</t>
+          <t>武汉蓝电</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>49.4</v>
+        <v>33.13</v>
       </c>
       <c r="E74" t="n">
-        <v>13.2768</v>
+        <v>15.8392</v>
       </c>
       <c r="F74" t="n">
-        <v>37.29</v>
+        <v>40.86</v>
       </c>
       <c r="G74" t="n">
-        <v>856739000</v>
+        <v>258518200</v>
       </c>
       <c r="H74" t="n">
-        <v>88029390.53</v>
+        <v>25608051.69</v>
       </c>
       <c r="I74" t="n">
-        <v>83176071.28</v>
+        <v>25649205.87</v>
       </c>
       <c r="J74" t="n">
-        <v>171205461.81</v>
+        <v>51257257.56</v>
       </c>
       <c r="K74" t="n">
-        <v>-4853319.25</v>
+        <v>41154.18</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.57</v>
+        <v>0.02</v>
       </c>
       <c r="M74" t="n">
-        <v>19.98</v>
+        <v>19.83</v>
       </c>
       <c r="N74" t="n">
-        <v>2400542908.4</v>
+        <v>663262666.26</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+          <t>当日价格振幅达到30%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>920025.BJ</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>凯达重工</t>
+          <t>武汉蓝电</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.49</v>
+        <v>33.13</v>
       </c>
       <c r="E75" t="n">
-        <v>-5.6647</v>
+        <v>15.8392</v>
       </c>
       <c r="F75" t="n">
-        <v>27.45</v>
+        <v>40.86</v>
       </c>
       <c r="G75" t="n">
-        <v>180966600</v>
+        <v>663285800</v>
       </c>
       <c r="H75" t="n">
-        <v>26152177.2</v>
+        <v>66569614.56</v>
       </c>
       <c r="I75" t="n">
-        <v>26881593.38</v>
+        <v>74059746.19</v>
       </c>
       <c r="J75" t="n">
-        <v>53033770.58</v>
+        <v>140629360.75</v>
       </c>
       <c r="K75" t="n">
-        <v>729416.1800000001</v>
+        <v>7490131.63</v>
       </c>
       <c r="L75" t="n">
-        <v>0.4</v>
+        <v>1.13</v>
       </c>
       <c r="M75" t="n">
-        <v>29.31</v>
+        <v>21.2</v>
       </c>
       <c r="N75" t="n">
-        <v>636990000</v>
+        <v>663262666.26</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>920201.BJ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>百瑞吉</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-8.5814</v>
-      </c>
-      <c r="F76" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>120725900</v>
-      </c>
-      <c r="H76" t="n">
-        <v>18309507.81</v>
-      </c>
-      <c r="I76" t="n">
-        <v>17336184.7</v>
-      </c>
-      <c r="J76" t="n">
-        <v>35645692.51</v>
-      </c>
-      <c r="K76" t="n">
-        <v>-973323.11</v>
-      </c>
-      <c r="L76" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="M76" t="n">
-        <v>29.53</v>
-      </c>
-      <c r="N76" t="n">
-        <v>320164291.36</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>920201.BJ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>百瑞吉</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-8.5814</v>
-      </c>
-      <c r="F77" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G77" t="n">
-        <v>538731900</v>
-      </c>
-      <c r="H77" t="n">
-        <v>47756180.97</v>
-      </c>
-      <c r="I77" t="n">
-        <v>70178276.73999999</v>
-      </c>
-      <c r="J77" t="n">
-        <v>117934457.71</v>
-      </c>
-      <c r="K77" t="n">
-        <v>22422095.77</v>
-      </c>
-      <c r="L77" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="M77" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="N77" t="n">
-        <v>320164291.36</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
           <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>920202.BJ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>安达股份</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-29.9694</v>
-      </c>
-      <c r="F78" t="n">
-        <v>66.59</v>
-      </c>
-      <c r="G78" t="n">
-        <v>318422400</v>
-      </c>
-      <c r="H78" t="n">
-        <v>28697285.78</v>
-      </c>
-      <c r="I78" t="n">
-        <v>33807128.15</v>
-      </c>
-      <c r="J78" t="n">
-        <v>62504413.93</v>
-      </c>
-      <c r="K78" t="n">
-        <v>5109842.37</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M78" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="N78" t="n">
-        <v>436016000</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>920229.BJ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>世纪数码</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>46.11</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-6.1661</v>
-      </c>
-      <c r="F79" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="G79" t="n">
-        <v>178223700</v>
-      </c>
-      <c r="H79" t="n">
-        <v>22567063.55</v>
-      </c>
-      <c r="I79" t="n">
-        <v>24166002.68</v>
-      </c>
-      <c r="J79" t="n">
-        <v>46733066.23</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1598939.13</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M79" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="N79" t="n">
-        <v>523348500</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>920779.BJ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>武汉蓝电</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.7042</v>
-      </c>
-      <c r="F80" t="n">
-        <v>40.47</v>
-      </c>
-      <c r="G80" t="n">
-        <v>242030900</v>
-      </c>
-      <c r="H80" t="n">
-        <v>51081752.99</v>
-      </c>
-      <c r="I80" t="n">
-        <v>21570398.4</v>
-      </c>
-      <c r="J80" t="n">
-        <v>72652151.39</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-29511354.59</v>
-      </c>
-      <c r="L80" t="n">
-        <v>-12.19</v>
-      </c>
-      <c r="M80" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="N80" t="n">
-        <v>572572057.2</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>trade_date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>exchange_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rzye</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rzmre</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rzche</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>rqye</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>rqmcl</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>rzrqye</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>rqyl</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>20260930</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SSE</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1296520652053</v>
-      </c>
-      <c r="D2" t="n">
-        <v>62006897126</v>
-      </c>
-      <c r="E2" t="n">
-        <v>84893467937</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18892593376</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55369387</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1315413245429</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3220216902</v>
       </c>
     </row>
   </sheetData>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>5559</v>
       </c>
       <c r="C2" t="n">
-        <v>1698</v>
+        <v>3297</v>
       </c>
       <c r="D2" t="n">
-        <v>3748</v>
+        <v>2145</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F2" t="n">
-        <v>16942.91</v>
+        <v>19166.92</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3811.9043</v>
+        <v>3813.7913</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.79</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="n">
-        <v>8111.83</v>
+        <v>8885.610000000001</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12620.897</v>
+        <v>12641.8584</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.07</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>4411.05</v>
+        <v>5096.94</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3036.6573</v>
+        <v>3043.3346</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.15</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>1760.38</v>
+        <v>2005.97</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4310.2765</v>
+        <v>4317.2549</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.09</v>
+        <v>0.16</v>
       </c>
       <c r="F5" t="n">
-        <v>4462.08</v>
+        <v>4961.79</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1456.3239</v>
+        <v>1457.2665</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.82</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>823.98</v>
+        <v>919.73</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7138.584</v>
+        <v>7155.9114</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2</v>
+        <v>0.24</v>
       </c>
       <c r="F7" t="n">
-        <v>3240.05</v>
+        <v>3862.83</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18365.14</v>
+        <v>20929.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20929.06</v>
+        <v>20481.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20481.34</v>
+        <v>21536.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21536.52</v>
+        <v>17831.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17831.28</v>
+        <v>16691.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17167.12</v>
+        <v>14215.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14215.96</v>
+        <v>14500.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14500.77</v>
+        <v>16942.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16942.91</v>
+        <v>19166.92</v>
       </c>
     </row>
   </sheetData>
@@ -877,157 +877,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>920157.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13.78</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>17.83</v>
+        <v>86.38</v>
       </c>
       <c r="E2" t="n">
-        <v>13.53</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>17.83</v>
+        <v>75.55</v>
       </c>
       <c r="G2" t="n">
-        <v>13.72</v>
+        <v>13.75</v>
       </c>
       <c r="H2" t="n">
-        <v>4.11</v>
+        <v>61.8</v>
       </c>
       <c r="I2" t="n">
-        <v>29.9563</v>
+        <v>449.4545</v>
       </c>
       <c r="J2" t="n">
-        <v>126131.57</v>
+        <v>122020.63</v>
       </c>
       <c r="K2" t="n">
-        <v>213939.18755</v>
+        <v>958833.20633</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300522.SZ</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.49</v>
+        <v>17.17</v>
       </c>
       <c r="D3" t="n">
-        <v>16.56</v>
+        <v>23.17</v>
       </c>
       <c r="E3" t="n">
-        <v>14.29</v>
+        <v>17.12</v>
       </c>
       <c r="F3" t="n">
-        <v>16.56</v>
+        <v>22.13</v>
       </c>
       <c r="G3" t="n">
-        <v>13.8</v>
+        <v>17.83</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>24.1167</v>
       </c>
       <c r="J3" t="n">
-        <v>261136.21</v>
+        <v>175694.48</v>
       </c>
       <c r="K3" t="n">
-        <v>419527.37476</v>
+        <v>357229.39702</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688196.SH</t>
+          <t>920021.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.35</v>
+        <v>7.39</v>
       </c>
       <c r="D4" t="n">
-        <v>36.12</v>
+        <v>9.18</v>
       </c>
       <c r="E4" t="n">
-        <v>30.11</v>
+        <v>7.16</v>
       </c>
       <c r="F4" t="n">
-        <v>36.12</v>
+        <v>8.83</v>
       </c>
       <c r="G4" t="n">
-        <v>30.1</v>
+        <v>7.35</v>
       </c>
       <c r="H4" t="n">
-        <v>6.02</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>20.1361</v>
       </c>
       <c r="J4" t="n">
-        <v>63994.43</v>
+        <v>495461.84</v>
       </c>
       <c r="K4" t="n">
-        <v>217545.128</v>
+        <v>410490.50027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301697.SZ</t>
+          <t>300369.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26.81</v>
+        <v>8.69</v>
       </c>
       <c r="D5" t="n">
-        <v>31.51</v>
+        <v>10.43</v>
       </c>
       <c r="E5" t="n">
-        <v>26.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>31.51</v>
+        <v>10.43</v>
       </c>
       <c r="G5" t="n">
-        <v>26.26</v>
+        <v>8.69</v>
       </c>
       <c r="H5" t="n">
-        <v>5.25</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9924</v>
+        <v>20.023</v>
       </c>
       <c r="J5" t="n">
-        <v>203348.6</v>
+        <v>1056408.63</v>
       </c>
       <c r="K5" t="n">
-        <v>620816.46738</v>
+        <v>1006656.8124</v>
       </c>
     </row>
     <row r="6">
@@ -1038,230 +1038,230 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.92</v>
+        <v>26.41</v>
       </c>
       <c r="D6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G6" t="n">
         <v>24.08</v>
       </c>
-      <c r="E6" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="G6" t="n">
-        <v>20.07</v>
-      </c>
       <c r="H6" t="n">
-        <v>4.01</v>
+        <v>4.82</v>
       </c>
       <c r="I6" t="n">
-        <v>19.9801</v>
+        <v>20.0166</v>
       </c>
       <c r="J6" t="n">
-        <v>177258.63</v>
+        <v>258655.07</v>
       </c>
       <c r="K6" t="n">
-        <v>400319.98489</v>
+        <v>722835.17603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301513.SZ</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>15.3</v>
       </c>
       <c r="D7" t="n">
-        <v>67.81999999999999</v>
+        <v>17.15</v>
       </c>
       <c r="E7" t="n">
-        <v>53.82</v>
+        <v>15.3</v>
       </c>
       <c r="F7" t="n">
-        <v>67.81</v>
+        <v>17.15</v>
       </c>
       <c r="G7" t="n">
-        <v>56.52</v>
+        <v>14.29</v>
       </c>
       <c r="H7" t="n">
-        <v>11.29</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>19.9752</v>
+        <v>20.014</v>
       </c>
       <c r="J7" t="n">
-        <v>97198.28</v>
+        <v>1507200.16</v>
       </c>
       <c r="K7" t="n">
-        <v>597216.21584</v>
+        <v>2488094.39299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300619.SZ</t>
+          <t>300364.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24.45</v>
+        <v>20.37</v>
       </c>
       <c r="D8" t="n">
-        <v>28.75</v>
+        <v>24.47</v>
       </c>
       <c r="E8" t="n">
-        <v>24.07</v>
+        <v>20.11</v>
       </c>
       <c r="F8" t="n">
-        <v>28.17</v>
+        <v>24.47</v>
       </c>
       <c r="G8" t="n">
-        <v>23.96</v>
+        <v>20.39</v>
       </c>
       <c r="H8" t="n">
-        <v>4.21</v>
+        <v>4.08</v>
       </c>
       <c r="I8" t="n">
-        <v>17.571</v>
+        <v>20.0098</v>
       </c>
       <c r="J8" t="n">
-        <v>253409.77</v>
+        <v>831570.26</v>
       </c>
       <c r="K8" t="n">
-        <v>698192.8372</v>
+        <v>1850122.25523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>920779.BJ</t>
+          <t>688152.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.99</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>35.33</v>
+        <v>45.85</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>37.45</v>
       </c>
       <c r="F9" t="n">
-        <v>33.13</v>
+        <v>45.85</v>
       </c>
       <c r="G9" t="n">
-        <v>28.6</v>
+        <v>38.21</v>
       </c>
       <c r="H9" t="n">
-        <v>4.53</v>
+        <v>7.64</v>
       </c>
       <c r="I9" t="n">
-        <v>15.8392</v>
+        <v>19.9948</v>
       </c>
       <c r="J9" t="n">
-        <v>81795.67999999999</v>
+        <v>114547.42</v>
       </c>
       <c r="K9" t="n">
-        <v>258518.21368</v>
+        <v>482931.983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>920252.BJ</t>
+          <t>300981.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.03</v>
+        <v>19.33</v>
       </c>
       <c r="D10" t="n">
-        <v>17.44</v>
+        <v>23.36</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7</v>
+        <v>18.5</v>
       </c>
       <c r="F10" t="n">
-        <v>16.83</v>
+        <v>23.36</v>
       </c>
       <c r="G10" t="n">
-        <v>14.73</v>
+        <v>19.47</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>3.89</v>
       </c>
       <c r="I10" t="n">
-        <v>14.2566</v>
+        <v>19.9795</v>
       </c>
       <c r="J10" t="n">
-        <v>95834.02</v>
+        <v>350282.29</v>
       </c>
       <c r="K10" t="n">
-        <v>157146.85282</v>
+        <v>732402.93476</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>301395.SZ</t>
+          <t>300413.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.66</v>
+        <v>19.25</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>11.54</v>
+        <v>18.79</v>
       </c>
       <c r="F11" t="n">
-        <v>13.09</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>11.51</v>
+        <v>19.17</v>
       </c>
       <c r="H11" t="n">
-        <v>1.58</v>
+        <v>3.83</v>
       </c>
       <c r="I11" t="n">
-        <v>13.7272</v>
+        <v>19.9791</v>
       </c>
       <c r="J11" t="n">
-        <v>143617.15</v>
+        <v>1141206.62</v>
       </c>
       <c r="K11" t="n">
-        <v>182080.50116</v>
+        <v>2384983.29123</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920202.BJ</t>
+          <t>001246.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.35</v>
+        <v>50.9</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82</v>
+        <v>52.88</v>
       </c>
       <c r="E2" t="n">
-        <v>14.25</v>
+        <v>45.01</v>
       </c>
       <c r="F2" t="n">
-        <v>14.3</v>
+        <v>45.05</v>
       </c>
       <c r="G2" t="n">
-        <v>18.32</v>
+        <v>53.55</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.02</v>
+        <v>-8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>-21.9432</v>
+        <v>-15.873</v>
       </c>
       <c r="J2" t="n">
-        <v>116534.4</v>
+        <v>719258.23</v>
       </c>
       <c r="K2" t="n">
-        <v>177659.40963</v>
+        <v>3466031.17698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>688578.SH</t>
+          <t>300599.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>92.83</v>
+        <v>14.13</v>
       </c>
       <c r="D3" t="n">
-        <v>94.97</v>
+        <v>14.5</v>
       </c>
       <c r="E3" t="n">
-        <v>89.26000000000001</v>
+        <v>12.46</v>
       </c>
       <c r="F3" t="n">
-        <v>89.26000000000001</v>
+        <v>13.52</v>
       </c>
       <c r="G3" t="n">
-        <v>111.58</v>
+        <v>15.58</v>
       </c>
       <c r="H3" t="n">
-        <v>-22.32</v>
+        <v>-2.06</v>
       </c>
       <c r="I3" t="n">
-        <v>-20.0036</v>
+        <v>-13.2221</v>
       </c>
       <c r="J3" t="n">
-        <v>66252.28</v>
+        <v>396262.14</v>
       </c>
       <c r="K3" t="n">
-        <v>598347.316</v>
+        <v>525414.72092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688498.SH</t>
+          <t>002717.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1361</v>
+        <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1412.92</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1290.4</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1290.4</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1613</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-322.6</v>
+        <v>-0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>-20</v>
+        <v>-10.7143</v>
       </c>
       <c r="J4" t="n">
-        <v>55108.84</v>
+        <v>29339</v>
       </c>
       <c r="K4" t="n">
-        <v>7298435.24</v>
+        <v>1466.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688048.SH</t>
+          <t>300491.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250</v>
+        <v>31.61</v>
       </c>
       <c r="D5" t="n">
-        <v>255.55</v>
+        <v>31.82</v>
       </c>
       <c r="E5" t="n">
-        <v>231.76</v>
+        <v>27.13</v>
       </c>
       <c r="F5" t="n">
-        <v>231.76</v>
+        <v>28.9</v>
       </c>
       <c r="G5" t="n">
-        <v>289.7</v>
+        <v>32.17</v>
       </c>
       <c r="H5" t="n">
-        <v>-57.94</v>
+        <v>-3.27</v>
       </c>
       <c r="I5" t="n">
-        <v>-20</v>
+        <v>-10.1647</v>
       </c>
       <c r="J5" t="n">
-        <v>125875.79</v>
+        <v>206981.96</v>
       </c>
       <c r="K5" t="n">
-        <v>2997676.78</v>
+        <v>594450.26816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>001246.SZ</t>
+          <t>603073.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60.63</v>
+        <v>22.97</v>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>22.97</v>
       </c>
       <c r="E6" t="n">
-        <v>52.22</v>
+        <v>20.67</v>
       </c>
       <c r="F6" t="n">
-        <v>53.55</v>
+        <v>20.67</v>
       </c>
       <c r="G6" t="n">
-        <v>65.09</v>
+        <v>22.97</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.54</v>
+        <v>-2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.7293</v>
+        <v>-10.0131</v>
       </c>
       <c r="J6" t="n">
-        <v>678115.9399999999</v>
+        <v>95831</v>
       </c>
       <c r="K6" t="n">
-        <v>3919921.88831</v>
+        <v>201331.598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688313.SH</t>
+          <t>002962.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>137.95</v>
+        <v>15.9</v>
       </c>
       <c r="D7" t="n">
-        <v>142.48</v>
+        <v>15.9</v>
       </c>
       <c r="E7" t="n">
-        <v>126.3</v>
+        <v>15.02</v>
       </c>
       <c r="F7" t="n">
-        <v>127.6</v>
+        <v>15.02</v>
       </c>
       <c r="G7" t="n">
-        <v>154.48</v>
+        <v>16.69</v>
       </c>
       <c r="H7" t="n">
-        <v>-26.88</v>
+        <v>-1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>-17.4003</v>
+        <v>-10.006</v>
       </c>
       <c r="J7" t="n">
-        <v>366169.9</v>
+        <v>218946.31</v>
       </c>
       <c r="K7" t="n">
-        <v>4864029.55</v>
+        <v>333502.54913</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300684.SZ</t>
+          <t>603823.SH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>106.89</v>
+        <v>45.01</v>
       </c>
       <c r="D8" t="n">
-        <v>107.78</v>
+        <v>45.13</v>
       </c>
       <c r="E8" t="n">
-        <v>88.31</v>
+        <v>41.93</v>
       </c>
       <c r="F8" t="n">
-        <v>90.09999999999999</v>
+        <v>41.93</v>
       </c>
       <c r="G8" t="n">
-        <v>108.1</v>
+        <v>46.59</v>
       </c>
       <c r="H8" t="n">
-        <v>-18</v>
+        <v>-4.66</v>
       </c>
       <c r="I8" t="n">
-        <v>-16.6512</v>
+        <v>-10.0021</v>
       </c>
       <c r="J8" t="n">
-        <v>349379.32</v>
+        <v>203173.18</v>
       </c>
       <c r="K8" t="n">
-        <v>3344494.42134</v>
+        <v>855381.191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300804.SZ</t>
+          <t>002927.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>19.67</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>19.93</v>
       </c>
       <c r="E9" t="n">
-        <v>46.05</v>
+        <v>17.64</v>
       </c>
       <c r="F9" t="n">
-        <v>46.62</v>
+        <v>17.64</v>
       </c>
       <c r="G9" t="n">
-        <v>55.41</v>
+        <v>19.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.789999999999999</v>
+        <v>-1.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-15.8636</v>
+        <v>-10</v>
       </c>
       <c r="J9" t="n">
-        <v>51137.02</v>
+        <v>159631</v>
       </c>
       <c r="K9" t="n">
-        <v>249628.31863</v>
+        <v>289675.61275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688536.SH</t>
+          <t>603400.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>45.8</v>
       </c>
       <c r="D10" t="n">
-        <v>326</v>
+        <v>46.25</v>
       </c>
       <c r="E10" t="n">
-        <v>276.12</v>
+        <v>42.93</v>
       </c>
       <c r="F10" t="n">
-        <v>280</v>
+        <v>42.93</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>47.7</v>
       </c>
       <c r="H10" t="n">
-        <v>-47</v>
+        <v>-4.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.3731</v>
+        <v>-10</v>
       </c>
       <c r="J10" t="n">
-        <v>55227.02</v>
+        <v>65689.42999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>1629368.192</v>
+        <v>286680.592</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688036.SH</t>
+          <t>002487.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53.3</v>
+        <v>47.23</v>
       </c>
       <c r="D11" t="n">
-        <v>53.3</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>45.26</v>
+        <v>43.75</v>
       </c>
       <c r="F11" t="n">
-        <v>46.1</v>
+        <v>43.75</v>
       </c>
       <c r="G11" t="n">
-        <v>53.8</v>
+        <v>48.61</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.7</v>
+        <v>-4.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.3123</v>
+        <v>-9.9979</v>
       </c>
       <c r="J11" t="n">
-        <v>275608.33</v>
+        <v>1051507.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1300439.787</v>
+        <v>4957547.92194</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,161 +1819,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000513.SZ</t>
+          <t>000011.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.61</v>
+        <v>12.59</v>
       </c>
       <c r="E2" t="n">
-        <v>-10</v>
+        <v>3.8779</v>
       </c>
       <c r="F2" t="n">
-        <v>6.15</v>
+        <v>21.58</v>
       </c>
       <c r="G2" t="n">
-        <v>1064992550</v>
+        <v>1377987783</v>
       </c>
       <c r="H2" t="n">
-        <v>239848307.26</v>
+        <v>167478280.14</v>
       </c>
       <c r="I2" t="n">
-        <v>177476408.76</v>
+        <v>133387168.32</v>
       </c>
       <c r="J2" t="n">
-        <v>417324716.02</v>
+        <v>300865448.46</v>
       </c>
       <c r="K2" t="n">
-        <v>-62371898.5</v>
+        <v>-34091111.82</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.86</v>
+        <v>-2.47</v>
       </c>
       <c r="M2" t="n">
-        <v>39.19</v>
+        <v>21.83</v>
       </c>
       <c r="N2" t="n">
-        <v>16808169442.68</v>
+        <v>6837227287.24</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000678.SZ</t>
+          <t>000420.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.24</v>
+        <v>3.81</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.0427</v>
+        <v>10.1156</v>
       </c>
       <c r="F3" t="n">
-        <v>28.23</v>
+        <v>9.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1684516377</v>
+        <v>893374748</v>
       </c>
       <c r="H3" t="n">
-        <v>318066578</v>
+        <v>55135495.22</v>
       </c>
       <c r="I3" t="n">
-        <v>232681777.63</v>
+        <v>233514396.34</v>
       </c>
       <c r="J3" t="n">
-        <v>550748355.63</v>
+        <v>288649891.56</v>
       </c>
       <c r="K3" t="n">
-        <v>-85384800.37</v>
+        <v>178378901.12</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.07</v>
+        <v>19.97</v>
       </c>
       <c r="M3" t="n">
-        <v>32.69</v>
+        <v>32.31</v>
       </c>
       <c r="N3" t="n">
-        <v>5625648395.28</v>
+        <v>9367934056.83</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000710.SZ</t>
+          <t>000678.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>贝瑞基因</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.27</v>
+        <v>12.62</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.5198</v>
+        <v>3.1046</v>
       </c>
       <c r="F4" t="n">
-        <v>26.12</v>
+        <v>26.56</v>
       </c>
       <c r="G4" t="n">
-        <v>965448630</v>
+        <v>1454170493</v>
       </c>
       <c r="H4" t="n">
-        <v>144701834.19</v>
+        <v>193749490.99</v>
       </c>
       <c r="I4" t="n">
-        <v>96337842.73999999</v>
+        <v>175303749.55</v>
       </c>
       <c r="J4" t="n">
-        <v>241039676.93</v>
+        <v>369053240.54</v>
       </c>
       <c r="K4" t="n">
-        <v>-48363991.45</v>
+        <v>-18445741.44</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.01</v>
+        <v>-1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>24.97</v>
+        <v>25.38</v>
       </c>
       <c r="N4" t="n">
-        <v>3445865966.66</v>
+        <v>5800300878.14</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1984,62 +1984,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000850.SZ</t>
+          <t>000911.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>*ST广糖</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.03</v>
+        <v>6.06</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.3573</v>
+        <v>7.2566</v>
       </c>
       <c r="F5" t="n">
-        <v>8.960000000000001</v>
+        <v>5.28</v>
       </c>
       <c r="G5" t="n">
-        <v>1082459473</v>
+        <v>269457465</v>
       </c>
       <c r="H5" t="n">
-        <v>112760076.65</v>
+        <v>53700708</v>
       </c>
       <c r="I5" t="n">
-        <v>77717221.92</v>
+        <v>36102266</v>
       </c>
       <c r="J5" t="n">
-        <v>190477298.57</v>
+        <v>89802974</v>
       </c>
       <c r="K5" t="n">
-        <v>-35042854.73</v>
+        <v>-17598442</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.24</v>
+        <v>-6.53</v>
       </c>
       <c r="M5" t="n">
-        <v>17.6</v>
+        <v>33.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3801798747.37</v>
+        <v>2425938097.08</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2053,92 +2053,92 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.56</v>
+        <v>22.75</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.0076</v>
+        <v>-3.438</v>
       </c>
       <c r="F6" t="n">
-        <v>7.17</v>
+        <v>14.89</v>
       </c>
       <c r="G6" t="n">
-        <v>422116630</v>
+        <v>1951239174</v>
       </c>
       <c r="H6" t="n">
-        <v>42119756</v>
+        <v>138646197.46</v>
       </c>
       <c r="I6" t="n">
-        <v>28573375</v>
+        <v>111797870.56</v>
       </c>
       <c r="J6" t="n">
-        <v>70693131</v>
+        <v>250444068.02</v>
       </c>
       <c r="K6" t="n">
-        <v>-13546381</v>
+        <v>-26848326.9</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.21</v>
+        <v>-1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>16.75</v>
+        <v>12.84</v>
       </c>
       <c r="N6" t="n">
-        <v>5815460848.44</v>
+        <v>5615523527.25</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002074.SZ</t>
+          <t>001300.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>三柏硕</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.3</v>
+        <v>14.86</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1017</v>
+        <v>9.992599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>6.87</v>
+        <v>3.41</v>
       </c>
       <c r="G7" t="n">
-        <v>8499477398</v>
+        <v>235208453</v>
       </c>
       <c r="H7" t="n">
-        <v>693167034.92</v>
+        <v>62910724</v>
       </c>
       <c r="I7" t="n">
-        <v>741383777.4</v>
+        <v>51357611</v>
       </c>
       <c r="J7" t="n">
-        <v>1434550812.32</v>
+        <v>114268335</v>
       </c>
       <c r="K7" t="n">
-        <v>48216742.48</v>
+        <v>-11553113</v>
       </c>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>-4.91</v>
       </c>
       <c r="M7" t="n">
-        <v>16.88</v>
+        <v>48.58</v>
       </c>
       <c r="N7" t="n">
-        <v>54357385697</v>
+        <v>3622510082.04</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -2149,106 +2149,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002188.SZ</t>
+          <t>001330.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>中天服务</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.97</v>
+        <v>6.97</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.7188</v>
+        <v>9.9369</v>
       </c>
       <c r="F8" t="n">
-        <v>30.32</v>
+        <v>20.92</v>
       </c>
       <c r="G8" t="n">
-        <v>478218174</v>
+        <v>1615588593</v>
       </c>
       <c r="H8" t="n">
-        <v>76675491.13</v>
+        <v>264020977.62</v>
       </c>
       <c r="I8" t="n">
-        <v>79537428.70999999</v>
+        <v>203306769</v>
       </c>
       <c r="J8" t="n">
-        <v>156212919.84</v>
+        <v>467327746.62</v>
       </c>
       <c r="K8" t="n">
-        <v>2861937.58</v>
+        <v>-60714208.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>-3.76</v>
       </c>
       <c r="M8" t="n">
-        <v>32.67</v>
+        <v>28.93</v>
       </c>
       <c r="N8" t="n">
-        <v>1536457151.79</v>
+        <v>8105045834.34</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002242.SZ</t>
+          <t>001336.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>楚环科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.75</v>
+        <v>22.72</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>10.0242</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>24.13</v>
       </c>
       <c r="G9" t="n">
-        <v>587846426</v>
+        <v>472608883</v>
       </c>
       <c r="H9" t="n">
-        <v>89014569.5</v>
+        <v>98576659.09999999</v>
       </c>
       <c r="I9" t="n">
-        <v>74952868</v>
+        <v>77260224.56</v>
       </c>
       <c r="J9" t="n">
-        <v>163967437.5</v>
+        <v>175836883.66</v>
       </c>
       <c r="K9" t="n">
-        <v>-14061701.5</v>
+        <v>-21316434.54</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.39</v>
+        <v>-4.51</v>
       </c>
       <c r="M9" t="n">
-        <v>27.89</v>
+        <v>37.21</v>
       </c>
       <c r="N9" t="n">
-        <v>10474277343.75</v>
+        <v>1460865623.36</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2259,216 +2259,216 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002285.SZ</t>
+          <t>002058.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>世联行</t>
+          <t>紫竹高科</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.21</v>
+        <v>24.44</v>
       </c>
       <c r="E10" t="n">
-        <v>6.2914</v>
+        <v>9.991</v>
       </c>
       <c r="F10" t="n">
-        <v>17.9</v>
+        <v>2.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1140776441</v>
+        <v>205210859</v>
       </c>
       <c r="H10" t="n">
-        <v>89277002.5</v>
+        <v>37451930</v>
       </c>
       <c r="I10" t="n">
-        <v>335628861.77</v>
+        <v>30675531</v>
       </c>
       <c r="J10" t="n">
-        <v>424905864.27</v>
+        <v>68127461</v>
       </c>
       <c r="K10" t="n">
-        <v>246351859.27</v>
+        <v>-6776399</v>
       </c>
       <c r="L10" t="n">
-        <v>21.6</v>
+        <v>-3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>37.25</v>
+        <v>33.2</v>
       </c>
       <c r="N10" t="n">
-        <v>6352620113.01</v>
+        <v>3503860934.08</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002316.SZ</t>
+          <t>002172.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>亚联发展</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.98</v>
+        <v>5.91</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6061</v>
+        <v>4.417</v>
       </c>
       <c r="F11" t="n">
-        <v>37.2</v>
+        <v>25.82</v>
       </c>
       <c r="G11" t="n">
-        <v>652297532</v>
+        <v>1149758062</v>
       </c>
       <c r="H11" t="n">
-        <v>105739849.18</v>
+        <v>103860574.72</v>
       </c>
       <c r="I11" t="n">
-        <v>78443870</v>
+        <v>84830721.01000001</v>
       </c>
       <c r="J11" t="n">
-        <v>184183719.18</v>
+        <v>188691295.73</v>
       </c>
       <c r="K11" t="n">
-        <v>-27295979.18</v>
+        <v>-19029853.71</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.18</v>
+        <v>-1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>28.24</v>
+        <v>16.41</v>
       </c>
       <c r="N11" t="n">
-        <v>1696860300</v>
+        <v>4521981714.3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>002212.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>天融信</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>150.66</v>
+        <v>7.56</v>
       </c>
       <c r="E12" t="n">
-        <v>-10</v>
+        <v>10.0437</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9</v>
+        <v>10.56</v>
       </c>
       <c r="G12" t="n">
-        <v>8202814551</v>
+        <v>882347755</v>
       </c>
       <c r="H12" t="n">
-        <v>1033956224.39</v>
+        <v>93560126.31999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1404425710.53</v>
+        <v>214479084.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2438381934.92</v>
+        <v>308039210.42</v>
       </c>
       <c r="K12" t="n">
-        <v>370469486.14</v>
+        <v>120918957.78</v>
       </c>
       <c r="L12" t="n">
-        <v>4.52</v>
+        <v>13.7</v>
       </c>
       <c r="M12" t="n">
-        <v>29.73</v>
+        <v>34.91</v>
       </c>
       <c r="N12" t="n">
-        <v>208863230787.18</v>
+        <v>8821379823.48</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002490.SZ</t>
+          <t>002242.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7.6</v>
+        <v>15.13</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9855</v>
+        <v>10.0364</v>
       </c>
       <c r="F13" t="n">
-        <v>12.5</v>
+        <v>18.28</v>
       </c>
       <c r="G13" t="n">
-        <v>499360191</v>
+        <v>2062716607</v>
       </c>
       <c r="H13" t="n">
-        <v>50052997.75</v>
+        <v>126917409.85</v>
       </c>
       <c r="I13" t="n">
-        <v>128250744.6</v>
+        <v>263931036.53</v>
       </c>
       <c r="J13" t="n">
-        <v>178303742.35</v>
+        <v>390848446.38</v>
       </c>
       <c r="K13" t="n">
-        <v>78197746.84999999</v>
+        <v>137013626.68</v>
       </c>
       <c r="L13" t="n">
-        <v>15.66</v>
+        <v>6.64</v>
       </c>
       <c r="M13" t="n">
-        <v>35.71</v>
+        <v>18.95</v>
       </c>
       <c r="N13" t="n">
-        <v>4117087200</v>
+        <v>11525513906.25</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2479,106 +2479,106 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002565.SZ</t>
+          <t>002285.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>顺灏股份</t>
+          <t>世联行</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.279999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="E14" t="n">
-        <v>9.9526</v>
+        <v>1.8692</v>
       </c>
       <c r="F14" t="n">
-        <v>16.09</v>
+        <v>16.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1557861796</v>
+        <v>1078343001</v>
       </c>
       <c r="H14" t="n">
-        <v>128410996.46</v>
+        <v>264195885.59</v>
       </c>
       <c r="I14" t="n">
-        <v>316318873.28</v>
+        <v>163602976.27</v>
       </c>
       <c r="J14" t="n">
-        <v>444729869.74</v>
+        <v>427798861.86</v>
       </c>
       <c r="K14" t="n">
-        <v>187907876.82</v>
+        <v>-100592909.32</v>
       </c>
       <c r="L14" t="n">
-        <v>12.06</v>
+        <v>-9.33</v>
       </c>
       <c r="M14" t="n">
-        <v>28.55</v>
+        <v>39.67</v>
       </c>
       <c r="N14" t="n">
-        <v>9836383996.16</v>
+        <v>6471360675.87</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002580.SZ</t>
+          <t>002316.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
+          <t>亚联发展</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21.36</v>
+        <v>4.85</v>
       </c>
       <c r="E15" t="n">
-        <v>9.4262</v>
+        <v>-2.6104</v>
       </c>
       <c r="F15" t="n">
-        <v>26.89</v>
+        <v>34.15</v>
       </c>
       <c r="G15" t="n">
-        <v>2546677482</v>
+        <v>548642459</v>
       </c>
       <c r="H15" t="n">
-        <v>194468814.7</v>
+        <v>80000080.93000001</v>
       </c>
       <c r="I15" t="n">
-        <v>383046481.49</v>
+        <v>98476173</v>
       </c>
       <c r="J15" t="n">
-        <v>577515296.1900001</v>
+        <v>178476253.93</v>
       </c>
       <c r="K15" t="n">
-        <v>188577666.79</v>
+        <v>18476092.07</v>
       </c>
       <c r="L15" t="n">
-        <v>7.4</v>
+        <v>3.37</v>
       </c>
       <c r="M15" t="n">
-        <v>22.68</v>
+        <v>32.53</v>
       </c>
       <c r="N15" t="n">
-        <v>9661956768</v>
+        <v>1652564750</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -2589,161 +2589,161 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002614.SZ</t>
+          <t>002317.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>众生药业</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.34</v>
+        <v>25.49</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4742</v>
+        <v>10.0129</v>
       </c>
       <c r="F16" t="n">
-        <v>21.88</v>
+        <v>6.43</v>
       </c>
       <c r="G16" t="n">
-        <v>780647189</v>
+        <v>1221113050</v>
       </c>
       <c r="H16" t="n">
-        <v>109395002</v>
+        <v>231001905.97</v>
       </c>
       <c r="I16" t="n">
-        <v>207894224.71</v>
+        <v>288677065.67</v>
       </c>
       <c r="J16" t="n">
-        <v>317289226.71</v>
+        <v>519678971.64</v>
       </c>
       <c r="K16" t="n">
-        <v>98499222.70999999</v>
+        <v>57675159.7</v>
       </c>
       <c r="L16" t="n">
-        <v>12.62</v>
+        <v>4.72</v>
       </c>
       <c r="M16" t="n">
-        <v>40.64</v>
+        <v>42.56</v>
       </c>
       <c r="N16" t="n">
-        <v>3680236093.74</v>
+        <v>19576889217.19</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002702.SZ</t>
+          <t>002487.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>海欣食品</t>
+          <t>大金重工</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.92</v>
+        <v>43.75</v>
       </c>
       <c r="E17" t="n">
-        <v>10.0372</v>
+        <v>-9.9979</v>
       </c>
       <c r="F17" t="n">
-        <v>14.39</v>
+        <v>16.67</v>
       </c>
       <c r="G17" t="n">
-        <v>371309038</v>
+        <v>4957547922</v>
       </c>
       <c r="H17" t="n">
-        <v>68058342.23999999</v>
+        <v>390508820.22</v>
       </c>
       <c r="I17" t="n">
-        <v>97790367.95999999</v>
+        <v>426474471.03</v>
       </c>
       <c r="J17" t="n">
-        <v>165848710.2</v>
+        <v>816983291.25</v>
       </c>
       <c r="K17" t="n">
-        <v>29732025.72</v>
+        <v>35965650.81</v>
       </c>
       <c r="L17" t="n">
-        <v>8.01</v>
+        <v>0.73</v>
       </c>
       <c r="M17" t="n">
-        <v>44.67</v>
+        <v>16.48</v>
       </c>
       <c r="N17" t="n">
-        <v>2715763000</v>
+        <v>27602761637.5</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>002531.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>*ST岭南</t>
+          <t>天顺风能</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.6774</v>
+        <v>-9.940099999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.12</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1203048</v>
+        <v>1398297545</v>
       </c>
       <c r="H18" t="n">
-        <v>899528</v>
+        <v>131438736.36</v>
       </c>
       <c r="I18" t="n">
-        <v>239176</v>
+        <v>113156976.48</v>
       </c>
       <c r="J18" t="n">
-        <v>1138704</v>
+        <v>244595712.84</v>
       </c>
       <c r="K18" t="n">
-        <v>-660352</v>
+        <v>-18281759.88</v>
       </c>
       <c r="L18" t="n">
-        <v>-54.89</v>
+        <v>-1.31</v>
       </c>
       <c r="M18" t="n">
-        <v>94.65000000000001</v>
+        <v>17.49</v>
       </c>
       <c r="N18" t="n">
-        <v>1001807444.96</v>
+        <v>13437251864.48</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2754,216 +2754,216 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002805.SZ</t>
+          <t>002636.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.67</v>
+        <v>71.67</v>
       </c>
       <c r="E19" t="n">
-        <v>10.0249</v>
+        <v>-9.9962</v>
       </c>
       <c r="F19" t="n">
-        <v>8.81</v>
+        <v>5.37</v>
       </c>
       <c r="G19" t="n">
-        <v>424878102</v>
+        <v>2807666916</v>
       </c>
       <c r="H19" t="n">
-        <v>72556113.2</v>
+        <v>165938892.54</v>
       </c>
       <c r="I19" t="n">
-        <v>120599472.45</v>
+        <v>278827847.78</v>
       </c>
       <c r="J19" t="n">
-        <v>193155585.65</v>
+        <v>444766740.32</v>
       </c>
       <c r="K19" t="n">
-        <v>48043359.25</v>
+        <v>112888955.24</v>
       </c>
       <c r="L19" t="n">
-        <v>11.31</v>
+        <v>4.02</v>
       </c>
       <c r="M19" t="n">
-        <v>45.46</v>
+        <v>15.84</v>
       </c>
       <c r="N19" t="n">
-        <v>4926679921.56</v>
+        <v>51977704470.21</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002866.SZ</t>
+          <t>002702.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>海欣食品</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.59</v>
+        <v>6.16</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>4.0541</v>
       </c>
       <c r="F20" t="n">
-        <v>20.57</v>
+        <v>36.76</v>
       </c>
       <c r="G20" t="n">
-        <v>671544940</v>
+        <v>1034853104</v>
       </c>
       <c r="H20" t="n">
-        <v>78757215.53</v>
+        <v>160261389.99</v>
       </c>
       <c r="I20" t="n">
-        <v>88311905.66</v>
+        <v>115983353.3</v>
       </c>
       <c r="J20" t="n">
-        <v>167069121.19</v>
+        <v>276244743.29</v>
       </c>
       <c r="K20" t="n">
-        <v>9554690.130000001</v>
+        <v>-44278036.69</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>-4.28</v>
       </c>
       <c r="M20" t="n">
-        <v>24.88</v>
+        <v>26.69</v>
       </c>
       <c r="N20" t="n">
-        <v>3416263739.46</v>
+        <v>2825861500</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002881.SZ</t>
+          <t>002733.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>美格智能</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.17</v>
+        <v>20.78</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.9976</v>
+        <v>10.0053</v>
       </c>
       <c r="F21" t="n">
-        <v>5.49</v>
+        <v>5.71</v>
       </c>
       <c r="G21" t="n">
-        <v>399034367</v>
+        <v>738681096</v>
       </c>
       <c r="H21" t="n">
-        <v>138064677.8</v>
+        <v>68556974.68000001</v>
       </c>
       <c r="I21" t="n">
-        <v>62268477.78</v>
+        <v>225547175.75</v>
       </c>
       <c r="J21" t="n">
-        <v>200333155.58</v>
+        <v>294104150.43</v>
       </c>
       <c r="K21" t="n">
-        <v>-75796200.02</v>
+        <v>156990201.07</v>
       </c>
       <c r="L21" t="n">
-        <v>-18.99</v>
+        <v>21.25</v>
       </c>
       <c r="M21" t="n">
-        <v>50.2</v>
+        <v>39.81</v>
       </c>
       <c r="N21" t="n">
-        <v>7008712801.2</v>
+        <v>7664968132.02</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002882.SZ</t>
+          <t>002805.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>金龙羽</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.95</v>
+        <v>19.44</v>
       </c>
       <c r="E22" t="n">
-        <v>7.8863</v>
+        <v>10.017</v>
       </c>
       <c r="F22" t="n">
-        <v>14.08</v>
+        <v>11.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2243498153</v>
+        <v>1032172020</v>
       </c>
       <c r="H22" t="n">
-        <v>237580058.68</v>
+        <v>166040397.98</v>
       </c>
       <c r="I22" t="n">
-        <v>288962072.48</v>
+        <v>206318135.27</v>
       </c>
       <c r="J22" t="n">
-        <v>526542131.16</v>
+        <v>372358533.25</v>
       </c>
       <c r="K22" t="n">
-        <v>51382013.8</v>
+        <v>40277737.29</v>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>3.9</v>
       </c>
       <c r="M22" t="n">
-        <v>23.47</v>
+        <v>36.08</v>
       </c>
       <c r="N22" t="n">
-        <v>6656381524.1</v>
+        <v>5420184361.92</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2974,51 +2974,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002962.SZ</t>
+          <t>002866.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>五方光电</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.69</v>
+        <v>18.32</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2158</v>
+        <v>-1.4524</v>
       </c>
       <c r="F23" t="n">
-        <v>29.24</v>
+        <v>41.53</v>
       </c>
       <c r="G23" t="n">
-        <v>971753286</v>
+        <v>1452604141</v>
       </c>
       <c r="H23" t="n">
-        <v>143627753.98</v>
+        <v>188722908.01</v>
       </c>
       <c r="I23" t="n">
-        <v>99543505</v>
+        <v>137642704.44</v>
       </c>
       <c r="J23" t="n">
-        <v>243171258.98</v>
+        <v>326365612.45</v>
       </c>
       <c r="K23" t="n">
-        <v>-44084248.98</v>
+        <v>-51080203.57</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.54</v>
+        <v>-3.52</v>
       </c>
       <c r="M23" t="n">
-        <v>25.02</v>
+        <v>22.47</v>
       </c>
       <c r="N23" t="n">
-        <v>3491810533.7</v>
+        <v>3366646138.08</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3029,216 +3029,216 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300522.SZ</t>
+          <t>002927.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>世名科技</t>
+          <t>泰永长征</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.56</v>
+        <v>17.64</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="F24" t="n">
-        <v>9.9</v>
+        <v>7.23</v>
       </c>
       <c r="G24" t="n">
-        <v>419527375</v>
+        <v>289675613</v>
       </c>
       <c r="H24" t="n">
-        <v>54330634</v>
+        <v>43702465.23</v>
       </c>
       <c r="I24" t="n">
-        <v>112478262.2</v>
+        <v>48963901</v>
       </c>
       <c r="J24" t="n">
-        <v>166808896.2</v>
+        <v>92666366.23</v>
       </c>
       <c r="K24" t="n">
-        <v>58147628.2</v>
+        <v>5261435.77</v>
       </c>
       <c r="L24" t="n">
-        <v>13.86</v>
+        <v>1.82</v>
       </c>
       <c r="M24" t="n">
-        <v>39.76</v>
+        <v>31.99</v>
       </c>
       <c r="N24" t="n">
-        <v>4366789912.08</v>
+        <v>3893815356.48</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300530.SZ</t>
+          <t>002962.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>领湃科技</t>
+          <t>五方光电</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.08</v>
+        <v>15.02</v>
       </c>
       <c r="E25" t="n">
-        <v>19.9801</v>
+        <v>-10.006</v>
       </c>
       <c r="F25" t="n">
-        <v>10.31</v>
+        <v>10.47</v>
       </c>
       <c r="G25" t="n">
-        <v>400319985</v>
+        <v>333502549</v>
       </c>
       <c r="H25" t="n">
-        <v>27337751.64</v>
+        <v>78905345.93000001</v>
       </c>
       <c r="I25" t="n">
-        <v>104104224.25</v>
+        <v>34448153.73</v>
       </c>
       <c r="J25" t="n">
-        <v>131441975.89</v>
+        <v>113353499.66</v>
       </c>
       <c r="K25" t="n">
-        <v>76766472.61</v>
+        <v>-44457192.2</v>
       </c>
       <c r="L25" t="n">
-        <v>19.18</v>
+        <v>-13.33</v>
       </c>
       <c r="M25" t="n">
-        <v>32.83</v>
+        <v>33.99</v>
       </c>
       <c r="N25" t="n">
-        <v>4140588604.32</v>
+        <v>3142420264.6</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300530.SZ</t>
+          <t>300189.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>领湃科技</t>
+          <t>神农种业</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24.08</v>
+        <v>6.69</v>
       </c>
       <c r="E26" t="n">
-        <v>19.9801</v>
+        <v>10.396</v>
       </c>
       <c r="F26" t="n">
-        <v>10.31</v>
+        <v>34.05</v>
       </c>
       <c r="G26" t="n">
-        <v>699811967</v>
+        <v>1928072616</v>
       </c>
       <c r="H26" t="n">
-        <v>59705310.5</v>
+        <v>179670757.3</v>
       </c>
       <c r="I26" t="n">
-        <v>125121308.68</v>
+        <v>251494209.16</v>
       </c>
       <c r="J26" t="n">
-        <v>184826619.18</v>
+        <v>431164966.46</v>
       </c>
       <c r="K26" t="n">
-        <v>65415998.18</v>
+        <v>71823451.86</v>
       </c>
       <c r="L26" t="n">
-        <v>9.35</v>
+        <v>3.73</v>
       </c>
       <c r="M26" t="n">
-        <v>26.41</v>
+        <v>22.36</v>
       </c>
       <c r="N26" t="n">
-        <v>4140588604.32</v>
+        <v>5929015336.56</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300619.SZ</t>
+          <t>300364.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>金银河</t>
+          <t>中文在线</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>28.17</v>
+        <v>24.47</v>
       </c>
       <c r="E27" t="n">
-        <v>17.571</v>
+        <v>20.0098</v>
       </c>
       <c r="F27" t="n">
-        <v>13.31</v>
+        <v>12.58</v>
       </c>
       <c r="G27" t="n">
-        <v>698192837</v>
+        <v>1850122255</v>
       </c>
       <c r="H27" t="n">
-        <v>71530063.06999999</v>
+        <v>222961391.4</v>
       </c>
       <c r="I27" t="n">
-        <v>130133681.2</v>
+        <v>366013366.63</v>
       </c>
       <c r="J27" t="n">
-        <v>201663744.27</v>
+        <v>588974758.03</v>
       </c>
       <c r="K27" t="n">
-        <v>58603618.13</v>
+        <v>143051975.23</v>
       </c>
       <c r="L27" t="n">
-        <v>8.390000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="M27" t="n">
-        <v>28.88</v>
+        <v>31.83</v>
       </c>
       <c r="N27" t="n">
-        <v>5364482003.82</v>
+        <v>16176766173.61</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3249,381 +3249,381 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300684.SZ</t>
+          <t>300369.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中石科技</t>
+          <t>绿盟科技</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>90.09999999999999</v>
+        <v>10.43</v>
       </c>
       <c r="E28" t="n">
-        <v>-16.6512</v>
+        <v>20.023</v>
       </c>
       <c r="F28" t="n">
-        <v>17.04</v>
+        <v>13.07</v>
       </c>
       <c r="G28" t="n">
-        <v>3344494421</v>
+        <v>1006656812</v>
       </c>
       <c r="H28" t="n">
-        <v>868062183.14</v>
+        <v>137297847.8</v>
       </c>
       <c r="I28" t="n">
-        <v>746367561.3099999</v>
+        <v>305361218.19</v>
       </c>
       <c r="J28" t="n">
-        <v>1614429744.45</v>
+        <v>442659065.99</v>
       </c>
       <c r="K28" t="n">
-        <v>-121694621.83</v>
+        <v>168063370.39</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.64</v>
+        <v>16.7</v>
       </c>
       <c r="M28" t="n">
-        <v>48.27</v>
+        <v>43.97</v>
       </c>
       <c r="N28" t="n">
-        <v>18468623847.7</v>
+        <v>8428023329.04</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300804.SZ</t>
+          <t>300413.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>广康生化</t>
+          <t>芒果超媒</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46.62</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>-15.8636</v>
+        <v>19.9791</v>
       </c>
       <c r="F29" t="n">
-        <v>18.6</v>
+        <v>11.17</v>
       </c>
       <c r="G29" t="n">
-        <v>249628319</v>
+        <v>2384983291</v>
       </c>
       <c r="H29" t="n">
-        <v>42776136.88</v>
+        <v>334146406.57</v>
       </c>
       <c r="I29" t="n">
-        <v>32395203</v>
+        <v>316089999.15</v>
       </c>
       <c r="J29" t="n">
-        <v>75171339.88</v>
+        <v>650236405.72</v>
       </c>
       <c r="K29" t="n">
-        <v>-10380933.88</v>
+        <v>-18056407.42</v>
       </c>
       <c r="L29" t="n">
-        <v>-4.16</v>
+        <v>-0.76</v>
       </c>
       <c r="M29" t="n">
-        <v>30.11</v>
+        <v>27.26</v>
       </c>
       <c r="N29" t="n">
-        <v>1282050000</v>
+        <v>23499099034</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>301139.SZ</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>元道退</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9399999999999999</v>
+        <v>17.15</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2967</v>
+        <v>20.014</v>
       </c>
       <c r="F30" t="n">
-        <v>24.84</v>
+        <v>12.56</v>
       </c>
       <c r="G30" t="n">
-        <v>18169047</v>
+        <v>2488094393</v>
       </c>
       <c r="H30" t="n">
-        <v>4026454.04</v>
+        <v>289775652.47</v>
       </c>
       <c r="I30" t="n">
-        <v>5401745.14</v>
+        <v>477357946.86</v>
       </c>
       <c r="J30" t="n">
-        <v>9428199.18</v>
+        <v>767133599.33</v>
       </c>
       <c r="K30" t="n">
-        <v>1375291.1</v>
+        <v>187582294.39</v>
       </c>
       <c r="L30" t="n">
-        <v>7.57</v>
+        <v>7.54</v>
       </c>
       <c r="M30" t="n">
-        <v>51.89</v>
+        <v>30.83</v>
       </c>
       <c r="N30" t="n">
-        <v>71586779.12</v>
+        <v>20576411362.5</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>301190.SZ</t>
+          <t>300981.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>中红医疗</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39.52</v>
+        <v>23.36</v>
       </c>
       <c r="E31" t="n">
-        <v>9.9917</v>
+        <v>19.9795</v>
       </c>
       <c r="F31" t="n">
-        <v>19.25</v>
+        <v>8.91</v>
       </c>
       <c r="G31" t="n">
-        <v>1876855229</v>
+        <v>732402935</v>
       </c>
       <c r="H31" t="n">
-        <v>257688339.16</v>
+        <v>77737947.8</v>
       </c>
       <c r="I31" t="n">
-        <v>333832391.26</v>
+        <v>204105121.02</v>
       </c>
       <c r="J31" t="n">
-        <v>591520730.42</v>
+        <v>281843068.82</v>
       </c>
       <c r="K31" t="n">
-        <v>76144052.09999999</v>
+        <v>126367173.22</v>
       </c>
       <c r="L31" t="n">
-        <v>4.06</v>
+        <v>17.25</v>
       </c>
       <c r="M31" t="n">
-        <v>31.52</v>
+        <v>38.48</v>
       </c>
       <c r="N31" t="n">
-        <v>7186870080</v>
+        <v>9180418773.440001</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>301190.SZ</t>
+          <t>300981.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>中红医疗</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>39.52</v>
+        <v>23.36</v>
       </c>
       <c r="E32" t="n">
-        <v>9.9917</v>
+        <v>19.9795</v>
       </c>
       <c r="F32" t="n">
-        <v>19.25</v>
+        <v>8.91</v>
       </c>
       <c r="G32" t="n">
-        <v>3148935162.11</v>
+        <v>2074575132</v>
       </c>
       <c r="H32" t="n">
-        <v>3148935162.11</v>
+        <v>251890378.94</v>
       </c>
       <c r="I32" t="n">
-        <v>3148935162.11</v>
+        <v>331183525.63</v>
       </c>
       <c r="J32" t="n">
-        <v>3148935162.11</v>
+        <v>583073904.5700001</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>79293146.69</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>28.11</v>
       </c>
       <c r="N32" t="n">
-        <v>7186870080</v>
+        <v>9180418773.440001</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>301513.SZ</t>
+          <t>301139.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>尚水智能</t>
+          <t>元道退</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>67.81</v>
+        <v>0.89</v>
       </c>
       <c r="E33" t="n">
-        <v>19.9752</v>
+        <v>-5.3191</v>
       </c>
       <c r="F33" t="n">
-        <v>48.24</v>
+        <v>21.73</v>
       </c>
       <c r="G33" t="n">
-        <v>597216216</v>
+        <v>15081719</v>
       </c>
       <c r="H33" t="n">
-        <v>72435592.95</v>
+        <v>4942011.09</v>
       </c>
       <c r="I33" t="n">
-        <v>40747565.21</v>
+        <v>2808720.88</v>
       </c>
       <c r="J33" t="n">
-        <v>113183158.16</v>
+        <v>7750731.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-31688027.74</v>
+        <v>-2133290.21</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.31</v>
+        <v>-14.14</v>
       </c>
       <c r="M33" t="n">
-        <v>18.95</v>
+        <v>51.39</v>
       </c>
       <c r="N33" t="n">
-        <v>1366302944.09</v>
+        <v>67778971.72</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>301686.SZ</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>中塑股份</t>
+          <t>尚水智能</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>160.61</v>
+        <v>71.89</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.142</v>
+        <v>6.0168</v>
       </c>
       <c r="F34" t="n">
-        <v>35.06</v>
+        <v>57.66</v>
       </c>
       <c r="G34" t="n">
-        <v>498836508</v>
+        <v>817661851</v>
       </c>
       <c r="H34" t="n">
-        <v>37634677.77</v>
+        <v>64315250.67</v>
       </c>
       <c r="I34" t="n">
-        <v>37085714.03</v>
+        <v>57628063.7</v>
       </c>
       <c r="J34" t="n">
-        <v>74720391.8</v>
+        <v>121943314.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-548963.74</v>
+        <v>-6687186.97</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.11</v>
+        <v>-0.82</v>
       </c>
       <c r="M34" t="n">
-        <v>14.98</v>
+        <v>14.91</v>
       </c>
       <c r="N34" t="n">
-        <v>1402616284.77</v>
+        <v>1448510819.21</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3634,51 +3634,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>301599.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>理奇智能</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>72.2</v>
+        <v>36.7</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.6751</v>
+        <v>-0.8108</v>
       </c>
       <c r="F35" t="n">
-        <v>34.1</v>
+        <v>33.83</v>
       </c>
       <c r="G35" t="n">
-        <v>1474938213</v>
+        <v>693604489</v>
       </c>
       <c r="H35" t="n">
-        <v>188609805.29</v>
+        <v>89646021.42</v>
       </c>
       <c r="I35" t="n">
-        <v>178672398.87</v>
+        <v>64535746.26</v>
       </c>
       <c r="J35" t="n">
-        <v>367282204.16</v>
+        <v>154181767.68</v>
       </c>
       <c r="K35" t="n">
-        <v>-9937406.42</v>
+        <v>-25110275.16</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.67</v>
+        <v>-3.62</v>
       </c>
       <c r="M35" t="n">
-        <v>24.9</v>
+        <v>22.23</v>
       </c>
       <c r="N35" t="n">
-        <v>4155936834.4</v>
+        <v>2007509671.2</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3689,51 +3689,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>301697.SZ</t>
+          <t>301689.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>贝特利</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31.51</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>19.9924</v>
+        <v>-1.6482</v>
       </c>
       <c r="F36" t="n">
-        <v>46.23</v>
+        <v>32.23</v>
       </c>
       <c r="G36" t="n">
-        <v>620816467</v>
+        <v>1300363300</v>
       </c>
       <c r="H36" t="n">
-        <v>35596816</v>
+        <v>150715868.24</v>
       </c>
       <c r="I36" t="n">
-        <v>182386730.82</v>
+        <v>221931751.74</v>
       </c>
       <c r="J36" t="n">
-        <v>217983546.82</v>
+        <v>372647619.98</v>
       </c>
       <c r="K36" t="n">
-        <v>146789914.82</v>
+        <v>71215883.5</v>
       </c>
       <c r="L36" t="n">
-        <v>23.64</v>
+        <v>5.48</v>
       </c>
       <c r="M36" t="n">
-        <v>35.11</v>
+        <v>28.66</v>
       </c>
       <c r="N36" t="n">
-        <v>1386157481.34</v>
+        <v>4087438706.52</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3744,51 +3744,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>301699.SZ</t>
+          <t>301697.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>贝特利</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>34.45</v>
+        <v>30.1</v>
       </c>
       <c r="E37" t="n">
-        <v>-8.7659</v>
+        <v>-4.4748</v>
       </c>
       <c r="F37" t="n">
-        <v>39</v>
+        <v>46.49</v>
       </c>
       <c r="G37" t="n">
-        <v>958849301</v>
+        <v>612084936</v>
       </c>
       <c r="H37" t="n">
-        <v>109905256.71</v>
+        <v>163923651.21</v>
       </c>
       <c r="I37" t="n">
-        <v>164730546.91</v>
+        <v>103305875.65</v>
       </c>
       <c r="J37" t="n">
-        <v>274635803.62</v>
+        <v>267229526.86</v>
       </c>
       <c r="K37" t="n">
-        <v>54825290.2</v>
+        <v>-60617775.56</v>
       </c>
       <c r="L37" t="n">
-        <v>5.72</v>
+        <v>-9.9</v>
       </c>
       <c r="M37" t="n">
-        <v>28.64</v>
+        <v>43.66</v>
       </c>
       <c r="N37" t="n">
-        <v>2409138418.05</v>
+        <v>1324130123.4</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3813,37 +3813,37 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.8</v>
+        <v>15.18</v>
       </c>
       <c r="E38" t="n">
-        <v>5.0228</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>40.85</v>
+        <v>31.47</v>
       </c>
       <c r="G38" t="n">
-        <v>3659491224</v>
+        <v>2959497543</v>
       </c>
       <c r="H38" t="n">
-        <v>291332063.83</v>
+        <v>300090326.97</v>
       </c>
       <c r="I38" t="n">
-        <v>415780335.59</v>
+        <v>360227768.17</v>
       </c>
       <c r="J38" t="n">
-        <v>707112399.42</v>
+        <v>660318095.14</v>
       </c>
       <c r="K38" t="n">
-        <v>124448271.76</v>
+        <v>60137441.2</v>
       </c>
       <c r="L38" t="n">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>19.32</v>
+        <v>22.31</v>
       </c>
       <c r="N38" t="n">
-        <v>8856608408.4</v>
+        <v>9742269249.24</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3854,161 +3854,161 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>600152.SH</t>
+          <t>600354.SH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>维科技术</t>
+          <t>敦煌种业</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.18</v>
+        <v>9.99</v>
       </c>
       <c r="E39" t="n">
-        <v>8.2547</v>
+        <v>10.022</v>
       </c>
       <c r="F39" t="n">
-        <v>21.71</v>
+        <v>23.67</v>
       </c>
       <c r="G39" t="n">
-        <v>2129038792</v>
+        <v>1198876915</v>
       </c>
       <c r="H39" t="n">
-        <v>352685175.15</v>
+        <v>97403113.37</v>
       </c>
       <c r="I39" t="n">
-        <v>257818145.1</v>
+        <v>185231436.61</v>
       </c>
       <c r="J39" t="n">
-        <v>610503320.25</v>
+        <v>282634549.98</v>
       </c>
       <c r="K39" t="n">
-        <v>-94867030.05</v>
+        <v>87828323.23999999</v>
       </c>
       <c r="L39" t="n">
-        <v>-4.46</v>
+        <v>7.33</v>
       </c>
       <c r="M39" t="n">
-        <v>28.68</v>
+        <v>23.57</v>
       </c>
       <c r="N39" t="n">
-        <v>4856948662.5</v>
+        <v>5272742779.2</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>600241.SH</t>
+          <t>600363.SH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>ST联光</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.69</v>
+        <v>10.26</v>
       </c>
       <c r="E40" t="n">
-        <v>9.9794</v>
+        <v>-6.5574</v>
       </c>
       <c r="F40" t="n">
-        <v>10.88</v>
+        <v>19.79</v>
       </c>
       <c r="G40" t="n">
-        <v>326386711</v>
+        <v>1709267778</v>
       </c>
       <c r="H40" t="n">
-        <v>49903908</v>
+        <v>214789445.11</v>
       </c>
       <c r="I40" t="n">
-        <v>28976646</v>
+        <v>143256562.42</v>
       </c>
       <c r="J40" t="n">
-        <v>78880554</v>
+        <v>358046007.53</v>
       </c>
       <c r="K40" t="n">
-        <v>-20927262</v>
+        <v>-71532882.69</v>
       </c>
       <c r="L40" t="n">
-        <v>-6.41</v>
+        <v>-4.19</v>
       </c>
       <c r="M40" t="n">
-        <v>24.17</v>
+        <v>20.95</v>
       </c>
       <c r="N40" t="n">
-        <v>3146089609.35</v>
+        <v>4626115497</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600241.SH</t>
+          <t>600400.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.69</v>
+        <v>3.98</v>
       </c>
       <c r="E41" t="n">
-        <v>9.9794</v>
+        <v>9.944800000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>10.88</v>
+        <v>8.51</v>
       </c>
       <c r="G41" t="n">
-        <v>401047975</v>
+        <v>1135204963</v>
       </c>
       <c r="H41" t="n">
-        <v>57761681</v>
+        <v>169017884.16</v>
       </c>
       <c r="I41" t="n">
-        <v>51854543</v>
+        <v>238307604.96</v>
       </c>
       <c r="J41" t="n">
-        <v>109616224</v>
+        <v>407325489.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-5907138</v>
+        <v>69289720.8</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.47</v>
+        <v>6.1</v>
       </c>
       <c r="M41" t="n">
-        <v>27.33</v>
+        <v>35.88</v>
       </c>
       <c r="N41" t="n">
-        <v>3146089609.35</v>
+        <v>9119659970.959999</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4019,106 +4019,106 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600330.SH</t>
+          <t>600408.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>24.21</v>
+        <v>3.78</v>
       </c>
       <c r="E42" t="n">
-        <v>-10</v>
+        <v>9.883699999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>8.130000000000001</v>
+        <v>20.91</v>
       </c>
       <c r="G42" t="n">
-        <v>2549925079</v>
+        <v>967844179</v>
       </c>
       <c r="H42" t="n">
-        <v>400718556.76</v>
+        <v>167586746.34</v>
       </c>
       <c r="I42" t="n">
-        <v>323962810.37</v>
+        <v>176589354.24</v>
       </c>
       <c r="J42" t="n">
-        <v>724681367.13</v>
+        <v>344176100.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-76755746.39</v>
+        <v>9002607.9</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.01</v>
+        <v>0.93</v>
       </c>
       <c r="M42" t="n">
-        <v>28.42</v>
+        <v>35.56</v>
       </c>
       <c r="N42" t="n">
-        <v>29861447211.36</v>
+        <v>3805704000</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600363.SH</t>
+          <t>600663.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ST联光</t>
+          <t>陆家嘴</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.98</v>
+        <v>10.15</v>
       </c>
       <c r="E43" t="n">
-        <v>-10</v>
+        <v>-8.723000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>15.64</v>
+        <v>2.27</v>
       </c>
       <c r="G43" t="n">
-        <v>776306835</v>
+        <v>939631958</v>
       </c>
       <c r="H43" t="n">
-        <v>130726305.97</v>
+        <v>183113298.86</v>
       </c>
       <c r="I43" t="n">
-        <v>70059005.09</v>
+        <v>84812175.73999999</v>
       </c>
       <c r="J43" t="n">
-        <v>200785311.06</v>
+        <v>267925474.6</v>
       </c>
       <c r="K43" t="n">
-        <v>-60667300.88</v>
+        <v>-98301123.12</v>
       </c>
       <c r="L43" t="n">
-        <v>-7.81</v>
+        <v>-10.46</v>
       </c>
       <c r="M43" t="n">
-        <v>25.86</v>
+        <v>28.51</v>
       </c>
       <c r="N43" t="n">
-        <v>4950755181</v>
+        <v>40379036785.85</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4129,161 +4129,161 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600400.SH</t>
+          <t>600722.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.62</v>
+        <v>16.88</v>
       </c>
       <c r="E44" t="n">
-        <v>10.0304</v>
+        <v>4.2619</v>
       </c>
       <c r="F44" t="n">
-        <v>4.81</v>
+        <v>23.27</v>
       </c>
       <c r="G44" t="n">
-        <v>391041912</v>
+        <v>2608503538</v>
       </c>
       <c r="H44" t="n">
-        <v>53522017</v>
+        <v>382242169.64</v>
       </c>
       <c r="I44" t="n">
-        <v>84348821.76000001</v>
+        <v>260958492.35</v>
       </c>
       <c r="J44" t="n">
-        <v>137870838.76</v>
+        <v>643200661.99</v>
       </c>
       <c r="K44" t="n">
-        <v>30826804.76</v>
+        <v>-121283677.29</v>
       </c>
       <c r="L44" t="n">
-        <v>7.88</v>
+        <v>-4.65</v>
       </c>
       <c r="M44" t="n">
-        <v>35.26</v>
+        <v>24.66</v>
       </c>
       <c r="N44" t="n">
-        <v>8294766104.24</v>
+        <v>11483796130.88</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600418.SH</t>
+          <t>600812.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>24.72</v>
+        <v>6.03</v>
       </c>
       <c r="E45" t="n">
-        <v>-10.0109</v>
+        <v>10.0365</v>
       </c>
       <c r="F45" t="n">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3614355828</v>
+        <v>687660547</v>
       </c>
       <c r="H45" t="n">
-        <v>536446969.47</v>
+        <v>58180459.21</v>
       </c>
       <c r="I45" t="n">
-        <v>598174797.35</v>
+        <v>83631800</v>
       </c>
       <c r="J45" t="n">
-        <v>1134621766.82</v>
+        <v>141812259.21</v>
       </c>
       <c r="K45" t="n">
-        <v>61727827.88</v>
+        <v>25451340.79</v>
       </c>
       <c r="L45" t="n">
-        <v>1.71</v>
+        <v>3.7</v>
       </c>
       <c r="M45" t="n">
-        <v>31.39</v>
+        <v>20.62</v>
       </c>
       <c r="N45" t="n">
-        <v>55723284980.4</v>
+        <v>10345854131.1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600663.SH</t>
+          <t>600812.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>陆家嘴</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.12</v>
+        <v>6.03</v>
       </c>
       <c r="E46" t="n">
-        <v>9.9901</v>
+        <v>10.0365</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>6.75</v>
       </c>
       <c r="G46" t="n">
-        <v>784346232</v>
+        <v>1182019547</v>
       </c>
       <c r="H46" t="n">
-        <v>160646705.91</v>
+        <v>65314507.21</v>
       </c>
       <c r="I46" t="n">
-        <v>289004500.07</v>
+        <v>107476046.83</v>
       </c>
       <c r="J46" t="n">
-        <v>449651205.98</v>
+        <v>172790554.04</v>
       </c>
       <c r="K46" t="n">
-        <v>128357794.16</v>
+        <v>42161539.62</v>
       </c>
       <c r="L46" t="n">
-        <v>16.36</v>
+        <v>3.57</v>
       </c>
       <c r="M46" t="n">
-        <v>57.33</v>
+        <v>14.62</v>
       </c>
       <c r="N46" t="n">
-        <v>44205328558.48</v>
+        <v>10345854131.1</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4294,1426 +4294,1426 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600699.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>均胜电子</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>21.11</v>
+        <v>12.53</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.0171</v>
+        <v>10.0088</v>
       </c>
       <c r="F47" t="n">
-        <v>6.13</v>
+        <v>4.78</v>
       </c>
       <c r="G47" t="n">
-        <v>1849983929</v>
+        <v>689935518</v>
       </c>
       <c r="H47" t="n">
-        <v>230340015.86</v>
+        <v>63691427.18</v>
       </c>
       <c r="I47" t="n">
-        <v>127878922.78</v>
+        <v>113462694</v>
       </c>
       <c r="J47" t="n">
-        <v>358218938.64</v>
+        <v>177154121.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-102461093.08</v>
+        <v>49771266.82</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.54</v>
+        <v>7.21</v>
       </c>
       <c r="M47" t="n">
-        <v>19.36</v>
+        <v>25.68</v>
       </c>
       <c r="N47" t="n">
-        <v>29462605584.93</v>
+        <v>13092444760.5</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600721.SH</t>
+          <t>600825.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.58</v>
+        <v>12.53</v>
       </c>
       <c r="E48" t="n">
-        <v>-4.0427</v>
+        <v>10.0088</v>
       </c>
       <c r="F48" t="n">
-        <v>24.54</v>
+        <v>4.78</v>
       </c>
       <c r="G48" t="n">
-        <v>1215941095</v>
+        <v>1126173900</v>
       </c>
       <c r="H48" t="n">
-        <v>105965179</v>
+        <v>1126173800</v>
       </c>
       <c r="I48" t="n">
-        <v>128303864</v>
+        <v>1126173900</v>
       </c>
       <c r="J48" t="n">
-        <v>234269043</v>
+        <v>1126173900</v>
       </c>
       <c r="K48" t="n">
-        <v>22338685</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>19.27</v>
+        <v>100</v>
       </c>
       <c r="N48" t="n">
-        <v>4837609248.3</v>
+        <v>13092444760.5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>连续10个交易日内4次出现同正向异常波动的证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>600802.SH</t>
+          <t>600865.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>百大集团</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7.14</v>
+        <v>11.51</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.3812</v>
+        <v>10.0382</v>
       </c>
       <c r="F49" t="n">
-        <v>17.23</v>
+        <v>10.85</v>
       </c>
       <c r="G49" t="n">
-        <v>572618337</v>
+        <v>449311790</v>
       </c>
       <c r="H49" t="n">
-        <v>49509944.38</v>
+        <v>90142461.41</v>
       </c>
       <c r="I49" t="n">
-        <v>52195372.48</v>
+        <v>85414679</v>
       </c>
       <c r="J49" t="n">
-        <v>101705316.86</v>
+        <v>175557140.41</v>
       </c>
       <c r="K49" t="n">
-        <v>2685428.1</v>
+        <v>-4727782.41</v>
       </c>
       <c r="L49" t="n">
-        <v>0.47</v>
+        <v>-1.05</v>
       </c>
       <c r="M49" t="n">
-        <v>17.76</v>
+        <v>39.07</v>
       </c>
       <c r="N49" t="n">
-        <v>3271893576</v>
+        <v>4330526037.16</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>600812.SH</t>
+          <t>601091.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.48</v>
+        <v>23.03</v>
       </c>
       <c r="E50" t="n">
-        <v>10.0402</v>
+        <v>-4.8347</v>
       </c>
       <c r="F50" t="n">
-        <v>5.27</v>
+        <v>27.56</v>
       </c>
       <c r="G50" t="n">
-        <v>494359000</v>
+        <v>1339327373</v>
       </c>
       <c r="H50" t="n">
-        <v>32265002</v>
+        <v>105240421.67</v>
       </c>
       <c r="I50" t="n">
-        <v>72129398</v>
+        <v>99736959.94</v>
       </c>
       <c r="J50" t="n">
-        <v>104394400</v>
+        <v>204977381.61</v>
       </c>
       <c r="K50" t="n">
-        <v>39864396</v>
+        <v>-5503461.73</v>
       </c>
       <c r="L50" t="n">
-        <v>8.06</v>
+        <v>-0.41</v>
       </c>
       <c r="M50" t="n">
-        <v>21.12</v>
+        <v>15.3</v>
       </c>
       <c r="N50" t="n">
-        <v>9402202427.6</v>
+        <v>4863088081.46</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>601118.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>海南橡胶</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.39</v>
+        <v>7.16</v>
       </c>
       <c r="E51" t="n">
-        <v>10.0483</v>
+        <v>9.9846</v>
       </c>
       <c r="F51" t="n">
-        <v>0.54</v>
+        <v>6.64</v>
       </c>
       <c r="G51" t="n">
-        <v>64324547</v>
+        <v>3665954768</v>
       </c>
       <c r="H51" t="n">
-        <v>10415016</v>
+        <v>595747293.4299999</v>
       </c>
       <c r="I51" t="n">
-        <v>39762490</v>
+        <v>532059052.27</v>
       </c>
       <c r="J51" t="n">
-        <v>50177506</v>
+        <v>1127806345.7</v>
       </c>
       <c r="K51" t="n">
-        <v>29347474</v>
+        <v>-63688241.16</v>
       </c>
       <c r="L51" t="n">
-        <v>45.62</v>
+        <v>-1.74</v>
       </c>
       <c r="M51" t="n">
-        <v>78.01000000000001</v>
+        <v>30.76</v>
       </c>
       <c r="N51" t="n">
-        <v>11901272611.5</v>
+        <v>30640703026.52</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>601929.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.39</v>
+        <v>2.5</v>
       </c>
       <c r="E52" t="n">
-        <v>10.0483</v>
+        <v>10.1322</v>
       </c>
       <c r="F52" t="n">
-        <v>0.54</v>
+        <v>5.72</v>
       </c>
       <c r="G52" t="n">
-        <v>515086700</v>
+        <v>475031390</v>
       </c>
       <c r="H52" t="n">
-        <v>515086700</v>
+        <v>60337659</v>
       </c>
       <c r="I52" t="n">
-        <v>515086800</v>
+        <v>166530634</v>
       </c>
       <c r="J52" t="n">
-        <v>515086800</v>
+        <v>226868293</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>106192975</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>22.35</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>47.76</v>
       </c>
       <c r="N52" t="n">
-        <v>11901272611.5</v>
+        <v>8724470420</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>601091.SH</t>
+          <t>603002.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>宏昌电子</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>24.2</v>
+        <v>17.68</v>
       </c>
       <c r="E53" t="n">
-        <v>4.5356</v>
+        <v>-5.404</v>
       </c>
       <c r="F53" t="n">
-        <v>38.82</v>
+        <v>14.03</v>
       </c>
       <c r="G53" t="n">
-        <v>1993050419</v>
+        <v>2962862410</v>
       </c>
       <c r="H53" t="n">
-        <v>133699807.62</v>
+        <v>565179113</v>
       </c>
       <c r="I53" t="n">
-        <v>151054858.82</v>
+        <v>289470157</v>
       </c>
       <c r="J53" t="n">
-        <v>284754666.44</v>
+        <v>854649270</v>
       </c>
       <c r="K53" t="n">
-        <v>17355051.2</v>
+        <v>-275708956</v>
       </c>
       <c r="L53" t="n">
-        <v>0.87</v>
+        <v>-9.31</v>
       </c>
       <c r="M53" t="n">
-        <v>14.29</v>
+        <v>28.85</v>
       </c>
       <c r="N53" t="n">
-        <v>5110149004.4</v>
+        <v>20050508039.12</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>603189.SH</t>
+          <t>603073.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>*ST网达</t>
+          <t>彩蝶实业</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.2</v>
+        <v>20.67</v>
       </c>
       <c r="E54" t="n">
-        <v>10.0324</v>
+        <v>-10.0131</v>
       </c>
       <c r="F54" t="n">
-        <v>3.19</v>
+        <v>8.26</v>
       </c>
       <c r="G54" t="n">
-        <v>85105250</v>
+        <v>201331598</v>
       </c>
       <c r="H54" t="n">
-        <v>22821920</v>
+        <v>40510897</v>
       </c>
       <c r="I54" t="n">
-        <v>19713386.97</v>
+        <v>33322707.54</v>
       </c>
       <c r="J54" t="n">
-        <v>42535306.97</v>
+        <v>73833604.54000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-3108533.03</v>
+        <v>-7188189.46</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.65</v>
+        <v>-3.57</v>
       </c>
       <c r="M54" t="n">
-        <v>49.98</v>
+        <v>36.67</v>
       </c>
       <c r="N54" t="n">
-        <v>2749393159.8</v>
+        <v>2397720000</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>603248.SH</t>
+          <t>603096.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>新经典</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>21.44</v>
+        <v>17.33</v>
       </c>
       <c r="E55" t="n">
-        <v>4.9437</v>
+        <v>10.0317</v>
       </c>
       <c r="F55" t="n">
-        <v>29.69</v>
+        <v>2.8</v>
       </c>
       <c r="G55" t="n">
-        <v>457048826</v>
+        <v>70710476</v>
       </c>
       <c r="H55" t="n">
-        <v>27520193.33</v>
+        <v>15737233</v>
       </c>
       <c r="I55" t="n">
-        <v>71000378.18000001</v>
+        <v>38748093</v>
       </c>
       <c r="J55" t="n">
-        <v>98520571.51000001</v>
+        <v>54485326</v>
       </c>
       <c r="K55" t="n">
-        <v>43480184.85</v>
+        <v>23010860</v>
       </c>
       <c r="L55" t="n">
-        <v>9.51</v>
+        <v>32.54</v>
       </c>
       <c r="M55" t="n">
-        <v>21.56</v>
+        <v>77.05</v>
       </c>
       <c r="N55" t="n">
-        <v>1533066149.44</v>
+        <v>2672886033.92</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>603538.SH</t>
+          <t>603101.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>汇嘉时代</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29.46</v>
+        <v>7.99</v>
       </c>
       <c r="E56" t="n">
-        <v>3.043</v>
+        <v>10.0551</v>
       </c>
       <c r="F56" t="n">
-        <v>25.68</v>
+        <v>3.99</v>
       </c>
       <c r="G56" t="n">
-        <v>2502003519</v>
+        <v>146219698</v>
       </c>
       <c r="H56" t="n">
-        <v>427480314.59</v>
+        <v>21220377.76</v>
       </c>
       <c r="I56" t="n">
-        <v>236980587.28</v>
+        <v>30398513.16</v>
       </c>
       <c r="J56" t="n">
-        <v>664460901.87</v>
+        <v>51618890.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-190499727.31</v>
+        <v>9178135.4</v>
       </c>
       <c r="L56" t="n">
-        <v>-7.61</v>
+        <v>6.28</v>
       </c>
       <c r="M56" t="n">
-        <v>26.56</v>
+        <v>35.3</v>
       </c>
       <c r="N56" t="n">
-        <v>9925661756.459999</v>
+        <v>3758496000</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>603773.SH</t>
+          <t>603200.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>80.7</v>
+        <v>53.92</v>
       </c>
       <c r="E57" t="n">
-        <v>-10.0033</v>
+        <v>9.571199999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>10.81</v>
+        <v>20.5</v>
       </c>
       <c r="G57" t="n">
-        <v>2041815052</v>
+        <v>3372370571</v>
       </c>
       <c r="H57" t="n">
-        <v>278949854.85</v>
+        <v>337537875.26</v>
       </c>
       <c r="I57" t="n">
-        <v>254224651.88</v>
+        <v>306241744.31</v>
       </c>
       <c r="J57" t="n">
-        <v>533174506.73</v>
+        <v>643779619.5700001</v>
       </c>
       <c r="K57" t="n">
-        <v>-24725202.97</v>
+        <v>-31296130.95</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.21</v>
+        <v>-0.93</v>
       </c>
       <c r="M57" t="n">
-        <v>26.11</v>
+        <v>19.09</v>
       </c>
       <c r="N57" t="n">
-        <v>18131565683.1</v>
+        <v>9461887153.76</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603906.SH</t>
+          <t>603232.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>格尔软件</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20.94</v>
+        <v>16.98</v>
       </c>
       <c r="E58" t="n">
-        <v>9.978999999999999</v>
+        <v>9.9741</v>
       </c>
       <c r="F58" t="n">
-        <v>14.89</v>
+        <v>10.83</v>
       </c>
       <c r="G58" t="n">
-        <v>2393681611</v>
+        <v>400137732</v>
       </c>
       <c r="H58" t="n">
-        <v>198599701.14</v>
+        <v>51700075.14</v>
       </c>
       <c r="I58" t="n">
-        <v>312657062.17</v>
+        <v>132438814.12</v>
       </c>
       <c r="J58" t="n">
-        <v>511256763.31</v>
+        <v>184138889.26</v>
       </c>
       <c r="K58" t="n">
-        <v>114057361.03</v>
+        <v>80738738.98</v>
       </c>
       <c r="L58" t="n">
-        <v>4.76</v>
+        <v>20.18</v>
       </c>
       <c r="M58" t="n">
-        <v>21.36</v>
+        <v>46.02</v>
       </c>
       <c r="N58" t="n">
-        <v>11789146772.82</v>
+        <v>3927473915.1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>603248.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.38</v>
+        <v>20.64</v>
       </c>
       <c r="E59" t="n">
-        <v>10.023</v>
+        <v>-3.7313</v>
       </c>
       <c r="F59" t="n">
-        <v>7.56</v>
+        <v>25.22</v>
       </c>
       <c r="G59" t="n">
-        <v>363872133</v>
+        <v>365545255</v>
       </c>
       <c r="H59" t="n">
-        <v>116258886.05</v>
+        <v>50423793.66</v>
       </c>
       <c r="I59" t="n">
-        <v>44517643.93</v>
+        <v>49553029.05</v>
       </c>
       <c r="J59" t="n">
-        <v>160776529.98</v>
+        <v>99976822.70999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-71741242.12</v>
+        <v>-870764.61</v>
       </c>
       <c r="L59" t="n">
-        <v>-19.72</v>
+        <v>-0.24</v>
       </c>
       <c r="M59" t="n">
-        <v>44.18</v>
+        <v>27.35</v>
       </c>
       <c r="N59" t="n">
-        <v>4899323520</v>
+        <v>1475862188.64</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>603400.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>华之杰</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.38</v>
+        <v>42.93</v>
       </c>
       <c r="E60" t="n">
-        <v>10.023</v>
+        <v>-10</v>
       </c>
       <c r="F60" t="n">
-        <v>7.56</v>
+        <v>18.13</v>
       </c>
       <c r="G60" t="n">
-        <v>495783866</v>
+        <v>286680592</v>
       </c>
       <c r="H60" t="n">
-        <v>124434685.05</v>
+        <v>56863177.58</v>
       </c>
       <c r="I60" t="n">
-        <v>103858012.48</v>
+        <v>43029256.97</v>
       </c>
       <c r="J60" t="n">
-        <v>228292697.53</v>
+        <v>99892434.55</v>
       </c>
       <c r="K60" t="n">
-        <v>-20576672.57</v>
+        <v>-13833920.61</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.15</v>
+        <v>-4.83</v>
       </c>
       <c r="M60" t="n">
-        <v>46.05</v>
+        <v>34.84</v>
       </c>
       <c r="N60" t="n">
-        <v>4899323520</v>
+        <v>1555357119.75</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>605388.SH</t>
+          <t>603400.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>华之杰</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6.93</v>
+        <v>42.93</v>
       </c>
       <c r="E61" t="n">
-        <v>-6.2246</v>
+        <v>-10</v>
       </c>
       <c r="F61" t="n">
-        <v>12.48</v>
+        <v>18.13</v>
       </c>
       <c r="G61" t="n">
-        <v>547241611</v>
+        <v>1158679255</v>
       </c>
       <c r="H61" t="n">
-        <v>75868702.81</v>
+        <v>168375728.76</v>
       </c>
       <c r="I61" t="n">
-        <v>50007617.2</v>
+        <v>151795838.79</v>
       </c>
       <c r="J61" t="n">
-        <v>125876320.01</v>
+        <v>320171567.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-25861085.61</v>
+        <v>-16579889.97</v>
       </c>
       <c r="L61" t="n">
-        <v>-4.73</v>
+        <v>-1.43</v>
       </c>
       <c r="M61" t="n">
-        <v>23</v>
+        <v>27.63</v>
       </c>
       <c r="N61" t="n">
-        <v>4161354120</v>
+        <v>1555357119.75</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>688048.SH</t>
+          <t>603757.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>长光华芯</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>231.76</v>
+        <v>72.78</v>
       </c>
       <c r="E62" t="n">
-        <v>-20</v>
+        <v>4.5539</v>
       </c>
       <c r="F62" t="n">
-        <v>7.14</v>
+        <v>6.87</v>
       </c>
       <c r="G62" t="n">
-        <v>2997676800</v>
+        <v>878390440</v>
       </c>
       <c r="H62" t="n">
-        <v>790458640.9400001</v>
+        <v>121701611.47</v>
       </c>
       <c r="I62" t="n">
-        <v>481482264.22</v>
+        <v>197975026.07</v>
       </c>
       <c r="J62" t="n">
-        <v>1271940905.16</v>
+        <v>319676637.54</v>
       </c>
       <c r="K62" t="n">
-        <v>-308976376.72</v>
+        <v>76273414.59999999</v>
       </c>
       <c r="L62" t="n">
-        <v>-10.31</v>
+        <v>8.68</v>
       </c>
       <c r="M62" t="n">
-        <v>42.43</v>
+        <v>36.39</v>
       </c>
       <c r="N62" t="n">
-        <v>40854639589.68</v>
+        <v>13576909510.02</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>688196.SH</t>
+          <t>603823.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>卓越新能</t>
+          <t>百合花</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>36.12</v>
+        <v>41.93</v>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>-10.0021</v>
       </c>
       <c r="F63" t="n">
-        <v>5.03</v>
+        <v>4.88</v>
       </c>
       <c r="G63" t="n">
-        <v>217545100</v>
+        <v>855381191</v>
       </c>
       <c r="H63" t="n">
-        <v>29114635.5</v>
+        <v>149012264.2</v>
       </c>
       <c r="I63" t="n">
-        <v>74914422.16</v>
+        <v>55608154</v>
       </c>
       <c r="J63" t="n">
-        <v>104029057.66</v>
+        <v>204620418.2</v>
       </c>
       <c r="K63" t="n">
-        <v>45799786.66</v>
+        <v>-93404110.2</v>
       </c>
       <c r="L63" t="n">
-        <v>21.05</v>
+        <v>-10.92</v>
       </c>
       <c r="M63" t="n">
-        <v>47.82</v>
+        <v>23.92</v>
       </c>
       <c r="N63" t="n">
-        <v>4594131515.4</v>
+        <v>17458297828.72</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>688313.SH</t>
+          <t>603928.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>仕佳光子</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>127.6</v>
+        <v>13.69</v>
       </c>
       <c r="E64" t="n">
-        <v>-17.4003</v>
+        <v>-4.7983</v>
       </c>
       <c r="F64" t="n">
-        <v>8.1</v>
+        <v>17.55</v>
       </c>
       <c r="G64" t="n">
-        <v>4864029600</v>
+        <v>828324867</v>
       </c>
       <c r="H64" t="n">
-        <v>952095821.77</v>
+        <v>114858713.7</v>
       </c>
       <c r="I64" t="n">
-        <v>1087411679.98</v>
+        <v>141185292.29</v>
       </c>
       <c r="J64" t="n">
-        <v>2039507501.75</v>
+        <v>256044005.99</v>
       </c>
       <c r="K64" t="n">
-        <v>135315858.21</v>
+        <v>26326578.59</v>
       </c>
       <c r="L64" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="M64" t="n">
-        <v>41.93</v>
+        <v>30.91</v>
       </c>
       <c r="N64" t="n">
-        <v>57673455452.8</v>
+        <v>4664237760</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>688498.SH</t>
+          <t>603949.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1290.4</v>
+        <v>15.61</v>
       </c>
       <c r="E65" t="n">
-        <v>-20</v>
+        <v>-5.7936</v>
       </c>
       <c r="F65" t="n">
-        <v>4.48</v>
+        <v>11.11</v>
       </c>
       <c r="G65" t="n">
-        <v>7298435200</v>
+        <v>1241488938</v>
       </c>
       <c r="H65" t="n">
-        <v>1859170030.03</v>
+        <v>59410838.05</v>
       </c>
       <c r="I65" t="n">
-        <v>1518283151.96</v>
+        <v>75166624.53</v>
       </c>
       <c r="J65" t="n">
-        <v>3377453181.99</v>
+        <v>134577462.58</v>
       </c>
       <c r="K65" t="n">
-        <v>-340886878.07</v>
+        <v>15755786.48</v>
       </c>
       <c r="L65" t="n">
-        <v>-4.67</v>
+        <v>1.27</v>
       </c>
       <c r="M65" t="n">
-        <v>46.28</v>
+        <v>10.84</v>
       </c>
       <c r="N65" t="n">
-        <v>158580022617.6</v>
+        <v>3281304327.14</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>688578.SH</t>
+          <t>605303.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>艾力斯</t>
+          <t>园林股份</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>89.26000000000001</v>
+        <v>32.21</v>
       </c>
       <c r="E66" t="n">
-        <v>-20.0036</v>
+        <v>2.1567</v>
       </c>
       <c r="F66" t="n">
-        <v>1.47</v>
+        <v>16.3</v>
       </c>
       <c r="G66" t="n">
-        <v>598347300</v>
+        <v>849336393</v>
       </c>
       <c r="H66" t="n">
-        <v>100011972.41</v>
+        <v>101800326.88</v>
       </c>
       <c r="I66" t="n">
-        <v>193555467.64</v>
+        <v>80357496</v>
       </c>
       <c r="J66" t="n">
-        <v>293567440.05</v>
+        <v>182157822.88</v>
       </c>
       <c r="K66" t="n">
-        <v>93543495.23</v>
+        <v>-21442830.88</v>
       </c>
       <c r="L66" t="n">
-        <v>15.63</v>
+        <v>-2.52</v>
       </c>
       <c r="M66" t="n">
-        <v>49.06</v>
+        <v>21.45</v>
       </c>
       <c r="N66" t="n">
-        <v>40167000000</v>
+        <v>5193456911.68</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>688806.SH</t>
+          <t>605366.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>泰诺麦博</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.15</v>
+        <v>9.94</v>
       </c>
       <c r="E67" t="n">
-        <v>-11.477</v>
+        <v>-9.963800000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>31.23</v>
+        <v>12.26</v>
       </c>
       <c r="G67" t="n">
-        <v>451776000</v>
+        <v>1033147537</v>
       </c>
       <c r="H67" t="n">
-        <v>64777690.18</v>
+        <v>90559628.52</v>
       </c>
       <c r="I67" t="n">
-        <v>60965401.23</v>
+        <v>66631506.33</v>
       </c>
       <c r="J67" t="n">
-        <v>125743091.41</v>
+        <v>157191134.85</v>
       </c>
       <c r="K67" t="n">
-        <v>-3812288.95</v>
+        <v>-23928122.19</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
       <c r="M67" t="n">
-        <v>27.83</v>
+        <v>15.21</v>
       </c>
       <c r="N67" t="n">
-        <v>1385346669</v>
+        <v>7681907338</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>920025.BJ</t>
+          <t>688152.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>凯达重工</t>
+          <t>麒麟信安</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.62</v>
+        <v>45.85</v>
       </c>
       <c r="E68" t="n">
-        <v>1.0408</v>
+        <v>19.9948</v>
       </c>
       <c r="F68" t="n">
-        <v>26.58</v>
+        <v>11.24</v>
       </c>
       <c r="G68" t="n">
-        <v>168695600</v>
+        <v>482932000</v>
       </c>
       <c r="H68" t="n">
-        <v>27743460.07</v>
+        <v>48350195.72</v>
       </c>
       <c r="I68" t="n">
-        <v>26626221.45</v>
+        <v>99241215.83</v>
       </c>
       <c r="J68" t="n">
-        <v>54369681.52</v>
+        <v>147591411.55</v>
       </c>
       <c r="K68" t="n">
-        <v>-1117238.62</v>
+        <v>50891020.11</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.66</v>
+        <v>10.54</v>
       </c>
       <c r="M68" t="n">
-        <v>32.23</v>
+        <v>30.56</v>
       </c>
       <c r="N68" t="n">
-        <v>643620000</v>
+        <v>4672026784.6</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>920201.BJ</t>
+          <t>688244.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>百瑞吉</t>
+          <t>永信至诚</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>39.01</v>
+        <v>24</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.2956</v>
+        <v>16.2228</v>
       </c>
       <c r="F69" t="n">
-        <v>30.93</v>
+        <v>15.66</v>
       </c>
       <c r="G69" t="n">
-        <v>94426400</v>
+        <v>496980400</v>
       </c>
       <c r="H69" t="n">
-        <v>17790706.51</v>
+        <v>57025546.09</v>
       </c>
       <c r="I69" t="n">
-        <v>26893047.7</v>
+        <v>28493121.97</v>
       </c>
       <c r="J69" t="n">
-        <v>44683754.21</v>
+        <v>85518668.06</v>
       </c>
       <c r="K69" t="n">
-        <v>9102341.189999999</v>
+        <v>-28532424.12</v>
       </c>
       <c r="L69" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.74</v>
       </c>
       <c r="M69" t="n">
-        <v>47.32</v>
+        <v>17.21</v>
       </c>
       <c r="N69" t="n">
-        <v>296806297.67</v>
+        <v>3623076456</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日价格振幅达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>920202.BJ</t>
+          <t>688806.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>安达股份</t>
+          <t>泰诺麦博</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.3</v>
+        <v>30.34</v>
       </c>
       <c r="E70" t="n">
-        <v>-21.9432</v>
+        <v>11.7495</v>
       </c>
       <c r="F70" t="n">
-        <v>48.96</v>
+        <v>42.08</v>
       </c>
       <c r="G70" t="n">
-        <v>177659400</v>
+        <v>631093500</v>
       </c>
       <c r="H70" t="n">
-        <v>21837052.7</v>
+        <v>102890216.27</v>
       </c>
       <c r="I70" t="n">
-        <v>16135353.5</v>
+        <v>80237512.36</v>
       </c>
       <c r="J70" t="n">
-        <v>37972406.2</v>
+        <v>183127728.63</v>
       </c>
       <c r="K70" t="n">
-        <v>-5701699.2</v>
+        <v>-22652703.91</v>
       </c>
       <c r="L70" t="n">
-        <v>-3.21</v>
+        <v>-3.59</v>
       </c>
       <c r="M70" t="n">
-        <v>21.37</v>
+        <v>29.02</v>
       </c>
       <c r="N70" t="n">
-        <v>340340000</v>
+        <v>1548118524.4</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>920202.BJ</t>
+          <t>920021.BJ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>安达股份</t>
+          <t>流金科技</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.3</v>
+        <v>8.83</v>
       </c>
       <c r="E71" t="n">
-        <v>-21.9432</v>
+        <v>20.1361</v>
       </c>
       <c r="F71" t="n">
-        <v>48.96</v>
+        <v>20.01</v>
       </c>
       <c r="G71" t="n">
-        <v>496081800</v>
+        <v>410490500</v>
       </c>
       <c r="H71" t="n">
-        <v>37015232.31</v>
+        <v>42678610.74</v>
       </c>
       <c r="I71" t="n">
-        <v>46618212.99</v>
+        <v>46788988.57</v>
       </c>
       <c r="J71" t="n">
-        <v>83633445.3</v>
+        <v>89467599.31</v>
       </c>
       <c r="K71" t="n">
-        <v>9602980.68</v>
+        <v>4110377.83</v>
       </c>
       <c r="L71" t="n">
-        <v>1.94</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>16.86</v>
+        <v>21.8</v>
       </c>
       <c r="N71" t="n">
-        <v>340340000</v>
+        <v>2185907762.59</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>力王股份</t>
+          <t>安达股份</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17.83</v>
+        <v>14.58</v>
       </c>
       <c r="E72" t="n">
-        <v>29.9563</v>
+        <v>1.958</v>
       </c>
       <c r="F72" t="n">
-        <v>25.69</v>
+        <v>32.57</v>
       </c>
       <c r="G72" t="n">
-        <v>213939200</v>
+        <v>111893300</v>
       </c>
       <c r="H72" t="n">
-        <v>17020893.9</v>
+        <v>11547940.37</v>
       </c>
       <c r="I72" t="n">
-        <v>32643239.34</v>
+        <v>12667503.66</v>
       </c>
       <c r="J72" t="n">
-        <v>49664133.24</v>
+        <v>24215444.03</v>
       </c>
       <c r="K72" t="n">
-        <v>15622345.44</v>
+        <v>1119563.29</v>
       </c>
       <c r="L72" t="n">
-        <v>7.3</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>23.21</v>
+        <v>21.64</v>
       </c>
       <c r="N72" t="n">
-        <v>875408425</v>
+        <v>347004000</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5724,165 +5724,275 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>920237.BJ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>力王股份</t>
+          <t>力佳科技</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>17.83</v>
+        <v>13.95</v>
       </c>
       <c r="E73" t="n">
-        <v>29.9563</v>
+        <v>6.9785</v>
       </c>
       <c r="F73" t="n">
-        <v>25.69</v>
+        <v>10</v>
       </c>
       <c r="G73" t="n">
-        <v>287974500</v>
+        <v>128622700</v>
       </c>
       <c r="H73" t="n">
-        <v>30515041.64</v>
+        <v>13005066.59</v>
       </c>
       <c r="I73" t="n">
-        <v>40053504.63</v>
+        <v>13612770.22</v>
       </c>
       <c r="J73" t="n">
-        <v>70568546.27</v>
+        <v>26617836.81</v>
       </c>
       <c r="K73" t="n">
-        <v>9538462.99</v>
+        <v>607703.63</v>
       </c>
       <c r="L73" t="n">
-        <v>3.31</v>
+        <v>0.47</v>
       </c>
       <c r="M73" t="n">
-        <v>24.51</v>
+        <v>20.69</v>
       </c>
       <c r="N73" t="n">
-        <v>875408425</v>
+        <v>1300586372.1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+          <t>当日价格振幅达到30%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>920779.BJ</t>
+          <t>920289.BJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>武汉蓝电</t>
+          <t>华汇智能</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>33.13</v>
+        <v>28.65</v>
       </c>
       <c r="E74" t="n">
-        <v>15.8392</v>
+        <v>6.7437</v>
       </c>
       <c r="F74" t="n">
-        <v>40.86</v>
+        <v>37.27</v>
       </c>
       <c r="G74" t="n">
-        <v>258518200</v>
+        <v>155132300</v>
       </c>
       <c r="H74" t="n">
-        <v>25608051.69</v>
+        <v>13872782.22</v>
       </c>
       <c r="I74" t="n">
-        <v>25649205.87</v>
+        <v>27907557.75</v>
       </c>
       <c r="J74" t="n">
-        <v>51257257.56</v>
+        <v>41780339.97</v>
       </c>
       <c r="K74" t="n">
-        <v>41154.18</v>
+        <v>14034775.53</v>
       </c>
       <c r="L74" t="n">
-        <v>0.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M74" t="n">
-        <v>19.83</v>
+        <v>26.93</v>
       </c>
       <c r="N74" t="n">
-        <v>663262666.26</v>
+        <v>413992987.05</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>920627.BJ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>力王股份</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="E75" t="n">
+        <v>24.1167</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>357229400</v>
+      </c>
+      <c r="H75" t="n">
+        <v>38089359.86</v>
+      </c>
+      <c r="I75" t="n">
+        <v>29290329.36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67379689.22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8799030.5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1086527675</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>920779.BJ</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>武汉蓝电</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>33.13</v>
-      </c>
-      <c r="E75" t="n">
-        <v>15.8392</v>
-      </c>
-      <c r="F75" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="G75" t="n">
-        <v>663285800</v>
-      </c>
-      <c r="H75" t="n">
-        <v>66569614.56</v>
-      </c>
-      <c r="I75" t="n">
-        <v>74059746.19</v>
-      </c>
-      <c r="J75" t="n">
-        <v>140629360.75</v>
-      </c>
-      <c r="K75" t="n">
-        <v>7490131.63</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="M75" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>663262666.26</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+      <c r="D76" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.9922</v>
+      </c>
+      <c r="F76" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="G76" t="n">
+        <v>294336600</v>
+      </c>
+      <c r="H76" t="n">
+        <v>26834436.28</v>
+      </c>
+      <c r="I76" t="n">
+        <v>38385176.44</v>
+      </c>
+      <c r="J76" t="n">
+        <v>65219612.72</v>
+      </c>
+      <c r="K76" t="n">
+        <v>11550740.16</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M76" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="N76" t="n">
+        <v>676475867.58</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>19.1318</v>
+      </c>
+      <c r="F77" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="G77" t="n">
+        <v>206983800</v>
+      </c>
+      <c r="H77" t="n">
+        <v>26222869.27</v>
+      </c>
+      <c r="I77" t="n">
+        <v>28434295.77</v>
+      </c>
+      <c r="J77" t="n">
+        <v>54657165.04</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2211426.5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M77" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="N77" t="n">
+        <v>678190840</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5559</v>
+        <v>5561</v>
       </c>
       <c r="C2" t="n">
-        <v>3297</v>
+        <v>1167</v>
       </c>
       <c r="D2" t="n">
-        <v>2145</v>
+        <v>4325</v>
       </c>
       <c r="E2" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>19166.92</v>
+        <v>15507.53</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3813.7913</v>
+        <v>3797.2424</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>-0.43</v>
       </c>
       <c r="F2" t="n">
-        <v>8885.610000000001</v>
+        <v>7149.1</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12641.8584</v>
+        <v>12384.8692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>-2.03</v>
       </c>
       <c r="F3" t="n">
-        <v>5096.94</v>
+        <v>4067.92</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3043.3346</v>
+        <v>2963.8238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>-2.61</v>
       </c>
       <c r="F4" t="n">
-        <v>2005.97</v>
+        <v>1535.84</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4317.2549</v>
+        <v>4287.9798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="F5" t="n">
-        <v>4961.79</v>
+        <v>4055.74</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1457.2665</v>
+        <v>1426.7216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>-2.1</v>
       </c>
       <c r="F6" t="n">
-        <v>919.73</v>
+        <v>646.17</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7155.9114</v>
+        <v>7021.4723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.24</v>
+        <v>-1.88</v>
       </c>
       <c r="F7" t="n">
-        <v>3862.83</v>
+        <v>3101.5</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260918</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20929.06</v>
+        <v>20481.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20481.34</v>
+        <v>21536.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21536.52</v>
+        <v>17831.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17831.28</v>
+        <v>16691.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16691.12</v>
+        <v>17167.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17167.12</v>
+        <v>14215.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14215.96</v>
+        <v>14500.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14500.77</v>
+        <v>16942.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16942.91</v>
+        <v>19166.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19166.92</v>
+        <v>15507.53</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920157.BJ</t>
+          <t>301052.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81.09999999999999</v>
+        <v>25.69</v>
       </c>
       <c r="D2" t="n">
-        <v>86.38</v>
+        <v>30.47</v>
       </c>
       <c r="E2" t="n">
-        <v>72.01000000000001</v>
+        <v>25.69</v>
       </c>
       <c r="F2" t="n">
-        <v>75.55</v>
+        <v>30.47</v>
       </c>
       <c r="G2" t="n">
-        <v>13.75</v>
+        <v>25.39</v>
       </c>
       <c r="H2" t="n">
-        <v>61.8</v>
+        <v>5.08</v>
       </c>
       <c r="I2" t="n">
-        <v>449.4545</v>
+        <v>20.0079</v>
       </c>
       <c r="J2" t="n">
-        <v>122020.63</v>
+        <v>203919.93</v>
       </c>
       <c r="K2" t="n">
-        <v>958833.20633</v>
+        <v>583938.70791</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>688004.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.17</v>
+        <v>31.35</v>
       </c>
       <c r="D3" t="n">
-        <v>23.17</v>
+        <v>37.25</v>
       </c>
       <c r="E3" t="n">
-        <v>17.12</v>
+        <v>30.52</v>
       </c>
       <c r="F3" t="n">
-        <v>22.13</v>
+        <v>37.25</v>
       </c>
       <c r="G3" t="n">
-        <v>17.83</v>
+        <v>31.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>6.21</v>
       </c>
       <c r="I3" t="n">
-        <v>24.1167</v>
+        <v>20.0064</v>
       </c>
       <c r="J3" t="n">
-        <v>175694.48</v>
+        <v>119620.95</v>
       </c>
       <c r="K3" t="n">
-        <v>357229.39702</v>
+        <v>410465.083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920021.BJ</t>
+          <t>301419.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.39</v>
+        <v>39.71</v>
       </c>
       <c r="D4" t="n">
-        <v>9.18</v>
+        <v>47.7</v>
       </c>
       <c r="E4" t="n">
-        <v>7.16</v>
+        <v>39.55</v>
       </c>
       <c r="F4" t="n">
-        <v>8.83</v>
+        <v>47.7</v>
       </c>
       <c r="G4" t="n">
-        <v>7.35</v>
+        <v>39.75</v>
       </c>
       <c r="H4" t="n">
-        <v>1.48</v>
+        <v>7.95</v>
       </c>
       <c r="I4" t="n">
-        <v>20.1361</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>495461.84</v>
+        <v>92772.56</v>
       </c>
       <c r="K4" t="n">
-        <v>410490.50027</v>
+        <v>422151.50032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300369.SZ</t>
+          <t>300829.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.69</v>
+        <v>25.12</v>
       </c>
       <c r="D5" t="n">
-        <v>10.43</v>
+        <v>28.02</v>
       </c>
       <c r="E5" t="n">
-        <v>8.529999999999999</v>
+        <v>24.35</v>
       </c>
       <c r="F5" t="n">
-        <v>10.43</v>
+        <v>28.02</v>
       </c>
       <c r="G5" t="n">
-        <v>8.69</v>
+        <v>23.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>4.67</v>
       </c>
       <c r="I5" t="n">
-        <v>20.023</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>1056408.63</v>
+        <v>237566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1006656.8124</v>
+        <v>613444.3536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300530.SZ</t>
+          <t>301030.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26.41</v>
+        <v>3.97</v>
       </c>
       <c r="D6" t="n">
-        <v>28.9</v>
+        <v>4.5</v>
       </c>
       <c r="E6" t="n">
-        <v>25.77</v>
+        <v>3.97</v>
       </c>
       <c r="F6" t="n">
-        <v>28.9</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>24.08</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>4.82</v>
+        <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0166</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>258655.07</v>
+        <v>137275.4</v>
       </c>
       <c r="K6" t="n">
-        <v>722835.17603</v>
+        <v>58458.942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300821.SZ</t>
+          <t>688517.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="D7" t="n">
-        <v>17.15</v>
+        <v>21.18</v>
       </c>
       <c r="E7" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="F7" t="n">
-        <v>17.15</v>
+        <v>21.18</v>
       </c>
       <c r="G7" t="n">
-        <v>14.29</v>
+        <v>17.65</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>3.53</v>
       </c>
       <c r="I7" t="n">
-        <v>20.014</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>1507200.16</v>
+        <v>228305.37</v>
       </c>
       <c r="K7" t="n">
-        <v>2488094.39299</v>
+        <v>470683.174</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300364.SZ</t>
+          <t>301658.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.37</v>
+        <v>22.81</v>
       </c>
       <c r="D8" t="n">
-        <v>24.47</v>
+        <v>27.12</v>
       </c>
       <c r="E8" t="n">
-        <v>20.11</v>
+        <v>22.18</v>
       </c>
       <c r="F8" t="n">
-        <v>24.47</v>
+        <v>27.12</v>
       </c>
       <c r="G8" t="n">
-        <v>20.39</v>
+        <v>22.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.08</v>
+        <v>4.52</v>
       </c>
       <c r="I8" t="n">
-        <v>20.0098</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>831570.26</v>
+        <v>206230.04</v>
       </c>
       <c r="K8" t="n">
-        <v>1850122.25523</v>
+        <v>512184.2921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688152.SH</t>
+          <t>300006.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>6.56</v>
       </c>
       <c r="D9" t="n">
-        <v>45.85</v>
+        <v>6.56</v>
       </c>
       <c r="E9" t="n">
-        <v>37.45</v>
+        <v>6.21</v>
       </c>
       <c r="F9" t="n">
-        <v>45.85</v>
+        <v>6.56</v>
       </c>
       <c r="G9" t="n">
-        <v>38.21</v>
+        <v>5.47</v>
       </c>
       <c r="H9" t="n">
-        <v>7.64</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>19.9948</v>
+        <v>19.9269</v>
       </c>
       <c r="J9" t="n">
-        <v>114547.42</v>
+        <v>2041837.18</v>
       </c>
       <c r="K9" t="n">
-        <v>482931.983</v>
+        <v>1333525.06243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300981.SZ</t>
+          <t>920575.BJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.33</v>
+        <v>4.72</v>
       </c>
       <c r="D10" t="n">
-        <v>23.36</v>
+        <v>5.8</v>
       </c>
       <c r="E10" t="n">
-        <v>18.5</v>
+        <v>4.72</v>
       </c>
       <c r="F10" t="n">
-        <v>23.36</v>
+        <v>5.57</v>
       </c>
       <c r="G10" t="n">
-        <v>19.47</v>
+        <v>4.74</v>
       </c>
       <c r="H10" t="n">
-        <v>3.89</v>
+        <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>19.9795</v>
+        <v>17.5105</v>
       </c>
       <c r="J10" t="n">
-        <v>350282.29</v>
+        <v>110560.77</v>
       </c>
       <c r="K10" t="n">
-        <v>732402.93476</v>
+        <v>58988.24465</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300413.SZ</t>
+          <t>301310.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.25</v>
+        <v>61.72</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>18.79</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>19.17</v>
+        <v>60.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.83</v>
+        <v>9.83</v>
       </c>
       <c r="I11" t="n">
-        <v>19.9791</v>
+        <v>16.3561</v>
       </c>
       <c r="J11" t="n">
-        <v>1141206.62</v>
+        <v>138623.95</v>
       </c>
       <c r="K11" t="n">
-        <v>2384983.29123</v>
+        <v>916400.87578</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001246.SZ</t>
+          <t>688670.SH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.9</v>
+        <v>16.51</v>
       </c>
       <c r="D2" t="n">
-        <v>52.88</v>
+        <v>17.45</v>
       </c>
       <c r="E2" t="n">
-        <v>45.01</v>
+        <v>15.34</v>
       </c>
       <c r="F2" t="n">
-        <v>45.05</v>
+        <v>15.34</v>
       </c>
       <c r="G2" t="n">
-        <v>53.55</v>
+        <v>19.17</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.5</v>
+        <v>-3.83</v>
       </c>
       <c r="I2" t="n">
-        <v>-15.873</v>
+        <v>-19.9791</v>
       </c>
       <c r="J2" t="n">
-        <v>719258.23</v>
+        <v>33601.26</v>
       </c>
       <c r="K2" t="n">
-        <v>3466031.17698</v>
+        <v>52771.278</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300599.SZ</t>
+          <t>688796.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.13</v>
+        <v>115.26</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>13.52</v>
+        <v>94.56</v>
       </c>
       <c r="G3" t="n">
-        <v>15.58</v>
+        <v>114.98</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.06</v>
+        <v>-20.42</v>
       </c>
       <c r="I3" t="n">
-        <v>-13.2221</v>
+        <v>-17.7596</v>
       </c>
       <c r="J3" t="n">
-        <v>396262.14</v>
+        <v>61350.93</v>
       </c>
       <c r="K3" t="n">
-        <v>525414.72092</v>
+        <v>621032.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>300198.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>2.05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>2.18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>2.02</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.7143</v>
+        <v>-15.1261</v>
       </c>
       <c r="J4" t="n">
-        <v>29339</v>
+        <v>484686.69</v>
       </c>
       <c r="K4" t="n">
-        <v>1466.95</v>
+        <v>100540.93345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300491.SZ</t>
+          <t>688662.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.61</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>31.82</v>
+        <v>110</v>
       </c>
       <c r="E5" t="n">
-        <v>27.13</v>
+        <v>95.81</v>
       </c>
       <c r="F5" t="n">
-        <v>28.9</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>32.17</v>
+        <v>114.76</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.27</v>
+        <v>-15.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.1647</v>
+        <v>-13.6459</v>
       </c>
       <c r="J5" t="n">
-        <v>206981.96</v>
+        <v>171882.76</v>
       </c>
       <c r="K5" t="n">
-        <v>594450.26816</v>
+        <v>1717867.811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>603073.SH</t>
+          <t>001246.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.97</v>
+        <v>43.5</v>
       </c>
       <c r="D6" t="n">
-        <v>22.97</v>
+        <v>44.1</v>
       </c>
       <c r="E6" t="n">
-        <v>20.67</v>
+        <v>38.98</v>
       </c>
       <c r="F6" t="n">
-        <v>20.67</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>22.97</v>
+        <v>45.05</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3</v>
+        <v>-6.05</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.0131</v>
+        <v>-13.4295</v>
       </c>
       <c r="J6" t="n">
-        <v>95831</v>
+        <v>596146.98</v>
       </c>
       <c r="K6" t="n">
-        <v>201331.598</v>
+        <v>2453944.30277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>002962.SZ</t>
+          <t>688399.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15.9</v>
+        <v>28.52</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>15.02</v>
+        <v>25.84</v>
       </c>
       <c r="F7" t="n">
-        <v>15.02</v>
+        <v>26.31</v>
       </c>
       <c r="G7" t="n">
-        <v>16.69</v>
+        <v>29.92</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.67</v>
+        <v>-3.61</v>
       </c>
       <c r="I7" t="n">
-        <v>-10.006</v>
+        <v>-12.0655</v>
       </c>
       <c r="J7" t="n">
-        <v>218946.31</v>
+        <v>72222.50999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>333502.54913</v>
+        <v>192969.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>603823.SH</t>
+          <t>300464.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45.01</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>45.13</v>
+        <v>9.42</v>
       </c>
       <c r="E8" t="n">
-        <v>41.93</v>
+        <v>8.34</v>
       </c>
       <c r="F8" t="n">
-        <v>41.93</v>
+        <v>8.34</v>
       </c>
       <c r="G8" t="n">
-        <v>46.59</v>
+        <v>9.35</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.66</v>
+        <v>-1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>-10.0021</v>
+        <v>-10.8021</v>
       </c>
       <c r="J8" t="n">
-        <v>203173.18</v>
+        <v>234014</v>
       </c>
       <c r="K8" t="n">
-        <v>855381.191</v>
+        <v>202460.839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>002927.SZ</t>
+          <t>688117.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.67</v>
+        <v>16.9</v>
       </c>
       <c r="D9" t="n">
-        <v>19.93</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>17.64</v>
+        <v>15.8</v>
       </c>
       <c r="F9" t="n">
-        <v>17.64</v>
+        <v>16.09</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6</v>
+        <v>18.03</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.96</v>
+        <v>-1.94</v>
       </c>
       <c r="I9" t="n">
-        <v>-10</v>
+        <v>-10.7598</v>
       </c>
       <c r="J9" t="n">
-        <v>159631</v>
+        <v>164429.83</v>
       </c>
       <c r="K9" t="n">
-        <v>289675.61275</v>
+        <v>269364.835</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>603400.SH</t>
+          <t>688655.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45.8</v>
+        <v>63.01</v>
       </c>
       <c r="D10" t="n">
-        <v>46.25</v>
+        <v>64.44</v>
       </c>
       <c r="E10" t="n">
-        <v>42.93</v>
+        <v>58.08</v>
       </c>
       <c r="F10" t="n">
-        <v>42.93</v>
+        <v>58.99</v>
       </c>
       <c r="G10" t="n">
-        <v>47.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.77</v>
+        <v>-7.11</v>
       </c>
       <c r="I10" t="n">
-        <v>-10</v>
+        <v>-10.7564</v>
       </c>
       <c r="J10" t="n">
-        <v>65689.42999999999</v>
+        <v>141261.3</v>
       </c>
       <c r="K10" t="n">
-        <v>286680.592</v>
+        <v>856477.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002487.SZ</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.23</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>32.98</v>
       </c>
       <c r="E11" t="n">
-        <v>43.75</v>
+        <v>30.1</v>
       </c>
       <c r="F11" t="n">
-        <v>43.75</v>
+        <v>30.24</v>
       </c>
       <c r="G11" t="n">
-        <v>48.61</v>
+        <v>33.79</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.86</v>
+        <v>-3.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.9979</v>
+        <v>-10.5061</v>
       </c>
       <c r="J11" t="n">
-        <v>1051507.1</v>
+        <v>57117.04</v>
       </c>
       <c r="K11" t="n">
-        <v>4957547.92194</v>
+        <v>178534.35799</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,216 +1819,216 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000011.SZ</t>
+          <t>000678.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.59</v>
+        <v>11.36</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8779</v>
+        <v>-9.9842</v>
       </c>
       <c r="F2" t="n">
-        <v>21.58</v>
+        <v>14.23</v>
       </c>
       <c r="G2" t="n">
-        <v>1377987783</v>
+        <v>757113723</v>
       </c>
       <c r="H2" t="n">
-        <v>167478280.14</v>
+        <v>132066744.55</v>
       </c>
       <c r="I2" t="n">
-        <v>133387168.32</v>
+        <v>112767131.65</v>
       </c>
       <c r="J2" t="n">
-        <v>300865448.46</v>
+        <v>244833876.2</v>
       </c>
       <c r="K2" t="n">
-        <v>-34091111.82</v>
+        <v>-19299612.9</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.47</v>
+        <v>-2.55</v>
       </c>
       <c r="M2" t="n">
-        <v>21.83</v>
+        <v>32.34</v>
       </c>
       <c r="N2" t="n">
-        <v>6837227287.24</v>
+        <v>5221190013.92</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000420.SZ</t>
+          <t>000710.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>贝瑞基因</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.81</v>
+        <v>11.7</v>
       </c>
       <c r="E3" t="n">
-        <v>10.1156</v>
+        <v>3.5398</v>
       </c>
       <c r="F3" t="n">
-        <v>9.76</v>
+        <v>27.83</v>
       </c>
       <c r="G3" t="n">
-        <v>893374748</v>
+        <v>1085607127</v>
       </c>
       <c r="H3" t="n">
-        <v>55135495.22</v>
+        <v>240644868.78</v>
       </c>
       <c r="I3" t="n">
-        <v>233514396.34</v>
+        <v>138171373</v>
       </c>
       <c r="J3" t="n">
-        <v>288649891.56</v>
+        <v>378816241.78</v>
       </c>
       <c r="K3" t="n">
-        <v>178378901.12</v>
+        <v>-102473495.78</v>
       </c>
       <c r="L3" t="n">
-        <v>19.97</v>
+        <v>-9.44</v>
       </c>
       <c r="M3" t="n">
-        <v>32.31</v>
+        <v>34.89</v>
       </c>
       <c r="N3" t="n">
-        <v>9367934056.83</v>
+        <v>3925670088.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000678.SZ</t>
+          <t>000892.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.62</v>
+        <v>5.34</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1046</v>
+        <v>10.1031</v>
       </c>
       <c r="F4" t="n">
-        <v>26.56</v>
+        <v>33.81</v>
       </c>
       <c r="G4" t="n">
-        <v>1454170493</v>
+        <v>1258263822</v>
       </c>
       <c r="H4" t="n">
-        <v>193749490.99</v>
+        <v>228913714.3</v>
       </c>
       <c r="I4" t="n">
-        <v>175303749.55</v>
+        <v>184517231.45</v>
       </c>
       <c r="J4" t="n">
-        <v>369053240.54</v>
+        <v>413430945.75</v>
       </c>
       <c r="K4" t="n">
-        <v>-18445741.44</v>
+        <v>-44396482.85</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.27</v>
+        <v>-3.53</v>
       </c>
       <c r="M4" t="n">
-        <v>25.38</v>
+        <v>32.86</v>
       </c>
       <c r="N4" t="n">
-        <v>5800300878.14</v>
+        <v>3795665613.36</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000911.SZ</t>
+          <t>000892.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*ST广糖</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.06</v>
+        <v>5.34</v>
       </c>
       <c r="E5" t="n">
-        <v>7.2566</v>
+        <v>10.1031</v>
       </c>
       <c r="F5" t="n">
-        <v>5.28</v>
+        <v>33.81</v>
       </c>
       <c r="G5" t="n">
-        <v>269457465</v>
+        <v>1869331060</v>
       </c>
       <c r="H5" t="n">
-        <v>53700708</v>
+        <v>306971720.6</v>
       </c>
       <c r="I5" t="n">
-        <v>36102266</v>
+        <v>316854405.15</v>
       </c>
       <c r="J5" t="n">
-        <v>89802974</v>
+        <v>623826125.75</v>
       </c>
       <c r="K5" t="n">
-        <v>-17598442</v>
+        <v>9882684.550000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.53</v>
+        <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>33.33</v>
+        <v>33.37</v>
       </c>
       <c r="N5" t="n">
-        <v>2425938097.08</v>
+        <v>3795665613.36</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2039,117 +2039,117 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001216.SZ</t>
+          <t>001300.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>三柏硕</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.75</v>
+        <v>13.39</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.438</v>
+        <v>-9.892300000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14.89</v>
+        <v>13.81</v>
       </c>
       <c r="G6" t="n">
-        <v>1951239174</v>
+        <v>483870745</v>
       </c>
       <c r="H6" t="n">
-        <v>138646197.46</v>
+        <v>56280595</v>
       </c>
       <c r="I6" t="n">
-        <v>111797870.56</v>
+        <v>35305550</v>
       </c>
       <c r="J6" t="n">
-        <v>250444068.02</v>
+        <v>91586145</v>
       </c>
       <c r="K6" t="n">
-        <v>-26848326.9</v>
+        <v>-20975045</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.38</v>
+        <v>-4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>12.84</v>
+        <v>18.93</v>
       </c>
       <c r="N6" t="n">
-        <v>5615523527.25</v>
+        <v>3264159488.46</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>001300.SZ</t>
+          <t>001330.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>三柏硕</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.86</v>
+        <v>7.67</v>
       </c>
       <c r="E7" t="n">
-        <v>9.992599999999999</v>
+        <v>10.043</v>
       </c>
       <c r="F7" t="n">
-        <v>3.41</v>
+        <v>17.8</v>
       </c>
       <c r="G7" t="n">
-        <v>235208453</v>
+        <v>1572119116</v>
       </c>
       <c r="H7" t="n">
-        <v>62910724</v>
+        <v>196580927</v>
       </c>
       <c r="I7" t="n">
-        <v>51357611</v>
+        <v>282189197</v>
       </c>
       <c r="J7" t="n">
-        <v>114268335</v>
+        <v>478770124</v>
       </c>
       <c r="K7" t="n">
-        <v>-11553113</v>
+        <v>85608270</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.91</v>
+        <v>5.45</v>
       </c>
       <c r="M7" t="n">
-        <v>48.58</v>
+        <v>30.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3622510082.04</v>
+        <v>8919038959.74</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2163,48 +2163,48 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.97</v>
+        <v>7.67</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9369</v>
+        <v>10.043</v>
       </c>
       <c r="F8" t="n">
-        <v>20.92</v>
+        <v>17.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1615588593</v>
+        <v>3187707709</v>
       </c>
       <c r="H8" t="n">
-        <v>264020977.62</v>
+        <v>435957637.62</v>
       </c>
       <c r="I8" t="n">
-        <v>203306769</v>
+        <v>418426843</v>
       </c>
       <c r="J8" t="n">
-        <v>467327746.62</v>
+        <v>854384480.62</v>
       </c>
       <c r="K8" t="n">
-        <v>-60714208.62</v>
+        <v>-17530794.62</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.76</v>
+        <v>-0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>28.93</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8105045834.34</v>
+        <v>8919038959.74</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2218,48 +2218,48 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.72</v>
+        <v>20.45</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0242</v>
+        <v>-9.991199999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>24.13</v>
+        <v>33.6</v>
       </c>
       <c r="G9" t="n">
-        <v>472608883</v>
+        <v>464210412</v>
       </c>
       <c r="H9" t="n">
-        <v>98576659.09999999</v>
+        <v>69050328.84999999</v>
       </c>
       <c r="I9" t="n">
-        <v>77260224.56</v>
+        <v>56574144.22</v>
       </c>
       <c r="J9" t="n">
-        <v>175836883.66</v>
+        <v>125624473.07</v>
       </c>
       <c r="K9" t="n">
-        <v>-21316434.54</v>
+        <v>-12476184.63</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.51</v>
+        <v>-2.69</v>
       </c>
       <c r="M9" t="n">
-        <v>37.21</v>
+        <v>27.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1460865623.36</v>
+        <v>1314907658.35</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2273,202 +2273,202 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24.44</v>
+        <v>25.3</v>
       </c>
       <c r="E10" t="n">
-        <v>9.991</v>
+        <v>3.5188</v>
       </c>
       <c r="F10" t="n">
-        <v>2.88</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>205210859</v>
+        <v>816172969</v>
       </c>
       <c r="H10" t="n">
-        <v>37451930</v>
+        <v>102041889.72</v>
       </c>
       <c r="I10" t="n">
-        <v>30675531</v>
+        <v>58379711.57</v>
       </c>
       <c r="J10" t="n">
-        <v>68127461</v>
+        <v>160421601.29</v>
       </c>
       <c r="K10" t="n">
-        <v>-6776399</v>
+        <v>-43662178.15</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.3</v>
+        <v>-5.35</v>
       </c>
       <c r="M10" t="n">
-        <v>33.2</v>
+        <v>19.66</v>
       </c>
       <c r="N10" t="n">
-        <v>3503860934.08</v>
+        <v>3627155549.6</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002172.SZ</t>
+          <t>002242.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>澳洋健康</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.91</v>
+        <v>16.64</v>
       </c>
       <c r="E11" t="n">
-        <v>4.417</v>
+        <v>9.9802</v>
       </c>
       <c r="F11" t="n">
-        <v>25.82</v>
+        <v>16.07</v>
       </c>
       <c r="G11" t="n">
-        <v>1149758062</v>
+        <v>1996903757</v>
       </c>
       <c r="H11" t="n">
-        <v>103860574.72</v>
+        <v>286332667.56</v>
       </c>
       <c r="I11" t="n">
-        <v>84830721.01000001</v>
+        <v>127212502.6</v>
       </c>
       <c r="J11" t="n">
-        <v>188691295.73</v>
+        <v>413545170.16</v>
       </c>
       <c r="K11" t="n">
-        <v>-19029853.71</v>
+        <v>-159120164.96</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.66</v>
+        <v>-7.97</v>
       </c>
       <c r="M11" t="n">
-        <v>16.41</v>
+        <v>20.71</v>
       </c>
       <c r="N11" t="n">
-        <v>4521981714.3</v>
+        <v>12675780000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002212.SZ</t>
+          <t>002242.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.56</v>
+        <v>16.64</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0437</v>
+        <v>9.9802</v>
       </c>
       <c r="F12" t="n">
-        <v>10.56</v>
+        <v>16.07</v>
       </c>
       <c r="G12" t="n">
-        <v>882347755</v>
+        <v>4059620364</v>
       </c>
       <c r="H12" t="n">
-        <v>93560126.31999999</v>
+        <v>287878486.9</v>
       </c>
       <c r="I12" t="n">
-        <v>214479084.1</v>
+        <v>250629770.38</v>
       </c>
       <c r="J12" t="n">
-        <v>308039210.42</v>
+        <v>538508257.28</v>
       </c>
       <c r="K12" t="n">
-        <v>120918957.78</v>
+        <v>-37248716.52</v>
       </c>
       <c r="L12" t="n">
-        <v>13.7</v>
+        <v>-0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>34.91</v>
+        <v>13.26</v>
       </c>
       <c r="N12" t="n">
-        <v>8821379823.48</v>
+        <v>12675780000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002242.SZ</t>
+          <t>002264.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>新华都</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.13</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0364</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>18.28</v>
+        <v>21.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2062716607</v>
+        <v>1122462178</v>
       </c>
       <c r="H13" t="n">
-        <v>126917409.85</v>
+        <v>92697093.25</v>
       </c>
       <c r="I13" t="n">
-        <v>263931036.53</v>
+        <v>210993179</v>
       </c>
       <c r="J13" t="n">
-        <v>390848446.38</v>
+        <v>303690272.25</v>
       </c>
       <c r="K13" t="n">
-        <v>137013626.68</v>
+        <v>118296085.75</v>
       </c>
       <c r="L13" t="n">
-        <v>6.64</v>
+        <v>10.54</v>
       </c>
       <c r="M13" t="n">
-        <v>18.95</v>
+        <v>27.06</v>
       </c>
       <c r="N13" t="n">
-        <v>11525513906.25</v>
+        <v>5298390078.08</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2493,202 +2493,202 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8692</v>
+        <v>-10.0917</v>
       </c>
       <c r="F14" t="n">
-        <v>16.73</v>
+        <v>12.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1078343001</v>
+        <v>755354600</v>
       </c>
       <c r="H14" t="n">
-        <v>264195885.59</v>
+        <v>210766159.58</v>
       </c>
       <c r="I14" t="n">
-        <v>163602976.27</v>
+        <v>137270590</v>
       </c>
       <c r="J14" t="n">
-        <v>427798861.86</v>
+        <v>348036749.58</v>
       </c>
       <c r="K14" t="n">
-        <v>-100592909.32</v>
+        <v>-73495569.58</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.33</v>
+        <v>-9.73</v>
       </c>
       <c r="M14" t="n">
-        <v>39.67</v>
+        <v>46.08</v>
       </c>
       <c r="N14" t="n">
-        <v>6471360675.87</v>
+        <v>5818287580.14</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002316.SZ</t>
+          <t>002343.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>亚联发展</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.85</v>
+        <v>6.69</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6104</v>
+        <v>10.0329</v>
       </c>
       <c r="F15" t="n">
-        <v>34.15</v>
+        <v>5.99</v>
       </c>
       <c r="G15" t="n">
-        <v>548642459</v>
+        <v>329715076</v>
       </c>
       <c r="H15" t="n">
-        <v>80000080.93000001</v>
+        <v>44462900.44</v>
       </c>
       <c r="I15" t="n">
-        <v>98476173</v>
+        <v>60187573.61</v>
       </c>
       <c r="J15" t="n">
-        <v>178476253.93</v>
+        <v>104650474.05</v>
       </c>
       <c r="K15" t="n">
-        <v>18476092.07</v>
+        <v>15724673.17</v>
       </c>
       <c r="L15" t="n">
-        <v>3.37</v>
+        <v>4.77</v>
       </c>
       <c r="M15" t="n">
-        <v>32.53</v>
+        <v>31.74</v>
       </c>
       <c r="N15" t="n">
-        <v>1652564750</v>
+        <v>3168921113.34</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002317.SZ</t>
+          <t>002396.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>众生药业</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.49</v>
+        <v>28.11</v>
       </c>
       <c r="E16" t="n">
-        <v>10.0129</v>
+        <v>-9.990399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>6.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1221113050</v>
+        <v>2138321909</v>
       </c>
       <c r="H16" t="n">
-        <v>231001905.97</v>
+        <v>552234506.79</v>
       </c>
       <c r="I16" t="n">
-        <v>288677065.67</v>
+        <v>345728347.88</v>
       </c>
       <c r="J16" t="n">
-        <v>519678971.64</v>
+        <v>897962854.67</v>
       </c>
       <c r="K16" t="n">
-        <v>57675159.7</v>
+        <v>-206506158.91</v>
       </c>
       <c r="L16" t="n">
-        <v>4.72</v>
+        <v>-9.66</v>
       </c>
       <c r="M16" t="n">
-        <v>42.56</v>
+        <v>41.99</v>
       </c>
       <c r="N16" t="n">
-        <v>19576889217.19</v>
+        <v>21290938629.66</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002487.SZ</t>
+          <t>002413.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大金重工</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.75</v>
+        <v>7.87</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.9979</v>
+        <v>-9.9542</v>
       </c>
       <c r="F17" t="n">
-        <v>16.67</v>
+        <v>11.44</v>
       </c>
       <c r="G17" t="n">
-        <v>4957547922</v>
+        <v>1225786153</v>
       </c>
       <c r="H17" t="n">
-        <v>390508820.22</v>
+        <v>174457517.23</v>
       </c>
       <c r="I17" t="n">
-        <v>426474471.03</v>
+        <v>106869920.06</v>
       </c>
       <c r="J17" t="n">
-        <v>816983291.25</v>
+        <v>281327437.29</v>
       </c>
       <c r="K17" t="n">
-        <v>35965650.81</v>
+        <v>-67587597.17</v>
       </c>
       <c r="L17" t="n">
-        <v>0.73</v>
+        <v>-5.51</v>
       </c>
       <c r="M17" t="n">
-        <v>16.48</v>
+        <v>22.95</v>
       </c>
       <c r="N17" t="n">
-        <v>27602761637.5</v>
+        <v>10195038011.39</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2713,257 +2713,257 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.52</v>
+        <v>8.27</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.940099999999999</v>
+        <v>9.9734</v>
       </c>
       <c r="F18" t="n">
-        <v>9.869999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1398297545</v>
+        <v>839926261</v>
       </c>
       <c r="H18" t="n">
-        <v>131438736.36</v>
+        <v>46323956.02</v>
       </c>
       <c r="I18" t="n">
-        <v>113156976.48</v>
+        <v>296299895.83</v>
       </c>
       <c r="J18" t="n">
-        <v>244595712.84</v>
+        <v>342623851.85</v>
       </c>
       <c r="K18" t="n">
-        <v>-18281759.88</v>
+        <v>249975939.81</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.31</v>
+        <v>29.76</v>
       </c>
       <c r="M18" t="n">
-        <v>17.49</v>
+        <v>40.79</v>
       </c>
       <c r="N18" t="n">
-        <v>13437251864.48</v>
+        <v>14777403313.73</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002636.SZ</t>
+          <t>002630.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>*ST华西</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.67</v>
+        <v>1.77</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.9962</v>
+        <v>5.988</v>
       </c>
       <c r="F19" t="n">
-        <v>5.37</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2807666916</v>
+        <v>69094117</v>
       </c>
       <c r="H19" t="n">
-        <v>165938892.54</v>
+        <v>8011677.28</v>
       </c>
       <c r="I19" t="n">
-        <v>278827847.78</v>
+        <v>8560571</v>
       </c>
       <c r="J19" t="n">
-        <v>444766740.32</v>
+        <v>16572248.28</v>
       </c>
       <c r="K19" t="n">
-        <v>112888955.24</v>
+        <v>548893.72</v>
       </c>
       <c r="L19" t="n">
-        <v>4.02</v>
+        <v>0.79</v>
       </c>
       <c r="M19" t="n">
-        <v>15.84</v>
+        <v>23.99</v>
       </c>
       <c r="N19" t="n">
-        <v>51977704470.21</v>
+        <v>1905473702.55</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002702.SZ</t>
+          <t>002630.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>海欣食品</t>
+          <t>*ST华西</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.16</v>
+        <v>1.77</v>
       </c>
       <c r="E20" t="n">
-        <v>4.0541</v>
+        <v>5.988</v>
       </c>
       <c r="F20" t="n">
-        <v>36.76</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1034853104</v>
+        <v>210733790</v>
       </c>
       <c r="H20" t="n">
-        <v>160261389.99</v>
+        <v>16534021.72</v>
       </c>
       <c r="I20" t="n">
-        <v>115983353.3</v>
+        <v>20128764</v>
       </c>
       <c r="J20" t="n">
-        <v>276244743.29</v>
+        <v>36662785.72</v>
       </c>
       <c r="K20" t="n">
-        <v>-44278036.69</v>
+        <v>3594742.28</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.28</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>26.69</v>
+        <v>17.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2825861500</v>
+        <v>1905473702.55</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002733.SZ</t>
+          <t>002636.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.78</v>
+        <v>64.5</v>
       </c>
       <c r="E21" t="n">
-        <v>10.0053</v>
+        <v>-10.0042</v>
       </c>
       <c r="F21" t="n">
-        <v>5.71</v>
+        <v>5.25</v>
       </c>
       <c r="G21" t="n">
-        <v>738681096</v>
+        <v>2519216770</v>
       </c>
       <c r="H21" t="n">
-        <v>68556974.68000001</v>
+        <v>165349453.48</v>
       </c>
       <c r="I21" t="n">
-        <v>225547175.75</v>
+        <v>255343913.54</v>
       </c>
       <c r="J21" t="n">
-        <v>294104150.43</v>
+        <v>420693367.02</v>
       </c>
       <c r="K21" t="n">
-        <v>156990201.07</v>
+        <v>89994460.06</v>
       </c>
       <c r="L21" t="n">
-        <v>21.25</v>
+        <v>3.57</v>
       </c>
       <c r="M21" t="n">
-        <v>39.81</v>
+        <v>16.7</v>
       </c>
       <c r="N21" t="n">
-        <v>7664968132.02</v>
+        <v>46777758313.5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002805.SZ</t>
+          <t>002692.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>远程股份</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.44</v>
+        <v>5.24</v>
       </c>
       <c r="E22" t="n">
-        <v>10.017</v>
+        <v>10.084</v>
       </c>
       <c r="F22" t="n">
-        <v>11.36</v>
+        <v>7.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1032172020</v>
+        <v>346829505</v>
       </c>
       <c r="H22" t="n">
-        <v>166040397.98</v>
+        <v>53816194.6</v>
       </c>
       <c r="I22" t="n">
-        <v>206318135.27</v>
+        <v>92201160.40000001</v>
       </c>
       <c r="J22" t="n">
-        <v>372358533.25</v>
+        <v>146017355</v>
       </c>
       <c r="K22" t="n">
-        <v>40277737.29</v>
+        <v>38384965.8</v>
       </c>
       <c r="L22" t="n">
-        <v>3.9</v>
+        <v>11.07</v>
       </c>
       <c r="M22" t="n">
-        <v>36.08</v>
+        <v>42.1</v>
       </c>
       <c r="N22" t="n">
-        <v>5420184361.92</v>
+        <v>3761595177</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2974,381 +2974,381 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002866.SZ</t>
+          <t>002696.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4524</v>
+        <v>9.9727</v>
       </c>
       <c r="F23" t="n">
-        <v>41.53</v>
+        <v>3.89</v>
       </c>
       <c r="G23" t="n">
-        <v>1452604141</v>
+        <v>312591690</v>
       </c>
       <c r="H23" t="n">
-        <v>188722908.01</v>
+        <v>45853020</v>
       </c>
       <c r="I23" t="n">
-        <v>137642704.44</v>
+        <v>91225018.14</v>
       </c>
       <c r="J23" t="n">
-        <v>326365612.45</v>
+        <v>137078038.14</v>
       </c>
       <c r="K23" t="n">
-        <v>-51080203.57</v>
+        <v>45371998.14</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.52</v>
+        <v>14.51</v>
       </c>
       <c r="M23" t="n">
-        <v>22.47</v>
+        <v>43.85</v>
       </c>
       <c r="N23" t="n">
-        <v>3366646138.08</v>
+        <v>2690784289.9</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002927.SZ</t>
+          <t>002717.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>泰永长征</t>
+          <t>*ST岭南</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.64</v>
+        <v>0.45</v>
       </c>
       <c r="E24" t="n">
         <v>-10</v>
       </c>
       <c r="F24" t="n">
-        <v>7.23</v>
+        <v>0.27</v>
       </c>
       <c r="G24" t="n">
-        <v>289675613</v>
+        <v>4833643</v>
       </c>
       <c r="H24" t="n">
-        <v>43702465.23</v>
+        <v>1878791</v>
       </c>
       <c r="I24" t="n">
-        <v>48963901</v>
+        <v>657881</v>
       </c>
       <c r="J24" t="n">
-        <v>92666366.23</v>
+        <v>2536672</v>
       </c>
       <c r="K24" t="n">
-        <v>5261435.77</v>
+        <v>-1220910</v>
       </c>
       <c r="L24" t="n">
-        <v>1.82</v>
+        <v>-25.26</v>
       </c>
       <c r="M24" t="n">
-        <v>31.99</v>
+        <v>52.48</v>
       </c>
       <c r="N24" t="n">
-        <v>3893815356.48</v>
+        <v>805023839.7</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002962.SZ</t>
+          <t>002805.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>五方光电</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.02</v>
+        <v>18.86</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.006</v>
+        <v>-2.9835</v>
       </c>
       <c r="F25" t="n">
-        <v>10.47</v>
+        <v>28.1</v>
       </c>
       <c r="G25" t="n">
-        <v>333502549</v>
+        <v>1557932557</v>
       </c>
       <c r="H25" t="n">
-        <v>78905345.93000001</v>
+        <v>279362408.11</v>
       </c>
       <c r="I25" t="n">
-        <v>34448153.73</v>
+        <v>253124816.96</v>
       </c>
       <c r="J25" t="n">
-        <v>113353499.66</v>
+        <v>532487225.07</v>
       </c>
       <c r="K25" t="n">
-        <v>-44457192.2</v>
+        <v>-26237591.15</v>
       </c>
       <c r="L25" t="n">
-        <v>-13.33</v>
+        <v>-1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>33.99</v>
+        <v>34.18</v>
       </c>
       <c r="N25" t="n">
-        <v>3142420264.6</v>
+        <v>5258471042.48</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300189.SZ</t>
+          <t>002866.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>神农种业</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.69</v>
+        <v>19.15</v>
       </c>
       <c r="E26" t="n">
-        <v>10.396</v>
+        <v>4.5306</v>
       </c>
       <c r="F26" t="n">
-        <v>34.05</v>
+        <v>36.34</v>
       </c>
       <c r="G26" t="n">
-        <v>1928072616</v>
+        <v>1257585997</v>
       </c>
       <c r="H26" t="n">
-        <v>179670757.3</v>
+        <v>153251813.11</v>
       </c>
       <c r="I26" t="n">
-        <v>251494209.16</v>
+        <v>118185052.15</v>
       </c>
       <c r="J26" t="n">
-        <v>431164966.46</v>
+        <v>271436865.26</v>
       </c>
       <c r="K26" t="n">
-        <v>71823451.86</v>
+        <v>-35066760.96</v>
       </c>
       <c r="L26" t="n">
-        <v>3.73</v>
+        <v>-2.79</v>
       </c>
       <c r="M26" t="n">
-        <v>22.36</v>
+        <v>21.58</v>
       </c>
       <c r="N26" t="n">
-        <v>5929015336.56</v>
+        <v>3519174320.1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300364.SZ</t>
+          <t>002869.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>金溢科技</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24.47</v>
+        <v>20.68</v>
       </c>
       <c r="E27" t="n">
-        <v>20.0098</v>
+        <v>6.3239</v>
       </c>
       <c r="F27" t="n">
-        <v>12.58</v>
+        <v>11.15</v>
       </c>
       <c r="G27" t="n">
-        <v>1850122255</v>
+        <v>890350805</v>
       </c>
       <c r="H27" t="n">
-        <v>222961391.4</v>
+        <v>113287381.49</v>
       </c>
       <c r="I27" t="n">
-        <v>366013366.63</v>
+        <v>201682771.26</v>
       </c>
       <c r="J27" t="n">
-        <v>588974758.03</v>
+        <v>314970152.75</v>
       </c>
       <c r="K27" t="n">
-        <v>143051975.23</v>
+        <v>88395389.77</v>
       </c>
       <c r="L27" t="n">
-        <v>7.73</v>
+        <v>9.93</v>
       </c>
       <c r="M27" t="n">
-        <v>31.83</v>
+        <v>35.38</v>
       </c>
       <c r="N27" t="n">
-        <v>16176766173.61</v>
+        <v>3276855169.72</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300369.SZ</t>
+          <t>200056.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>*ST皇庭B</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.43</v>
+        <v>0.53</v>
       </c>
       <c r="E28" t="n">
-        <v>20.023</v>
+        <v>-10.1695</v>
       </c>
       <c r="F28" t="n">
-        <v>13.07</v>
+        <v>0.13</v>
       </c>
       <c r="G28" t="n">
-        <v>1006656812</v>
+        <v>143763</v>
       </c>
       <c r="H28" t="n">
-        <v>137297847.8</v>
+        <v>143763.13</v>
       </c>
       <c r="I28" t="n">
-        <v>305361218.19</v>
+        <v>114663.02</v>
       </c>
       <c r="J28" t="n">
-        <v>442659065.99</v>
+        <v>258426.15</v>
       </c>
       <c r="K28" t="n">
-        <v>168063370.39</v>
+        <v>-29100.11</v>
       </c>
       <c r="L28" t="n">
-        <v>16.7</v>
+        <v>-20.24</v>
       </c>
       <c r="M28" t="n">
-        <v>43.97</v>
+        <v>179.76</v>
       </c>
       <c r="N28" t="n">
-        <v>8428023329.04</v>
+        <v>2324986251.8</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300413.SZ</t>
+          <t>300006.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>6.56</v>
       </c>
       <c r="E29" t="n">
-        <v>19.9791</v>
+        <v>19.9269</v>
       </c>
       <c r="F29" t="n">
-        <v>11.17</v>
+        <v>19.34</v>
       </c>
       <c r="G29" t="n">
-        <v>2384983291</v>
+        <v>1333525062</v>
       </c>
       <c r="H29" t="n">
-        <v>334146406.57</v>
+        <v>228733785.98</v>
       </c>
       <c r="I29" t="n">
-        <v>316089999.15</v>
+        <v>549451533.54</v>
       </c>
       <c r="J29" t="n">
-        <v>650236405.72</v>
+        <v>778185319.52</v>
       </c>
       <c r="K29" t="n">
-        <v>-18056407.42</v>
+        <v>320717747.56</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.76</v>
+        <v>24.05</v>
       </c>
       <c r="M29" t="n">
-        <v>27.26</v>
+        <v>58.36</v>
       </c>
       <c r="N29" t="n">
-        <v>23499099034</v>
+        <v>6926185090.88</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3359,1481 +3359,1481 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300821.SZ</t>
+          <t>300198.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>*ST纳川</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17.15</v>
+        <v>2.02</v>
       </c>
       <c r="E30" t="n">
-        <v>20.014</v>
+        <v>-15.1261</v>
       </c>
       <c r="F30" t="n">
-        <v>12.56</v>
+        <v>4.73</v>
       </c>
       <c r="G30" t="n">
-        <v>2488094393</v>
+        <v>100540933</v>
       </c>
       <c r="H30" t="n">
-        <v>289775652.47</v>
+        <v>14672829</v>
       </c>
       <c r="I30" t="n">
-        <v>477357946.86</v>
+        <v>8885806.35</v>
       </c>
       <c r="J30" t="n">
-        <v>767133599.33</v>
+        <v>23558635.35</v>
       </c>
       <c r="K30" t="n">
-        <v>187582294.39</v>
+        <v>-5787022.65</v>
       </c>
       <c r="L30" t="n">
-        <v>7.54</v>
+        <v>-5.76</v>
       </c>
       <c r="M30" t="n">
-        <v>30.83</v>
+        <v>23.43</v>
       </c>
       <c r="N30" t="n">
-        <v>20576411362.5</v>
+        <v>2069463424.88</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300981.SZ</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>中红医疗</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>23.36</v>
+        <v>17.99</v>
       </c>
       <c r="E31" t="n">
-        <v>19.9795</v>
+        <v>4.898</v>
       </c>
       <c r="F31" t="n">
-        <v>8.91</v>
+        <v>18.75</v>
       </c>
       <c r="G31" t="n">
-        <v>732402935</v>
+        <v>6938512621</v>
       </c>
       <c r="H31" t="n">
-        <v>77737947.8</v>
+        <v>826703715.25</v>
       </c>
       <c r="I31" t="n">
-        <v>204105121.02</v>
+        <v>872130972.1900001</v>
       </c>
       <c r="J31" t="n">
-        <v>281843068.82</v>
+        <v>1698834687.44</v>
       </c>
       <c r="K31" t="n">
-        <v>126367173.22</v>
+        <v>45427256.94</v>
       </c>
       <c r="L31" t="n">
-        <v>17.25</v>
+        <v>0.65</v>
       </c>
       <c r="M31" t="n">
-        <v>38.48</v>
+        <v>24.48</v>
       </c>
       <c r="N31" t="n">
-        <v>9180418773.440001</v>
+        <v>21584235592.5</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300981.SZ</t>
+          <t>300829.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>中红医疗</t>
+          <t>金丹科技</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>23.36</v>
+        <v>28.02</v>
       </c>
       <c r="E32" t="n">
-        <v>19.9795</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>8.91</v>
+        <v>14.13</v>
       </c>
       <c r="G32" t="n">
-        <v>2074575132</v>
+        <v>613444354</v>
       </c>
       <c r="H32" t="n">
-        <v>251890378.94</v>
+        <v>110681910.4</v>
       </c>
       <c r="I32" t="n">
-        <v>331183525.63</v>
+        <v>129567622.2</v>
       </c>
       <c r="J32" t="n">
-        <v>583073904.5700001</v>
+        <v>240249532.6</v>
       </c>
       <c r="K32" t="n">
-        <v>79293146.69</v>
+        <v>18885711.8</v>
       </c>
       <c r="L32" t="n">
-        <v>3.82</v>
+        <v>3.08</v>
       </c>
       <c r="M32" t="n">
-        <v>28.11</v>
+        <v>39.16</v>
       </c>
       <c r="N32" t="n">
-        <v>9180418773.440001</v>
+        <v>4711053904.62</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>301139.SZ</t>
+          <t>300829.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>元道退</t>
+          <t>金丹科技</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.89</v>
+        <v>28.02</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.3191</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>21.73</v>
+        <v>14.13</v>
       </c>
       <c r="G33" t="n">
-        <v>15081719</v>
+        <v>1393754985</v>
       </c>
       <c r="H33" t="n">
-        <v>4942011.09</v>
+        <v>272927745.24</v>
       </c>
       <c r="I33" t="n">
-        <v>2808720.88</v>
+        <v>238041160.17</v>
       </c>
       <c r="J33" t="n">
-        <v>7750731.97</v>
+        <v>510968905.41</v>
       </c>
       <c r="K33" t="n">
-        <v>-2133290.21</v>
+        <v>-34886585.07</v>
       </c>
       <c r="L33" t="n">
-        <v>-14.14</v>
+        <v>-2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>51.39</v>
+        <v>36.66</v>
       </c>
       <c r="N33" t="n">
-        <v>67778971.72</v>
+        <v>4711053904.62</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>301513.SZ</t>
+          <t>301052.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>尚水智能</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>71.89</v>
+        <v>30.47</v>
       </c>
       <c r="E34" t="n">
-        <v>6.0168</v>
+        <v>20.0079</v>
       </c>
       <c r="F34" t="n">
-        <v>57.66</v>
+        <v>25.41</v>
       </c>
       <c r="G34" t="n">
-        <v>817661851</v>
+        <v>583938708</v>
       </c>
       <c r="H34" t="n">
-        <v>64315250.67</v>
+        <v>84240213</v>
       </c>
       <c r="I34" t="n">
-        <v>57628063.7</v>
+        <v>114228789.6</v>
       </c>
       <c r="J34" t="n">
-        <v>121943314.37</v>
+        <v>198469002.6</v>
       </c>
       <c r="K34" t="n">
-        <v>-6687186.97</v>
+        <v>29988576.6</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.82</v>
+        <v>5.14</v>
       </c>
       <c r="M34" t="n">
-        <v>14.91</v>
+        <v>33.99</v>
       </c>
       <c r="N34" t="n">
-        <v>1448510819.21</v>
+        <v>2444906523.18</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>301599.SZ</t>
+          <t>301052.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>理奇智能</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36.7</v>
+        <v>30.47</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8108</v>
+        <v>20.0079</v>
       </c>
       <c r="F35" t="n">
-        <v>33.83</v>
+        <v>25.41</v>
       </c>
       <c r="G35" t="n">
-        <v>693604489</v>
+        <v>769112880</v>
       </c>
       <c r="H35" t="n">
-        <v>89646021.42</v>
+        <v>107859747</v>
       </c>
       <c r="I35" t="n">
-        <v>64535746.26</v>
+        <v>152159415.75</v>
       </c>
       <c r="J35" t="n">
-        <v>154181767.68</v>
+        <v>260019162.75</v>
       </c>
       <c r="K35" t="n">
-        <v>-25110275.16</v>
+        <v>44299668.75</v>
       </c>
       <c r="L35" t="n">
-        <v>-3.62</v>
+        <v>5.76</v>
       </c>
       <c r="M35" t="n">
-        <v>22.23</v>
+        <v>33.81</v>
       </c>
       <c r="N35" t="n">
-        <v>2007509671.2</v>
+        <v>2444906523.18</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>301689.SZ</t>
+          <t>301139.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>元道退</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>71.01000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6482</v>
+        <v>-7.8652</v>
       </c>
       <c r="F36" t="n">
-        <v>32.23</v>
+        <v>16.1</v>
       </c>
       <c r="G36" t="n">
-        <v>1300363300</v>
+        <v>10341787</v>
       </c>
       <c r="H36" t="n">
-        <v>150715868.24</v>
+        <v>2796645.2</v>
       </c>
       <c r="I36" t="n">
-        <v>221931751.74</v>
+        <v>2727476.95</v>
       </c>
       <c r="J36" t="n">
-        <v>372647619.98</v>
+        <v>5524122.15</v>
       </c>
       <c r="K36" t="n">
-        <v>71215883.5</v>
+        <v>-69168.25</v>
       </c>
       <c r="L36" t="n">
-        <v>5.48</v>
+        <v>-0.67</v>
       </c>
       <c r="M36" t="n">
-        <v>28.66</v>
+        <v>53.42</v>
       </c>
       <c r="N36" t="n">
-        <v>4087438706.52</v>
+        <v>62448041.36</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>301697.SZ</t>
+          <t>301419.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>贝特利</t>
+          <t>阿莱德</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30.1</v>
+        <v>47.7</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.4748</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>46.49</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>612084936</v>
+        <v>422151500</v>
       </c>
       <c r="H37" t="n">
-        <v>163923651.21</v>
+        <v>57220341.51</v>
       </c>
       <c r="I37" t="n">
-        <v>103305875.65</v>
+        <v>100655004.42</v>
       </c>
       <c r="J37" t="n">
-        <v>267229526.86</v>
+        <v>157875345.93</v>
       </c>
       <c r="K37" t="n">
-        <v>-60617775.56</v>
+        <v>43434662.91</v>
       </c>
       <c r="L37" t="n">
-        <v>-9.9</v>
+        <v>10.29</v>
       </c>
       <c r="M37" t="n">
-        <v>43.66</v>
+        <v>37.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1324130123.4</v>
+        <v>5347325025</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>600127.SH</t>
+          <t>301513.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>尚水智能</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.18</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>-6.3569</v>
       </c>
       <c r="F38" t="n">
-        <v>31.47</v>
+        <v>41.76</v>
       </c>
       <c r="G38" t="n">
-        <v>2959497543</v>
+        <v>572096025</v>
       </c>
       <c r="H38" t="n">
-        <v>300090326.97</v>
+        <v>57188902.75</v>
       </c>
       <c r="I38" t="n">
-        <v>360227768.17</v>
+        <v>63994592.24</v>
       </c>
       <c r="J38" t="n">
-        <v>660318095.14</v>
+        <v>121183494.99</v>
       </c>
       <c r="K38" t="n">
-        <v>60137441.2</v>
+        <v>6805689.49</v>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>1.19</v>
       </c>
       <c r="M38" t="n">
-        <v>22.31</v>
+        <v>21.18</v>
       </c>
       <c r="N38" t="n">
-        <v>9742269249.24</v>
+        <v>1356429939.48</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>600354.SH</t>
+          <t>301658.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>敦煌种业</t>
+          <t>首航新能</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.99</v>
+        <v>27.12</v>
       </c>
       <c r="E39" t="n">
-        <v>10.022</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
-        <v>23.67</v>
+        <v>21.17</v>
       </c>
       <c r="G39" t="n">
-        <v>1198876915</v>
+        <v>512184292</v>
       </c>
       <c r="H39" t="n">
-        <v>97403113.37</v>
+        <v>84737954.73</v>
       </c>
       <c r="I39" t="n">
-        <v>185231436.61</v>
+        <v>169174246.55</v>
       </c>
       <c r="J39" t="n">
-        <v>282634549.98</v>
+        <v>253912201.28</v>
       </c>
       <c r="K39" t="n">
-        <v>87828323.23999999</v>
+        <v>84436291.81999999</v>
       </c>
       <c r="L39" t="n">
-        <v>7.33</v>
+        <v>16.49</v>
       </c>
       <c r="M39" t="n">
-        <v>23.57</v>
+        <v>49.57</v>
       </c>
       <c r="N39" t="n">
-        <v>5272742779.2</v>
+        <v>2641940388.72</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>600363.SH</t>
+          <t>301697.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ST联光</t>
+          <t>贝特利</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.26</v>
+        <v>28.82</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.5574</v>
+        <v>-4.2525</v>
       </c>
       <c r="F40" t="n">
-        <v>19.79</v>
+        <v>30.08</v>
       </c>
       <c r="G40" t="n">
-        <v>1709267778</v>
+        <v>378422423</v>
       </c>
       <c r="H40" t="n">
-        <v>214789445.11</v>
+        <v>72238157.56</v>
       </c>
       <c r="I40" t="n">
-        <v>143256562.42</v>
+        <v>41041460.36</v>
       </c>
       <c r="J40" t="n">
-        <v>358046007.53</v>
+        <v>113279617.92</v>
       </c>
       <c r="K40" t="n">
-        <v>-71532882.69</v>
+        <v>-31196697.2</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.19</v>
+        <v>-8.24</v>
       </c>
       <c r="M40" t="n">
-        <v>20.95</v>
+        <v>29.93</v>
       </c>
       <c r="N40" t="n">
-        <v>4626115497</v>
+        <v>1267821599.88</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600400.SH</t>
+          <t>600127.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.98</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="n">
-        <v>9.944800000000001</v>
+        <v>-8.4321</v>
       </c>
       <c r="F41" t="n">
-        <v>8.51</v>
+        <v>58.23</v>
       </c>
       <c r="G41" t="n">
-        <v>1135204963</v>
+        <v>5880540889</v>
       </c>
       <c r="H41" t="n">
-        <v>169017884.16</v>
+        <v>607753249.11</v>
       </c>
       <c r="I41" t="n">
-        <v>238307604.96</v>
+        <v>672544191.16</v>
       </c>
       <c r="J41" t="n">
-        <v>407325489.12</v>
+        <v>1280297440.27</v>
       </c>
       <c r="K41" t="n">
-        <v>69289720.8</v>
+        <v>64790942.05</v>
       </c>
       <c r="L41" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="M41" t="n">
-        <v>35.88</v>
+        <v>21.77</v>
       </c>
       <c r="N41" t="n">
-        <v>9119659970.959999</v>
+        <v>8920786730.200001</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600408.SH</t>
+          <t>600241.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.78</v>
+        <v>12.94</v>
       </c>
       <c r="E42" t="n">
-        <v>9.883699999999999</v>
+        <v>10.034</v>
       </c>
       <c r="F42" t="n">
-        <v>20.91</v>
+        <v>32.01</v>
       </c>
       <c r="G42" t="n">
-        <v>967844179</v>
+        <v>1199299592</v>
       </c>
       <c r="H42" t="n">
-        <v>167586746.34</v>
+        <v>155912671.2</v>
       </c>
       <c r="I42" t="n">
-        <v>176589354.24</v>
+        <v>84027289.3</v>
       </c>
       <c r="J42" t="n">
-        <v>344176100.58</v>
+        <v>239939960.5</v>
       </c>
       <c r="K42" t="n">
-        <v>9002607.9</v>
+        <v>-71885381.90000001</v>
       </c>
       <c r="L42" t="n">
-        <v>0.93</v>
+        <v>-5.99</v>
       </c>
       <c r="M42" t="n">
-        <v>35.56</v>
+        <v>20.01</v>
       </c>
       <c r="N42" t="n">
-        <v>3805704000</v>
+        <v>3808269368.1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600663.SH</t>
+          <t>600241.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>陆家嘴</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.15</v>
+        <v>12.94</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.723000000000001</v>
+        <v>10.034</v>
       </c>
       <c r="F43" t="n">
-        <v>2.27</v>
+        <v>32.01</v>
       </c>
       <c r="G43" t="n">
-        <v>939631958</v>
+        <v>1268238664</v>
       </c>
       <c r="H43" t="n">
-        <v>183113298.86</v>
+        <v>158379919.2</v>
       </c>
       <c r="I43" t="n">
-        <v>84812175.73999999</v>
+        <v>84207151.3</v>
       </c>
       <c r="J43" t="n">
-        <v>267925474.6</v>
+        <v>242587070.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-98301123.12</v>
+        <v>-74172767.90000001</v>
       </c>
       <c r="L43" t="n">
-        <v>-10.46</v>
+        <v>-5.85</v>
       </c>
       <c r="M43" t="n">
-        <v>28.51</v>
+        <v>19.13</v>
       </c>
       <c r="N43" t="n">
-        <v>40379036785.85</v>
+        <v>3808269368.1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600722.SH</t>
+          <t>600354.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>敦煌种业</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16.88</v>
+        <v>9.31</v>
       </c>
       <c r="E44" t="n">
-        <v>4.2619</v>
+        <v>-6.8068</v>
       </c>
       <c r="F44" t="n">
-        <v>23.27</v>
+        <v>32.14</v>
       </c>
       <c r="G44" t="n">
-        <v>2608503538</v>
+        <v>1674873713</v>
       </c>
       <c r="H44" t="n">
-        <v>382242169.64</v>
+        <v>209740213.44</v>
       </c>
       <c r="I44" t="n">
-        <v>260958492.35</v>
+        <v>154449869.8</v>
       </c>
       <c r="J44" t="n">
-        <v>643200661.99</v>
+        <v>364190083.24</v>
       </c>
       <c r="K44" t="n">
-        <v>-121283677.29</v>
+        <v>-55290343.64</v>
       </c>
       <c r="L44" t="n">
-        <v>-4.65</v>
+        <v>-3.3</v>
       </c>
       <c r="M44" t="n">
-        <v>24.66</v>
+        <v>21.74</v>
       </c>
       <c r="N44" t="n">
-        <v>11483796130.88</v>
+        <v>4913837364.8</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600812.SH</t>
+          <t>600371.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.03</v>
+        <v>14.03</v>
       </c>
       <c r="E45" t="n">
-        <v>10.0365</v>
+        <v>-6.2792</v>
       </c>
       <c r="F45" t="n">
-        <v>6.75</v>
+        <v>31.51</v>
       </c>
       <c r="G45" t="n">
-        <v>687660547</v>
+        <v>1403613823</v>
       </c>
       <c r="H45" t="n">
-        <v>58180459.21</v>
+        <v>194006408.66</v>
       </c>
       <c r="I45" t="n">
-        <v>83631800</v>
+        <v>171012660.05</v>
       </c>
       <c r="J45" t="n">
-        <v>141812259.21</v>
+        <v>365019068.71</v>
       </c>
       <c r="K45" t="n">
-        <v>25451340.79</v>
+        <v>-22993748.61</v>
       </c>
       <c r="L45" t="n">
-        <v>3.7</v>
+        <v>-1.64</v>
       </c>
       <c r="M45" t="n">
-        <v>20.62</v>
+        <v>26.01</v>
       </c>
       <c r="N45" t="n">
-        <v>10345854131.1</v>
+        <v>4104869340</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600812.SH</t>
+          <t>600408.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.03</v>
+        <v>3.53</v>
       </c>
       <c r="E46" t="n">
-        <v>10.0365</v>
+        <v>-6.6138</v>
       </c>
       <c r="F46" t="n">
-        <v>6.75</v>
+        <v>25.65</v>
       </c>
       <c r="G46" t="n">
-        <v>1182019547</v>
+        <v>970367820</v>
       </c>
       <c r="H46" t="n">
-        <v>65314507.21</v>
+        <v>138586753.91</v>
       </c>
       <c r="I46" t="n">
-        <v>107476046.83</v>
+        <v>122759497</v>
       </c>
       <c r="J46" t="n">
-        <v>172790554.04</v>
+        <v>261346250.91</v>
       </c>
       <c r="K46" t="n">
-        <v>42161539.62</v>
+        <v>-15827256.91</v>
       </c>
       <c r="L46" t="n">
-        <v>3.57</v>
+        <v>-1.63</v>
       </c>
       <c r="M46" t="n">
-        <v>14.62</v>
+        <v>26.93</v>
       </c>
       <c r="N46" t="n">
-        <v>10345854131.1</v>
+        <v>3554004000</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>600664.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.53</v>
+        <v>6.65</v>
       </c>
       <c r="E47" t="n">
-        <v>10.0088</v>
+        <v>-10.0135</v>
       </c>
       <c r="F47" t="n">
-        <v>4.78</v>
+        <v>2.36</v>
       </c>
       <c r="G47" t="n">
-        <v>689935518</v>
+        <v>395914400</v>
       </c>
       <c r="H47" t="n">
-        <v>63691427.18</v>
+        <v>38760855</v>
       </c>
       <c r="I47" t="n">
-        <v>113462694</v>
+        <v>96341875</v>
       </c>
       <c r="J47" t="n">
-        <v>177154121.18</v>
+        <v>135102730</v>
       </c>
       <c r="K47" t="n">
-        <v>49771266.82</v>
+        <v>57581020</v>
       </c>
       <c r="L47" t="n">
-        <v>7.21</v>
+        <v>14.54</v>
       </c>
       <c r="M47" t="n">
-        <v>25.68</v>
+        <v>34.12</v>
       </c>
       <c r="N47" t="n">
-        <v>13092444760.5</v>
+        <v>16748090675.4</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600825.SH</t>
+          <t>600693.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.53</v>
+        <v>11.18</v>
       </c>
       <c r="E48" t="n">
-        <v>10.0088</v>
+        <v>10.0394</v>
       </c>
       <c r="F48" t="n">
-        <v>4.78</v>
+        <v>3.12</v>
       </c>
       <c r="G48" t="n">
-        <v>1126173900</v>
+        <v>302864557</v>
       </c>
       <c r="H48" t="n">
-        <v>1126173800</v>
+        <v>24097372</v>
       </c>
       <c r="I48" t="n">
-        <v>1126173900</v>
+        <v>111134376.34</v>
       </c>
       <c r="J48" t="n">
-        <v>1126173900</v>
+        <v>135231748.34</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>87037004.34</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>28.74</v>
       </c>
       <c r="M48" t="n">
-        <v>100</v>
+        <v>44.65</v>
       </c>
       <c r="N48" t="n">
-        <v>13092444760.5</v>
+        <v>9714892102.76</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>连续10个交易日内4次出现同正向异常波动的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>600865.SH</t>
+          <t>600693.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.51</v>
+        <v>11.18</v>
       </c>
       <c r="E49" t="n">
-        <v>10.0382</v>
+        <v>10.0394</v>
       </c>
       <c r="F49" t="n">
-        <v>10.85</v>
+        <v>3.12</v>
       </c>
       <c r="G49" t="n">
-        <v>449311790</v>
+        <v>1675467932</v>
       </c>
       <c r="H49" t="n">
-        <v>90142461.41</v>
+        <v>192541032.58</v>
       </c>
       <c r="I49" t="n">
-        <v>85414679</v>
+        <v>197191727.34</v>
       </c>
       <c r="J49" t="n">
-        <v>175557140.41</v>
+        <v>389732759.92</v>
       </c>
       <c r="K49" t="n">
-        <v>-4727782.41</v>
+        <v>4650694.76</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.05</v>
+        <v>0.28</v>
       </c>
       <c r="M49" t="n">
-        <v>39.07</v>
+        <v>23.26</v>
       </c>
       <c r="N49" t="n">
-        <v>4330526037.16</v>
+        <v>9714892102.76</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>601091.SH</t>
+          <t>600722.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>沈鼓集团</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>23.03</v>
+        <v>15.19</v>
       </c>
       <c r="E50" t="n">
-        <v>-4.8347</v>
+        <v>-10.0118</v>
       </c>
       <c r="F50" t="n">
-        <v>27.56</v>
+        <v>12.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1339327373</v>
+        <v>1312808494</v>
       </c>
       <c r="H50" t="n">
-        <v>105240421.67</v>
+        <v>192743391.91</v>
       </c>
       <c r="I50" t="n">
-        <v>99736959.94</v>
+        <v>125973227.71</v>
       </c>
       <c r="J50" t="n">
-        <v>204977381.61</v>
+        <v>318716619.62</v>
       </c>
       <c r="K50" t="n">
-        <v>-5503461.73</v>
+        <v>-66770164.2</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.41</v>
+        <v>-5.09</v>
       </c>
       <c r="M50" t="n">
-        <v>15.3</v>
+        <v>24.28</v>
       </c>
       <c r="N50" t="n">
-        <v>4863088081.46</v>
+        <v>10334055878.44</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>601118.SH</t>
+          <t>600831.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>广电网络</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.16</v>
+        <v>3.91</v>
       </c>
       <c r="E51" t="n">
-        <v>9.9846</v>
+        <v>10.1408</v>
       </c>
       <c r="F51" t="n">
-        <v>6.64</v>
+        <v>5.6</v>
       </c>
       <c r="G51" t="n">
-        <v>3665954768</v>
+        <v>154024936</v>
       </c>
       <c r="H51" t="n">
-        <v>595747293.4299999</v>
+        <v>15818367</v>
       </c>
       <c r="I51" t="n">
-        <v>532059052.27</v>
+        <v>45804017</v>
       </c>
       <c r="J51" t="n">
-        <v>1127806345.7</v>
+        <v>61622384</v>
       </c>
       <c r="K51" t="n">
-        <v>-63688241.16</v>
+        <v>29985650</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.74</v>
+        <v>19.47</v>
       </c>
       <c r="M51" t="n">
-        <v>30.76</v>
+        <v>40.01</v>
       </c>
       <c r="N51" t="n">
-        <v>30640703026.52</v>
+        <v>2779802738.72</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>601929.SH</t>
+          <t>601595.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>上海电影</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.5</v>
+        <v>27.21</v>
       </c>
       <c r="E52" t="n">
-        <v>10.1322</v>
+        <v>9.9838</v>
       </c>
       <c r="F52" t="n">
-        <v>5.72</v>
+        <v>6.35</v>
       </c>
       <c r="G52" t="n">
-        <v>475031390</v>
+        <v>1048825401</v>
       </c>
       <c r="H52" t="n">
-        <v>60337659</v>
+        <v>206107081.8</v>
       </c>
       <c r="I52" t="n">
-        <v>166530634</v>
+        <v>236765873.41</v>
       </c>
       <c r="J52" t="n">
-        <v>226868293</v>
+        <v>442872955.21</v>
       </c>
       <c r="K52" t="n">
-        <v>106192975</v>
+        <v>30658791.61</v>
       </c>
       <c r="L52" t="n">
-        <v>22.35</v>
+        <v>2.92</v>
       </c>
       <c r="M52" t="n">
-        <v>47.76</v>
+        <v>42.23</v>
       </c>
       <c r="N52" t="n">
-        <v>8724470420</v>
+        <v>12195522000</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>603002.SH</t>
+          <t>601811.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>宏昌电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17.68</v>
+        <v>23</v>
       </c>
       <c r="E53" t="n">
-        <v>-5.404</v>
+        <v>9.995200000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>14.03</v>
+        <v>7.27</v>
       </c>
       <c r="G53" t="n">
-        <v>2962862410</v>
+        <v>2437712048</v>
       </c>
       <c r="H53" t="n">
-        <v>565179113</v>
+        <v>166897814</v>
       </c>
       <c r="I53" t="n">
-        <v>289470157</v>
+        <v>127077958.55</v>
       </c>
       <c r="J53" t="n">
-        <v>854649270</v>
+        <v>293975772.55</v>
       </c>
       <c r="K53" t="n">
-        <v>-275708956</v>
+        <v>-39819855.45</v>
       </c>
       <c r="L53" t="n">
-        <v>-9.31</v>
+        <v>-1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>28.85</v>
+        <v>12.06</v>
       </c>
       <c r="N53" t="n">
-        <v>20050508039.12</v>
+        <v>18213789700</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>603073.SH</t>
+          <t>601929.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>彩蝶实业</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>20.67</v>
+        <v>2.75</v>
       </c>
       <c r="E54" t="n">
-        <v>-10.0131</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>8.26</v>
+        <v>14.77</v>
       </c>
       <c r="G54" t="n">
-        <v>201331598</v>
+        <v>1871067704</v>
       </c>
       <c r="H54" t="n">
-        <v>40510897</v>
+        <v>224928516.25</v>
       </c>
       <c r="I54" t="n">
-        <v>33322707.54</v>
+        <v>409434951.59</v>
       </c>
       <c r="J54" t="n">
-        <v>73833604.54000001</v>
+        <v>634363467.84</v>
       </c>
       <c r="K54" t="n">
-        <v>-7188189.46</v>
+        <v>184506435.34</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>36.67</v>
+        <v>33.9</v>
       </c>
       <c r="N54" t="n">
-        <v>2397720000</v>
+        <v>9596917462</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>603096.SH</t>
+          <t>603002.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>新经典</t>
+          <t>宏昌电子</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.33</v>
+        <v>15.91</v>
       </c>
       <c r="E55" t="n">
-        <v>10.0317</v>
+        <v>-10.0113</v>
       </c>
       <c r="F55" t="n">
-        <v>2.8</v>
+        <v>7.87</v>
       </c>
       <c r="G55" t="n">
-        <v>70710476</v>
+        <v>1443603203</v>
       </c>
       <c r="H55" t="n">
-        <v>15737233</v>
+        <v>187718335.78</v>
       </c>
       <c r="I55" t="n">
-        <v>38748093</v>
+        <v>196688252.5</v>
       </c>
       <c r="J55" t="n">
-        <v>54485326</v>
+        <v>384406588.28</v>
       </c>
       <c r="K55" t="n">
-        <v>23010860</v>
+        <v>8969916.720000001</v>
       </c>
       <c r="L55" t="n">
-        <v>32.54</v>
+        <v>0.62</v>
       </c>
       <c r="M55" t="n">
-        <v>77.05</v>
+        <v>26.63</v>
       </c>
       <c r="N55" t="n">
-        <v>2672886033.92</v>
+        <v>18043189078.19</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>603101.SH</t>
+          <t>603032.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>汇嘉时代</t>
+          <t>德新科技</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7.99</v>
+        <v>20.42</v>
       </c>
       <c r="E56" t="n">
-        <v>10.0551</v>
+        <v>10.0216</v>
       </c>
       <c r="F56" t="n">
-        <v>3.99</v>
+        <v>13.93</v>
       </c>
       <c r="G56" t="n">
-        <v>146219698</v>
+        <v>653535811</v>
       </c>
       <c r="H56" t="n">
-        <v>21220377.76</v>
+        <v>78640254.89</v>
       </c>
       <c r="I56" t="n">
-        <v>30398513.16</v>
+        <v>106867166.98</v>
       </c>
       <c r="J56" t="n">
-        <v>51618890.92</v>
+        <v>185507421.87</v>
       </c>
       <c r="K56" t="n">
-        <v>9178135.4</v>
+        <v>28226912.09</v>
       </c>
       <c r="L56" t="n">
-        <v>6.28</v>
+        <v>4.32</v>
       </c>
       <c r="M56" t="n">
-        <v>35.3</v>
+        <v>28.39</v>
       </c>
       <c r="N56" t="n">
-        <v>3758496000</v>
+        <v>4755442272</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4844,51 +4844,51 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>603200.SH</t>
+          <t>603096.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>新经典</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>53.92</v>
+        <v>19.06</v>
       </c>
       <c r="E57" t="n">
-        <v>9.571199999999999</v>
+        <v>9.982699999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>20.5</v>
+        <v>2.41</v>
       </c>
       <c r="G57" t="n">
-        <v>3372370571</v>
+        <v>141462549</v>
       </c>
       <c r="H57" t="n">
-        <v>337537875.26</v>
+        <v>25789410.8</v>
       </c>
       <c r="I57" t="n">
-        <v>306241744.31</v>
+        <v>58854617</v>
       </c>
       <c r="J57" t="n">
-        <v>643779619.5700001</v>
+        <v>84644027.8</v>
       </c>
       <c r="K57" t="n">
-        <v>-31296130.95</v>
+        <v>33065206.2</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.93</v>
+        <v>23.37</v>
       </c>
       <c r="M57" t="n">
-        <v>19.09</v>
+        <v>59.83</v>
       </c>
       <c r="N57" t="n">
-        <v>9461887153.76</v>
+        <v>2939711933.44</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4899,51 +4899,51 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603232.SH</t>
+          <t>603200.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>格尔软件</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16.98</v>
+        <v>54.01</v>
       </c>
       <c r="E58" t="n">
-        <v>9.9741</v>
+        <v>0.1669</v>
       </c>
       <c r="F58" t="n">
-        <v>10.83</v>
+        <v>18.44</v>
       </c>
       <c r="G58" t="n">
-        <v>400137732</v>
+        <v>1717431119</v>
       </c>
       <c r="H58" t="n">
-        <v>51700075.14</v>
+        <v>144433872.98</v>
       </c>
       <c r="I58" t="n">
-        <v>132438814.12</v>
+        <v>246001872.32</v>
       </c>
       <c r="J58" t="n">
-        <v>184138889.26</v>
+        <v>390435745.3</v>
       </c>
       <c r="K58" t="n">
-        <v>80738738.98</v>
+        <v>101567999.34</v>
       </c>
       <c r="L58" t="n">
-        <v>20.18</v>
+        <v>5.91</v>
       </c>
       <c r="M58" t="n">
-        <v>46.02</v>
+        <v>22.73</v>
       </c>
       <c r="N58" t="n">
-        <v>3927473915.1</v>
+        <v>9477680363.030001</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4954,326 +4954,326 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603248.SH</t>
+          <t>603232.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>格尔软件</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.64</v>
+        <v>18.68</v>
       </c>
       <c r="E59" t="n">
-        <v>-3.7313</v>
+        <v>10.0118</v>
       </c>
       <c r="F59" t="n">
-        <v>25.22</v>
+        <v>18.07</v>
       </c>
       <c r="G59" t="n">
-        <v>365545255</v>
+        <v>1144485642</v>
       </c>
       <c r="H59" t="n">
-        <v>50423793.66</v>
+        <v>173042218.28</v>
       </c>
       <c r="I59" t="n">
-        <v>49553029.05</v>
+        <v>235489868.58</v>
       </c>
       <c r="J59" t="n">
-        <v>99976822.70999999</v>
+        <v>408532086.86</v>
       </c>
       <c r="K59" t="n">
-        <v>-870764.61</v>
+        <v>62447650.3</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.24</v>
+        <v>5.46</v>
       </c>
       <c r="M59" t="n">
-        <v>27.35</v>
+        <v>35.7</v>
       </c>
       <c r="N59" t="n">
-        <v>1475862188.64</v>
+        <v>4320683906.6</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603400.SH</t>
+          <t>603533.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>华之杰</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>42.93</v>
+        <v>27.98</v>
       </c>
       <c r="E60" t="n">
-        <v>-10</v>
+        <v>9.984299999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>18.13</v>
+        <v>17.84</v>
       </c>
       <c r="G60" t="n">
-        <v>286680592</v>
+        <v>2969418383</v>
       </c>
       <c r="H60" t="n">
-        <v>56863177.58</v>
+        <v>432721422.04</v>
       </c>
       <c r="I60" t="n">
-        <v>43029256.97</v>
+        <v>586543725.09</v>
       </c>
       <c r="J60" t="n">
-        <v>99892434.55</v>
+        <v>1019265147.13</v>
       </c>
       <c r="K60" t="n">
-        <v>-13833920.61</v>
+        <v>153822303.05</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.83</v>
+        <v>5.18</v>
       </c>
       <c r="M60" t="n">
-        <v>34.84</v>
+        <v>34.33</v>
       </c>
       <c r="N60" t="n">
-        <v>1555357119.75</v>
+        <v>12280333443.3</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>603400.SH</t>
+          <t>603588.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>华之杰</t>
+          <t>高能环境</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>42.93</v>
+        <v>14.93</v>
       </c>
       <c r="E61" t="n">
-        <v>-10</v>
+        <v>-10.006</v>
       </c>
       <c r="F61" t="n">
-        <v>18.13</v>
+        <v>3.93</v>
       </c>
       <c r="G61" t="n">
-        <v>1158679255</v>
+        <v>941487994</v>
       </c>
       <c r="H61" t="n">
-        <v>168375728.76</v>
+        <v>163292072.38</v>
       </c>
       <c r="I61" t="n">
-        <v>151795838.79</v>
+        <v>84338198</v>
       </c>
       <c r="J61" t="n">
-        <v>320171567.55</v>
+        <v>247630270.38</v>
       </c>
       <c r="K61" t="n">
-        <v>-16579889.97</v>
+        <v>-78953874.38</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.43</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>27.63</v>
+        <v>26.3</v>
       </c>
       <c r="N61" t="n">
-        <v>1555357119.75</v>
+        <v>22741890443.01</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>603757.SH</t>
+          <t>603668.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>天马科技</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>72.78</v>
+        <v>9.41</v>
       </c>
       <c r="E62" t="n">
-        <v>4.5539</v>
+        <v>-10.0382</v>
       </c>
       <c r="F62" t="n">
-        <v>6.87</v>
+        <v>4.1</v>
       </c>
       <c r="G62" t="n">
-        <v>878390440</v>
+        <v>200202218</v>
       </c>
       <c r="H62" t="n">
-        <v>121701611.47</v>
+        <v>52012296.1</v>
       </c>
       <c r="I62" t="n">
-        <v>197975026.07</v>
+        <v>33030408</v>
       </c>
       <c r="J62" t="n">
-        <v>319676637.54</v>
+        <v>85042704.09999999</v>
       </c>
       <c r="K62" t="n">
-        <v>76273414.59999999</v>
+        <v>-18981888.1</v>
       </c>
       <c r="L62" t="n">
-        <v>8.68</v>
+        <v>-9.48</v>
       </c>
       <c r="M62" t="n">
-        <v>36.39</v>
+        <v>42.48</v>
       </c>
       <c r="N62" t="n">
-        <v>13576909510.02</v>
+        <v>4759547248.12</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>603823.SH</t>
+          <t>603968.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>百合花</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>41.93</v>
+        <v>13.05</v>
       </c>
       <c r="E63" t="n">
-        <v>-10.0021</v>
+        <v>10.0337</v>
       </c>
       <c r="F63" t="n">
-        <v>4.88</v>
+        <v>12.85</v>
       </c>
       <c r="G63" t="n">
-        <v>855381191</v>
+        <v>321073559</v>
       </c>
       <c r="H63" t="n">
-        <v>149012264.2</v>
+        <v>25779779.9</v>
       </c>
       <c r="I63" t="n">
-        <v>55608154</v>
+        <v>57736092.53</v>
       </c>
       <c r="J63" t="n">
-        <v>204620418.2</v>
+        <v>83515872.43000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-93404110.2</v>
+        <v>31956312.63</v>
       </c>
       <c r="L63" t="n">
-        <v>-10.92</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>23.92</v>
+        <v>26.01</v>
       </c>
       <c r="N63" t="n">
-        <v>17458297828.72</v>
+        <v>2668464000</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>605058.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.69</v>
+        <v>54.9</v>
       </c>
       <c r="E64" t="n">
-        <v>-4.7983</v>
+        <v>2.9053</v>
       </c>
       <c r="F64" t="n">
-        <v>17.55</v>
+        <v>14.5</v>
       </c>
       <c r="G64" t="n">
-        <v>828324867</v>
+        <v>1114419928</v>
       </c>
       <c r="H64" t="n">
-        <v>114858713.7</v>
+        <v>127793281.7</v>
       </c>
       <c r="I64" t="n">
-        <v>141185292.29</v>
+        <v>171582462.14</v>
       </c>
       <c r="J64" t="n">
-        <v>256044005.99</v>
+        <v>299375743.84</v>
       </c>
       <c r="K64" t="n">
-        <v>26326578.59</v>
+        <v>43789180.44</v>
       </c>
       <c r="L64" t="n">
-        <v>3.18</v>
+        <v>3.93</v>
       </c>
       <c r="M64" t="n">
-        <v>30.91</v>
+        <v>26.86</v>
       </c>
       <c r="N64" t="n">
-        <v>4664237760</v>
+        <v>7846802758.8</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5284,216 +5284,216 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>603949.SH</t>
+          <t>605136.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.61</v>
+        <v>10.38</v>
       </c>
       <c r="E65" t="n">
-        <v>-5.7936</v>
+        <v>9.957599999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>11.11</v>
+        <v>1.03</v>
       </c>
       <c r="G65" t="n">
-        <v>1241488938</v>
+        <v>201487173</v>
       </c>
       <c r="H65" t="n">
-        <v>59410838.05</v>
+        <v>18327864</v>
       </c>
       <c r="I65" t="n">
-        <v>75166624.53</v>
+        <v>51699204</v>
       </c>
       <c r="J65" t="n">
-        <v>134577462.58</v>
+        <v>70027068</v>
       </c>
       <c r="K65" t="n">
-        <v>15755786.48</v>
+        <v>33371340</v>
       </c>
       <c r="L65" t="n">
-        <v>1.27</v>
+        <v>16.56</v>
       </c>
       <c r="M65" t="n">
-        <v>10.84</v>
+        <v>34.76</v>
       </c>
       <c r="N65" t="n">
-        <v>3281304327.14</v>
+        <v>4156759230</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>605303.SH</t>
+          <t>605287.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32.21</v>
+        <v>44.2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.1567</v>
+        <v>10.005</v>
       </c>
       <c r="F66" t="n">
-        <v>16.3</v>
+        <v>1.67</v>
       </c>
       <c r="G66" t="n">
-        <v>849336393</v>
+        <v>453462081</v>
       </c>
       <c r="H66" t="n">
-        <v>101800326.88</v>
+        <v>116195015</v>
       </c>
       <c r="I66" t="n">
-        <v>80357496</v>
+        <v>150388074</v>
       </c>
       <c r="J66" t="n">
-        <v>182157822.88</v>
+        <v>266583089</v>
       </c>
       <c r="K66" t="n">
-        <v>-21442830.88</v>
+        <v>34193059</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.52</v>
+        <v>7.54</v>
       </c>
       <c r="M66" t="n">
-        <v>21.45</v>
+        <v>58.79</v>
       </c>
       <c r="N66" t="n">
-        <v>5193456911.68</v>
+        <v>6188000000</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>605366.SH</t>
+          <t>605577.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9.94</v>
+        <v>17.82</v>
       </c>
       <c r="E67" t="n">
-        <v>-9.963800000000001</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>12.26</v>
+        <v>3.19</v>
       </c>
       <c r="G67" t="n">
-        <v>1033147537</v>
+        <v>843192239</v>
       </c>
       <c r="H67" t="n">
-        <v>90559628.52</v>
+        <v>125133492</v>
       </c>
       <c r="I67" t="n">
-        <v>66631506.33</v>
+        <v>208317320</v>
       </c>
       <c r="J67" t="n">
-        <v>157191134.85</v>
+        <v>333450812</v>
       </c>
       <c r="K67" t="n">
-        <v>-23928122.19</v>
+        <v>83183828</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.32</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>15.21</v>
+        <v>39.55</v>
       </c>
       <c r="N67" t="n">
-        <v>7681907338</v>
+        <v>7920000009.9</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>688152.SH</t>
+          <t>688004.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>麒麟信安</t>
+          <t>博汇科技</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>45.85</v>
+        <v>37.25</v>
       </c>
       <c r="E68" t="n">
-        <v>19.9948</v>
+        <v>20.0064</v>
       </c>
       <c r="F68" t="n">
-        <v>11.24</v>
+        <v>14.94</v>
       </c>
       <c r="G68" t="n">
-        <v>482932000</v>
+        <v>410465100</v>
       </c>
       <c r="H68" t="n">
-        <v>48350195.72</v>
+        <v>48837263.08</v>
       </c>
       <c r="I68" t="n">
-        <v>99241215.83</v>
+        <v>102743591.1</v>
       </c>
       <c r="J68" t="n">
-        <v>147591411.55</v>
+        <v>151580854.18</v>
       </c>
       <c r="K68" t="n">
-        <v>50891020.11</v>
+        <v>53906328.02</v>
       </c>
       <c r="L68" t="n">
-        <v>10.54</v>
+        <v>13.13</v>
       </c>
       <c r="M68" t="n">
-        <v>30.56</v>
+        <v>36.93</v>
       </c>
       <c r="N68" t="n">
-        <v>4672026784.6</v>
+        <v>2983278000</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5504,326 +5504,326 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>688244.SH</t>
+          <t>688004.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>永信至诚</t>
+          <t>博汇科技</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>24</v>
+        <v>37.25</v>
       </c>
       <c r="E69" t="n">
-        <v>16.2228</v>
+        <v>20.0064</v>
       </c>
       <c r="F69" t="n">
-        <v>15.66</v>
+        <v>14.94</v>
       </c>
       <c r="G69" t="n">
-        <v>496980400</v>
+        <v>910457300</v>
       </c>
       <c r="H69" t="n">
-        <v>57025546.09</v>
+        <v>114607806.32</v>
       </c>
       <c r="I69" t="n">
-        <v>28493121.97</v>
+        <v>193190764.28</v>
       </c>
       <c r="J69" t="n">
-        <v>85518668.06</v>
+        <v>307798570.6</v>
       </c>
       <c r="K69" t="n">
-        <v>-28532424.12</v>
+        <v>78582957.95999999</v>
       </c>
       <c r="L69" t="n">
-        <v>-5.74</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>17.21</v>
+        <v>33.81</v>
       </c>
       <c r="N69" t="n">
-        <v>3623076456</v>
+        <v>2983278000</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到30%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>688806.SH</t>
+          <t>688517.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>泰诺麦博</t>
+          <t>金冠电气</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30.34</v>
+        <v>21.18</v>
       </c>
       <c r="E70" t="n">
-        <v>11.7495</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>42.08</v>
+        <v>16.71</v>
       </c>
       <c r="G70" t="n">
-        <v>631093500</v>
+        <v>470683200</v>
       </c>
       <c r="H70" t="n">
-        <v>102890216.27</v>
+        <v>107536019.43</v>
       </c>
       <c r="I70" t="n">
-        <v>80237512.36</v>
+        <v>115456064.22</v>
       </c>
       <c r="J70" t="n">
-        <v>183127728.63</v>
+        <v>222992083.65</v>
       </c>
       <c r="K70" t="n">
-        <v>-22652703.91</v>
+        <v>7920044.79</v>
       </c>
       <c r="L70" t="n">
-        <v>-3.59</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>29.02</v>
+        <v>47.38</v>
       </c>
       <c r="N70" t="n">
-        <v>1548118524.4</v>
+        <v>2893467237.12</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>920021.BJ</t>
+          <t>688670.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>流金科技</t>
+          <t>金迪克</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.83</v>
+        <v>15.34</v>
       </c>
       <c r="E71" t="n">
-        <v>20.1361</v>
+        <v>-19.9791</v>
       </c>
       <c r="F71" t="n">
-        <v>20.01</v>
+        <v>2.73</v>
       </c>
       <c r="G71" t="n">
-        <v>410490500</v>
+        <v>52771300</v>
       </c>
       <c r="H71" t="n">
-        <v>42678610.74</v>
+        <v>9120081.76</v>
       </c>
       <c r="I71" t="n">
-        <v>46788988.57</v>
+        <v>8561093.41</v>
       </c>
       <c r="J71" t="n">
-        <v>89467599.31</v>
+        <v>17681175.17</v>
       </c>
       <c r="K71" t="n">
-        <v>4110377.83</v>
+        <v>-558988.35</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>-1.06</v>
       </c>
       <c r="M71" t="n">
-        <v>21.8</v>
+        <v>33.51</v>
       </c>
       <c r="N71" t="n">
-        <v>2185907762.59</v>
+        <v>1889888000</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>当日收盘价涨幅达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>920202.BJ</t>
+          <t>688796.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>安达股份</t>
+          <t>百奥赛图</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.58</v>
+        <v>94.56</v>
       </c>
       <c r="E72" t="n">
-        <v>1.958</v>
+        <v>-17.7596</v>
       </c>
       <c r="F72" t="n">
-        <v>32.57</v>
+        <v>15.89</v>
       </c>
       <c r="G72" t="n">
-        <v>111893300</v>
+        <v>621032600</v>
       </c>
       <c r="H72" t="n">
-        <v>11547940.37</v>
+        <v>209708226.67</v>
       </c>
       <c r="I72" t="n">
-        <v>12667503.66</v>
+        <v>109506858.83</v>
       </c>
       <c r="J72" t="n">
-        <v>24215444.03</v>
+        <v>319215085.5</v>
       </c>
       <c r="K72" t="n">
-        <v>1119563.29</v>
+        <v>-100201367.84</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>-16.13</v>
       </c>
       <c r="M72" t="n">
-        <v>21.64</v>
+        <v>51.4</v>
       </c>
       <c r="N72" t="n">
-        <v>347004000</v>
+        <v>3650725010.88</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>920237.BJ</t>
+          <t>688806.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>力佳科技</t>
+          <t>泰诺麦博</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.95</v>
+        <v>28.28</v>
       </c>
       <c r="E73" t="n">
-        <v>6.9785</v>
+        <v>-6.7897</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>31.77</v>
       </c>
       <c r="G73" t="n">
-        <v>128622700</v>
+        <v>480112200</v>
       </c>
       <c r="H73" t="n">
-        <v>13005066.59</v>
+        <v>84524571.06999999</v>
       </c>
       <c r="I73" t="n">
-        <v>13612770.22</v>
+        <v>51368743.97</v>
       </c>
       <c r="J73" t="n">
-        <v>26617836.81</v>
+        <v>135893315.04</v>
       </c>
       <c r="K73" t="n">
-        <v>607703.63</v>
+        <v>-33155827.1</v>
       </c>
       <c r="L73" t="n">
-        <v>0.47</v>
+        <v>-6.91</v>
       </c>
       <c r="M73" t="n">
-        <v>20.69</v>
+        <v>28.3</v>
       </c>
       <c r="N73" t="n">
-        <v>1300586372.1</v>
+        <v>1443005664.8</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>920289.BJ</t>
+          <t>920157.BJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>华汇智能</t>
+          <t>宇特光电</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.65</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>6.7437</v>
+        <v>-5.8901</v>
       </c>
       <c r="F74" t="n">
-        <v>37.27</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>155132300</v>
+        <v>728936900</v>
       </c>
       <c r="H74" t="n">
-        <v>13872782.22</v>
+        <v>87362114.42</v>
       </c>
       <c r="I74" t="n">
-        <v>27907557.75</v>
+        <v>74451792.81999999</v>
       </c>
       <c r="J74" t="n">
-        <v>41780339.97</v>
+        <v>161813907.24</v>
       </c>
       <c r="K74" t="n">
-        <v>14034775.53</v>
+        <v>-12910321.6</v>
       </c>
       <c r="L74" t="n">
-        <v>9.050000000000001</v>
+        <v>-1.77</v>
       </c>
       <c r="M74" t="n">
-        <v>26.93</v>
+        <v>22.2</v>
       </c>
       <c r="N74" t="n">
-        <v>413992987.05</v>
+        <v>911179703.7</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5834,51 +5834,51 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>920202.BJ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>力王股份</t>
+          <t>安达股份</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>22.13</v>
+        <v>13.09</v>
       </c>
       <c r="E75" t="n">
-        <v>24.1167</v>
+        <v>-10.2195</v>
       </c>
       <c r="F75" t="n">
-        <v>35.78</v>
+        <v>26.61</v>
       </c>
       <c r="G75" t="n">
-        <v>357229400</v>
+        <v>86575900</v>
       </c>
       <c r="H75" t="n">
-        <v>38089359.86</v>
+        <v>9304440.42</v>
       </c>
       <c r="I75" t="n">
-        <v>29290329.36</v>
+        <v>7835077.51</v>
       </c>
       <c r="J75" t="n">
-        <v>67379689.22</v>
+        <v>17139517.93</v>
       </c>
       <c r="K75" t="n">
-        <v>-8799030.5</v>
+        <v>-1469362.91</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.46</v>
+        <v>-1.7</v>
       </c>
       <c r="M75" t="n">
-        <v>18.86</v>
+        <v>19.8</v>
       </c>
       <c r="N75" t="n">
-        <v>1086527675</v>
+        <v>311542000</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -5889,51 +5889,51 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>920779.BJ</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>武汉蓝电</t>
+          <t>力王股份</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>33.79</v>
+        <v>21.05</v>
       </c>
       <c r="E76" t="n">
-        <v>1.9922</v>
+        <v>-4.8803</v>
       </c>
       <c r="F76" t="n">
-        <v>43.99</v>
+        <v>27.4</v>
       </c>
       <c r="G76" t="n">
-        <v>294336600</v>
+        <v>279381200</v>
       </c>
       <c r="H76" t="n">
-        <v>26834436.28</v>
+        <v>32188435.19</v>
       </c>
       <c r="I76" t="n">
-        <v>38385176.44</v>
+        <v>44512078.14</v>
       </c>
       <c r="J76" t="n">
-        <v>65219612.72</v>
+        <v>76700513.33</v>
       </c>
       <c r="K76" t="n">
-        <v>11550740.16</v>
+        <v>12323642.95</v>
       </c>
       <c r="L76" t="n">
-        <v>3.92</v>
+        <v>4.41</v>
       </c>
       <c r="M76" t="n">
-        <v>22.16</v>
+        <v>27.45</v>
       </c>
       <c r="N76" t="n">
-        <v>676475867.58</v>
+        <v>1033502375</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -5944,53 +5944,108 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-10.5061</v>
+      </c>
+      <c r="F77" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="G77" t="n">
+        <v>178534400</v>
+      </c>
+      <c r="H77" t="n">
+        <v>33874598.14</v>
+      </c>
+      <c r="I77" t="n">
+        <v>32464533.68</v>
+      </c>
+      <c r="J77" t="n">
+        <v>66339131.82</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-1410064.46</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="M77" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="N77" t="n">
+        <v>605404860.48</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>920895.BJ</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>花溪科技</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E77" t="n">
-        <v>19.1318</v>
-      </c>
-      <c r="F77" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="G77" t="n">
-        <v>206983800</v>
-      </c>
-      <c r="H77" t="n">
-        <v>26222869.27</v>
-      </c>
-      <c r="I77" t="n">
-        <v>28434295.77</v>
-      </c>
-      <c r="J77" t="n">
-        <v>54657165.04</v>
-      </c>
-      <c r="K77" t="n">
-        <v>2211426.5</v>
-      </c>
-      <c r="L77" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="M77" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="N77" t="n">
-        <v>678190840</v>
-      </c>
-      <c r="O77" t="inlineStr">
+      <c r="D78" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-5.1695</v>
+      </c>
+      <c r="F78" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="G78" t="n">
+        <v>188676300</v>
+      </c>
+      <c r="H78" t="n">
+        <v>36452392.88</v>
+      </c>
+      <c r="I78" t="n">
+        <v>27575403.76</v>
+      </c>
+      <c r="J78" t="n">
+        <v>64027796.64</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-8876989.119999999</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M78" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="N78" t="n">
+        <v>643131822</v>
+      </c>
+      <c r="O78" t="inlineStr">
         <is>
           <t>当日换手率达到20%的前5只股票</t>
         </is>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20261013</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2909</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2486</v>
+      </c>
+      <c r="E2" t="n">
+        <v>166</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16889.09</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3797.2424</v>
+        <v>3800.8644</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.43</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7149.1</v>
+        <v>7793.02</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12384.8692</v>
+        <v>12353.6993</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.03</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>4067.92</v>
+        <v>4370.59</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2963.8238</v>
+        <v>2958.3446</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.61</v>
+        <v>-0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>1535.84</v>
+        <v>1769.56</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4287.9798</v>
+        <v>4275.68</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.68</v>
+        <v>-0.29</v>
       </c>
       <c r="F5" t="n">
-        <v>4055.74</v>
+        <v>4420.38</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1426.7216</v>
+        <v>1427.1775</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1</v>
+        <v>0.03</v>
       </c>
       <c r="F6" t="n">
-        <v>646.17</v>
+        <v>769.8</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7021.4723</v>
+        <v>7023.2205</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.88</v>
+        <v>0.02</v>
       </c>
       <c r="F7" t="n">
-        <v>3101.5</v>
+        <v>3378.28</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,4593 @@
           <t>20261013</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>16889.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301660.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="I2" t="n">
+        <v>223.0641</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1711578</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7140360.93946</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300107.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20.0278</v>
+      </c>
+      <c r="J3" t="n">
+        <v>720129.83</v>
+      </c>
+      <c r="K3" t="n">
+        <v>591176.93791</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>688655.SH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20.0034</v>
+      </c>
+      <c r="J4" t="n">
+        <v>177588.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1144112.739</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301030.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>472922.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>236508.6982</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301041.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>114196.71</v>
+      </c>
+      <c r="K6" t="n">
+        <v>410407.02001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301010.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>151344.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>333320.10758</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>920066.BJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15.8947</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40316.63</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84765.30568999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>920821.BJ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14.7868</v>
+      </c>
+      <c r="J9" t="n">
+        <v>105075.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>214681.5431</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.7114</v>
+      </c>
+      <c r="J10" t="n">
+        <v>226015.11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>918958.566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300489.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>250</v>
+      </c>
+      <c r="D11" t="n">
+        <v>313</v>
+      </c>
+      <c r="E11" t="n">
+        <v>250</v>
+      </c>
+      <c r="F11" t="n">
+        <v>301.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>264.06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.0726</v>
+      </c>
+      <c r="J11" t="n">
+        <v>186979</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5291343.95423</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>688778.SH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-10.0409</v>
+      </c>
+      <c r="J2" t="n">
+        <v>189890.48</v>
+      </c>
+      <c r="K2" t="n">
+        <v>809668.727</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>603008.SH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-10.0352</v>
+      </c>
+      <c r="J3" t="n">
+        <v>177473</v>
+      </c>
+      <c r="K3" t="n">
+        <v>191999.352</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>002768.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>66</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66</v>
+      </c>
+      <c r="E4" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-10.0015</v>
+      </c>
+      <c r="J4" t="n">
+        <v>113173.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>707450.11581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="D5" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>873520.86</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3847979.73032</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>002058.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>185330.58</v>
+      </c>
+      <c r="K6" t="n">
+        <v>425645.73182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>603668.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-9.9894</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41493</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35144.571</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-9.9795</v>
+      </c>
+      <c r="J8" t="n">
+        <v>502037</v>
+      </c>
+      <c r="K8" t="n">
+        <v>671423.661</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>001336.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-9.9756</v>
+      </c>
+      <c r="J9" t="n">
+        <v>169378.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>313367.93214</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-9.9739</v>
+      </c>
+      <c r="J10" t="n">
+        <v>59553</v>
+      </c>
+      <c r="K10" t="n">
+        <v>102676.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>600812.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-9.954800000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2187796.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1320339.291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000759.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中百集团</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.5732</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G2" t="n">
+        <v>924555074</v>
+      </c>
+      <c r="H2" t="n">
+        <v>139661189</v>
+      </c>
+      <c r="I2" t="n">
+        <v>208380580.04</v>
+      </c>
+      <c r="J2" t="n">
+        <v>348041769.04</v>
+      </c>
+      <c r="K2" t="n">
+        <v>68719391.04000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4347330945.75</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000892.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>欢瑞世纪</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3.7453</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1073574623</v>
+      </c>
+      <c r="H3" t="n">
+        <v>143474829.43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>170583001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>314057830.43</v>
+      </c>
+      <c r="K3" t="n">
+        <v>27108171.57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3653505852.56</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>001231.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>农心科技</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.9961</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>461930707</v>
+      </c>
+      <c r="H4" t="n">
+        <v>89581630.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>53331204.16</v>
+      </c>
+      <c r="J4" t="n">
+        <v>142912834.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-36250426.64</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1435625878.95</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>001330.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3.5202</v>
+      </c>
+      <c r="F5" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2446816092</v>
+      </c>
+      <c r="H5" t="n">
+        <v>426416861.38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>331512684.93</v>
+      </c>
+      <c r="J5" t="n">
+        <v>757929546.3099999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-94904176.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8605070182.799999</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>001336.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>楚环科技</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.9756</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>313367932</v>
+      </c>
+      <c r="H6" t="n">
+        <v>44006384.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20075945.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>64082330.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-23930439</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1183738385.83</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>002058.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G7" t="n">
+        <v>425645732</v>
+      </c>
+      <c r="H7" t="n">
+        <v>42310987.23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>38877879</v>
+      </c>
+      <c r="J7" t="n">
+        <v>81188866.23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-3433108.23</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3264439994.64</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>002242.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.1899</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2330711699</v>
+      </c>
+      <c r="H8" t="n">
+        <v>137689042.18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>288112171.76</v>
+      </c>
+      <c r="J8" t="n">
+        <v>425801213.94</v>
+      </c>
+      <c r="K8" t="n">
+        <v>150423129.58</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13460398593.75</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>002300.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>太阳电缆</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.284</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="G9" t="n">
+        <v>599357200</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33196360.63</v>
+      </c>
+      <c r="I9" t="n">
+        <v>93019895.69</v>
+      </c>
+      <c r="J9" t="n">
+        <v>126216256.32</v>
+      </c>
+      <c r="K9" t="n">
+        <v>59823535.06</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5756665725.7</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002430.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>杭氧股份</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.992000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1214131068</v>
+      </c>
+      <c r="H10" t="n">
+        <v>253011064.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>335754239.82</v>
+      </c>
+      <c r="J10" t="n">
+        <v>588765304.12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82743175.52</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="M10" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26912849384.32</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3847979730</v>
+      </c>
+      <c r="H11" t="n">
+        <v>502847244.36</v>
+      </c>
+      <c r="I11" t="n">
+        <v>267164578.34</v>
+      </c>
+      <c r="J11" t="n">
+        <v>770011822.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-235682666.02</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>26744710075.74</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.9732</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1263571237</v>
+      </c>
+      <c r="H12" t="n">
+        <v>282305031.59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>272947192.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>555252223.99</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-9357839.189999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9585890562.51</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002591.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>恒大高新</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-6.5642</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>399853820</v>
+      </c>
+      <c r="H13" t="n">
+        <v>58180091.64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>73756724.78</v>
+      </c>
+      <c r="J13" t="n">
+        <v>131936816.42</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15576633.14</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>33</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1495298370.78</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002636.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.155</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3104131606</v>
+      </c>
+      <c r="H14" t="n">
+        <v>243056314.59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>335838362.18</v>
+      </c>
+      <c r="J14" t="n">
+        <v>578894676.77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>92782047.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48721392302.34</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002639.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>雪人集团</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0302</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1296895576</v>
+      </c>
+      <c r="H15" t="n">
+        <v>126500448.03</v>
+      </c>
+      <c r="I15" t="n">
+        <v>259790178.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>386290626.31</v>
+      </c>
+      <c r="K15" t="n">
+        <v>133289730.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9630932767.040001</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002640.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>跨境通</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.887</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="G16" t="n">
+        <v>990419762</v>
+      </c>
+      <c r="H16" t="n">
+        <v>91931777</v>
+      </c>
+      <c r="I16" t="n">
+        <v>214787387.89</v>
+      </c>
+      <c r="J16" t="n">
+        <v>306719164.89</v>
+      </c>
+      <c r="K16" t="n">
+        <v>122855610.89</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6022738324.2</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.995900000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="G17" t="n">
+        <v>871931341</v>
+      </c>
+      <c r="H17" t="n">
+        <v>83152568</v>
+      </c>
+      <c r="I17" t="n">
+        <v>107457695.48</v>
+      </c>
+      <c r="J17" t="n">
+        <v>190610263.48</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24305127.48</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6353005350</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002692.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>远程股份</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-5.916</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>835504139</v>
+      </c>
+      <c r="H18" t="n">
+        <v>88107505.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>57224649</v>
+      </c>
+      <c r="J18" t="n">
+        <v>145332154.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-30882856.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3539058057.75</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002768.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>国恩股份</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-10.0015</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G19" t="n">
+        <v>707450116</v>
+      </c>
+      <c r="H19" t="n">
+        <v>181764506.42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>169855069.77</v>
+      </c>
+      <c r="J19" t="n">
+        <v>351619576.19</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-11909436.65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="M19" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15617309309.97</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002811.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>郑中设计</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.983700000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1426503429</v>
+      </c>
+      <c r="H20" t="n">
+        <v>297019427.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>282920380</v>
+      </c>
+      <c r="J20" t="n">
+        <v>579939807.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-14099047.15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="M20" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5737692868.03</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-9.9739</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G21" t="n">
+        <v>102676860</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23192041.44</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7296125</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30488166.44</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-15895916.44</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-15.48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3168175732.56</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002980.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>华盛昌</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1805614149</v>
+      </c>
+      <c r="H22" t="n">
+        <v>337521880.63</v>
+      </c>
+      <c r="I22" t="n">
+        <v>374152275.46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>711674156.09</v>
+      </c>
+      <c r="K22" t="n">
+        <v>36630394.83</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>39.41</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11754335344.95</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>111024.SH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>澳弘转债</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>226.163</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20.0001</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>5862805060</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1080837410</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1088407670</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2169245080</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7570260</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M23" t="n">
+        <v>37</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>300107.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>建新股份</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.0278</v>
+      </c>
+      <c r="F24" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="G24" t="n">
+        <v>591176938</v>
+      </c>
+      <c r="H24" t="n">
+        <v>72008048</v>
+      </c>
+      <c r="I24" t="n">
+        <v>104767358.08</v>
+      </c>
+      <c r="J24" t="n">
+        <v>176775406.08</v>
+      </c>
+      <c r="K24" t="n">
+        <v>32759310.08</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M24" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3001057205.47</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>301010.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>晶雪节能</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="G25" t="n">
+        <v>333320108</v>
+      </c>
+      <c r="H25" t="n">
+        <v>45055884</v>
+      </c>
+      <c r="I25" t="n">
+        <v>63882037.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>108937921.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>18826153.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M25" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2559600000</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>301030.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>*ST仕净</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>236508698</v>
+      </c>
+      <c r="H26" t="n">
+        <v>39825659</v>
+      </c>
+      <c r="I26" t="n">
+        <v>17353164</v>
+      </c>
+      <c r="J26" t="n">
+        <v>57178823</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-22472495</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1091370834</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>301030.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>*ST仕净</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>294967640</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40368379</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25523781.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>65892160.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-14844597.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="M27" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1091370834</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>301041.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>金百泽</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="G28" t="n">
+        <v>410407020</v>
+      </c>
+      <c r="H28" t="n">
+        <v>84036017</v>
+      </c>
+      <c r="I28" t="n">
+        <v>113588911.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>197624928.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29552894.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3171173957.46</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.363</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1025964667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>143073909.47</v>
+      </c>
+      <c r="I29" t="n">
+        <v>113553860.27</v>
+      </c>
+      <c r="J29" t="n">
+        <v>256627769.74</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-29520049.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="M29" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2387133871.5</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4.878</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9355831</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3595304.43</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2333829</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5929133.43</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1261475.43</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="M30" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="N30" t="n">
+        <v>59401795.44</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.7184</v>
+      </c>
+      <c r="F31" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="G31" t="n">
+        <v>625779753</v>
+      </c>
+      <c r="H31" t="n">
+        <v>66994074.28</v>
+      </c>
+      <c r="I31" t="n">
+        <v>53732650.85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>120726725.13</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-13261423.43</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="M31" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1393302589.35</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>托伦斯</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.2141</v>
+      </c>
+      <c r="F32" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1318176996</v>
+      </c>
+      <c r="H32" t="n">
+        <v>266943661.27</v>
+      </c>
+      <c r="I32" t="n">
+        <v>190452581.66</v>
+      </c>
+      <c r="J32" t="n">
+        <v>457396242.93</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-76491079.61</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3826173389.3</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301655.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>绿控传动</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.5639</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>393916798</v>
+      </c>
+      <c r="H33" t="n">
+        <v>67777519.16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>39819973.85</v>
+      </c>
+      <c r="J33" t="n">
+        <v>107597493.01</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-27957545.31</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1087780467.72</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301660.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>粤芯半导体</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>223.0641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7140360939</v>
+      </c>
+      <c r="H34" t="n">
+        <v>160426591.28</v>
+      </c>
+      <c r="I34" t="n">
+        <v>542244236.76</v>
+      </c>
+      <c r="J34" t="n">
+        <v>702670828.04</v>
+      </c>
+      <c r="K34" t="n">
+        <v>381817645.48</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9458843993.200001</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.9048</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1421442600</v>
+      </c>
+      <c r="H35" t="n">
+        <v>240774373.65</v>
+      </c>
+      <c r="I35" t="n">
+        <v>158900721.39</v>
+      </c>
+      <c r="J35" t="n">
+        <v>399675095.04</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-81873652.26000001</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="M35" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4124278035.8</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.6763</v>
+      </c>
+      <c r="F36" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3958550113</v>
+      </c>
+      <c r="H36" t="n">
+        <v>522315007.17</v>
+      </c>
+      <c r="I36" t="n">
+        <v>429889607.91</v>
+      </c>
+      <c r="J36" t="n">
+        <v>952204615.08</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-92425399.26000001</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="M36" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9337945821.9</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600202.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>哈空调</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.0394</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="G37" t="n">
+        <v>157008710</v>
+      </c>
+      <c r="H37" t="n">
+        <v>40605167</v>
+      </c>
+      <c r="I37" t="n">
+        <v>63191700</v>
+      </c>
+      <c r="J37" t="n">
+        <v>103796867</v>
+      </c>
+      <c r="K37" t="n">
+        <v>22586533</v>
+      </c>
+      <c r="L37" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2142874356.48</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.6182</v>
+      </c>
+      <c r="F38" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1297886308</v>
+      </c>
+      <c r="H38" t="n">
+        <v>104488990.12</v>
+      </c>
+      <c r="I38" t="n">
+        <v>109991669.39</v>
+      </c>
+      <c r="J38" t="n">
+        <v>214480659.51</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5502679.27</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3784725198.9</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600354.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>敦煌种业</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.1074</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1071380764</v>
+      </c>
+      <c r="H39" t="n">
+        <v>88002623.73999999</v>
+      </c>
+      <c r="I39" t="n">
+        <v>191312465.17</v>
+      </c>
+      <c r="J39" t="n">
+        <v>279315088.91</v>
+      </c>
+      <c r="K39" t="n">
+        <v>103309841.43</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4908559344</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600408.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>安泰集团</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.5326</v>
+      </c>
+      <c r="F40" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>932857812</v>
+      </c>
+      <c r="H40" t="n">
+        <v>118776182.23</v>
+      </c>
+      <c r="I40" t="n">
+        <v>212827514</v>
+      </c>
+      <c r="J40" t="n">
+        <v>331603696.23</v>
+      </c>
+      <c r="K40" t="n">
+        <v>94051331.77</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="M40" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3715092000</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600712.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10.0559</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G41" t="n">
+        <v>155774758</v>
+      </c>
+      <c r="H41" t="n">
+        <v>26318367.43</v>
+      </c>
+      <c r="I41" t="n">
+        <v>39901036.43</v>
+      </c>
+      <c r="J41" t="n">
+        <v>66219403.86</v>
+      </c>
+      <c r="K41" t="n">
+        <v>13582669</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3183411872.61</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600812.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-9.954800000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1320339291</v>
+      </c>
+      <c r="H42" t="n">
+        <v>109098272.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>97728633.47</v>
+      </c>
+      <c r="J42" t="n">
+        <v>206826905.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-11369638.61</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="M42" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10242910308.9</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600831.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>广电网络</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9.974399999999999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="G43" t="n">
+        <v>476817938</v>
+      </c>
+      <c r="H43" t="n">
+        <v>75749096</v>
+      </c>
+      <c r="I43" t="n">
+        <v>80126918.31999999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>155876014.32</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4377822.32</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M43" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3057072065.6</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0392</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>75515922</v>
+      </c>
+      <c r="H44" t="n">
+        <v>9547793</v>
+      </c>
+      <c r="I44" t="n">
+        <v>37822505.88</v>
+      </c>
+      <c r="J44" t="n">
+        <v>47370298.88</v>
+      </c>
+      <c r="K44" t="n">
+        <v>28274712.88</v>
+      </c>
+      <c r="L44" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="M44" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2150622222</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600851.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>海欣股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="G45" t="n">
+        <v>769184897</v>
+      </c>
+      <c r="H45" t="n">
+        <v>81863395.16</v>
+      </c>
+      <c r="I45" t="n">
+        <v>94147282.15000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>176010677.31</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12283886.99</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7105799802.5</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="F46" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1241771822</v>
+      </c>
+      <c r="H46" t="n">
+        <v>71983066.18000001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>137835321.83</v>
+      </c>
+      <c r="J46" t="n">
+        <v>209818388.01</v>
+      </c>
+      <c r="K46" t="n">
+        <v>65852255.65</v>
+      </c>
+      <c r="L46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4622362053.98</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-8.087</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1284042479</v>
+      </c>
+      <c r="H47" t="n">
+        <v>85970103.16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>76604673.51000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>162574776.67</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-9365429.65</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M47" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="N47" t="n">
+        <v>16740848446</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603008.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ST喜临门</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-10.0352</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G48" t="n">
+        <v>191999352</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50485812</v>
+      </c>
+      <c r="I48" t="n">
+        <v>25510863</v>
+      </c>
+      <c r="J48" t="n">
+        <v>75996675</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-24974949</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-13.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3763948685.7</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603188.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>亚邦股份</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10.0806</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G49" t="n">
+        <v>166699377</v>
+      </c>
+      <c r="H49" t="n">
+        <v>23949339</v>
+      </c>
+      <c r="I49" t="n">
+        <v>68955602</v>
+      </c>
+      <c r="J49" t="n">
+        <v>92904941</v>
+      </c>
+      <c r="K49" t="n">
+        <v>45006263</v>
+      </c>
+      <c r="L49" t="n">
+        <v>27</v>
+      </c>
+      <c r="M49" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3113128200</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-9.9795</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>671423661</v>
+      </c>
+      <c r="H50" t="n">
+        <v>71891618</v>
+      </c>
+      <c r="I50" t="n">
+        <v>107316499</v>
+      </c>
+      <c r="J50" t="n">
+        <v>179208117</v>
+      </c>
+      <c r="K50" t="n">
+        <v>35424881</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="M50" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4655897910</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603386.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>骏亚科技</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0126</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G51" t="n">
+        <v>189429301</v>
+      </c>
+      <c r="H51" t="n">
+        <v>39212558</v>
+      </c>
+      <c r="I51" t="n">
+        <v>65088994</v>
+      </c>
+      <c r="J51" t="n">
+        <v>104301552</v>
+      </c>
+      <c r="K51" t="n">
+        <v>25876436</v>
+      </c>
+      <c r="L51" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="M51" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5700855123.2</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603598.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>引力传媒</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-3.0657</v>
+      </c>
+      <c r="F52" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="G52" t="n">
+        <v>916789383</v>
+      </c>
+      <c r="H52" t="n">
+        <v>94480779</v>
+      </c>
+      <c r="I52" t="n">
+        <v>129959374</v>
+      </c>
+      <c r="J52" t="n">
+        <v>224440153</v>
+      </c>
+      <c r="K52" t="n">
+        <v>35478595</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="M52" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5381535408</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603668.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>天马科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-9.9894</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G53" t="n">
+        <v>35144571</v>
+      </c>
+      <c r="H53" t="n">
+        <v>19743400.6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4205355</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23948755.6</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-15538045.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-44.21</v>
+      </c>
+      <c r="M53" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4284098320.04</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603668.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>天马科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-9.9894</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G54" t="n">
+        <v>446824063</v>
+      </c>
+      <c r="H54" t="n">
+        <v>90294134.34</v>
+      </c>
+      <c r="I54" t="n">
+        <v>76712726</v>
+      </c>
+      <c r="J54" t="n">
+        <v>167006860.34</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-13581408.34</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="M54" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4284098320.04</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603968.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>醋化股份</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10.0383</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>403470988</v>
+      </c>
+      <c r="H55" t="n">
+        <v>63312980</v>
+      </c>
+      <c r="I55" t="n">
+        <v>92265043</v>
+      </c>
+      <c r="J55" t="n">
+        <v>155578023</v>
+      </c>
+      <c r="K55" t="n">
+        <v>28952063</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="M55" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2936332800</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603968.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>醋化股份</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10.0383</v>
+      </c>
+      <c r="F56" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>724544547</v>
+      </c>
+      <c r="H56" t="n">
+        <v>71163654.90000001</v>
+      </c>
+      <c r="I56" t="n">
+        <v>121087731.53</v>
+      </c>
+      <c r="J56" t="n">
+        <v>192251386.43</v>
+      </c>
+      <c r="K56" t="n">
+        <v>49924076.63</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M56" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2936332800</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603997.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>继峰股份</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-9.9154</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G57" t="n">
+        <v>600802918</v>
+      </c>
+      <c r="H57" t="n">
+        <v>230448829.34</v>
+      </c>
+      <c r="I57" t="n">
+        <v>111759232</v>
+      </c>
+      <c r="J57" t="n">
+        <v>342208061.34</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-118689597.34</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-19.76</v>
+      </c>
+      <c r="M57" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="N57" t="n">
+        <v>14910944206.08</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3252423948</v>
+      </c>
+      <c r="H58" t="n">
+        <v>394952440.3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>373529905.78</v>
+      </c>
+      <c r="J58" t="n">
+        <v>768482346.08</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-21422534.52</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8631483034.68</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>605366.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>宏柏新材</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4.8045</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G59" t="n">
+        <v>848484637</v>
+      </c>
+      <c r="H59" t="n">
+        <v>93056490.37</v>
+      </c>
+      <c r="I59" t="n">
+        <v>146021397.27</v>
+      </c>
+      <c r="J59" t="n">
+        <v>239077887.64</v>
+      </c>
+      <c r="K59" t="n">
+        <v>52964906.9</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="M59" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7249123826</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>605399.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>晨光新材</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-2.2382</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G60" t="n">
+        <v>213251000</v>
+      </c>
+      <c r="H60" t="n">
+        <v>33704498.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>43130953.7</v>
+      </c>
+      <c r="J60" t="n">
+        <v>76835452.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>9426455.199999999</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M60" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3804071837.92</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>688655.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>迅捷兴</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="E61" t="n">
+        <v>20.0034</v>
+      </c>
+      <c r="F61" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1144112700</v>
+      </c>
+      <c r="H61" t="n">
+        <v>155792795.42</v>
+      </c>
+      <c r="I61" t="n">
+        <v>205414603.19</v>
+      </c>
+      <c r="J61" t="n">
+        <v>361207398.61</v>
+      </c>
+      <c r="K61" t="n">
+        <v>49621807.77</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M61" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="N61" t="n">
+        <v>9442678100</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>920157.BJ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>宇特光电</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>67.26000000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-5.4008</v>
+      </c>
+      <c r="F62" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="G62" t="n">
+        <v>517159600</v>
+      </c>
+      <c r="H62" t="n">
+        <v>70464975.95</v>
+      </c>
+      <c r="I62" t="n">
+        <v>77056814.16</v>
+      </c>
+      <c r="J62" t="n">
+        <v>147521790.11</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6591838.21</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M62" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="N62" t="n">
+        <v>861968310.42</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>920298.BJ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>腾信精密</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4.2302</v>
+      </c>
+      <c r="F63" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>262623700</v>
+      </c>
+      <c r="H63" t="n">
+        <v>42808126.68</v>
+      </c>
+      <c r="I63" t="n">
+        <v>37817195.7</v>
+      </c>
+      <c r="J63" t="n">
+        <v>80625322.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-4990930.98</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="M63" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1149795000</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>920627.BJ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>力王股份</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-7.3634</v>
+      </c>
+      <c r="F64" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="G64" t="n">
+        <v>232355600</v>
+      </c>
+      <c r="H64" t="n">
+        <v>43516936.88</v>
+      </c>
+      <c r="I64" t="n">
+        <v>27223140.52</v>
+      </c>
+      <c r="J64" t="n">
+        <v>70740077.40000001</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-16293796.36</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-7.01</v>
+      </c>
+      <c r="M64" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="N64" t="n">
+        <v>957401250</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-4.9272</v>
+      </c>
+      <c r="F65" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="G65" t="n">
+        <v>131568100</v>
+      </c>
+      <c r="H65" t="n">
+        <v>16333789.34</v>
+      </c>
+      <c r="I65" t="n">
+        <v>37545659.14</v>
+      </c>
+      <c r="J65" t="n">
+        <v>53879448.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>21211869.8</v>
+      </c>
+      <c r="L65" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="M65" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="N65" t="n">
+        <v>575575057.5</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>920895.BJ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>花溪科技</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="G66" t="n">
+        <v>129057700</v>
+      </c>
+      <c r="H66" t="n">
+        <v>20714755.24</v>
+      </c>
+      <c r="I66" t="n">
+        <v>30275781.21</v>
+      </c>
+      <c r="J66" t="n">
+        <v>50990536.45</v>
+      </c>
+      <c r="K66" t="n">
+        <v>9561025.970000001</v>
+      </c>
+      <c r="L66" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M66" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="N66" t="n">
+        <v>646867619</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4110 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.9476</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>402682361</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30952794</v>
+      </c>
+      <c r="I2" t="n">
+        <v>103060526</v>
+      </c>
+      <c r="J2" t="n">
+        <v>134013320</v>
+      </c>
+      <c r="K2" t="n">
+        <v>72107732</v>
+      </c>
+      <c r="L2" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4179210367.5</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000601.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>韶能股份</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1071692049</v>
+      </c>
+      <c r="H3" t="n">
+        <v>72839820.12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>194011008.87</v>
+      </c>
+      <c r="J3" t="n">
+        <v>266850828.99</v>
+      </c>
+      <c r="K3" t="n">
+        <v>121171188.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7188012253.62</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000668.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>荣丰控股</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.0195</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65411712</v>
+      </c>
+      <c r="H4" t="n">
+        <v>37565400</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17314302</v>
+      </c>
+      <c r="J4" t="n">
+        <v>54879702</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-20251098</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-30.96</v>
+      </c>
+      <c r="M4" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3321563551.8</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G5" t="n">
+        <v>741429726</v>
+      </c>
+      <c r="H5" t="n">
+        <v>150688201</v>
+      </c>
+      <c r="I5" t="n">
+        <v>149245451.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>299933652.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1442749.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14605584699.85</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1640521141</v>
+      </c>
+      <c r="H6" t="n">
+        <v>254590951.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>336245752.69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>590836704.55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>81654800.83</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="M6" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14605584699.85</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000892.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>欢瑞世纪</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1946</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1081871934</v>
+      </c>
+      <c r="H7" t="n">
+        <v>192419069</v>
+      </c>
+      <c r="I7" t="n">
+        <v>123533022</v>
+      </c>
+      <c r="J7" t="n">
+        <v>315952091</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-68886047</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3646397864.52</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001209.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>洪兴股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-7.0951</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>196701125</v>
+      </c>
+      <c r="H8" t="n">
+        <v>49936088.11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>35491233.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>85427321.70999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-14444854.51</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1737007589.72</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.9954</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="G9" t="n">
+        <v>985457943</v>
+      </c>
+      <c r="H9" t="n">
+        <v>56931663.17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>96715150.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>153646813.42</v>
+      </c>
+      <c r="K9" t="n">
+        <v>39783487.08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5921600414.01</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001246.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>力勤资源</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-8.331</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1852731646</v>
+      </c>
+      <c r="H10" t="n">
+        <v>146512866.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>138816645.94</v>
+      </c>
+      <c r="J10" t="n">
+        <v>285329512.19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-7696220.31</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5210656130.88</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001318.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9786</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>617584588</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84749294</v>
+      </c>
+      <c r="I11" t="n">
+        <v>80737191</v>
+      </c>
+      <c r="J11" t="n">
+        <v>165486485</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4012103</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4361443800</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001318.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.9786</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="G12" t="n">
+        <v>970127876</v>
+      </c>
+      <c r="H12" t="n">
+        <v>119314448.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>115921600.66</v>
+      </c>
+      <c r="J12" t="n">
+        <v>235236049.46</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-3392848.14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4361443800</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001330.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>博纳影业</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.6216</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2244968815</v>
+      </c>
+      <c r="H13" t="n">
+        <v>329351169.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>283329564.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>612680734.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-46021605.05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8744611861.440001</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>001336.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>楚环科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-8.310700000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="G14" t="n">
+        <v>979085491</v>
+      </c>
+      <c r="H14" t="n">
+        <v>94436593.75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>82948639.72</v>
+      </c>
+      <c r="J14" t="n">
+        <v>177385233.47</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-11487954.03</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1085361431.44</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002029.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>七匹狼</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.979200000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>473233170</v>
+      </c>
+      <c r="H15" t="n">
+        <v>33638907.63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>189998396</v>
+      </c>
+      <c r="J15" t="n">
+        <v>223637303.63</v>
+      </c>
+      <c r="K15" t="n">
+        <v>156359488.37</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="M15" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7039995046.22</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002080.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中材科技</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9.9923</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3025480377</v>
+      </c>
+      <c r="H16" t="n">
+        <v>593246705.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>219926384.61</v>
+      </c>
+      <c r="J16" t="n">
+        <v>813173090.51</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-373320321.29</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-12.34</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="N16" t="n">
+        <v>77999184184.32001</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0543</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="G17" t="n">
+        <v>574199579</v>
+      </c>
+      <c r="H17" t="n">
+        <v>61557254</v>
+      </c>
+      <c r="I17" t="n">
+        <v>104169447</v>
+      </c>
+      <c r="J17" t="n">
+        <v>165726701</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42612193</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="M17" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3836810316.6</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-10.0024</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3004836279</v>
+      </c>
+      <c r="H18" t="n">
+        <v>256763759.45</v>
+      </c>
+      <c r="I18" t="n">
+        <v>231901953.14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>488665712.59</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-24861806.31</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M18" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24069608147.9</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002639.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>雪人集团</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.1809</v>
+      </c>
+      <c r="F19" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2922718033</v>
+      </c>
+      <c r="H19" t="n">
+        <v>288865047.79</v>
+      </c>
+      <c r="I19" t="n">
+        <v>361846248.06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>650711295.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>72981200.27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10033596851.2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002647.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>仁东控股</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-9.963100000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>287600867</v>
+      </c>
+      <c r="H20" t="n">
+        <v>89783326.98999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>36116939</v>
+      </c>
+      <c r="J20" t="n">
+        <v>125900265.99</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-53666387.99</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-18.66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9909246572.32</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002692.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>远程股份</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-9.9391</v>
+      </c>
+      <c r="F21" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="G21" t="n">
+        <v>497362608</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50679501</v>
+      </c>
+      <c r="I21" t="n">
+        <v>37195665</v>
+      </c>
+      <c r="J21" t="n">
+        <v>87875166</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-13483836</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="M21" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3187305837</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.0451</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>341072489</v>
+      </c>
+      <c r="H22" t="n">
+        <v>64199514</v>
+      </c>
+      <c r="I22" t="n">
+        <v>46638988.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>110838502.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-17560525.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3259024450.5</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002768.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>国恩股份</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-9.9984</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>506853335</v>
+      </c>
+      <c r="H23" t="n">
+        <v>141677792.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>135636812.64</v>
+      </c>
+      <c r="J23" t="n">
+        <v>277314604.76</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-6040979.48</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M23" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14055830637.24</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-7.2506</v>
+      </c>
+      <c r="F24" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="G24" t="n">
+        <v>874141008</v>
+      </c>
+      <c r="H24" t="n">
+        <v>92359435.98999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>142325362.35</v>
+      </c>
+      <c r="J24" t="n">
+        <v>234684798.34</v>
+      </c>
+      <c r="K24" t="n">
+        <v>49965926.36</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M24" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2938464615.06</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002878.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>元隆雅图</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.1863</v>
+      </c>
+      <c r="F25" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="G25" t="n">
+        <v>634136512</v>
+      </c>
+      <c r="H25" t="n">
+        <v>122670529.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>61916432</v>
+      </c>
+      <c r="J25" t="n">
+        <v>184586961.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-60754097.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-9.58</v>
+      </c>
+      <c r="M25" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3421004169</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002917.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>金奥博</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>422256602</v>
+      </c>
+      <c r="H26" t="n">
+        <v>69463735.25</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31420205</v>
+      </c>
+      <c r="J26" t="n">
+        <v>100883940.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-38043530.25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3152615445.1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002949.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>华阳国际</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-7.8911</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>292550203</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49348622</v>
+      </c>
+      <c r="I27" t="n">
+        <v>40344393</v>
+      </c>
+      <c r="J27" t="n">
+        <v>89693015</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-9004229</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="M27" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2003899138.84</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002990.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5.0775</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3455092319</v>
+      </c>
+      <c r="H28" t="n">
+        <v>563830262.13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>691899685.5700001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1255729947.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>128069423.44</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M28" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8426033271.15</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>300006.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20.0608</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1284272767</v>
+      </c>
+      <c r="H29" t="n">
+        <v>218570226.26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>194325816.68</v>
+      </c>
+      <c r="J29" t="n">
+        <v>412896042.94</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-24244409.58</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8340985094.2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>300006.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20.0608</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4327696636</v>
+      </c>
+      <c r="H30" t="n">
+        <v>872841286.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>864541049.48</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1737382335.53</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-8300236.57</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M30" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="N30" t="n">
+        <v>8340985094.2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300107.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>建新股份</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.5191</v>
+      </c>
+      <c r="F31" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1151560974</v>
+      </c>
+      <c r="H31" t="n">
+        <v>121660129.8</v>
+      </c>
+      <c r="I31" t="n">
+        <v>59238038.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>180898168.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-62422091.3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3136678562.38</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>300299.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>富春股份</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.0698</v>
+      </c>
+      <c r="F32" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1228542846</v>
+      </c>
+      <c r="H32" t="n">
+        <v>115162234.59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>319321474.22</v>
+      </c>
+      <c r="J32" t="n">
+        <v>434483708.81</v>
+      </c>
+      <c r="K32" t="n">
+        <v>204159239.63</v>
+      </c>
+      <c r="L32" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="M32" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4743449264.8</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>300299.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>富春股份</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20.0698</v>
+      </c>
+      <c r="F33" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1537795068</v>
+      </c>
+      <c r="H33" t="n">
+        <v>168608655.59</v>
+      </c>
+      <c r="I33" t="n">
+        <v>349562190.62</v>
+      </c>
+      <c r="J33" t="n">
+        <v>518170846.21</v>
+      </c>
+      <c r="K33" t="n">
+        <v>180953535.03</v>
+      </c>
+      <c r="L33" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="M33" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4743449264.8</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>300338.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>*ST开元</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20.1646</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G34" t="n">
+        <v>62797201</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8115942</v>
+      </c>
+      <c r="I34" t="n">
+        <v>12363234</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20479176</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4247292</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="M34" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1021822586.64</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>300853.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>申昊科技</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-15.6682</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>412119742</v>
+      </c>
+      <c r="H35" t="n">
+        <v>178632085.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>70261215</v>
+      </c>
+      <c r="J35" t="n">
+        <v>248893300.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-108370870.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-26.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4009915324.8</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301010.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>晶雪节能</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="E36" t="n">
+        <v>14.135</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1047850594</v>
+      </c>
+      <c r="H36" t="n">
+        <v>92772141.31999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>92055231.36</v>
+      </c>
+      <c r="J36" t="n">
+        <v>184827372.68</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-716909.96</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2921400000</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14.4874</v>
+      </c>
+      <c r="F37" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1192859864</v>
+      </c>
+      <c r="H37" t="n">
+        <v>140758343.41</v>
+      </c>
+      <c r="I37" t="n">
+        <v>140296578.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>281054921.71</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-461765.11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M37" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2732967383.64</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>301132.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>满坤科技</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>75</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18.3152</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1472679650</v>
+      </c>
+      <c r="H38" t="n">
+        <v>349946455.19</v>
+      </c>
+      <c r="I38" t="n">
+        <v>273054994.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>623001449.39</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-76891460.98999999</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M38" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7105555650</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>301132.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>满坤科技</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>18.3152</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2356475815</v>
+      </c>
+      <c r="H39" t="n">
+        <v>608135756.6900001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>430469277.79</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1038605034.48</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-177666478.9</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="M39" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7105555650</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.4103</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11089784</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2206980.92</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3252828.93</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5459809.85</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1045848.01</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="M40" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="N40" t="n">
+        <v>63209602.84</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>63</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-8.893700000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="G41" t="n">
+        <v>502054343</v>
+      </c>
+      <c r="H41" t="n">
+        <v>42006535.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>56737513.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>98744048.39</v>
+      </c>
+      <c r="K41" t="n">
+        <v>14730978.19</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1269386307</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>301689.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>电科思仪</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-10.2442</v>
+      </c>
+      <c r="F42" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1415247270</v>
+      </c>
+      <c r="H42" t="n">
+        <v>114241946.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>261630852.33</v>
+      </c>
+      <c r="J42" t="n">
+        <v>375872798.41</v>
+      </c>
+      <c r="K42" t="n">
+        <v>147388906.25</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="M42" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3701776978.12</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>301697.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>贝特利</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-11.0759</v>
+      </c>
+      <c r="F43" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G43" t="n">
+        <v>423412247</v>
+      </c>
+      <c r="H43" t="n">
+        <v>61351583</v>
+      </c>
+      <c r="I43" t="n">
+        <v>35015652.25</v>
+      </c>
+      <c r="J43" t="n">
+        <v>96367235.25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-26335930.75</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M43" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1112533249.86</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600097.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>开创国际</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0324</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G44" t="n">
+        <v>139364473</v>
+      </c>
+      <c r="H44" t="n">
+        <v>31835927</v>
+      </c>
+      <c r="I44" t="n">
+        <v>62000135</v>
+      </c>
+      <c r="J44" t="n">
+        <v>93836062</v>
+      </c>
+      <c r="K44" t="n">
+        <v>30164208</v>
+      </c>
+      <c r="L44" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="M44" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2457552901.8</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.4433</v>
+      </c>
+      <c r="F45" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3569794781</v>
+      </c>
+      <c r="H45" t="n">
+        <v>492201008.46</v>
+      </c>
+      <c r="I45" t="n">
+        <v>393339200.17</v>
+      </c>
+      <c r="J45" t="n">
+        <v>885540208.63</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-98861808.29000001</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M45" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="N45" t="n">
+        <v>9472720297.68</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600202.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>哈空调</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.0179</v>
+      </c>
+      <c r="F46" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="G46" t="n">
+        <v>509564277</v>
+      </c>
+      <c r="H46" t="n">
+        <v>114261234</v>
+      </c>
+      <c r="I46" t="n">
+        <v>110682145</v>
+      </c>
+      <c r="J46" t="n">
+        <v>224943379</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-3579089</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2357545132.8</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600206.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>有研新材</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-9.9955</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3081795661</v>
+      </c>
+      <c r="H47" t="n">
+        <v>254119460.43</v>
+      </c>
+      <c r="I47" t="n">
+        <v>141434150.61</v>
+      </c>
+      <c r="J47" t="n">
+        <v>395553611.04</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-112685309.82</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="M47" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33616632813.72</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.7216</v>
+      </c>
+      <c r="F48" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1432269357</v>
+      </c>
+      <c r="H48" t="n">
+        <v>261723756.96</v>
+      </c>
+      <c r="I48" t="n">
+        <v>96573643.34</v>
+      </c>
+      <c r="J48" t="n">
+        <v>358297400.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-165150113.62</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-11.53</v>
+      </c>
+      <c r="M48" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3887730939.15</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600252.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>中恒集团</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10.2222</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="G49" t="n">
+        <v>478186341</v>
+      </c>
+      <c r="H49" t="n">
+        <v>33096637.6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>164547827.67</v>
+      </c>
+      <c r="J49" t="n">
+        <v>197644465.27</v>
+      </c>
+      <c r="K49" t="n">
+        <v>131451190.07</v>
+      </c>
+      <c r="L49" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="M49" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7896724413.6</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600391.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>航发科技</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0052</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1587702739</v>
+      </c>
+      <c r="H50" t="n">
+        <v>366405407.96</v>
+      </c>
+      <c r="I50" t="n">
+        <v>358279215.59</v>
+      </c>
+      <c r="J50" t="n">
+        <v>724684623.55</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-8126192.37</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M50" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="N50" t="n">
+        <v>14083318796.22</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600408.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>安泰集团</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0271</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1123247877</v>
+      </c>
+      <c r="H51" t="n">
+        <v>174993192.84</v>
+      </c>
+      <c r="I51" t="n">
+        <v>111103840.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>286097033.44</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-63889352.24</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="M51" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4087608000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>600693.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.8943</v>
+      </c>
+      <c r="F52" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2918768439</v>
+      </c>
+      <c r="H52" t="n">
+        <v>292348462.21</v>
+      </c>
+      <c r="I52" t="n">
+        <v>266815974.36</v>
+      </c>
+      <c r="J52" t="n">
+        <v>559164436.5700001</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-25532487.85</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M52" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="N52" t="n">
+        <v>10592534412.58</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9.9786</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="G53" t="n">
+        <v>238932737</v>
+      </c>
+      <c r="H53" t="n">
+        <v>35678680.53</v>
+      </c>
+      <c r="I53" t="n">
+        <v>75948169.88</v>
+      </c>
+      <c r="J53" t="n">
+        <v>111626850.41</v>
+      </c>
+      <c r="K53" t="n">
+        <v>40269489.35</v>
+      </c>
+      <c r="L53" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2365224582</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>601026.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>道生天合</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-9.9732</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="G54" t="n">
+        <v>141372790</v>
+      </c>
+      <c r="H54" t="n">
+        <v>18067966</v>
+      </c>
+      <c r="I54" t="n">
+        <v>14656152.7</v>
+      </c>
+      <c r="J54" t="n">
+        <v>32724118.7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-3411813.3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="M54" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1494102530.5</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>601188.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>龙江交通</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.9688</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="G55" t="n">
+        <v>902421797</v>
+      </c>
+      <c r="H55" t="n">
+        <v>151321710.04</v>
+      </c>
+      <c r="I55" t="n">
+        <v>145554817</v>
+      </c>
+      <c r="J55" t="n">
+        <v>296876527.04</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-5766893.04</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M55" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4608308799.95</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>601579.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>会稽山</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-7.9185</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3390903565</v>
+      </c>
+      <c r="H56" t="n">
+        <v>481738970.13</v>
+      </c>
+      <c r="I56" t="n">
+        <v>693626602.1799999</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1175365572.31</v>
+      </c>
+      <c r="K56" t="n">
+        <v>211887632.05</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M56" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="N56" t="n">
+        <v>15165427626.67</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.9811</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1427454356</v>
+      </c>
+      <c r="H57" t="n">
+        <v>86759823.40000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>119089081</v>
+      </c>
+      <c r="J57" t="n">
+        <v>205848904.4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>32329257.6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M57" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="N57" t="n">
+        <v>18411765675</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603096.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>新经典</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0143</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="G58" t="n">
+        <v>863042695</v>
+      </c>
+      <c r="H58" t="n">
+        <v>163913709.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>78709063.91</v>
+      </c>
+      <c r="J58" t="n">
+        <v>242622773.31</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-85204645.48999999</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3558192775.68</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603466.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>风语筑</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.4422</v>
+      </c>
+      <c r="F59" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2044087639</v>
+      </c>
+      <c r="H59" t="n">
+        <v>304056468.32</v>
+      </c>
+      <c r="I59" t="n">
+        <v>344246691.63</v>
+      </c>
+      <c r="J59" t="n">
+        <v>648303159.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>40190223.31</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M59" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="N59" t="n">
+        <v>8036179833.64</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603661.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>恒林股份</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-10.0114</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G60" t="n">
+        <v>191055155</v>
+      </c>
+      <c r="H60" t="n">
+        <v>61267368.2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>31569790</v>
+      </c>
+      <c r="J60" t="n">
+        <v>92837158.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-29697578.2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-15.54</v>
+      </c>
+      <c r="M60" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4400080860.84</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603668.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>天马科技</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10.0354</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G61" t="n">
+        <v>413985411</v>
+      </c>
+      <c r="H61" t="n">
+        <v>76345957.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>70356167.65000001</v>
+      </c>
+      <c r="J61" t="n">
+        <v>146702125.35</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-5989790.05</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="M61" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3854171097.84</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>603968.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>醋化股份</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.0279</v>
+      </c>
+      <c r="F62" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="G62" t="n">
+        <v>596555864</v>
+      </c>
+      <c r="H62" t="n">
+        <v>89743318</v>
+      </c>
+      <c r="I62" t="n">
+        <v>63435240</v>
+      </c>
+      <c r="J62" t="n">
+        <v>153178558</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-26308078</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3230784000</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>603992.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>松霖科技</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.0134</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1016503611</v>
+      </c>
+      <c r="H63" t="n">
+        <v>116098850.45</v>
+      </c>
+      <c r="I63" t="n">
+        <v>115139434.19</v>
+      </c>
+      <c r="J63" t="n">
+        <v>231238284.64</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-959416.26</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M63" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="N63" t="n">
+        <v>10903259190.2</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>605069.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-10.0081</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G64" t="n">
+        <v>158273833</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20586327.61</v>
+      </c>
+      <c r="I64" t="n">
+        <v>11863664</v>
+      </c>
+      <c r="J64" t="n">
+        <v>32449991.61</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-8722663.609999999</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="M64" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2341377424.68</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>605136.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>丽人丽妆</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-8.931699999999999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1033351447</v>
+      </c>
+      <c r="H65" t="n">
+        <v>120769391.4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>66415785</v>
+      </c>
+      <c r="J65" t="n">
+        <v>187185176.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-54353606.4</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="M65" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4164768400</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>605189.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>富春染织</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10.0339</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>96853921</v>
+      </c>
+      <c r="H66" t="n">
+        <v>12187107</v>
+      </c>
+      <c r="I66" t="n">
+        <v>60833286</v>
+      </c>
+      <c r="J66" t="n">
+        <v>73020393</v>
+      </c>
+      <c r="K66" t="n">
+        <v>48646179</v>
+      </c>
+      <c r="L66" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="M66" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3866553059.97</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>605287.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>德才股份</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.7686</v>
+      </c>
+      <c r="F67" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1570486131</v>
+      </c>
+      <c r="H67" t="n">
+        <v>191955107.94</v>
+      </c>
+      <c r="I67" t="n">
+        <v>355586416.4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>547541524.34</v>
+      </c>
+      <c r="K67" t="n">
+        <v>163631308.46</v>
+      </c>
+      <c r="L67" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="M67" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6846000000</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-3.3163</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1244031011</v>
+      </c>
+      <c r="H68" t="n">
+        <v>125983002.79</v>
+      </c>
+      <c r="I68" t="n">
+        <v>73246086.58</v>
+      </c>
+      <c r="J68" t="n">
+        <v>199229089.37</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-52736916.21</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="M68" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="N68" t="n">
+        <v>8422222232.75</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>688573.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>信宇人</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-20.0114</v>
+      </c>
+      <c r="F69" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="G69" t="n">
+        <v>195324700</v>
+      </c>
+      <c r="H69" t="n">
+        <v>24900108.44</v>
+      </c>
+      <c r="I69" t="n">
+        <v>24413725.78</v>
+      </c>
+      <c r="J69" t="n">
+        <v>49313834.22</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-486382.66</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="N69" t="n">
+        <v>744494987.75</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920021.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>流金科技</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.2069</v>
+      </c>
+      <c r="F70" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="G70" t="n">
+        <v>629745300</v>
+      </c>
+      <c r="H70" t="n">
+        <v>104380389.49</v>
+      </c>
+      <c r="I70" t="n">
+        <v>77100917.73</v>
+      </c>
+      <c r="J70" t="n">
+        <v>181481307.22</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-27279471.76</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="M70" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2287405178.52</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>920066.BJ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>科拜尔</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-4.178</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="G71" t="n">
+        <v>98052400</v>
+      </c>
+      <c r="H71" t="n">
+        <v>13999619.62</v>
+      </c>
+      <c r="I71" t="n">
+        <v>11504568.73</v>
+      </c>
+      <c r="J71" t="n">
+        <v>25504188.35</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-2495050.89</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="M71" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="N71" t="n">
+        <v>419327178.6</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920157.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>宇特光电</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>60</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-10.7939</v>
+      </c>
+      <c r="F72" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="G72" t="n">
+        <v>412242300</v>
+      </c>
+      <c r="H72" t="n">
+        <v>59247775</v>
+      </c>
+      <c r="I72" t="n">
+        <v>70570514.58</v>
+      </c>
+      <c r="J72" t="n">
+        <v>129818289.58</v>
+      </c>
+      <c r="K72" t="n">
+        <v>11322739.58</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M72" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="N72" t="n">
+        <v>768928020</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920627.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>力王股份</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>220259700</v>
+      </c>
+      <c r="H73" t="n">
+        <v>31810690.04</v>
+      </c>
+      <c r="I73" t="n">
+        <v>28987729.39</v>
+      </c>
+      <c r="J73" t="n">
+        <v>60798419.43</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-2822960.65</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M73" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="N73" t="n">
+        <v>967220750</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-2.4348</v>
+      </c>
+      <c r="F74" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="G74" t="n">
+        <v>120726100</v>
+      </c>
+      <c r="H74" t="n">
+        <v>33335849.91</v>
+      </c>
+      <c r="I74" t="n">
+        <v>12385074.56</v>
+      </c>
+      <c r="J74" t="n">
+        <v>45720924.47</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-20950775.35</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-17.35</v>
+      </c>
+      <c r="M74" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="N74" t="n">
+        <v>561561056.1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,3493 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000048.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>京基智农</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G2" t="n">
+        <v>365663288</v>
+      </c>
+      <c r="H2" t="n">
+        <v>105646302.22</v>
+      </c>
+      <c r="I2" t="n">
+        <v>42125344.53</v>
+      </c>
+      <c r="J2" t="n">
+        <v>147771646.75</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-63520957.69</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-17.37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8765253540</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1697317801</v>
+      </c>
+      <c r="H3" t="n">
+        <v>141659872.96</v>
+      </c>
+      <c r="I3" t="n">
+        <v>127718213.73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>269378086.69</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-13941659.23</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4557283904.25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.3768</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5466007524</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1115044986.42</v>
+      </c>
+      <c r="I4" t="n">
+        <v>877616047.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1992661033.69</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-237428939.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15390895160.29</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000892.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>欢瑞世纪</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.2378</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1493650431</v>
+      </c>
+      <c r="H5" t="n">
+        <v>170996679.28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>278948407.08</v>
+      </c>
+      <c r="J5" t="n">
+        <v>449945086.36</v>
+      </c>
+      <c r="K5" t="n">
+        <v>107951727.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3873853481.8</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000995.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>皇台酒业</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.0412</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1064510133</v>
+      </c>
+      <c r="H6" t="n">
+        <v>142520601.62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>190267954</v>
+      </c>
+      <c r="J6" t="n">
+        <v>332788555.62</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47747352.38</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2371944960</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>001246.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>力勤资源</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.2077</v>
+      </c>
+      <c r="F7" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1415242537</v>
+      </c>
+      <c r="H7" t="n">
+        <v>110192299.17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>202231634.48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>312423933.65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>92039335.31</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5147725501.28</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001359.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>平安电工</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-10.0013</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>332845411</v>
+      </c>
+      <c r="H8" t="n">
+        <v>66732964.08</v>
+      </c>
+      <c r="I8" t="n">
+        <v>86953663.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>153686627.58</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20220699.42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M8" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4248088499.72</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>002029.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>七匹狼</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-7.9395</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="G9" t="n">
+        <v>951676533</v>
+      </c>
+      <c r="H9" t="n">
+        <v>246053509.36</v>
+      </c>
+      <c r="I9" t="n">
+        <v>67082662.22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>313136171.58</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-178970847.14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6481054040.66</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002058.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.2192</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>590788773</v>
+      </c>
+      <c r="H10" t="n">
+        <v>47288646.28</v>
+      </c>
+      <c r="I10" t="n">
+        <v>49591410.32</v>
+      </c>
+      <c r="J10" t="n">
+        <v>96880056.59999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2302764.04</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3403504851.68</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002134.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天津普林</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9864</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>647137324</v>
+      </c>
+      <c r="H11" t="n">
+        <v>116450678</v>
+      </c>
+      <c r="I11" t="n">
+        <v>201083307</v>
+      </c>
+      <c r="J11" t="n">
+        <v>317533985</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84632629</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="M11" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6016264959.64</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>681668185</v>
+      </c>
+      <c r="H12" t="n">
+        <v>109505179</v>
+      </c>
+      <c r="I12" t="n">
+        <v>91264479.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>200769658.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-18240699.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4220491348.26</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002487.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>大金重工</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-7.4181</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9351705903</v>
+      </c>
+      <c r="H13" t="n">
+        <v>741064841.9400001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>598996905.83</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1340061747.77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-142067936.11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22284103795.12</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.0306</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3413709870</v>
+      </c>
+      <c r="H14" t="n">
+        <v>743659777.98</v>
+      </c>
+      <c r="I14" t="n">
+        <v>531324418.74</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1274984196.72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-212335359.24</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17220158694.97</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002639.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>雪人集团</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.1184</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6892370868</v>
+      </c>
+      <c r="H15" t="n">
+        <v>720766967.78</v>
+      </c>
+      <c r="I15" t="n">
+        <v>819679557.48</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1540446525.26</v>
+      </c>
+      <c r="K15" t="n">
+        <v>98912589.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M15" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10145814710.72</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002692.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>远程股份</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9.9099</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>315721961</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29968003</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20148843</v>
+      </c>
+      <c r="J16" t="n">
+        <v>50116846</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-9819160</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2871446700</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0513</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>781879528</v>
+      </c>
+      <c r="H17" t="n">
+        <v>95553496.18000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>94014612.59999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>189568108.78</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1538883.58</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3586598190.14</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002741.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>光华科技</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-10.0091</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="G18" t="n">
+        <v>806289336</v>
+      </c>
+      <c r="H18" t="n">
+        <v>259165584.82</v>
+      </c>
+      <c r="I18" t="n">
+        <v>132488319.52</v>
+      </c>
+      <c r="J18" t="n">
+        <v>391653904.34</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-126677265.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-15.71</v>
+      </c>
+      <c r="M18" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8467223655.55</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002768.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>国恩股份</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2.4587</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1082518731</v>
+      </c>
+      <c r="H19" t="n">
+        <v>233043194.85</v>
+      </c>
+      <c r="I19" t="n">
+        <v>253690351.48</v>
+      </c>
+      <c r="J19" t="n">
+        <v>486733546.33</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20647156.63</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13710236811.45</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002866.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.1882</v>
+      </c>
+      <c r="F20" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="G20" t="n">
+        <v>781703428</v>
+      </c>
+      <c r="H20" t="n">
+        <v>108692486.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>64519140</v>
+      </c>
+      <c r="J20" t="n">
+        <v>173211626.42</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-44173346.42</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2973380704.92</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002917.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>金奥博</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="G21" t="n">
+        <v>339628692</v>
+      </c>
+      <c r="H21" t="n">
+        <v>43833478.45</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25239454.08</v>
+      </c>
+      <c r="J21" t="n">
+        <v>69072932.53</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-18594024.37</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2837353900.59</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002945.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>华林证券</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.0071</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1226005804</v>
+      </c>
+      <c r="H22" t="n">
+        <v>98757139.06</v>
+      </c>
+      <c r="I22" t="n">
+        <v>291501562.16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>390258701.22</v>
+      </c>
+      <c r="K22" t="n">
+        <v>192744423.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="N22" t="n">
+        <v>41553000000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>111024.SH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>澳弘转债</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>266.152</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13.2374</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>22174393130</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4212744280</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4221171990</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8433916270</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8427710</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M23" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>127096.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>泰坦转债</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-16.3611</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>984932853</v>
+      </c>
+      <c r="H24" t="n">
+        <v>298584895.83</v>
+      </c>
+      <c r="I24" t="n">
+        <v>268854581.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>567439477.53</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-29730314.13</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="M24" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>127116.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>瑞鹄转02</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>143</v>
+      </c>
+      <c r="E25" t="n">
+        <v>43</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>195994266</v>
+      </c>
+      <c r="H25" t="n">
+        <v>71126237</v>
+      </c>
+      <c r="I25" t="n">
+        <v>103290200</v>
+      </c>
+      <c r="J25" t="n">
+        <v>174416437</v>
+      </c>
+      <c r="K25" t="n">
+        <v>32163963</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300111.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>向日葵</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20.0647</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G26" t="n">
+        <v>852999783</v>
+      </c>
+      <c r="H26" t="n">
+        <v>69280774.45</v>
+      </c>
+      <c r="I26" t="n">
+        <v>177694077.76</v>
+      </c>
+      <c r="J26" t="n">
+        <v>246974852.21</v>
+      </c>
+      <c r="K26" t="n">
+        <v>108413303.31</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="M26" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4775551748.94</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>301041.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>金百泽</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.2551</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="G27" t="n">
+        <v>984017527</v>
+      </c>
+      <c r="H27" t="n">
+        <v>153472324.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>133926657.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>287398981.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-19545667.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="M27" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3243856569.34</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.8462</v>
+      </c>
+      <c r="F28" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1295404580</v>
+      </c>
+      <c r="H28" t="n">
+        <v>154238989.26</v>
+      </c>
+      <c r="I28" t="n">
+        <v>124709244.69</v>
+      </c>
+      <c r="J28" t="n">
+        <v>278948233.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-29529744.57</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="M28" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2838081513.78</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301053.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>远信工业</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-20.0127</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>257478426</v>
+      </c>
+      <c r="H29" t="n">
+        <v>80877098.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>27564081.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>108441180.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-53313017.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-20.71</v>
+      </c>
+      <c r="M29" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3097842410.16</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-3.6145</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8285814</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2069746.98</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2662086.21</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4731833.19</v>
+      </c>
+      <c r="K30" t="n">
+        <v>592339.23</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>60924918.4</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301282.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>金禄电子</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G31" t="n">
+        <v>558033204</v>
+      </c>
+      <c r="H31" t="n">
+        <v>85132000.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>205882993.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>291014993.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>120750993.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="M31" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8814767520</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301282.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>金禄电子</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1476072049</v>
+      </c>
+      <c r="H32" t="n">
+        <v>315302221.71</v>
+      </c>
+      <c r="I32" t="n">
+        <v>418904417.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>734206639.01</v>
+      </c>
+      <c r="K32" t="n">
+        <v>103602195.59</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M32" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8814767520</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.9048</v>
+      </c>
+      <c r="F33" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="G33" t="n">
+        <v>527136819</v>
+      </c>
+      <c r="H33" t="n">
+        <v>57087392</v>
+      </c>
+      <c r="I33" t="n">
+        <v>36981727.37</v>
+      </c>
+      <c r="J33" t="n">
+        <v>94069119.37</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-20105664.63</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="M33" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1318952819.94</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.6607</v>
+      </c>
+      <c r="F34" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1095178257</v>
+      </c>
+      <c r="H34" t="n">
+        <v>216930113.06</v>
+      </c>
+      <c r="I34" t="n">
+        <v>103920170.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>320850283.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-113009942.16</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="M34" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2358344902.5</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301569.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>联亚药业</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>401.7143</v>
+      </c>
+      <c r="F35" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2978500206</v>
+      </c>
+      <c r="H35" t="n">
+        <v>79383294.45999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>216634476.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>296017771.26</v>
+      </c>
+      <c r="K35" t="n">
+        <v>137251182.34</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M35" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4103700284.96</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301591.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>肯特股份</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.7293</v>
+      </c>
+      <c r="F36" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="G36" t="n">
+        <v>648094829</v>
+      </c>
+      <c r="H36" t="n">
+        <v>77598820.72</v>
+      </c>
+      <c r="I36" t="n">
+        <v>86711981.98</v>
+      </c>
+      <c r="J36" t="n">
+        <v>164310802.7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9113161.26</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M36" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1814159821.32</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-9.0108</v>
+      </c>
+      <c r="F37" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3043486011</v>
+      </c>
+      <c r="H37" t="n">
+        <v>344363393.62</v>
+      </c>
+      <c r="I37" t="n">
+        <v>416281062.19</v>
+      </c>
+      <c r="J37" t="n">
+        <v>760644455.8099999</v>
+      </c>
+      <c r="K37" t="n">
+        <v>71917668.56999999</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8619148617.74</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5.9046</v>
+      </c>
+      <c r="F38" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1313167283</v>
+      </c>
+      <c r="H38" t="n">
+        <v>101187389.68</v>
+      </c>
+      <c r="I38" t="n">
+        <v>72005576.86</v>
+      </c>
+      <c r="J38" t="n">
+        <v>173192966.54</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-29181812.82</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="M38" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4117286588.85</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600668.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>尖峰集团</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.0551</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>269210913</v>
+      </c>
+      <c r="H39" t="n">
+        <v>49337571.95</v>
+      </c>
+      <c r="I39" t="n">
+        <v>77468981.78</v>
+      </c>
+      <c r="J39" t="n">
+        <v>126806553.73</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28131409.83</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="M39" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3299075746.06</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600693.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-10.0082</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>67268040</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24390796.73</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5730728</v>
+      </c>
+      <c r="J40" t="n">
+        <v>30121524.73</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-18660068.73</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-27.74</v>
+      </c>
+      <c r="M40" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="N40" t="n">
+        <v>9532412018.540001</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10.0457</v>
+      </c>
+      <c r="F41" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="G41" t="n">
+        <v>677157971</v>
+      </c>
+      <c r="H41" t="n">
+        <v>74476581</v>
+      </c>
+      <c r="I41" t="n">
+        <v>265919347</v>
+      </c>
+      <c r="J41" t="n">
+        <v>340395928</v>
+      </c>
+      <c r="K41" t="n">
+        <v>191442766</v>
+      </c>
+      <c r="L41" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4633799001.75</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600792.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>云煤能源</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="G42" t="n">
+        <v>408986899</v>
+      </c>
+      <c r="H42" t="n">
+        <v>62255239.99</v>
+      </c>
+      <c r="I42" t="n">
+        <v>51097498</v>
+      </c>
+      <c r="J42" t="n">
+        <v>113352737.99</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-11157741.99</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="M42" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4994656200</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600812.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.0503</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2115357572</v>
+      </c>
+      <c r="H43" t="n">
+        <v>144141733.32</v>
+      </c>
+      <c r="I43" t="n">
+        <v>220380359.94</v>
+      </c>
+      <c r="J43" t="n">
+        <v>364522093.26</v>
+      </c>
+      <c r="K43" t="n">
+        <v>76238626.62</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="N43" t="n">
+        <v>11272348530.9</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-8.8788</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="G44" t="n">
+        <v>356130376</v>
+      </c>
+      <c r="H44" t="n">
+        <v>85735880</v>
+      </c>
+      <c r="I44" t="n">
+        <v>38155398</v>
+      </c>
+      <c r="J44" t="n">
+        <v>123891278</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-47580482</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-13.36</v>
+      </c>
+      <c r="M44" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2155220844</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600869.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>远东股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.7927</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4219613738</v>
+      </c>
+      <c r="H45" t="n">
+        <v>264028090.73</v>
+      </c>
+      <c r="I45" t="n">
+        <v>528219165.97</v>
+      </c>
+      <c r="J45" t="n">
+        <v>792247256.7</v>
+      </c>
+      <c r="K45" t="n">
+        <v>264191075.24</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="M45" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="N45" t="n">
+        <v>40125897647.68</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>601118.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-10.0145</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1203264723</v>
+      </c>
+      <c r="H46" t="n">
+        <v>171376843.56</v>
+      </c>
+      <c r="I46" t="n">
+        <v>183478182.9</v>
+      </c>
+      <c r="J46" t="n">
+        <v>354855026.46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>12101339.34</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="N46" t="n">
+        <v>26532452341.4</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10.0215</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1566969940</v>
+      </c>
+      <c r="H47" t="n">
+        <v>128643123.91</v>
+      </c>
+      <c r="I47" t="n">
+        <v>141653520.77</v>
+      </c>
+      <c r="J47" t="n">
+        <v>270296644.68</v>
+      </c>
+      <c r="K47" t="n">
+        <v>13010396.86</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M47" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="N47" t="n">
+        <v>20256901762</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.0215</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2994424296</v>
+      </c>
+      <c r="H48" t="n">
+        <v>199562073.37</v>
+      </c>
+      <c r="I48" t="n">
+        <v>244390862.77</v>
+      </c>
+      <c r="J48" t="n">
+        <v>443952936.14</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44828789.4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="N48" t="n">
+        <v>20256901762</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>601872.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-10.0093</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2429133829</v>
+      </c>
+      <c r="H49" t="n">
+        <v>461929365.19</v>
+      </c>
+      <c r="I49" t="n">
+        <v>342906681</v>
+      </c>
+      <c r="J49" t="n">
+        <v>804836046.1900001</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-119022684.19</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="M49" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="N49" t="n">
+        <v>156080829243.66</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603096.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>新经典</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7802</v>
+      </c>
+      <c r="F50" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1001962167</v>
+      </c>
+      <c r="H50" t="n">
+        <v>79067297.12</v>
+      </c>
+      <c r="I50" t="n">
+        <v>73627732.54000001</v>
+      </c>
+      <c r="J50" t="n">
+        <v>152695029.66</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-5439564.58</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="M50" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3585955008</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603172.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>万丰股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0214</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>97926517</v>
+      </c>
+      <c r="H51" t="n">
+        <v>16585904</v>
+      </c>
+      <c r="I51" t="n">
+        <v>32515020.8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>49100924.8</v>
+      </c>
+      <c r="K51" t="n">
+        <v>15929116.8</v>
+      </c>
+      <c r="L51" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="M51" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2738291400</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603230.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G52" t="n">
+        <v>934846572</v>
+      </c>
+      <c r="H52" t="n">
+        <v>64683497</v>
+      </c>
+      <c r="I52" t="n">
+        <v>178888703</v>
+      </c>
+      <c r="J52" t="n">
+        <v>243572200</v>
+      </c>
+      <c r="K52" t="n">
+        <v>114205206</v>
+      </c>
+      <c r="L52" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M52" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5133153960</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603386.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>骏亚科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9.9946</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1305184469</v>
+      </c>
+      <c r="H53" t="n">
+        <v>228427850.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>280496698</v>
+      </c>
+      <c r="J53" t="n">
+        <v>508924548.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>52068847.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M53" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6608031840</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603533.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>掌阅科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-3.0414</v>
+      </c>
+      <c r="F54" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3472377592</v>
+      </c>
+      <c r="H54" t="n">
+        <v>421344021.04</v>
+      </c>
+      <c r="I54" t="n">
+        <v>519922065.22</v>
+      </c>
+      <c r="J54" t="n">
+        <v>941266086.26</v>
+      </c>
+      <c r="K54" t="n">
+        <v>98578044.18000001</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M54" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="N54" t="n">
+        <v>12732397183.35</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603598.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>引力传媒</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-6.7093</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1381251196</v>
+      </c>
+      <c r="H55" t="n">
+        <v>305208070.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>148327373.18</v>
+      </c>
+      <c r="J55" t="n">
+        <v>453535444.08</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-156880697.72</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="M55" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5522017256</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603968.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>醋化股份</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F56" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="G56" t="n">
+        <v>428528223</v>
+      </c>
+      <c r="H56" t="n">
+        <v>53509432</v>
+      </c>
+      <c r="I56" t="n">
+        <v>41547774</v>
+      </c>
+      <c r="J56" t="n">
+        <v>95057206</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-11961658</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="M56" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2907705600</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>605189.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>富春染织</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.9815</v>
+      </c>
+      <c r="F57" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>821036080</v>
+      </c>
+      <c r="H57" t="n">
+        <v>79922883.95999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>168397925.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>248320809.76</v>
+      </c>
+      <c r="K57" t="n">
+        <v>88475041.84</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="M57" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4252493661.15</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>688552.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>航天南湖</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7.3946</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="G58" t="n">
+        <v>944279300</v>
+      </c>
+      <c r="H58" t="n">
+        <v>195102719.69</v>
+      </c>
+      <c r="I58" t="n">
+        <v>298685188.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>493787907.99</v>
+      </c>
+      <c r="K58" t="n">
+        <v>103582468.61</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="M58" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="N58" t="n">
+        <v>11510274240</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>920157.BJ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>宇特光电</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>58</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-3.3333</v>
+      </c>
+      <c r="F59" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="G59" t="n">
+        <v>229939100</v>
+      </c>
+      <c r="H59" t="n">
+        <v>35823058.47</v>
+      </c>
+      <c r="I59" t="n">
+        <v>32139147.66</v>
+      </c>
+      <c r="J59" t="n">
+        <v>67962206.13</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-3683910.81</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="M59" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="N59" t="n">
+        <v>743297086</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>920201.BJ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>百瑞吉</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>13.3313</v>
+      </c>
+      <c r="F60" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="G60" t="n">
+        <v>139254900</v>
+      </c>
+      <c r="H60" t="n">
+        <v>31184709.12</v>
+      </c>
+      <c r="I60" t="n">
+        <v>24843012.97</v>
+      </c>
+      <c r="J60" t="n">
+        <v>56027722.09</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-6341696.15</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="M60" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="N60" t="n">
+        <v>282654549.05</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>920268.BJ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>百迈科</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.4942</v>
+      </c>
+      <c r="F61" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>103278100</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16396262.68</v>
+      </c>
+      <c r="I61" t="n">
+        <v>15560742.23</v>
+      </c>
+      <c r="J61" t="n">
+        <v>31957004.91</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-835520.45</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M61" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="N61" t="n">
+        <v>415094947.28</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>920627.BJ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>力王股份</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7.9695</v>
+      </c>
+      <c r="F62" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="G62" t="n">
+        <v>253985200</v>
+      </c>
+      <c r="H62" t="n">
+        <v>28257121.79</v>
+      </c>
+      <c r="I62" t="n">
+        <v>53780297.32</v>
+      </c>
+      <c r="J62" t="n">
+        <v>82037419.11</v>
+      </c>
+      <c r="K62" t="n">
+        <v>25523175.53</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="M62" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1044303825</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="E63" t="n">
+        <v>8.6988</v>
+      </c>
+      <c r="F63" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="G63" t="n">
+        <v>167186300</v>
+      </c>
+      <c r="H63" t="n">
+        <v>29592249.92</v>
+      </c>
+      <c r="I63" t="n">
+        <v>38173575.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>67765825.20999999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>8581325.369999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="M63" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="N63" t="n">
+        <v>610409860.98</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1071,7 +1072,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300411.SZ</t>
+          <t>301586.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1080,37 +1081,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.1</v>
+        <v>27.7</v>
       </c>
       <c r="D7" t="n">
-        <v>9.6</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>8.07</v>
+        <v>27.56</v>
       </c>
       <c r="F7" t="n">
-        <v>9.6</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>27.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>365179.66</v>
+        <v>73658.45</v>
       </c>
       <c r="K7" t="n">
-        <v>334505.7705</v>
+        <v>234615.41545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>301586.SZ</t>
+          <t>300411.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1119,31 +1120,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.7</v>
+        <v>8.1</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>9.6</v>
       </c>
       <c r="E8" t="n">
-        <v>27.56</v>
+        <v>8.07</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>9.6</v>
       </c>
       <c r="G8" t="n">
-        <v>27.5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="n">
         <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>73658.45</v>
+        <v>365179.66</v>
       </c>
       <c r="K8" t="n">
-        <v>234615.41545</v>
+        <v>334505.7705</v>
       </c>
     </row>
     <row r="9">
@@ -1727,4 +1728,3450 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.9567</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1396717639</v>
+      </c>
+      <c r="H2" t="n">
+        <v>112571712.72</v>
+      </c>
+      <c r="I2" t="n">
+        <v>130675443.68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>243247156.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18103730.96</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4976194444.5</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.9567</v>
+      </c>
+      <c r="F3" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3094035440</v>
+      </c>
+      <c r="H3" t="n">
+        <v>231378883.08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>214383656.54</v>
+      </c>
+      <c r="J3" t="n">
+        <v>445762539.62</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-16995226.54</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4976194444.5</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000668.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>荣丰控股</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.5717</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>270574089</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39289601</v>
+      </c>
+      <c r="I4" t="n">
+        <v>48121535</v>
+      </c>
+      <c r="J4" t="n">
+        <v>87411136</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8831934</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3036690285.2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000887.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中鼎股份</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.9938</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1117016917</v>
+      </c>
+      <c r="H5" t="n">
+        <v>114244630.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>266505810.98</v>
+      </c>
+      <c r="J5" t="n">
+        <v>380750441.42</v>
+      </c>
+      <c r="K5" t="n">
+        <v>152261180.54</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="M5" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23290647173.76</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000892.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>欢瑞世纪</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-8.2569</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1193509095</v>
+      </c>
+      <c r="H6" t="n">
+        <v>246585538.79</v>
+      </c>
+      <c r="I6" t="n">
+        <v>145084988.23</v>
+      </c>
+      <c r="J6" t="n">
+        <v>391670527.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-101500550.56</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3553994020</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000995.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>皇台酒业</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.8063</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>814274751</v>
+      </c>
+      <c r="H7" t="n">
+        <v>145168172.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>77298447.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>222466619.73</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-67869724.63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2533386240</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001231.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>农心科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.8598</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="G8" t="n">
+        <v>585430165</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59684292.28</v>
+      </c>
+      <c r="I8" t="n">
+        <v>57776030.84</v>
+      </c>
+      <c r="J8" t="n">
+        <v>117460323.12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1908261.44</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1048307572.95</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001318.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0177</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>827067754</v>
+      </c>
+      <c r="H9" t="n">
+        <v>111422547.67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>59779783.12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>171202330.79</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-51642764.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4316218200</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001696.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>宗申动力</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.979200000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1046956264</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43599646.86</v>
+      </c>
+      <c r="I10" t="n">
+        <v>198458358.67</v>
+      </c>
+      <c r="J10" t="n">
+        <v>242058005.53</v>
+      </c>
+      <c r="K10" t="n">
+        <v>154858711.81</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="M10" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14148319546.53</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002058.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2.9065</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="G11" t="n">
+        <v>552321686</v>
+      </c>
+      <c r="H11" t="n">
+        <v>48108927.64</v>
+      </c>
+      <c r="I11" t="n">
+        <v>34261006</v>
+      </c>
+      <c r="J11" t="n">
+        <v>82369933.64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-13847921.64</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3304582427.6</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002134.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天津普林</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-9.983599999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>910705867</v>
+      </c>
+      <c r="H12" t="n">
+        <v>199651172</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85902790</v>
+      </c>
+      <c r="J12" t="n">
+        <v>285553962</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-113748382</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-12.49</v>
+      </c>
+      <c r="M12" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5415627167.86</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.7138</v>
+      </c>
+      <c r="F13" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2123309579</v>
+      </c>
+      <c r="H13" t="n">
+        <v>188616709.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>166396507.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>355013217.05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-22220201.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4419437068.38</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002531.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天顺风能</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.9407</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1290600253</v>
+      </c>
+      <c r="H14" t="n">
+        <v>100682910.87</v>
+      </c>
+      <c r="I14" t="n">
+        <v>187591162.92</v>
+      </c>
+      <c r="J14" t="n">
+        <v>288274073.79</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86908252.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13240696318.59</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-9.993600000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1550919008</v>
+      </c>
+      <c r="H15" t="n">
+        <v>316339814.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>157057346</v>
+      </c>
+      <c r="J15" t="n">
+        <v>473397160.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-159282468.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-10.27</v>
+      </c>
+      <c r="M15" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15499248335.34</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-10.0035</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>753840446</v>
+      </c>
+      <c r="H16" t="n">
+        <v>81482623.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>102151996.96</v>
+      </c>
+      <c r="J16" t="n">
+        <v>183634620.26</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20669373.66</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M16" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6088001030</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-9.972</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="G17" t="n">
+        <v>892636675</v>
+      </c>
+      <c r="H17" t="n">
+        <v>99316369.72</v>
+      </c>
+      <c r="I17" t="n">
+        <v>59776833.85</v>
+      </c>
+      <c r="J17" t="n">
+        <v>159093203.57</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-39539535.87</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3228941147.88</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002815.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>崇达技术</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5539031681</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1362955446.12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1327804004.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2690759450.72</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-35151441.52</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M18" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="N18" t="n">
+        <v>18239429775.33</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002889.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.9923</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>237071570</v>
+      </c>
+      <c r="H19" t="n">
+        <v>30216904.06</v>
+      </c>
+      <c r="I19" t="n">
+        <v>68644536</v>
+      </c>
+      <c r="J19" t="n">
+        <v>98861440.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>38427631.94</v>
+      </c>
+      <c r="L19" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="M19" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3595881967.74</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>003029.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.005</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>785607306</v>
+      </c>
+      <c r="H20" t="n">
+        <v>174754611.88</v>
+      </c>
+      <c r="I20" t="n">
+        <v>59379752.63</v>
+      </c>
+      <c r="J20" t="n">
+        <v>234134364.51</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-115374859.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-14.69</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3861071005.62</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>003029.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.005</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1077726892</v>
+      </c>
+      <c r="H21" t="n">
+        <v>182170005.88</v>
+      </c>
+      <c r="I21" t="n">
+        <v>150291067.63</v>
+      </c>
+      <c r="J21" t="n">
+        <v>332461073.51</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-31878938.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="M21" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3861071005.62</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>300006.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19.9262</v>
+      </c>
+      <c r="F22" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3024020411</v>
+      </c>
+      <c r="H22" t="n">
+        <v>393872623.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>446605493.16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>840478116.83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>52732869.49</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10294253755.5</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>300045.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>华力创通</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20.0378</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G23" t="n">
+        <v>845572506</v>
+      </c>
+      <c r="H23" t="n">
+        <v>101367661.84</v>
+      </c>
+      <c r="I23" t="n">
+        <v>208165878.42</v>
+      </c>
+      <c r="J23" t="n">
+        <v>309533540.26</v>
+      </c>
+      <c r="K23" t="n">
+        <v>106798216.58</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="M23" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6648931660.2</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>300111.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>向日葵</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.625299999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2265317077</v>
+      </c>
+      <c r="H24" t="n">
+        <v>263854357.23</v>
+      </c>
+      <c r="I24" t="n">
+        <v>264068606.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>527922963.99</v>
+      </c>
+      <c r="K24" t="n">
+        <v>214249.53</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5187459177.42</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>300411.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>金盾股份</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>334505771</v>
+      </c>
+      <c r="H25" t="n">
+        <v>52634090</v>
+      </c>
+      <c r="I25" t="n">
+        <v>104700143</v>
+      </c>
+      <c r="J25" t="n">
+        <v>157334233</v>
+      </c>
+      <c r="K25" t="n">
+        <v>52066053</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="M25" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2967508800</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300581.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>晨曦航空</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20.0203</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>591620877</v>
+      </c>
+      <c r="H26" t="n">
+        <v>55070878</v>
+      </c>
+      <c r="I26" t="n">
+        <v>118183395.39</v>
+      </c>
+      <c r="J26" t="n">
+        <v>173254273.39</v>
+      </c>
+      <c r="K26" t="n">
+        <v>63112517.39</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="M26" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6496793738.26</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300681.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>英搏尔</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19.977</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="G27" t="n">
+        <v>593115163</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50524012.78</v>
+      </c>
+      <c r="I27" t="n">
+        <v>123240618.08</v>
+      </c>
+      <c r="J27" t="n">
+        <v>173764630.86</v>
+      </c>
+      <c r="K27" t="n">
+        <v>72716605.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M27" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4810224717</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>301002.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>崧盛股份</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="F28" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="G28" t="n">
+        <v>890156269</v>
+      </c>
+      <c r="H28" t="n">
+        <v>188421025.02</v>
+      </c>
+      <c r="I28" t="n">
+        <v>69294217.59</v>
+      </c>
+      <c r="J28" t="n">
+        <v>257715242.61</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-119126807.43</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-13.38</v>
+      </c>
+      <c r="M28" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2802429008.4</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.6293</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1263400369</v>
+      </c>
+      <c r="H29" t="n">
+        <v>132905357.98</v>
+      </c>
+      <c r="I29" t="n">
+        <v>104468570.89</v>
+      </c>
+      <c r="J29" t="n">
+        <v>237373928.87</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-28436787.09</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2912704522.2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6495335</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2213203.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1797442</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4010645.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-415761.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="N30" t="n">
+        <v>58640233.96</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301345.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>涛涛车业</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>145.25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-18.8275</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="G31" t="n">
+        <v>731329681</v>
+      </c>
+      <c r="H31" t="n">
+        <v>288018948.22</v>
+      </c>
+      <c r="I31" t="n">
+        <v>124193772.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>412212720.62</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-163825175.82</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5106550037.75</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-14.2377</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="G32" t="n">
+        <v>431763634</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46126920.28</v>
+      </c>
+      <c r="I32" t="n">
+        <v>31519041.56</v>
+      </c>
+      <c r="J32" t="n">
+        <v>77645961.84</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-14607878.72</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="M32" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1131164242.46</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-8.014799999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="G33" t="n">
+        <v>870147410</v>
+      </c>
+      <c r="H33" t="n">
+        <v>108221404.36</v>
+      </c>
+      <c r="I33" t="n">
+        <v>88145578.97</v>
+      </c>
+      <c r="J33" t="n">
+        <v>196366983.33</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-20075825.39</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="M33" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2169327925.87</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301586.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>佳力奇</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="G34" t="n">
+        <v>234615415</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40753363</v>
+      </c>
+      <c r="I34" t="n">
+        <v>76478432</v>
+      </c>
+      <c r="J34" t="n">
+        <v>117231795</v>
+      </c>
+      <c r="K34" t="n">
+        <v>35725069</v>
+      </c>
+      <c r="L34" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="M34" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1746065310</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.860799999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3496792838</v>
+      </c>
+      <c r="H35" t="n">
+        <v>383006644.84</v>
+      </c>
+      <c r="I35" t="n">
+        <v>452632473.93</v>
+      </c>
+      <c r="J35" t="n">
+        <v>835639118.77</v>
+      </c>
+      <c r="K35" t="n">
+        <v>69625829.09</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M35" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>9382870647.16</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.1437</v>
+      </c>
+      <c r="F36" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1113788464</v>
+      </c>
+      <c r="H36" t="n">
+        <v>62947288.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>60222938</v>
+      </c>
+      <c r="J36" t="n">
+        <v>123170226.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-2724350.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4164374927.25</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600319.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>亚星化学</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.0478</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G37" t="n">
+        <v>144373637</v>
+      </c>
+      <c r="H37" t="n">
+        <v>28465828.06</v>
+      </c>
+      <c r="I37" t="n">
+        <v>45761515.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>74227343.34999999</v>
+      </c>
+      <c r="K37" t="n">
+        <v>17295687.23</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="M37" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2675194749.6</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600613.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>神奇制药</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.1612</v>
+      </c>
+      <c r="F38" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1011319789</v>
+      </c>
+      <c r="H38" t="n">
+        <v>140357178.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>144061754</v>
+      </c>
+      <c r="J38" t="n">
+        <v>284418932.1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3704575.9</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M38" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3862841481.63</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600668.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>尖峰集团</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.0125</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="G39" t="n">
+        <v>804230377</v>
+      </c>
+      <c r="H39" t="n">
+        <v>102115460.64</v>
+      </c>
+      <c r="I39" t="n">
+        <v>121972292.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>224087753.24</v>
+      </c>
+      <c r="K39" t="n">
+        <v>19856831.96</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M39" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3629396221.26</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600671.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>天目药业</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-10.0177</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G40" t="n">
+        <v>191825397</v>
+      </c>
+      <c r="H40" t="n">
+        <v>51945437.12</v>
+      </c>
+      <c r="I40" t="n">
+        <v>46867532</v>
+      </c>
+      <c r="J40" t="n">
+        <v>98812969.12</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-5077905.12</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="M40" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2471941819.9</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600693.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-10.0273</v>
+      </c>
+      <c r="F41" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2040450989</v>
+      </c>
+      <c r="H41" t="n">
+        <v>212188947.59</v>
+      </c>
+      <c r="I41" t="n">
+        <v>144462677.9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>356651625.49</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-67726269.69</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="M41" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8576563958.34</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600699.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>均胜电子</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10.0271</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1369565299</v>
+      </c>
+      <c r="H42" t="n">
+        <v>185589597.74</v>
+      </c>
+      <c r="I42" t="n">
+        <v>225181623.75</v>
+      </c>
+      <c r="J42" t="n">
+        <v>410771221.49</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39592026.01</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M42" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="N42" t="n">
+        <v>28332112428.9</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-8.547700000000001</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1530107731</v>
+      </c>
+      <c r="H43" t="n">
+        <v>309758909</v>
+      </c>
+      <c r="I43" t="n">
+        <v>126702842.99</v>
+      </c>
+      <c r="J43" t="n">
+        <v>436461751.99</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-183056066.01</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="M43" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4237714937.7</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0649</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="G44" t="n">
+        <v>502953497</v>
+      </c>
+      <c r="H44" t="n">
+        <v>29148264.26</v>
+      </c>
+      <c r="I44" t="n">
+        <v>123154299.88</v>
+      </c>
+      <c r="J44" t="n">
+        <v>152302564.14</v>
+      </c>
+      <c r="K44" t="n">
+        <v>94006035.62</v>
+      </c>
+      <c r="L44" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="M44" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3106924152</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-10.0284</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="G45" t="n">
+        <v>254262782</v>
+      </c>
+      <c r="H45" t="n">
+        <v>38716785.36</v>
+      </c>
+      <c r="I45" t="n">
+        <v>15680129.7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>54396915.06</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-23036655.66</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="M45" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1939085610</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-6.1076</v>
+      </c>
+      <c r="F46" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1014374653</v>
+      </c>
+      <c r="H46" t="n">
+        <v>114384727.91</v>
+      </c>
+      <c r="I46" t="n">
+        <v>51126267.28</v>
+      </c>
+      <c r="J46" t="n">
+        <v>165510995.19</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-63258460.63</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="M46" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4090230835.34</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>603067.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>振华股份</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>38</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-8.168200000000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2183368520</v>
+      </c>
+      <c r="H47" t="n">
+        <v>268569103.79</v>
+      </c>
+      <c r="I47" t="n">
+        <v>418597563.18</v>
+      </c>
+      <c r="J47" t="n">
+        <v>687166666.97</v>
+      </c>
+      <c r="K47" t="n">
+        <v>150028459.39</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M47" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="N47" t="n">
+        <v>28709965352</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>603168.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>莎普爱思</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.0529</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G48" t="n">
+        <v>143556503</v>
+      </c>
+      <c r="H48" t="n">
+        <v>41575289.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>38093035</v>
+      </c>
+      <c r="J48" t="n">
+        <v>79668324.40000001</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-3482254.4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="M48" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2324487391.2</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>603258.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>电魂网络</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-9.9941</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="G49" t="n">
+        <v>449120617</v>
+      </c>
+      <c r="H49" t="n">
+        <v>49848552.45</v>
+      </c>
+      <c r="I49" t="n">
+        <v>37743752</v>
+      </c>
+      <c r="J49" t="n">
+        <v>87592304.45</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-12104800.45</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="M49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3651494625.5</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>603259.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-6.6019</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G50" t="n">
+        <v>12339620040</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2256398713.96</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3697313032.83</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5953711746.79</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1440914318.87</v>
+      </c>
+      <c r="L50" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="M50" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="N50" t="n">
+        <v>356894339497.8</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>603386.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>骏亚科技</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-7.8519</v>
+      </c>
+      <c r="F51" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G51" t="n">
+        <v>931290875</v>
+      </c>
+      <c r="H51" t="n">
+        <v>178415593</v>
+      </c>
+      <c r="I51" t="n">
+        <v>173948428</v>
+      </c>
+      <c r="J51" t="n">
+        <v>352364021</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-4467165</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M51" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="N51" t="n">
+        <v>6089178969.6</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603668.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>天马科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0583</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="G52" t="n">
+        <v>391146757</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50819113.34</v>
+      </c>
+      <c r="I52" t="n">
+        <v>72854811.95999999</v>
+      </c>
+      <c r="J52" t="n">
+        <v>123673925.3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>22035698.62</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="M52" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3818765326.6</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603893.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>瑞芯微</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>171.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-9.9947</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3973576356</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1252028330.83</v>
+      </c>
+      <c r="I53" t="n">
+        <v>665380087.37</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1917408418.2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-586648243.46</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="M53" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>72396869737.5</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603968.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>醋化股份</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-6.1181</v>
+      </c>
+      <c r="F54" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="G54" t="n">
+        <v>518829620</v>
+      </c>
+      <c r="H54" t="n">
+        <v>52094007</v>
+      </c>
+      <c r="I54" t="n">
+        <v>39294083</v>
+      </c>
+      <c r="J54" t="n">
+        <v>91388090</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-12799924</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="M54" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2729808000</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603999.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.973800000000001</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G55" t="n">
+        <v>287865248</v>
+      </c>
+      <c r="H55" t="n">
+        <v>35411089</v>
+      </c>
+      <c r="I55" t="n">
+        <v>110955844.02</v>
+      </c>
+      <c r="J55" t="n">
+        <v>146366933.02</v>
+      </c>
+      <c r="K55" t="n">
+        <v>75544755.02</v>
+      </c>
+      <c r="L55" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4826880000</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>688592.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>司南导航</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="E56" t="n">
+        <v>19.9808</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="G56" t="n">
+        <v>128778800</v>
+      </c>
+      <c r="H56" t="n">
+        <v>17209185.05</v>
+      </c>
+      <c r="I56" t="n">
+        <v>34988971.72</v>
+      </c>
+      <c r="J56" t="n">
+        <v>52198156.77</v>
+      </c>
+      <c r="K56" t="n">
+        <v>17779786.67</v>
+      </c>
+      <c r="L56" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="M56" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1382280590.16</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>920006.BJ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>晟楠科技</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="E57" t="n">
+        <v>29.9769</v>
+      </c>
+      <c r="F57" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="G57" t="n">
+        <v>328030800</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20476813.65</v>
+      </c>
+      <c r="I57" t="n">
+        <v>41102260.32</v>
+      </c>
+      <c r="J57" t="n">
+        <v>61579073.97</v>
+      </c>
+      <c r="K57" t="n">
+        <v>20625446.67</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="M57" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1073523135.52</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>920157.BJ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>宇特光电</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="F58" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>273209700</v>
+      </c>
+      <c r="H58" t="n">
+        <v>35742530.73</v>
+      </c>
+      <c r="I58" t="n">
+        <v>35257074.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>70999605.03</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-485456.43</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="N58" t="n">
+        <v>747269880.77</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>920162.BJ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>莫森泰克</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-29.9723</v>
+      </c>
+      <c r="F59" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="G59" t="n">
+        <v>228647300</v>
+      </c>
+      <c r="H59" t="n">
+        <v>19427024.91</v>
+      </c>
+      <c r="I59" t="n">
+        <v>15700612.04</v>
+      </c>
+      <c r="J59" t="n">
+        <v>35127636.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-3726412.87</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="M59" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="N59" t="n">
+        <v>348534000</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>920201.BJ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>百瑞吉</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-7.6716</v>
+      </c>
+      <c r="F60" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="G60" t="n">
+        <v>93535100</v>
+      </c>
+      <c r="H60" t="n">
+        <v>21305786.67</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10958138.79</v>
+      </c>
+      <c r="J60" t="n">
+        <v>32263925.46</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-10347647.88</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-11.06</v>
+      </c>
+      <c r="M60" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="N60" t="n">
+        <v>260970418.1</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>920690.BJ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>捷众科技</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="E61" t="n">
+        <v>30</v>
+      </c>
+      <c r="F61" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="G61" t="n">
+        <v>158998600</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20924745.17</v>
+      </c>
+      <c r="I61" t="n">
+        <v>25786813.62</v>
+      </c>
+      <c r="J61" t="n">
+        <v>46711558.79</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4862068.45</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1077994188.96</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>920779.BJ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>武汉蓝电</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-2.427</v>
+      </c>
+      <c r="F62" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="G62" t="n">
+        <v>147329300</v>
+      </c>
+      <c r="H62" t="n">
+        <v>33566092.96</v>
+      </c>
+      <c r="I62" t="n">
+        <v>17849577.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>51415670.46</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-15716515.46</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="M62" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="N62" t="n">
+        <v>595595059.5</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4043 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2074070171</v>
+      </c>
+      <c r="H2" t="n">
+        <v>126698638.16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>166959274.69</v>
+      </c>
+      <c r="J2" t="n">
+        <v>293657912.85</v>
+      </c>
+      <c r="K2" t="n">
+        <v>40260636.53</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5079385455</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000576.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>甘化科工</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.0342</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>694298461</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60922555.45</v>
+      </c>
+      <c r="I3" t="n">
+        <v>135289203.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>196211759.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>74366648.34999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="M3" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4186317268.65</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.1774</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3538659636</v>
+      </c>
+      <c r="H4" t="n">
+        <v>641806938.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>668745124.66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1310552062.68</v>
+      </c>
+      <c r="K4" t="n">
+        <v>26938186.64</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14700773846.57</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000949.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>新乡化纤</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-9.9533</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>445659200</v>
+      </c>
+      <c r="H5" t="n">
+        <v>99106326.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>62310194.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>161416521.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-36796131.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9591143962.92</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>983582111</v>
+      </c>
+      <c r="H6" t="n">
+        <v>154512773.36</v>
+      </c>
+      <c r="I6" t="n">
+        <v>91885801</v>
+      </c>
+      <c r="J6" t="n">
+        <v>246398574.36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-62626972.36</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7501244832.9</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000995.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>皇台酒业</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.381</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="G7" t="n">
+        <v>821833903</v>
+      </c>
+      <c r="H7" t="n">
+        <v>93950343.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>68930803.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>162881146.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-25019539.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2473067520</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001216.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G8" t="n">
+        <v>997818283</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82002494</v>
+      </c>
+      <c r="I8" t="n">
+        <v>133812501.37</v>
+      </c>
+      <c r="J8" t="n">
+        <v>215814995.37</v>
+      </c>
+      <c r="K8" t="n">
+        <v>51810007.37</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6000587997.69</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001318.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.0196</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>685852054</v>
+      </c>
+      <c r="H9" t="n">
+        <v>74239060.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>51454154.28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>125693214.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-22784905.92</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3883748400</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002085.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>万丰奥威</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.9899</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1111435155</v>
+      </c>
+      <c r="H10" t="n">
+        <v>205491992</v>
+      </c>
+      <c r="I10" t="n">
+        <v>164933995.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>370425987.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-40557996.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23143942968</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002085.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>万丰奥威</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9899</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1752122172</v>
+      </c>
+      <c r="H11" t="n">
+        <v>237141347.22</v>
+      </c>
+      <c r="I11" t="n">
+        <v>364141049.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>601282396.54</v>
+      </c>
+      <c r="K11" t="n">
+        <v>126999702.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23143942968</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002134.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天津普林</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8.9457</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1205967397</v>
+      </c>
+      <c r="H12" t="n">
+        <v>107587408.54</v>
+      </c>
+      <c r="I12" t="n">
+        <v>212070413.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>319657822.44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>104483005.36</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5900092218.02</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0375</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="G13" t="n">
+        <v>715675583</v>
+      </c>
+      <c r="H13" t="n">
+        <v>86675050.91</v>
+      </c>
+      <c r="I13" t="n">
+        <v>171673115.81</v>
+      </c>
+      <c r="J13" t="n">
+        <v>258348166.72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84998064.90000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M13" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7047896850.67</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002242.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.059</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2865615482</v>
+      </c>
+      <c r="H14" t="n">
+        <v>195193062.22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>294594491.59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>489787553.81</v>
+      </c>
+      <c r="K14" t="n">
+        <v>99401429.37</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14237399531.25</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.9678</v>
+      </c>
+      <c r="F15" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2100884692</v>
+      </c>
+      <c r="H15" t="n">
+        <v>155508032.59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>371266984.54</v>
+      </c>
+      <c r="J15" t="n">
+        <v>526775017.13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>215758951.95</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4859959734.36</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.9678</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4905862456</v>
+      </c>
+      <c r="H16" t="n">
+        <v>298515874.29</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481349022.12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>779864896.41</v>
+      </c>
+      <c r="K16" t="n">
+        <v>182833147.83</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4859959734.36</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002626.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>金达威</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1203357156</v>
+      </c>
+      <c r="H17" t="n">
+        <v>247494655.39</v>
+      </c>
+      <c r="I17" t="n">
+        <v>259613939.22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>507108594.61</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12119283.83</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11209251098.36</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-9.988300000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>528373652</v>
+      </c>
+      <c r="H18" t="n">
+        <v>72492696.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>77959561.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>150452257.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5466865.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5479910760</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-10.0414</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="G19" t="n">
+        <v>845883155</v>
+      </c>
+      <c r="H19" t="n">
+        <v>60063078.38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>67199540.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>127262618.68</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7136461.92</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2904709997.42</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002724.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>海洋王</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.0654</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>409184062</v>
+      </c>
+      <c r="H20" t="n">
+        <v>38694459.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>133202040</v>
+      </c>
+      <c r="J20" t="n">
+        <v>171896499.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>94507580.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4769747193.38</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002767.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>先锋电子</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-6.7073</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>286147780</v>
+      </c>
+      <c r="H21" t="n">
+        <v>73384707.51000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>54366413</v>
+      </c>
+      <c r="J21" t="n">
+        <v>127751120.51</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-19018294.51</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="M21" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2192677548.93</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002889.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.993</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="G22" t="n">
+        <v>776661934</v>
+      </c>
+      <c r="H22" t="n">
+        <v>76736326.63</v>
+      </c>
+      <c r="I22" t="n">
+        <v>80446099.55</v>
+      </c>
+      <c r="J22" t="n">
+        <v>157182426.18</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3709772.92</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3955218879.96</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>123235.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>亿田转债</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>182.786</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.0538</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>2515190691</v>
+      </c>
+      <c r="H23" t="n">
+        <v>755737628.37</v>
+      </c>
+      <c r="I23" t="n">
+        <v>763383616.22</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1519121244.59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7645987.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>123286.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>国科转债</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>143</v>
+      </c>
+      <c r="E24" t="n">
+        <v>43</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>107824288</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37854128</v>
+      </c>
+      <c r="I24" t="n">
+        <v>68653728</v>
+      </c>
+      <c r="J24" t="n">
+        <v>106507856</v>
+      </c>
+      <c r="K24" t="n">
+        <v>30799600</v>
+      </c>
+      <c r="L24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="M24" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>123288.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>隆新转债</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>130</v>
+      </c>
+      <c r="E25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>82658940</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14802060</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29443700</v>
+      </c>
+      <c r="J25" t="n">
+        <v>44245760</v>
+      </c>
+      <c r="K25" t="n">
+        <v>14641640</v>
+      </c>
+      <c r="L25" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="M25" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>300411.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>金盾股份</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="F26" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1307205246</v>
+      </c>
+      <c r="H26" t="n">
+        <v>168823575.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>171982496.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>340806072</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3158920.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M26" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3394088190</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300798.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>锦鸡股份</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19.9478</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>786021719</v>
+      </c>
+      <c r="H27" t="n">
+        <v>94264198.20999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>168185024.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>262449223.17</v>
+      </c>
+      <c r="K27" t="n">
+        <v>73920826.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3732472991.2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300852.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>四会富仕</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19.9938</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1954940001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>297100840.69</v>
+      </c>
+      <c r="I28" t="n">
+        <v>306617637.72</v>
+      </c>
+      <c r="J28" t="n">
+        <v>603718478.41</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9516797.029999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M28" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11922338568.34</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-6.3361</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1077681054</v>
+      </c>
+      <c r="H29" t="n">
+        <v>108384997.68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>135542746.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>243927743.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>27157748.62</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M29" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2728152996</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.5974</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6950213</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1791991.85</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2351303</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4143294.85</v>
+      </c>
+      <c r="K30" t="n">
+        <v>559311.15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="N30" t="n">
+        <v>60163356.92</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>301230.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>泓博医药</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-6.8374</v>
+      </c>
+      <c r="F31" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1650774915</v>
+      </c>
+      <c r="H31" t="n">
+        <v>357976202.96</v>
+      </c>
+      <c r="I31" t="n">
+        <v>310039417</v>
+      </c>
+      <c r="J31" t="n">
+        <v>668015619.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-47936785.96</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5565978829.8</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日振幅值达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301313.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>39</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20</v>
+      </c>
+      <c r="F32" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="G32" t="n">
+        <v>866904607</v>
+      </c>
+      <c r="H32" t="n">
+        <v>99484313.68000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>159638992.64</v>
+      </c>
+      <c r="J32" t="n">
+        <v>259123306.32</v>
+      </c>
+      <c r="K32" t="n">
+        <v>60154678.96</v>
+      </c>
+      <c r="L32" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M32" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3069749085</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301513.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>尚水智能</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.9291</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="G33" t="n">
+        <v>556603278</v>
+      </c>
+      <c r="H33" t="n">
+        <v>36219642.87</v>
+      </c>
+      <c r="I33" t="n">
+        <v>78702733.66</v>
+      </c>
+      <c r="J33" t="n">
+        <v>114922376.53</v>
+      </c>
+      <c r="K33" t="n">
+        <v>42483090.79</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M33" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1275637500</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301591.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>肯特股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19.9949</v>
+      </c>
+      <c r="F34" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="G34" t="n">
+        <v>658530506</v>
+      </c>
+      <c r="H34" t="n">
+        <v>54089077.03</v>
+      </c>
+      <c r="I34" t="n">
+        <v>140642431.59</v>
+      </c>
+      <c r="J34" t="n">
+        <v>194731508.62</v>
+      </c>
+      <c r="K34" t="n">
+        <v>86553354.56</v>
+      </c>
+      <c r="L34" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2121659687.56</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301666.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>大普微</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="E35" t="n">
+        <v>19.9993</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2313276771</v>
+      </c>
+      <c r="H35" t="n">
+        <v>252487358.16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>451538606.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>704025964.45</v>
+      </c>
+      <c r="K35" t="n">
+        <v>199051248.13</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="N35" t="n">
+        <v>11464114979.59</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-9.9863</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2943598217</v>
+      </c>
+      <c r="H36" t="n">
+        <v>427332311.04</v>
+      </c>
+      <c r="I36" t="n">
+        <v>255571938.89</v>
+      </c>
+      <c r="J36" t="n">
+        <v>682904249.9299999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-171760372.15</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8445867148.88</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>600148.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>长春一东</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10.0123</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G37" t="n">
+        <v>103475786</v>
+      </c>
+      <c r="H37" t="n">
+        <v>21146656.94</v>
+      </c>
+      <c r="I37" t="n">
+        <v>37487483.18</v>
+      </c>
+      <c r="J37" t="n">
+        <v>58634140.12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16340826.24</v>
+      </c>
+      <c r="L37" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="M37" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2534559619.5</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>600167.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>联美控股</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-10.052</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G38" t="n">
+        <v>76731191</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12857628</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11271369</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24128997</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1586259</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="M38" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11744142002.97</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>600178.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>东安动力</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10.0488</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G39" t="n">
+        <v>176472126</v>
+      </c>
+      <c r="H39" t="n">
+        <v>26159287</v>
+      </c>
+      <c r="I39" t="n">
+        <v>23098220</v>
+      </c>
+      <c r="J39" t="n">
+        <v>49257507</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-3061067</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="M39" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5261851096.08</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>600178.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>东安动力</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.0488</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G40" t="n">
+        <v>408534903</v>
+      </c>
+      <c r="H40" t="n">
+        <v>39118531</v>
+      </c>
+      <c r="I40" t="n">
+        <v>67915013.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>107033544.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>28796482.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="M40" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5261851096.08</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-9.964700000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1096433645</v>
+      </c>
+      <c r="H41" t="n">
+        <v>55104567.78</v>
+      </c>
+      <c r="I41" t="n">
+        <v>71117895.34</v>
+      </c>
+      <c r="J41" t="n">
+        <v>126222463.12</v>
+      </c>
+      <c r="K41" t="n">
+        <v>16013327.56</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3749408945.1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600267.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>海正药业</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10.0365</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G42" t="n">
+        <v>118360253</v>
+      </c>
+      <c r="H42" t="n">
+        <v>21100176</v>
+      </c>
+      <c r="I42" t="n">
+        <v>83609568</v>
+      </c>
+      <c r="J42" t="n">
+        <v>104709744</v>
+      </c>
+      <c r="K42" t="n">
+        <v>62509392</v>
+      </c>
+      <c r="L42" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="N42" t="n">
+        <v>14234081477.76</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600537.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>*ST亿晶</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-10.2041</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G43" t="n">
+        <v>120770652</v>
+      </c>
+      <c r="H43" t="n">
+        <v>22520588</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8425121.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30945709.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-14095466.4</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-11.67</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2083338431.68</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600593.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>大连圣亚</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-10.0063</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G44" t="n">
+        <v>538404443</v>
+      </c>
+      <c r="H44" t="n">
+        <v>63033124</v>
+      </c>
+      <c r="I44" t="n">
+        <v>60908576</v>
+      </c>
+      <c r="J44" t="n">
+        <v>123941700</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-2124548</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M44" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5560296000</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600693.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-10.0304</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1160824880</v>
+      </c>
+      <c r="H45" t="n">
+        <v>85300091.78</v>
+      </c>
+      <c r="I45" t="n">
+        <v>98242298.15000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>183542389.93</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12942206.37</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M45" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7716300704.16</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600693.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-10.0304</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3268543909</v>
+      </c>
+      <c r="H46" t="n">
+        <v>277665792.19</v>
+      </c>
+      <c r="I46" t="n">
+        <v>236432858.56</v>
+      </c>
+      <c r="J46" t="n">
+        <v>514098650.75</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-41232933.63</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M46" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="N46" t="n">
+        <v>7716300704.16</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600721.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>百花医药</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-3.539</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1066070363</v>
+      </c>
+      <c r="H47" t="n">
+        <v>140297084</v>
+      </c>
+      <c r="I47" t="n">
+        <v>133768300</v>
+      </c>
+      <c r="J47" t="n">
+        <v>274065384</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-6528784</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M47" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4087741360.05</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600802.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.5074</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="G48" t="n">
+        <v>777080663</v>
+      </c>
+      <c r="H48" t="n">
+        <v>128961137.23</v>
+      </c>
+      <c r="I48" t="n">
+        <v>116752571.49</v>
+      </c>
+      <c r="J48" t="n">
+        <v>245713708.72</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-12208565.74</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="M48" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3184826380</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600825.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.7704</v>
+      </c>
+      <c r="F49" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3996045888</v>
+      </c>
+      <c r="H49" t="n">
+        <v>247238307.62</v>
+      </c>
+      <c r="I49" t="n">
+        <v>201991394.06</v>
+      </c>
+      <c r="J49" t="n">
+        <v>449229701.68</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-45246913.56</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="N49" t="n">
+        <v>16279352703</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600847.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-9.9605</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="G50" t="n">
+        <v>791635629</v>
+      </c>
+      <c r="H50" t="n">
+        <v>104850844.36</v>
+      </c>
+      <c r="I50" t="n">
+        <v>73127700.66</v>
+      </c>
+      <c r="J50" t="n">
+        <v>177978545.02</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-31723143.7</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1745943486</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600860.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>京城股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9.987399999999999</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G51" t="n">
+        <v>219424837</v>
+      </c>
+      <c r="H51" t="n">
+        <v>28937466</v>
+      </c>
+      <c r="I51" t="n">
+        <v>52954701</v>
+      </c>
+      <c r="J51" t="n">
+        <v>81892167</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24017235</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="M51" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3863154855.6</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>601778.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>晶科科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.1538</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G52" t="n">
+        <v>692221445</v>
+      </c>
+      <c r="H52" t="n">
+        <v>88409841</v>
+      </c>
+      <c r="I52" t="n">
+        <v>127935065.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>216344906.3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>39525224.3</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M52" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="N52" t="n">
+        <v>13328512094.18</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603001.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>奥康国际</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7.3333</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G53" t="n">
+        <v>203794949</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50752557</v>
+      </c>
+      <c r="I53" t="n">
+        <v>56383195</v>
+      </c>
+      <c r="J53" t="n">
+        <v>107135752</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5630638</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M53" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4519044600</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603067.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>振华股份</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-9.131600000000001</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4657309661</v>
+      </c>
+      <c r="H54" t="n">
+        <v>570020925.96</v>
+      </c>
+      <c r="I54" t="n">
+        <v>671171441.59</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1241192367.55</v>
+      </c>
+      <c r="K54" t="n">
+        <v>101150515.63</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M54" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="N54" t="n">
+        <v>26088292200.12</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603188.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>亚邦股份</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10.099</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="G55" t="n">
+        <v>505378552</v>
+      </c>
+      <c r="H55" t="n">
+        <v>63939294</v>
+      </c>
+      <c r="I55" t="n">
+        <v>107524408.12</v>
+      </c>
+      <c r="J55" t="n">
+        <v>171463702.12</v>
+      </c>
+      <c r="K55" t="n">
+        <v>43585114.12</v>
+      </c>
+      <c r="L55" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M55" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3170145200</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603197.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>保隆科技</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10.0034</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>236013274</v>
+      </c>
+      <c r="H56" t="n">
+        <v>31694470.36</v>
+      </c>
+      <c r="I56" t="n">
+        <v>133895177.92</v>
+      </c>
+      <c r="J56" t="n">
+        <v>165589648.28</v>
+      </c>
+      <c r="K56" t="n">
+        <v>102200707.56</v>
+      </c>
+      <c r="L56" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="N56" t="n">
+        <v>6826548265.91</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603278.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>大业股份</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.9899</v>
+      </c>
+      <c r="F57" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G57" t="n">
+        <v>646487569</v>
+      </c>
+      <c r="H57" t="n">
+        <v>90598540.65000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>90902715</v>
+      </c>
+      <c r="J57" t="n">
+        <v>181501255.65</v>
+      </c>
+      <c r="K57" t="n">
+        <v>304174.35</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M57" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3725177372.8</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603286.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>日盈电子</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0129</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="G58" t="n">
+        <v>197904924</v>
+      </c>
+      <c r="H58" t="n">
+        <v>29052250.99</v>
+      </c>
+      <c r="I58" t="n">
+        <v>71426590</v>
+      </c>
+      <c r="J58" t="n">
+        <v>100478840.99</v>
+      </c>
+      <c r="K58" t="n">
+        <v>42374339.01</v>
+      </c>
+      <c r="L58" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4995631605.54</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603330.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>天洋新材</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.035</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="G59" t="n">
+        <v>270782543</v>
+      </c>
+      <c r="H59" t="n">
+        <v>44685528</v>
+      </c>
+      <c r="I59" t="n">
+        <v>92334252.84999999</v>
+      </c>
+      <c r="J59" t="n">
+        <v>137019780.85</v>
+      </c>
+      <c r="K59" t="n">
+        <v>47648724.85</v>
+      </c>
+      <c r="L59" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M59" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3835305758.9</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603348.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>文灿股份</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9.993499999999999</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G60" t="n">
+        <v>274422734</v>
+      </c>
+      <c r="H60" t="n">
+        <v>45933726.91</v>
+      </c>
+      <c r="I60" t="n">
+        <v>54624226.14</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100557953.05</v>
+      </c>
+      <c r="K60" t="n">
+        <v>8690499.23</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M60" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5295795913.28</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603466.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>风语筑</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4.9842</v>
+      </c>
+      <c r="F61" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1510616252</v>
+      </c>
+      <c r="H61" t="n">
+        <v>215257716.99</v>
+      </c>
+      <c r="I61" t="n">
+        <v>250388084.53</v>
+      </c>
+      <c r="J61" t="n">
+        <v>465645801.52</v>
+      </c>
+      <c r="K61" t="n">
+        <v>35130367.54</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M61" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="N61" t="n">
+        <v>7893420162.28</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>603608.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>天创股份</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="E62" t="n">
+        <v>6.2673</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G62" t="n">
+        <v>280767733</v>
+      </c>
+      <c r="H62" t="n">
+        <v>44468410.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>83182776.88</v>
+      </c>
+      <c r="J62" t="n">
+        <v>127651187.48</v>
+      </c>
+      <c r="K62" t="n">
+        <v>38714366.28</v>
+      </c>
+      <c r="L62" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="M62" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="N62" t="n">
+        <v>8143568745.44</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>603999.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-10.0239</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="G63" t="n">
+        <v>430951144</v>
+      </c>
+      <c r="H63" t="n">
+        <v>95106130</v>
+      </c>
+      <c r="I63" t="n">
+        <v>28496461</v>
+      </c>
+      <c r="J63" t="n">
+        <v>123602591</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-66609669</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-15.46</v>
+      </c>
+      <c r="M63" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4343040000</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>605577.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-9.9939</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2311044751</v>
+      </c>
+      <c r="H64" t="n">
+        <v>148499119.08</v>
+      </c>
+      <c r="I64" t="n">
+        <v>117431514.66</v>
+      </c>
+      <c r="J64" t="n">
+        <v>265930633.74</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-31067604.42</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="N64" t="n">
+        <v>6604444452.7</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E65" t="n">
+        <v>19.7531</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6752200</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1534894.05</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1892551.99</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3427446.04</v>
+      </c>
+      <c r="K65" t="n">
+        <v>357657.94</v>
+      </c>
+      <c r="L65" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="N65" t="n">
+        <v>196586666.99</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>688507.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>索辰科技</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>19.9967</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="G66" t="n">
+        <v>964286300</v>
+      </c>
+      <c r="H66" t="n">
+        <v>142008103.75</v>
+      </c>
+      <c r="I66" t="n">
+        <v>182313303.06</v>
+      </c>
+      <c r="J66" t="n">
+        <v>324321406.81</v>
+      </c>
+      <c r="K66" t="n">
+        <v>40305199.31</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M66" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="N66" t="n">
+        <v>7055480109</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>688836.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>宇树科技</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>495.92</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.146</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3089026400</v>
+      </c>
+      <c r="H67" t="n">
+        <v>260443570.18</v>
+      </c>
+      <c r="I67" t="n">
+        <v>442611906.48</v>
+      </c>
+      <c r="J67" t="n">
+        <v>703055476.66</v>
+      </c>
+      <c r="K67" t="n">
+        <v>182168336.3</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M67" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14921102102.4</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>920006.BJ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>晟楠科技</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-9.617100000000001</v>
+      </c>
+      <c r="F68" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="G68" t="n">
+        <v>246866500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>37921411.53</v>
+      </c>
+      <c r="I68" t="n">
+        <v>25105783.77</v>
+      </c>
+      <c r="J68" t="n">
+        <v>63027195.3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-12815627.76</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="M68" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="N68" t="n">
+        <v>970281373.6</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>920157.BJ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>宇特光电</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17.4756</v>
+      </c>
+      <c r="F69" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>424038300</v>
+      </c>
+      <c r="H69" t="n">
+        <v>64821431.99</v>
+      </c>
+      <c r="I69" t="n">
+        <v>43281662.01</v>
+      </c>
+      <c r="J69" t="n">
+        <v>108103094</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-21539769.98</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="N69" t="n">
+        <v>877859489.5</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>920162.BJ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>莫森泰克</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-14.5742</v>
+      </c>
+      <c r="F70" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="G70" t="n">
+        <v>126378100</v>
+      </c>
+      <c r="H70" t="n">
+        <v>9983377.32</v>
+      </c>
+      <c r="I70" t="n">
+        <v>11710383.08</v>
+      </c>
+      <c r="J70" t="n">
+        <v>21693760.4</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1727005.76</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M70" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="N70" t="n">
+        <v>297738000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>920196.BJ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>南方乳业</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-25.8422</v>
+      </c>
+      <c r="F71" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>267539300</v>
+      </c>
+      <c r="H71" t="n">
+        <v>40706198.17</v>
+      </c>
+      <c r="I71" t="n">
+        <v>31152770.4</v>
+      </c>
+      <c r="J71" t="n">
+        <v>71858968.56999999</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-9553427.77</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="M71" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="N71" t="n">
+        <v>412053709.9</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>920690.BJ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>捷众科技</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="E72" t="n">
+        <v>7.5364</v>
+      </c>
+      <c r="F72" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="G72" t="n">
+        <v>335351100</v>
+      </c>
+      <c r="H72" t="n">
+        <v>35592899.83</v>
+      </c>
+      <c r="I72" t="n">
+        <v>29399339.82</v>
+      </c>
+      <c r="J72" t="n">
+        <v>64992239.65</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-6193560.01</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1159235954.76</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>920690.BJ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>捷众科技</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7.5364</v>
+      </c>
+      <c r="F73" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="G73" t="n">
+        <v>494349700</v>
+      </c>
+      <c r="H73" t="n">
+        <v>46656963.04</v>
+      </c>
+      <c r="I73" t="n">
+        <v>41923735.13</v>
+      </c>
+      <c r="J73" t="n">
+        <v>88580698.17</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-4733227.91</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="M73" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1159235954.76</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1727,4 +1728,4597 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000056.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*ST皇庭</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9.9138</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>139005900</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17995671</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14717186</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32712857</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-3278485</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2017716961.08</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.7436</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2042838632</v>
+      </c>
+      <c r="H3" t="n">
+        <v>219423833.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>177743446.57</v>
+      </c>
+      <c r="J3" t="n">
+        <v>397167280.33</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-41680387.19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5306258643.25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000530.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.7436</v>
+      </c>
+      <c r="F4" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2042838632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>219423833.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>177743446.57</v>
+      </c>
+      <c r="J4" t="n">
+        <v>397167280.33</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-41680387.19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5306258643.25</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.6423</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4848540045</v>
+      </c>
+      <c r="H5" t="n">
+        <v>781525964.22</v>
+      </c>
+      <c r="I5" t="n">
+        <v>685221310.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1466747274.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-96304653.48999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="M5" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15236212796.87</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000993.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10.0122</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G6" t="n">
+        <v>276225032</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54726675.73</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35652074</v>
+      </c>
+      <c r="J6" t="n">
+        <v>90378749.73</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-19074601.73</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6750204446.7</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>001225.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>和泰机电</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-7.0856</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>506943550</v>
+      </c>
+      <c r="H7" t="n">
+        <v>56310140.98</v>
+      </c>
+      <c r="I7" t="n">
+        <v>29113122.27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>85423263.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-27197018.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2608142619.6</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001318.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>阳光乳业</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-2.6201</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2201297607</v>
+      </c>
+      <c r="H8" t="n">
+        <v>167526835.97</v>
+      </c>
+      <c r="I8" t="n">
+        <v>164294288.03</v>
+      </c>
+      <c r="J8" t="n">
+        <v>331821124</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-3232547.94</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3781990800</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001323.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>慕思股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.995100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G9" t="n">
+        <v>193888732</v>
+      </c>
+      <c r="H9" t="n">
+        <v>51697715.46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>52390380.99</v>
+      </c>
+      <c r="J9" t="n">
+        <v>104088096.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>692665.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6919043906.97</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002028.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>思源电气</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>112.59</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2404685136</v>
+      </c>
+      <c r="H10" t="n">
+        <v>958441140.77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>588752146.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1547193287.47</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-369688994.07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-15.37</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="N10" t="n">
+        <v>68767175376.99001</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0068</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="G11" t="n">
+        <v>996590616</v>
+      </c>
+      <c r="H11" t="n">
+        <v>164072209.24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>279281440.47</v>
+      </c>
+      <c r="J11" t="n">
+        <v>443353649.71</v>
+      </c>
+      <c r="K11" t="n">
+        <v>115209231.23</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="M11" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7753166310.88</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002164.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>宁波东力</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0068</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1712266199</v>
+      </c>
+      <c r="H12" t="n">
+        <v>215960284.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>352044104.55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>568004388.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>136083820.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7753166310.88</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002242.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0054</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2391220325</v>
+      </c>
+      <c r="H13" t="n">
+        <v>228936152.62</v>
+      </c>
+      <c r="I13" t="n">
+        <v>333929265.81</v>
+      </c>
+      <c r="J13" t="n">
+        <v>562865418.4299999</v>
+      </c>
+      <c r="K13" t="n">
+        <v>104993113.19</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15661901250</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002245.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>蔚蓝锂芯</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1848805361</v>
+      </c>
+      <c r="H14" t="n">
+        <v>457849689.91</v>
+      </c>
+      <c r="I14" t="n">
+        <v>256349098.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>714198788.64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-201500591.18</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>38.63</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20709100758.06</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002343.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.0975</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1738155713</v>
+      </c>
+      <c r="H15" t="n">
+        <v>288769974</v>
+      </c>
+      <c r="I15" t="n">
+        <v>185568326.24</v>
+      </c>
+      <c r="J15" t="n">
+        <v>474338300.24</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-103201647.76</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4855222931.5</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002679.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>福建金森</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-10.0257</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>228728943</v>
+      </c>
+      <c r="H16" t="n">
+        <v>22054761.02</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16036801</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38091562.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-6017960.02</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="M16" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2475438000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0115</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>867543886</v>
+      </c>
+      <c r="H17" t="n">
+        <v>62965493.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>131584724</v>
+      </c>
+      <c r="J17" t="n">
+        <v>194550217.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>68619230.05</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3195515256.08</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.0115</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>867543886</v>
+      </c>
+      <c r="H18" t="n">
+        <v>62965493.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>131584724</v>
+      </c>
+      <c r="J18" t="n">
+        <v>194550217.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>68619230.05</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3195515256.08</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002889.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-6.6709</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1010249346</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100143712.84</v>
+      </c>
+      <c r="I19" t="n">
+        <v>82505738.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>182649451.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-17637974.65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3691370098.26</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002889.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-6.6709</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1010249346</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100143712.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>82505738.19</v>
+      </c>
+      <c r="J20" t="n">
+        <v>182649451.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-17637974.65</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3691370098.26</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002929.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>润建股份</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1609985726</v>
+      </c>
+      <c r="H21" t="n">
+        <v>254271578.24</v>
+      </c>
+      <c r="I21" t="n">
+        <v>254460182.17</v>
+      </c>
+      <c r="J21" t="n">
+        <v>508731760.41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>188603.93</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11056692303.36</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002929.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>润建股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1843176572</v>
+      </c>
+      <c r="H22" t="n">
+        <v>303465505.64</v>
+      </c>
+      <c r="I22" t="n">
+        <v>353710891.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>657176397.14</v>
+      </c>
+      <c r="K22" t="n">
+        <v>50245385.86</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M22" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11056692303.36</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>003029.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.0041</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1124024246</v>
+      </c>
+      <c r="H23" t="n">
+        <v>117618564.81</v>
+      </c>
+      <c r="I23" t="n">
+        <v>135972755.46</v>
+      </c>
+      <c r="J23" t="n">
+        <v>253591320.27</v>
+      </c>
+      <c r="K23" t="n">
+        <v>18354190.65</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4672264641.18</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>003029.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.0041</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1298413609</v>
+      </c>
+      <c r="H24" t="n">
+        <v>124554350.81</v>
+      </c>
+      <c r="I24" t="n">
+        <v>141566478.46</v>
+      </c>
+      <c r="J24" t="n">
+        <v>266120829.27</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17012127.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4672264641.18</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>111012.SH</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>福新转债</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>405.951</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13.9169</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>8496868220</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1572564740</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1574309950</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3146874690</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1745210</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M25" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>127117.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>奥士转债</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>131840709</v>
+      </c>
+      <c r="H26" t="n">
+        <v>64981588.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>66300949</v>
+      </c>
+      <c r="J26" t="n">
+        <v>131282537.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1319360.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>300006.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-15.4853</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2329051164</v>
+      </c>
+      <c r="H27" t="n">
+        <v>422900453.65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>244504269.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>667404723.45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-178396183.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-7.66</v>
+      </c>
+      <c r="M27" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8182611959.5</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>300115.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>长盈精密</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19.9903</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2183228726</v>
+      </c>
+      <c r="H28" t="n">
+        <v>223767122.41</v>
+      </c>
+      <c r="I28" t="n">
+        <v>464599022.22</v>
+      </c>
+      <c r="J28" t="n">
+        <v>688366144.63</v>
+      </c>
+      <c r="K28" t="n">
+        <v>240831899.81</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="M28" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33486989639.43</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>300244.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>迪安诊断</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.989</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1831155095</v>
+      </c>
+      <c r="H29" t="n">
+        <v>291155171.05</v>
+      </c>
+      <c r="I29" t="n">
+        <v>436495312.06</v>
+      </c>
+      <c r="J29" t="n">
+        <v>727650483.11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>145340141.01</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="M29" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10926573949.69</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>300466.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>赛摩智能</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="G30" t="n">
+        <v>295925068</v>
+      </c>
+      <c r="H30" t="n">
+        <v>44285745.88</v>
+      </c>
+      <c r="I30" t="n">
+        <v>128993182</v>
+      </c>
+      <c r="J30" t="n">
+        <v>173278927.88</v>
+      </c>
+      <c r="K30" t="n">
+        <v>84707436.12</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="M30" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3979072736.64</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300716.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>*ST泉为</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-19.2405</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="G31" t="n">
+        <v>138929349</v>
+      </c>
+      <c r="H31" t="n">
+        <v>44595509.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25388807</v>
+      </c>
+      <c r="J31" t="n">
+        <v>69984316.09999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-19206702.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-13.82</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2041855200</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>301030.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>*ST仕净</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19.898</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>166425535</v>
+      </c>
+      <c r="H32" t="n">
+        <v>22287029</v>
+      </c>
+      <c r="I32" t="n">
+        <v>17137452</v>
+      </c>
+      <c r="J32" t="n">
+        <v>39424481</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-5149577</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="M32" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N32" t="n">
+        <v>949896837</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>301052.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>果麦文化</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-4.7353</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="G33" t="n">
+        <v>940681559</v>
+      </c>
+      <c r="H33" t="n">
+        <v>108880665.65</v>
+      </c>
+      <c r="I33" t="n">
+        <v>141889875.55</v>
+      </c>
+      <c r="J33" t="n">
+        <v>250770541.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>33009209.9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2598966927.66</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>元道退</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.2658</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5430860</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2280514</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1885851</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4166365</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-394663</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="M34" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="N34" t="n">
+        <v>59401795.44</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>301190.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>善水科技</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-18.9405</v>
+      </c>
+      <c r="F35" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1283312022</v>
+      </c>
+      <c r="H35" t="n">
+        <v>142712310.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>76688737.78</v>
+      </c>
+      <c r="J35" t="n">
+        <v>219401048.58</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-66023573.02</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="M35" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7930652940</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>301313.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1103340486</v>
+      </c>
+      <c r="H36" t="n">
+        <v>141078784.96</v>
+      </c>
+      <c r="I36" t="n">
+        <v>216542515.66</v>
+      </c>
+      <c r="J36" t="n">
+        <v>357621300.62</v>
+      </c>
+      <c r="K36" t="n">
+        <v>75463730.7</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3683698902</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>301313.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1103340486</v>
+      </c>
+      <c r="H37" t="n">
+        <v>141078784.96</v>
+      </c>
+      <c r="I37" t="n">
+        <v>216542515.66</v>
+      </c>
+      <c r="J37" t="n">
+        <v>357621300.62</v>
+      </c>
+      <c r="K37" t="n">
+        <v>75463730.7</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="M37" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3683698902</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>301313.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1970245093</v>
+      </c>
+      <c r="H38" t="n">
+        <v>209461884.36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>342307012.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>551768896.66</v>
+      </c>
+      <c r="K38" t="n">
+        <v>132845127.94</v>
+      </c>
+      <c r="L38" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="M38" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3683698902</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>301591.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>肯特股份</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>49</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.2231</v>
+      </c>
+      <c r="F39" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1066162966</v>
+      </c>
+      <c r="H39" t="n">
+        <v>146328000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>108132610.21</v>
+      </c>
+      <c r="J39" t="n">
+        <v>254460610.21</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-38195389.79</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="M39" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2190042652</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>301660.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>粤芯半导体</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-13.5257</v>
+      </c>
+      <c r="F40" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3093268969</v>
+      </c>
+      <c r="H40" t="n">
+        <v>245665401.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>173350698.05</v>
+      </c>
+      <c r="J40" t="n">
+        <v>419016099.85</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-72314703.75</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M40" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7450058567.84</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>600127.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="F41" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2726696970</v>
+      </c>
+      <c r="H41" t="n">
+        <v>345767371.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>368676704.01</v>
+      </c>
+      <c r="J41" t="n">
+        <v>714444075.61</v>
+      </c>
+      <c r="K41" t="n">
+        <v>22909332.41</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M41" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8497209806.32</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>600148.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>长春一东</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9.994400000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22</v>
+      </c>
+      <c r="G42" t="n">
+        <v>599953035</v>
+      </c>
+      <c r="H42" t="n">
+        <v>64239530.33</v>
+      </c>
+      <c r="I42" t="n">
+        <v>37395048.72</v>
+      </c>
+      <c r="J42" t="n">
+        <v>101634579.05</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-26844481.61</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="M42" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2787874065</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600178.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>东安动力</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.0177</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G43" t="n">
+        <v>94031737</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5855038</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32313158</v>
+      </c>
+      <c r="J43" t="n">
+        <v>38168196</v>
+      </c>
+      <c r="K43" t="n">
+        <v>26458120</v>
+      </c>
+      <c r="L43" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5788969158.01</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.9074</v>
+      </c>
+      <c r="F44" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1281306440</v>
+      </c>
+      <c r="H44" t="n">
+        <v>79654847</v>
+      </c>
+      <c r="I44" t="n">
+        <v>123123538</v>
+      </c>
+      <c r="J44" t="n">
+        <v>202778385</v>
+      </c>
+      <c r="K44" t="n">
+        <v>43468691</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M44" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4008394806.3</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600241.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.9074</v>
+      </c>
+      <c r="F45" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1281306440</v>
+      </c>
+      <c r="H45" t="n">
+        <v>79654847</v>
+      </c>
+      <c r="I45" t="n">
+        <v>123123538</v>
+      </c>
+      <c r="J45" t="n">
+        <v>202778385</v>
+      </c>
+      <c r="K45" t="n">
+        <v>43468691</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M45" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4008394806.3</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600267.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>海正药业</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.0332</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G46" t="n">
+        <v>769799338</v>
+      </c>
+      <c r="H46" t="n">
+        <v>112652452.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>222484641.98</v>
+      </c>
+      <c r="J46" t="n">
+        <v>335137094.18</v>
+      </c>
+      <c r="K46" t="n">
+        <v>109832189.78</v>
+      </c>
+      <c r="L46" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="M46" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="N46" t="n">
+        <v>15662210713.92</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600267.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>海正药业</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10.0332</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G47" t="n">
+        <v>888159591</v>
+      </c>
+      <c r="H47" t="n">
+        <v>115332184.2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>222484641.98</v>
+      </c>
+      <c r="J47" t="n">
+        <v>337816826.18</v>
+      </c>
+      <c r="K47" t="n">
+        <v>107152457.78</v>
+      </c>
+      <c r="L47" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="M47" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="N47" t="n">
+        <v>15662210713.92</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600302.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ST标准</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10.0486</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G48" t="n">
+        <v>44617772</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8535053</v>
+      </c>
+      <c r="I48" t="n">
+        <v>11198981</v>
+      </c>
+      <c r="J48" t="n">
+        <v>19734034</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2663928</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M48" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2349406569.16</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600403.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>大有能源</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-9.195399999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="G49" t="n">
+        <v>535343348</v>
+      </c>
+      <c r="H49" t="n">
+        <v>32878254.08</v>
+      </c>
+      <c r="I49" t="n">
+        <v>36929248.35</v>
+      </c>
+      <c r="J49" t="n">
+        <v>69807502.43000001</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4050994.27</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M49" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="N49" t="n">
+        <v>15109934380.64</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>601091.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>沈鼓集团</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.3405</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="G50" t="n">
+        <v>864455487</v>
+      </c>
+      <c r="H50" t="n">
+        <v>52101051.54</v>
+      </c>
+      <c r="I50" t="n">
+        <v>64650447.01</v>
+      </c>
+      <c r="J50" t="n">
+        <v>116751498.55</v>
+      </c>
+      <c r="K50" t="n">
+        <v>12549395.47</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M50" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3990984139.8</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>601811.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-9.238099999999999</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1283994319</v>
+      </c>
+      <c r="H51" t="n">
+        <v>140019824.52</v>
+      </c>
+      <c r="I51" t="n">
+        <v>139709123.56</v>
+      </c>
+      <c r="J51" t="n">
+        <v>279728948.08</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-310700.96</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M51" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="N51" t="n">
+        <v>18205870661</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>603096.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>新经典</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-8.571400000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1855525674</v>
+      </c>
+      <c r="H52" t="n">
+        <v>123325038.77</v>
+      </c>
+      <c r="I52" t="n">
+        <v>115537034.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>238862073.37</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-7788004.17</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M52" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2665174302.72</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>603105.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>芯能科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-9.950699999999999</v>
+      </c>
+      <c r="F53" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="G53" t="n">
+        <v>558863400</v>
+      </c>
+      <c r="H53" t="n">
+        <v>81044647.31999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>33821296</v>
+      </c>
+      <c r="J53" t="n">
+        <v>114865943.32</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-47223351.32</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="M53" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4570103967.5</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>603119.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>浙江荣泰</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>50.46</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.0065</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1272920550</v>
+      </c>
+      <c r="H54" t="n">
+        <v>175566770.01</v>
+      </c>
+      <c r="I54" t="n">
+        <v>255215048.11</v>
+      </c>
+      <c r="J54" t="n">
+        <v>430781818.12</v>
+      </c>
+      <c r="K54" t="n">
+        <v>79648278.09999999</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="M54" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="N54" t="n">
+        <v>23860513985.28</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603193.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>润本股份</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-8.6364</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G55" t="n">
+        <v>210897268</v>
+      </c>
+      <c r="H55" t="n">
+        <v>68968317.05</v>
+      </c>
+      <c r="I55" t="n">
+        <v>53387184</v>
+      </c>
+      <c r="J55" t="n">
+        <v>122355501.05</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-15581133.05</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="M55" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7319093050.26</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603466.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>风语筑</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.2344</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1985197244</v>
+      </c>
+      <c r="H56" t="n">
+        <v>290668424.64</v>
+      </c>
+      <c r="I56" t="n">
+        <v>265331090.96</v>
+      </c>
+      <c r="J56" t="n">
+        <v>555999515.6</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-25337333.68</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M56" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="N56" t="n">
+        <v>8464458847.72</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603626.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>科森科技</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.9955</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1698422615</v>
+      </c>
+      <c r="H57" t="n">
+        <v>237332365.22</v>
+      </c>
+      <c r="I57" t="n">
+        <v>247078086.26</v>
+      </c>
+      <c r="J57" t="n">
+        <v>484410451.48</v>
+      </c>
+      <c r="K57" t="n">
+        <v>9745721.039999999</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M57" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="N57" t="n">
+        <v>13555710826.7</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603636.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0248</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="G58" t="n">
+        <v>664860357</v>
+      </c>
+      <c r="H58" t="n">
+        <v>81744828.42</v>
+      </c>
+      <c r="I58" t="n">
+        <v>63815496</v>
+      </c>
+      <c r="J58" t="n">
+        <v>145560324.42</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-17929332.42</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5159405049.47</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603636.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.0248</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1403597664</v>
+      </c>
+      <c r="H59" t="n">
+        <v>132219669.35</v>
+      </c>
+      <c r="I59" t="n">
+        <v>104618334.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>236838003.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-27601334.75</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M59" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5159405049.47</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603696.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>安记食品</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10.0324</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G60" t="n">
+        <v>137507655</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16657074</v>
+      </c>
+      <c r="I60" t="n">
+        <v>50200664</v>
+      </c>
+      <c r="J60" t="n">
+        <v>66857738</v>
+      </c>
+      <c r="K60" t="n">
+        <v>33543590</v>
+      </c>
+      <c r="L60" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="M60" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3198720000</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603999.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-9.946899999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>380053414</v>
+      </c>
+      <c r="H61" t="n">
+        <v>79443772</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31176594</v>
+      </c>
+      <c r="J61" t="n">
+        <v>110620366</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-48267178</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3911040000</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>605488.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>福莱新材</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.0106</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G62" t="n">
+        <v>371807587</v>
+      </c>
+      <c r="H62" t="n">
+        <v>47973795.49</v>
+      </c>
+      <c r="I62" t="n">
+        <v>86153417.61</v>
+      </c>
+      <c r="J62" t="n">
+        <v>134127213.1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>38179622.12</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M62" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="N62" t="n">
+        <v>9249853332.51</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>688004.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>博汇科技</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="E63" t="n">
+        <v>20.0065</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="G63" t="n">
+        <v>353307100</v>
+      </c>
+      <c r="H63" t="n">
+        <v>61290791.79</v>
+      </c>
+      <c r="I63" t="n">
+        <v>58470077.3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>119760869.09</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-2820714.49</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2978472720</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>688018.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>乐鑫科技</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>140.72</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.8577</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2457680400</v>
+      </c>
+      <c r="H64" t="n">
+        <v>372999009.48</v>
+      </c>
+      <c r="I64" t="n">
+        <v>630213628.3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1003212637.78</v>
+      </c>
+      <c r="K64" t="n">
+        <v>257214618.82</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="M64" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="N64" t="n">
+        <v>32982560243.92</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>688071.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>华